--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="830">
   <si>
     <t>_Id</t>
   </si>
@@ -2098,97 +2098,97 @@
     <t>10114</t>
   </si>
   <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>地狱土城外</t>
+  </si>
+  <si>
+    <t>1200-1</t>
+  </si>
+  <si>
+    <t>地狱狼爪</t>
+  </si>
+  <si>
+    <t>202003,300091,104,504,210045</t>
+  </si>
+  <si>
+    <t>10115</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>地狱土城</t>
+  </si>
+  <si>
+    <t>1200-2</t>
+  </si>
+  <si>
+    <t>地狱虫皮</t>
+  </si>
+  <si>
+    <t>202003,300091,104,504,210046</t>
+  </si>
+  <si>
+    <t>10116</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>地狱龙城外</t>
+  </si>
+  <si>
+    <t>1200-3</t>
+  </si>
+  <si>
+    <t>地狱鹰羽</t>
+  </si>
+  <si>
+    <t>202003,300091,104,504,210047</t>
+  </si>
+  <si>
+    <t>10117</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>地狱龙城</t>
+  </si>
+  <si>
+    <t>1200-4</t>
+  </si>
+  <si>
+    <t>地狱虫角</t>
+  </si>
+  <si>
+    <t>202003,300091,104,504,210048</t>
+  </si>
+  <si>
+    <t>10118</t>
+  </si>
+  <si>
+    <t>1119</t>
+  </si>
+  <si>
+    <t>地狱圣域</t>
+  </si>
+  <si>
+    <t>1200-5</t>
+  </si>
+  <si>
+    <t>地狱蜈膏</t>
+  </si>
+  <si>
+    <t>202003,300091,104,504,210049</t>
+  </si>
+  <si>
+    <t>10119</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>地狱土城外</t>
-  </si>
-  <si>
-    <t>1200-1</t>
-  </si>
-  <si>
-    <t>地狱狼爪</t>
-  </si>
-  <si>
-    <t>202003,300091,104,504,210045</t>
-  </si>
-  <si>
-    <t>10115</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>地狱土城</t>
-  </si>
-  <si>
-    <t>1200-2</t>
-  </si>
-  <si>
-    <t>地狱虫皮</t>
-  </si>
-  <si>
-    <t>202003,300091,104,504,210046</t>
-  </si>
-  <si>
-    <t>10116</t>
-  </si>
-  <si>
-    <t>1117</t>
-  </si>
-  <si>
-    <t>地狱龙城外</t>
-  </si>
-  <si>
-    <t>1200-3</t>
-  </si>
-  <si>
-    <t>地狱鹰羽</t>
-  </si>
-  <si>
-    <t>202003,300091,104,504,210047</t>
-  </si>
-  <si>
-    <t>10117</t>
-  </si>
-  <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>地狱龙城</t>
-  </si>
-  <si>
-    <t>1200-4</t>
-  </si>
-  <si>
-    <t>地狱虫角</t>
-  </si>
-  <si>
-    <t>202003,300091,104,504,210048</t>
-  </si>
-  <si>
-    <t>10118</t>
-  </si>
-  <si>
-    <t>1119</t>
-  </si>
-  <si>
-    <t>地狱圣域</t>
-  </si>
-  <si>
-    <t>1200-5</t>
-  </si>
-  <si>
-    <t>地狱蜈膏</t>
-  </si>
-  <si>
-    <t>202003,300091,104,504,210049</t>
-  </si>
-  <si>
-    <t>10119</t>
   </si>
   <si>
     <t>1120</t>
@@ -2727,12 +2727,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7237,18 +7237,12 @@
         <v>678</v>
       </c>
     </row>
-    <row r="121" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A121" s="1" t="s">
+    <row r="121" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C121" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>681</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
@@ -7257,36 +7251,30 @@
         <v>4</v>
       </c>
       <c r="G121" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="H121" s="1" t="s">
         <v>682</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>683</v>
       </c>
       <c r="I121" s="1">
         <v>0</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="K121" s="7" t="s">
         <v>623</v>
       </c>
       <c r="L121" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="122" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C122" s="1" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="122" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A122" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C122" s="1" t="s">
+      <c r="D122" s="1" t="s">
         <v>686</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>687</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
@@ -7295,36 +7283,30 @@
         <v>4</v>
       </c>
       <c r="G122" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="H122" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>689</v>
       </c>
       <c r="I122" s="1">
         <v>0</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K122" s="7" t="s">
         <v>623</v>
       </c>
       <c r="L122" s="1" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="123" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C123" s="1" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="123" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A123" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C123" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>692</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>693</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
@@ -7333,36 +7315,30 @@
         <v>4</v>
       </c>
       <c r="G123" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="H123" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="I123" s="1">
         <v>0</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K123" s="7" t="s">
         <v>623</v>
       </c>
       <c r="L123" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="124" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C124" s="1" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="124" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A124" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C124" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>698</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>699</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
@@ -7371,36 +7347,30 @@
         <v>4</v>
       </c>
       <c r="G124" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="H124" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>701</v>
       </c>
       <c r="I124" s="1">
         <v>0</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="K124" s="7" t="s">
         <v>623</v>
       </c>
       <c r="L124" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="125" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C125" s="1" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="125" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A125" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C125" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>704</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>705</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
@@ -7409,30 +7379,30 @@
         <v>4</v>
       </c>
       <c r="G125" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="H125" s="1" t="s">
         <v>706</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>707</v>
       </c>
       <c r="I125" s="1">
         <v>0</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="K125" s="7" t="s">
         <v>623</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A126" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>710</v>
@@ -7467,10 +7437,10 @@
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A127" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>716</v>
@@ -7505,10 +7475,10 @@
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A128" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>722</v>
@@ -7543,10 +7513,10 @@
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A129" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>728</v>
@@ -7581,10 +7551,10 @@
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A130" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>734</v>
@@ -7619,10 +7589,10 @@
     </row>
     <row r="131" customHeight="1" spans="1:12">
       <c r="A131" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>740</v>
@@ -7657,10 +7627,10 @@
     </row>
     <row r="132" customHeight="1" spans="1:12">
       <c r="A132" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>746</v>
@@ -7695,10 +7665,10 @@
     </row>
     <row r="133" customHeight="1" spans="1:12">
       <c r="A133" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>752</v>
@@ -7733,10 +7703,10 @@
     </row>
     <row r="134" customHeight="1" spans="1:12">
       <c r="A134" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>758</v>
@@ -7771,10 +7741,10 @@
     </row>
     <row r="135" customHeight="1" spans="1:12">
       <c r="A135" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>764</v>
@@ -7809,10 +7779,10 @@
     </row>
     <row r="136" customHeight="1" spans="1:12">
       <c r="A136" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>770</v>
@@ -7847,10 +7817,10 @@
     </row>
     <row r="137" customHeight="1" spans="1:12">
       <c r="A137" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>776</v>
@@ -7885,10 +7855,10 @@
     </row>
     <row r="138" customHeight="1" spans="1:12">
       <c r="A138" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>782</v>
@@ -7923,10 +7893,10 @@
     </row>
     <row r="139" customHeight="1" spans="1:12">
       <c r="A139" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>788</v>
@@ -7961,10 +7931,10 @@
     </row>
     <row r="140" customHeight="1" spans="1:12">
       <c r="A140" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>794</v>
@@ -7999,10 +7969,10 @@
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A141" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>800</v>
@@ -8037,10 +8007,10 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A142" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>806</v>
@@ -8075,10 +8045,10 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A143" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>812</v>
@@ -8113,10 +8083,10 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A144" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>818</v>
@@ -8151,10 +8121,10 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A145" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>824</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="831">
   <si>
     <t>_Id</t>
   </si>
@@ -115,7 +115,7 @@
     <t>1000</t>
   </si>
   <si>
-    <t>银杏小村</t>
+    <t>新手小村</t>
   </si>
   <si>
     <t>10</t>
@@ -133,7 +133,7 @@
     <t>1001</t>
   </si>
   <si>
-    <t>银杏村外</t>
+    <t>新手村外</t>
   </si>
   <si>
     <t>20</t>
@@ -154,7 +154,7 @@
     <t>1002</t>
   </si>
   <si>
-    <t>比奇城外</t>
+    <t>自然农场</t>
   </si>
   <si>
     <t>30</t>
@@ -169,7 +169,7 @@
     <t>1003</t>
   </si>
   <si>
-    <t>比奇城</t>
+    <t>老兵之城</t>
   </si>
   <si>
     <t>40</t>
@@ -190,7 +190,7 @@
     <t>1004</t>
   </si>
   <si>
-    <t>沃玛森林</t>
+    <t>兽人森林</t>
   </si>
   <si>
     <t>50</t>
@@ -205,7 +205,7 @@
     <t>1005</t>
   </si>
   <si>
-    <t>自然洞穴</t>
+    <t>蝙蝠洞穴</t>
   </si>
   <si>
     <t>60</t>
@@ -241,7 +241,7 @@
     <t>1007</t>
   </si>
   <si>
-    <t>连接通道</t>
+    <t>黑暗通道</t>
   </si>
   <si>
     <t>80</t>
@@ -271,7 +271,7 @@
     <t>1009</t>
   </si>
   <si>
-    <t>毒蛇蛇谷</t>
+    <t>毒蛇谷</t>
   </si>
   <si>
     <t>100</t>
@@ -286,7 +286,7 @@
     <t>1010</t>
   </si>
   <si>
-    <t>土城城外</t>
+    <t>野狼山</t>
   </si>
   <si>
     <t>110</t>
@@ -307,7 +307,7 @@
     <t>1011</t>
   </si>
   <si>
-    <t>土城</t>
+    <t>沙虫洞</t>
   </si>
   <si>
     <t>120</t>
@@ -322,7 +322,7 @@
     <t>1012</t>
   </si>
   <si>
-    <t>龙城城外</t>
+    <t>鹰愁涧</t>
   </si>
   <si>
     <t>130</t>
@@ -337,7 +337,7 @@
     <t>1013</t>
   </si>
   <si>
-    <t>龙城</t>
+    <t>角虫谷</t>
   </si>
   <si>
     <t>140</t>
@@ -352,7 +352,7 @@
     <t>1014</t>
   </si>
   <si>
-    <t>幽冥圣域</t>
+    <t>蜈蚣洞</t>
   </si>
   <si>
     <t>150</t>
@@ -373,7 +373,7 @@
     <t>1015</t>
   </si>
   <si>
-    <t>死亡棺材</t>
+    <t>钳虫洞</t>
   </si>
   <si>
     <t>160</t>
@@ -388,7 +388,7 @@
     <t>1016</t>
   </si>
   <si>
-    <t>一线天</t>
+    <t>蠕虫洞</t>
   </si>
   <si>
     <t>170</t>
@@ -403,7 +403,7 @@
     <t>1017</t>
   </si>
   <si>
-    <t>石墓大厅</t>
+    <t>魔猪大厅</t>
   </si>
   <si>
     <t>180</t>
@@ -418,7 +418,7 @@
     <t>1018</t>
   </si>
   <si>
-    <t>石墓阵</t>
+    <t>魔猪教堂</t>
   </si>
   <si>
     <t>190</t>
@@ -448,7 +448,7 @@
     <t>1020</t>
   </si>
   <si>
-    <t>沃玛禁地</t>
+    <t>魔族禁地</t>
   </si>
   <si>
     <t>210</t>
@@ -469,7 +469,7 @@
     <t>1021</t>
   </si>
   <si>
-    <t>沃玛大殿</t>
+    <t>魔族神殿</t>
   </si>
   <si>
     <t>220</t>
@@ -484,7 +484,7 @@
     <t>1022</t>
   </si>
   <si>
-    <t>祖玛禁地</t>
+    <t>邪魔禁地</t>
   </si>
   <si>
     <t>230</t>
@@ -499,7 +499,7 @@
     <t>1023</t>
   </si>
   <si>
-    <t>祖玛大殿</t>
+    <t>邪魔神殿</t>
   </si>
   <si>
     <t>240</t>
@@ -514,7 +514,7 @@
     <t>1024</t>
   </si>
   <si>
-    <t>封魔殿</t>
+    <t>封魔神殿</t>
   </si>
   <si>
     <t>250</t>
@@ -529,7 +529,7 @@
     <t>1025</t>
   </si>
   <si>
-    <t>烈焰殿</t>
+    <t>烈焰神殿</t>
   </si>
   <si>
     <t>260</t>
@@ -544,6 +544,9 @@
     <t>1026</t>
   </si>
   <si>
+    <t>封邪神殿</t>
+  </si>
+  <si>
     <t>270</t>
   </si>
   <si>
@@ -556,7 +559,7 @@
     <t>1027</t>
   </si>
   <si>
-    <t>尸魔洞</t>
+    <t>尸魔神殿</t>
   </si>
   <si>
     <t>280</t>
@@ -571,7 +574,7 @@
     <t>1028</t>
   </si>
   <si>
-    <t>骨魔洞</t>
+    <t>骨魔神殿</t>
   </si>
   <si>
     <t>290</t>
@@ -586,7 +589,7 @@
     <t>1029</t>
   </si>
   <si>
-    <t>牛魔神殿</t>
+    <t>魔牛神殿</t>
   </si>
   <si>
     <t>300</t>
@@ -601,7 +604,7 @@
     <t>1030</t>
   </si>
   <si>
-    <t>赤月峡谷</t>
+    <t>水龙谷</t>
   </si>
   <si>
     <t>310</t>
@@ -616,7 +619,7 @@
     <t>1031</t>
   </si>
   <si>
-    <t>赤月祭坛</t>
+    <t>土龙谷</t>
   </si>
   <si>
     <t>320</t>
@@ -631,7 +634,7 @@
     <t>1032</t>
   </si>
   <si>
-    <t>赤月魔巢</t>
+    <t>毒龙谷</t>
   </si>
   <si>
     <t>330</t>
@@ -646,7 +649,7 @@
     <t>1033</t>
   </si>
   <si>
-    <t>魔龙城</t>
+    <t>火龙谷</t>
   </si>
   <si>
     <t>340</t>
@@ -661,7 +664,7 @@
     <t>1034</t>
   </si>
   <si>
-    <t>火龙殿</t>
+    <t>冰龙谷</t>
   </si>
   <si>
     <t>350</t>
@@ -712,7 +715,7 @@
     <t>1037</t>
   </si>
   <si>
-    <t>幻影城外</t>
+    <t>幻影农场</t>
   </si>
   <si>
     <t>380</t>
@@ -757,7 +760,7 @@
     <t>1040</t>
   </si>
   <si>
-    <t>幻影洞穴</t>
+    <t>幻影蝠洞</t>
   </si>
   <si>
     <t>410</t>
@@ -838,7 +841,7 @@
     <t>1045</t>
   </si>
   <si>
-    <t>幻影土城外</t>
+    <t>幻影狼山</t>
   </si>
   <si>
     <t>460</t>
@@ -859,7 +862,7 @@
     <t>1046</t>
   </si>
   <si>
-    <t>幻影土城</t>
+    <t>幻影沙洞</t>
   </si>
   <si>
     <t>470</t>
@@ -874,7 +877,7 @@
     <t>1047</t>
   </si>
   <si>
-    <t>幻影龙城外</t>
+    <t>幻影鹰崖</t>
   </si>
   <si>
     <t>480</t>
@@ -889,7 +892,7 @@
     <t>1048</t>
   </si>
   <si>
-    <t>幻影龙城</t>
+    <t>幻影虫谷</t>
   </si>
   <si>
     <t>490</t>
@@ -904,7 +907,7 @@
     <t>1049</t>
   </si>
   <si>
-    <t>幻影圣域</t>
+    <t>幻影虫洞</t>
   </si>
   <si>
     <t>500</t>
@@ -919,7 +922,7 @@
     <t>1050</t>
   </si>
   <si>
-    <t>幻影棺材</t>
+    <t>幻影虫穴</t>
   </si>
   <si>
     <t>510</t>
@@ -940,7 +943,7 @@
     <t>1051</t>
   </si>
   <si>
-    <t>幻影一线天</t>
+    <t>幻影虫巢</t>
   </si>
   <si>
     <t>520</t>
@@ -958,7 +961,7 @@
     <t>1052</t>
   </si>
   <si>
-    <t>幻影石墓</t>
+    <t>幻影魔猪厅</t>
   </si>
   <si>
     <t>530</t>
@@ -976,7 +979,7 @@
     <t>1053</t>
   </si>
   <si>
-    <t>幻影猪洞</t>
+    <t>幻影魔猪殿</t>
   </si>
   <si>
     <t>540</t>
@@ -1012,7 +1015,7 @@
     <t>1055</t>
   </si>
   <si>
-    <t>幻影沃玛禁地</t>
+    <t>幻影魔禁地</t>
   </si>
   <si>
     <t>560</t>
@@ -1033,7 +1036,7 @@
     <t>1056</t>
   </si>
   <si>
-    <t>幻影沃玛大殿</t>
+    <t>幻影魔神殿</t>
   </si>
   <si>
     <t>570</t>
@@ -1051,7 +1054,7 @@
     <t>1057</t>
   </si>
   <si>
-    <t>幻影祖玛禁地</t>
+    <t>幻影邪禁地</t>
   </si>
   <si>
     <t>580</t>
@@ -1069,7 +1072,7 @@
     <t>1058</t>
   </si>
   <si>
-    <t>幻影祖玛大殿</t>
+    <t>幻影邪魔殿</t>
   </si>
   <si>
     <t>590</t>
@@ -1105,7 +1108,7 @@
     <t>1060</t>
   </si>
   <si>
-    <t>幻影烈焰</t>
+    <t>幻影烈焰殿</t>
   </si>
   <si>
     <t>610</t>
@@ -1123,7 +1126,7 @@
     <t>1061</t>
   </si>
   <si>
-    <t>幻影封魔</t>
+    <t>幻影封邪殿</t>
   </si>
   <si>
     <t>620</t>
@@ -1141,7 +1144,7 @@
     <t>1062</t>
   </si>
   <si>
-    <t>幻影尸魔</t>
+    <t>幻影尸魔殿</t>
   </si>
   <si>
     <t>630</t>
@@ -1159,7 +1162,7 @@
     <t>1063</t>
   </si>
   <si>
-    <t>幻影骨魔</t>
+    <t>幻影骨魔殿</t>
   </si>
   <si>
     <t>640</t>
@@ -1177,7 +1180,7 @@
     <t>1064</t>
   </si>
   <si>
-    <t>幻影牛魔</t>
+    <t>幻影魔牛殿</t>
   </si>
   <si>
     <t>650</t>
@@ -1195,7 +1198,7 @@
     <t>1065</t>
   </si>
   <si>
-    <t>幻影峡谷</t>
+    <t>幻影水龙谷</t>
   </si>
   <si>
     <t>660</t>
@@ -1213,7 +1216,7 @@
     <t>1066</t>
   </si>
   <si>
-    <t>幻影祭坛</t>
+    <t>幻影土龙谷</t>
   </si>
   <si>
     <t>670</t>
@@ -1231,7 +1234,7 @@
     <t>1067</t>
   </si>
   <si>
-    <t>幻影魔巢</t>
+    <t>幻影毒龙谷</t>
   </si>
   <si>
     <t>680</t>
@@ -1249,7 +1252,7 @@
     <t>1068</t>
   </si>
   <si>
-    <t>幻影魔龙城</t>
+    <t>幻影火龙谷</t>
   </si>
   <si>
     <t>690</t>
@@ -1267,7 +1270,7 @@
     <t>1069</t>
   </si>
   <si>
-    <t>幻影火龙殿</t>
+    <t>幻影冰龙谷</t>
   </si>
   <si>
     <t>700</t>
@@ -1321,7 +1324,7 @@
     <t>1072</t>
   </si>
   <si>
-    <t>噩梦城外</t>
+    <t>噩梦农场</t>
   </si>
   <si>
     <t>750-3</t>
@@ -1375,7 +1378,7 @@
     <t>1075</t>
   </si>
   <si>
-    <t>噩梦洞穴</t>
+    <t>噩梦蝠洞</t>
   </si>
   <si>
     <t>800-1</t>
@@ -1468,7 +1471,7 @@
     <t>1080</t>
   </si>
   <si>
-    <t>噩梦土城外</t>
+    <t>噩梦狼山</t>
   </si>
   <si>
     <t>850-1</t>
@@ -1486,7 +1489,7 @@
     <t>1081</t>
   </si>
   <si>
-    <t>噩梦土城</t>
+    <t>噩梦沙洞</t>
   </si>
   <si>
     <t>850-2</t>
@@ -1504,7 +1507,7 @@
     <t>1082</t>
   </si>
   <si>
-    <t>噩梦龙城外</t>
+    <t>噩梦鹰崖</t>
   </si>
   <si>
     <t>850-3</t>
@@ -1522,7 +1525,7 @@
     <t>1083</t>
   </si>
   <si>
-    <t>噩梦龙城</t>
+    <t>噩梦虫谷</t>
   </si>
   <si>
     <t>850-4</t>
@@ -1540,7 +1543,7 @@
     <t>1084</t>
   </si>
   <si>
-    <t>噩梦圣域</t>
+    <t>噩梦虫洞</t>
   </si>
   <si>
     <t>850-5</t>
@@ -1558,7 +1561,7 @@
     <t>1085</t>
   </si>
   <si>
-    <t>噩梦棺材</t>
+    <t>噩梦虫穴</t>
   </si>
   <si>
     <t>900-1</t>
@@ -1576,7 +1579,7 @@
     <t>1086</t>
   </si>
   <si>
-    <t>噩梦一线天</t>
+    <t>噩梦虫巢</t>
   </si>
   <si>
     <t>900-2</t>
@@ -1594,7 +1597,7 @@
     <t>1087</t>
   </si>
   <si>
-    <t>噩梦石墓</t>
+    <t>噩梦魔猪厅</t>
   </si>
   <si>
     <t>900-3</t>
@@ -1612,7 +1615,7 @@
     <t>1088</t>
   </si>
   <si>
-    <t>噩梦猪洞</t>
+    <t>噩梦魔猪殿</t>
   </si>
   <si>
     <t>900-4</t>
@@ -1648,7 +1651,7 @@
     <t>1090</t>
   </si>
   <si>
-    <t>噩梦沃玛禁地</t>
+    <t>噩梦魔禁地</t>
   </si>
   <si>
     <t>950-1</t>
@@ -1666,7 +1669,7 @@
     <t>1091</t>
   </si>
   <si>
-    <t>噩梦沃玛大殿</t>
+    <t>噩梦魔神殿</t>
   </si>
   <si>
     <t>950-2</t>
@@ -1684,7 +1687,7 @@
     <t>1092</t>
   </si>
   <si>
-    <t>噩梦祖玛禁地</t>
+    <t>噩梦邪禁地</t>
   </si>
   <si>
     <t>950-3</t>
@@ -1702,7 +1705,7 @@
     <t>1093</t>
   </si>
   <si>
-    <t>噩梦祖玛大殿</t>
+    <t>噩梦邪魔殿</t>
   </si>
   <si>
     <t>950-4</t>
@@ -1738,7 +1741,7 @@
     <t>1095</t>
   </si>
   <si>
-    <t>噩梦烈焰</t>
+    <t>噩梦烈焰殿</t>
   </si>
   <si>
     <t>1000-1</t>
@@ -1756,7 +1759,7 @@
     <t>1096</t>
   </si>
   <si>
-    <t>噩梦封魔</t>
+    <t>噩梦封邪殿</t>
   </si>
   <si>
     <t>1000-2</t>
@@ -1774,7 +1777,7 @@
     <t>1097</t>
   </si>
   <si>
-    <t>噩梦尸魔</t>
+    <t>噩梦尸魔殿</t>
   </si>
   <si>
     <t>1000-3</t>
@@ -1792,7 +1795,7 @@
     <t>1098</t>
   </si>
   <si>
-    <t>噩梦骨魔</t>
+    <t>噩梦骨魔殿</t>
   </si>
   <si>
     <t>1000-4</t>
@@ -1810,7 +1813,7 @@
     <t>1099</t>
   </si>
   <si>
-    <t>噩梦牛魔</t>
+    <t>噩梦魔牛殿</t>
   </si>
   <si>
     <t>1000-5</t>
@@ -1828,7 +1831,7 @@
     <t>1100</t>
   </si>
   <si>
-    <t>噩梦峡谷</t>
+    <t>噩梦水龙谷</t>
   </si>
   <si>
     <t>1050-1</t>
@@ -1846,7 +1849,7 @@
     <t>1101</t>
   </si>
   <si>
-    <t>噩梦祭坛</t>
+    <t>噩梦土龙谷</t>
   </si>
   <si>
     <t>1050-2</t>
@@ -1864,7 +1867,7 @@
     <t>1102</t>
   </si>
   <si>
-    <t>噩梦魔巢</t>
+    <t>噩梦毒龙谷</t>
   </si>
   <si>
     <t>1050-3</t>
@@ -1882,7 +1885,7 @@
     <t>1103</t>
   </si>
   <si>
-    <t>噩梦魔龙</t>
+    <t>噩梦火龙谷</t>
   </si>
   <si>
     <t>1050-4</t>
@@ -1900,7 +1903,7 @@
     <t>1104</t>
   </si>
   <si>
-    <t>噩梦火龙</t>
+    <t>噩梦冰龙谷</t>
   </si>
   <si>
     <t>1050-5</t>
@@ -1957,7 +1960,7 @@
     <t>1107</t>
   </si>
   <si>
-    <t>地狱城外</t>
+    <t>地狱农场</t>
   </si>
   <si>
     <t>1100-3</t>
@@ -2011,7 +2014,7 @@
     <t>1110</t>
   </si>
   <si>
-    <t>地狱洞穴</t>
+    <t>地狱蝠洞</t>
   </si>
   <si>
     <t>1150-1</t>
@@ -2101,7 +2104,7 @@
     <t>1115</t>
   </si>
   <si>
-    <t>地狱土城外</t>
+    <t>地狱狼山</t>
   </si>
   <si>
     <t>1200-1</t>
@@ -2119,7 +2122,7 @@
     <t>1116</t>
   </si>
   <si>
-    <t>地狱土城</t>
+    <t>地狱沙洞</t>
   </si>
   <si>
     <t>1200-2</t>
@@ -2137,7 +2140,7 @@
     <t>1117</t>
   </si>
   <si>
-    <t>地狱龙城外</t>
+    <t>地狱鹰崖</t>
   </si>
   <si>
     <t>1200-3</t>
@@ -2155,7 +2158,7 @@
     <t>1118</t>
   </si>
   <si>
-    <t>地狱龙城</t>
+    <t>地狱虫谷</t>
   </si>
   <si>
     <t>1200-4</t>
@@ -2173,7 +2176,7 @@
     <t>1119</t>
   </si>
   <si>
-    <t>地狱圣域</t>
+    <t>地狱虫洞</t>
   </si>
   <si>
     <t>1200-5</t>
@@ -2194,7 +2197,7 @@
     <t>1120</t>
   </si>
   <si>
-    <t>地狱棺材</t>
+    <t>地狱虫穴</t>
   </si>
   <si>
     <t>1250-1</t>
@@ -2212,7 +2215,7 @@
     <t>1121</t>
   </si>
   <si>
-    <t>地狱一线天</t>
+    <t>地狱虫巢</t>
   </si>
   <si>
     <t>1250-2</t>
@@ -2230,7 +2233,7 @@
     <t>1122</t>
   </si>
   <si>
-    <t>地狱石墓</t>
+    <t>地狱魔猪厅</t>
   </si>
   <si>
     <t>1250-3</t>
@@ -2248,7 +2251,7 @@
     <t>1123</t>
   </si>
   <si>
-    <t>地狱猪洞</t>
+    <t>地狱魔猪殿</t>
   </si>
   <si>
     <t>1250-4</t>
@@ -2284,7 +2287,7 @@
     <t>1125</t>
   </si>
   <si>
-    <t>地狱沃玛禁地</t>
+    <t>地狱魔禁地</t>
   </si>
   <si>
     <t>1300-1</t>
@@ -2302,7 +2305,7 @@
     <t>1126</t>
   </si>
   <si>
-    <t>地狱沃玛大殿</t>
+    <t>地狱魔神殿</t>
   </si>
   <si>
     <t>1300-2</t>
@@ -2320,7 +2323,7 @@
     <t>1127</t>
   </si>
   <si>
-    <t>地狱祖玛禁地</t>
+    <t>地狱邪禁地</t>
   </si>
   <si>
     <t>1300-3</t>
@@ -2338,7 +2341,7 @@
     <t>1128</t>
   </si>
   <si>
-    <t>地狱祖玛大殿</t>
+    <t>地狱邪魔殿</t>
   </si>
   <si>
     <t>1300-4</t>
@@ -2374,7 +2377,7 @@
     <t>1130</t>
   </si>
   <si>
-    <t>地狱烈焰</t>
+    <t>地狱烈焰殿</t>
   </si>
   <si>
     <t>1350-1</t>
@@ -2392,7 +2395,7 @@
     <t>1131</t>
   </si>
   <si>
-    <t>地狱封魔</t>
+    <t>地狱封邪殿</t>
   </si>
   <si>
     <t>1350-2</t>
@@ -2410,7 +2413,7 @@
     <t>1132</t>
   </si>
   <si>
-    <t>地狱尸魔</t>
+    <t>地狱尸魔殿</t>
   </si>
   <si>
     <t>1350-3</t>
@@ -2428,7 +2431,7 @@
     <t>1133</t>
   </si>
   <si>
-    <t>地狱骨魔</t>
+    <t>地狱骨魔殿</t>
   </si>
   <si>
     <t>1350-4</t>
@@ -2446,7 +2449,7 @@
     <t>1134</t>
   </si>
   <si>
-    <t>地狱牛魔</t>
+    <t>地狱魔牛殿</t>
   </si>
   <si>
     <t>1350-5</t>
@@ -2464,7 +2467,7 @@
     <t>1135</t>
   </si>
   <si>
-    <t>地狱峡谷</t>
+    <t>地狱水龙谷</t>
   </si>
   <si>
     <t>1400-1</t>
@@ -2482,7 +2485,7 @@
     <t>1136</t>
   </si>
   <si>
-    <t>地狱祭坛</t>
+    <t>地狱土龙谷</t>
   </si>
   <si>
     <t>1400-2</t>
@@ -2500,7 +2503,7 @@
     <t>1137</t>
   </si>
   <si>
-    <t>地狱魔巢</t>
+    <t>地狱毒龙谷</t>
   </si>
   <si>
     <t>1400-3</t>
@@ -2518,7 +2521,7 @@
     <t>1138</t>
   </si>
   <si>
-    <t>地狱魔龙</t>
+    <t>地狱火龙谷</t>
   </si>
   <si>
     <t>1400-4</t>
@@ -2536,7 +2539,7 @@
     <t>1139</t>
   </si>
   <si>
-    <t>地狱火龙</t>
+    <t>地狱冰龙谷</t>
   </si>
   <si>
     <t>1400-5</t>
@@ -2727,12 +2730,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4457,7 +4460,7 @@
         <v>160</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -4466,27 +4469,27 @@
         <v>1</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>133</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:12">
       <c r="C33" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -4495,27 +4498,27 @@
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>133</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:12">
       <c r="C34" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -4524,27 +4527,27 @@
         <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>133</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:12">
       <c r="C35" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -4553,27 +4556,27 @@
         <v>1</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>133</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:12">
       <c r="C36" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -4582,27 +4585,27 @@
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>133</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:12">
       <c r="C37" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4611,27 +4614,27 @@
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>133</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:12">
       <c r="C38" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4640,27 +4643,27 @@
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>133</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:12">
       <c r="C39" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4669,27 +4672,27 @@
         <v>1</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>133</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:12">
       <c r="C40" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4698,27 +4701,27 @@
         <v>1</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>133</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:12">
       <c r="C41" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
@@ -4727,30 +4730,30 @@
         <v>2</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H41" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="J41" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:12">
       <c r="C42" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -4759,27 +4762,27 @@
         <v>2</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:12">
       <c r="C43" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -4788,27 +4791,27 @@
         <v>2</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:12">
       <c r="C44" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
@@ -4817,27 +4820,27 @@
         <v>2</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:12">
       <c r="C45" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
@@ -4846,27 +4849,27 @@
         <v>2</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C46" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
@@ -4875,30 +4878,30 @@
         <v>2</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H46" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="J46" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C47" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
@@ -4907,27 +4910,27 @@
         <v>2</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C48" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
@@ -4936,27 +4939,27 @@
         <v>2</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C49" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
@@ -4965,27 +4968,27 @@
         <v>2</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C50" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
@@ -4994,27 +4997,27 @@
         <v>2</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C51" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
@@ -5023,30 +5026,30 @@
         <v>2</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H51" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="J51" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C52" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
@@ -5055,27 +5058,27 @@
         <v>2</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C53" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
@@ -5084,27 +5087,27 @@
         <v>2</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C54" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
@@ -5113,27 +5116,27 @@
         <v>2</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C55" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
@@ -5142,27 +5145,27 @@
         <v>2</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C56" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
@@ -5171,30 +5174,30 @@
         <v>2</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H56" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="J56" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C57" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
@@ -5203,30 +5206,30 @@
         <v>2</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H57" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="J57" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C58" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
@@ -5235,30 +5238,30 @@
         <v>2</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H58" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="J58" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C59" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
@@ -5267,30 +5270,30 @@
         <v>2</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H59" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="J59" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C60" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
@@ -5299,30 +5302,31 @@
         <v>2</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H60" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="J60" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B61" s="1"/>
       <c r="C61" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
@@ -5331,30 +5335,31 @@
         <v>2</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I61" s="1">
         <v>600</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B62" s="1"/>
       <c r="C62" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
@@ -5363,30 +5368,31 @@
         <v>2</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I62" s="1">
         <v>600</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B63" s="1"/>
       <c r="C63" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
@@ -5395,30 +5401,31 @@
         <v>2</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I63" s="1">
         <v>600</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B64" s="1"/>
       <c r="C64" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
@@ -5427,30 +5434,31 @@
         <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I64" s="1">
         <v>600</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:12">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="2:12">
+      <c r="B65" s="1"/>
       <c r="C65" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
@@ -5459,30 +5467,30 @@
         <v>2</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I65" s="1">
         <v>600</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C66" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
@@ -5491,30 +5499,30 @@
         <v>2</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I66" s="1">
         <v>650</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C67" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
@@ -5523,30 +5531,30 @@
         <v>2</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I67" s="1">
         <v>650</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C68" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
@@ -5555,30 +5563,30 @@
         <v>2</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I68" s="1">
         <v>650</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C69" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
@@ -5587,30 +5595,30 @@
         <v>2</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I69" s="1">
         <v>650</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C70" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
@@ -5619,30 +5627,30 @@
         <v>2</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I70" s="1">
         <v>650</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C71" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
@@ -5651,30 +5659,30 @@
         <v>2</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="I71" s="1">
         <v>700</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C72" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
@@ -5683,30 +5691,30 @@
         <v>2</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I72" s="1">
         <v>700</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C73" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
@@ -5715,30 +5723,30 @@
         <v>2</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I73" s="1">
         <v>700</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C74" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -5747,30 +5755,30 @@
         <v>2</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I74" s="1">
         <v>700</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C75" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
@@ -5779,30 +5787,30 @@
         <v>2</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I75" s="1">
         <v>700</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:12">
       <c r="C76" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E76" s="1">
         <v>3</v>
@@ -5811,30 +5819,30 @@
         <v>3</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I76" s="1">
         <v>750</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:12">
       <c r="C77" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E77" s="1">
         <v>3</v>
@@ -5843,30 +5851,30 @@
         <v>3</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I77" s="1">
         <v>750</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E78" s="1">
         <v>3</v>
@@ -5875,30 +5883,30 @@
         <v>3</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I78" s="1">
         <v>750</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E79" s="1">
         <v>3</v>
@@ -5907,30 +5915,30 @@
         <v>3</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I79" s="1">
         <v>750</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E80" s="1">
         <v>3</v>
@@ -5939,30 +5947,30 @@
         <v>3</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I80" s="1">
         <v>750</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E81" s="1">
         <v>3</v>
@@ -5971,30 +5979,30 @@
         <v>3</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I81" s="1">
         <v>800</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E82" s="1">
         <v>3</v>
@@ -6003,30 +6011,30 @@
         <v>3</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="I82" s="1">
         <v>800</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E83" s="1">
         <v>3</v>
@@ -6035,30 +6043,30 @@
         <v>3</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="I83" s="1">
         <v>800</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E84" s="1">
         <v>3</v>
@@ -6067,30 +6075,30 @@
         <v>3</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I84" s="1">
         <v>800</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E85" s="1">
         <v>3</v>
@@ -6099,30 +6107,30 @@
         <v>3</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I85" s="1">
         <v>800</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C86" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E86" s="1">
         <v>3</v>
@@ -6131,30 +6139,30 @@
         <v>3</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I86" s="1">
         <v>850</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C87" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E87" s="1">
         <v>3</v>
@@ -6163,30 +6171,30 @@
         <v>3</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I87" s="1">
         <v>850</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C88" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E88" s="1">
         <v>3</v>
@@ -6195,30 +6203,30 @@
         <v>3</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I88" s="1">
         <v>850</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C89" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E89" s="1">
         <v>3</v>
@@ -6227,30 +6235,30 @@
         <v>3</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I89" s="1">
         <v>850</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C90" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E90" s="1">
         <v>3</v>
@@ -6259,30 +6267,30 @@
         <v>3</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I90" s="1">
         <v>850</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C91" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E91" s="1">
         <v>3</v>
@@ -6291,30 +6299,30 @@
         <v>3</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I91" s="1">
         <v>900</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C92" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E92" s="1">
         <v>3</v>
@@ -6323,30 +6331,30 @@
         <v>3</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I92" s="1">
         <v>900</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C93" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E93" s="1">
         <v>3</v>
@@ -6355,30 +6363,30 @@
         <v>3</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I93" s="1">
         <v>900</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C94" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E94" s="1">
         <v>3</v>
@@ -6387,30 +6395,30 @@
         <v>3</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I94" s="1">
         <v>900</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C95" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E95" s="1">
         <v>3</v>
@@ -6419,30 +6427,30 @@
         <v>3</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I95" s="1">
         <v>900</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E96" s="1">
         <v>3</v>
@@ -6451,30 +6459,30 @@
         <v>3</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I96" s="1">
         <v>950</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E97" s="1">
         <v>3</v>
@@ -6483,30 +6491,30 @@
         <v>3</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I97" s="1">
         <v>950</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E98" s="1">
         <v>3</v>
@@ -6515,30 +6523,30 @@
         <v>3</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I98" s="1">
         <v>950</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E99" s="1">
         <v>3</v>
@@ -6547,30 +6555,30 @@
         <v>3</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I99" s="1">
         <v>950</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E100" s="1">
         <v>3</v>
@@ -6579,30 +6587,30 @@
         <v>3</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I100" s="1">
         <v>950</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E101" s="1">
         <v>3</v>
@@ -6611,30 +6619,30 @@
         <v>3</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="I101" s="1">
         <v>1000</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E102" s="1">
         <v>3</v>
@@ -6643,30 +6651,30 @@
         <v>3</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I102" s="1">
         <v>1000</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E103" s="1">
         <v>3</v>
@@ -6675,30 +6683,30 @@
         <v>3</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I103" s="1">
         <v>1000</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E104" s="1">
         <v>3</v>
@@ -6707,30 +6715,30 @@
         <v>3</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I104" s="1">
         <v>1000</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E105" s="1">
         <v>3</v>
@@ -6739,30 +6747,30 @@
         <v>3</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I105" s="1">
         <v>1000</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C106" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E106" s="1">
         <v>3</v>
@@ -6771,30 +6779,30 @@
         <v>3</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I106" s="1">
         <v>1050</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C107" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E107" s="1">
         <v>3</v>
@@ -6803,30 +6811,30 @@
         <v>3</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I107" s="1">
         <v>1050</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C108" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E108" s="1">
         <v>3</v>
@@ -6835,30 +6843,30 @@
         <v>3</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I108" s="1">
         <v>1050</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C109" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E109" s="1">
         <v>3</v>
@@ -6867,30 +6875,30 @@
         <v>3</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I109" s="1">
         <v>1050</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C110" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E110" s="1">
         <v>3</v>
@@ -6899,30 +6907,30 @@
         <v>3</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I110" s="1">
         <v>1050</v>
       </c>
       <c r="J110" s="7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E111" s="1">
         <v>4</v>
@@ -6931,30 +6939,30 @@
         <v>4</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I111" s="1">
         <v>0</v>
       </c>
       <c r="J111" s="7" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E112" s="1">
         <v>4</v>
@@ -6963,30 +6971,30 @@
         <v>4</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="I112" s="1">
         <v>0</v>
       </c>
       <c r="J112" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:12">
       <c r="C113" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E113" s="1">
         <v>4</v>
@@ -6995,30 +7003,30 @@
         <v>4</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I113" s="1">
         <v>0</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E114" s="1">
         <v>4</v>
@@ -7027,30 +7035,30 @@
         <v>4</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="I114" s="1">
         <v>0</v>
       </c>
       <c r="J114" s="7" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E115" s="1">
         <v>4</v>
@@ -7059,30 +7067,30 @@
         <v>4</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="I115" s="1">
         <v>0</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E116" s="1">
         <v>4</v>
@@ -7091,30 +7099,30 @@
         <v>4</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="I116" s="1">
         <v>0</v>
       </c>
       <c r="J116" s="7" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:12">
       <c r="C117" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E117" s="1">
         <v>4</v>
@@ -7123,30 +7131,30 @@
         <v>4</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="I117" s="1">
         <v>0</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="3:12">
       <c r="C118" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E118" s="1">
         <v>4</v>
@@ -7155,30 +7163,30 @@
         <v>4</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="I118" s="1">
         <v>0</v>
       </c>
       <c r="J118" s="7" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:12">
       <c r="C119" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E119" s="1">
         <v>4</v>
@@ -7187,30 +7195,30 @@
         <v>4</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="I119" s="1">
         <v>0</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:12">
       <c r="C120" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E120" s="1">
         <v>4</v>
@@ -7219,30 +7227,30 @@
         <v>4</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I120" s="1">
         <v>0</v>
       </c>
       <c r="J120" s="7" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C121" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
@@ -7251,30 +7259,30 @@
         <v>4</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I121" s="1">
         <v>0</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C122" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
@@ -7283,30 +7291,30 @@
         <v>4</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I122" s="1">
         <v>0</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C123" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
@@ -7315,30 +7323,30 @@
         <v>4</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="I123" s="1">
         <v>0</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C124" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
@@ -7347,30 +7355,30 @@
         <v>4</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I124" s="1">
         <v>0</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C125" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
@@ -7379,36 +7387,36 @@
         <v>4</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I125" s="1">
         <v>0</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="K125" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A126" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
@@ -7417,36 +7425,36 @@
         <v>4</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I126" s="1">
         <v>0</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="K126" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A127" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
@@ -7455,36 +7463,36 @@
         <v>4</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I127" s="1">
         <v>0</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="K127" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A128" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
@@ -7493,36 +7501,36 @@
         <v>4</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I128" s="1">
         <v>0</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K128" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A129" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
@@ -7531,36 +7539,36 @@
         <v>4</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="I129" s="1">
         <v>0</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K129" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A130" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
@@ -7569,36 +7577,36 @@
         <v>4</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="I130" s="1">
         <v>0</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="K130" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="1:12">
       <c r="A131" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
@@ -7607,36 +7615,36 @@
         <v>4</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="I131" s="1">
         <v>0</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K131" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="1:12">
       <c r="A132" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
@@ -7645,36 +7653,36 @@
         <v>4</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="I132" s="1">
         <v>0</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="K132" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:12">
       <c r="A133" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
@@ -7683,36 +7691,36 @@
         <v>4</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="I133" s="1">
         <v>0</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="K133" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:12">
       <c r="A134" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
@@ -7721,36 +7729,36 @@
         <v>4</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="I134" s="1">
         <v>0</v>
       </c>
       <c r="J134" s="7" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="K134" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:12">
       <c r="A135" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
@@ -7759,36 +7767,36 @@
         <v>4</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="I135" s="1">
         <v>0</v>
       </c>
       <c r="J135" s="7" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K135" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:12">
       <c r="A136" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
@@ -7797,36 +7805,36 @@
         <v>4</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I136" s="1">
         <v>0</v>
       </c>
       <c r="J136" s="7" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="K136" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="1:12">
       <c r="A137" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
@@ -7835,36 +7843,36 @@
         <v>4</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="I137" s="1">
         <v>0</v>
       </c>
       <c r="J137" s="7" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="K137" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:12">
       <c r="A138" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
@@ -7873,36 +7881,36 @@
         <v>4</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="I138" s="1">
         <v>0</v>
       </c>
       <c r="J138" s="7" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="K138" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:12">
       <c r="A139" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
@@ -7911,36 +7919,36 @@
         <v>4</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="I139" s="1">
         <v>0</v>
       </c>
       <c r="J139" s="7" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="K139" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:12">
       <c r="A140" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
@@ -7949,36 +7957,36 @@
         <v>4</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="I140" s="1">
         <v>0</v>
       </c>
       <c r="J140" s="7" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K140" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A141" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
@@ -7987,36 +7995,36 @@
         <v>4</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="I141" s="1">
         <v>0</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="K141" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A142" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
@@ -8025,36 +8033,36 @@
         <v>4</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="I142" s="1">
         <v>0</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K142" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A143" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
@@ -8063,36 +8071,36 @@
         <v>4</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="I143" s="1">
         <v>0</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="K143" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A144" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
@@ -8101,36 +8109,36 @@
         <v>4</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="I144" s="1">
         <v>0</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="K144" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A145" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
@@ -8139,22 +8147,22 @@
         <v>4</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="I145" s="1">
         <v>0</v>
       </c>
       <c r="J145" s="7" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="K145" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="831">
   <si>
     <t>_Id</t>
   </si>
@@ -2191,97 +2191,97 @@
     <t>10119</t>
   </si>
   <si>
+    <t>1120</t>
+  </si>
+  <si>
+    <t>地狱虫穴</t>
+  </si>
+  <si>
+    <t>1250-1</t>
+  </si>
+  <si>
+    <t>地狱虫心</t>
+  </si>
+  <si>
+    <t>202004,300091,104,504,210050</t>
+  </si>
+  <si>
+    <t>10120</t>
+  </si>
+  <si>
+    <t>1121</t>
+  </si>
+  <si>
+    <t>地狱虫巢</t>
+  </si>
+  <si>
+    <t>1250-2</t>
+  </si>
+  <si>
+    <t>地狱龙皮</t>
+  </si>
+  <si>
+    <t>202004,300091,104,504,210051</t>
+  </si>
+  <si>
+    <t>10121</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>地狱魔猪厅</t>
+  </si>
+  <si>
+    <t>1250-3</t>
+  </si>
+  <si>
+    <t>地狱猪皮</t>
+  </si>
+  <si>
+    <t>202004,300091,104,504,210052</t>
+  </si>
+  <si>
+    <t>10122</t>
+  </si>
+  <si>
+    <t>1123</t>
+  </si>
+  <si>
+    <t>地狱魔猪殿</t>
+  </si>
+  <si>
+    <t>1250-4</t>
+  </si>
+  <si>
+    <t>地狱猪心</t>
+  </si>
+  <si>
+    <t>202004,300091,104,504,210053</t>
+  </si>
+  <si>
+    <t>10123</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>地狱桃源</t>
+  </si>
+  <si>
+    <t>1250-5</t>
+  </si>
+  <si>
+    <t>地狱蝎皮</t>
+  </si>
+  <si>
+    <t>202004,300091,104,504,210054</t>
+  </si>
+  <si>
+    <t>10124</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>地狱虫穴</t>
-  </si>
-  <si>
-    <t>1250-1</t>
-  </si>
-  <si>
-    <t>地狱虫心</t>
-  </si>
-  <si>
-    <t>202004,300091,104,504,210050</t>
-  </si>
-  <si>
-    <t>10120</t>
-  </si>
-  <si>
-    <t>1121</t>
-  </si>
-  <si>
-    <t>地狱虫巢</t>
-  </si>
-  <si>
-    <t>1250-2</t>
-  </si>
-  <si>
-    <t>地狱龙皮</t>
-  </si>
-  <si>
-    <t>202004,300091,104,504,210051</t>
-  </si>
-  <si>
-    <t>10121</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>地狱魔猪厅</t>
-  </si>
-  <si>
-    <t>1250-3</t>
-  </si>
-  <si>
-    <t>地狱猪皮</t>
-  </si>
-  <si>
-    <t>202004,300091,104,504,210052</t>
-  </si>
-  <si>
-    <t>10122</t>
-  </si>
-  <si>
-    <t>1123</t>
-  </si>
-  <si>
-    <t>地狱魔猪殿</t>
-  </si>
-  <si>
-    <t>1250-4</t>
-  </si>
-  <si>
-    <t>地狱猪心</t>
-  </si>
-  <si>
-    <t>202004,300091,104,504,210053</t>
-  </si>
-  <si>
-    <t>10123</t>
-  </si>
-  <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>地狱桃源</t>
-  </si>
-  <si>
-    <t>1250-5</t>
-  </si>
-  <si>
-    <t>地狱蝎皮</t>
-  </si>
-  <si>
-    <t>202004,300091,104,504,210054</t>
-  </si>
-  <si>
-    <t>10124</t>
   </si>
   <si>
     <t>1125</t>
@@ -7405,18 +7405,12 @@
         <v>709</v>
       </c>
     </row>
-    <row r="126" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A126" s="1" t="s">
+    <row r="126" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C126" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="C126" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>712</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
@@ -7425,36 +7419,30 @@
         <v>4</v>
       </c>
       <c r="G126" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="H126" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>714</v>
       </c>
       <c r="I126" s="1">
         <v>0</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K126" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L126" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="127" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C127" s="1" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="127" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A127" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="C127" s="1" t="s">
+      <c r="D127" s="1" t="s">
         <v>717</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>718</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
@@ -7463,36 +7451,30 @@
         <v>4</v>
       </c>
       <c r="G127" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="H127" s="1" t="s">
         <v>719</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>720</v>
       </c>
       <c r="I127" s="1">
         <v>0</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="K127" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L127" s="1" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="128" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C128" s="1" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="128" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A128" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="C128" s="1" t="s">
+      <c r="D128" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>724</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
@@ -7501,36 +7483,30 @@
         <v>4</v>
       </c>
       <c r="G128" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="H128" s="1" t="s">
         <v>725</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>726</v>
       </c>
       <c r="I128" s="1">
         <v>0</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K128" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L128" s="1" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="129" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C129" s="1" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="129" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A129" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="C129" s="1" t="s">
+      <c r="D129" s="1" t="s">
         <v>729</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>730</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
@@ -7539,36 +7515,30 @@
         <v>4</v>
       </c>
       <c r="G129" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="H129" s="1" t="s">
         <v>731</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>732</v>
       </c>
       <c r="I129" s="1">
         <v>0</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K129" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L129" s="1" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="130" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C130" s="1" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="130" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A130" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="C130" s="1" t="s">
+      <c r="D130" s="1" t="s">
         <v>735</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>736</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
@@ -7577,30 +7547,30 @@
         <v>4</v>
       </c>
       <c r="G130" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="H130" s="1" t="s">
         <v>737</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>738</v>
       </c>
       <c r="I130" s="1">
         <v>0</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="K130" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="1:12">
       <c r="A131" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>741</v>
@@ -7635,10 +7605,10 @@
     </row>
     <row r="132" customHeight="1" spans="1:12">
       <c r="A132" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>747</v>
@@ -7673,10 +7643,10 @@
     </row>
     <row r="133" customHeight="1" spans="1:12">
       <c r="A133" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>753</v>
@@ -7711,10 +7681,10 @@
     </row>
     <row r="134" customHeight="1" spans="1:12">
       <c r="A134" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>759</v>
@@ -7749,10 +7719,10 @@
     </row>
     <row r="135" customHeight="1" spans="1:12">
       <c r="A135" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>765</v>
@@ -7787,10 +7757,10 @@
     </row>
     <row r="136" customHeight="1" spans="1:12">
       <c r="A136" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>771</v>
@@ -7825,10 +7795,10 @@
     </row>
     <row r="137" customHeight="1" spans="1:12">
       <c r="A137" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>777</v>
@@ -7863,10 +7833,10 @@
     </row>
     <row r="138" customHeight="1" spans="1:12">
       <c r="A138" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>783</v>
@@ -7901,10 +7871,10 @@
     </row>
     <row r="139" customHeight="1" spans="1:12">
       <c r="A139" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>789</v>
@@ -7939,10 +7909,10 @@
     </row>
     <row r="140" customHeight="1" spans="1:12">
       <c r="A140" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>795</v>
@@ -7977,10 +7947,10 @@
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A141" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>801</v>
@@ -8015,10 +7985,10 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A142" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>807</v>
@@ -8053,10 +8023,10 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A143" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>813</v>
@@ -8091,10 +8061,10 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A144" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>819</v>
@@ -8129,10 +8099,10 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A145" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>710</v>
+        <v>740</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>825</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -2113,7 +2113,7 @@
     <t>地狱狼爪</t>
   </si>
   <si>
-    <t>202003,300091,104,504,210045</t>
+    <t>202001,300091,104,504,210045</t>
   </si>
   <si>
     <t>10115</t>
@@ -2131,7 +2131,7 @@
     <t>地狱虫皮</t>
   </si>
   <si>
-    <t>202003,300091,104,504,210046</t>
+    <t>202001,300091,104,504,210046</t>
   </si>
   <si>
     <t>10116</t>
@@ -2149,7 +2149,7 @@
     <t>地狱鹰羽</t>
   </si>
   <si>
-    <t>202003,300091,104,504,210047</t>
+    <t>202001,300091,104,504,210047</t>
   </si>
   <si>
     <t>10117</t>
@@ -2167,7 +2167,7 @@
     <t>地狱虫角</t>
   </si>
   <si>
-    <t>202003,300091,104,504,210048</t>
+    <t>202001,300091,104,504,210048</t>
   </si>
   <si>
     <t>10118</t>
@@ -2185,7 +2185,7 @@
     <t>地狱蜈膏</t>
   </si>
   <si>
-    <t>202003,300091,104,504,210049</t>
+    <t>202001,300091,104,504,210049</t>
   </si>
   <si>
     <t>10119</t>
@@ -2203,7 +2203,7 @@
     <t>地狱虫心</t>
   </si>
   <si>
-    <t>202004,300091,104,504,210050</t>
+    <t>202001,300091,104,504,210050</t>
   </si>
   <si>
     <t>10120</t>
@@ -2221,7 +2221,7 @@
     <t>地狱龙皮</t>
   </si>
   <si>
-    <t>202004,300091,104,504,210051</t>
+    <t>202001,300091,104,504,210051</t>
   </si>
   <si>
     <t>10121</t>
@@ -2239,7 +2239,7 @@
     <t>地狱猪皮</t>
   </si>
   <si>
-    <t>202004,300091,104,504,210052</t>
+    <t>202001,300091,104,504,210052</t>
   </si>
   <si>
     <t>10122</t>
@@ -2257,7 +2257,7 @@
     <t>地狱猪心</t>
   </si>
   <si>
-    <t>202004,300091,104,504,210053</t>
+    <t>202001,300091,104,504,210053</t>
   </si>
   <si>
     <t>10123</t>
@@ -2275,7 +2275,7 @@
     <t>地狱蝎皮</t>
   </si>
   <si>
-    <t>202004,300091,104,504,210054</t>
+    <t>202001,300091,104,504,210054</t>
   </si>
   <si>
     <t>10124</t>
@@ -2296,7 +2296,7 @@
     <t>地狱宝甲</t>
   </si>
   <si>
-    <t>202005,300091,104,504,210055</t>
+    <t>202001,300091,104,504,210055</t>
   </si>
   <si>
     <t>10125</t>
@@ -2314,7 +2314,7 @@
     <t>地狱号角</t>
   </si>
   <si>
-    <t>202005,300091,104,504,210056</t>
+    <t>202001,300091,104,504,210056</t>
   </si>
   <si>
     <t>10126</t>
@@ -2332,7 +2332,7 @@
     <t>地狱雕像</t>
   </si>
   <si>
-    <t>202005,300091,104,504,210057</t>
+    <t>202001,300091,104,504,210057</t>
   </si>
   <si>
     <t>10127</t>
@@ -2350,7 +2350,7 @@
     <t>地狱神像</t>
   </si>
   <si>
-    <t>202005,300091,104,504,210058</t>
+    <t>202001,300091,104,504,210058</t>
   </si>
   <si>
     <t>10128</t>
@@ -2368,7 +2368,7 @@
     <t>地狱獠牙</t>
   </si>
   <si>
-    <t>202005,300091,104,504,210059</t>
+    <t>202001,300091,104,504,210059</t>
   </si>
   <si>
     <t>10129</t>
@@ -2386,7 +2386,7 @@
     <t>地狱树心</t>
   </si>
   <si>
-    <t>202006,300091,104,504,210060</t>
+    <t>202001,300091,104,504,210060</t>
   </si>
   <si>
     <t>10130</t>
@@ -2404,7 +2404,7 @@
     <t>地狱魔心</t>
   </si>
   <si>
-    <t>202006,300091,104,504,210061</t>
+    <t>202001,300091,104,504,210061</t>
   </si>
   <si>
     <t>10131</t>
@@ -2422,7 +2422,7 @@
     <t>地狱尸心</t>
   </si>
   <si>
-    <t>202006,300091,104,504,210062</t>
+    <t>202001,300091,104,504,210062</t>
   </si>
   <si>
     <t>10132</t>
@@ -2440,7 +2440,7 @@
     <t>地狱法杖</t>
   </si>
   <si>
-    <t>202006,300091,104,504,210063</t>
+    <t>202001,300091,104,504,210063</t>
   </si>
   <si>
     <t>10133</t>
@@ -2458,7 +2458,7 @@
     <t>地狱权杖</t>
   </si>
   <si>
-    <t>202006,300091,104,504,210064</t>
+    <t>202001,300091,104,504,210064</t>
   </si>
   <si>
     <t>10134</t>
@@ -2476,7 +2476,7 @@
     <t>地狱战锤</t>
   </si>
   <si>
-    <t>202007,300091,104,504,210065</t>
+    <t>202001,300091,104,504,210065</t>
   </si>
   <si>
     <t>10135</t>
@@ -2494,7 +2494,7 @@
     <t>地狱血核</t>
   </si>
   <si>
-    <t>202007,300091,104,504,210066</t>
+    <t>202001,300091,104,504,210066</t>
   </si>
   <si>
     <t>10136</t>
@@ -2512,7 +2512,7 @@
     <t>地狱魔核</t>
   </si>
   <si>
-    <t>202007,300091,104,504,210067</t>
+    <t>202001,300091,104,504,210067</t>
   </si>
   <si>
     <t>10137</t>
@@ -2530,7 +2530,7 @@
     <t>地狱龙甲</t>
   </si>
   <si>
-    <t>202007,300091,104,504,210068</t>
+    <t>202001,300091,104,504,210068</t>
   </si>
   <si>
     <t>10138</t>
@@ -2548,7 +2548,7 @@
     <t>地狱龙爪</t>
   </si>
   <si>
-    <t>202007,300091,104,504,210069</t>
+    <t>202001,300091,104,504,210069</t>
   </si>
   <si>
     <t>10139</t>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="831">
   <si>
     <t>_Id</t>
   </si>
@@ -2281,97 +2281,97 @@
     <t>10124</t>
   </si>
   <si>
+    <t>1125</t>
+  </si>
+  <si>
+    <t>地狱魔禁地</t>
+  </si>
+  <si>
+    <t>1300-1</t>
+  </si>
+  <si>
+    <t>地狱宝甲</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210055</t>
+  </si>
+  <si>
+    <t>10125</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>地狱魔神殿</t>
+  </si>
+  <si>
+    <t>1300-2</t>
+  </si>
+  <si>
+    <t>地狱号角</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210056</t>
+  </si>
+  <si>
+    <t>10126</t>
+  </si>
+  <si>
+    <t>1127</t>
+  </si>
+  <si>
+    <t>地狱邪禁地</t>
+  </si>
+  <si>
+    <t>1300-3</t>
+  </si>
+  <si>
+    <t>地狱雕像</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210057</t>
+  </si>
+  <si>
+    <t>10127</t>
+  </si>
+  <si>
+    <t>1128</t>
+  </si>
+  <si>
+    <t>地狱邪魔殿</t>
+  </si>
+  <si>
+    <t>1300-4</t>
+  </si>
+  <si>
+    <t>地狱神像</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210058</t>
+  </si>
+  <si>
+    <t>10128</t>
+  </si>
+  <si>
+    <t>1129</t>
+  </si>
+  <si>
+    <t>地狱封魔殿</t>
+  </si>
+  <si>
+    <t>1300-5</t>
+  </si>
+  <si>
+    <t>地狱獠牙</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210059</t>
+  </si>
+  <si>
+    <t>10129</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>地狱魔禁地</t>
-  </si>
-  <si>
-    <t>1300-1</t>
-  </si>
-  <si>
-    <t>地狱宝甲</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210055</t>
-  </si>
-  <si>
-    <t>10125</t>
-  </si>
-  <si>
-    <t>1126</t>
-  </si>
-  <si>
-    <t>地狱魔神殿</t>
-  </si>
-  <si>
-    <t>1300-2</t>
-  </si>
-  <si>
-    <t>地狱号角</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210056</t>
-  </si>
-  <si>
-    <t>10126</t>
-  </si>
-  <si>
-    <t>1127</t>
-  </si>
-  <si>
-    <t>地狱邪禁地</t>
-  </si>
-  <si>
-    <t>1300-3</t>
-  </si>
-  <si>
-    <t>地狱雕像</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210057</t>
-  </si>
-  <si>
-    <t>10127</t>
-  </si>
-  <si>
-    <t>1128</t>
-  </si>
-  <si>
-    <t>地狱邪魔殿</t>
-  </si>
-  <si>
-    <t>1300-4</t>
-  </si>
-  <si>
-    <t>地狱神像</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210058</t>
-  </si>
-  <si>
-    <t>10128</t>
-  </si>
-  <si>
-    <t>1129</t>
-  </si>
-  <si>
-    <t>地狱封魔殿</t>
-  </si>
-  <si>
-    <t>1300-5</t>
-  </si>
-  <si>
-    <t>地狱獠牙</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210059</t>
-  </si>
-  <si>
-    <t>10129</t>
   </si>
   <si>
     <t>1130</t>
@@ -2730,12 +2730,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3568,19 +3568,19 @@
   <dimension ref="A3:M145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.25454545454545" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="65.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="50.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.37272727272727" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.75454545454545" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.87272727272727" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7545454545455" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.3727272727273" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.12727272727273" style="1" customWidth="1"/>
+    <col min="10" max="10" width="65.3727272727273" style="1" customWidth="1"/>
+    <col min="11" max="11" width="50.3727272727273" style="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="3" customWidth="1"/>
-    <col min="13" max="13" width="45.25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="45.2545454545455" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -7565,18 +7565,12 @@
         <v>739</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="1:12">
-      <c r="A131" s="1" t="s">
+    <row r="131" customHeight="1" spans="3:12">
+      <c r="C131" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="C131" s="1" t="s">
+      <c r="D131" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>742</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
@@ -7585,36 +7579,30 @@
         <v>4</v>
       </c>
       <c r="G131" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="H131" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="H131" s="1" t="s">
-        <v>744</v>
       </c>
       <c r="I131" s="1">
         <v>0</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="K131" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L131" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:12">
+      <c r="C132" s="1" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="132" customHeight="1" spans="1:12">
-      <c r="A132" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="C132" s="1" t="s">
+      <c r="D132" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
@@ -7623,36 +7611,30 @@
         <v>4</v>
       </c>
       <c r="G132" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="H132" s="1" t="s">
         <v>749</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>750</v>
       </c>
       <c r="I132" s="1">
         <v>0</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="K132" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L132" s="1" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:12">
+      <c r="C133" s="1" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="133" customHeight="1" spans="1:12">
-      <c r="A133" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
@@ -7661,36 +7643,30 @@
         <v>4</v>
       </c>
       <c r="G133" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>756</v>
       </c>
       <c r="I133" s="1">
         <v>0</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="K133" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L133" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:12">
+      <c r="C134" s="1" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="134" customHeight="1" spans="1:12">
-      <c r="A134" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="C134" s="1" t="s">
+      <c r="D134" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>760</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
@@ -7699,36 +7675,30 @@
         <v>4</v>
       </c>
       <c r="G134" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="H134" s="1" t="s">
         <v>761</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>762</v>
       </c>
       <c r="I134" s="1">
         <v>0</v>
       </c>
       <c r="J134" s="7" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="K134" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L134" s="1" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:12">
+      <c r="C135" s="1" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="135" customHeight="1" spans="1:12">
-      <c r="A135" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="C135" s="1" t="s">
+      <c r="D135" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>766</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
@@ -7737,30 +7707,30 @@
         <v>4</v>
       </c>
       <c r="G135" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="H135" s="1" t="s">
         <v>767</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>768</v>
       </c>
       <c r="I135" s="1">
         <v>0</v>
       </c>
       <c r="J135" s="7" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="K135" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:12">
       <c r="A136" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>771</v>
@@ -7795,10 +7765,10 @@
     </row>
     <row r="137" customHeight="1" spans="1:12">
       <c r="A137" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>777</v>
@@ -7833,10 +7803,10 @@
     </row>
     <row r="138" customHeight="1" spans="1:12">
       <c r="A138" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>783</v>
@@ -7871,10 +7841,10 @@
     </row>
     <row r="139" customHeight="1" spans="1:12">
       <c r="A139" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>789</v>
@@ -7909,10 +7879,10 @@
     </row>
     <row r="140" customHeight="1" spans="1:12">
       <c r="A140" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>795</v>
@@ -7947,10 +7917,10 @@
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A141" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>801</v>
@@ -7985,10 +7955,10 @@
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A142" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>807</v>
@@ -8023,10 +7993,10 @@
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A143" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>813</v>
@@ -8061,10 +8031,10 @@
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A144" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>819</v>
@@ -8099,10 +8069,10 @@
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A145" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>825</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="832">
   <si>
     <t>_Id</t>
   </si>
@@ -2371,97 +2371,100 @@
     <t>10129</t>
   </si>
   <si>
+    <t>1130</t>
+  </si>
+  <si>
+    <t>地狱烈焰殿</t>
+  </si>
+  <si>
+    <t>1350-1</t>
+  </si>
+  <si>
+    <t>地狱树心</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210060,2009</t>
+  </si>
+  <si>
+    <t>10,2500,1000,18000,600000,10000</t>
+  </si>
+  <si>
+    <t>10130</t>
+  </si>
+  <si>
+    <t>1131</t>
+  </si>
+  <si>
+    <t>地狱封邪殿</t>
+  </si>
+  <si>
+    <t>1350-2</t>
+  </si>
+  <si>
+    <t>地狱魔心</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210061,2009</t>
+  </si>
+  <si>
+    <t>10131</t>
+  </si>
+  <si>
+    <t>1132</t>
+  </si>
+  <si>
+    <t>地狱尸魔殿</t>
+  </si>
+  <si>
+    <t>1350-3</t>
+  </si>
+  <si>
+    <t>地狱尸心</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210062,2009</t>
+  </si>
+  <si>
+    <t>10132</t>
+  </si>
+  <si>
+    <t>1133</t>
+  </si>
+  <si>
+    <t>地狱骨魔殿</t>
+  </si>
+  <si>
+    <t>1350-4</t>
+  </si>
+  <si>
+    <t>地狱法杖</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210063,2009</t>
+  </si>
+  <si>
+    <t>10133</t>
+  </si>
+  <si>
+    <t>1134</t>
+  </si>
+  <si>
+    <t>地狱魔牛殿</t>
+  </si>
+  <si>
+    <t>1350-5</t>
+  </si>
+  <si>
+    <t>地狱权杖</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210064,2009</t>
+  </si>
+  <si>
+    <t>10134</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1130</t>
-  </si>
-  <si>
-    <t>地狱烈焰殿</t>
-  </si>
-  <si>
-    <t>1350-1</t>
-  </si>
-  <si>
-    <t>地狱树心</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210060</t>
-  </si>
-  <si>
-    <t>10130</t>
-  </si>
-  <si>
-    <t>1131</t>
-  </si>
-  <si>
-    <t>地狱封邪殿</t>
-  </si>
-  <si>
-    <t>1350-2</t>
-  </si>
-  <si>
-    <t>地狱魔心</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210061</t>
-  </si>
-  <si>
-    <t>10131</t>
-  </si>
-  <si>
-    <t>1132</t>
-  </si>
-  <si>
-    <t>地狱尸魔殿</t>
-  </si>
-  <si>
-    <t>1350-3</t>
-  </si>
-  <si>
-    <t>地狱尸心</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210062</t>
-  </si>
-  <si>
-    <t>10132</t>
-  </si>
-  <si>
-    <t>1133</t>
-  </si>
-  <si>
-    <t>地狱骨魔殿</t>
-  </si>
-  <si>
-    <t>1350-4</t>
-  </si>
-  <si>
-    <t>地狱法杖</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210063</t>
-  </si>
-  <si>
-    <t>10133</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>地狱魔牛殿</t>
-  </si>
-  <si>
-    <t>1350-5</t>
-  </si>
-  <si>
-    <t>地狱权杖</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210064</t>
-  </si>
-  <si>
-    <t>10134</t>
   </si>
   <si>
     <t>1135</t>
@@ -2730,12 +2733,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3568,19 +3571,19 @@
   <dimension ref="A3:M145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.25454545454545" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.25833333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.37272727272727" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3727272727273" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.75454545454545" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.87272727272727" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7545454545455" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.3727272727273" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.12727272727273" style="1" customWidth="1"/>
-    <col min="10" max="10" width="65.3727272727273" style="1" customWidth="1"/>
-    <col min="11" max="11" width="50.3727272727273" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.75833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7583333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="65.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="50.375" style="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="3" customWidth="1"/>
-    <col min="13" max="13" width="45.2545454545455" style="1" customWidth="1"/>
+    <col min="13" max="13" width="45.2583333333333" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -7725,18 +7728,12 @@
         <v>769</v>
       </c>
     </row>
-    <row r="136" customHeight="1" spans="1:12">
-      <c r="A136" s="1" t="s">
+    <row r="136" customHeight="1" spans="3:12">
+      <c r="C136" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>771</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>772</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
@@ -7745,31 +7742,25 @@
         <v>4</v>
       </c>
       <c r="G136" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="H136" s="1" t="s">
         <v>773</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>774</v>
       </c>
       <c r="I136" s="1">
         <v>0</v>
       </c>
       <c r="J136" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="K136" s="7" t="s">
         <v>775</v>
-      </c>
-      <c r="K136" s="7" t="s">
-        <v>624</v>
       </c>
       <c r="L136" s="1" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="137" customHeight="1" spans="1:12">
-      <c r="A137" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>770</v>
-      </c>
+    <row r="137" customHeight="1" spans="3:12">
       <c r="C137" s="1" t="s">
         <v>777</v>
       </c>
@@ -7795,19 +7786,13 @@
         <v>781</v>
       </c>
       <c r="K137" s="7" t="s">
-        <v>624</v>
+        <v>775</v>
       </c>
       <c r="L137" s="1" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="138" customHeight="1" spans="1:12">
-      <c r="A138" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>770</v>
-      </c>
+    <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1" t="s">
         <v>783</v>
       </c>
@@ -7833,19 +7818,13 @@
         <v>787</v>
       </c>
       <c r="K138" s="7" t="s">
-        <v>624</v>
+        <v>775</v>
       </c>
       <c r="L138" s="1" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="139" customHeight="1" spans="1:12">
-      <c r="A139" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>770</v>
-      </c>
+    <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1" t="s">
         <v>789</v>
       </c>
@@ -7871,19 +7850,13 @@
         <v>793</v>
       </c>
       <c r="K139" s="7" t="s">
-        <v>624</v>
+        <v>775</v>
       </c>
       <c r="L139" s="1" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="1:12">
-      <c r="A140" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>770</v>
-      </c>
+    <row r="140" customHeight="1" spans="3:12">
       <c r="C140" s="1" t="s">
         <v>795</v>
       </c>
@@ -7909,7 +7882,7 @@
         <v>799</v>
       </c>
       <c r="K140" s="7" t="s">
-        <v>624</v>
+        <v>775</v>
       </c>
       <c r="L140" s="1" t="s">
         <v>800</v>
@@ -7917,16 +7890,16 @@
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A141" s="1" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
@@ -7935,36 +7908,36 @@
         <v>4</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="I141" s="1">
         <v>0</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="K141" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A142" s="1" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
@@ -7973,36 +7946,36 @@
         <v>4</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I142" s="1">
         <v>0</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="K142" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A143" s="1" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
@@ -8011,36 +7984,36 @@
         <v>4</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="I143" s="1">
         <v>0</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K143" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A144" s="1" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
@@ -8049,36 +8022,36 @@
         <v>4</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I144" s="1">
         <v>0</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="K144" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A145" s="1" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
@@ -8087,22 +8060,22 @@
         <v>4</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I145" s="1">
         <v>0</v>
       </c>
       <c r="J145" s="7" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="K145" s="7" t="s">
         <v>624</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -2733,12 +2733,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3571,19 +3571,19 @@
   <dimension ref="A3:M145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.25833333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.25454545454545" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.75833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7583333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="65.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="50.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.37272727272727" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.75454545454545" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.87272727272727" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7545454545455" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.3727272727273" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.12727272727273" style="1" customWidth="1"/>
+    <col min="10" max="10" width="65.3727272727273" style="1" customWidth="1"/>
+    <col min="11" max="11" width="50.3727272727273" style="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="3" customWidth="1"/>
-    <col min="13" max="13" width="45.2583333333333" style="1" customWidth="1"/>
+    <col min="13" max="13" width="45.2545454545455" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -1297,7 +1297,10 @@
     <t>红装,梦魇鸡爪</t>
   </si>
   <si>
-    <t>200750,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504</t>
+    <t>200750,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
+  </si>
+  <si>
+    <t>10,500,500,500,1250,2500,2500,5000,100000,200000,1000,18000,140000</t>
   </si>
   <si>
     <t>10070</t>
@@ -1315,7 +1318,7 @@
     <t>梦魇鹿茸</t>
   </si>
   <si>
-    <t>200751,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504</t>
+    <t>200751,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
     <t>10071</t>
@@ -1333,7 +1336,7 @@
     <t>梦魇草帽</t>
   </si>
   <si>
-    <t>200752,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504</t>
+    <t>200752,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
     <t>10072</t>
@@ -1351,7 +1354,7 @@
     <t>梦魇猫爪</t>
   </si>
   <si>
-    <t>200753,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504</t>
+    <t>200753,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
     <t>10073</t>
@@ -1369,7 +1372,7 @@
     <t>梦魇花朵</t>
   </si>
   <si>
-    <t>200754,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504</t>
+    <t>200754,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
     <t>10074</t>
@@ -1387,10 +1390,10 @@
     <t>梦魇冰晶</t>
   </si>
   <si>
-    <t>200800,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210005</t>
-  </si>
-  <si>
-    <t>10,500,500,500,1250,2500,2500,5000,100000,200000,1000,18000,300000</t>
+    <t>200800,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210005,1009</t>
+  </si>
+  <si>
+    <t>10,500,500,500,1250,2500,2500,5000,100000,200000,1000,18000,300000,140000</t>
   </si>
   <si>
     <t>10075</t>
@@ -1408,7 +1411,7 @@
     <t>梦魇蝠翼</t>
   </si>
   <si>
-    <t>200801,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210006</t>
+    <t>200801,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210006,1009</t>
   </si>
   <si>
     <t>10076</t>
@@ -1426,7 +1429,7 @@
     <t>梦魇魂火</t>
   </si>
   <si>
-    <t>200802,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210007</t>
+    <t>200802,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210007,1009</t>
   </si>
   <si>
     <t>10077</t>
@@ -1444,7 +1447,7 @@
     <t>梦魇腐肉</t>
   </si>
   <si>
-    <t>200803,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210008</t>
+    <t>200803,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210008,1009</t>
   </si>
   <si>
     <t>10078</t>
@@ -1462,7 +1465,7 @@
     <t>梦魇蛇胆</t>
   </si>
   <si>
-    <t>200804,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210009</t>
+    <t>200804,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210009,1009</t>
   </si>
   <si>
     <t>10079</t>
@@ -1480,7 +1483,7 @@
     <t>梦魇狼爪</t>
   </si>
   <si>
-    <t>200850,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210010</t>
+    <t>200850,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210010,1009</t>
   </si>
   <si>
     <t>10080</t>
@@ -1498,7 +1501,7 @@
     <t>梦魇虫皮</t>
   </si>
   <si>
-    <t>200851,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210011</t>
+    <t>200851,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210011,1009</t>
   </si>
   <si>
     <t>10081</t>
@@ -1516,7 +1519,7 @@
     <t>梦魇鹰羽</t>
   </si>
   <si>
-    <t>200852,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210012</t>
+    <t>200852,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210012,1009</t>
   </si>
   <si>
     <t>10082</t>
@@ -1534,7 +1537,7 @@
     <t>梦魇虫角</t>
   </si>
   <si>
-    <t>200853,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210013</t>
+    <t>200853,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210013,1009</t>
   </si>
   <si>
     <t>10083</t>
@@ -1552,7 +1555,7 @@
     <t>梦魇蜈膏</t>
   </si>
   <si>
-    <t>200854,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210014</t>
+    <t>200854,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210014,1009</t>
   </si>
   <si>
     <t>10084</t>
@@ -1570,7 +1573,7 @@
     <t>梦魇虫心</t>
   </si>
   <si>
-    <t>200900,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210015</t>
+    <t>200900,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210015,1009</t>
   </si>
   <si>
     <t>10085</t>
@@ -1588,7 +1591,7 @@
     <t>梦魇龙皮</t>
   </si>
   <si>
-    <t>200901,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210016</t>
+    <t>200901,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210016,1009</t>
   </si>
   <si>
     <t>10086</t>
@@ -1606,7 +1609,7 @@
     <t>梦魇猪皮</t>
   </si>
   <si>
-    <t>200902,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210017</t>
+    <t>200902,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210017,1009</t>
   </si>
   <si>
     <t>10087</t>
@@ -1624,7 +1627,7 @@
     <t>梦魇猪心</t>
   </si>
   <si>
-    <t>200903,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210018</t>
+    <t>200903,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210018,1009</t>
   </si>
   <si>
     <t>10088</t>
@@ -1642,7 +1645,7 @@
     <t>梦魇蝎皮</t>
   </si>
   <si>
-    <t>200904,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210019</t>
+    <t>200904,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210019,1009</t>
   </si>
   <si>
     <t>10089</t>
@@ -1660,7 +1663,7 @@
     <t>噩梦宝甲</t>
   </si>
   <si>
-    <t>200950,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210020</t>
+    <t>200950,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210020,1009</t>
   </si>
   <si>
     <t>10090</t>
@@ -1678,7 +1681,7 @@
     <t>噩梦号角</t>
   </si>
   <si>
-    <t>200951,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210021</t>
+    <t>200951,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210021,1009</t>
   </si>
   <si>
     <t>10091</t>
@@ -1696,7 +1699,7 @@
     <t>噩梦雕像</t>
   </si>
   <si>
-    <t>200952,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210022</t>
+    <t>200952,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210022,1009</t>
   </si>
   <si>
     <t>10092</t>
@@ -1714,7 +1717,7 @@
     <t>噩梦神像</t>
   </si>
   <si>
-    <t>200953,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210023</t>
+    <t>200953,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210023,1009</t>
   </si>
   <si>
     <t>10093</t>
@@ -1732,7 +1735,7 @@
     <t>噩梦獠牙</t>
   </si>
   <si>
-    <t>200954,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210024</t>
+    <t>200954,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210024,1009</t>
   </si>
   <si>
     <t>10094</t>
@@ -1750,7 +1753,7 @@
     <t>噩梦树心</t>
   </si>
   <si>
-    <t>201000,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210025</t>
+    <t>201000,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210025,1009</t>
   </si>
   <si>
     <t>10095</t>
@@ -1768,7 +1771,7 @@
     <t>噩梦魔心</t>
   </si>
   <si>
-    <t>201001,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210026</t>
+    <t>201001,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210026,1009</t>
   </si>
   <si>
     <t>10096</t>
@@ -1786,7 +1789,7 @@
     <t>噩梦尸心</t>
   </si>
   <si>
-    <t>201002,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210027</t>
+    <t>201002,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210027,1009</t>
   </si>
   <si>
     <t>10097</t>
@@ -1804,7 +1807,7 @@
     <t>噩梦法杖</t>
   </si>
   <si>
-    <t>201003,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210028</t>
+    <t>201003,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210028,1009</t>
   </si>
   <si>
     <t>10098</t>
@@ -1822,7 +1825,7 @@
     <t>噩梦权杖</t>
   </si>
   <si>
-    <t>201004,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210029</t>
+    <t>201004,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210029,1009</t>
   </si>
   <si>
     <t>10099</t>
@@ -1840,7 +1843,7 @@
     <t>噩梦战锤</t>
   </si>
   <si>
-    <t>201050,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210030</t>
+    <t>201050,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210030,1009</t>
   </si>
   <si>
     <t>10100</t>
@@ -1858,7 +1861,7 @@
     <t>噩梦血核</t>
   </si>
   <si>
-    <t>201051,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210031</t>
+    <t>201051,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210031,1009</t>
   </si>
   <si>
     <t>10101</t>
@@ -1876,7 +1879,7 @@
     <t>噩梦魔核</t>
   </si>
   <si>
-    <t>201052,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210032</t>
+    <t>201052,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210032,1009</t>
   </si>
   <si>
     <t>10102</t>
@@ -1894,7 +1897,7 @@
     <t>噩梦龙甲</t>
   </si>
   <si>
-    <t>201053,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210033</t>
+    <t>201053,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210033,1009</t>
   </si>
   <si>
     <t>10103</t>
@@ -1912,7 +1915,7 @@
     <t>噩梦龙爪</t>
   </si>
   <si>
-    <t>201054,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210034</t>
+    <t>201054,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210034,1009</t>
   </si>
   <si>
     <t>10104</t>
@@ -1930,10 +1933,10 @@
     <t>金装</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210035</t>
-  </si>
-  <si>
-    <t>10,2500,1000,18000,600000</t>
+    <t>202001,300091,104,504,210035,1009</t>
+  </si>
+  <si>
+    <t>10,2500,1000,18000,600000,140000</t>
   </si>
   <si>
     <t>10105</t>
@@ -1951,7 +1954,7 @@
     <t>地狱鹿茸</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210036</t>
+    <t>202001,300091,104,504,210036,1009</t>
   </si>
   <si>
     <t>10106</t>
@@ -1969,7 +1972,7 @@
     <t>地狱草帽</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210037</t>
+    <t>202001,300091,104,504,210037,1009</t>
   </si>
   <si>
     <t>10107</t>
@@ -1987,7 +1990,7 @@
     <t>地狱猫爪</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210038</t>
+    <t>202001,300091,104,504,210038,1009</t>
   </si>
   <si>
     <t>10108</t>
@@ -2005,7 +2008,7 @@
     <t>地狱花朵</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210039</t>
+    <t>202001,300091,104,504,210039,1009</t>
   </si>
   <si>
     <t>10109</t>
@@ -2023,7 +2026,7 @@
     <t>地狱冰晶</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210040</t>
+    <t>202001,300091,104,504,210040,1009</t>
   </si>
   <si>
     <t>10110</t>
@@ -2041,7 +2044,7 @@
     <t>地狱蝠翼</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210041</t>
+    <t>202001,300091,104,504,210041,1009</t>
   </si>
   <si>
     <t>10111</t>
@@ -2059,7 +2062,7 @@
     <t>地狱魂火</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210042</t>
+    <t>202001,300091,104,504,210042,1009</t>
   </si>
   <si>
     <t>10112</t>
@@ -2077,7 +2080,7 @@
     <t>地狱腐肉</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210043</t>
+    <t>202001,300091,104,504,210043,1009</t>
   </si>
   <si>
     <t>10113</t>
@@ -2095,7 +2098,7 @@
     <t>地狱蛇胆</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210044</t>
+    <t>202001,300091,104,504,210044,1009</t>
   </si>
   <si>
     <t>10114</t>
@@ -2113,7 +2116,7 @@
     <t>地狱狼爪</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210045</t>
+    <t>202001,300091,104,504,210045,1009</t>
   </si>
   <si>
     <t>10115</t>
@@ -2131,7 +2134,7 @@
     <t>地狱虫皮</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210046</t>
+    <t>202001,300091,104,504,210046,1009</t>
   </si>
   <si>
     <t>10116</t>
@@ -2149,7 +2152,7 @@
     <t>地狱鹰羽</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210047</t>
+    <t>202001,300091,104,504,210047,1009</t>
   </si>
   <si>
     <t>10117</t>
@@ -2167,7 +2170,7 @@
     <t>地狱虫角</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210048</t>
+    <t>202001,300091,104,504,210048,1009</t>
   </si>
   <si>
     <t>10118</t>
@@ -2185,7 +2188,7 @@
     <t>地狱蜈膏</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210049</t>
+    <t>202001,300091,104,504,210049,1009</t>
   </si>
   <si>
     <t>10119</t>
@@ -2203,7 +2206,7 @@
     <t>地狱虫心</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210050</t>
+    <t>202001,300091,104,504,210050,1009</t>
   </si>
   <si>
     <t>10120</t>
@@ -2221,7 +2224,7 @@
     <t>地狱龙皮</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210051</t>
+    <t>202001,300091,104,504,210051,1009</t>
   </si>
   <si>
     <t>10121</t>
@@ -2239,7 +2242,7 @@
     <t>地狱猪皮</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210052</t>
+    <t>202001,300091,104,504,210052,1009</t>
   </si>
   <si>
     <t>10122</t>
@@ -2257,7 +2260,7 @@
     <t>地狱猪心</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210053</t>
+    <t>202001,300091,104,504,210053,1009</t>
   </si>
   <si>
     <t>10123</t>
@@ -2275,7 +2278,7 @@
     <t>地狱蝎皮</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210054</t>
+    <t>202001,300091,104,504,210054,1009</t>
   </si>
   <si>
     <t>10124</t>
@@ -2293,7 +2296,7 @@
     <t>地狱宝甲</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210055</t>
+    <t>202001,300091,104,504,210055,1009</t>
   </si>
   <si>
     <t>10125</t>
@@ -2311,7 +2314,7 @@
     <t>地狱号角</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210056</t>
+    <t>202001,300091,104,504,210056,1009</t>
   </si>
   <si>
     <t>10126</t>
@@ -2329,7 +2332,7 @@
     <t>地狱雕像</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210057</t>
+    <t>202001,300091,104,504,210057,1009</t>
   </si>
   <si>
     <t>10127</t>
@@ -2347,7 +2350,7 @@
     <t>地狱神像</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210058</t>
+    <t>202001,300091,104,504,210058,1009</t>
   </si>
   <si>
     <t>10128</t>
@@ -2365,7 +2368,7 @@
     <t>地狱獠牙</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210059</t>
+    <t>202001,300091,104,504,210059,1009</t>
   </si>
   <si>
     <t>10129</t>
@@ -2383,10 +2386,7 @@
     <t>地狱树心</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210060,2009</t>
-  </si>
-  <si>
-    <t>10,2500,1000,18000,600000,10000</t>
+    <t>202001,300091,104,504,210060,1009</t>
   </si>
   <si>
     <t>10130</t>
@@ -2404,7 +2404,7 @@
     <t>地狱魔心</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210061,2009</t>
+    <t>202001,300091,104,504,210061,1009</t>
   </si>
   <si>
     <t>10131</t>
@@ -2422,7 +2422,7 @@
     <t>地狱尸心</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210062,2009</t>
+    <t>202001,300091,104,504,210062,1009</t>
   </si>
   <si>
     <t>10132</t>
@@ -2440,7 +2440,7 @@
     <t>地狱法杖</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210063,2009</t>
+    <t>202001,300091,104,504,210063,1009</t>
   </si>
   <si>
     <t>10133</t>
@@ -2458,7 +2458,7 @@
     <t>地狱权杖</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210064,2009</t>
+    <t>202001,300091,104,504,210064,1009</t>
   </si>
   <si>
     <t>10134</t>
@@ -2479,7 +2479,7 @@
     <t>地狱战锤</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210065</t>
+    <t>202001,300091,104,504,210065,1009</t>
   </si>
   <si>
     <t>10135</t>
@@ -2497,7 +2497,7 @@
     <t>地狱血核</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210066</t>
+    <t>202001,300091,104,504,210066,1009</t>
   </si>
   <si>
     <t>10136</t>
@@ -2515,7 +2515,7 @@
     <t>地狱魔核</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210067</t>
+    <t>202001,300091,104,504,210067,1009</t>
   </si>
   <si>
     <t>10137</t>
@@ -2533,7 +2533,7 @@
     <t>地狱龙甲</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210068</t>
+    <t>202001,300091,104,504,210068,1009</t>
   </si>
   <si>
     <t>10138</t>
@@ -2551,7 +2551,7 @@
     <t>地狱龙爪</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210069</t>
+    <t>202001,300091,104,504,210069,1009</t>
   </si>
   <si>
     <t>10139</t>
@@ -3580,8 +3580,8 @@
     <col min="7" max="7" width="10.7545454545455" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.3727272727273" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.12727272727273" style="1" customWidth="1"/>
-    <col min="10" max="10" width="65.3727272727273" style="1" customWidth="1"/>
-    <col min="11" max="11" width="50.3727272727273" style="1" customWidth="1"/>
+    <col min="10" max="10" width="93.7272727272727" style="1" customWidth="1"/>
+    <col min="11" max="11" width="68.7272727272727" style="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="3" customWidth="1"/>
     <col min="13" max="13" width="45.2545454545455" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
@@ -5834,18 +5834,18 @@
         <v>412</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>322</v>
+        <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:12">
       <c r="C77" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E77" s="1">
         <v>3</v>
@@ -5854,30 +5854,30 @@
         <v>3</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I77" s="1">
         <v>750</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>322</v>
+        <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E78" s="1">
         <v>3</v>
@@ -5886,30 +5886,30 @@
         <v>3</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I78" s="1">
         <v>750</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>322</v>
+        <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E79" s="1">
         <v>3</v>
@@ -5918,30 +5918,30 @@
         <v>3</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I79" s="1">
         <v>750</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>322</v>
+        <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E80" s="1">
         <v>3</v>
@@ -5950,30 +5950,30 @@
         <v>3</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I80" s="1">
         <v>750</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>322</v>
+        <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E81" s="1">
         <v>3</v>
@@ -5982,30 +5982,30 @@
         <v>3</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I81" s="1">
         <v>800</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E82" s="1">
         <v>3</v>
@@ -6014,30 +6014,30 @@
         <v>3</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I82" s="1">
         <v>800</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E83" s="1">
         <v>3</v>
@@ -6046,30 +6046,30 @@
         <v>3</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I83" s="1">
         <v>800</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E84" s="1">
         <v>3</v>
@@ -6078,30 +6078,30 @@
         <v>3</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I84" s="1">
         <v>800</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E85" s="1">
         <v>3</v>
@@ -6110,30 +6110,30 @@
         <v>3</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I85" s="1">
         <v>800</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C86" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E86" s="1">
         <v>3</v>
@@ -6142,30 +6142,30 @@
         <v>3</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I86" s="1">
         <v>850</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C87" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E87" s="1">
         <v>3</v>
@@ -6174,30 +6174,30 @@
         <v>3</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I87" s="1">
         <v>850</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C88" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E88" s="1">
         <v>3</v>
@@ -6206,30 +6206,30 @@
         <v>3</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I88" s="1">
         <v>850</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C89" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E89" s="1">
         <v>3</v>
@@ -6238,30 +6238,30 @@
         <v>3</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I89" s="1">
         <v>850</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C90" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E90" s="1">
         <v>3</v>
@@ -6270,30 +6270,30 @@
         <v>3</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I90" s="1">
         <v>850</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C91" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E91" s="1">
         <v>3</v>
@@ -6302,30 +6302,30 @@
         <v>3</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I91" s="1">
         <v>900</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C92" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E92" s="1">
         <v>3</v>
@@ -6334,30 +6334,30 @@
         <v>3</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I92" s="1">
         <v>900</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C93" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E93" s="1">
         <v>3</v>
@@ -6366,30 +6366,30 @@
         <v>3</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I93" s="1">
         <v>900</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C94" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E94" s="1">
         <v>3</v>
@@ -6398,30 +6398,30 @@
         <v>3</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I94" s="1">
         <v>900</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C95" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E95" s="1">
         <v>3</v>
@@ -6430,30 +6430,30 @@
         <v>3</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I95" s="1">
         <v>900</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E96" s="1">
         <v>3</v>
@@ -6462,30 +6462,30 @@
         <v>3</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I96" s="1">
         <v>950</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E97" s="1">
         <v>3</v>
@@ -6494,30 +6494,30 @@
         <v>3</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I97" s="1">
         <v>950</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E98" s="1">
         <v>3</v>
@@ -6526,30 +6526,30 @@
         <v>3</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I98" s="1">
         <v>950</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E99" s="1">
         <v>3</v>
@@ -6558,30 +6558,30 @@
         <v>3</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I99" s="1">
         <v>950</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E100" s="1">
         <v>3</v>
@@ -6590,30 +6590,30 @@
         <v>3</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I100" s="1">
         <v>950</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E101" s="1">
         <v>3</v>
@@ -6622,30 +6622,30 @@
         <v>3</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I101" s="1">
         <v>1000</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E102" s="1">
         <v>3</v>
@@ -6654,30 +6654,30 @@
         <v>3</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I102" s="1">
         <v>1000</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E103" s="1">
         <v>3</v>
@@ -6686,30 +6686,30 @@
         <v>3</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I103" s="1">
         <v>1000</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E104" s="1">
         <v>3</v>
@@ -6718,30 +6718,30 @@
         <v>3</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I104" s="1">
         <v>1000</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E105" s="1">
         <v>3</v>
@@ -6750,30 +6750,30 @@
         <v>3</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I105" s="1">
         <v>1000</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C106" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E106" s="1">
         <v>3</v>
@@ -6782,30 +6782,30 @@
         <v>3</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I106" s="1">
         <v>1050</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C107" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E107" s="1">
         <v>3</v>
@@ -6814,30 +6814,30 @@
         <v>3</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="I107" s="1">
         <v>1050</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C108" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E108" s="1">
         <v>3</v>
@@ -6846,30 +6846,30 @@
         <v>3</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I108" s="1">
         <v>1050</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C109" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E109" s="1">
         <v>3</v>
@@ -6878,30 +6878,30 @@
         <v>3</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I109" s="1">
         <v>1050</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C110" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E110" s="1">
         <v>3</v>
@@ -6910,30 +6910,30 @@
         <v>3</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I110" s="1">
         <v>1050</v>
       </c>
       <c r="J110" s="7" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E111" s="1">
         <v>4</v>
@@ -6942,30 +6942,30 @@
         <v>4</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="I111" s="1">
         <v>0</v>
       </c>
       <c r="J111" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E112" s="1">
         <v>4</v>
@@ -6974,30 +6974,30 @@
         <v>4</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="I112" s="1">
         <v>0</v>
       </c>
       <c r="J112" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:12">
       <c r="C113" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E113" s="1">
         <v>4</v>
@@ -7006,30 +7006,30 @@
         <v>4</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="I113" s="1">
         <v>0</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E114" s="1">
         <v>4</v>
@@ -7038,30 +7038,30 @@
         <v>4</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="I114" s="1">
         <v>0</v>
       </c>
       <c r="J114" s="7" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E115" s="1">
         <v>4</v>
@@ -7070,30 +7070,30 @@
         <v>4</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="I115" s="1">
         <v>0</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E116" s="1">
         <v>4</v>
@@ -7102,30 +7102,30 @@
         <v>4</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I116" s="1">
         <v>0</v>
       </c>
       <c r="J116" s="7" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:12">
       <c r="C117" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E117" s="1">
         <v>4</v>
@@ -7134,30 +7134,30 @@
         <v>4</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I117" s="1">
         <v>0</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="3:12">
       <c r="C118" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E118" s="1">
         <v>4</v>
@@ -7166,30 +7166,30 @@
         <v>4</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="I118" s="1">
         <v>0</v>
       </c>
       <c r="J118" s="7" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:12">
       <c r="C119" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E119" s="1">
         <v>4</v>
@@ -7198,30 +7198,30 @@
         <v>4</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="I119" s="1">
         <v>0</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:12">
       <c r="C120" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E120" s="1">
         <v>4</v>
@@ -7230,30 +7230,30 @@
         <v>4</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="I120" s="1">
         <v>0</v>
       </c>
       <c r="J120" s="7" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C121" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
@@ -7262,30 +7262,30 @@
         <v>4</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="I121" s="1">
         <v>0</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C122" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
@@ -7294,30 +7294,30 @@
         <v>4</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="I122" s="1">
         <v>0</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C123" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
@@ -7326,30 +7326,30 @@
         <v>4</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="I123" s="1">
         <v>0</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C124" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
@@ -7358,30 +7358,30 @@
         <v>4</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="I124" s="1">
         <v>0</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C125" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
@@ -7390,30 +7390,30 @@
         <v>4</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I125" s="1">
         <v>0</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="K125" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C126" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
@@ -7422,30 +7422,30 @@
         <v>4</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I126" s="1">
         <v>0</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="K126" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C127" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
@@ -7454,30 +7454,30 @@
         <v>4</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I127" s="1">
         <v>0</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="K127" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C128" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
@@ -7486,30 +7486,30 @@
         <v>4</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I128" s="1">
         <v>0</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K128" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C129" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
@@ -7518,30 +7518,30 @@
         <v>4</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="I129" s="1">
         <v>0</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K129" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C130" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
@@ -7550,30 +7550,30 @@
         <v>4</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="I130" s="1">
         <v>0</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="K130" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="3:12">
       <c r="C131" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
@@ -7582,30 +7582,30 @@
         <v>4</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="I131" s="1">
         <v>0</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K131" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="3:12">
       <c r="C132" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
@@ -7614,30 +7614,30 @@
         <v>4</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="I132" s="1">
         <v>0</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="K132" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="3:12">
       <c r="C133" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
@@ -7646,30 +7646,30 @@
         <v>4</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="I133" s="1">
         <v>0</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="K133" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="3:12">
       <c r="C134" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
@@ -7678,30 +7678,30 @@
         <v>4</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="I134" s="1">
         <v>0</v>
       </c>
       <c r="J134" s="7" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="K134" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="3:12">
       <c r="C135" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
@@ -7710,30 +7710,30 @@
         <v>4</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="I135" s="1">
         <v>0</v>
       </c>
       <c r="J135" s="7" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K135" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="3:12">
       <c r="C136" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
@@ -7742,19 +7742,19 @@
         <v>4</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I136" s="1">
         <v>0</v>
       </c>
       <c r="J136" s="7" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="K136" s="7" t="s">
-        <v>775</v>
+        <v>625</v>
       </c>
       <c r="L136" s="1" t="s">
         <v>776</v>
@@ -7786,7 +7786,7 @@
         <v>781</v>
       </c>
       <c r="K137" s="7" t="s">
-        <v>775</v>
+        <v>625</v>
       </c>
       <c r="L137" s="1" t="s">
         <v>782</v>
@@ -7818,7 +7818,7 @@
         <v>787</v>
       </c>
       <c r="K138" s="7" t="s">
-        <v>775</v>
+        <v>625</v>
       </c>
       <c r="L138" s="1" t="s">
         <v>788</v>
@@ -7850,7 +7850,7 @@
         <v>793</v>
       </c>
       <c r="K139" s="7" t="s">
-        <v>775</v>
+        <v>625</v>
       </c>
       <c r="L139" s="1" t="s">
         <v>794</v>
@@ -7882,7 +7882,7 @@
         <v>799</v>
       </c>
       <c r="K140" s="7" t="s">
-        <v>775</v>
+        <v>625</v>
       </c>
       <c r="L140" s="1" t="s">
         <v>800</v>
@@ -7920,7 +7920,7 @@
         <v>806</v>
       </c>
       <c r="K141" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L141" s="1" t="s">
         <v>807</v>
@@ -7958,7 +7958,7 @@
         <v>812</v>
       </c>
       <c r="K142" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L142" s="1" t="s">
         <v>813</v>
@@ -7996,7 +7996,7 @@
         <v>818</v>
       </c>
       <c r="K143" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L143" s="1" t="s">
         <v>819</v>
@@ -8034,7 +8034,7 @@
         <v>824</v>
       </c>
       <c r="K144" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L144" s="1" t="s">
         <v>825</v>
@@ -8072,7 +8072,7 @@
         <v>830</v>
       </c>
       <c r="K145" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L145" s="1" t="s">
         <v>831</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -1300,7 +1300,7 @@
     <t>200750,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
-    <t>10,500,500,500,1250,2500,2500,5000,100000,200000,1000,18000,140000</t>
+    <t>10,500,500,500,1250,2500,2500,5000,100000,200000,1000,18000,100000</t>
   </si>
   <si>
     <t>10070</t>
@@ -1393,7 +1393,7 @@
     <t>200800,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210005,1009</t>
   </si>
   <si>
-    <t>10,500,500,500,1250,2500,2500,5000,100000,200000,1000,18000,300000,140000</t>
+    <t>10,500,500,500,1250,2500,2500,5000,100000,200000,1000,18000,300000,100000</t>
   </si>
   <si>
     <t>10075</t>
@@ -2733,12 +2733,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3571,19 +3571,19 @@
   <dimension ref="A3:M145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.25454545454545" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.25833333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.37272727272727" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3727272727273" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.75454545454545" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.87272727272727" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7545454545455" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.3727272727273" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.12727272727273" style="1" customWidth="1"/>
-    <col min="10" max="10" width="93.7272727272727" style="1" customWidth="1"/>
-    <col min="11" max="11" width="68.7272727272727" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.75833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7583333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="93.725" style="1" customWidth="1"/>
+    <col min="11" max="11" width="68.725" style="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="3" customWidth="1"/>
-    <col min="13" max="13" width="45.2545454545455" style="1" customWidth="1"/>
+    <col min="13" max="13" width="45.2583333333333" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -3569,22 +3569,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A3:M145"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.25833333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.75833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7583333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="93.725" style="1" customWidth="1"/>
-    <col min="11" max="11" width="68.725" style="1" customWidth="1"/>
-    <col min="12" max="12" width="6" style="3" customWidth="1"/>
-    <col min="13" max="13" width="45.2583333333333" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="1" max="3" width="9.25" style="1" customWidth="1"/>
+    <col min="4" max="10" width="11.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="70.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="39.375" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:13">

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -3569,13 +3569,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A3:M145"/>
-  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9.25" style="1" customWidth="1"/>
-    <col min="4" max="10" width="11.625" style="1" customWidth="1"/>
+    <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="4" max="9" width="11.6272727272727" style="1" customWidth="1"/>
+    <col min="10" max="10" width="75.8181818181818" style="1" customWidth="1"/>
     <col min="11" max="11" width="70.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="39.375" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="9.25" style="1" customWidth="1"/>
+    <col min="12" max="12" width="39.3727272727273" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9.25454545454545" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:13">

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="831">
   <si>
     <t>_Id</t>
   </si>
@@ -2462,9 +2462,6 @@
   </si>
   <si>
     <t>10134</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>1135</t>
@@ -3568,7 +3565,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M145"/>
+  <dimension ref="B3:M145"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
@@ -7880,18 +7877,12 @@
         <v>800</v>
       </c>
     </row>
-    <row r="141" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A141" s="1" t="s">
+    <row r="141" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C141" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="C141" s="1" t="s">
+      <c r="D141" s="1" t="s">
         <v>802</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>803</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
@@ -7900,36 +7891,30 @@
         <v>4</v>
       </c>
       <c r="G141" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="H141" s="1" t="s">
         <v>804</v>
-      </c>
-      <c r="H141" s="1" t="s">
-        <v>805</v>
       </c>
       <c r="I141" s="1">
         <v>0</v>
       </c>
       <c r="J141" s="7" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="K141" s="7" t="s">
         <v>625</v>
       </c>
       <c r="L141" s="1" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="142" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C142" s="1" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="142" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A142" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="C142" s="1" t="s">
+      <c r="D142" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>809</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
@@ -7938,36 +7923,30 @@
         <v>4</v>
       </c>
       <c r="G142" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="H142" s="1" t="s">
         <v>810</v>
-      </c>
-      <c r="H142" s="1" t="s">
-        <v>811</v>
       </c>
       <c r="I142" s="1">
         <v>0</v>
       </c>
       <c r="J142" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="K142" s="7" t="s">
         <v>625</v>
       </c>
       <c r="L142" s="1" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="143" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C143" s="1" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="143" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A143" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="C143" s="1" t="s">
+      <c r="D143" s="1" t="s">
         <v>814</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>815</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
@@ -7976,36 +7955,30 @@
         <v>4</v>
       </c>
       <c r="G143" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="H143" s="1" t="s">
         <v>816</v>
-      </c>
-      <c r="H143" s="1" t="s">
-        <v>817</v>
       </c>
       <c r="I143" s="1">
         <v>0</v>
       </c>
       <c r="J143" s="7" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="K143" s="7" t="s">
         <v>625</v>
       </c>
       <c r="L143" s="1" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="144" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C144" s="1" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="144" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A144" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="C144" s="1" t="s">
+      <c r="D144" s="1" t="s">
         <v>820</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>821</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
@@ -8014,36 +7987,30 @@
         <v>4</v>
       </c>
       <c r="G144" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="H144" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="H144" s="1" t="s">
-        <v>823</v>
       </c>
       <c r="I144" s="1">
         <v>0</v>
       </c>
       <c r="J144" s="7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="K144" s="7" t="s">
         <v>625</v>
       </c>
       <c r="L144" s="1" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="145" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C145" s="1" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="145" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A145" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="C145" s="1" t="s">
+      <c r="D145" s="1" t="s">
         <v>826</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>827</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
@@ -8052,22 +8019,22 @@
         <v>4</v>
       </c>
       <c r="G145" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="H145" s="1" t="s">
         <v>828</v>
-      </c>
-      <c r="H145" s="1" t="s">
-        <v>829</v>
       </c>
       <c r="I145" s="1">
         <v>0</v>
       </c>
       <c r="J145" s="7" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K145" s="7" t="s">
         <v>625</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="971">
   <si>
     <t>_Id</t>
   </si>
@@ -2552,6 +2552,426 @@
   </si>
   <si>
     <t>10139</t>
+  </si>
+  <si>
+    <t>1140</t>
+  </si>
+  <si>
+    <t>深渊小村</t>
+  </si>
+  <si>
+    <t>1450-1</t>
+  </si>
+  <si>
+    <t>暗金装备</t>
+  </si>
+  <si>
+    <t>1141</t>
+  </si>
+  <si>
+    <t>深渊村外</t>
+  </si>
+  <si>
+    <t>1450-2</t>
+  </si>
+  <si>
+    <t>深渊鹿茸</t>
+  </si>
+  <si>
+    <t>1142</t>
+  </si>
+  <si>
+    <t>深渊农场</t>
+  </si>
+  <si>
+    <t>1450-3</t>
+  </si>
+  <si>
+    <t>深渊草帽</t>
+  </si>
+  <si>
+    <t>1143</t>
+  </si>
+  <si>
+    <t>深渊老城</t>
+  </si>
+  <si>
+    <t>1450-4</t>
+  </si>
+  <si>
+    <t>深渊猫爪</t>
+  </si>
+  <si>
+    <t>1144</t>
+  </si>
+  <si>
+    <t>深渊森林</t>
+  </si>
+  <si>
+    <t>1450-5</t>
+  </si>
+  <si>
+    <t>深渊花朵</t>
+  </si>
+  <si>
+    <t>1145</t>
+  </si>
+  <si>
+    <t>深渊蝠洞</t>
+  </si>
+  <si>
+    <t>1500-1</t>
+  </si>
+  <si>
+    <t>深渊冰晶</t>
+  </si>
+  <si>
+    <t>1146</t>
+  </si>
+  <si>
+    <t>深渊骷髅洞</t>
+  </si>
+  <si>
+    <t>1500-2</t>
+  </si>
+  <si>
+    <t>深渊蝠翼</t>
+  </si>
+  <si>
+    <t>1147</t>
+  </si>
+  <si>
+    <t>深渊通道</t>
+  </si>
+  <si>
+    <t>1500-3</t>
+  </si>
+  <si>
+    <t>深渊魂火</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>深渊尸洞</t>
+  </si>
+  <si>
+    <t>1500-4</t>
+  </si>
+  <si>
+    <t>深渊腐肉</t>
+  </si>
+  <si>
+    <t>1149</t>
+  </si>
+  <si>
+    <t>深渊蛇谷</t>
+  </si>
+  <si>
+    <t>1500-5</t>
+  </si>
+  <si>
+    <t>深渊蛇胆</t>
+  </si>
+  <si>
+    <t>1150</t>
+  </si>
+  <si>
+    <t>深渊狼山</t>
+  </si>
+  <si>
+    <t>1550-1</t>
+  </si>
+  <si>
+    <t>深渊狼爪</t>
+  </si>
+  <si>
+    <t>1151</t>
+  </si>
+  <si>
+    <t>深渊沙洞</t>
+  </si>
+  <si>
+    <t>1550-2</t>
+  </si>
+  <si>
+    <t>深渊虫皮</t>
+  </si>
+  <si>
+    <t>1152</t>
+  </si>
+  <si>
+    <t>深渊鹰崖</t>
+  </si>
+  <si>
+    <t>1550-3</t>
+  </si>
+  <si>
+    <t>深渊鹰羽</t>
+  </si>
+  <si>
+    <t>1153</t>
+  </si>
+  <si>
+    <t>深渊虫谷</t>
+  </si>
+  <si>
+    <t>1550-4</t>
+  </si>
+  <si>
+    <t>深渊虫角</t>
+  </si>
+  <si>
+    <t>1154</t>
+  </si>
+  <si>
+    <t>深渊虫洞</t>
+  </si>
+  <si>
+    <t>1550-5</t>
+  </si>
+  <si>
+    <t>深渊蜈膏</t>
+  </si>
+  <si>
+    <t>1155</t>
+  </si>
+  <si>
+    <t>深渊虫穴</t>
+  </si>
+  <si>
+    <t>1600-1</t>
+  </si>
+  <si>
+    <t>深渊虫心</t>
+  </si>
+  <si>
+    <t>1156</t>
+  </si>
+  <si>
+    <t>深渊虫巢</t>
+  </si>
+  <si>
+    <t>1600-2</t>
+  </si>
+  <si>
+    <t>深渊龙皮</t>
+  </si>
+  <si>
+    <t>1157</t>
+  </si>
+  <si>
+    <t>深渊魔猪厅</t>
+  </si>
+  <si>
+    <t>1600-3</t>
+  </si>
+  <si>
+    <t>深渊猪皮</t>
+  </si>
+  <si>
+    <t>1158</t>
+  </si>
+  <si>
+    <t>深渊魔猪殿</t>
+  </si>
+  <si>
+    <t>1600-4</t>
+  </si>
+  <si>
+    <t>深渊猪心</t>
+  </si>
+  <si>
+    <t>1159</t>
+  </si>
+  <si>
+    <t>深渊桃源</t>
+  </si>
+  <si>
+    <t>1600-5</t>
+  </si>
+  <si>
+    <t>深渊蝎皮</t>
+  </si>
+  <si>
+    <t>1160</t>
+  </si>
+  <si>
+    <t>深渊魔禁地</t>
+  </si>
+  <si>
+    <t>1650-1</t>
+  </si>
+  <si>
+    <t>深渊宝甲</t>
+  </si>
+  <si>
+    <t>1161</t>
+  </si>
+  <si>
+    <t>深渊魔神殿</t>
+  </si>
+  <si>
+    <t>1650-2</t>
+  </si>
+  <si>
+    <t>深渊号角</t>
+  </si>
+  <si>
+    <t>1162</t>
+  </si>
+  <si>
+    <t>深渊邪禁地</t>
+  </si>
+  <si>
+    <t>1650-3</t>
+  </si>
+  <si>
+    <t>深渊雕像</t>
+  </si>
+  <si>
+    <t>1163</t>
+  </si>
+  <si>
+    <t>深渊邪魔殿</t>
+  </si>
+  <si>
+    <t>1650-4</t>
+  </si>
+  <si>
+    <t>深渊神像</t>
+  </si>
+  <si>
+    <t>1164</t>
+  </si>
+  <si>
+    <t>深渊封魔殿</t>
+  </si>
+  <si>
+    <t>1650-5</t>
+  </si>
+  <si>
+    <t>深渊獠牙</t>
+  </si>
+  <si>
+    <t>1165</t>
+  </si>
+  <si>
+    <t>深渊烈焰殿</t>
+  </si>
+  <si>
+    <t>1700-1</t>
+  </si>
+  <si>
+    <t>深渊树心</t>
+  </si>
+  <si>
+    <t>1166</t>
+  </si>
+  <si>
+    <t>深渊封邪殿</t>
+  </si>
+  <si>
+    <t>1700-2</t>
+  </si>
+  <si>
+    <t>深渊魔心</t>
+  </si>
+  <si>
+    <t>1167</t>
+  </si>
+  <si>
+    <t>深渊尸魔殿</t>
+  </si>
+  <si>
+    <t>1700-3</t>
+  </si>
+  <si>
+    <t>深渊尸心</t>
+  </si>
+  <si>
+    <t>1168</t>
+  </si>
+  <si>
+    <t>深渊骨魔殿</t>
+  </si>
+  <si>
+    <t>1700-4</t>
+  </si>
+  <si>
+    <t>深渊法杖</t>
+  </si>
+  <si>
+    <t>1169</t>
+  </si>
+  <si>
+    <t>深渊魔牛殿</t>
+  </si>
+  <si>
+    <t>1700-5</t>
+  </si>
+  <si>
+    <t>深渊权杖</t>
+  </si>
+  <si>
+    <t>1170</t>
+  </si>
+  <si>
+    <t>深渊水龙谷</t>
+  </si>
+  <si>
+    <t>1750-1</t>
+  </si>
+  <si>
+    <t>深渊战锤</t>
+  </si>
+  <si>
+    <t>1171</t>
+  </si>
+  <si>
+    <t>深渊土龙谷</t>
+  </si>
+  <si>
+    <t>1750-2</t>
+  </si>
+  <si>
+    <t>深渊血核</t>
+  </si>
+  <si>
+    <t>1172</t>
+  </si>
+  <si>
+    <t>深渊毒龙谷</t>
+  </si>
+  <si>
+    <t>1750-3</t>
+  </si>
+  <si>
+    <t>深渊魔核</t>
+  </si>
+  <si>
+    <t>1173</t>
+  </si>
+  <si>
+    <t>深渊火龙谷</t>
+  </si>
+  <si>
+    <t>1750-4</t>
+  </si>
+  <si>
+    <t>深渊龙甲</t>
+  </si>
+  <si>
+    <t>1174</t>
+  </si>
+  <si>
+    <t>深渊冰龙谷</t>
+  </si>
+  <si>
+    <t>1750-5</t>
+  </si>
+  <si>
+    <t>深渊龙爪</t>
   </si>
 </sst>
 </file>
@@ -3565,15 +3985,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:M145"/>
-  <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
+  <dimension ref="B3:M180"/>
+  <sheetFormatPr defaultColWidth="9.25833333333333" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
-    <col min="4" max="9" width="11.6272727272727" style="1" customWidth="1"/>
-    <col min="10" max="10" width="75.8181818181818" style="1" customWidth="1"/>
+    <col min="1" max="3" width="9.25833333333333" style="1" customWidth="1"/>
+    <col min="4" max="9" width="11.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="75.8166666666667" style="1" customWidth="1"/>
     <col min="11" max="11" width="70.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="39.3727272727273" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="12" max="12" width="39.375" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9.25833333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:13">
@@ -8037,12 +8457,1132 @@
         <v>830</v>
       </c>
     </row>
+    <row r="146" customHeight="1" spans="3:12">
+      <c r="C146" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="E146" s="1">
+        <v>5</v>
+      </c>
+      <c r="F146" s="1">
+        <v>5</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="I146" s="1">
+        <v>0</v>
+      </c>
+      <c r="J146" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="K146" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L146" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="3:12">
+      <c r="C147" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="E147" s="1">
+        <v>5</v>
+      </c>
+      <c r="F147" s="1">
+        <v>5</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="I147" s="1">
+        <v>0</v>
+      </c>
+      <c r="J147" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="K147" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L147" s="1" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="3:12">
+      <c r="C148" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="E148" s="1">
+        <v>5</v>
+      </c>
+      <c r="F148" s="1">
+        <v>5</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="I148" s="1">
+        <v>0</v>
+      </c>
+      <c r="J148" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="K148" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L148" s="1" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="3:12">
+      <c r="C149" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="E149" s="1">
+        <v>5</v>
+      </c>
+      <c r="F149" s="1">
+        <v>5</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="I149" s="1">
+        <v>0</v>
+      </c>
+      <c r="J149" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="K149" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="3:12">
+      <c r="C150" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="E150" s="1">
+        <v>5</v>
+      </c>
+      <c r="F150" s="1">
+        <v>5</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="I150" s="1">
+        <v>0</v>
+      </c>
+      <c r="J150" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="K150" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="3:12">
+      <c r="C151" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="E151" s="1">
+        <v>5</v>
+      </c>
+      <c r="F151" s="1">
+        <v>5</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="I151" s="1">
+        <v>0</v>
+      </c>
+      <c r="J151" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="K151" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L151" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="3:12">
+      <c r="C152" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="E152" s="1">
+        <v>5</v>
+      </c>
+      <c r="F152" s="1">
+        <v>5</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="I152" s="1">
+        <v>0</v>
+      </c>
+      <c r="J152" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="K152" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L152" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="3:12">
+      <c r="C153" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="E153" s="1">
+        <v>5</v>
+      </c>
+      <c r="F153" s="1">
+        <v>5</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="I153" s="1">
+        <v>0</v>
+      </c>
+      <c r="J153" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="K153" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="3:12">
+      <c r="C154" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="E154" s="1">
+        <v>5</v>
+      </c>
+      <c r="F154" s="1">
+        <v>5</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="I154" s="1">
+        <v>0</v>
+      </c>
+      <c r="J154" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="K154" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L154" s="1" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="3:12">
+      <c r="C155" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="E155" s="1">
+        <v>5</v>
+      </c>
+      <c r="F155" s="1">
+        <v>5</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="I155" s="1">
+        <v>0</v>
+      </c>
+      <c r="J155" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="K155" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L155" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="156" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C156" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="E156" s="1">
+        <v>5</v>
+      </c>
+      <c r="F156" s="1">
+        <v>5</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="I156" s="1">
+        <v>0</v>
+      </c>
+      <c r="J156" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="K156" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L156" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="157" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C157" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="E157" s="1">
+        <v>5</v>
+      </c>
+      <c r="F157" s="1">
+        <v>5</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="I157" s="1">
+        <v>0</v>
+      </c>
+      <c r="J157" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="K157" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L157" s="1" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="158" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C158" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="E158" s="1">
+        <v>5</v>
+      </c>
+      <c r="F158" s="1">
+        <v>5</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="I158" s="1">
+        <v>0</v>
+      </c>
+      <c r="J158" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="K158" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L158" s="1" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="159" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C159" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="E159" s="1">
+        <v>5</v>
+      </c>
+      <c r="F159" s="1">
+        <v>5</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="I159" s="1">
+        <v>0</v>
+      </c>
+      <c r="J159" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="K159" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L159" s="1" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="160" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C160" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="E160" s="1">
+        <v>5</v>
+      </c>
+      <c r="F160" s="1">
+        <v>5</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="I160" s="1">
+        <v>0</v>
+      </c>
+      <c r="J160" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="K160" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L160" s="1" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="161" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C161" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="E161" s="1">
+        <v>5</v>
+      </c>
+      <c r="F161" s="1">
+        <v>5</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="I161" s="1">
+        <v>0</v>
+      </c>
+      <c r="J161" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="K161" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L161" s="1" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="162" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C162" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="E162" s="1">
+        <v>5</v>
+      </c>
+      <c r="F162" s="1">
+        <v>5</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="I162" s="1">
+        <v>0</v>
+      </c>
+      <c r="J162" s="7" t="s">
+        <v>721</v>
+      </c>
+      <c r="K162" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L162" s="1" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="163" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C163" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="E163" s="1">
+        <v>5</v>
+      </c>
+      <c r="F163" s="1">
+        <v>5</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="I163" s="1">
+        <v>0</v>
+      </c>
+      <c r="J163" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="K163" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L163" s="1" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="164" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C164" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="E164" s="1">
+        <v>5</v>
+      </c>
+      <c r="F164" s="1">
+        <v>5</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="I164" s="1">
+        <v>0</v>
+      </c>
+      <c r="J164" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="K164" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L164" s="1" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="165" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C165" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="E165" s="1">
+        <v>5</v>
+      </c>
+      <c r="F165" s="1">
+        <v>5</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="I165" s="1">
+        <v>0</v>
+      </c>
+      <c r="J165" s="7" t="s">
+        <v>739</v>
+      </c>
+      <c r="K165" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L165" s="1" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" spans="3:12">
+      <c r="C166" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="E166" s="1">
+        <v>5</v>
+      </c>
+      <c r="F166" s="1">
+        <v>5</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="I166" s="1">
+        <v>0</v>
+      </c>
+      <c r="J166" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="K166" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L166" s="1" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="3:12">
+      <c r="C167" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="E167" s="1">
+        <v>5</v>
+      </c>
+      <c r="F167" s="1">
+        <v>5</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="I167" s="1">
+        <v>0</v>
+      </c>
+      <c r="J167" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="K167" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L167" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" spans="3:12">
+      <c r="C168" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="E168" s="1">
+        <v>5</v>
+      </c>
+      <c r="F168" s="1">
+        <v>5</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="I168" s="1">
+        <v>0</v>
+      </c>
+      <c r="J168" s="7" t="s">
+        <v>757</v>
+      </c>
+      <c r="K168" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L168" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" spans="3:12">
+      <c r="C169" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="E169" s="1">
+        <v>5</v>
+      </c>
+      <c r="F169" s="1">
+        <v>5</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="I169" s="1">
+        <v>0</v>
+      </c>
+      <c r="J169" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="K169" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L169" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" spans="3:12">
+      <c r="C170" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="E170" s="1">
+        <v>5</v>
+      </c>
+      <c r="F170" s="1">
+        <v>5</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="I170" s="1">
+        <v>0</v>
+      </c>
+      <c r="J170" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="K170" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L170" s="1" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" spans="3:12">
+      <c r="C171" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="E171" s="1">
+        <v>5</v>
+      </c>
+      <c r="F171" s="1">
+        <v>5</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="I171" s="1">
+        <v>0</v>
+      </c>
+      <c r="J171" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="K171" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L171" s="1" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" spans="3:12">
+      <c r="C172" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="E172" s="1">
+        <v>5</v>
+      </c>
+      <c r="F172" s="1">
+        <v>5</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="I172" s="1">
+        <v>0</v>
+      </c>
+      <c r="J172" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="K172" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L172" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" spans="3:12">
+      <c r="C173" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="E173" s="1">
+        <v>5</v>
+      </c>
+      <c r="F173" s="1">
+        <v>5</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="I173" s="1">
+        <v>0</v>
+      </c>
+      <c r="J173" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="K173" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L173" s="1" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" spans="3:12">
+      <c r="C174" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E174" s="1">
+        <v>5</v>
+      </c>
+      <c r="F174" s="1">
+        <v>5</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="I174" s="1">
+        <v>0</v>
+      </c>
+      <c r="J174" s="7" t="s">
+        <v>793</v>
+      </c>
+      <c r="K174" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L174" s="1" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" spans="3:12">
+      <c r="C175" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="E175" s="1">
+        <v>5</v>
+      </c>
+      <c r="F175" s="1">
+        <v>5</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="H175" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="I175" s="1">
+        <v>0</v>
+      </c>
+      <c r="J175" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="K175" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L175" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="176" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C176" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="E176" s="1">
+        <v>5</v>
+      </c>
+      <c r="F176" s="1">
+        <v>5</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="I176" s="1">
+        <v>0</v>
+      </c>
+      <c r="J176" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="K176" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L176" s="1" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="177" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C177" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="E177" s="1">
+        <v>5</v>
+      </c>
+      <c r="F177" s="1">
+        <v>5</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="I177" s="1">
+        <v>0</v>
+      </c>
+      <c r="J177" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="K177" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L177" s="1" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="178" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C178" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="E178" s="1">
+        <v>5</v>
+      </c>
+      <c r="F178" s="1">
+        <v>5</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="I178" s="1">
+        <v>0</v>
+      </c>
+      <c r="J178" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="K178" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L178" s="1" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="179" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C179" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="E179" s="1">
+        <v>5</v>
+      </c>
+      <c r="F179" s="1">
+        <v>5</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="I179" s="1">
+        <v>0</v>
+      </c>
+      <c r="J179" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="K179" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L179" s="1" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="180" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C180" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="E180" s="1">
+        <v>5</v>
+      </c>
+      <c r="F180" s="1">
+        <v>5</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="I180" s="1">
+        <v>0</v>
+      </c>
+      <c r="J180" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="K180" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L180" s="1" t="s">
+        <v>830</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C3:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C144 C145:C180 C181:C1048576" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="980">
   <si>
     <t>_Id</t>
   </si>
@@ -2566,6 +2566,12 @@
     <t>暗金装备</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210070,1009</t>
+  </si>
+  <si>
+    <t>10,2500,1000,18000,600000,100000</t>
+  </si>
+  <si>
     <t>1141</t>
   </si>
   <si>
@@ -2614,6 +2620,9 @@
     <t>深渊花朵</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>1145</t>
   </si>
   <si>
@@ -2626,6 +2635,9 @@
     <t>深渊冰晶</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210071,1009</t>
+  </si>
+  <si>
     <t>1146</t>
   </si>
   <si>
@@ -2686,6 +2698,9 @@
     <t>深渊狼爪</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210072,1009</t>
+  </si>
+  <si>
     <t>1151</t>
   </si>
   <si>
@@ -2746,6 +2761,9 @@
     <t>深渊虫心</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210073,1009</t>
+  </si>
+  <si>
     <t>1156</t>
   </si>
   <si>
@@ -2806,6 +2824,9 @@
     <t>深渊宝甲</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210074,1009</t>
+  </si>
+  <si>
     <t>1161</t>
   </si>
   <si>
@@ -2866,6 +2887,9 @@
     <t>深渊树心</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210075,1009</t>
+  </si>
+  <si>
     <t>1166</t>
   </si>
   <si>
@@ -2924,6 +2948,9 @@
   </si>
   <si>
     <t>深渊战锤</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210076,1009</t>
   </si>
   <si>
     <t>1171</t>
@@ -3161,12 +3188,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -3491,7 +3524,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3515,16 +3548,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -3533,101 +3566,103 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3985,115 +4020,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:M180"/>
+  <dimension ref="A3:M180"/>
   <sheetFormatPr defaultColWidth="9.25833333333333" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25833333333333" style="1" customWidth="1"/>
     <col min="4" max="9" width="11.625" style="1" customWidth="1"/>
     <col min="10" max="10" width="75.8166666666667" style="1" customWidth="1"/>
     <col min="11" max="11" width="70.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="39.375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="39.375" style="4" customWidth="1"/>
     <col min="13" max="16384" width="9.25833333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:13">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="4"/>
+      <c r="M3" s="5"/>
     </row>
     <row r="4" customHeight="1" spans="3:13">
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="4"/>
+      <c r="M4" s="5"/>
     </row>
     <row r="5" customHeight="1" spans="3:13">
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="4"/>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" customHeight="1" spans="3:12">
       <c r="C6" s="1" t="s">
@@ -5298,10 +5333,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="6" t="s">
+      <c r="J46" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="6" t="s">
+      <c r="K46" s="7" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -5327,10 +5362,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="6" t="s">
+      <c r="J47" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="6" t="s">
+      <c r="K47" s="7" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -5356,10 +5391,10 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="6" t="s">
+      <c r="J48" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="6" t="s">
+      <c r="K48" s="7" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
@@ -5385,10 +5420,10 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="6" t="s">
+      <c r="J49" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="6" t="s">
+      <c r="K49" s="7" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
@@ -5414,10 +5449,10 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="6" t="s">
+      <c r="J50" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="6" t="s">
+      <c r="K50" s="7" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
@@ -5446,10 +5481,10 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="6" t="s">
+      <c r="J51" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="6" t="s">
+      <c r="K51" s="7" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
@@ -5475,10 +5510,10 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="6" t="s">
+      <c r="J52" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="6" t="s">
+      <c r="K52" s="7" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -5504,10 +5539,10 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="6" t="s">
+      <c r="J53" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="6" t="s">
+      <c r="K53" s="7" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
@@ -5533,10 +5568,10 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="6" t="s">
+      <c r="J54" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="6" t="s">
+      <c r="K54" s="7" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
@@ -5562,10 +5597,10 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="6" t="s">
+      <c r="J55" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="6" t="s">
+      <c r="K55" s="7" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -5594,10 +5629,10 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="6" t="s">
+      <c r="J56" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="6" t="s">
+      <c r="K56" s="7" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
@@ -5626,10 +5661,10 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="6" t="s">
+      <c r="J57" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="6" t="s">
+      <c r="K57" s="7" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
@@ -5658,10 +5693,10 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="6" t="s">
+      <c r="J58" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="6" t="s">
+      <c r="K58" s="7" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -5690,10 +5725,10 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="6" t="s">
+      <c r="J59" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="6" t="s">
+      <c r="K59" s="7" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
@@ -5722,10 +5757,10 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="6" t="s">
+      <c r="J60" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="6" t="s">
+      <c r="K60" s="7" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -5755,10 +5790,10 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="7" t="s">
+      <c r="J61" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="7" t="s">
+      <c r="K61" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -5788,10 +5823,10 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="7" t="s">
+      <c r="J62" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="7" t="s">
+      <c r="K62" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -5821,10 +5856,10 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="7" t="s">
+      <c r="J63" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="7" t="s">
+      <c r="K63" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
@@ -5854,10 +5889,10 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="7" t="s">
+      <c r="J64" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="7" t="s">
+      <c r="K64" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
@@ -5887,10 +5922,10 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="7" t="s">
+      <c r="J65" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="7" t="s">
+      <c r="K65" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
@@ -5919,10 +5954,10 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="7" t="s">
+      <c r="J66" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="7" t="s">
+      <c r="K66" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
@@ -5951,10 +5986,10 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="7" t="s">
+      <c r="J67" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="7" t="s">
+      <c r="K67" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
@@ -5983,10 +6018,10 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="7" t="s">
+      <c r="J68" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="7" t="s">
+      <c r="K68" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -6015,10 +6050,10 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="7" t="s">
+      <c r="J69" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="7" t="s">
+      <c r="K69" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
@@ -6047,10 +6082,10 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="7" t="s">
+      <c r="J70" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="7" t="s">
+      <c r="K70" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
@@ -6079,10 +6114,10 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="7" t="s">
+      <c r="J71" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="7" t="s">
+      <c r="K71" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -6111,10 +6146,10 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="7" t="s">
+      <c r="J72" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="7" t="s">
+      <c r="K72" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -6143,10 +6178,10 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="7" t="s">
+      <c r="J73" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="7" t="s">
+      <c r="K73" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -6175,10 +6210,10 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="7" t="s">
+      <c r="J74" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="7" t="s">
+      <c r="K74" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
@@ -6207,10 +6242,10 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="7" t="s">
+      <c r="J75" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="7" t="s">
+      <c r="K75" s="8" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
@@ -6239,10 +6274,10 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="7" t="s">
+      <c r="J76" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="7" t="s">
+      <c r="K76" s="8" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
@@ -6271,10 +6306,10 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="7" t="s">
+      <c r="J77" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="7" t="s">
+      <c r="K77" s="8" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
@@ -6303,10 +6338,10 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="7" t="s">
+      <c r="J78" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="7" t="s">
+      <c r="K78" s="8" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
@@ -6335,10 +6370,10 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="7" t="s">
+      <c r="J79" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="7" t="s">
+      <c r="K79" s="8" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
@@ -6367,10 +6402,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="7" t="s">
+      <c r="J80" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="7" t="s">
+      <c r="K80" s="8" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -6399,10 +6434,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="7" t="s">
+      <c r="J81" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="7" t="s">
+      <c r="K81" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -6431,10 +6466,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="7" t="s">
+      <c r="J82" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="7" t="s">
+      <c r="K82" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -6463,10 +6498,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="7" t="s">
+      <c r="J83" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="7" t="s">
+      <c r="K83" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -6495,10 +6530,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="7" t="s">
+      <c r="J84" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="7" t="s">
+      <c r="K84" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -6527,10 +6562,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="7" t="s">
+      <c r="J85" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="7" t="s">
+      <c r="K85" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -6559,10 +6594,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="7" t="s">
+      <c r="J86" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="7" t="s">
+      <c r="K86" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -6591,10 +6626,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="7" t="s">
+      <c r="J87" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="7" t="s">
+      <c r="K87" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -6623,10 +6658,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="7" t="s">
+      <c r="J88" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="7" t="s">
+      <c r="K88" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -6655,10 +6690,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="7" t="s">
+      <c r="J89" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="7" t="s">
+      <c r="K89" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -6687,10 +6722,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="7" t="s">
+      <c r="J90" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="7" t="s">
+      <c r="K90" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -6719,10 +6754,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="7" t="s">
+      <c r="J91" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="7" t="s">
+      <c r="K91" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -6751,10 +6786,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="7" t="s">
+      <c r="J92" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="7" t="s">
+      <c r="K92" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -6783,10 +6818,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="7" t="s">
+      <c r="J93" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="7" t="s">
+      <c r="K93" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -6815,10 +6850,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="7" t="s">
+      <c r="J94" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="7" t="s">
+      <c r="K94" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -6847,10 +6882,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="7" t="s">
+      <c r="J95" s="8" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="7" t="s">
+      <c r="K95" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -6879,10 +6914,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="7" t="s">
+      <c r="J96" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="7" t="s">
+      <c r="K96" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -6911,10 +6946,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="7" t="s">
+      <c r="J97" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="7" t="s">
+      <c r="K97" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -6943,10 +6978,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="7" t="s">
+      <c r="J98" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="7" t="s">
+      <c r="K98" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -6975,10 +7010,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="7" t="s">
+      <c r="J99" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="7" t="s">
+      <c r="K99" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -7007,10 +7042,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="7" t="s">
+      <c r="J100" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="7" t="s">
+      <c r="K100" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -7039,10 +7074,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="7" t="s">
+      <c r="J101" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="7" t="s">
+      <c r="K101" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -7071,10 +7106,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="7" t="s">
+      <c r="J102" s="8" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="7" t="s">
+      <c r="K102" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -7103,10 +7138,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="7" t="s">
+      <c r="J103" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="7" t="s">
+      <c r="K103" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -7135,10 +7170,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="7" t="s">
+      <c r="J104" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="7" t="s">
+      <c r="K104" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -7167,10 +7202,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="7" t="s">
+      <c r="J105" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="7" t="s">
+      <c r="K105" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -7199,10 +7234,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="7" t="s">
+      <c r="J106" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="7" t="s">
+      <c r="K106" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -7231,10 +7266,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="7" t="s">
+      <c r="J107" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="7" t="s">
+      <c r="K107" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -7263,10 +7298,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="7" t="s">
+      <c r="J108" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="7" t="s">
+      <c r="K108" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -7295,10 +7330,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="7" t="s">
+      <c r="J109" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="7" t="s">
+      <c r="K109" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -7327,10 +7362,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="7" t="s">
+      <c r="J110" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="7" t="s">
+      <c r="K110" s="8" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -7359,10 +7394,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="7" t="s">
+      <c r="J111" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="7" t="s">
+      <c r="K111" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -7391,10 +7426,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="7" t="s">
+      <c r="J112" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="7" t="s">
+      <c r="K112" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -7423,10 +7458,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="7" t="s">
+      <c r="J113" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="7" t="s">
+      <c r="K113" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -7455,10 +7490,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="7" t="s">
+      <c r="J114" s="8" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="7" t="s">
+      <c r="K114" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -7487,10 +7522,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="7" t="s">
+      <c r="J115" s="8" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="7" t="s">
+      <c r="K115" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -7519,10 +7554,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="7" t="s">
+      <c r="J116" s="8" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="7" t="s">
+      <c r="K116" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -7551,10 +7586,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="7" t="s">
+      <c r="J117" s="8" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="7" t="s">
+      <c r="K117" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -7583,10 +7618,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="7" t="s">
+      <c r="J118" s="8" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="7" t="s">
+      <c r="K118" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -7615,10 +7650,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="7" t="s">
+      <c r="J119" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="7" t="s">
+      <c r="K119" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -7647,10 +7682,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="7" t="s">
+      <c r="J120" s="8" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="7" t="s">
+      <c r="K120" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -7679,10 +7714,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="7" t="s">
+      <c r="J121" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="7" t="s">
+      <c r="K121" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -7711,10 +7746,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="7" t="s">
+      <c r="J122" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="7" t="s">
+      <c r="K122" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -7743,10 +7778,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="7" t="s">
+      <c r="J123" s="8" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="7" t="s">
+      <c r="K123" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -7775,10 +7810,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="7" t="s">
+      <c r="J124" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="7" t="s">
+      <c r="K124" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -7807,10 +7842,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="7" t="s">
+      <c r="J125" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="7" t="s">
+      <c r="K125" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -7839,10 +7874,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="7" t="s">
+      <c r="J126" s="8" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="7" t="s">
+      <c r="K126" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -7871,10 +7906,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="7" t="s">
+      <c r="J127" s="8" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="7" t="s">
+      <c r="K127" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -7903,10 +7938,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="7" t="s">
+      <c r="J128" s="8" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="7" t="s">
+      <c r="K128" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -7935,10 +7970,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="7" t="s">
+      <c r="J129" s="8" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="7" t="s">
+      <c r="K129" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -7967,10 +8002,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="7" t="s">
+      <c r="J130" s="8" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="7" t="s">
+      <c r="K130" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -7999,10 +8034,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="7" t="s">
+      <c r="J131" s="8" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="7" t="s">
+      <c r="K131" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -8031,10 +8066,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="7" t="s">
+      <c r="J132" s="8" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="7" t="s">
+      <c r="K132" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -8063,10 +8098,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="7" t="s">
+      <c r="J133" s="8" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="7" t="s">
+      <c r="K133" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -8095,10 +8130,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="7" t="s">
+      <c r="J134" s="8" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="7" t="s">
+      <c r="K134" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -8127,10 +8162,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="7" t="s">
+      <c r="J135" s="8" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="7" t="s">
+      <c r="K135" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -8159,10 +8194,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="7" t="s">
+      <c r="J136" s="8" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="7" t="s">
+      <c r="K136" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -8191,10 +8226,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="7" t="s">
+      <c r="J137" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="K137" s="7" t="s">
+      <c r="K137" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -8223,10 +8258,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="7" t="s">
+      <c r="J138" s="8" t="s">
         <v>787</v>
       </c>
-      <c r="K138" s="7" t="s">
+      <c r="K138" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -8255,10 +8290,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="7" t="s">
+      <c r="J139" s="8" t="s">
         <v>793</v>
       </c>
-      <c r="K139" s="7" t="s">
+      <c r="K139" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -8287,10 +8322,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="7" t="s">
+      <c r="J140" s="8" t="s">
         <v>799</v>
       </c>
-      <c r="K140" s="7" t="s">
+      <c r="K140" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -8319,10 +8354,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="7" t="s">
+      <c r="J141" s="8" t="s">
         <v>805</v>
       </c>
-      <c r="K141" s="7" t="s">
+      <c r="K141" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -8351,10 +8386,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="7" t="s">
+      <c r="J142" s="8" t="s">
         <v>811</v>
       </c>
-      <c r="K142" s="7" t="s">
+      <c r="K142" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -8383,10 +8418,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="7" t="s">
+      <c r="J143" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="K143" s="7" t="s">
+      <c r="K143" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -8415,10 +8450,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="7" t="s">
+      <c r="J144" s="8" t="s">
         <v>823</v>
       </c>
-      <c r="K144" s="7" t="s">
+      <c r="K144" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -8447,54 +8482,54 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="7" t="s">
+      <c r="J145" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="K145" s="7" t="s">
+      <c r="K145" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L145" s="1" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="146" customHeight="1" spans="3:12">
-      <c r="C146" s="1" t="s">
+    <row r="146" s="3" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C146" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="D146" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="E146" s="1">
+      <c r="E146" s="3">
         <v>5</v>
       </c>
-      <c r="F146" s="1">
+      <c r="F146" s="3">
         <v>5</v>
       </c>
-      <c r="G146" s="1" t="s">
+      <c r="G146" s="3" t="s">
         <v>833</v>
       </c>
-      <c r="H146" s="1" t="s">
+      <c r="H146" s="3" t="s">
         <v>834</v>
       </c>
-      <c r="I146" s="1">
+      <c r="I146" s="3">
         <v>0</v>
       </c>
-      <c r="J146" s="7" t="s">
-        <v>624</v>
-      </c>
-      <c r="K146" s="7" t="s">
-        <v>625</v>
-      </c>
-      <c r="L146" s="1" t="s">
+      <c r="J146" s="9" t="s">
+        <v>835</v>
+      </c>
+      <c r="K146" s="9" t="s">
+        <v>836</v>
+      </c>
+      <c r="L146" s="3" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="E147" s="1">
         <v>5</v>
@@ -8503,18 +8538,18 @@
         <v>5</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="7" t="s">
-        <v>631</v>
-      </c>
-      <c r="K147" s="7" t="s">
+      <c r="J147" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="K147" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L147" s="1" t="s">
@@ -8523,10 +8558,10 @@
     </row>
     <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="E148" s="1">
         <v>5</v>
@@ -8535,18 +8570,18 @@
         <v>5</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="K148" s="7" t="s">
+      <c r="J148" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="K148" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L148" s="1" t="s">
@@ -8555,10 +8590,10 @@
     </row>
     <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E149" s="1">
         <v>5</v>
@@ -8567,18 +8602,18 @@
         <v>5</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="K149" s="7" t="s">
+      <c r="J149" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="K149" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L149" s="1" t="s">
@@ -8587,10 +8622,10 @@
     </row>
     <row r="150" customHeight="1" spans="3:12">
       <c r="C150" s="1" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="E150" s="1">
         <v>5</v>
@@ -8599,30 +8634,36 @@
         <v>5</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="7" t="s">
-        <v>649</v>
-      </c>
-      <c r="K150" s="7" t="s">
+      <c r="J150" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="K150" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L150" s="1" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="3:12">
+    <row r="151" customHeight="1" spans="1:12">
+      <c r="A151" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C151" s="1" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
@@ -8631,30 +8672,36 @@
         <v>5</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="7" t="s">
-        <v>655</v>
-      </c>
-      <c r="K151" s="7" t="s">
+      <c r="J151" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="K151" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L151" s="1" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="3:12">
+    <row r="152" customHeight="1" spans="1:12">
+      <c r="A152" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C152" s="1" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
@@ -8663,30 +8710,36 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="7" t="s">
-        <v>661</v>
-      </c>
-      <c r="K152" s="7" t="s">
+      <c r="J152" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="K152" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L152" s="1" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="3:12">
+    <row r="153" customHeight="1" spans="1:12">
+      <c r="A153" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C153" s="1" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
@@ -8695,30 +8748,36 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="7" t="s">
-        <v>667</v>
-      </c>
-      <c r="K153" s="7" t="s">
+      <c r="J153" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="K153" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L153" s="1" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="3:12">
+    <row r="154" customHeight="1" spans="1:12">
+      <c r="A154" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C154" s="1" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
@@ -8727,30 +8786,36 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="7" t="s">
-        <v>673</v>
-      </c>
-      <c r="K154" s="7" t="s">
+      <c r="J154" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="K154" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L154" s="1" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="155" customHeight="1" spans="3:12">
+    <row r="155" customHeight="1" spans="1:12">
+      <c r="A155" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C155" s="1" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
@@ -8759,30 +8824,36 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="7" t="s">
-        <v>679</v>
-      </c>
-      <c r="K155" s="7" t="s">
+      <c r="J155" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="K155" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L155" s="1" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="156" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="156" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A156" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C156" s="1" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
@@ -8791,30 +8862,36 @@
         <v>5</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="7" t="s">
-        <v>685</v>
-      </c>
-      <c r="K156" s="7" t="s">
+      <c r="J156" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="K156" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L156" s="1" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="157" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="157" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A157" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C157" s="1" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
@@ -8823,30 +8900,36 @@
         <v>5</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="7" t="s">
-        <v>691</v>
-      </c>
-      <c r="K157" s="7" t="s">
+      <c r="J157" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="K157" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L157" s="1" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="158" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="158" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A158" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C158" s="1" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
@@ -8855,30 +8938,36 @@
         <v>5</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="7" t="s">
-        <v>697</v>
-      </c>
-      <c r="K158" s="7" t="s">
+      <c r="J158" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="K158" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L158" s="1" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="159" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="159" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A159" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C159" s="1" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
@@ -8887,30 +8976,36 @@
         <v>5</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="7" t="s">
-        <v>703</v>
-      </c>
-      <c r="K159" s="7" t="s">
+      <c r="J159" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="K159" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="160" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="160" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A160" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C160" s="1" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
@@ -8919,30 +9014,36 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="7" t="s">
-        <v>709</v>
-      </c>
-      <c r="K160" s="7" t="s">
+      <c r="J160" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="K160" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L160" s="1" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="161" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="161" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A161" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C161" s="1" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
@@ -8951,30 +9052,36 @@
         <v>5</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="7" t="s">
-        <v>715</v>
-      </c>
-      <c r="K161" s="7" t="s">
+      <c r="J161" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="K161" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L161" s="1" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="162" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="162" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A162" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C162" s="1" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
@@ -8983,30 +9090,36 @@
         <v>5</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="7" t="s">
-        <v>721</v>
-      </c>
-      <c r="K162" s="7" t="s">
+      <c r="J162" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="K162" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L162" s="1" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="163" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="163" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A163" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C163" s="1" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9015,30 +9128,36 @@
         <v>5</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="7" t="s">
-        <v>727</v>
-      </c>
-      <c r="K163" s="7" t="s">
+      <c r="J163" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="K163" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L163" s="1" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="164" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="164" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A164" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C164" s="1" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
@@ -9047,30 +9166,36 @@
         <v>5</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="7" t="s">
-        <v>733</v>
-      </c>
-      <c r="K164" s="7" t="s">
+      <c r="J164" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="K164" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L164" s="1" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="165" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="165" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A165" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C165" s="1" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -9079,30 +9204,36 @@
         <v>5</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="7" t="s">
-        <v>739</v>
-      </c>
-      <c r="K165" s="7" t="s">
+      <c r="J165" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="K165" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L165" s="1" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="166" customHeight="1" spans="3:12">
+    <row r="166" customHeight="1" spans="1:12">
+      <c r="A166" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C166" s="1" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
@@ -9111,30 +9242,36 @@
         <v>5</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="7" t="s">
-        <v>745</v>
-      </c>
-      <c r="K166" s="7" t="s">
+      <c r="J166" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="K166" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L166" s="1" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="167" customHeight="1" spans="3:12">
+    <row r="167" customHeight="1" spans="1:12">
+      <c r="A167" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C167" s="1" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
@@ -9143,30 +9280,36 @@
         <v>5</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="7" t="s">
-        <v>751</v>
-      </c>
-      <c r="K167" s="7" t="s">
+      <c r="J167" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="K167" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L167" s="1" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="168" customHeight="1" spans="3:12">
+    <row r="168" customHeight="1" spans="1:12">
+      <c r="A168" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C168" s="1" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -9175,30 +9318,36 @@
         <v>5</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="K168" s="7" t="s">
+      <c r="J168" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="K168" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L168" s="1" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="169" customHeight="1" spans="3:12">
+    <row r="169" customHeight="1" spans="1:12">
+      <c r="A169" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C169" s="1" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
@@ -9207,30 +9356,36 @@
         <v>5</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="7" t="s">
-        <v>763</v>
-      </c>
-      <c r="K169" s="7" t="s">
+      <c r="J169" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="K169" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L169" s="1" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="170" customHeight="1" spans="3:12">
+    <row r="170" customHeight="1" spans="1:12">
+      <c r="A170" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C170" s="1" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -9239,30 +9394,36 @@
         <v>5</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="7" t="s">
-        <v>769</v>
-      </c>
-      <c r="K170" s="7" t="s">
+      <c r="J170" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="K170" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L170" s="1" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="171" customHeight="1" spans="3:12">
+    <row r="171" customHeight="1" spans="1:12">
+      <c r="A171" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C171" s="1" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -9271,30 +9432,36 @@
         <v>5</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="K171" s="7" t="s">
+      <c r="J171" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="K171" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L171" s="1" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="172" customHeight="1" spans="3:12">
+    <row r="172" customHeight="1" spans="1:12">
+      <c r="A172" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C172" s="1" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
@@ -9303,30 +9470,36 @@
         <v>5</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="7" t="s">
-        <v>781</v>
-      </c>
-      <c r="K172" s="7" t="s">
+      <c r="J172" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="K172" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L172" s="1" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="173" customHeight="1" spans="3:12">
+    <row r="173" customHeight="1" spans="1:12">
+      <c r="A173" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C173" s="1" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
@@ -9335,30 +9508,36 @@
         <v>5</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="7" t="s">
-        <v>787</v>
-      </c>
-      <c r="K173" s="7" t="s">
+      <c r="J173" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="K173" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L173" s="1" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="174" customHeight="1" spans="3:12">
+    <row r="174" customHeight="1" spans="1:12">
+      <c r="A174" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C174" s="1" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -9367,30 +9546,36 @@
         <v>5</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="7" t="s">
-        <v>793</v>
-      </c>
-      <c r="K174" s="7" t="s">
+      <c r="J174" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="K174" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L174" s="1" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="175" customHeight="1" spans="3:12">
+    <row r="175" customHeight="1" spans="1:12">
+      <c r="A175" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C175" s="1" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
@@ -9399,30 +9584,36 @@
         <v>5</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="7" t="s">
-        <v>799</v>
-      </c>
-      <c r="K175" s="7" t="s">
+      <c r="J175" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="K175" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L175" s="1" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="176" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="176" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A176" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C176" s="1" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
@@ -9431,30 +9622,36 @@
         <v>5</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="7" t="s">
-        <v>805</v>
-      </c>
-      <c r="K176" s="7" t="s">
+      <c r="J176" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="K176" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L176" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="177" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="177" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A177" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C177" s="1" t="s">
-        <v>955</v>
+        <v>964</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
@@ -9463,30 +9660,36 @@
         <v>5</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>957</v>
+        <v>966</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="K177" s="7" t="s">
+      <c r="J177" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="K177" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L177" s="1" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="178" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="178" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A178" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C178" s="1" t="s">
-        <v>959</v>
+        <v>968</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>960</v>
+        <v>969</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
@@ -9495,30 +9698,36 @@
         <v>5</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>962</v>
+        <v>971</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="7" t="s">
-        <v>817</v>
-      </c>
-      <c r="K178" s="7" t="s">
+      <c r="J178" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="K178" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L178" s="1" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="179" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="179" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A179" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C179" s="1" t="s">
-        <v>963</v>
+        <v>972</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>964</v>
+        <v>973</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -9527,30 +9736,36 @@
         <v>5</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>965</v>
+        <v>974</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>966</v>
+        <v>975</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="K179" s="7" t="s">
+      <c r="J179" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="K179" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L179" s="1" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="180" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="180" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A180" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C180" s="1" t="s">
-        <v>967</v>
+        <v>976</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>968</v>
+        <v>977</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
@@ -9559,18 +9774,18 @@
         <v>5</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>969</v>
+        <v>978</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>970</v>
+        <v>979</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="7" t="s">
-        <v>829</v>
-      </c>
-      <c r="K180" s="7" t="s">
+      <c r="J180" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="K180" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L180" s="1" t="s">
@@ -9582,7 +9797,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C144 C145:C180 C181:C1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C1048576" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="979">
   <si>
     <t>_Id</t>
   </si>
@@ -2618,9 +2618,6 @@
   </si>
   <si>
     <t>深渊花朵</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>1145</t>
@@ -4020,15 +4017,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M180"/>
-  <sheetFormatPr defaultColWidth="9.25833333333333" defaultRowHeight="18" customHeight="1"/>
+  <dimension ref="B3:M180"/>
+  <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9.25833333333333" style="1" customWidth="1"/>
-    <col min="4" max="9" width="11.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="75.8166666666667" style="1" customWidth="1"/>
+    <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="4" max="9" width="11.6272727272727" style="1" customWidth="1"/>
+    <col min="10" max="10" width="75.8181818181818" style="1" customWidth="1"/>
     <col min="11" max="11" width="70.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="39.375" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9.25833333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="39.3727272727273" style="4" customWidth="1"/>
+    <col min="13" max="16384" width="9.25454545454545" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:13">
@@ -8652,18 +8649,12 @@
         <v>650</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="1:12">
-      <c r="A151" s="1" t="s">
+    <row r="151" customHeight="1" spans="3:12">
+      <c r="C151" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="C151" s="1" t="s">
+      <c r="D151" s="1" t="s">
         <v>854</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>855</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
@@ -8672,16 +8663,16 @@
         <v>5</v>
       </c>
       <c r="G151" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="H151" s="1" t="s">
         <v>856</v>
-      </c>
-      <c r="H151" s="1" t="s">
-        <v>857</v>
       </c>
       <c r="I151" s="1">
         <v>0</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K151" s="8" t="s">
         <v>625</v>
@@ -8690,18 +8681,12 @@
         <v>656</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="1:12">
-      <c r="A152" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="152" customHeight="1" spans="3:12">
       <c r="C152" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>859</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>860</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
@@ -8710,16 +8695,16 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="H152" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="H152" s="1" t="s">
-        <v>862</v>
       </c>
       <c r="I152" s="1">
         <v>0</v>
       </c>
       <c r="J152" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K152" s="8" t="s">
         <v>625</v>
@@ -8728,18 +8713,12 @@
         <v>662</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="1:12">
-      <c r="A153" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="153" customHeight="1" spans="3:12">
       <c r="C153" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>864</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
@@ -8748,16 +8727,16 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="H153" s="1" t="s">
         <v>865</v>
-      </c>
-      <c r="H153" s="1" t="s">
-        <v>866</v>
       </c>
       <c r="I153" s="1">
         <v>0</v>
       </c>
       <c r="J153" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K153" s="8" t="s">
         <v>625</v>
@@ -8766,18 +8745,12 @@
         <v>668</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="1:12">
-      <c r="A154" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="154" customHeight="1" spans="3:12">
       <c r="C154" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>867</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>868</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
@@ -8786,16 +8759,16 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="H154" s="1" t="s">
         <v>869</v>
-      </c>
-      <c r="H154" s="1" t="s">
-        <v>870</v>
       </c>
       <c r="I154" s="1">
         <v>0</v>
       </c>
       <c r="J154" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K154" s="8" t="s">
         <v>625</v>
@@ -8804,18 +8777,12 @@
         <v>674</v>
       </c>
     </row>
-    <row r="155" customHeight="1" spans="1:12">
-      <c r="A155" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="155" customHeight="1" spans="3:12">
       <c r="C155" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>871</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>872</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
@@ -8824,16 +8791,16 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="H155" s="1" t="s">
         <v>873</v>
-      </c>
-      <c r="H155" s="1" t="s">
-        <v>874</v>
       </c>
       <c r="I155" s="1">
         <v>0</v>
       </c>
       <c r="J155" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K155" s="8" t="s">
         <v>625</v>
@@ -8842,18 +8809,12 @@
         <v>680</v>
       </c>
     </row>
-    <row r="156" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A156" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="156" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C156" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>875</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>876</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
@@ -8862,16 +8823,16 @@
         <v>5</v>
       </c>
       <c r="G156" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="H156" s="1" t="s">
         <v>877</v>
-      </c>
-      <c r="H156" s="1" t="s">
-        <v>878</v>
       </c>
       <c r="I156" s="1">
         <v>0</v>
       </c>
       <c r="J156" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K156" s="8" t="s">
         <v>625</v>
@@ -8880,18 +8841,12 @@
         <v>686</v>
       </c>
     </row>
-    <row r="157" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A157" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="157" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C157" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>880</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>881</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
@@ -8900,16 +8855,16 @@
         <v>5</v>
       </c>
       <c r="G157" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="H157" s="1" t="s">
         <v>882</v>
-      </c>
-      <c r="H157" s="1" t="s">
-        <v>883</v>
       </c>
       <c r="I157" s="1">
         <v>0</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K157" s="8" t="s">
         <v>625</v>
@@ -8918,18 +8873,12 @@
         <v>692</v>
       </c>
     </row>
-    <row r="158" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A158" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="158" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C158" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>884</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>885</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
@@ -8938,16 +8887,16 @@
         <v>5</v>
       </c>
       <c r="G158" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="H158" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="H158" s="1" t="s">
-        <v>887</v>
       </c>
       <c r="I158" s="1">
         <v>0</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K158" s="8" t="s">
         <v>625</v>
@@ -8956,18 +8905,12 @@
         <v>698</v>
       </c>
     </row>
-    <row r="159" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A159" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="159" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C159" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>888</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>889</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
@@ -8976,16 +8919,16 @@
         <v>5</v>
       </c>
       <c r="G159" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="H159" s="1" t="s">
         <v>890</v>
-      </c>
-      <c r="H159" s="1" t="s">
-        <v>891</v>
       </c>
       <c r="I159" s="1">
         <v>0</v>
       </c>
       <c r="J159" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K159" s="8" t="s">
         <v>625</v>
@@ -8994,18 +8937,12 @@
         <v>704</v>
       </c>
     </row>
-    <row r="160" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A160" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="160" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C160" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>892</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>893</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
@@ -9014,16 +8951,16 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="H160" s="1" t="s">
         <v>894</v>
-      </c>
-      <c r="H160" s="1" t="s">
-        <v>895</v>
       </c>
       <c r="I160" s="1">
         <v>0</v>
       </c>
       <c r="J160" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K160" s="8" t="s">
         <v>625</v>
@@ -9032,18 +8969,12 @@
         <v>710</v>
       </c>
     </row>
-    <row r="161" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A161" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="161" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C161" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>896</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>897</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
@@ -9052,16 +8983,16 @@
         <v>5</v>
       </c>
       <c r="G161" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="H161" s="1" t="s">
         <v>898</v>
-      </c>
-      <c r="H161" s="1" t="s">
-        <v>899</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K161" s="8" t="s">
         <v>625</v>
@@ -9070,18 +9001,12 @@
         <v>716</v>
       </c>
     </row>
-    <row r="162" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A162" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="162" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C162" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>901</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>902</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
@@ -9090,16 +9015,16 @@
         <v>5</v>
       </c>
       <c r="G162" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="H162" s="1" t="s">
         <v>903</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>904</v>
       </c>
       <c r="I162" s="1">
         <v>0</v>
       </c>
       <c r="J162" s="8" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K162" s="8" t="s">
         <v>625</v>
@@ -9108,18 +9033,12 @@
         <v>722</v>
       </c>
     </row>
-    <row r="163" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A163" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="163" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C163" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>905</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>906</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9128,16 +9047,16 @@
         <v>5</v>
       </c>
       <c r="G163" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="H163" s="1" t="s">
         <v>907</v>
-      </c>
-      <c r="H163" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="I163" s="1">
         <v>0</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K163" s="8" t="s">
         <v>625</v>
@@ -9146,18 +9065,12 @@
         <v>728</v>
       </c>
     </row>
-    <row r="164" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A164" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="164" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C164" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>909</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>910</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
@@ -9166,16 +9079,16 @@
         <v>5</v>
       </c>
       <c r="G164" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="H164" s="1" t="s">
         <v>911</v>
-      </c>
-      <c r="H164" s="1" t="s">
-        <v>912</v>
       </c>
       <c r="I164" s="1">
         <v>0</v>
       </c>
       <c r="J164" s="8" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K164" s="8" t="s">
         <v>625</v>
@@ -9184,18 +9097,12 @@
         <v>734</v>
       </c>
     </row>
-    <row r="165" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A165" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="165" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C165" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>913</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>914</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -9204,16 +9111,16 @@
         <v>5</v>
       </c>
       <c r="G165" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="H165" s="1" t="s">
         <v>915</v>
-      </c>
-      <c r="H165" s="1" t="s">
-        <v>916</v>
       </c>
       <c r="I165" s="1">
         <v>0</v>
       </c>
       <c r="J165" s="8" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K165" s="8" t="s">
         <v>625</v>
@@ -9222,18 +9129,12 @@
         <v>740</v>
       </c>
     </row>
-    <row r="166" customHeight="1" spans="1:12">
-      <c r="A166" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="166" customHeight="1" spans="3:12">
       <c r="C166" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="D166" s="2" t="s">
         <v>917</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>918</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
@@ -9242,16 +9143,16 @@
         <v>5</v>
       </c>
       <c r="G166" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="H166" s="1" t="s">
         <v>919</v>
-      </c>
-      <c r="H166" s="1" t="s">
-        <v>920</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
       </c>
       <c r="J166" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="K166" s="8" t="s">
         <v>625</v>
@@ -9260,18 +9161,12 @@
         <v>746</v>
       </c>
     </row>
-    <row r="167" customHeight="1" spans="1:12">
-      <c r="A167" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="167" customHeight="1" spans="3:12">
       <c r="C167" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>922</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>923</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
@@ -9280,16 +9175,16 @@
         <v>5</v>
       </c>
       <c r="G167" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="H167" s="1" t="s">
         <v>924</v>
-      </c>
-      <c r="H167" s="1" t="s">
-        <v>925</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
       </c>
       <c r="J167" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="K167" s="8" t="s">
         <v>625</v>
@@ -9298,18 +9193,12 @@
         <v>752</v>
       </c>
     </row>
-    <row r="168" customHeight="1" spans="1:12">
-      <c r="A168" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="168" customHeight="1" spans="3:12">
       <c r="C168" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="D168" s="2" t="s">
         <v>926</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>927</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -9318,16 +9207,16 @@
         <v>5</v>
       </c>
       <c r="G168" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="H168" s="1" t="s">
         <v>928</v>
-      </c>
-      <c r="H168" s="1" t="s">
-        <v>929</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="K168" s="8" t="s">
         <v>625</v>
@@ -9336,18 +9225,12 @@
         <v>758</v>
       </c>
     </row>
-    <row r="169" customHeight="1" spans="1:12">
-      <c r="A169" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="169" customHeight="1" spans="3:12">
       <c r="C169" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="D169" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>931</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
@@ -9356,16 +9239,16 @@
         <v>5</v>
       </c>
       <c r="G169" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="H169" s="1" t="s">
         <v>932</v>
-      </c>
-      <c r="H169" s="1" t="s">
-        <v>933</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="K169" s="8" t="s">
         <v>625</v>
@@ -9374,18 +9257,12 @@
         <v>764</v>
       </c>
     </row>
-    <row r="170" customHeight="1" spans="1:12">
-      <c r="A170" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="170" customHeight="1" spans="3:12">
       <c r="C170" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="D170" s="2" t="s">
         <v>934</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>935</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -9394,16 +9271,16 @@
         <v>5</v>
       </c>
       <c r="G170" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="H170" s="1" t="s">
         <v>936</v>
-      </c>
-      <c r="H170" s="1" t="s">
-        <v>937</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
       </c>
       <c r="J170" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="K170" s="8" t="s">
         <v>625</v>
@@ -9412,18 +9289,12 @@
         <v>770</v>
       </c>
     </row>
-    <row r="171" customHeight="1" spans="1:12">
-      <c r="A171" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="171" customHeight="1" spans="3:12">
       <c r="C171" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>938</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>939</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -9432,16 +9303,16 @@
         <v>5</v>
       </c>
       <c r="G171" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="H171" s="1" t="s">
         <v>940</v>
-      </c>
-      <c r="H171" s="1" t="s">
-        <v>941</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
       </c>
       <c r="J171" s="8" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="K171" s="8" t="s">
         <v>625</v>
@@ -9450,18 +9321,12 @@
         <v>776</v>
       </c>
     </row>
-    <row r="172" customHeight="1" spans="1:12">
-      <c r="A172" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="172" customHeight="1" spans="3:12">
       <c r="C172" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>943</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>944</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
@@ -9470,16 +9335,16 @@
         <v>5</v>
       </c>
       <c r="G172" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="H172" s="1" t="s">
         <v>945</v>
-      </c>
-      <c r="H172" s="1" t="s">
-        <v>946</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
       </c>
       <c r="J172" s="8" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="K172" s="8" t="s">
         <v>625</v>
@@ -9488,18 +9353,12 @@
         <v>782</v>
       </c>
     </row>
-    <row r="173" customHeight="1" spans="1:12">
-      <c r="A173" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="173" customHeight="1" spans="3:12">
       <c r="C173" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>947</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>948</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
@@ -9508,16 +9367,16 @@
         <v>5</v>
       </c>
       <c r="G173" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="H173" s="1" t="s">
         <v>949</v>
-      </c>
-      <c r="H173" s="1" t="s">
-        <v>950</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
       </c>
       <c r="J173" s="8" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="K173" s="8" t="s">
         <v>625</v>
@@ -9526,18 +9385,12 @@
         <v>788</v>
       </c>
     </row>
-    <row r="174" customHeight="1" spans="1:12">
-      <c r="A174" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="174" customHeight="1" spans="3:12">
       <c r="C174" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>951</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>952</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -9546,16 +9399,16 @@
         <v>5</v>
       </c>
       <c r="G174" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="H174" s="1" t="s">
         <v>953</v>
-      </c>
-      <c r="H174" s="1" t="s">
-        <v>954</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
       </c>
       <c r="J174" s="8" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="K174" s="8" t="s">
         <v>625</v>
@@ -9564,18 +9417,12 @@
         <v>794</v>
       </c>
     </row>
-    <row r="175" customHeight="1" spans="1:12">
-      <c r="A175" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="175" customHeight="1" spans="3:12">
       <c r="C175" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>955</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>956</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
@@ -9584,16 +9431,16 @@
         <v>5</v>
       </c>
       <c r="G175" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="H175" s="1" t="s">
         <v>957</v>
-      </c>
-      <c r="H175" s="1" t="s">
-        <v>958</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="K175" s="8" t="s">
         <v>625</v>
@@ -9602,18 +9449,12 @@
         <v>800</v>
       </c>
     </row>
-    <row r="176" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A176" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="176" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C176" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>959</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>960</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
@@ -9622,16 +9463,16 @@
         <v>5</v>
       </c>
       <c r="G176" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="H176" s="1" t="s">
         <v>961</v>
-      </c>
-      <c r="H176" s="1" t="s">
-        <v>962</v>
       </c>
       <c r="I176" s="1">
         <v>0</v>
       </c>
       <c r="J176" s="8" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="K176" s="8" t="s">
         <v>625</v>
@@ -9640,18 +9481,12 @@
         <v>806</v>
       </c>
     </row>
-    <row r="177" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A177" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="177" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C177" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>964</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>965</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
@@ -9660,16 +9495,16 @@
         <v>5</v>
       </c>
       <c r="G177" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="H177" s="1" t="s">
         <v>966</v>
-      </c>
-      <c r="H177" s="1" t="s">
-        <v>967</v>
       </c>
       <c r="I177" s="1">
         <v>0</v>
       </c>
       <c r="J177" s="8" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="K177" s="8" t="s">
         <v>625</v>
@@ -9678,18 +9513,12 @@
         <v>812</v>
       </c>
     </row>
-    <row r="178" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A178" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="178" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C178" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>968</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>969</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
@@ -9698,16 +9527,16 @@
         <v>5</v>
       </c>
       <c r="G178" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="H178" s="1" t="s">
         <v>970</v>
-      </c>
-      <c r="H178" s="1" t="s">
-        <v>971</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
       </c>
       <c r="J178" s="8" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="K178" s="8" t="s">
         <v>625</v>
@@ -9716,18 +9545,12 @@
         <v>818</v>
       </c>
     </row>
-    <row r="179" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A179" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="179" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C179" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>972</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>973</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -9736,16 +9559,16 @@
         <v>5</v>
       </c>
       <c r="G179" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="H179" s="1" t="s">
         <v>974</v>
-      </c>
-      <c r="H179" s="1" t="s">
-        <v>975</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
       </c>
       <c r="J179" s="8" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="K179" s="8" t="s">
         <v>625</v>
@@ -9754,18 +9577,12 @@
         <v>824</v>
       </c>
     </row>
-    <row r="180" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A180" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>853</v>
-      </c>
+    <row r="180" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C180" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>976</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>977</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
@@ -9774,16 +9591,16 @@
         <v>5</v>
       </c>
       <c r="G180" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="H180" s="1" t="s">
         <v>978</v>
-      </c>
-      <c r="H180" s="1" t="s">
-        <v>979</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
       </c>
       <c r="J180" s="8" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="K180" s="8" t="s">
         <v>625</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="980">
   <si>
     <t>_Id</t>
   </si>
@@ -2618,6 +2618,9 @@
   </si>
   <si>
     <t>深渊花朵</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>1145</t>
@@ -4017,15 +4020,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:M180"/>
-  <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
+  <dimension ref="A3:M180"/>
+  <sheetFormatPr defaultColWidth="9.25833333333333" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
-    <col min="4" max="9" width="11.6272727272727" style="1" customWidth="1"/>
-    <col min="10" max="10" width="75.8181818181818" style="1" customWidth="1"/>
+    <col min="1" max="3" width="9.25833333333333" style="1" customWidth="1"/>
+    <col min="4" max="9" width="11.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="75.8166666666667" style="1" customWidth="1"/>
     <col min="11" max="11" width="70.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="39.3727272727273" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="12" max="12" width="39.375" style="4" customWidth="1"/>
+    <col min="13" max="16384" width="9.25833333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:13">
@@ -8649,12 +8652,18 @@
         <v>650</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="3:12">
+    <row r="151" customHeight="1" spans="1:12">
+      <c r="A151" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C151" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
@@ -8663,16 +8672,16 @@
         <v>5</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="I151" s="1">
         <v>0</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K151" s="8" t="s">
         <v>625</v>
@@ -8681,12 +8690,18 @@
         <v>656</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="3:12">
+    <row r="152" customHeight="1" spans="1:12">
+      <c r="A152" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C152" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
@@ -8695,16 +8710,16 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I152" s="1">
         <v>0</v>
       </c>
       <c r="J152" s="8" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K152" s="8" t="s">
         <v>625</v>
@@ -8713,12 +8728,18 @@
         <v>662</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="3:12">
+    <row r="153" customHeight="1" spans="1:12">
+      <c r="A153" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C153" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
@@ -8727,16 +8748,16 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I153" s="1">
         <v>0</v>
       </c>
       <c r="J153" s="8" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K153" s="8" t="s">
         <v>625</v>
@@ -8745,12 +8766,18 @@
         <v>668</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="3:12">
+    <row r="154" customHeight="1" spans="1:12">
+      <c r="A154" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C154" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
@@ -8759,16 +8786,16 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="I154" s="1">
         <v>0</v>
       </c>
       <c r="J154" s="8" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K154" s="8" t="s">
         <v>625</v>
@@ -8777,12 +8804,18 @@
         <v>674</v>
       </c>
     </row>
-    <row r="155" customHeight="1" spans="3:12">
+    <row r="155" customHeight="1" spans="1:12">
+      <c r="A155" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C155" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
@@ -8791,16 +8824,16 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="I155" s="1">
         <v>0</v>
       </c>
       <c r="J155" s="8" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K155" s="8" t="s">
         <v>625</v>
@@ -8809,12 +8842,18 @@
         <v>680</v>
       </c>
     </row>
-    <row r="156" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="156" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A156" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C156" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
@@ -8823,16 +8862,16 @@
         <v>5</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="I156" s="1">
         <v>0</v>
       </c>
       <c r="J156" s="8" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="K156" s="8" t="s">
         <v>625</v>
@@ -8841,12 +8880,18 @@
         <v>686</v>
       </c>
     </row>
-    <row r="157" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="157" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A157" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C157" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
@@ -8855,16 +8900,16 @@
         <v>5</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="I157" s="1">
         <v>0</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="K157" s="8" t="s">
         <v>625</v>
@@ -8873,12 +8918,18 @@
         <v>692</v>
       </c>
     </row>
-    <row r="158" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="158" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A158" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C158" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
@@ -8887,16 +8938,16 @@
         <v>5</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="I158" s="1">
         <v>0</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="K158" s="8" t="s">
         <v>625</v>
@@ -8905,12 +8956,18 @@
         <v>698</v>
       </c>
     </row>
-    <row r="159" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="159" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A159" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C159" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
@@ -8919,16 +8976,16 @@
         <v>5</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="I159" s="1">
         <v>0</v>
       </c>
       <c r="J159" s="8" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="K159" s="8" t="s">
         <v>625</v>
@@ -8937,12 +8994,18 @@
         <v>704</v>
       </c>
     </row>
-    <row r="160" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="160" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A160" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C160" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
@@ -8951,16 +9014,16 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="I160" s="1">
         <v>0</v>
       </c>
       <c r="J160" s="8" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="K160" s="8" t="s">
         <v>625</v>
@@ -8969,12 +9032,18 @@
         <v>710</v>
       </c>
     </row>
-    <row r="161" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="161" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A161" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C161" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
@@ -8983,16 +9052,16 @@
         <v>5</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="K161" s="8" t="s">
         <v>625</v>
@@ -9001,12 +9070,18 @@
         <v>716</v>
       </c>
     </row>
-    <row r="162" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="162" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A162" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C162" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
@@ -9015,16 +9090,16 @@
         <v>5</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="I162" s="1">
         <v>0</v>
       </c>
       <c r="J162" s="8" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="K162" s="8" t="s">
         <v>625</v>
@@ -9033,12 +9108,18 @@
         <v>722</v>
       </c>
     </row>
-    <row r="163" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="163" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A163" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C163" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9047,16 +9128,16 @@
         <v>5</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="I163" s="1">
         <v>0</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="K163" s="8" t="s">
         <v>625</v>
@@ -9065,12 +9146,18 @@
         <v>728</v>
       </c>
     </row>
-    <row r="164" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="164" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A164" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C164" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
@@ -9079,16 +9166,16 @@
         <v>5</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="I164" s="1">
         <v>0</v>
       </c>
       <c r="J164" s="8" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="K164" s="8" t="s">
         <v>625</v>
@@ -9097,12 +9184,18 @@
         <v>734</v>
       </c>
     </row>
-    <row r="165" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="165" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A165" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C165" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -9111,16 +9204,16 @@
         <v>5</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="I165" s="1">
         <v>0</v>
       </c>
       <c r="J165" s="8" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="K165" s="8" t="s">
         <v>625</v>
@@ -9129,12 +9222,18 @@
         <v>740</v>
       </c>
     </row>
-    <row r="166" customHeight="1" spans="3:12">
+    <row r="166" customHeight="1" spans="1:12">
+      <c r="A166" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C166" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
@@ -9143,16 +9242,16 @@
         <v>5</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
       </c>
       <c r="J166" s="8" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="K166" s="8" t="s">
         <v>625</v>
@@ -9161,12 +9260,18 @@
         <v>746</v>
       </c>
     </row>
-    <row r="167" customHeight="1" spans="3:12">
+    <row r="167" customHeight="1" spans="1:12">
+      <c r="A167" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C167" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
@@ -9175,16 +9280,16 @@
         <v>5</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
       </c>
       <c r="J167" s="8" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="K167" s="8" t="s">
         <v>625</v>
@@ -9193,12 +9298,18 @@
         <v>752</v>
       </c>
     </row>
-    <row r="168" customHeight="1" spans="3:12">
+    <row r="168" customHeight="1" spans="1:12">
+      <c r="A168" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C168" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -9207,16 +9318,16 @@
         <v>5</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="K168" s="8" t="s">
         <v>625</v>
@@ -9225,12 +9336,18 @@
         <v>758</v>
       </c>
     </row>
-    <row r="169" customHeight="1" spans="3:12">
+    <row r="169" customHeight="1" spans="1:12">
+      <c r="A169" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C169" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
@@ -9239,16 +9356,16 @@
         <v>5</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="K169" s="8" t="s">
         <v>625</v>
@@ -9257,12 +9374,18 @@
         <v>764</v>
       </c>
     </row>
-    <row r="170" customHeight="1" spans="3:12">
+    <row r="170" customHeight="1" spans="1:12">
+      <c r="A170" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C170" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -9271,16 +9394,16 @@
         <v>5</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
       </c>
       <c r="J170" s="8" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="K170" s="8" t="s">
         <v>625</v>
@@ -9289,12 +9412,18 @@
         <v>770</v>
       </c>
     </row>
-    <row r="171" customHeight="1" spans="3:12">
+    <row r="171" customHeight="1" spans="1:12">
+      <c r="A171" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C171" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -9303,16 +9432,16 @@
         <v>5</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
       </c>
       <c r="J171" s="8" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="K171" s="8" t="s">
         <v>625</v>
@@ -9321,12 +9450,18 @@
         <v>776</v>
       </c>
     </row>
-    <row r="172" customHeight="1" spans="3:12">
+    <row r="172" customHeight="1" spans="1:12">
+      <c r="A172" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C172" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
@@ -9335,16 +9470,16 @@
         <v>5</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
       </c>
       <c r="J172" s="8" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="K172" s="8" t="s">
         <v>625</v>
@@ -9353,12 +9488,18 @@
         <v>782</v>
       </c>
     </row>
-    <row r="173" customHeight="1" spans="3:12">
+    <row r="173" customHeight="1" spans="1:12">
+      <c r="A173" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C173" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
@@ -9367,16 +9508,16 @@
         <v>5</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
       </c>
       <c r="J173" s="8" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="K173" s="8" t="s">
         <v>625</v>
@@ -9385,12 +9526,18 @@
         <v>788</v>
       </c>
     </row>
-    <row r="174" customHeight="1" spans="3:12">
+    <row r="174" customHeight="1" spans="1:12">
+      <c r="A174" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C174" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -9399,16 +9546,16 @@
         <v>5</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
       </c>
       <c r="J174" s="8" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="K174" s="8" t="s">
         <v>625</v>
@@ -9417,12 +9564,18 @@
         <v>794</v>
       </c>
     </row>
-    <row r="175" customHeight="1" spans="3:12">
+    <row r="175" customHeight="1" spans="1:12">
+      <c r="A175" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C175" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
@@ -9431,16 +9584,16 @@
         <v>5</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="K175" s="8" t="s">
         <v>625</v>
@@ -9449,12 +9602,18 @@
         <v>800</v>
       </c>
     </row>
-    <row r="176" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="176" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A176" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C176" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
@@ -9463,16 +9622,16 @@
         <v>5</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="I176" s="1">
         <v>0</v>
       </c>
       <c r="J176" s="8" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="K176" s="8" t="s">
         <v>625</v>
@@ -9481,12 +9640,18 @@
         <v>806</v>
       </c>
     </row>
-    <row r="177" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="177" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A177" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C177" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
@@ -9495,16 +9660,16 @@
         <v>5</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I177" s="1">
         <v>0</v>
       </c>
       <c r="J177" s="8" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="K177" s="8" t="s">
         <v>625</v>
@@ -9513,12 +9678,18 @@
         <v>812</v>
       </c>
     </row>
-    <row r="178" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="178" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A178" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C178" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
@@ -9527,16 +9698,16 @@
         <v>5</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
       </c>
       <c r="J178" s="8" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="K178" s="8" t="s">
         <v>625</v>
@@ -9545,12 +9716,18 @@
         <v>818</v>
       </c>
     </row>
-    <row r="179" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="179" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A179" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C179" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -9559,16 +9736,16 @@
         <v>5</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
       </c>
       <c r="J179" s="8" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="K179" s="8" t="s">
         <v>625</v>
@@ -9577,12 +9754,18 @@
         <v>824</v>
       </c>
     </row>
-    <row r="180" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="180" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A180" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>853</v>
+      </c>
       <c r="C180" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
@@ -9591,16 +9774,16 @@
         <v>5</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
       </c>
       <c r="J180" s="8" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="K180" s="8" t="s">
         <v>625</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="1015">
   <si>
     <t>_Id</t>
   </si>
@@ -2572,6 +2572,9 @@
     <t>10,2500,1000,18000,600000,100000</t>
   </si>
   <si>
+    <t>10140</t>
+  </si>
+  <si>
     <t>1141</t>
   </si>
   <si>
@@ -2584,6 +2587,9 @@
     <t>深渊鹿茸</t>
   </si>
   <si>
+    <t>10141</t>
+  </si>
+  <si>
     <t>1142</t>
   </si>
   <si>
@@ -2596,6 +2602,9 @@
     <t>深渊草帽</t>
   </si>
   <si>
+    <t>10142</t>
+  </si>
+  <si>
     <t>1143</t>
   </si>
   <si>
@@ -2608,6 +2617,9 @@
     <t>深渊猫爪</t>
   </si>
   <si>
+    <t>10143</t>
+  </si>
+  <si>
     <t>1144</t>
   </si>
   <si>
@@ -2620,6 +2632,9 @@
     <t>深渊花朵</t>
   </si>
   <si>
+    <t>10144</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
@@ -2638,6 +2653,9 @@
     <t>202002,300091,105,504,210071,1009</t>
   </si>
   <si>
+    <t>10145</t>
+  </si>
+  <si>
     <t>1146</t>
   </si>
   <si>
@@ -2650,6 +2668,9 @@
     <t>深渊蝠翼</t>
   </si>
   <si>
+    <t>10146</t>
+  </si>
+  <si>
     <t>1147</t>
   </si>
   <si>
@@ -2662,6 +2683,9 @@
     <t>深渊魂火</t>
   </si>
   <si>
+    <t>10147</t>
+  </si>
+  <si>
     <t>1148</t>
   </si>
   <si>
@@ -2674,6 +2698,9 @@
     <t>深渊腐肉</t>
   </si>
   <si>
+    <t>10148</t>
+  </si>
+  <si>
     <t>1149</t>
   </si>
   <si>
@@ -2686,6 +2713,9 @@
     <t>深渊蛇胆</t>
   </si>
   <si>
+    <t>10149</t>
+  </si>
+  <si>
     <t>1150</t>
   </si>
   <si>
@@ -2701,6 +2731,9 @@
     <t>202002,300091,105,504,210072,1009</t>
   </si>
   <si>
+    <t>10150</t>
+  </si>
+  <si>
     <t>1151</t>
   </si>
   <si>
@@ -2713,6 +2746,9 @@
     <t>深渊虫皮</t>
   </si>
   <si>
+    <t>10151</t>
+  </si>
+  <si>
     <t>1152</t>
   </si>
   <si>
@@ -2725,6 +2761,9 @@
     <t>深渊鹰羽</t>
   </si>
   <si>
+    <t>10152</t>
+  </si>
+  <si>
     <t>1153</t>
   </si>
   <si>
@@ -2737,6 +2776,9 @@
     <t>深渊虫角</t>
   </si>
   <si>
+    <t>10153</t>
+  </si>
+  <si>
     <t>1154</t>
   </si>
   <si>
@@ -2749,6 +2791,9 @@
     <t>深渊蜈膏</t>
   </si>
   <si>
+    <t>10154</t>
+  </si>
+  <si>
     <t>1155</t>
   </si>
   <si>
@@ -2764,6 +2809,9 @@
     <t>202002,300091,105,504,210073,1009</t>
   </si>
   <si>
+    <t>10155</t>
+  </si>
+  <si>
     <t>1156</t>
   </si>
   <si>
@@ -2776,6 +2824,9 @@
     <t>深渊龙皮</t>
   </si>
   <si>
+    <t>10156</t>
+  </si>
+  <si>
     <t>1157</t>
   </si>
   <si>
@@ -2788,6 +2839,9 @@
     <t>深渊猪皮</t>
   </si>
   <si>
+    <t>10157</t>
+  </si>
+  <si>
     <t>1158</t>
   </si>
   <si>
@@ -2800,6 +2854,9 @@
     <t>深渊猪心</t>
   </si>
   <si>
+    <t>10158</t>
+  </si>
+  <si>
     <t>1159</t>
   </si>
   <si>
@@ -2812,6 +2869,9 @@
     <t>深渊蝎皮</t>
   </si>
   <si>
+    <t>10159</t>
+  </si>
+  <si>
     <t>1160</t>
   </si>
   <si>
@@ -2827,6 +2887,9 @@
     <t>202002,300091,105,504,210074,1009</t>
   </si>
   <si>
+    <t>10160</t>
+  </si>
+  <si>
     <t>1161</t>
   </si>
   <si>
@@ -2839,6 +2902,9 @@
     <t>深渊号角</t>
   </si>
   <si>
+    <t>10161</t>
+  </si>
+  <si>
     <t>1162</t>
   </si>
   <si>
@@ -2851,6 +2917,9 @@
     <t>深渊雕像</t>
   </si>
   <si>
+    <t>10162</t>
+  </si>
+  <si>
     <t>1163</t>
   </si>
   <si>
@@ -2863,6 +2932,9 @@
     <t>深渊神像</t>
   </si>
   <si>
+    <t>10163</t>
+  </si>
+  <si>
     <t>1164</t>
   </si>
   <si>
@@ -2875,6 +2947,9 @@
     <t>深渊獠牙</t>
   </si>
   <si>
+    <t>10164</t>
+  </si>
+  <si>
     <t>1165</t>
   </si>
   <si>
@@ -2890,6 +2965,9 @@
     <t>202002,300091,105,504,210075,1009</t>
   </si>
   <si>
+    <t>10165</t>
+  </si>
+  <si>
     <t>1166</t>
   </si>
   <si>
@@ -2902,6 +2980,9 @@
     <t>深渊魔心</t>
   </si>
   <si>
+    <t>10166</t>
+  </si>
+  <si>
     <t>1167</t>
   </si>
   <si>
@@ -2914,6 +2995,9 @@
     <t>深渊尸心</t>
   </si>
   <si>
+    <t>10167</t>
+  </si>
+  <si>
     <t>1168</t>
   </si>
   <si>
@@ -2926,6 +3010,9 @@
     <t>深渊法杖</t>
   </si>
   <si>
+    <t>10168</t>
+  </si>
+  <si>
     <t>1169</t>
   </si>
   <si>
@@ -2938,6 +3025,9 @@
     <t>深渊权杖</t>
   </si>
   <si>
+    <t>10169</t>
+  </si>
+  <si>
     <t>1170</t>
   </si>
   <si>
@@ -2953,6 +3043,9 @@
     <t>202002,300091,105,504,210076,1009</t>
   </si>
   <si>
+    <t>10170</t>
+  </si>
+  <si>
     <t>1171</t>
   </si>
   <si>
@@ -2965,6 +3058,9 @@
     <t>深渊血核</t>
   </si>
   <si>
+    <t>10171</t>
+  </si>
+  <si>
     <t>1172</t>
   </si>
   <si>
@@ -2977,6 +3073,9 @@
     <t>深渊魔核</t>
   </si>
   <si>
+    <t>10172</t>
+  </si>
+  <si>
     <t>1173</t>
   </si>
   <si>
@@ -2989,6 +3088,9 @@
     <t>深渊龙甲</t>
   </si>
   <si>
+    <t>10173</t>
+  </si>
+  <si>
     <t>1174</t>
   </si>
   <si>
@@ -2999,6 +3101,9 @@
   </si>
   <si>
     <t>深渊龙爪</t>
+  </si>
+  <si>
+    <t>10174</t>
   </si>
 </sst>
 </file>
@@ -8520,16 +8625,16 @@
       <c r="K146" s="9" t="s">
         <v>836</v>
       </c>
-      <c r="L146" s="3" t="s">
-        <v>626</v>
+      <c r="L146" s="9" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E147" s="1">
         <v>5</v>
@@ -8538,10 +8643,10 @@
         <v>5</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="I147" s="1">
         <v>0</v>
@@ -8552,16 +8657,16 @@
       <c r="K147" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L147" s="1" t="s">
-        <v>632</v>
+      <c r="L147" s="7" t="s">
+        <v>842</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="E148" s="1">
         <v>5</v>
@@ -8570,10 +8675,10 @@
         <v>5</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="I148" s="1">
         <v>0</v>
@@ -8584,16 +8689,16 @@
       <c r="K148" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L148" s="1" t="s">
-        <v>638</v>
+      <c r="L148" s="7" t="s">
+        <v>847</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="E149" s="1">
         <v>5</v>
@@ -8602,10 +8707,10 @@
         <v>5</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="I149" s="1">
         <v>0</v>
@@ -8616,16 +8721,16 @@
       <c r="K149" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L149" s="1" t="s">
-        <v>644</v>
+      <c r="L149" s="7" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="3:12">
       <c r="C150" s="1" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="E150" s="1">
         <v>5</v>
@@ -8634,10 +8739,10 @@
         <v>5</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="I150" s="1">
         <v>0</v>
@@ -8648,22 +8753,22 @@
       <c r="K150" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L150" s="1" t="s">
-        <v>650</v>
+      <c r="L150" s="7" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="1:12">
       <c r="A151" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
@@ -8672,36 +8777,36 @@
         <v>5</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="I151" s="1">
         <v>0</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="K151" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L151" s="1" t="s">
-        <v>656</v>
+      <c r="L151" s="7" t="s">
+        <v>864</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="1:12">
       <c r="A152" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
@@ -8710,36 +8815,36 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="I152" s="1">
         <v>0</v>
       </c>
       <c r="J152" s="8" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="K152" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L152" s="1" t="s">
-        <v>662</v>
+      <c r="L152" s="7" t="s">
+        <v>869</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="1:12">
       <c r="A153" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
@@ -8748,36 +8853,36 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="I153" s="1">
         <v>0</v>
       </c>
       <c r="J153" s="8" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="K153" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L153" s="1" t="s">
-        <v>668</v>
+      <c r="L153" s="7" t="s">
+        <v>874</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="1:12">
       <c r="A154" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
@@ -8786,36 +8891,36 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="I154" s="1">
         <v>0</v>
       </c>
       <c r="J154" s="8" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="K154" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L154" s="1" t="s">
-        <v>674</v>
+      <c r="L154" s="7" t="s">
+        <v>879</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="1:12">
       <c r="A155" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>872</v>
+        <v>881</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
@@ -8824,36 +8929,36 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="I155" s="1">
         <v>0</v>
       </c>
       <c r="J155" s="8" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="K155" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L155" s="1" t="s">
-        <v>680</v>
+      <c r="L155" s="7" t="s">
+        <v>884</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A156" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>875</v>
+        <v>885</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>876</v>
+        <v>886</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
@@ -8862,36 +8967,36 @@
         <v>5</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="I156" s="1">
         <v>0</v>
       </c>
       <c r="J156" s="8" t="s">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="K156" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L156" s="1" t="s">
-        <v>686</v>
+      <c r="L156" s="7" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A157" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>880</v>
+        <v>891</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
@@ -8900,36 +9005,36 @@
         <v>5</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>882</v>
+        <v>893</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="I157" s="1">
         <v>0</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="K157" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L157" s="1" t="s">
-        <v>692</v>
+      <c r="L157" s="7" t="s">
+        <v>895</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A158" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
@@ -8938,36 +9043,36 @@
         <v>5</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="I158" s="1">
         <v>0</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="K158" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L158" s="1" t="s">
-        <v>698</v>
+      <c r="L158" s="7" t="s">
+        <v>900</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A159" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>888</v>
+        <v>901</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
@@ -8976,36 +9081,36 @@
         <v>5</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>890</v>
+        <v>903</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>891</v>
+        <v>904</v>
       </c>
       <c r="I159" s="1">
         <v>0</v>
       </c>
       <c r="J159" s="8" t="s">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="K159" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L159" s="1" t="s">
-        <v>704</v>
+      <c r="L159" s="7" t="s">
+        <v>905</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A160" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>892</v>
+        <v>906</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>893</v>
+        <v>907</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
@@ -9014,36 +9119,36 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>894</v>
+        <v>908</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>895</v>
+        <v>909</v>
       </c>
       <c r="I160" s="1">
         <v>0</v>
       </c>
       <c r="J160" s="8" t="s">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="K160" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L160" s="1" t="s">
-        <v>710</v>
+      <c r="L160" s="7" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A161" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>897</v>
+        <v>912</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
@@ -9052,36 +9157,36 @@
         <v>5</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="K161" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L161" s="1" t="s">
-        <v>716</v>
+      <c r="L161" s="7" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A162" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>901</v>
+        <v>917</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>902</v>
+        <v>918</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
@@ -9090,36 +9195,36 @@
         <v>5</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>903</v>
+        <v>919</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
       <c r="I162" s="1">
         <v>0</v>
       </c>
       <c r="J162" s="8" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="K162" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L162" s="1" t="s">
-        <v>722</v>
+      <c r="L162" s="7" t="s">
+        <v>921</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A163" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>905</v>
+        <v>922</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>906</v>
+        <v>923</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9128,36 +9233,36 @@
         <v>5</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>908</v>
+        <v>925</v>
       </c>
       <c r="I163" s="1">
         <v>0</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="K163" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L163" s="1" t="s">
-        <v>728</v>
+      <c r="L163" s="7" t="s">
+        <v>926</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A164" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>910</v>
+        <v>928</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
@@ -9166,36 +9271,36 @@
         <v>5</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>911</v>
+        <v>929</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
       <c r="I164" s="1">
         <v>0</v>
       </c>
       <c r="J164" s="8" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="K164" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L164" s="1" t="s">
-        <v>734</v>
+      <c r="L164" s="7" t="s">
+        <v>931</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A165" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>913</v>
+        <v>932</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>914</v>
+        <v>933</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -9204,36 +9309,36 @@
         <v>5</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>915</v>
+        <v>934</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>916</v>
+        <v>935</v>
       </c>
       <c r="I165" s="1">
         <v>0</v>
       </c>
       <c r="J165" s="8" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="K165" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L165" s="1" t="s">
-        <v>740</v>
+      <c r="L165" s="7" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="166" customHeight="1" spans="1:12">
       <c r="A166" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>917</v>
+        <v>937</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>918</v>
+        <v>938</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
@@ -9242,36 +9347,36 @@
         <v>5</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>919</v>
+        <v>939</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>920</v>
+        <v>940</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
       </c>
       <c r="J166" s="8" t="s">
-        <v>921</v>
+        <v>941</v>
       </c>
       <c r="K166" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L166" s="1" t="s">
-        <v>746</v>
+      <c r="L166" s="7" t="s">
+        <v>942</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="1:12">
       <c r="A167" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>922</v>
+        <v>943</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>923</v>
+        <v>944</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
@@ -9280,36 +9385,36 @@
         <v>5</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>924</v>
+        <v>945</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>925</v>
+        <v>946</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
       </c>
       <c r="J167" s="8" t="s">
-        <v>921</v>
+        <v>941</v>
       </c>
       <c r="K167" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L167" s="1" t="s">
-        <v>752</v>
+      <c r="L167" s="7" t="s">
+        <v>947</v>
       </c>
     </row>
     <row r="168" customHeight="1" spans="1:12">
       <c r="A168" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>926</v>
+        <v>948</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>927</v>
+        <v>949</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -9318,36 +9423,36 @@
         <v>5</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>928</v>
+        <v>950</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>929</v>
+        <v>951</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>921</v>
+        <v>941</v>
       </c>
       <c r="K168" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L168" s="1" t="s">
-        <v>758</v>
+      <c r="L168" s="7" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="169" customHeight="1" spans="1:12">
       <c r="A169" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>930</v>
+        <v>953</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>931</v>
+        <v>954</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
@@ -9356,36 +9461,36 @@
         <v>5</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>932</v>
+        <v>955</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>933</v>
+        <v>956</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>921</v>
+        <v>941</v>
       </c>
       <c r="K169" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L169" s="1" t="s">
-        <v>764</v>
+      <c r="L169" s="7" t="s">
+        <v>957</v>
       </c>
     </row>
     <row r="170" customHeight="1" spans="1:12">
       <c r="A170" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>934</v>
+        <v>958</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>935</v>
+        <v>959</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -9394,36 +9499,36 @@
         <v>5</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>936</v>
+        <v>960</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>937</v>
+        <v>961</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
       </c>
       <c r="J170" s="8" t="s">
-        <v>921</v>
+        <v>941</v>
       </c>
       <c r="K170" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L170" s="1" t="s">
-        <v>770</v>
+      <c r="L170" s="7" t="s">
+        <v>962</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="1:12">
       <c r="A171" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>938</v>
+        <v>963</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>939</v>
+        <v>964</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -9432,36 +9537,36 @@
         <v>5</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>940</v>
+        <v>965</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>941</v>
+        <v>966</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
       </c>
       <c r="J171" s="8" t="s">
-        <v>942</v>
+        <v>967</v>
       </c>
       <c r="K171" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L171" s="1" t="s">
-        <v>776</v>
+      <c r="L171" s="7" t="s">
+        <v>968</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="1:12">
       <c r="A172" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>943</v>
+        <v>969</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>944</v>
+        <v>970</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
@@ -9470,36 +9575,36 @@
         <v>5</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>945</v>
+        <v>971</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>946</v>
+        <v>972</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
       </c>
       <c r="J172" s="8" t="s">
-        <v>942</v>
+        <v>967</v>
       </c>
       <c r="K172" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L172" s="1" t="s">
-        <v>782</v>
+      <c r="L172" s="7" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="1:12">
       <c r="A173" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>948</v>
+        <v>975</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
@@ -9508,36 +9613,36 @@
         <v>5</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>950</v>
+        <v>977</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
       </c>
       <c r="J173" s="8" t="s">
-        <v>942</v>
+        <v>967</v>
       </c>
       <c r="K173" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L173" s="1" t="s">
-        <v>788</v>
+      <c r="L173" s="7" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="1:12">
       <c r="A174" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>951</v>
+        <v>979</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>952</v>
+        <v>980</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -9546,36 +9651,36 @@
         <v>5</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>953</v>
+        <v>981</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>954</v>
+        <v>982</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
       </c>
       <c r="J174" s="8" t="s">
-        <v>942</v>
+        <v>967</v>
       </c>
       <c r="K174" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L174" s="1" t="s">
-        <v>794</v>
+      <c r="L174" s="7" t="s">
+        <v>983</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="1:12">
       <c r="A175" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>955</v>
+        <v>984</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>956</v>
+        <v>985</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
@@ -9584,36 +9689,36 @@
         <v>5</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>957</v>
+        <v>986</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>958</v>
+        <v>987</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>942</v>
+        <v>967</v>
       </c>
       <c r="K175" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L175" s="1" t="s">
-        <v>800</v>
+      <c r="L175" s="7" t="s">
+        <v>988</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A176" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>959</v>
+        <v>989</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>960</v>
+        <v>990</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
@@ -9622,36 +9727,36 @@
         <v>5</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>961</v>
+        <v>991</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>962</v>
+        <v>992</v>
       </c>
       <c r="I176" s="1">
         <v>0</v>
       </c>
       <c r="J176" s="8" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
       <c r="K176" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L176" s="1" t="s">
-        <v>806</v>
+      <c r="L176" s="7" t="s">
+        <v>994</v>
       </c>
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A177" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>964</v>
+        <v>995</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>965</v>
+        <v>996</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
@@ -9660,36 +9765,36 @@
         <v>5</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>966</v>
+        <v>997</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>967</v>
+        <v>998</v>
       </c>
       <c r="I177" s="1">
         <v>0</v>
       </c>
       <c r="J177" s="8" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
       <c r="K177" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L177" s="1" t="s">
-        <v>812</v>
+      <c r="L177" s="7" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A178" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>968</v>
+        <v>1000</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>969</v>
+        <v>1001</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
@@ -9698,36 +9803,36 @@
         <v>5</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>970</v>
+        <v>1002</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>971</v>
+        <v>1003</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
       </c>
       <c r="J178" s="8" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
       <c r="K178" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L178" s="1" t="s">
-        <v>818</v>
+      <c r="L178" s="7" t="s">
+        <v>1004</v>
       </c>
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A179" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>973</v>
+        <v>1006</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -9736,36 +9841,36 @@
         <v>5</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>975</v>
+        <v>1008</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
       </c>
       <c r="J179" s="8" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
       <c r="K179" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L179" s="1" t="s">
-        <v>824</v>
+      <c r="L179" s="7" t="s">
+        <v>1009</v>
       </c>
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A180" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>976</v>
+        <v>1010</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>977</v>
+        <v>1011</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
@@ -9774,22 +9879,22 @@
         <v>5</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>978</v>
+        <v>1012</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>979</v>
+        <v>1013</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
       </c>
       <c r="J180" s="8" t="s">
-        <v>963</v>
+        <v>993</v>
       </c>
       <c r="K180" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="L180" s="1" t="s">
-        <v>830</v>
+      <c r="L180" s="7" t="s">
+        <v>1014</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="1015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="1014">
   <si>
     <t>_Id</t>
   </si>
@@ -2567,9 +2567,6 @@
   </si>
   <si>
     <t>202002,300091,105,504,210070,1009</t>
-  </si>
-  <si>
-    <t>10,2500,1000,18000,600000,100000</t>
   </si>
   <si>
     <t>10140</t>
@@ -8623,18 +8620,18 @@
         <v>835</v>
       </c>
       <c r="K146" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="L146" s="9" t="s">
         <v>836</v>
-      </c>
-      <c r="L146" s="9" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>838</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>839</v>
       </c>
       <c r="E147" s="1">
         <v>5</v>
@@ -8643,10 +8640,10 @@
         <v>5</v>
       </c>
       <c r="G147" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="H147" s="1" t="s">
         <v>840</v>
-      </c>
-      <c r="H147" s="1" t="s">
-        <v>841</v>
       </c>
       <c r="I147" s="1">
         <v>0</v>
@@ -8658,15 +8655,15 @@
         <v>625</v>
       </c>
       <c r="L147" s="7" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>843</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>844</v>
       </c>
       <c r="E148" s="1">
         <v>5</v>
@@ -8675,10 +8672,10 @@
         <v>5</v>
       </c>
       <c r="G148" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="H148" s="1" t="s">
         <v>845</v>
-      </c>
-      <c r="H148" s="1" t="s">
-        <v>846</v>
       </c>
       <c r="I148" s="1">
         <v>0</v>
@@ -8690,15 +8687,15 @@
         <v>625</v>
       </c>
       <c r="L148" s="7" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>848</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>849</v>
       </c>
       <c r="E149" s="1">
         <v>5</v>
@@ -8707,10 +8704,10 @@
         <v>5</v>
       </c>
       <c r="G149" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="H149" s="1" t="s">
         <v>850</v>
-      </c>
-      <c r="H149" s="1" t="s">
-        <v>851</v>
       </c>
       <c r="I149" s="1">
         <v>0</v>
@@ -8722,15 +8719,15 @@
         <v>625</v>
       </c>
       <c r="L149" s="7" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="3:12">
       <c r="C150" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>853</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>854</v>
       </c>
       <c r="E150" s="1">
         <v>5</v>
@@ -8739,10 +8736,10 @@
         <v>5</v>
       </c>
       <c r="G150" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="H150" s="1" t="s">
         <v>855</v>
-      </c>
-      <c r="H150" s="1" t="s">
-        <v>856</v>
       </c>
       <c r="I150" s="1">
         <v>0</v>
@@ -8754,21 +8751,21 @@
         <v>625</v>
       </c>
       <c r="L150" s="7" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="1:12">
       <c r="A151" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="C151" s="1" t="s">
+      <c r="D151" s="1" t="s">
         <v>859</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>860</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
@@ -8777,36 +8774,36 @@
         <v>5</v>
       </c>
       <c r="G151" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="H151" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="H151" s="1" t="s">
-        <v>862</v>
       </c>
       <c r="I151" s="1">
         <v>0</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K151" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L151" s="7" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="1:12">
       <c r="A152" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C152" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>865</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>866</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
@@ -8815,36 +8812,36 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="H152" s="1" t="s">
         <v>867</v>
-      </c>
-      <c r="H152" s="1" t="s">
-        <v>868</v>
       </c>
       <c r="I152" s="1">
         <v>0</v>
       </c>
       <c r="J152" s="8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K152" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L152" s="7" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="1:12">
       <c r="A153" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C153" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>870</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>871</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
@@ -8853,36 +8850,36 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="H153" s="1" t="s">
         <v>872</v>
-      </c>
-      <c r="H153" s="1" t="s">
-        <v>873</v>
       </c>
       <c r="I153" s="1">
         <v>0</v>
       </c>
       <c r="J153" s="8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K153" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L153" s="7" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="1:12">
       <c r="A154" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C154" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>875</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>876</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
@@ -8891,36 +8888,36 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="H154" s="1" t="s">
         <v>877</v>
-      </c>
-      <c r="H154" s="1" t="s">
-        <v>878</v>
       </c>
       <c r="I154" s="1">
         <v>0</v>
       </c>
       <c r="J154" s="8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K154" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L154" s="7" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="1:12">
       <c r="A155" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C155" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>880</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>881</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
@@ -8929,36 +8926,36 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="H155" s="1" t="s">
         <v>882</v>
-      </c>
-      <c r="H155" s="1" t="s">
-        <v>883</v>
       </c>
       <c r="I155" s="1">
         <v>0</v>
       </c>
       <c r="J155" s="8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K155" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L155" s="7" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A156" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C156" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>885</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>886</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
@@ -8967,36 +8964,36 @@
         <v>5</v>
       </c>
       <c r="G156" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="H156" s="1" t="s">
         <v>887</v>
-      </c>
-      <c r="H156" s="1" t="s">
-        <v>888</v>
       </c>
       <c r="I156" s="1">
         <v>0</v>
       </c>
       <c r="J156" s="8" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="K156" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L156" s="7" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A157" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C157" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>891</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>892</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
@@ -9005,36 +9002,36 @@
         <v>5</v>
       </c>
       <c r="G157" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="H157" s="1" t="s">
         <v>893</v>
-      </c>
-      <c r="H157" s="1" t="s">
-        <v>894</v>
       </c>
       <c r="I157" s="1">
         <v>0</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="K157" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L157" s="7" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A158" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C158" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>896</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>897</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
@@ -9043,36 +9040,36 @@
         <v>5</v>
       </c>
       <c r="G158" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="H158" s="1" t="s">
         <v>898</v>
-      </c>
-      <c r="H158" s="1" t="s">
-        <v>899</v>
       </c>
       <c r="I158" s="1">
         <v>0</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="K158" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L158" s="7" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A159" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C159" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>901</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>902</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
@@ -9081,36 +9078,36 @@
         <v>5</v>
       </c>
       <c r="G159" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="H159" s="1" t="s">
         <v>903</v>
-      </c>
-      <c r="H159" s="1" t="s">
-        <v>904</v>
       </c>
       <c r="I159" s="1">
         <v>0</v>
       </c>
       <c r="J159" s="8" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="K159" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L159" s="7" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A160" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C160" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>906</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>907</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
@@ -9119,36 +9116,36 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="H160" s="1" t="s">
         <v>908</v>
-      </c>
-      <c r="H160" s="1" t="s">
-        <v>909</v>
       </c>
       <c r="I160" s="1">
         <v>0</v>
       </c>
       <c r="J160" s="8" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="K160" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L160" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A161" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C161" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>911</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>912</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
@@ -9157,36 +9154,36 @@
         <v>5</v>
       </c>
       <c r="G161" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="H161" s="1" t="s">
         <v>913</v>
-      </c>
-      <c r="H161" s="1" t="s">
-        <v>914</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="K161" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L161" s="7" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A162" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C162" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>917</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>918</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
@@ -9195,36 +9192,36 @@
         <v>5</v>
       </c>
       <c r="G162" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="H162" s="1" t="s">
         <v>919</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>920</v>
       </c>
       <c r="I162" s="1">
         <v>0</v>
       </c>
       <c r="J162" s="8" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="K162" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L162" s="7" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A163" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C163" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>922</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>923</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9233,36 +9230,36 @@
         <v>5</v>
       </c>
       <c r="G163" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="H163" s="1" t="s">
         <v>924</v>
-      </c>
-      <c r="H163" s="1" t="s">
-        <v>925</v>
       </c>
       <c r="I163" s="1">
         <v>0</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="K163" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L163" s="7" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A164" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C164" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>927</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>928</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
@@ -9271,36 +9268,36 @@
         <v>5</v>
       </c>
       <c r="G164" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="H164" s="1" t="s">
         <v>929</v>
-      </c>
-      <c r="H164" s="1" t="s">
-        <v>930</v>
       </c>
       <c r="I164" s="1">
         <v>0</v>
       </c>
       <c r="J164" s="8" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="K164" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L164" s="7" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A165" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C165" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>932</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>933</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -9309,36 +9306,36 @@
         <v>5</v>
       </c>
       <c r="G165" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="H165" s="1" t="s">
         <v>934</v>
-      </c>
-      <c r="H165" s="1" t="s">
-        <v>935</v>
       </c>
       <c r="I165" s="1">
         <v>0</v>
       </c>
       <c r="J165" s="8" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="K165" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="166" customHeight="1" spans="1:12">
       <c r="A166" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C166" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="D166" s="2" t="s">
         <v>937</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>938</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
@@ -9347,36 +9344,36 @@
         <v>5</v>
       </c>
       <c r="G166" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="H166" s="1" t="s">
         <v>939</v>
-      </c>
-      <c r="H166" s="1" t="s">
-        <v>940</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
       </c>
       <c r="J166" s="8" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="K166" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L166" s="7" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="1:12">
       <c r="A167" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C167" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>943</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>944</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
@@ -9385,36 +9382,36 @@
         <v>5</v>
       </c>
       <c r="G167" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="H167" s="1" t="s">
         <v>945</v>
-      </c>
-      <c r="H167" s="1" t="s">
-        <v>946</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
       </c>
       <c r="J167" s="8" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="K167" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L167" s="7" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="168" customHeight="1" spans="1:12">
       <c r="A168" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C168" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="D168" s="2" t="s">
         <v>948</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>949</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -9423,36 +9420,36 @@
         <v>5</v>
       </c>
       <c r="G168" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="H168" s="1" t="s">
         <v>950</v>
-      </c>
-      <c r="H168" s="1" t="s">
-        <v>951</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="K168" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L168" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="169" customHeight="1" spans="1:12">
       <c r="A169" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C169" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="D169" s="2" t="s">
         <v>953</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>954</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
@@ -9461,36 +9458,36 @@
         <v>5</v>
       </c>
       <c r="G169" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="H169" s="1" t="s">
         <v>955</v>
-      </c>
-      <c r="H169" s="1" t="s">
-        <v>956</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="K169" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L169" s="7" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="170" customHeight="1" spans="1:12">
       <c r="A170" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C170" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="D170" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>959</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -9499,36 +9496,36 @@
         <v>5</v>
       </c>
       <c r="G170" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="H170" s="1" t="s">
         <v>960</v>
-      </c>
-      <c r="H170" s="1" t="s">
-        <v>961</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
       </c>
       <c r="J170" s="8" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="K170" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="1:12">
       <c r="A171" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C171" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>963</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>964</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -9537,36 +9534,36 @@
         <v>5</v>
       </c>
       <c r="G171" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="H171" s="1" t="s">
         <v>965</v>
-      </c>
-      <c r="H171" s="1" t="s">
-        <v>966</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
       </c>
       <c r="J171" s="8" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="K171" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L171" s="7" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="1:12">
       <c r="A172" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C172" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>969</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>970</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
@@ -9575,36 +9572,36 @@
         <v>5</v>
       </c>
       <c r="G172" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="H172" s="1" t="s">
         <v>971</v>
-      </c>
-      <c r="H172" s="1" t="s">
-        <v>972</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
       </c>
       <c r="J172" s="8" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="K172" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L172" s="7" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="1:12">
       <c r="A173" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C173" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>974</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>975</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
@@ -9613,36 +9610,36 @@
         <v>5</v>
       </c>
       <c r="G173" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="H173" s="1" t="s">
         <v>976</v>
-      </c>
-      <c r="H173" s="1" t="s">
-        <v>977</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
       </c>
       <c r="J173" s="8" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="K173" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L173" s="7" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="1:12">
       <c r="A174" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C174" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>979</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>980</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -9651,36 +9648,36 @@
         <v>5</v>
       </c>
       <c r="G174" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="H174" s="1" t="s">
         <v>981</v>
-      </c>
-      <c r="H174" s="1" t="s">
-        <v>982</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
       </c>
       <c r="J174" s="8" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="K174" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L174" s="7" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="1:12">
       <c r="A175" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C175" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>984</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>985</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
@@ -9689,36 +9686,36 @@
         <v>5</v>
       </c>
       <c r="G175" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="H175" s="1" t="s">
         <v>986</v>
-      </c>
-      <c r="H175" s="1" t="s">
-        <v>987</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="K175" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L175" s="7" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A176" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C176" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>989</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>990</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
@@ -9727,36 +9724,36 @@
         <v>5</v>
       </c>
       <c r="G176" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="H176" s="1" t="s">
         <v>991</v>
-      </c>
-      <c r="H176" s="1" t="s">
-        <v>992</v>
       </c>
       <c r="I176" s="1">
         <v>0</v>
       </c>
       <c r="J176" s="8" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="K176" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L176" s="7" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A177" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C177" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>996</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
@@ -9765,36 +9762,36 @@
         <v>5</v>
       </c>
       <c r="G177" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="H177" s="1" t="s">
         <v>997</v>
-      </c>
-      <c r="H177" s="1" t="s">
-        <v>998</v>
       </c>
       <c r="I177" s="1">
         <v>0</v>
       </c>
       <c r="J177" s="8" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="K177" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L177" s="7" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A178" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C178" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>1000</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>1001</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
@@ -9803,36 +9800,36 @@
         <v>5</v>
       </c>
       <c r="G178" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H178" s="1" t="s">
         <v>1002</v>
-      </c>
-      <c r="H178" s="1" t="s">
-        <v>1003</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
       </c>
       <c r="J178" s="8" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="K178" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L178" s="7" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A179" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C179" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>1005</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>1006</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -9841,36 +9838,36 @@
         <v>5</v>
       </c>
       <c r="G179" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H179" s="1" t="s">
         <v>1007</v>
-      </c>
-      <c r="H179" s="1" t="s">
-        <v>1008</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
       </c>
       <c r="J179" s="8" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="K179" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L179" s="7" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A180" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C180" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>1010</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>1011</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
@@ -9879,22 +9876,22 @@
         <v>5</v>
       </c>
       <c r="G180" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H180" s="1" t="s">
         <v>1012</v>
-      </c>
-      <c r="H180" s="1" t="s">
-        <v>1013</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
       </c>
       <c r="J180" s="8" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="K180" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L180" s="7" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="1014">
   <si>
     <t>_Id</t>
   </si>
@@ -2632,85 +2632,85 @@
     <t>10144</t>
   </si>
   <si>
+    <t>1145</t>
+  </si>
+  <si>
+    <t>深渊蝠洞</t>
+  </si>
+  <si>
+    <t>1500-1</t>
+  </si>
+  <si>
+    <t>深渊冰晶</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210071,1009</t>
+  </si>
+  <si>
+    <t>10145</t>
+  </si>
+  <si>
+    <t>1146</t>
+  </si>
+  <si>
+    <t>深渊骷髅洞</t>
+  </si>
+  <si>
+    <t>1500-2</t>
+  </si>
+  <si>
+    <t>深渊蝠翼</t>
+  </si>
+  <si>
+    <t>10146</t>
+  </si>
+  <si>
+    <t>1147</t>
+  </si>
+  <si>
+    <t>深渊通道</t>
+  </si>
+  <si>
+    <t>1500-3</t>
+  </si>
+  <si>
+    <t>深渊魂火</t>
+  </si>
+  <si>
+    <t>10147</t>
+  </si>
+  <si>
+    <t>1148</t>
+  </si>
+  <si>
+    <t>深渊尸洞</t>
+  </si>
+  <si>
+    <t>1500-4</t>
+  </si>
+  <si>
+    <t>深渊腐肉</t>
+  </si>
+  <si>
+    <t>10148</t>
+  </si>
+  <si>
+    <t>1149</t>
+  </si>
+  <si>
+    <t>深渊蛇谷</t>
+  </si>
+  <si>
+    <t>1500-5</t>
+  </si>
+  <si>
+    <t>深渊蛇胆</t>
+  </si>
+  <si>
+    <t>10149</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1145</t>
-  </si>
-  <si>
-    <t>深渊蝠洞</t>
-  </si>
-  <si>
-    <t>1500-1</t>
-  </si>
-  <si>
-    <t>深渊冰晶</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210071,1009</t>
-  </si>
-  <si>
-    <t>10145</t>
-  </si>
-  <si>
-    <t>1146</t>
-  </si>
-  <si>
-    <t>深渊骷髅洞</t>
-  </si>
-  <si>
-    <t>1500-2</t>
-  </si>
-  <si>
-    <t>深渊蝠翼</t>
-  </si>
-  <si>
-    <t>10146</t>
-  </si>
-  <si>
-    <t>1147</t>
-  </si>
-  <si>
-    <t>深渊通道</t>
-  </si>
-  <si>
-    <t>1500-3</t>
-  </si>
-  <si>
-    <t>深渊魂火</t>
-  </si>
-  <si>
-    <t>10147</t>
-  </si>
-  <si>
-    <t>1148</t>
-  </si>
-  <si>
-    <t>深渊尸洞</t>
-  </si>
-  <si>
-    <t>1500-4</t>
-  </si>
-  <si>
-    <t>深渊腐肉</t>
-  </si>
-  <si>
-    <t>10148</t>
-  </si>
-  <si>
-    <t>1149</t>
-  </si>
-  <si>
-    <t>深渊蛇谷</t>
-  </si>
-  <si>
-    <t>1500-5</t>
-  </si>
-  <si>
-    <t>深渊蛇胆</t>
-  </si>
-  <si>
-    <t>10149</t>
   </si>
   <si>
     <t>1150</t>
@@ -8754,18 +8754,12 @@
         <v>856</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="1:12">
-      <c r="A151" s="1" t="s">
+    <row r="151" customHeight="1" spans="3:12">
+      <c r="C151" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="C151" s="1" t="s">
+      <c r="D151" s="1" t="s">
         <v>858</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>859</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
@@ -8774,36 +8768,30 @@
         <v>5</v>
       </c>
       <c r="G151" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="H151" s="1" t="s">
         <v>860</v>
-      </c>
-      <c r="H151" s="1" t="s">
-        <v>861</v>
       </c>
       <c r="I151" s="1">
         <v>0</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K151" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L151" s="7" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="3:12">
+      <c r="C152" s="1" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="152" customHeight="1" spans="1:12">
-      <c r="A152" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="C152" s="1" t="s">
+      <c r="D152" s="1" t="s">
         <v>864</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>865</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
@@ -8812,36 +8800,30 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="H152" s="1" t="s">
         <v>866</v>
-      </c>
-      <c r="H152" s="1" t="s">
-        <v>867</v>
       </c>
       <c r="I152" s="1">
         <v>0</v>
       </c>
       <c r="J152" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K152" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L152" s="7" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="3:12">
+      <c r="C153" s="1" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="153" customHeight="1" spans="1:12">
-      <c r="A153" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="C153" s="1" t="s">
+      <c r="D153" s="1" t="s">
         <v>869</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>870</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
@@ -8850,36 +8832,30 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="H153" s="1" t="s">
         <v>871</v>
-      </c>
-      <c r="H153" s="1" t="s">
-        <v>872</v>
       </c>
       <c r="I153" s="1">
         <v>0</v>
       </c>
       <c r="J153" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K153" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L153" s="7" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="3:12">
+      <c r="C154" s="1" t="s">
         <v>873</v>
       </c>
-    </row>
-    <row r="154" customHeight="1" spans="1:12">
-      <c r="A154" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="C154" s="1" t="s">
+      <c r="D154" s="1" t="s">
         <v>874</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>875</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
@@ -8888,36 +8864,30 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="H154" s="1" t="s">
         <v>876</v>
-      </c>
-      <c r="H154" s="1" t="s">
-        <v>877</v>
       </c>
       <c r="I154" s="1">
         <v>0</v>
       </c>
       <c r="J154" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K154" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L154" s="7" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="3:12">
+      <c r="C155" s="1" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="155" customHeight="1" spans="1:12">
-      <c r="A155" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="C155" s="1" t="s">
+      <c r="D155" s="1" t="s">
         <v>879</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>880</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
@@ -8926,30 +8896,30 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="H155" s="1" t="s">
         <v>881</v>
-      </c>
-      <c r="H155" s="1" t="s">
-        <v>882</v>
       </c>
       <c r="I155" s="1">
         <v>0</v>
       </c>
       <c r="J155" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K155" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L155" s="7" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A156" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>884</v>
@@ -8984,10 +8954,10 @@
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A157" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>890</v>
@@ -9022,10 +8992,10 @@
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A158" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>895</v>
@@ -9060,10 +9030,10 @@
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A159" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>900</v>
@@ -9098,10 +9068,10 @@
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A160" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>905</v>
@@ -9136,10 +9106,10 @@
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A161" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>910</v>
@@ -9174,10 +9144,10 @@
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A162" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>916</v>
@@ -9212,10 +9182,10 @@
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A163" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>921</v>
@@ -9250,10 +9220,10 @@
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A164" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>926</v>
@@ -9288,10 +9258,10 @@
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A165" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>931</v>
@@ -9326,10 +9296,10 @@
     </row>
     <row r="166" customHeight="1" spans="1:12">
       <c r="A166" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>936</v>
@@ -9364,10 +9334,10 @@
     </row>
     <row r="167" customHeight="1" spans="1:12">
       <c r="A167" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>942</v>
@@ -9402,10 +9372,10 @@
     </row>
     <row r="168" customHeight="1" spans="1:12">
       <c r="A168" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>947</v>
@@ -9440,10 +9410,10 @@
     </row>
     <row r="169" customHeight="1" spans="1:12">
       <c r="A169" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>952</v>
@@ -9478,10 +9448,10 @@
     </row>
     <row r="170" customHeight="1" spans="1:12">
       <c r="A170" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>957</v>
@@ -9516,10 +9486,10 @@
     </row>
     <row r="171" customHeight="1" spans="1:12">
       <c r="A171" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>962</v>
@@ -9554,10 +9524,10 @@
     </row>
     <row r="172" customHeight="1" spans="1:12">
       <c r="A172" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>968</v>
@@ -9592,10 +9562,10 @@
     </row>
     <row r="173" customHeight="1" spans="1:12">
       <c r="A173" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>973</v>
@@ -9630,10 +9600,10 @@
     </row>
     <row r="174" customHeight="1" spans="1:12">
       <c r="A174" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>978</v>
@@ -9668,10 +9638,10 @@
     </row>
     <row r="175" customHeight="1" spans="1:12">
       <c r="A175" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>983</v>
@@ -9706,10 +9676,10 @@
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A176" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>988</v>
@@ -9744,10 +9714,10 @@
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A177" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>994</v>
@@ -9782,10 +9752,10 @@
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A178" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>999</v>
@@ -9820,10 +9790,10 @@
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A179" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>1004</v>
@@ -9858,10 +9828,10 @@
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A180" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1009</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="1014">
   <si>
     <t>_Id</t>
   </si>
@@ -2710,85 +2710,85 @@
     <t>10149</t>
   </si>
   <si>
+    <t>1150</t>
+  </si>
+  <si>
+    <t>深渊狼山</t>
+  </si>
+  <si>
+    <t>1550-1</t>
+  </si>
+  <si>
+    <t>深渊狼爪</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210072,1009</t>
+  </si>
+  <si>
+    <t>10150</t>
+  </si>
+  <si>
+    <t>1151</t>
+  </si>
+  <si>
+    <t>深渊沙洞</t>
+  </si>
+  <si>
+    <t>1550-2</t>
+  </si>
+  <si>
+    <t>深渊虫皮</t>
+  </si>
+  <si>
+    <t>10151</t>
+  </si>
+  <si>
+    <t>1152</t>
+  </si>
+  <si>
+    <t>深渊鹰崖</t>
+  </si>
+  <si>
+    <t>1550-3</t>
+  </si>
+  <si>
+    <t>深渊鹰羽</t>
+  </si>
+  <si>
+    <t>10152</t>
+  </si>
+  <si>
+    <t>1153</t>
+  </si>
+  <si>
+    <t>深渊虫谷</t>
+  </si>
+  <si>
+    <t>1550-4</t>
+  </si>
+  <si>
+    <t>深渊虫角</t>
+  </si>
+  <si>
+    <t>10153</t>
+  </si>
+  <si>
+    <t>1154</t>
+  </si>
+  <si>
+    <t>深渊虫洞</t>
+  </si>
+  <si>
+    <t>1550-5</t>
+  </si>
+  <si>
+    <t>深渊蜈膏</t>
+  </si>
+  <si>
+    <t>10154</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1150</t>
-  </si>
-  <si>
-    <t>深渊狼山</t>
-  </si>
-  <si>
-    <t>1550-1</t>
-  </si>
-  <si>
-    <t>深渊狼爪</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210072,1009</t>
-  </si>
-  <si>
-    <t>10150</t>
-  </si>
-  <si>
-    <t>1151</t>
-  </si>
-  <si>
-    <t>深渊沙洞</t>
-  </si>
-  <si>
-    <t>1550-2</t>
-  </si>
-  <si>
-    <t>深渊虫皮</t>
-  </si>
-  <si>
-    <t>10151</t>
-  </si>
-  <si>
-    <t>1152</t>
-  </si>
-  <si>
-    <t>深渊鹰崖</t>
-  </si>
-  <si>
-    <t>1550-3</t>
-  </si>
-  <si>
-    <t>深渊鹰羽</t>
-  </si>
-  <si>
-    <t>10152</t>
-  </si>
-  <si>
-    <t>1153</t>
-  </si>
-  <si>
-    <t>深渊虫谷</t>
-  </si>
-  <si>
-    <t>1550-4</t>
-  </si>
-  <si>
-    <t>深渊虫角</t>
-  </si>
-  <si>
-    <t>10153</t>
-  </si>
-  <si>
-    <t>1154</t>
-  </si>
-  <si>
-    <t>深渊虫洞</t>
-  </si>
-  <si>
-    <t>1550-5</t>
-  </si>
-  <si>
-    <t>深渊蜈膏</t>
-  </si>
-  <si>
-    <t>10154</t>
   </si>
   <si>
     <t>1155</t>
@@ -8914,18 +8914,12 @@
         <v>882</v>
       </c>
     </row>
-    <row r="156" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A156" s="1" t="s">
+    <row r="156" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C156" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="C156" s="1" t="s">
+      <c r="D156" s="1" t="s">
         <v>884</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>885</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
@@ -8934,36 +8928,30 @@
         <v>5</v>
       </c>
       <c r="G156" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="H156" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="H156" s="1" t="s">
-        <v>887</v>
       </c>
       <c r="I156" s="1">
         <v>0</v>
       </c>
       <c r="J156" s="8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K156" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L156" s="7" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="157" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C157" s="1" t="s">
         <v>889</v>
       </c>
-    </row>
-    <row r="157" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A157" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="C157" s="1" t="s">
+      <c r="D157" s="1" t="s">
         <v>890</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>891</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
@@ -8972,36 +8960,30 @@
         <v>5</v>
       </c>
       <c r="G157" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="H157" s="1" t="s">
         <v>892</v>
-      </c>
-      <c r="H157" s="1" t="s">
-        <v>893</v>
       </c>
       <c r="I157" s="1">
         <v>0</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K157" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L157" s="7" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="158" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C158" s="1" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="158" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A158" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="C158" s="1" t="s">
+      <c r="D158" s="1" t="s">
         <v>895</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>896</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
@@ -9010,36 +8992,30 @@
         <v>5</v>
       </c>
       <c r="G158" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="H158" s="1" t="s">
         <v>897</v>
-      </c>
-      <c r="H158" s="1" t="s">
-        <v>898</v>
       </c>
       <c r="I158" s="1">
         <v>0</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K158" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L158" s="7" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="159" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C159" s="1" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="159" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A159" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="C159" s="1" t="s">
+      <c r="D159" s="1" t="s">
         <v>900</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>901</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
@@ -9048,36 +9024,30 @@
         <v>5</v>
       </c>
       <c r="G159" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="H159" s="1" t="s">
         <v>902</v>
-      </c>
-      <c r="H159" s="1" t="s">
-        <v>903</v>
       </c>
       <c r="I159" s="1">
         <v>0</v>
       </c>
       <c r="J159" s="8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K159" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L159" s="7" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="160" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C160" s="1" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="160" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A160" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="C160" s="1" t="s">
+      <c r="D160" s="1" t="s">
         <v>905</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>906</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
@@ -9086,30 +9056,30 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="H160" s="1" t="s">
         <v>907</v>
-      </c>
-      <c r="H160" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="I160" s="1">
         <v>0</v>
       </c>
       <c r="J160" s="8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K160" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L160" s="7" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A161" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>910</v>
@@ -9144,10 +9114,10 @@
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A162" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>916</v>
@@ -9182,10 +9152,10 @@
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A163" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>921</v>
@@ -9220,10 +9190,10 @@
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A164" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>926</v>
@@ -9258,10 +9228,10 @@
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A165" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>931</v>
@@ -9296,10 +9266,10 @@
     </row>
     <row r="166" customHeight="1" spans="1:12">
       <c r="A166" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>936</v>
@@ -9334,10 +9304,10 @@
     </row>
     <row r="167" customHeight="1" spans="1:12">
       <c r="A167" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>942</v>
@@ -9372,10 +9342,10 @@
     </row>
     <row r="168" customHeight="1" spans="1:12">
       <c r="A168" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>947</v>
@@ -9410,10 +9380,10 @@
     </row>
     <row r="169" customHeight="1" spans="1:12">
       <c r="A169" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>952</v>
@@ -9448,10 +9418,10 @@
     </row>
     <row r="170" customHeight="1" spans="1:12">
       <c r="A170" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>957</v>
@@ -9486,10 +9456,10 @@
     </row>
     <row r="171" customHeight="1" spans="1:12">
       <c r="A171" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>962</v>
@@ -9524,10 +9494,10 @@
     </row>
     <row r="172" customHeight="1" spans="1:12">
       <c r="A172" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>968</v>
@@ -9562,10 +9532,10 @@
     </row>
     <row r="173" customHeight="1" spans="1:12">
       <c r="A173" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>973</v>
@@ -9600,10 +9570,10 @@
     </row>
     <row r="174" customHeight="1" spans="1:12">
       <c r="A174" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>978</v>
@@ -9638,10 +9608,10 @@
     </row>
     <row r="175" customHeight="1" spans="1:12">
       <c r="A175" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>983</v>
@@ -9676,10 +9646,10 @@
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A176" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>988</v>
@@ -9714,10 +9684,10 @@
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A177" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>994</v>
@@ -9752,10 +9722,10 @@
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A178" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>999</v>
@@ -9790,10 +9760,10 @@
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A179" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>1004</v>
@@ -9828,10 +9798,10 @@
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A180" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1009</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="1014">
   <si>
     <t>_Id</t>
   </si>
@@ -2788,85 +2788,85 @@
     <t>10154</t>
   </si>
   <si>
+    <t>1155</t>
+  </si>
+  <si>
+    <t>深渊虫穴</t>
+  </si>
+  <si>
+    <t>1600-1</t>
+  </si>
+  <si>
+    <t>深渊虫心</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210073,1009</t>
+  </si>
+  <si>
+    <t>10155</t>
+  </si>
+  <si>
+    <t>1156</t>
+  </si>
+  <si>
+    <t>深渊虫巢</t>
+  </si>
+  <si>
+    <t>1600-2</t>
+  </si>
+  <si>
+    <t>深渊龙皮</t>
+  </si>
+  <si>
+    <t>10156</t>
+  </si>
+  <si>
+    <t>1157</t>
+  </si>
+  <si>
+    <t>深渊魔猪厅</t>
+  </si>
+  <si>
+    <t>1600-3</t>
+  </si>
+  <si>
+    <t>深渊猪皮</t>
+  </si>
+  <si>
+    <t>10157</t>
+  </si>
+  <si>
+    <t>1158</t>
+  </si>
+  <si>
+    <t>深渊魔猪殿</t>
+  </si>
+  <si>
+    <t>1600-4</t>
+  </si>
+  <si>
+    <t>深渊猪心</t>
+  </si>
+  <si>
+    <t>10158</t>
+  </si>
+  <si>
+    <t>1159</t>
+  </si>
+  <si>
+    <t>深渊桃源</t>
+  </si>
+  <si>
+    <t>1600-5</t>
+  </si>
+  <si>
+    <t>深渊蝎皮</t>
+  </si>
+  <si>
+    <t>10159</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1155</t>
-  </si>
-  <si>
-    <t>深渊虫穴</t>
-  </si>
-  <si>
-    <t>1600-1</t>
-  </si>
-  <si>
-    <t>深渊虫心</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210073,1009</t>
-  </si>
-  <si>
-    <t>10155</t>
-  </si>
-  <si>
-    <t>1156</t>
-  </si>
-  <si>
-    <t>深渊虫巢</t>
-  </si>
-  <si>
-    <t>1600-2</t>
-  </si>
-  <si>
-    <t>深渊龙皮</t>
-  </si>
-  <si>
-    <t>10156</t>
-  </si>
-  <si>
-    <t>1157</t>
-  </si>
-  <si>
-    <t>深渊魔猪厅</t>
-  </si>
-  <si>
-    <t>1600-3</t>
-  </si>
-  <si>
-    <t>深渊猪皮</t>
-  </si>
-  <si>
-    <t>10157</t>
-  </si>
-  <si>
-    <t>1158</t>
-  </si>
-  <si>
-    <t>深渊魔猪殿</t>
-  </si>
-  <si>
-    <t>1600-4</t>
-  </si>
-  <si>
-    <t>深渊猪心</t>
-  </si>
-  <si>
-    <t>10158</t>
-  </si>
-  <si>
-    <t>1159</t>
-  </si>
-  <si>
-    <t>深渊桃源</t>
-  </si>
-  <si>
-    <t>1600-5</t>
-  </si>
-  <si>
-    <t>深渊蝎皮</t>
-  </si>
-  <si>
-    <t>10159</t>
   </si>
   <si>
     <t>1160</t>
@@ -4123,14 +4123,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A3:M180"/>
-  <sheetFormatPr defaultColWidth="9.25833333333333" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.25663716814159" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9.25833333333333" style="1" customWidth="1"/>
-    <col min="4" max="9" width="11.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="75.8166666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="70.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="39.375" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9.25833333333333" style="1" customWidth="1"/>
+    <col min="1" max="3" width="9.25663716814159" style="1" customWidth="1"/>
+    <col min="4" max="9" width="11.6283185840708" style="1" customWidth="1"/>
+    <col min="10" max="10" width="75.8141592920354" style="1" customWidth="1"/>
+    <col min="11" max="11" width="70.5044247787611" style="1" customWidth="1"/>
+    <col min="12" max="12" width="39.3716814159292" style="4" customWidth="1"/>
+    <col min="13" max="16384" width="9.25663716814159" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:13">
@@ -9074,18 +9074,12 @@
         <v>908</v>
       </c>
     </row>
-    <row r="161" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A161" s="1" t="s">
+    <row r="161" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C161" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="C161" s="1" t="s">
+      <c r="D161" s="1" t="s">
         <v>910</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>911</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
@@ -9094,36 +9088,30 @@
         <v>5</v>
       </c>
       <c r="G161" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="H161" s="1" t="s">
         <v>912</v>
-      </c>
-      <c r="H161" s="1" t="s">
-        <v>913</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="K161" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L161" s="7" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="162" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C162" s="1" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="162" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A162" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="C162" s="1" t="s">
+      <c r="D162" s="1" t="s">
         <v>916</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>917</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
@@ -9132,36 +9120,30 @@
         <v>5</v>
       </c>
       <c r="G162" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="H162" s="1" t="s">
         <v>918</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>919</v>
       </c>
       <c r="I162" s="1">
         <v>0</v>
       </c>
       <c r="J162" s="8" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="K162" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L162" s="7" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="163" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C163" s="1" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="163" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A163" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="C163" s="1" t="s">
+      <c r="D163" s="1" t="s">
         <v>921</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>922</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9170,36 +9152,30 @@
         <v>5</v>
       </c>
       <c r="G163" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="H163" s="1" t="s">
         <v>923</v>
-      </c>
-      <c r="H163" s="1" t="s">
-        <v>924</v>
       </c>
       <c r="I163" s="1">
         <v>0</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="K163" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L163" s="7" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="164" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C164" s="1" t="s">
         <v>925</v>
       </c>
-    </row>
-    <row r="164" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A164" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="C164" s="1" t="s">
+      <c r="D164" s="1" t="s">
         <v>926</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>927</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
@@ -9208,36 +9184,30 @@
         <v>5</v>
       </c>
       <c r="G164" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="H164" s="1" t="s">
         <v>928</v>
-      </c>
-      <c r="H164" s="1" t="s">
-        <v>929</v>
       </c>
       <c r="I164" s="1">
         <v>0</v>
       </c>
       <c r="J164" s="8" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="K164" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L164" s="7" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="165" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C165" s="1" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="165" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A165" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="C165" s="1" t="s">
+      <c r="D165" s="1" t="s">
         <v>931</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>932</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -9246,30 +9216,30 @@
         <v>5</v>
       </c>
       <c r="G165" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="H165" s="1" t="s">
         <v>933</v>
-      </c>
-      <c r="H165" s="1" t="s">
-        <v>934</v>
       </c>
       <c r="I165" s="1">
         <v>0</v>
       </c>
       <c r="J165" s="8" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="K165" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="166" customHeight="1" spans="1:12">
       <c r="A166" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>936</v>
@@ -9304,10 +9274,10 @@
     </row>
     <row r="167" customHeight="1" spans="1:12">
       <c r="A167" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>942</v>
@@ -9342,10 +9312,10 @@
     </row>
     <row r="168" customHeight="1" spans="1:12">
       <c r="A168" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>947</v>
@@ -9380,10 +9350,10 @@
     </row>
     <row r="169" customHeight="1" spans="1:12">
       <c r="A169" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>952</v>
@@ -9418,10 +9388,10 @@
     </row>
     <row r="170" customHeight="1" spans="1:12">
       <c r="A170" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>957</v>
@@ -9456,10 +9426,10 @@
     </row>
     <row r="171" customHeight="1" spans="1:12">
       <c r="A171" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>962</v>
@@ -9494,10 +9464,10 @@
     </row>
     <row r="172" customHeight="1" spans="1:12">
       <c r="A172" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>968</v>
@@ -9532,10 +9502,10 @@
     </row>
     <row r="173" customHeight="1" spans="1:12">
       <c r="A173" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>973</v>
@@ -9570,10 +9540,10 @@
     </row>
     <row r="174" customHeight="1" spans="1:12">
       <c r="A174" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>978</v>
@@ -9608,10 +9578,10 @@
     </row>
     <row r="175" customHeight="1" spans="1:12">
       <c r="A175" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>983</v>
@@ -9646,10 +9616,10 @@
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A176" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>988</v>
@@ -9684,10 +9654,10 @@
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A177" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>994</v>
@@ -9722,10 +9692,10 @@
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A178" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>999</v>
@@ -9760,10 +9730,10 @@
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A179" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>1004</v>
@@ -9798,10 +9768,10 @@
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A180" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1009</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="1014">
   <si>
     <t>_Id</t>
   </si>
@@ -2866,85 +2866,85 @@
     <t>10159</t>
   </si>
   <si>
+    <t>1160</t>
+  </si>
+  <si>
+    <t>深渊魔禁地</t>
+  </si>
+  <si>
+    <t>1650-1</t>
+  </si>
+  <si>
+    <t>深渊宝甲</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210074,1009</t>
+  </si>
+  <si>
+    <t>10160</t>
+  </si>
+  <si>
+    <t>1161</t>
+  </si>
+  <si>
+    <t>深渊魔神殿</t>
+  </si>
+  <si>
+    <t>1650-2</t>
+  </si>
+  <si>
+    <t>深渊号角</t>
+  </si>
+  <si>
+    <t>10161</t>
+  </si>
+  <si>
+    <t>1162</t>
+  </si>
+  <si>
+    <t>深渊邪禁地</t>
+  </si>
+  <si>
+    <t>1650-3</t>
+  </si>
+  <si>
+    <t>深渊雕像</t>
+  </si>
+  <si>
+    <t>10162</t>
+  </si>
+  <si>
+    <t>1163</t>
+  </si>
+  <si>
+    <t>深渊邪魔殿</t>
+  </si>
+  <si>
+    <t>1650-4</t>
+  </si>
+  <si>
+    <t>深渊神像</t>
+  </si>
+  <si>
+    <t>10163</t>
+  </si>
+  <si>
+    <t>1164</t>
+  </si>
+  <si>
+    <t>深渊封魔殿</t>
+  </si>
+  <si>
+    <t>1650-5</t>
+  </si>
+  <si>
+    <t>深渊獠牙</t>
+  </si>
+  <si>
+    <t>10164</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1160</t>
-  </si>
-  <si>
-    <t>深渊魔禁地</t>
-  </si>
-  <si>
-    <t>1650-1</t>
-  </si>
-  <si>
-    <t>深渊宝甲</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210074,1009</t>
-  </si>
-  <si>
-    <t>10160</t>
-  </si>
-  <si>
-    <t>1161</t>
-  </si>
-  <si>
-    <t>深渊魔神殿</t>
-  </si>
-  <si>
-    <t>1650-2</t>
-  </si>
-  <si>
-    <t>深渊号角</t>
-  </si>
-  <si>
-    <t>10161</t>
-  </si>
-  <si>
-    <t>1162</t>
-  </si>
-  <si>
-    <t>深渊邪禁地</t>
-  </si>
-  <si>
-    <t>1650-3</t>
-  </si>
-  <si>
-    <t>深渊雕像</t>
-  </si>
-  <si>
-    <t>10162</t>
-  </si>
-  <si>
-    <t>1163</t>
-  </si>
-  <si>
-    <t>深渊邪魔殿</t>
-  </si>
-  <si>
-    <t>1650-4</t>
-  </si>
-  <si>
-    <t>深渊神像</t>
-  </si>
-  <si>
-    <t>10163</t>
-  </si>
-  <si>
-    <t>1164</t>
-  </si>
-  <si>
-    <t>深渊封魔殿</t>
-  </si>
-  <si>
-    <t>1650-5</t>
-  </si>
-  <si>
-    <t>深渊獠牙</t>
-  </si>
-  <si>
-    <t>10164</t>
   </si>
   <si>
     <t>1165</t>
@@ -9234,18 +9234,12 @@
         <v>934</v>
       </c>
     </row>
-    <row r="166" customHeight="1" spans="1:12">
-      <c r="A166" s="1" t="s">
+    <row r="166" customHeight="1" spans="3:12">
+      <c r="C166" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="C166" s="1" t="s">
+      <c r="D166" s="2" t="s">
         <v>936</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>937</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
@@ -9254,36 +9248,30 @@
         <v>5</v>
       </c>
       <c r="G166" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="H166" s="1" t="s">
         <v>938</v>
-      </c>
-      <c r="H166" s="1" t="s">
-        <v>939</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
       </c>
       <c r="J166" s="8" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="K166" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L166" s="7" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="3:12">
+      <c r="C167" s="1" t="s">
         <v>941</v>
       </c>
-    </row>
-    <row r="167" customHeight="1" spans="1:12">
-      <c r="A167" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="C167" s="1" t="s">
+      <c r="D167" s="2" t="s">
         <v>942</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>943</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
@@ -9292,36 +9280,30 @@
         <v>5</v>
       </c>
       <c r="G167" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="H167" s="1" t="s">
         <v>944</v>
-      </c>
-      <c r="H167" s="1" t="s">
-        <v>945</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
       </c>
       <c r="J167" s="8" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="K167" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L167" s="7" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" spans="3:12">
+      <c r="C168" s="1" t="s">
         <v>946</v>
       </c>
-    </row>
-    <row r="168" customHeight="1" spans="1:12">
-      <c r="A168" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="C168" s="1" t="s">
+      <c r="D168" s="2" t="s">
         <v>947</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>948</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -9330,36 +9312,30 @@
         <v>5</v>
       </c>
       <c r="G168" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="H168" s="1" t="s">
         <v>949</v>
-      </c>
-      <c r="H168" s="1" t="s">
-        <v>950</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="K168" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L168" s="7" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" spans="3:12">
+      <c r="C169" s="1" t="s">
         <v>951</v>
       </c>
-    </row>
-    <row r="169" customHeight="1" spans="1:12">
-      <c r="A169" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="C169" s="1" t="s">
+      <c r="D169" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>953</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
@@ -9368,36 +9344,30 @@
         <v>5</v>
       </c>
       <c r="G169" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="H169" s="1" t="s">
         <v>954</v>
-      </c>
-      <c r="H169" s="1" t="s">
-        <v>955</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="K169" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L169" s="7" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" spans="3:12">
+      <c r="C170" s="1" t="s">
         <v>956</v>
       </c>
-    </row>
-    <row r="170" customHeight="1" spans="1:12">
-      <c r="A170" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="C170" s="1" t="s">
+      <c r="D170" s="2" t="s">
         <v>957</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>958</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -9406,30 +9376,30 @@
         <v>5</v>
       </c>
       <c r="G170" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="H170" s="1" t="s">
         <v>959</v>
-      </c>
-      <c r="H170" s="1" t="s">
-        <v>960</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
       </c>
       <c r="J170" s="8" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="K170" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="1:12">
       <c r="A171" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>962</v>
@@ -9464,10 +9434,10 @@
     </row>
     <row r="172" customHeight="1" spans="1:12">
       <c r="A172" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>968</v>
@@ -9502,10 +9472,10 @@
     </row>
     <row r="173" customHeight="1" spans="1:12">
       <c r="A173" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>973</v>
@@ -9540,10 +9510,10 @@
     </row>
     <row r="174" customHeight="1" spans="1:12">
       <c r="A174" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>978</v>
@@ -9578,10 +9548,10 @@
     </row>
     <row r="175" customHeight="1" spans="1:12">
       <c r="A175" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>983</v>
@@ -9616,10 +9586,10 @@
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A176" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>988</v>
@@ -9654,10 +9624,10 @@
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A177" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>994</v>
@@ -9692,10 +9662,10 @@
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A178" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>999</v>
@@ -9730,10 +9700,10 @@
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A179" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>1004</v>
@@ -9768,10 +9738,10 @@
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A180" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1009</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="1014">
   <si>
     <t>_Id</t>
   </si>
@@ -2944,85 +2944,85 @@
     <t>10164</t>
   </si>
   <si>
+    <t>1165</t>
+  </si>
+  <si>
+    <t>深渊烈焰殿</t>
+  </si>
+  <si>
+    <t>1700-1</t>
+  </si>
+  <si>
+    <t>深渊树心</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210075,1009</t>
+  </si>
+  <si>
+    <t>10165</t>
+  </si>
+  <si>
+    <t>1166</t>
+  </si>
+  <si>
+    <t>深渊封邪殿</t>
+  </si>
+  <si>
+    <t>1700-2</t>
+  </si>
+  <si>
+    <t>深渊魔心</t>
+  </si>
+  <si>
+    <t>10166</t>
+  </si>
+  <si>
+    <t>1167</t>
+  </si>
+  <si>
+    <t>深渊尸魔殿</t>
+  </si>
+  <si>
+    <t>1700-3</t>
+  </si>
+  <si>
+    <t>深渊尸心</t>
+  </si>
+  <si>
+    <t>10167</t>
+  </si>
+  <si>
+    <t>1168</t>
+  </si>
+  <si>
+    <t>深渊骨魔殿</t>
+  </si>
+  <si>
+    <t>1700-4</t>
+  </si>
+  <si>
+    <t>深渊法杖</t>
+  </si>
+  <si>
+    <t>10168</t>
+  </si>
+  <si>
+    <t>1169</t>
+  </si>
+  <si>
+    <t>深渊魔牛殿</t>
+  </si>
+  <si>
+    <t>1700-5</t>
+  </si>
+  <si>
+    <t>深渊权杖</t>
+  </si>
+  <si>
+    <t>10169</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1165</t>
-  </si>
-  <si>
-    <t>深渊烈焰殿</t>
-  </si>
-  <si>
-    <t>1700-1</t>
-  </si>
-  <si>
-    <t>深渊树心</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210075,1009</t>
-  </si>
-  <si>
-    <t>10165</t>
-  </si>
-  <si>
-    <t>1166</t>
-  </si>
-  <si>
-    <t>深渊封邪殿</t>
-  </si>
-  <si>
-    <t>1700-2</t>
-  </si>
-  <si>
-    <t>深渊魔心</t>
-  </si>
-  <si>
-    <t>10166</t>
-  </si>
-  <si>
-    <t>1167</t>
-  </si>
-  <si>
-    <t>深渊尸魔殿</t>
-  </si>
-  <si>
-    <t>1700-3</t>
-  </si>
-  <si>
-    <t>深渊尸心</t>
-  </si>
-  <si>
-    <t>10167</t>
-  </si>
-  <si>
-    <t>1168</t>
-  </si>
-  <si>
-    <t>深渊骨魔殿</t>
-  </si>
-  <si>
-    <t>1700-4</t>
-  </si>
-  <si>
-    <t>深渊法杖</t>
-  </si>
-  <si>
-    <t>10168</t>
-  </si>
-  <si>
-    <t>1169</t>
-  </si>
-  <si>
-    <t>深渊魔牛殿</t>
-  </si>
-  <si>
-    <t>1700-5</t>
-  </si>
-  <si>
-    <t>深渊权杖</t>
-  </si>
-  <si>
-    <t>10169</t>
   </si>
   <si>
     <t>1170</t>
@@ -3279,12 +3279,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -9394,18 +9394,12 @@
         <v>960</v>
       </c>
     </row>
-    <row r="171" customHeight="1" spans="1:12">
-      <c r="A171" s="1" t="s">
+    <row r="171" customHeight="1" spans="3:12">
+      <c r="C171" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="C171" s="1" t="s">
+      <c r="D171" s="1" t="s">
         <v>962</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>963</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -9414,36 +9408,30 @@
         <v>5</v>
       </c>
       <c r="G171" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="H171" s="1" t="s">
         <v>964</v>
-      </c>
-      <c r="H171" s="1" t="s">
-        <v>965</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
       </c>
       <c r="J171" s="8" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="K171" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L171" s="7" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" spans="3:12">
+      <c r="C172" s="1" t="s">
         <v>967</v>
       </c>
-    </row>
-    <row r="172" customHeight="1" spans="1:12">
-      <c r="A172" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="C172" s="1" t="s">
+      <c r="D172" s="1" t="s">
         <v>968</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>969</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
@@ -9452,36 +9440,30 @@
         <v>5</v>
       </c>
       <c r="G172" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="H172" s="1" t="s">
         <v>970</v>
-      </c>
-      <c r="H172" s="1" t="s">
-        <v>971</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
       </c>
       <c r="J172" s="8" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="K172" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L172" s="7" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" spans="3:12">
+      <c r="C173" s="1" t="s">
         <v>972</v>
       </c>
-    </row>
-    <row r="173" customHeight="1" spans="1:12">
-      <c r="A173" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="C173" s="1" t="s">
+      <c r="D173" s="1" t="s">
         <v>973</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>974</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
@@ -9490,36 +9472,30 @@
         <v>5</v>
       </c>
       <c r="G173" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="H173" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="H173" s="1" t="s">
-        <v>976</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
       </c>
       <c r="J173" s="8" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="K173" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L173" s="7" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" spans="3:12">
+      <c r="C174" s="1" t="s">
         <v>977</v>
       </c>
-    </row>
-    <row r="174" customHeight="1" spans="1:12">
-      <c r="A174" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="C174" s="1" t="s">
+      <c r="D174" s="1" t="s">
         <v>978</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>979</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -9528,36 +9504,30 @@
         <v>5</v>
       </c>
       <c r="G174" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="H174" s="1" t="s">
         <v>980</v>
-      </c>
-      <c r="H174" s="1" t="s">
-        <v>981</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
       </c>
       <c r="J174" s="8" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="K174" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L174" s="7" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" spans="3:12">
+      <c r="C175" s="1" t="s">
         <v>982</v>
       </c>
-    </row>
-    <row r="175" customHeight="1" spans="1:12">
-      <c r="A175" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="C175" s="1" t="s">
+      <c r="D175" s="1" t="s">
         <v>983</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>984</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
@@ -9566,30 +9536,30 @@
         <v>5</v>
       </c>
       <c r="G175" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="H175" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="H175" s="1" t="s">
-        <v>986</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="K175" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L175" s="7" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A176" s="1" t="s">
-        <v>961</v>
+        <v>987</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>961</v>
+        <v>987</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>988</v>
@@ -9624,10 +9594,10 @@
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A177" s="1" t="s">
-        <v>961</v>
+        <v>987</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>961</v>
+        <v>987</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>994</v>
@@ -9662,10 +9632,10 @@
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A178" s="1" t="s">
-        <v>961</v>
+        <v>987</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>961</v>
+        <v>987</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>999</v>
@@ -9700,10 +9670,10 @@
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A179" s="1" t="s">
-        <v>961</v>
+        <v>987</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>961</v>
+        <v>987</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>1004</v>
@@ -9738,10 +9708,10 @@
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A180" s="1" t="s">
-        <v>961</v>
+        <v>987</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>961</v>
+        <v>987</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>1009</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="1007">
   <si>
     <t>_Id</t>
   </si>
@@ -1933,10 +1933,10 @@
     <t>金装</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210035,1009</t>
-  </si>
-  <si>
-    <t>10,2500,1000,18000,600000,140000</t>
+    <t>202001,300091,104,504,210035,1009,505</t>
+  </si>
+  <si>
+    <t>10,2500,1000,18000,600000,140000,600000</t>
   </si>
   <si>
     <t>10105</t>
@@ -1954,7 +1954,7 @@
     <t>地狱鹿茸</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210036,1009</t>
+    <t>202001,300091,104,504,210036,1009,505</t>
   </si>
   <si>
     <t>10106</t>
@@ -1972,7 +1972,7 @@
     <t>地狱草帽</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210037,1009</t>
+    <t>202001,300091,104,504,210037,1009,505</t>
   </si>
   <si>
     <t>10107</t>
@@ -1990,7 +1990,7 @@
     <t>地狱猫爪</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210038,1009</t>
+    <t>202001,300091,104,504,210038,1009,505</t>
   </si>
   <si>
     <t>10108</t>
@@ -2008,7 +2008,7 @@
     <t>地狱花朵</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210039,1009</t>
+    <t>202001,300091,104,504,210039,1009,505</t>
   </si>
   <si>
     <t>10109</t>
@@ -2026,7 +2026,7 @@
     <t>地狱冰晶</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210040,1009</t>
+    <t>202001,300091,104,504,210040,1009,505</t>
   </si>
   <si>
     <t>10110</t>
@@ -2044,7 +2044,7 @@
     <t>地狱蝠翼</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210041,1009</t>
+    <t>202001,300091,104,504,210041,1009,505</t>
   </si>
   <si>
     <t>10111</t>
@@ -2062,7 +2062,7 @@
     <t>地狱魂火</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210042,1009</t>
+    <t>202001,300091,104,504,210042,1009,505</t>
   </si>
   <si>
     <t>10112</t>
@@ -2080,7 +2080,7 @@
     <t>地狱腐肉</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210043,1009</t>
+    <t>202001,300091,104,504,210043,1009,505</t>
   </si>
   <si>
     <t>10113</t>
@@ -2098,7 +2098,7 @@
     <t>地狱蛇胆</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210044,1009</t>
+    <t>202001,300091,104,504,210044,1009,505</t>
   </si>
   <si>
     <t>10114</t>
@@ -2116,7 +2116,7 @@
     <t>地狱狼爪</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210045,1009</t>
+    <t>202001,300091,104,504,210045,1009,505</t>
   </si>
   <si>
     <t>10115</t>
@@ -2134,7 +2134,7 @@
     <t>地狱虫皮</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210046,1009</t>
+    <t>202001,300091,104,504,210046,1009,505</t>
   </si>
   <si>
     <t>10116</t>
@@ -2152,7 +2152,7 @@
     <t>地狱鹰羽</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210047,1009</t>
+    <t>202001,300091,104,504,210047,1009,505</t>
   </si>
   <si>
     <t>10117</t>
@@ -2170,7 +2170,7 @@
     <t>地狱虫角</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210048,1009</t>
+    <t>202001,300091,104,504,210048,1009,505</t>
   </si>
   <si>
     <t>10118</t>
@@ -2188,7 +2188,7 @@
     <t>地狱蜈膏</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210049,1009</t>
+    <t>202001,300091,104,504,210049,1009,505</t>
   </si>
   <si>
     <t>10119</t>
@@ -2206,7 +2206,7 @@
     <t>地狱虫心</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210050,1009</t>
+    <t>202001,300091,104,504,210050,1009,505</t>
   </si>
   <si>
     <t>10120</t>
@@ -2224,7 +2224,7 @@
     <t>地狱龙皮</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210051,1009</t>
+    <t>202001,300091,104,504,210051,1009,505</t>
   </si>
   <si>
     <t>10121</t>
@@ -2242,7 +2242,7 @@
     <t>地狱猪皮</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210052,1009</t>
+    <t>202001,300091,104,504,210052,1009,505</t>
   </si>
   <si>
     <t>10122</t>
@@ -2260,7 +2260,7 @@
     <t>地狱猪心</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210053,1009</t>
+    <t>202001,300091,104,504,210053,1009,505</t>
   </si>
   <si>
     <t>10123</t>
@@ -2278,7 +2278,7 @@
     <t>地狱蝎皮</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210054,1009</t>
+    <t>202001,300091,104,504,210054,1009,505</t>
   </si>
   <si>
     <t>10124</t>
@@ -2296,7 +2296,7 @@
     <t>地狱宝甲</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210055,1009</t>
+    <t>202001,300091,104,504,210055,1009,505</t>
   </si>
   <si>
     <t>10125</t>
@@ -2314,7 +2314,7 @@
     <t>地狱号角</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210056,1009</t>
+    <t>202001,300091,104,504,210056,1009,505</t>
   </si>
   <si>
     <t>10126</t>
@@ -2332,7 +2332,7 @@
     <t>地狱雕像</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210057,1009</t>
+    <t>202001,300091,104,504,210057,1009,505</t>
   </si>
   <si>
     <t>10127</t>
@@ -2350,7 +2350,7 @@
     <t>地狱神像</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210058,1009</t>
+    <t>202001,300091,104,504,210058,1009,505</t>
   </si>
   <si>
     <t>10128</t>
@@ -2368,7 +2368,7 @@
     <t>地狱獠牙</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210059,1009</t>
+    <t>202001,300091,104,504,210059,1009,505</t>
   </si>
   <si>
     <t>10129</t>
@@ -2386,7 +2386,7 @@
     <t>地狱树心</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210060,1009</t>
+    <t>202001,300091,104,504,210060,1009,505</t>
   </si>
   <si>
     <t>10130</t>
@@ -2404,7 +2404,7 @@
     <t>地狱魔心</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210061,1009</t>
+    <t>202001,300091,104,504,210061,1009,505</t>
   </si>
   <si>
     <t>10131</t>
@@ -2422,7 +2422,7 @@
     <t>地狱尸心</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210062,1009</t>
+    <t>202001,300091,104,504,210062,1009,505</t>
   </si>
   <si>
     <t>10132</t>
@@ -2440,7 +2440,7 @@
     <t>地狱法杖</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210063,1009</t>
+    <t>202001,300091,104,504,210063,1009,505</t>
   </si>
   <si>
     <t>10133</t>
@@ -2458,7 +2458,7 @@
     <t>地狱权杖</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210064,1009</t>
+    <t>202001,300091,104,504,210064,1009,505</t>
   </si>
   <si>
     <t>10134</t>
@@ -2476,7 +2476,7 @@
     <t>地狱战锤</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210065,1009</t>
+    <t>202001,300091,104,504,210065,1009,505</t>
   </si>
   <si>
     <t>10135</t>
@@ -2494,7 +2494,7 @@
     <t>地狱血核</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210066,1009</t>
+    <t>202001,300091,104,504,210066,1009,505</t>
   </si>
   <si>
     <t>10136</t>
@@ -2512,7 +2512,7 @@
     <t>地狱魔核</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210067,1009</t>
+    <t>202001,300091,104,504,210067,1009,505</t>
   </si>
   <si>
     <t>10137</t>
@@ -2530,7 +2530,7 @@
     <t>地狱龙甲</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210068,1009</t>
+    <t>202001,300091,104,504,210068,1009,505</t>
   </si>
   <si>
     <t>10138</t>
@@ -2548,7 +2548,7 @@
     <t>地狱龙爪</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210069,1009</t>
+    <t>202001,300091,104,504,210069,1009,505</t>
   </si>
   <si>
     <t>10139</t>
@@ -2566,7 +2566,7 @@
     <t>暗金装备</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210070,1009</t>
+    <t>202002,300091,105,504,210070,1009,505</t>
   </si>
   <si>
     <t>10140</t>
@@ -2644,9 +2644,6 @@
     <t>深渊冰晶</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210071,1009</t>
-  </si>
-  <si>
     <t>10145</t>
   </si>
   <si>
@@ -2722,9 +2719,6 @@
     <t>深渊狼爪</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210072,1009</t>
-  </si>
-  <si>
     <t>10150</t>
   </si>
   <si>
@@ -2800,9 +2794,6 @@
     <t>深渊虫心</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210073,1009</t>
-  </si>
-  <si>
     <t>10155</t>
   </si>
   <si>
@@ -2878,9 +2869,6 @@
     <t>深渊宝甲</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210074,1009</t>
-  </si>
-  <si>
     <t>10160</t>
   </si>
   <si>
@@ -2956,9 +2944,6 @@
     <t>深渊树心</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210075,1009</t>
-  </si>
-  <si>
     <t>10165</t>
   </si>
   <si>
@@ -3022,9 +3007,6 @@
     <t>10169</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>1170</t>
   </si>
   <si>
@@ -3035,9 +3017,6 @@
   </si>
   <si>
     <t>深渊战锤</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210076,1009</t>
   </si>
   <si>
     <t>10170</t>
@@ -3279,12 +3258,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4122,15 +4101,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M180"/>
-  <sheetFormatPr defaultColWidth="9.25663716814159" defaultRowHeight="18" customHeight="1"/>
+  <dimension ref="B3:M180"/>
+  <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9.25663716814159" style="1" customWidth="1"/>
-    <col min="4" max="9" width="11.6283185840708" style="1" customWidth="1"/>
-    <col min="10" max="10" width="75.8141592920354" style="1" customWidth="1"/>
-    <col min="11" max="11" width="70.5044247787611" style="1" customWidth="1"/>
-    <col min="12" max="12" width="39.3716814159292" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9.25663716814159" style="1" customWidth="1"/>
+    <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="4" max="9" width="11.6272727272727" style="1" customWidth="1"/>
+    <col min="10" max="10" width="75.8181818181818" style="1" customWidth="1"/>
+    <col min="11" max="11" width="70.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="39.3727272727273" style="4" customWidth="1"/>
+    <col min="13" max="16384" width="9.25454545454545" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:13">
@@ -8777,21 +8756,21 @@
         <v>0</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>861</v>
+        <v>835</v>
       </c>
       <c r="K151" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L151" s="7" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="3:12">
       <c r="C152" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>864</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
@@ -8800,30 +8779,30 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="H152" s="1" t="s">
         <v>865</v>
-      </c>
-      <c r="H152" s="1" t="s">
-        <v>866</v>
       </c>
       <c r="I152" s="1">
         <v>0</v>
       </c>
       <c r="J152" s="8" t="s">
-        <v>861</v>
+        <v>835</v>
       </c>
       <c r="K152" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L152" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="3:12">
       <c r="C153" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>868</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>869</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
@@ -8832,30 +8811,30 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="H153" s="1" t="s">
         <v>870</v>
-      </c>
-      <c r="H153" s="1" t="s">
-        <v>871</v>
       </c>
       <c r="I153" s="1">
         <v>0</v>
       </c>
       <c r="J153" s="8" t="s">
-        <v>861</v>
+        <v>835</v>
       </c>
       <c r="K153" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L153" s="7" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="3:12">
       <c r="C154" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>873</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>874</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
@@ -8864,30 +8843,30 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="H154" s="1" t="s">
         <v>875</v>
-      </c>
-      <c r="H154" s="1" t="s">
-        <v>876</v>
       </c>
       <c r="I154" s="1">
         <v>0</v>
       </c>
       <c r="J154" s="8" t="s">
-        <v>861</v>
+        <v>835</v>
       </c>
       <c r="K154" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L154" s="7" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="3:12">
       <c r="C155" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>878</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>879</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
@@ -8896,30 +8875,30 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="H155" s="1" t="s">
         <v>880</v>
-      </c>
-      <c r="H155" s="1" t="s">
-        <v>881</v>
       </c>
       <c r="I155" s="1">
         <v>0</v>
       </c>
       <c r="J155" s="8" t="s">
-        <v>861</v>
+        <v>835</v>
       </c>
       <c r="K155" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L155" s="7" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C156" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>883</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>884</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
@@ -8928,30 +8907,30 @@
         <v>5</v>
       </c>
       <c r="G156" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="H156" s="1" t="s">
         <v>885</v>
-      </c>
-      <c r="H156" s="1" t="s">
-        <v>886</v>
       </c>
       <c r="I156" s="1">
         <v>0</v>
       </c>
       <c r="J156" s="8" t="s">
-        <v>887</v>
+        <v>835</v>
       </c>
       <c r="K156" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L156" s="7" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C157" s="1" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
@@ -8960,30 +8939,30 @@
         <v>5</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="I157" s="1">
         <v>0</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>887</v>
+        <v>835</v>
       </c>
       <c r="K157" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L157" s="7" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C158" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
@@ -8992,30 +8971,30 @@
         <v>5</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="I158" s="1">
         <v>0</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>887</v>
+        <v>835</v>
       </c>
       <c r="K158" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L158" s="7" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C159" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
@@ -9024,30 +9003,30 @@
         <v>5</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="I159" s="1">
         <v>0</v>
       </c>
       <c r="J159" s="8" t="s">
-        <v>887</v>
+        <v>835</v>
       </c>
       <c r="K159" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L159" s="7" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C160" s="1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
@@ -9056,30 +9035,30 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="I160" s="1">
         <v>0</v>
       </c>
       <c r="J160" s="8" t="s">
-        <v>887</v>
+        <v>835</v>
       </c>
       <c r="K160" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L160" s="7" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C161" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
@@ -9088,30 +9067,30 @@
         <v>5</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>913</v>
+        <v>835</v>
       </c>
       <c r="K161" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L161" s="7" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C162" s="1" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
@@ -9120,30 +9099,30 @@
         <v>5</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="I162" s="1">
         <v>0</v>
       </c>
       <c r="J162" s="8" t="s">
-        <v>913</v>
+        <v>835</v>
       </c>
       <c r="K162" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L162" s="7" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C163" s="1" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9152,30 +9131,30 @@
         <v>5</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="I163" s="1">
         <v>0</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>913</v>
+        <v>835</v>
       </c>
       <c r="K163" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L163" s="7" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C164" s="1" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
@@ -9184,30 +9163,30 @@
         <v>5</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="I164" s="1">
         <v>0</v>
       </c>
       <c r="J164" s="8" t="s">
-        <v>913</v>
+        <v>835</v>
       </c>
       <c r="K164" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L164" s="7" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C165" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -9216,30 +9195,30 @@
         <v>5</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="I165" s="1">
         <v>0</v>
       </c>
       <c r="J165" s="8" t="s">
-        <v>913</v>
+        <v>835</v>
       </c>
       <c r="K165" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="166" customHeight="1" spans="3:12">
       <c r="C166" s="1" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
@@ -9248,30 +9227,30 @@
         <v>5</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
       </c>
       <c r="J166" s="8" t="s">
-        <v>939</v>
+        <v>835</v>
       </c>
       <c r="K166" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L166" s="7" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="3:12">
       <c r="C167" s="1" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
@@ -9280,30 +9259,30 @@
         <v>5</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
       </c>
       <c r="J167" s="8" t="s">
-        <v>939</v>
+        <v>835</v>
       </c>
       <c r="K167" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L167" s="7" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
     </row>
     <row r="168" customHeight="1" spans="3:12">
       <c r="C168" s="1" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -9312,30 +9291,30 @@
         <v>5</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>939</v>
+        <v>835</v>
       </c>
       <c r="K168" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L168" s="7" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
     </row>
     <row r="169" customHeight="1" spans="3:12">
       <c r="C169" s="1" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
@@ -9344,30 +9323,30 @@
         <v>5</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>939</v>
+        <v>835</v>
       </c>
       <c r="K169" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L169" s="7" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
     </row>
     <row r="170" customHeight="1" spans="3:12">
       <c r="C170" s="1" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -9376,30 +9355,30 @@
         <v>5</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
       </c>
       <c r="J170" s="8" t="s">
-        <v>939</v>
+        <v>835</v>
       </c>
       <c r="K170" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="3:12">
       <c r="C171" s="1" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -9408,30 +9387,30 @@
         <v>5</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
       </c>
       <c r="J171" s="8" t="s">
-        <v>965</v>
+        <v>835</v>
       </c>
       <c r="K171" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L171" s="7" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="3:12">
       <c r="C172" s="1" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
@@ -9440,30 +9419,30 @@
         <v>5</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
       </c>
       <c r="J172" s="8" t="s">
-        <v>965</v>
+        <v>835</v>
       </c>
       <c r="K172" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L172" s="7" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="3:12">
       <c r="C173" s="1" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
@@ -9472,30 +9451,30 @@
         <v>5</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
       </c>
       <c r="J173" s="8" t="s">
-        <v>965</v>
+        <v>835</v>
       </c>
       <c r="K173" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L173" s="7" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="3:12">
       <c r="C174" s="1" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -9504,30 +9483,30 @@
         <v>5</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
       </c>
       <c r="J174" s="8" t="s">
-        <v>965</v>
+        <v>835</v>
       </c>
       <c r="K174" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L174" s="7" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="3:12">
       <c r="C175" s="1" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
@@ -9536,36 +9515,30 @@
         <v>5</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>965</v>
+        <v>835</v>
       </c>
       <c r="K175" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L175" s="7" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="176" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A176" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>987</v>
-      </c>
+        <v>981</v>
+      </c>
+    </row>
+    <row r="176" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C176" s="1" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
@@ -9574,36 +9547,30 @@
         <v>5</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="I176" s="1">
         <v>0</v>
       </c>
       <c r="J176" s="8" t="s">
-        <v>992</v>
+        <v>835</v>
       </c>
       <c r="K176" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L176" s="7" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="177" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A177" s="1" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="177" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C177" s="1" t="s">
         <v>987</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>994</v>
-      </c>
       <c r="D177" s="1" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
@@ -9612,36 +9579,30 @@
         <v>5</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="I177" s="1">
         <v>0</v>
       </c>
       <c r="J177" s="8" t="s">
-        <v>992</v>
+        <v>835</v>
       </c>
       <c r="K177" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L177" s="7" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="178" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A178" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>987</v>
-      </c>
+        <v>991</v>
+      </c>
+    </row>
+    <row r="178" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C178" s="1" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
@@ -9650,36 +9611,30 @@
         <v>5</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
       </c>
       <c r="J178" s="8" t="s">
-        <v>992</v>
+        <v>835</v>
       </c>
       <c r="K178" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L178" s="7" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="179" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A179" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>987</v>
-      </c>
+        <v>996</v>
+      </c>
+    </row>
+    <row r="179" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C179" s="1" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -9688,36 +9643,30 @@
         <v>5</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
       </c>
       <c r="J179" s="8" t="s">
-        <v>992</v>
+        <v>835</v>
       </c>
       <c r="K179" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L179" s="7" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="180" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A180" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>987</v>
-      </c>
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="180" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C180" s="1" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
@@ -9726,22 +9675,22 @@
         <v>5</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
       </c>
       <c r="J180" s="8" t="s">
-        <v>992</v>
+        <v>835</v>
       </c>
       <c r="K180" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L180" s="7" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="1003">
   <si>
     <t>_Id</t>
   </si>
@@ -1933,460 +1933,448 @@
     <t>金装</t>
   </si>
   <si>
-    <t>202001,300091,104,504,210035,1009,505</t>
+    <t>202001,300091,104,504,210035,1009</t>
+  </si>
+  <si>
+    <t>10,2500,1000,18000,600000,140000</t>
+  </si>
+  <si>
+    <t>10105</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>地狱村外</t>
+  </si>
+  <si>
+    <t>1100-2</t>
+  </si>
+  <si>
+    <t>地狱鹿茸</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210036,1009</t>
+  </si>
+  <si>
+    <t>10106</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>地狱农场</t>
+  </si>
+  <si>
+    <t>1100-3</t>
+  </si>
+  <si>
+    <t>地狱草帽</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210037,1009</t>
+  </si>
+  <si>
+    <t>10107</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>地狱老城</t>
+  </si>
+  <si>
+    <t>1100-4</t>
+  </si>
+  <si>
+    <t>地狱猫爪</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210038,1009</t>
+  </si>
+  <si>
+    <t>10108</t>
+  </si>
+  <si>
+    <t>1109</t>
+  </si>
+  <si>
+    <t>地狱森林</t>
+  </si>
+  <si>
+    <t>1100-5</t>
+  </si>
+  <si>
+    <t>地狱花朵</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210039,1009</t>
+  </si>
+  <si>
+    <t>10109</t>
+  </si>
+  <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>地狱蝠洞</t>
+  </si>
+  <si>
+    <t>1150-1</t>
+  </si>
+  <si>
+    <t>地狱冰晶</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210040,1009</t>
+  </si>
+  <si>
+    <t>10110</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>地狱骷髅洞</t>
+  </si>
+  <si>
+    <t>1150-2</t>
+  </si>
+  <si>
+    <t>地狱蝠翼</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210041,1009</t>
+  </si>
+  <si>
+    <t>10111</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>地狱通道</t>
+  </si>
+  <si>
+    <t>1150-3</t>
+  </si>
+  <si>
+    <t>地狱魂火</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210042,1009</t>
+  </si>
+  <si>
+    <t>10112</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>地狱尸洞</t>
+  </si>
+  <si>
+    <t>1150-4</t>
+  </si>
+  <si>
+    <t>地狱腐肉</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210043,1009</t>
+  </si>
+  <si>
+    <t>10113</t>
+  </si>
+  <si>
+    <t>1114</t>
+  </si>
+  <si>
+    <t>地狱蛇谷</t>
+  </si>
+  <si>
+    <t>1150-5</t>
+  </si>
+  <si>
+    <t>地狱蛇胆</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210044,1009</t>
+  </si>
+  <si>
+    <t>10114</t>
+  </si>
+  <si>
+    <t>1115</t>
+  </si>
+  <si>
+    <t>地狱狼山</t>
+  </si>
+  <si>
+    <t>1200-1</t>
+  </si>
+  <si>
+    <t>地狱狼爪</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210045,1009</t>
+  </si>
+  <si>
+    <t>10115</t>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>地狱沙洞</t>
+  </si>
+  <si>
+    <t>1200-2</t>
+  </si>
+  <si>
+    <t>地狱虫皮</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210046,1009</t>
+  </si>
+  <si>
+    <t>10116</t>
+  </si>
+  <si>
+    <t>1117</t>
+  </si>
+  <si>
+    <t>地狱鹰崖</t>
+  </si>
+  <si>
+    <t>1200-3</t>
+  </si>
+  <si>
+    <t>地狱鹰羽</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210047,1009</t>
+  </si>
+  <si>
+    <t>10117</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>地狱虫谷</t>
+  </si>
+  <si>
+    <t>1200-4</t>
+  </si>
+  <si>
+    <t>地狱虫角</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210048,1009</t>
+  </si>
+  <si>
+    <t>10118</t>
+  </si>
+  <si>
+    <t>1119</t>
+  </si>
+  <si>
+    <t>地狱虫洞</t>
+  </si>
+  <si>
+    <t>1200-5</t>
+  </si>
+  <si>
+    <t>地狱蜈膏</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210049,1009</t>
+  </si>
+  <si>
+    <t>10119</t>
+  </si>
+  <si>
+    <t>1120</t>
+  </si>
+  <si>
+    <t>地狱虫穴</t>
+  </si>
+  <si>
+    <t>1250-1</t>
+  </si>
+  <si>
+    <t>地狱虫心</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210050,1009</t>
+  </si>
+  <si>
+    <t>10120</t>
+  </si>
+  <si>
+    <t>1121</t>
+  </si>
+  <si>
+    <t>地狱虫巢</t>
+  </si>
+  <si>
+    <t>1250-2</t>
+  </si>
+  <si>
+    <t>地狱龙皮</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210051,1009</t>
+  </si>
+  <si>
+    <t>10121</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>地狱魔猪厅</t>
+  </si>
+  <si>
+    <t>1250-3</t>
+  </si>
+  <si>
+    <t>地狱猪皮</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210052,1009</t>
+  </si>
+  <si>
+    <t>10122</t>
+  </si>
+  <si>
+    <t>1123</t>
+  </si>
+  <si>
+    <t>地狱魔猪殿</t>
+  </si>
+  <si>
+    <t>1250-4</t>
+  </si>
+  <si>
+    <t>地狱猪心</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210053,1009</t>
+  </si>
+  <si>
+    <t>10123</t>
+  </si>
+  <si>
+    <t>1124</t>
+  </si>
+  <si>
+    <t>地狱桃源</t>
+  </si>
+  <si>
+    <t>1250-5</t>
+  </si>
+  <si>
+    <t>地狱蝎皮</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210054,1009</t>
+  </si>
+  <si>
+    <t>10124</t>
+  </si>
+  <si>
+    <t>1125</t>
+  </si>
+  <si>
+    <t>地狱魔禁地</t>
+  </si>
+  <si>
+    <t>1300-1</t>
+  </si>
+  <si>
+    <t>地狱宝甲</t>
+  </si>
+  <si>
+    <t>10125</t>
+  </si>
+  <si>
+    <t>1126</t>
+  </si>
+  <si>
+    <t>地狱魔神殿</t>
+  </si>
+  <si>
+    <t>1300-2</t>
+  </si>
+  <si>
+    <t>地狱号角</t>
+  </si>
+  <si>
+    <t>10126</t>
+  </si>
+  <si>
+    <t>1127</t>
+  </si>
+  <si>
+    <t>地狱邪禁地</t>
+  </si>
+  <si>
+    <t>1300-3</t>
+  </si>
+  <si>
+    <t>地狱雕像</t>
+  </si>
+  <si>
+    <t>10127</t>
+  </si>
+  <si>
+    <t>1128</t>
+  </si>
+  <si>
+    <t>地狱邪魔殿</t>
+  </si>
+  <si>
+    <t>1300-4</t>
+  </si>
+  <si>
+    <t>地狱神像</t>
+  </si>
+  <si>
+    <t>10128</t>
+  </si>
+  <si>
+    <t>1129</t>
+  </si>
+  <si>
+    <t>地狱封魔殿</t>
+  </si>
+  <si>
+    <t>1300-5</t>
+  </si>
+  <si>
+    <t>地狱獠牙</t>
+  </si>
+  <si>
+    <t>10129</t>
+  </si>
+  <si>
+    <t>1130</t>
+  </si>
+  <si>
+    <t>地狱烈焰殿</t>
+  </si>
+  <si>
+    <t>1350-1</t>
+  </si>
+  <si>
+    <t>地狱树心</t>
+  </si>
+  <si>
+    <t>202001,300091,104,504,210060,1009,505</t>
   </si>
   <si>
     <t>10,2500,1000,18000,600000,140000,600000</t>
-  </si>
-  <si>
-    <t>10105</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>地狱村外</t>
-  </si>
-  <si>
-    <t>1100-2</t>
-  </si>
-  <si>
-    <t>地狱鹿茸</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210036,1009,505</t>
-  </si>
-  <si>
-    <t>10106</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>地狱农场</t>
-  </si>
-  <si>
-    <t>1100-3</t>
-  </si>
-  <si>
-    <t>地狱草帽</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210037,1009,505</t>
-  </si>
-  <si>
-    <t>10107</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>地狱老城</t>
-  </si>
-  <si>
-    <t>1100-4</t>
-  </si>
-  <si>
-    <t>地狱猫爪</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210038,1009,505</t>
-  </si>
-  <si>
-    <t>10108</t>
-  </si>
-  <si>
-    <t>1109</t>
-  </si>
-  <si>
-    <t>地狱森林</t>
-  </si>
-  <si>
-    <t>1100-5</t>
-  </si>
-  <si>
-    <t>地狱花朵</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210039,1009,505</t>
-  </si>
-  <si>
-    <t>10109</t>
-  </si>
-  <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>地狱蝠洞</t>
-  </si>
-  <si>
-    <t>1150-1</t>
-  </si>
-  <si>
-    <t>地狱冰晶</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210040,1009,505</t>
-  </si>
-  <si>
-    <t>10110</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>地狱骷髅洞</t>
-  </si>
-  <si>
-    <t>1150-2</t>
-  </si>
-  <si>
-    <t>地狱蝠翼</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210041,1009,505</t>
-  </si>
-  <si>
-    <t>10111</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
-    <t>地狱通道</t>
-  </si>
-  <si>
-    <t>1150-3</t>
-  </si>
-  <si>
-    <t>地狱魂火</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210042,1009,505</t>
-  </si>
-  <si>
-    <t>10112</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>地狱尸洞</t>
-  </si>
-  <si>
-    <t>1150-4</t>
-  </si>
-  <si>
-    <t>地狱腐肉</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210043,1009,505</t>
-  </si>
-  <si>
-    <t>10113</t>
-  </si>
-  <si>
-    <t>1114</t>
-  </si>
-  <si>
-    <t>地狱蛇谷</t>
-  </si>
-  <si>
-    <t>1150-5</t>
-  </si>
-  <si>
-    <t>地狱蛇胆</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210044,1009,505</t>
-  </si>
-  <si>
-    <t>10114</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>地狱狼山</t>
-  </si>
-  <si>
-    <t>1200-1</t>
-  </si>
-  <si>
-    <t>地狱狼爪</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210045,1009,505</t>
-  </si>
-  <si>
-    <t>10115</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>地狱沙洞</t>
-  </si>
-  <si>
-    <t>1200-2</t>
-  </si>
-  <si>
-    <t>地狱虫皮</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210046,1009,505</t>
-  </si>
-  <si>
-    <t>10116</t>
-  </si>
-  <si>
-    <t>1117</t>
-  </si>
-  <si>
-    <t>地狱鹰崖</t>
-  </si>
-  <si>
-    <t>1200-3</t>
-  </si>
-  <si>
-    <t>地狱鹰羽</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210047,1009,505</t>
-  </si>
-  <si>
-    <t>10117</t>
-  </si>
-  <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>地狱虫谷</t>
-  </si>
-  <si>
-    <t>1200-4</t>
-  </si>
-  <si>
-    <t>地狱虫角</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210048,1009,505</t>
-  </si>
-  <si>
-    <t>10118</t>
-  </si>
-  <si>
-    <t>1119</t>
-  </si>
-  <si>
-    <t>地狱虫洞</t>
-  </si>
-  <si>
-    <t>1200-5</t>
-  </si>
-  <si>
-    <t>地狱蜈膏</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210049,1009,505</t>
-  </si>
-  <si>
-    <t>10119</t>
-  </si>
-  <si>
-    <t>1120</t>
-  </si>
-  <si>
-    <t>地狱虫穴</t>
-  </si>
-  <si>
-    <t>1250-1</t>
-  </si>
-  <si>
-    <t>地狱虫心</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210050,1009,505</t>
-  </si>
-  <si>
-    <t>10120</t>
-  </si>
-  <si>
-    <t>1121</t>
-  </si>
-  <si>
-    <t>地狱虫巢</t>
-  </si>
-  <si>
-    <t>1250-2</t>
-  </si>
-  <si>
-    <t>地狱龙皮</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210051,1009,505</t>
-  </si>
-  <si>
-    <t>10121</t>
-  </si>
-  <si>
-    <t>1122</t>
-  </si>
-  <si>
-    <t>地狱魔猪厅</t>
-  </si>
-  <si>
-    <t>1250-3</t>
-  </si>
-  <si>
-    <t>地狱猪皮</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210052,1009,505</t>
-  </si>
-  <si>
-    <t>10122</t>
-  </si>
-  <si>
-    <t>1123</t>
-  </si>
-  <si>
-    <t>地狱魔猪殿</t>
-  </si>
-  <si>
-    <t>1250-4</t>
-  </si>
-  <si>
-    <t>地狱猪心</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210053,1009,505</t>
-  </si>
-  <si>
-    <t>10123</t>
-  </si>
-  <si>
-    <t>1124</t>
-  </si>
-  <si>
-    <t>地狱桃源</t>
-  </si>
-  <si>
-    <t>1250-5</t>
-  </si>
-  <si>
-    <t>地狱蝎皮</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210054,1009,505</t>
-  </si>
-  <si>
-    <t>10124</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>地狱魔禁地</t>
-  </si>
-  <si>
-    <t>1300-1</t>
-  </si>
-  <si>
-    <t>地狱宝甲</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210055,1009,505</t>
-  </si>
-  <si>
-    <t>10125</t>
-  </si>
-  <si>
-    <t>1126</t>
-  </si>
-  <si>
-    <t>地狱魔神殿</t>
-  </si>
-  <si>
-    <t>1300-2</t>
-  </si>
-  <si>
-    <t>地狱号角</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210056,1009,505</t>
-  </si>
-  <si>
-    <t>10126</t>
-  </si>
-  <si>
-    <t>1127</t>
-  </si>
-  <si>
-    <t>地狱邪禁地</t>
-  </si>
-  <si>
-    <t>1300-3</t>
-  </si>
-  <si>
-    <t>地狱雕像</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210057,1009,505</t>
-  </si>
-  <si>
-    <t>10127</t>
-  </si>
-  <si>
-    <t>1128</t>
-  </si>
-  <si>
-    <t>地狱邪魔殿</t>
-  </si>
-  <si>
-    <t>1300-4</t>
-  </si>
-  <si>
-    <t>地狱神像</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210058,1009,505</t>
-  </si>
-  <si>
-    <t>10128</t>
-  </si>
-  <si>
-    <t>1129</t>
-  </si>
-  <si>
-    <t>地狱封魔殿</t>
-  </si>
-  <si>
-    <t>1300-5</t>
-  </si>
-  <si>
-    <t>地狱獠牙</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210059,1009,505</t>
-  </si>
-  <si>
-    <t>10129</t>
-  </si>
-  <si>
-    <t>1130</t>
-  </si>
-  <si>
-    <t>地狱烈焰殿</t>
-  </si>
-  <si>
-    <t>1350-1</t>
-  </si>
-  <si>
-    <t>地狱树心</t>
-  </si>
-  <si>
-    <t>202001,300091,104,504,210060,1009,505</t>
   </si>
   <si>
     <t>10130</t>
@@ -8116,21 +8104,21 @@
         <v>0</v>
       </c>
       <c r="J131" s="8" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="K131" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="3:12">
       <c r="C132" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D132" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
@@ -8139,30 +8127,30 @@
         <v>4</v>
       </c>
       <c r="G132" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="H132" s="1" t="s">
         <v>749</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>750</v>
       </c>
       <c r="I132" s="1">
         <v>0</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="K132" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="3:12">
       <c r="C133" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
@@ -8171,30 +8159,30 @@
         <v>4</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="I133" s="1">
         <v>0</v>
       </c>
       <c r="J133" s="8" t="s">
-        <v>757</v>
+        <v>739</v>
       </c>
       <c r="K133" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="3:12">
       <c r="C134" s="1" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
@@ -8203,30 +8191,30 @@
         <v>4</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="I134" s="1">
         <v>0</v>
       </c>
       <c r="J134" s="8" t="s">
-        <v>763</v>
+        <v>739</v>
       </c>
       <c r="K134" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="3:12">
       <c r="C135" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
@@ -8235,30 +8223,30 @@
         <v>4</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="I135" s="1">
         <v>0</v>
       </c>
       <c r="J135" s="8" t="s">
-        <v>769</v>
+        <v>739</v>
       </c>
       <c r="K135" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="3:12">
       <c r="C136" s="1" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
@@ -8267,30 +8255,30 @@
         <v>4</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="I136" s="1">
         <v>0</v>
       </c>
       <c r="J136" s="8" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="K136" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="3:12">
       <c r="C137" s="1" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
@@ -8299,30 +8287,30 @@
         <v>4</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="I137" s="1">
         <v>0</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="K137" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
@@ -8331,30 +8319,30 @@
         <v>4</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="I138" s="1">
         <v>0</v>
       </c>
       <c r="J138" s="8" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="K138" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
@@ -8363,30 +8351,30 @@
         <v>4</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="I139" s="1">
         <v>0</v>
       </c>
       <c r="J139" s="8" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="K139" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="3:12">
       <c r="C140" s="1" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
@@ -8395,30 +8383,30 @@
         <v>4</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="I140" s="1">
         <v>0</v>
       </c>
       <c r="J140" s="8" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="K140" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C141" s="1" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
@@ -8427,30 +8415,30 @@
         <v>4</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="I141" s="1">
         <v>0</v>
       </c>
       <c r="J141" s="8" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="K141" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C142" s="1" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
@@ -8459,30 +8447,30 @@
         <v>4</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="I142" s="1">
         <v>0</v>
       </c>
       <c r="J142" s="8" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="K142" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C143" s="1" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
@@ -8491,30 +8479,30 @@
         <v>4</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="I143" s="1">
         <v>0</v>
       </c>
       <c r="J143" s="8" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="K143" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C144" s="1" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
@@ -8523,30 +8511,30 @@
         <v>4</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="I144" s="1">
         <v>0</v>
       </c>
       <c r="J144" s="8" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="K144" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C145" s="1" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
@@ -8555,30 +8543,30 @@
         <v>4</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="I145" s="1">
         <v>0</v>
       </c>
       <c r="J145" s="8" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="K145" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
     </row>
     <row r="146" s="3" customFormat="1" customHeight="1" spans="3:12">
       <c r="C146" s="3" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="E146" s="3">
         <v>5</v>
@@ -8587,30 +8575,30 @@
         <v>5</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="I146" s="3">
         <v>0</v>
       </c>
       <c r="J146" s="9" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K146" s="9" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L146" s="9" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="E147" s="1">
         <v>5</v>
@@ -8619,30 +8607,30 @@
         <v>5</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="I147" s="1">
         <v>0</v>
       </c>
       <c r="J147" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K147" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L147" s="7" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="E148" s="1">
         <v>5</v>
@@ -8651,30 +8639,30 @@
         <v>5</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="I148" s="1">
         <v>0</v>
       </c>
       <c r="J148" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K148" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L148" s="7" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="E149" s="1">
         <v>5</v>
@@ -8683,30 +8671,30 @@
         <v>5</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="I149" s="1">
         <v>0</v>
       </c>
       <c r="J149" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K149" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L149" s="7" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="3:12">
       <c r="C150" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="E150" s="1">
         <v>5</v>
@@ -8715,30 +8703,30 @@
         <v>5</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="I150" s="1">
         <v>0</v>
       </c>
       <c r="J150" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K150" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L150" s="7" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="3:12">
       <c r="C151" s="1" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
@@ -8747,30 +8735,30 @@
         <v>5</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="I151" s="1">
         <v>0</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K151" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L151" s="7" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="3:12">
       <c r="C152" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
@@ -8779,30 +8767,30 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="I152" s="1">
         <v>0</v>
       </c>
       <c r="J152" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K152" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L152" s="7" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="3:12">
       <c r="C153" s="1" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
@@ -8811,30 +8799,30 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="I153" s="1">
         <v>0</v>
       </c>
       <c r="J153" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K153" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L153" s="7" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="3:12">
       <c r="C154" s="1" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
@@ -8843,30 +8831,30 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="I154" s="1">
         <v>0</v>
       </c>
       <c r="J154" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K154" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L154" s="7" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="3:12">
       <c r="C155" s="1" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
@@ -8875,30 +8863,30 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="I155" s="1">
         <v>0</v>
       </c>
       <c r="J155" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K155" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L155" s="7" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C156" s="1" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
@@ -8907,30 +8895,30 @@
         <v>5</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="I156" s="1">
         <v>0</v>
       </c>
       <c r="J156" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K156" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L156" s="7" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C157" s="1" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
@@ -8939,30 +8927,30 @@
         <v>5</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I157" s="1">
         <v>0</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K157" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L157" s="7" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C158" s="1" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
@@ -8971,30 +8959,30 @@
         <v>5</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="I158" s="1">
         <v>0</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K158" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L158" s="7" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C159" s="1" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
@@ -9003,30 +8991,30 @@
         <v>5</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="I159" s="1">
         <v>0</v>
       </c>
       <c r="J159" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K159" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L159" s="7" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C160" s="1" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
@@ -9035,30 +9023,30 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="I160" s="1">
         <v>0</v>
       </c>
       <c r="J160" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K160" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L160" s="7" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C161" s="1" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
@@ -9067,30 +9055,30 @@
         <v>5</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K161" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L161" s="7" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C162" s="1" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
@@ -9099,30 +9087,30 @@
         <v>5</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="I162" s="1">
         <v>0</v>
       </c>
       <c r="J162" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K162" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L162" s="7" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C163" s="1" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9131,30 +9119,30 @@
         <v>5</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="I163" s="1">
         <v>0</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K163" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L163" s="7" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C164" s="1" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
@@ -9163,30 +9151,30 @@
         <v>5</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="I164" s="1">
         <v>0</v>
       </c>
       <c r="J164" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K164" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L164" s="7" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C165" s="1" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -9195,30 +9183,30 @@
         <v>5</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="I165" s="1">
         <v>0</v>
       </c>
       <c r="J165" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K165" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="166" customHeight="1" spans="3:12">
       <c r="C166" s="1" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
@@ -9227,30 +9215,30 @@
         <v>5</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
       </c>
       <c r="J166" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K166" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L166" s="7" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="3:12">
       <c r="C167" s="1" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
@@ -9259,30 +9247,30 @@
         <v>5</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
       </c>
       <c r="J167" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K167" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L167" s="7" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="168" customHeight="1" spans="3:12">
       <c r="C168" s="1" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -9291,30 +9279,30 @@
         <v>5</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K168" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L168" s="7" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
     </row>
     <row r="169" customHeight="1" spans="3:12">
       <c r="C169" s="1" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
@@ -9323,30 +9311,30 @@
         <v>5</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K169" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L169" s="7" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
     </row>
     <row r="170" customHeight="1" spans="3:12">
       <c r="C170" s="1" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -9355,30 +9343,30 @@
         <v>5</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
       </c>
       <c r="J170" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K170" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="3:12">
       <c r="C171" s="1" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -9387,30 +9375,30 @@
         <v>5</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
       </c>
       <c r="J171" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K171" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L171" s="7" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="3:12">
       <c r="C172" s="1" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
@@ -9419,30 +9407,30 @@
         <v>5</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
       </c>
       <c r="J172" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K172" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L172" s="7" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="3:12">
       <c r="C173" s="1" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
@@ -9451,30 +9439,30 @@
         <v>5</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
       </c>
       <c r="J173" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K173" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L173" s="7" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="3:12">
       <c r="C174" s="1" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -9483,30 +9471,30 @@
         <v>5</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
       </c>
       <c r="J174" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K174" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L174" s="7" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="3:12">
       <c r="C175" s="1" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
@@ -9515,30 +9503,30 @@
         <v>5</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K175" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L175" s="7" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C176" s="1" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
@@ -9547,30 +9535,30 @@
         <v>5</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="I176" s="1">
         <v>0</v>
       </c>
       <c r="J176" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K176" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L176" s="7" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C177" s="1" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
@@ -9579,30 +9567,30 @@
         <v>5</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="I177" s="1">
         <v>0</v>
       </c>
       <c r="J177" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K177" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L177" s="7" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C178" s="1" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
@@ -9611,30 +9599,30 @@
         <v>5</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
       </c>
       <c r="J178" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K178" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L178" s="7" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C179" s="1" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -9643,30 +9631,30 @@
         <v>5</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
       </c>
       <c r="J179" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K179" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L179" s="7" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C180" s="1" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
@@ -9675,22 +9663,22 @@
         <v>5</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
       </c>
       <c r="J180" s="8" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K180" s="8" t="s">
-        <v>625</v>
+        <v>771</v>
       </c>
       <c r="L180" s="7" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="1014">
   <si>
     <t>_Id</t>
   </si>
@@ -2296,6 +2296,9 @@
     <t>地狱宝甲</t>
   </si>
   <si>
+    <t>202001,300091,104,504,210055,1009</t>
+  </si>
+  <si>
     <t>10125</t>
   </si>
   <si>
@@ -2311,6 +2314,9 @@
     <t>地狱号角</t>
   </si>
   <si>
+    <t>202001,300091,104,504,210056,1009</t>
+  </si>
+  <si>
     <t>10126</t>
   </si>
   <si>
@@ -2326,6 +2332,9 @@
     <t>地狱雕像</t>
   </si>
   <si>
+    <t>202001,300091,104,504,210057,1009</t>
+  </si>
+  <si>
     <t>10127</t>
   </si>
   <si>
@@ -2341,6 +2350,9 @@
     <t>地狱神像</t>
   </si>
   <si>
+    <t>202001,300091,104,504,210058,1009</t>
+  </si>
+  <si>
     <t>10128</t>
   </si>
   <si>
@@ -2356,6 +2368,9 @@
     <t>地狱獠牙</t>
   </si>
   <si>
+    <t>202001,300091,104,504,210059,1009</t>
+  </si>
+  <si>
     <t>10129</t>
   </si>
   <si>
@@ -2632,6 +2647,9 @@
     <t>深渊冰晶</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210071,1009,505</t>
+  </si>
+  <si>
     <t>10145</t>
   </si>
   <si>
@@ -2707,6 +2725,9 @@
     <t>深渊狼爪</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210072,1009,505</t>
+  </si>
+  <si>
     <t>10150</t>
   </si>
   <si>
@@ -2782,6 +2803,9 @@
     <t>深渊虫心</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210073,1009,505</t>
+  </si>
+  <si>
     <t>10155</t>
   </si>
   <si>
@@ -2857,6 +2881,9 @@
     <t>深渊宝甲</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210074,1009,505</t>
+  </si>
+  <si>
     <t>10160</t>
   </si>
   <si>
@@ -2932,6 +2959,9 @@
     <t>深渊树心</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210075,1009,505</t>
+  </si>
+  <si>
     <t>10165</t>
   </si>
   <si>
@@ -3005,6 +3035,9 @@
   </si>
   <si>
     <t>深渊战锤</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210076,1009,505</t>
   </si>
   <si>
     <t>10170</t>
@@ -8104,21 +8137,21 @@
         <v>0</v>
       </c>
       <c r="J131" s="8" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="K131" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="3:12">
       <c r="C132" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
@@ -8127,30 +8160,30 @@
         <v>4</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="I132" s="1">
         <v>0</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="K132" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="3:12">
       <c r="C133" s="1" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
@@ -8159,30 +8192,30 @@
         <v>4</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="I133" s="1">
         <v>0</v>
       </c>
       <c r="J133" s="8" t="s">
-        <v>739</v>
+        <v>757</v>
       </c>
       <c r="K133" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="3:12">
       <c r="C134" s="1" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
@@ -8191,30 +8224,30 @@
         <v>4</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="I134" s="1">
         <v>0</v>
       </c>
       <c r="J134" s="8" t="s">
-        <v>739</v>
+        <v>763</v>
       </c>
       <c r="K134" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="3:12">
       <c r="C135" s="1" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
@@ -8223,30 +8256,30 @@
         <v>4</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="I135" s="1">
         <v>0</v>
       </c>
       <c r="J135" s="8" t="s">
-        <v>739</v>
+        <v>769</v>
       </c>
       <c r="K135" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="3:12">
       <c r="C136" s="1" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
@@ -8255,30 +8288,30 @@
         <v>4</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="I136" s="1">
         <v>0</v>
       </c>
       <c r="J136" s="8" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="K136" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="3:12">
       <c r="C137" s="1" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
@@ -8287,30 +8320,30 @@
         <v>4</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="I137" s="1">
         <v>0</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="K137" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
@@ -8319,30 +8352,30 @@
         <v>4</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="I138" s="1">
         <v>0</v>
       </c>
       <c r="J138" s="8" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="K138" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
@@ -8351,30 +8384,30 @@
         <v>4</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="I139" s="1">
         <v>0</v>
       </c>
       <c r="J139" s="8" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="K139" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="3:12">
       <c r="C140" s="1" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
@@ -8383,30 +8416,30 @@
         <v>4</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="I140" s="1">
         <v>0</v>
       </c>
       <c r="J140" s="8" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="K140" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C141" s="1" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
@@ -8415,30 +8448,30 @@
         <v>4</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="I141" s="1">
         <v>0</v>
       </c>
       <c r="J141" s="8" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="K141" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C142" s="1" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
@@ -8447,30 +8480,30 @@
         <v>4</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="I142" s="1">
         <v>0</v>
       </c>
       <c r="J142" s="8" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="K142" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C143" s="1" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
@@ -8479,30 +8512,30 @@
         <v>4</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="I143" s="1">
         <v>0</v>
       </c>
       <c r="J143" s="8" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="K143" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C144" s="1" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
@@ -8511,30 +8544,30 @@
         <v>4</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="I144" s="1">
         <v>0</v>
       </c>
       <c r="J144" s="8" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="K144" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C145" s="1" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
@@ -8543,30 +8576,30 @@
         <v>4</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="I145" s="1">
         <v>0</v>
       </c>
       <c r="J145" s="8" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="K145" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
     </row>
     <row r="146" s="3" customFormat="1" customHeight="1" spans="3:12">
       <c r="C146" s="3" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="E146" s="3">
         <v>5</v>
@@ -8575,30 +8608,30 @@
         <v>5</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="I146" s="3">
         <v>0</v>
       </c>
       <c r="J146" s="9" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="K146" s="9" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L146" s="9" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="E147" s="1">
         <v>5</v>
@@ -8607,30 +8640,30 @@
         <v>5</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="I147" s="1">
         <v>0</v>
       </c>
       <c r="J147" s="8" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="K147" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L147" s="7" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="E148" s="1">
         <v>5</v>
@@ -8639,30 +8672,30 @@
         <v>5</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="I148" s="1">
         <v>0</v>
       </c>
       <c r="J148" s="8" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="K148" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L148" s="7" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="E149" s="1">
         <v>5</v>
@@ -8671,30 +8704,30 @@
         <v>5</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="I149" s="1">
         <v>0</v>
       </c>
       <c r="J149" s="8" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="K149" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L149" s="7" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="3:12">
       <c r="C150" s="1" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="E150" s="1">
         <v>5</v>
@@ -8703,30 +8736,30 @@
         <v>5</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="I150" s="1">
         <v>0</v>
       </c>
       <c r="J150" s="8" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="K150" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L150" s="7" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="3:12">
       <c r="C151" s="1" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
@@ -8735,30 +8768,30 @@
         <v>5</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="I151" s="1">
         <v>0</v>
       </c>
       <c r="J151" s="8" t="s">
-        <v>831</v>
+        <v>862</v>
       </c>
       <c r="K151" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L151" s="7" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="3:12">
       <c r="C152" s="1" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
@@ -8767,30 +8800,30 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="I152" s="1">
         <v>0</v>
       </c>
       <c r="J152" s="8" t="s">
-        <v>831</v>
+        <v>862</v>
       </c>
       <c r="K152" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L152" s="7" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="3:12">
       <c r="C153" s="1" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
@@ -8799,30 +8832,30 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="I153" s="1">
         <v>0</v>
       </c>
       <c r="J153" s="8" t="s">
-        <v>831</v>
+        <v>862</v>
       </c>
       <c r="K153" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L153" s="7" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="3:12">
       <c r="C154" s="1" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
@@ -8831,30 +8864,30 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="I154" s="1">
         <v>0</v>
       </c>
       <c r="J154" s="8" t="s">
-        <v>831</v>
+        <v>862</v>
       </c>
       <c r="K154" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L154" s="7" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="3:12">
       <c r="C155" s="1" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
@@ -8863,30 +8896,30 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="I155" s="1">
         <v>0</v>
       </c>
       <c r="J155" s="8" t="s">
-        <v>831</v>
+        <v>862</v>
       </c>
       <c r="K155" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L155" s="7" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C156" s="1" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
@@ -8895,30 +8928,30 @@
         <v>5</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="I156" s="1">
         <v>0</v>
       </c>
       <c r="J156" s="8" t="s">
-        <v>831</v>
+        <v>888</v>
       </c>
       <c r="K156" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L156" s="7" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C157" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
@@ -8927,30 +8960,30 @@
         <v>5</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="I157" s="1">
         <v>0</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>831</v>
+        <v>888</v>
       </c>
       <c r="K157" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L157" s="7" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C158" s="1" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
@@ -8959,30 +8992,30 @@
         <v>5</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="I158" s="1">
         <v>0</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>831</v>
+        <v>888</v>
       </c>
       <c r="K158" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L158" s="7" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C159" s="1" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
@@ -8991,30 +9024,30 @@
         <v>5</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="I159" s="1">
         <v>0</v>
       </c>
       <c r="J159" s="8" t="s">
-        <v>831</v>
+        <v>888</v>
       </c>
       <c r="K159" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L159" s="7" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C160" s="1" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
@@ -9023,30 +9056,30 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="I160" s="1">
         <v>0</v>
       </c>
       <c r="J160" s="8" t="s">
-        <v>831</v>
+        <v>888</v>
       </c>
       <c r="K160" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L160" s="7" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C161" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
@@ -9055,30 +9088,30 @@
         <v>5</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
       <c r="J161" s="8" t="s">
-        <v>831</v>
+        <v>914</v>
       </c>
       <c r="K161" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L161" s="7" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C162" s="1" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
@@ -9087,30 +9120,30 @@
         <v>5</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="I162" s="1">
         <v>0</v>
       </c>
       <c r="J162" s="8" t="s">
-        <v>831</v>
+        <v>914</v>
       </c>
       <c r="K162" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L162" s="7" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C163" s="1" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9119,30 +9152,30 @@
         <v>5</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="I163" s="1">
         <v>0</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>831</v>
+        <v>914</v>
       </c>
       <c r="K163" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L163" s="7" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C164" s="1" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
@@ -9151,30 +9184,30 @@
         <v>5</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="I164" s="1">
         <v>0</v>
       </c>
       <c r="J164" s="8" t="s">
-        <v>831</v>
+        <v>914</v>
       </c>
       <c r="K164" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L164" s="7" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C165" s="1" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -9183,30 +9216,30 @@
         <v>5</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="I165" s="1">
         <v>0</v>
       </c>
       <c r="J165" s="8" t="s">
-        <v>831</v>
+        <v>914</v>
       </c>
       <c r="K165" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
     </row>
     <row r="166" customHeight="1" spans="3:12">
       <c r="C166" s="1" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
@@ -9215,30 +9248,30 @@
         <v>5</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
       </c>
       <c r="J166" s="8" t="s">
-        <v>831</v>
+        <v>940</v>
       </c>
       <c r="K166" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L166" s="7" t="s">
-        <v>932</v>
+        <v>941</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="3:12">
       <c r="C167" s="1" t="s">
-        <v>933</v>
+        <v>942</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
@@ -9247,30 +9280,30 @@
         <v>5</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>935</v>
+        <v>944</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>936</v>
+        <v>945</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
       </c>
       <c r="J167" s="8" t="s">
-        <v>831</v>
+        <v>940</v>
       </c>
       <c r="K167" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L167" s="7" t="s">
-        <v>937</v>
+        <v>946</v>
       </c>
     </row>
     <row r="168" customHeight="1" spans="3:12">
       <c r="C168" s="1" t="s">
-        <v>938</v>
+        <v>947</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -9279,30 +9312,30 @@
         <v>5</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>940</v>
+        <v>949</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>941</v>
+        <v>950</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>831</v>
+        <v>940</v>
       </c>
       <c r="K168" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L168" s="7" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
     </row>
     <row r="169" customHeight="1" spans="3:12">
       <c r="C169" s="1" t="s">
-        <v>943</v>
+        <v>952</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>944</v>
+        <v>953</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
@@ -9311,30 +9344,30 @@
         <v>5</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>831</v>
+        <v>940</v>
       </c>
       <c r="K169" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L169" s="7" t="s">
-        <v>947</v>
+        <v>956</v>
       </c>
     </row>
     <row r="170" customHeight="1" spans="3:12">
       <c r="C170" s="1" t="s">
-        <v>948</v>
+        <v>957</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>949</v>
+        <v>958</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -9343,30 +9376,30 @@
         <v>5</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>950</v>
+        <v>959</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>951</v>
+        <v>960</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
       </c>
       <c r="J170" s="8" t="s">
-        <v>831</v>
+        <v>940</v>
       </c>
       <c r="K170" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>952</v>
+        <v>961</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="3:12">
       <c r="C171" s="1" t="s">
-        <v>953</v>
+        <v>962</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>954</v>
+        <v>963</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -9375,30 +9408,30 @@
         <v>5</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>955</v>
+        <v>964</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
       </c>
       <c r="J171" s="8" t="s">
-        <v>831</v>
+        <v>966</v>
       </c>
       <c r="K171" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L171" s="7" t="s">
-        <v>957</v>
+        <v>967</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="3:12">
       <c r="C172" s="1" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
@@ -9407,30 +9440,30 @@
         <v>5</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
       </c>
       <c r="J172" s="8" t="s">
-        <v>831</v>
+        <v>966</v>
       </c>
       <c r="K172" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L172" s="7" t="s">
-        <v>962</v>
+        <v>972</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="3:12">
       <c r="C173" s="1" t="s">
-        <v>963</v>
+        <v>973</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
@@ -9439,30 +9472,30 @@
         <v>5</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
       </c>
       <c r="J173" s="8" t="s">
-        <v>831</v>
+        <v>966</v>
       </c>
       <c r="K173" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L173" s="7" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="3:12">
       <c r="C174" s="1" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -9471,30 +9504,30 @@
         <v>5</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
       </c>
       <c r="J174" s="8" t="s">
-        <v>831</v>
+        <v>966</v>
       </c>
       <c r="K174" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L174" s="7" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="3:12">
       <c r="C175" s="1" t="s">
-        <v>973</v>
+        <v>983</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>974</v>
+        <v>984</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
@@ -9503,30 +9536,30 @@
         <v>5</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>831</v>
+        <v>966</v>
       </c>
       <c r="K175" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L175" s="7" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C176" s="1" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
@@ -9535,30 +9568,30 @@
         <v>5</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>981</v>
+        <v>991</v>
       </c>
       <c r="I176" s="1">
         <v>0</v>
       </c>
       <c r="J176" s="8" t="s">
-        <v>831</v>
+        <v>992</v>
       </c>
       <c r="K176" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L176" s="7" t="s">
-        <v>982</v>
+        <v>993</v>
       </c>
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C177" s="1" t="s">
-        <v>983</v>
+        <v>994</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>984</v>
+        <v>995</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
@@ -9567,30 +9600,30 @@
         <v>5</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>985</v>
+        <v>996</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>986</v>
+        <v>997</v>
       </c>
       <c r="I177" s="1">
         <v>0</v>
       </c>
       <c r="J177" s="8" t="s">
-        <v>831</v>
+        <v>992</v>
       </c>
       <c r="K177" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L177" s="7" t="s">
-        <v>987</v>
+        <v>998</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C178" s="1" t="s">
-        <v>988</v>
+        <v>999</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>989</v>
+        <v>1000</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
@@ -9599,30 +9632,30 @@
         <v>5</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>990</v>
+        <v>1001</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>991</v>
+        <v>1002</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
       </c>
       <c r="J178" s="8" t="s">
-        <v>831</v>
+        <v>992</v>
       </c>
       <c r="K178" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L178" s="7" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C179" s="1" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -9631,30 +9664,30 @@
         <v>5</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>995</v>
+        <v>1006</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>996</v>
+        <v>1007</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
       </c>
       <c r="J179" s="8" t="s">
-        <v>831</v>
+        <v>992</v>
       </c>
       <c r="K179" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L179" s="7" t="s">
-        <v>997</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C180" s="1" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
@@ -9663,22 +9696,22 @@
         <v>5</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
       </c>
       <c r="J180" s="8" t="s">
-        <v>831</v>
+        <v>992</v>
       </c>
       <c r="K180" s="8" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L180" s="7" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1197">
   <si>
     <t>_Id</t>
   </si>
@@ -3101,6 +3101,555 @@
   </si>
   <si>
     <t>10174</t>
+  </si>
+  <si>
+    <t>1175</t>
+  </si>
+  <si>
+    <t>混沌小村</t>
+  </si>
+  <si>
+    <t>1800-1</t>
+  </si>
+  <si>
+    <t>混沌装备</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,202003</t>
+  </si>
+  <si>
+    <t>100,25000,10000,180000,1000000,140000,600000,20000</t>
+  </si>
+  <si>
+    <t>10175</t>
+  </si>
+  <si>
+    <t>1176</t>
+  </si>
+  <si>
+    <t>混沌村外</t>
+  </si>
+  <si>
+    <t>1800-2</t>
+  </si>
+  <si>
+    <t>混沌鹿茸</t>
+  </si>
+  <si>
+    <t>10176</t>
+  </si>
+  <si>
+    <t>1177</t>
+  </si>
+  <si>
+    <t>混沌农场</t>
+  </si>
+  <si>
+    <t>1800-3</t>
+  </si>
+  <si>
+    <t>混沌草帽</t>
+  </si>
+  <si>
+    <t>10177</t>
+  </si>
+  <si>
+    <t>1178</t>
+  </si>
+  <si>
+    <t>混沌老城</t>
+  </si>
+  <si>
+    <t>1800-4</t>
+  </si>
+  <si>
+    <t>混沌猫爪</t>
+  </si>
+  <si>
+    <t>10178</t>
+  </si>
+  <si>
+    <t>1179</t>
+  </si>
+  <si>
+    <t>混沌森林</t>
+  </si>
+  <si>
+    <t>1800-5</t>
+  </si>
+  <si>
+    <t>混沌花朵</t>
+  </si>
+  <si>
+    <t>10179</t>
+  </si>
+  <si>
+    <t>1180</t>
+  </si>
+  <si>
+    <t>混沌蝠洞</t>
+  </si>
+  <si>
+    <t>1850-1</t>
+  </si>
+  <si>
+    <t>混沌冰晶</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210078,1009,505,202003</t>
+  </si>
+  <si>
+    <t>10180</t>
+  </si>
+  <si>
+    <t>1181</t>
+  </si>
+  <si>
+    <t>混沌骷髅洞</t>
+  </si>
+  <si>
+    <t>1850-2</t>
+  </si>
+  <si>
+    <t>混沌蝠翼</t>
+  </si>
+  <si>
+    <t>10181</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>混沌通道</t>
+  </si>
+  <si>
+    <t>1850-3</t>
+  </si>
+  <si>
+    <t>混沌魂火</t>
+  </si>
+  <si>
+    <t>10182</t>
+  </si>
+  <si>
+    <t>1183</t>
+  </si>
+  <si>
+    <t>混沌尸洞</t>
+  </si>
+  <si>
+    <t>1850-4</t>
+  </si>
+  <si>
+    <t>混沌腐肉</t>
+  </si>
+  <si>
+    <t>10183</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>混沌蛇谷</t>
+  </si>
+  <si>
+    <t>1850-5</t>
+  </si>
+  <si>
+    <t>混沌蛇胆</t>
+  </si>
+  <si>
+    <t>10184</t>
+  </si>
+  <si>
+    <t>1185</t>
+  </si>
+  <si>
+    <t>混沌狼山</t>
+  </si>
+  <si>
+    <t>1900-1</t>
+  </si>
+  <si>
+    <t>混沌狼爪</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210079,1009,505,202003</t>
+  </si>
+  <si>
+    <t>10185</t>
+  </si>
+  <si>
+    <t>1186</t>
+  </si>
+  <si>
+    <t>混沌沙洞</t>
+  </si>
+  <si>
+    <t>1900-2</t>
+  </si>
+  <si>
+    <t>混沌虫皮</t>
+  </si>
+  <si>
+    <t>10186</t>
+  </si>
+  <si>
+    <t>1187</t>
+  </si>
+  <si>
+    <t>混沌鹰崖</t>
+  </si>
+  <si>
+    <t>1900-3</t>
+  </si>
+  <si>
+    <t>混沌鹰羽</t>
+  </si>
+  <si>
+    <t>10187</t>
+  </si>
+  <si>
+    <t>1188</t>
+  </si>
+  <si>
+    <t>混沌虫谷</t>
+  </si>
+  <si>
+    <t>1900-4</t>
+  </si>
+  <si>
+    <t>混沌虫角</t>
+  </si>
+  <si>
+    <t>10188</t>
+  </si>
+  <si>
+    <t>1189</t>
+  </si>
+  <si>
+    <t>混沌虫洞</t>
+  </si>
+  <si>
+    <t>1900-5</t>
+  </si>
+  <si>
+    <t>混沌蜈膏</t>
+  </si>
+  <si>
+    <t>10189</t>
+  </si>
+  <si>
+    <t>1190</t>
+  </si>
+  <si>
+    <t>混沌虫穴</t>
+  </si>
+  <si>
+    <t>1950-1</t>
+  </si>
+  <si>
+    <t>混沌虫心</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210080,1009,505,202003</t>
+  </si>
+  <si>
+    <t>10190</t>
+  </si>
+  <si>
+    <t>1191</t>
+  </si>
+  <si>
+    <t>混沌虫巢</t>
+  </si>
+  <si>
+    <t>1950-2</t>
+  </si>
+  <si>
+    <t>混沌龙皮</t>
+  </si>
+  <si>
+    <t>10191</t>
+  </si>
+  <si>
+    <t>1192</t>
+  </si>
+  <si>
+    <t>混沌魔猪厅</t>
+  </si>
+  <si>
+    <t>1950-3</t>
+  </si>
+  <si>
+    <t>混沌猪皮</t>
+  </si>
+  <si>
+    <t>10192</t>
+  </si>
+  <si>
+    <t>1193</t>
+  </si>
+  <si>
+    <t>混沌魔猪殿</t>
+  </si>
+  <si>
+    <t>1950-4</t>
+  </si>
+  <si>
+    <t>混沌猪心</t>
+  </si>
+  <si>
+    <t>10193</t>
+  </si>
+  <si>
+    <t>1194</t>
+  </si>
+  <si>
+    <t>混沌桃源</t>
+  </si>
+  <si>
+    <t>1950-5</t>
+  </si>
+  <si>
+    <t>混沌蝎皮</t>
+  </si>
+  <si>
+    <t>10194</t>
+  </si>
+  <si>
+    <t>1195</t>
+  </si>
+  <si>
+    <t>混沌魔禁地</t>
+  </si>
+  <si>
+    <t>2000-1</t>
+  </si>
+  <si>
+    <t>混沌宝甲</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210081,1009,505,202003</t>
+  </si>
+  <si>
+    <t>10195</t>
+  </si>
+  <si>
+    <t>1196</t>
+  </si>
+  <si>
+    <t>混沌魔神殿</t>
+  </si>
+  <si>
+    <t>2000-2</t>
+  </si>
+  <si>
+    <t>混沌号角</t>
+  </si>
+  <si>
+    <t>10196</t>
+  </si>
+  <si>
+    <t>1197</t>
+  </si>
+  <si>
+    <t>混沌邪禁地</t>
+  </si>
+  <si>
+    <t>2000-3</t>
+  </si>
+  <si>
+    <t>混沌雕像</t>
+  </si>
+  <si>
+    <t>10197</t>
+  </si>
+  <si>
+    <t>1198</t>
+  </si>
+  <si>
+    <t>混沌邪魔殿</t>
+  </si>
+  <si>
+    <t>2000-4</t>
+  </si>
+  <si>
+    <t>混沌神像</t>
+  </si>
+  <si>
+    <t>10198</t>
+  </si>
+  <si>
+    <t>1199</t>
+  </si>
+  <si>
+    <t>混沌封魔殿</t>
+  </si>
+  <si>
+    <t>2000-5</t>
+  </si>
+  <si>
+    <t>混沌獠牙</t>
+  </si>
+  <si>
+    <t>10199</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>混沌烈焰殿</t>
+  </si>
+  <si>
+    <t>2050-1</t>
+  </si>
+  <si>
+    <t>混沌树心</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210082,1009,505,202003</t>
+  </si>
+  <si>
+    <t>10200</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>混沌封邪殿</t>
+  </si>
+  <si>
+    <t>2050-2</t>
+  </si>
+  <si>
+    <t>混沌魔心</t>
+  </si>
+  <si>
+    <t>10201</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>混沌尸魔殿</t>
+  </si>
+  <si>
+    <t>2050-3</t>
+  </si>
+  <si>
+    <t>混沌尸心</t>
+  </si>
+  <si>
+    <t>10202</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>混沌骨魔殿</t>
+  </si>
+  <si>
+    <t>2050-4</t>
+  </si>
+  <si>
+    <t>混沌法杖</t>
+  </si>
+  <si>
+    <t>10203</t>
+  </si>
+  <si>
+    <t>1204</t>
+  </si>
+  <si>
+    <t>混沌魔牛殿</t>
+  </si>
+  <si>
+    <t>2050-5</t>
+  </si>
+  <si>
+    <t>混沌权杖</t>
+  </si>
+  <si>
+    <t>10204</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>混沌水龙谷</t>
+  </si>
+  <si>
+    <t>2100-1</t>
+  </si>
+  <si>
+    <t>混沌战锤</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210083,1009,505,202003</t>
+  </si>
+  <si>
+    <t>10205</t>
+  </si>
+  <si>
+    <t>1206</t>
+  </si>
+  <si>
+    <t>混沌土龙谷</t>
+  </si>
+  <si>
+    <t>2100-2</t>
+  </si>
+  <si>
+    <t>混沌血核</t>
+  </si>
+  <si>
+    <t>10206</t>
+  </si>
+  <si>
+    <t>1207</t>
+  </si>
+  <si>
+    <t>混沌毒龙谷</t>
+  </si>
+  <si>
+    <t>2100-3</t>
+  </si>
+  <si>
+    <t>混沌魔核</t>
+  </si>
+  <si>
+    <t>10207</t>
+  </si>
+  <si>
+    <t>1208</t>
+  </si>
+  <si>
+    <t>混沌火龙谷</t>
+  </si>
+  <si>
+    <t>2100-4</t>
+  </si>
+  <si>
+    <t>混沌龙甲</t>
+  </si>
+  <si>
+    <t>10208</t>
+  </si>
+  <si>
+    <t>1209</t>
+  </si>
+  <si>
+    <t>混沌冰龙谷</t>
+  </si>
+  <si>
+    <t>2100-5</t>
+  </si>
+  <si>
+    <t>混沌龙爪</t>
+  </si>
+  <si>
+    <t>10209</t>
   </si>
 </sst>
 </file>
@@ -3750,7 +4299,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3762,6 +4311,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -4122,7 +4672,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:M180"/>
+  <dimension ref="B3:M215"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
@@ -5435,10 +5985,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="7" t="s">
+      <c r="J46" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="7" t="s">
+      <c r="K46" s="8" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -5464,10 +6014,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="7" t="s">
+      <c r="J47" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="7" t="s">
+      <c r="K47" s="8" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -5493,10 +6043,10 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="7" t="s">
+      <c r="J48" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="7" t="s">
+      <c r="K48" s="8" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
@@ -5522,10 +6072,10 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="7" t="s">
+      <c r="J49" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="7" t="s">
+      <c r="K49" s="8" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
@@ -5551,10 +6101,10 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="7" t="s">
+      <c r="J50" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="7" t="s">
+      <c r="K50" s="8" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
@@ -5583,10 +6133,10 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="7" t="s">
+      <c r="J51" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="7" t="s">
+      <c r="K51" s="8" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
@@ -5612,10 +6162,10 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="7" t="s">
+      <c r="J52" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="7" t="s">
+      <c r="K52" s="8" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -5641,10 +6191,10 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="7" t="s">
+      <c r="J53" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="7" t="s">
+      <c r="K53" s="8" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
@@ -5670,10 +6220,10 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="7" t="s">
+      <c r="J54" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="7" t="s">
+      <c r="K54" s="8" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
@@ -5699,10 +6249,10 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="7" t="s">
+      <c r="J55" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="7" t="s">
+      <c r="K55" s="8" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -5731,10 +6281,10 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="7" t="s">
+      <c r="J56" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="7" t="s">
+      <c r="K56" s="8" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
@@ -5763,10 +6313,10 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="7" t="s">
+      <c r="J57" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="7" t="s">
+      <c r="K57" s="8" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
@@ -5795,10 +6345,10 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="7" t="s">
+      <c r="J58" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="7" t="s">
+      <c r="K58" s="8" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -5827,10 +6377,10 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="7" t="s">
+      <c r="J59" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="7" t="s">
+      <c r="K59" s="8" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
@@ -5859,10 +6409,10 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="7" t="s">
+      <c r="J60" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="7" t="s">
+      <c r="K60" s="8" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -5892,10 +6442,10 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="8" t="s">
+      <c r="J61" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="8" t="s">
+      <c r="K61" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -5925,10 +6475,10 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="8" t="s">
+      <c r="J62" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="8" t="s">
+      <c r="K62" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -5958,10 +6508,10 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="8" t="s">
+      <c r="J63" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="8" t="s">
+      <c r="K63" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
@@ -5991,10 +6541,10 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="8" t="s">
+      <c r="J64" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="8" t="s">
+      <c r="K64" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
@@ -6024,10 +6574,10 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="8" t="s">
+      <c r="J65" s="9" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="8" t="s">
+      <c r="K65" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
@@ -6056,10 +6606,10 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="8" t="s">
+      <c r="J66" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="8" t="s">
+      <c r="K66" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
@@ -6088,10 +6638,10 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="8" t="s">
+      <c r="J67" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="8" t="s">
+      <c r="K67" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
@@ -6120,10 +6670,10 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="8" t="s">
+      <c r="J68" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="8" t="s">
+      <c r="K68" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -6152,10 +6702,10 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="8" t="s">
+      <c r="J69" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="8" t="s">
+      <c r="K69" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
@@ -6184,10 +6734,10 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="8" t="s">
+      <c r="J70" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="8" t="s">
+      <c r="K70" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
@@ -6216,10 +6766,10 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="8" t="s">
+      <c r="J71" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="8" t="s">
+      <c r="K71" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -6248,10 +6798,10 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="8" t="s">
+      <c r="J72" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="8" t="s">
+      <c r="K72" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -6280,10 +6830,10 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="8" t="s">
+      <c r="J73" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="8" t="s">
+      <c r="K73" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -6312,10 +6862,10 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="8" t="s">
+      <c r="J74" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="8" t="s">
+      <c r="K74" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
@@ -6344,10 +6894,10 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="8" t="s">
+      <c r="J75" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="8" t="s">
+      <c r="K75" s="9" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
@@ -6376,10 +6926,10 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="8" t="s">
+      <c r="J76" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="8" t="s">
+      <c r="K76" s="9" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
@@ -6408,10 +6958,10 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="8" t="s">
+      <c r="J77" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="8" t="s">
+      <c r="K77" s="9" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
@@ -6440,10 +6990,10 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="8" t="s">
+      <c r="J78" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="8" t="s">
+      <c r="K78" s="9" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
@@ -6472,10 +7022,10 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="8" t="s">
+      <c r="J79" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="8" t="s">
+      <c r="K79" s="9" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
@@ -6504,10 +7054,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="8" t="s">
+      <c r="J80" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="8" t="s">
+      <c r="K80" s="9" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -6536,10 +7086,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="8" t="s">
+      <c r="J81" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="8" t="s">
+      <c r="K81" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -6568,10 +7118,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="8" t="s">
+      <c r="J82" s="9" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="8" t="s">
+      <c r="K82" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -6600,10 +7150,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="8" t="s">
+      <c r="J83" s="9" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="8" t="s">
+      <c r="K83" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -6632,10 +7182,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="8" t="s">
+      <c r="J84" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="8" t="s">
+      <c r="K84" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -6664,10 +7214,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="8" t="s">
+      <c r="J85" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="8" t="s">
+      <c r="K85" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -6696,10 +7246,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="8" t="s">
+      <c r="J86" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="8" t="s">
+      <c r="K86" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -6728,10 +7278,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="8" t="s">
+      <c r="J87" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="8" t="s">
+      <c r="K87" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -6760,10 +7310,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="8" t="s">
+      <c r="J88" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="8" t="s">
+      <c r="K88" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -6792,10 +7342,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="8" t="s">
+      <c r="J89" s="9" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="8" t="s">
+      <c r="K89" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -6824,10 +7374,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="8" t="s">
+      <c r="J90" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="8" t="s">
+      <c r="K90" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -6856,10 +7406,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="8" t="s">
+      <c r="J91" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="8" t="s">
+      <c r="K91" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -6888,10 +7438,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="8" t="s">
+      <c r="J92" s="9" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="8" t="s">
+      <c r="K92" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -6920,10 +7470,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="8" t="s">
+      <c r="J93" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="8" t="s">
+      <c r="K93" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -6952,10 +7502,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="8" t="s">
+      <c r="J94" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="8" t="s">
+      <c r="K94" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -6984,10 +7534,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="8" t="s">
+      <c r="J95" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="8" t="s">
+      <c r="K95" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -7016,10 +7566,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="8" t="s">
+      <c r="J96" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="8" t="s">
+      <c r="K96" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -7048,10 +7598,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="8" t="s">
+      <c r="J97" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="8" t="s">
+      <c r="K97" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -7080,10 +7630,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="8" t="s">
+      <c r="J98" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="8" t="s">
+      <c r="K98" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -7112,10 +7662,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="8" t="s">
+      <c r="J99" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="8" t="s">
+      <c r="K99" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -7144,10 +7694,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="8" t="s">
+      <c r="J100" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="8" t="s">
+      <c r="K100" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -7176,10 +7726,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="8" t="s">
+      <c r="J101" s="9" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="8" t="s">
+      <c r="K101" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -7208,10 +7758,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="8" t="s">
+      <c r="J102" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="8" t="s">
+      <c r="K102" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -7240,10 +7790,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="8" t="s">
+      <c r="J103" s="9" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="8" t="s">
+      <c r="K103" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -7272,10 +7822,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="8" t="s">
+      <c r="J104" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="8" t="s">
+      <c r="K104" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -7304,10 +7854,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="8" t="s">
+      <c r="J105" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="8" t="s">
+      <c r="K105" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -7336,10 +7886,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="8" t="s">
+      <c r="J106" s="9" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="8" t="s">
+      <c r="K106" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -7368,10 +7918,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="8" t="s">
+      <c r="J107" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="8" t="s">
+      <c r="K107" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -7400,10 +7950,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="8" t="s">
+      <c r="J108" s="9" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="8" t="s">
+      <c r="K108" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -7432,10 +7982,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="8" t="s">
+      <c r="J109" s="9" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="8" t="s">
+      <c r="K109" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -7464,10 +8014,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="8" t="s">
+      <c r="J110" s="9" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="8" t="s">
+      <c r="K110" s="9" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -7496,10 +8046,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="8" t="s">
+      <c r="J111" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="8" t="s">
+      <c r="K111" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -7528,10 +8078,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="8" t="s">
+      <c r="J112" s="9" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="8" t="s">
+      <c r="K112" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -7560,10 +8110,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="8" t="s">
+      <c r="J113" s="9" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="8" t="s">
+      <c r="K113" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -7592,10 +8142,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="8" t="s">
+      <c r="J114" s="9" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="8" t="s">
+      <c r="K114" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -7624,10 +8174,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="8" t="s">
+      <c r="J115" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="8" t="s">
+      <c r="K115" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -7656,10 +8206,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="8" t="s">
+      <c r="J116" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="8" t="s">
+      <c r="K116" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -7688,10 +8238,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="8" t="s">
+      <c r="J117" s="9" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="8" t="s">
+      <c r="K117" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -7720,10 +8270,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="8" t="s">
+      <c r="J118" s="9" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="8" t="s">
+      <c r="K118" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -7752,10 +8302,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="8" t="s">
+      <c r="J119" s="9" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="8" t="s">
+      <c r="K119" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -7784,10 +8334,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="8" t="s">
+      <c r="J120" s="9" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="8" t="s">
+      <c r="K120" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -7816,10 +8366,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="8" t="s">
+      <c r="J121" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="8" t="s">
+      <c r="K121" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -7848,10 +8398,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="8" t="s">
+      <c r="J122" s="9" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="8" t="s">
+      <c r="K122" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -7880,10 +8430,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="8" t="s">
+      <c r="J123" s="9" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="8" t="s">
+      <c r="K123" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -7912,10 +8462,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="8" t="s">
+      <c r="J124" s="9" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="8" t="s">
+      <c r="K124" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -7944,10 +8494,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="8" t="s">
+      <c r="J125" s="9" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="8" t="s">
+      <c r="K125" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -7976,10 +8526,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="8" t="s">
+      <c r="J126" s="9" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="8" t="s">
+      <c r="K126" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -8008,10 +8558,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="8" t="s">
+      <c r="J127" s="9" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="8" t="s">
+      <c r="K127" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -8040,10 +8590,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="8" t="s">
+      <c r="J128" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="8" t="s">
+      <c r="K128" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -8072,10 +8622,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="8" t="s">
+      <c r="J129" s="9" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="8" t="s">
+      <c r="K129" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -8104,10 +8654,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="8" t="s">
+      <c r="J130" s="9" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="8" t="s">
+      <c r="K130" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -8136,10 +8686,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="8" t="s">
+      <c r="J131" s="9" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="8" t="s">
+      <c r="K131" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -8168,10 +8718,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="8" t="s">
+      <c r="J132" s="9" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="8" t="s">
+      <c r="K132" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -8200,10 +8750,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="8" t="s">
+      <c r="J133" s="9" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="8" t="s">
+      <c r="K133" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -8232,10 +8782,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="8" t="s">
+      <c r="J134" s="9" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="8" t="s">
+      <c r="K134" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -8264,10 +8814,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="8" t="s">
+      <c r="J135" s="9" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="8" t="s">
+      <c r="K135" s="9" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -8296,10 +8846,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="8" t="s">
+      <c r="J136" s="9" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="8" t="s">
+      <c r="K136" s="9" t="s">
         <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -8328,10 +8878,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="8" t="s">
+      <c r="J137" s="9" t="s">
         <v>782</v>
       </c>
-      <c r="K137" s="8" t="s">
+      <c r="K137" s="9" t="s">
         <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -8360,10 +8910,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="8" t="s">
+      <c r="J138" s="9" t="s">
         <v>788</v>
       </c>
-      <c r="K138" s="8" t="s">
+      <c r="K138" s="9" t="s">
         <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -8392,10 +8942,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="8" t="s">
+      <c r="J139" s="9" t="s">
         <v>794</v>
       </c>
-      <c r="K139" s="8" t="s">
+      <c r="K139" s="9" t="s">
         <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -8424,10 +8974,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="8" t="s">
+      <c r="J140" s="9" t="s">
         <v>800</v>
       </c>
-      <c r="K140" s="8" t="s">
+      <c r="K140" s="9" t="s">
         <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -8456,10 +9006,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="8" t="s">
+      <c r="J141" s="9" t="s">
         <v>806</v>
       </c>
-      <c r="K141" s="8" t="s">
+      <c r="K141" s="9" t="s">
         <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -8488,10 +9038,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="8" t="s">
+      <c r="J142" s="9" t="s">
         <v>812</v>
       </c>
-      <c r="K142" s="8" t="s">
+      <c r="K142" s="9" t="s">
         <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -8520,10 +9070,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="8" t="s">
+      <c r="J143" s="9" t="s">
         <v>818</v>
       </c>
-      <c r="K143" s="8" t="s">
+      <c r="K143" s="9" t="s">
         <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -8552,10 +9102,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="8" t="s">
+      <c r="J144" s="9" t="s">
         <v>824</v>
       </c>
-      <c r="K144" s="8" t="s">
+      <c r="K144" s="9" t="s">
         <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -8584,10 +9134,10 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="8" t="s">
+      <c r="J145" s="9" t="s">
         <v>830</v>
       </c>
-      <c r="K145" s="8" t="s">
+      <c r="K145" s="9" t="s">
         <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
@@ -8616,13 +9166,13 @@
       <c r="I146" s="3">
         <v>0</v>
       </c>
-      <c r="J146" s="9" t="s">
+      <c r="J146" s="10" t="s">
         <v>836</v>
       </c>
-      <c r="K146" s="9" t="s">
+      <c r="K146" s="10" t="s">
         <v>776</v>
       </c>
-      <c r="L146" s="9" t="s">
+      <c r="L146" s="10" t="s">
         <v>837</v>
       </c>
     </row>
@@ -8648,13 +9198,13 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="8" t="s">
+      <c r="J147" s="9" t="s">
         <v>836</v>
       </c>
-      <c r="K147" s="8" t="s">
+      <c r="K147" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L147" s="7" t="s">
+      <c r="L147" s="8" t="s">
         <v>842</v>
       </c>
     </row>
@@ -8680,13 +9230,13 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="8" t="s">
+      <c r="J148" s="9" t="s">
         <v>836</v>
       </c>
-      <c r="K148" s="8" t="s">
+      <c r="K148" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L148" s="7" t="s">
+      <c r="L148" s="8" t="s">
         <v>847</v>
       </c>
     </row>
@@ -8712,13 +9262,13 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="8" t="s">
+      <c r="J149" s="9" t="s">
         <v>836</v>
       </c>
-      <c r="K149" s="8" t="s">
+      <c r="K149" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L149" s="7" t="s">
+      <c r="L149" s="8" t="s">
         <v>852</v>
       </c>
     </row>
@@ -8744,13 +9294,13 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="8" t="s">
+      <c r="J150" s="9" t="s">
         <v>836</v>
       </c>
-      <c r="K150" s="8" t="s">
+      <c r="K150" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L150" s="7" t="s">
+      <c r="L150" s="8" t="s">
         <v>857</v>
       </c>
     </row>
@@ -8776,13 +9326,13 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="8" t="s">
+      <c r="J151" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="K151" s="8" t="s">
+      <c r="K151" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L151" s="7" t="s">
+      <c r="L151" s="8" t="s">
         <v>863</v>
       </c>
     </row>
@@ -8808,13 +9358,13 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="8" t="s">
+      <c r="J152" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="K152" s="8" t="s">
+      <c r="K152" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L152" s="7" t="s">
+      <c r="L152" s="8" t="s">
         <v>868</v>
       </c>
     </row>
@@ -8840,13 +9390,13 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="8" t="s">
+      <c r="J153" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="K153" s="8" t="s">
+      <c r="K153" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L153" s="7" t="s">
+      <c r="L153" s="8" t="s">
         <v>873</v>
       </c>
     </row>
@@ -8872,13 +9422,13 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="8" t="s">
+      <c r="J154" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="K154" s="8" t="s">
+      <c r="K154" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L154" s="7" t="s">
+      <c r="L154" s="8" t="s">
         <v>878</v>
       </c>
     </row>
@@ -8904,13 +9454,13 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="8" t="s">
+      <c r="J155" s="9" t="s">
         <v>862</v>
       </c>
-      <c r="K155" s="8" t="s">
+      <c r="K155" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L155" s="7" t="s">
+      <c r="L155" s="8" t="s">
         <v>883</v>
       </c>
     </row>
@@ -8936,13 +9486,13 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="8" t="s">
+      <c r="J156" s="9" t="s">
         <v>888</v>
       </c>
-      <c r="K156" s="8" t="s">
+      <c r="K156" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L156" s="7" t="s">
+      <c r="L156" s="8" t="s">
         <v>889</v>
       </c>
     </row>
@@ -8968,13 +9518,13 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="8" t="s">
+      <c r="J157" s="9" t="s">
         <v>888</v>
       </c>
-      <c r="K157" s="8" t="s">
+      <c r="K157" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L157" s="7" t="s">
+      <c r="L157" s="8" t="s">
         <v>894</v>
       </c>
     </row>
@@ -9000,13 +9550,13 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="8" t="s">
+      <c r="J158" s="9" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="8" t="s">
+      <c r="K158" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L158" s="7" t="s">
+      <c r="L158" s="8" t="s">
         <v>899</v>
       </c>
     </row>
@@ -9032,13 +9582,13 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="8" t="s">
+      <c r="J159" s="9" t="s">
         <v>888</v>
       </c>
-      <c r="K159" s="8" t="s">
+      <c r="K159" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L159" s="7" t="s">
+      <c r="L159" s="8" t="s">
         <v>904</v>
       </c>
     </row>
@@ -9064,13 +9614,13 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="8" t="s">
+      <c r="J160" s="9" t="s">
         <v>888</v>
       </c>
-      <c r="K160" s="8" t="s">
+      <c r="K160" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L160" s="7" t="s">
+      <c r="L160" s="8" t="s">
         <v>909</v>
       </c>
     </row>
@@ -9096,13 +9646,13 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="8" t="s">
+      <c r="J161" s="9" t="s">
         <v>914</v>
       </c>
-      <c r="K161" s="8" t="s">
+      <c r="K161" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L161" s="7" t="s">
+      <c r="L161" s="8" t="s">
         <v>915</v>
       </c>
     </row>
@@ -9128,13 +9678,13 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="8" t="s">
+      <c r="J162" s="9" t="s">
         <v>914</v>
       </c>
-      <c r="K162" s="8" t="s">
+      <c r="K162" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L162" s="7" t="s">
+      <c r="L162" s="8" t="s">
         <v>920</v>
       </c>
     </row>
@@ -9160,13 +9710,13 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="8" t="s">
+      <c r="J163" s="9" t="s">
         <v>914</v>
       </c>
-      <c r="K163" s="8" t="s">
+      <c r="K163" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L163" s="7" t="s">
+      <c r="L163" s="8" t="s">
         <v>925</v>
       </c>
     </row>
@@ -9192,13 +9742,13 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="8" t="s">
+      <c r="J164" s="9" t="s">
         <v>914</v>
       </c>
-      <c r="K164" s="8" t="s">
+      <c r="K164" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L164" s="7" t="s">
+      <c r="L164" s="8" t="s">
         <v>930</v>
       </c>
     </row>
@@ -9224,13 +9774,13 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="8" t="s">
+      <c r="J165" s="9" t="s">
         <v>914</v>
       </c>
-      <c r="K165" s="8" t="s">
+      <c r="K165" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L165" s="7" t="s">
+      <c r="L165" s="8" t="s">
         <v>935</v>
       </c>
     </row>
@@ -9256,13 +9806,13 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="8" t="s">
+      <c r="J166" s="9" t="s">
         <v>940</v>
       </c>
-      <c r="K166" s="8" t="s">
+      <c r="K166" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L166" s="7" t="s">
+      <c r="L166" s="8" t="s">
         <v>941</v>
       </c>
     </row>
@@ -9288,13 +9838,13 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="8" t="s">
+      <c r="J167" s="9" t="s">
         <v>940</v>
       </c>
-      <c r="K167" s="8" t="s">
+      <c r="K167" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L167" s="7" t="s">
+      <c r="L167" s="8" t="s">
         <v>946</v>
       </c>
     </row>
@@ -9320,13 +9870,13 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="8" t="s">
+      <c r="J168" s="9" t="s">
         <v>940</v>
       </c>
-      <c r="K168" s="8" t="s">
+      <c r="K168" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L168" s="7" t="s">
+      <c r="L168" s="8" t="s">
         <v>951</v>
       </c>
     </row>
@@ -9352,13 +9902,13 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="8" t="s">
+      <c r="J169" s="9" t="s">
         <v>940</v>
       </c>
-      <c r="K169" s="8" t="s">
+      <c r="K169" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L169" s="7" t="s">
+      <c r="L169" s="8" t="s">
         <v>956</v>
       </c>
     </row>
@@ -9384,13 +9934,13 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="8" t="s">
+      <c r="J170" s="9" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="8" t="s">
+      <c r="K170" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L170" s="7" t="s">
+      <c r="L170" s="8" t="s">
         <v>961</v>
       </c>
     </row>
@@ -9416,13 +9966,13 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="8" t="s">
+      <c r="J171" s="9" t="s">
         <v>966</v>
       </c>
-      <c r="K171" s="8" t="s">
+      <c r="K171" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L171" s="7" t="s">
+      <c r="L171" s="8" t="s">
         <v>967</v>
       </c>
     </row>
@@ -9448,13 +9998,13 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="8" t="s">
+      <c r="J172" s="9" t="s">
         <v>966</v>
       </c>
-      <c r="K172" s="8" t="s">
+      <c r="K172" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L172" s="7" t="s">
+      <c r="L172" s="8" t="s">
         <v>972</v>
       </c>
     </row>
@@ -9480,13 +10030,13 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="8" t="s">
+      <c r="J173" s="9" t="s">
         <v>966</v>
       </c>
-      <c r="K173" s="8" t="s">
+      <c r="K173" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L173" s="7" t="s">
+      <c r="L173" s="8" t="s">
         <v>977</v>
       </c>
     </row>
@@ -9512,13 +10062,13 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="8" t="s">
+      <c r="J174" s="9" t="s">
         <v>966</v>
       </c>
-      <c r="K174" s="8" t="s">
+      <c r="K174" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L174" s="7" t="s">
+      <c r="L174" s="8" t="s">
         <v>982</v>
       </c>
     </row>
@@ -9544,13 +10094,13 @@
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="8" t="s">
+      <c r="J175" s="9" t="s">
         <v>966</v>
       </c>
-      <c r="K175" s="8" t="s">
+      <c r="K175" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L175" s="7" t="s">
+      <c r="L175" s="8" t="s">
         <v>987</v>
       </c>
     </row>
@@ -9576,13 +10126,13 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="8" t="s">
+      <c r="J176" s="9" t="s">
         <v>992</v>
       </c>
-      <c r="K176" s="8" t="s">
+      <c r="K176" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L176" s="7" t="s">
+      <c r="L176" s="8" t="s">
         <v>993</v>
       </c>
     </row>
@@ -9608,13 +10158,13 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="8" t="s">
+      <c r="J177" s="9" t="s">
         <v>992</v>
       </c>
-      <c r="K177" s="8" t="s">
+      <c r="K177" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L177" s="7" t="s">
+      <c r="L177" s="8" t="s">
         <v>998</v>
       </c>
     </row>
@@ -9640,13 +10190,13 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="8" t="s">
+      <c r="J178" s="9" t="s">
         <v>992</v>
       </c>
-      <c r="K178" s="8" t="s">
+      <c r="K178" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L178" s="7" t="s">
+      <c r="L178" s="8" t="s">
         <v>1003</v>
       </c>
     </row>
@@ -9672,13 +10222,13 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="8" t="s">
+      <c r="J179" s="9" t="s">
         <v>992</v>
       </c>
-      <c r="K179" s="8" t="s">
+      <c r="K179" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L179" s="7" t="s">
+      <c r="L179" s="8" t="s">
         <v>1008</v>
       </c>
     </row>
@@ -9704,22 +10254,1142 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="8" t="s">
+      <c r="J180" s="9" t="s">
         <v>992</v>
       </c>
-      <c r="K180" s="8" t="s">
+      <c r="K180" s="9" t="s">
         <v>776</v>
       </c>
-      <c r="L180" s="7" t="s">
+      <c r="L180" s="8" t="s">
         <v>1013</v>
+      </c>
+    </row>
+    <row r="181" s="3" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C181" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E181" s="3">
+        <v>5</v>
+      </c>
+      <c r="F181" s="3">
+        <v>5</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H181" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I181" s="3">
+        <v>0</v>
+      </c>
+      <c r="J181" s="10" t="s">
+        <v>1018</v>
+      </c>
+      <c r="K181" s="10" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L181" s="8" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" spans="3:12">
+      <c r="C182" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E182" s="1">
+        <v>5</v>
+      </c>
+      <c r="F182" s="1">
+        <v>5</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="I182" s="1">
+        <v>0</v>
+      </c>
+      <c r="J182" s="9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="K182" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L182" s="8" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="3:12">
+      <c r="C183" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E183" s="1">
+        <v>5</v>
+      </c>
+      <c r="F183" s="1">
+        <v>5</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I183" s="1">
+        <v>0</v>
+      </c>
+      <c r="J183" s="9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="K183" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L183" s="8" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="3:12">
+      <c r="C184" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E184" s="1">
+        <v>5</v>
+      </c>
+      <c r="F184" s="1">
+        <v>5</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I184" s="1">
+        <v>0</v>
+      </c>
+      <c r="J184" s="9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="K184" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L184" s="8" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="3:12">
+      <c r="C185" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E185" s="1">
+        <v>5</v>
+      </c>
+      <c r="F185" s="1">
+        <v>5</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I185" s="1">
+        <v>0</v>
+      </c>
+      <c r="J185" s="9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="K185" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L185" s="8" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" spans="3:12">
+      <c r="C186" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E186" s="1">
+        <v>5</v>
+      </c>
+      <c r="F186" s="1">
+        <v>5</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H186" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I186" s="1">
+        <v>0</v>
+      </c>
+      <c r="J186" s="9" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K186" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L186" s="8" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="3:12">
+      <c r="C187" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E187" s="1">
+        <v>5</v>
+      </c>
+      <c r="F187" s="1">
+        <v>5</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I187" s="1">
+        <v>0</v>
+      </c>
+      <c r="J187" s="9" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K187" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L187" s="8" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="3:12">
+      <c r="C188" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E188" s="1">
+        <v>5</v>
+      </c>
+      <c r="F188" s="1">
+        <v>5</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H188" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I188" s="1">
+        <v>0</v>
+      </c>
+      <c r="J188" s="9" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K188" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L188" s="8" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="3:12">
+      <c r="C189" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E189" s="1">
+        <v>5</v>
+      </c>
+      <c r="F189" s="1">
+        <v>5</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H189" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I189" s="1">
+        <v>0</v>
+      </c>
+      <c r="J189" s="9" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K189" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L189" s="8" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="3:12">
+      <c r="C190" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E190" s="1">
+        <v>5</v>
+      </c>
+      <c r="F190" s="1">
+        <v>5</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="I190" s="1">
+        <v>0</v>
+      </c>
+      <c r="J190" s="9" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K190" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L190" s="8" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="191" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C191" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E191" s="1">
+        <v>5</v>
+      </c>
+      <c r="F191" s="1">
+        <v>5</v>
+      </c>
+      <c r="G191" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I191" s="1">
+        <v>0</v>
+      </c>
+      <c r="J191" s="9" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K191" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L191" s="8" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="192" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C192" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E192" s="1">
+        <v>5</v>
+      </c>
+      <c r="F192" s="1">
+        <v>5</v>
+      </c>
+      <c r="G192" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I192" s="1">
+        <v>0</v>
+      </c>
+      <c r="J192" s="9" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K192" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L192" s="8" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="193" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C193" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E193" s="1">
+        <v>5</v>
+      </c>
+      <c r="F193" s="1">
+        <v>5</v>
+      </c>
+      <c r="G193" s="7" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I193" s="1">
+        <v>0</v>
+      </c>
+      <c r="J193" s="9" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K193" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L193" s="8" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="194" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C194" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E194" s="1">
+        <v>5</v>
+      </c>
+      <c r="F194" s="1">
+        <v>5</v>
+      </c>
+      <c r="G194" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="I194" s="1">
+        <v>0</v>
+      </c>
+      <c r="J194" s="9" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K194" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L194" s="8" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="195" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C195" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E195" s="1">
+        <v>5</v>
+      </c>
+      <c r="F195" s="1">
+        <v>5</v>
+      </c>
+      <c r="G195" s="7" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I195" s="1">
+        <v>0</v>
+      </c>
+      <c r="J195" s="9" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K195" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L195" s="8" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="196" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C196" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E196" s="1">
+        <v>5</v>
+      </c>
+      <c r="F196" s="1">
+        <v>5</v>
+      </c>
+      <c r="G196" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I196" s="1">
+        <v>0</v>
+      </c>
+      <c r="J196" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K196" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L196" s="8" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="197" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C197" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E197" s="1">
+        <v>5</v>
+      </c>
+      <c r="F197" s="1">
+        <v>5</v>
+      </c>
+      <c r="G197" s="7" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I197" s="1">
+        <v>0</v>
+      </c>
+      <c r="J197" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K197" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L197" s="8" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="198" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C198" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E198" s="1">
+        <v>5</v>
+      </c>
+      <c r="F198" s="1">
+        <v>5</v>
+      </c>
+      <c r="G198" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I198" s="1">
+        <v>0</v>
+      </c>
+      <c r="J198" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K198" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L198" s="8" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="199" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C199" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E199" s="1">
+        <v>5</v>
+      </c>
+      <c r="F199" s="1">
+        <v>5</v>
+      </c>
+      <c r="G199" s="7" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I199" s="1">
+        <v>0</v>
+      </c>
+      <c r="J199" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K199" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L199" s="8" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="200" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C200" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E200" s="1">
+        <v>5</v>
+      </c>
+      <c r="F200" s="1">
+        <v>5</v>
+      </c>
+      <c r="G200" s="7" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="I200" s="1">
+        <v>0</v>
+      </c>
+      <c r="J200" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K200" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L200" s="8" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" spans="3:12">
+      <c r="C201" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E201" s="1">
+        <v>5</v>
+      </c>
+      <c r="F201" s="1">
+        <v>5</v>
+      </c>
+      <c r="G201" s="7" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H201" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="I201" s="1">
+        <v>0</v>
+      </c>
+      <c r="J201" s="9" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K201" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L201" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" spans="3:12">
+      <c r="C202" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E202" s="1">
+        <v>5</v>
+      </c>
+      <c r="F202" s="1">
+        <v>5</v>
+      </c>
+      <c r="G202" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="I202" s="1">
+        <v>0</v>
+      </c>
+      <c r="J202" s="9" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K202" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L202" s="8" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="3:12">
+      <c r="C203" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E203" s="1">
+        <v>5</v>
+      </c>
+      <c r="F203" s="1">
+        <v>5</v>
+      </c>
+      <c r="G203" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I203" s="1">
+        <v>0</v>
+      </c>
+      <c r="J203" s="9" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K203" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L203" s="8" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="3:12">
+      <c r="C204" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E204" s="1">
+        <v>5</v>
+      </c>
+      <c r="F204" s="1">
+        <v>5</v>
+      </c>
+      <c r="G204" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="I204" s="1">
+        <v>0</v>
+      </c>
+      <c r="J204" s="9" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K204" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L204" s="8" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="3:12">
+      <c r="C205" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E205" s="1">
+        <v>5</v>
+      </c>
+      <c r="F205" s="1">
+        <v>5</v>
+      </c>
+      <c r="G205" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="I205" s="1">
+        <v>0</v>
+      </c>
+      <c r="J205" s="9" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K205" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L205" s="8" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" spans="3:12">
+      <c r="C206" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E206" s="1">
+        <v>5</v>
+      </c>
+      <c r="F206" s="1">
+        <v>5</v>
+      </c>
+      <c r="G206" s="7" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I206" s="1">
+        <v>0</v>
+      </c>
+      <c r="J206" s="9" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K206" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L206" s="8" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="3:12">
+      <c r="C207" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E207" s="1">
+        <v>5</v>
+      </c>
+      <c r="F207" s="1">
+        <v>5</v>
+      </c>
+      <c r="G207" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I207" s="1">
+        <v>0</v>
+      </c>
+      <c r="J207" s="9" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K207" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L207" s="8" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" spans="3:12">
+      <c r="C208" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E208" s="1">
+        <v>5</v>
+      </c>
+      <c r="F208" s="1">
+        <v>5</v>
+      </c>
+      <c r="G208" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I208" s="1">
+        <v>0</v>
+      </c>
+      <c r="J208" s="9" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K208" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L208" s="8" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" spans="3:12">
+      <c r="C209" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E209" s="1">
+        <v>5</v>
+      </c>
+      <c r="F209" s="1">
+        <v>5</v>
+      </c>
+      <c r="G209" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I209" s="1">
+        <v>0</v>
+      </c>
+      <c r="J209" s="9" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K209" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L209" s="8" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" spans="3:12">
+      <c r="C210" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E210" s="1">
+        <v>5</v>
+      </c>
+      <c r="F210" s="1">
+        <v>5</v>
+      </c>
+      <c r="G210" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I210" s="1">
+        <v>0</v>
+      </c>
+      <c r="J210" s="9" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K210" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L210" s="8" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="211" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C211" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E211" s="1">
+        <v>5</v>
+      </c>
+      <c r="F211" s="1">
+        <v>5</v>
+      </c>
+      <c r="G211" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="I211" s="1">
+        <v>0</v>
+      </c>
+      <c r="J211" s="9" t="s">
+        <v>1175</v>
+      </c>
+      <c r="K211" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L211" s="8" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C212" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E212" s="1">
+        <v>5</v>
+      </c>
+      <c r="F212" s="1">
+        <v>5</v>
+      </c>
+      <c r="G212" s="7" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H212" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="I212" s="1">
+        <v>0</v>
+      </c>
+      <c r="J212" s="9" t="s">
+        <v>1175</v>
+      </c>
+      <c r="K212" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L212" s="8" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="213" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C213" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E213" s="1">
+        <v>5</v>
+      </c>
+      <c r="F213" s="1">
+        <v>5</v>
+      </c>
+      <c r="G213" s="7" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H213" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="I213" s="1">
+        <v>0</v>
+      </c>
+      <c r="J213" s="9" t="s">
+        <v>1175</v>
+      </c>
+      <c r="K213" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L213" s="8" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="214" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C214" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E214" s="1">
+        <v>5</v>
+      </c>
+      <c r="F214" s="1">
+        <v>5</v>
+      </c>
+      <c r="G214" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H214" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="I214" s="1">
+        <v>0</v>
+      </c>
+      <c r="J214" s="9" t="s">
+        <v>1175</v>
+      </c>
+      <c r="K214" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L214" s="8" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="215" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C215" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E215" s="1">
+        <v>5</v>
+      </c>
+      <c r="F215" s="1">
+        <v>5</v>
+      </c>
+      <c r="G215" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H215" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="I215" s="1">
+        <v>0</v>
+      </c>
+      <c r="J215" s="9" t="s">
+        <v>1175</v>
+      </c>
+      <c r="K215" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L215" s="8" t="s">
+        <v>1196</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C179 C180:C215 C216:C1048576" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="1198">
   <si>
     <t>_Id</t>
   </si>
@@ -3101,6 +3101,9 @@
   </si>
   <si>
     <t>10174</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>1175</t>
@@ -4672,7 +4675,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:M215"/>
+  <dimension ref="A3:M215"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
@@ -10264,12 +10267,18 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="181" s="3" customFormat="1" customHeight="1" spans="3:12">
+    <row r="181" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A181" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>1014</v>
+      </c>
       <c r="C181" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E181" s="3">
         <v>5</v>
@@ -10278,30 +10287,36 @@
         <v>5</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="I181" s="3">
         <v>0</v>
       </c>
       <c r="J181" s="10" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="K181" s="10" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L181" s="8" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="182" customHeight="1" spans="3:12">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" spans="1:12">
+      <c r="A182" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C182" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="E182" s="1">
         <v>5</v>
@@ -10310,30 +10325,36 @@
         <v>5</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="I182" s="1">
         <v>0</v>
       </c>
       <c r="J182" s="9" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="K182" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L182" s="8" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="183" customHeight="1" spans="3:12">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="1:12">
+      <c r="A183" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C183" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E183" s="1">
         <v>5</v>
@@ -10342,30 +10363,36 @@
         <v>5</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="I183" s="1">
         <v>0</v>
       </c>
       <c r="J183" s="9" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="K183" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L183" s="8" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="184" customHeight="1" spans="3:12">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="1:12">
+      <c r="A184" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C184" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E184" s="1">
         <v>5</v>
@@ -10374,30 +10401,36 @@
         <v>5</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="I184" s="1">
         <v>0</v>
       </c>
       <c r="J184" s="9" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="K184" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L184" s="8" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="185" customHeight="1" spans="3:12">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="1:12">
+      <c r="A185" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C185" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="E185" s="1">
         <v>5</v>
@@ -10406,30 +10439,36 @@
         <v>5</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="I185" s="1">
         <v>0</v>
       </c>
       <c r="J185" s="9" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="K185" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L185" s="8" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="186" customHeight="1" spans="3:12">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" spans="1:12">
+      <c r="A186" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C186" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E186" s="1">
         <v>5</v>
@@ -10438,30 +10477,36 @@
         <v>5</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="I186" s="1">
         <v>0</v>
       </c>
       <c r="J186" s="9" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="K186" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L186" s="8" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="187" customHeight="1" spans="3:12">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="1:12">
+      <c r="A187" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C187" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E187" s="1">
         <v>5</v>
@@ -10470,30 +10515,36 @@
         <v>5</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="I187" s="1">
         <v>0</v>
       </c>
       <c r="J187" s="9" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="K187" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L187" s="8" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="188" customHeight="1" spans="3:12">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="1:12">
+      <c r="A188" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C188" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="E188" s="1">
         <v>5</v>
@@ -10502,30 +10553,36 @@
         <v>5</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="I188" s="1">
         <v>0</v>
       </c>
       <c r="J188" s="9" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="K188" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L188" s="8" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="189" customHeight="1" spans="3:12">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="1:12">
+      <c r="A189" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C189" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="E189" s="1">
         <v>5</v>
@@ -10534,30 +10591,36 @@
         <v>5</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="I189" s="1">
         <v>0</v>
       </c>
       <c r="J189" s="9" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="K189" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L189" s="8" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="190" customHeight="1" spans="3:12">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="1:12">
+      <c r="A190" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C190" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E190" s="1">
         <v>5</v>
@@ -10566,30 +10629,36 @@
         <v>5</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="I190" s="1">
         <v>0</v>
       </c>
       <c r="J190" s="9" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="K190" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L190" s="8" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="191" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="191" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A191" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C191" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="E191" s="1">
         <v>5</v>
@@ -10598,30 +10667,36 @@
         <v>5</v>
       </c>
       <c r="G191" s="7" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="I191" s="1">
         <v>0</v>
       </c>
       <c r="J191" s="9" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="K191" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L191" s="8" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="192" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="192" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A192" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C192" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E192" s="1">
         <v>5</v>
@@ -10630,30 +10705,36 @@
         <v>5</v>
       </c>
       <c r="G192" s="7" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="I192" s="1">
         <v>0</v>
       </c>
       <c r="J192" s="9" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="K192" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L192" s="8" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="193" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="193" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A193" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C193" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="E193" s="1">
         <v>5</v>
@@ -10662,30 +10743,36 @@
         <v>5</v>
       </c>
       <c r="G193" s="7" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
       </c>
       <c r="J193" s="9" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="K193" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L193" s="8" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="194" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="194" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A194" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C194" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E194" s="1">
         <v>5</v>
@@ -10694,30 +10781,36 @@
         <v>5</v>
       </c>
       <c r="G194" s="7" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
       </c>
       <c r="J194" s="9" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="K194" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L194" s="8" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="195" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="195" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A195" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C195" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E195" s="1">
         <v>5</v>
@@ -10726,30 +10819,36 @@
         <v>5</v>
       </c>
       <c r="G195" s="7" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="I195" s="1">
         <v>0</v>
       </c>
       <c r="J195" s="9" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="K195" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L195" s="8" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="196" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="196" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A196" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C196" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E196" s="1">
         <v>5</v>
@@ -10758,30 +10857,36 @@
         <v>5</v>
       </c>
       <c r="G196" s="7" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="I196" s="1">
         <v>0</v>
       </c>
       <c r="J196" s="9" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="K196" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L196" s="8" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="197" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="197" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A197" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C197" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="E197" s="1">
         <v>5</v>
@@ -10790,30 +10895,36 @@
         <v>5</v>
       </c>
       <c r="G197" s="7" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="I197" s="1">
         <v>0</v>
       </c>
       <c r="J197" s="9" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="K197" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L197" s="8" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="198" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="198" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A198" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C198" s="1" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="E198" s="1">
         <v>5</v>
@@ -10822,30 +10933,36 @@
         <v>5</v>
       </c>
       <c r="G198" s="7" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="I198" s="1">
         <v>0</v>
       </c>
       <c r="J198" s="9" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="K198" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L198" s="8" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="199" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="199" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A199" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C199" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="E199" s="1">
         <v>5</v>
@@ -10854,30 +10971,36 @@
         <v>5</v>
       </c>
       <c r="G199" s="7" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="I199" s="1">
         <v>0</v>
       </c>
       <c r="J199" s="9" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="K199" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L199" s="8" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="200" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="200" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A200" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C200" s="1" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E200" s="1">
         <v>5</v>
@@ -10886,30 +11009,36 @@
         <v>5</v>
       </c>
       <c r="G200" s="7" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="I200" s="1">
         <v>0</v>
       </c>
       <c r="J200" s="9" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="K200" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L200" s="8" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="201" customHeight="1" spans="3:12">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" spans="1:12">
+      <c r="A201" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C201" s="1" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="E201" s="1">
         <v>5</v>
@@ -10918,30 +11047,36 @@
         <v>5</v>
       </c>
       <c r="G201" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="I201" s="1">
         <v>0</v>
       </c>
       <c r="J201" s="9" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="K201" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L201" s="8" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="202" customHeight="1" spans="3:12">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" spans="1:12">
+      <c r="A202" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C202" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="E202" s="1">
         <v>5</v>
@@ -10950,30 +11085,36 @@
         <v>5</v>
       </c>
       <c r="G202" s="7" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="I202" s="1">
         <v>0</v>
       </c>
       <c r="J202" s="9" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="K202" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L202" s="8" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="203" customHeight="1" spans="3:12">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="1:12">
+      <c r="A203" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C203" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E203" s="1">
         <v>5</v>
@@ -10982,30 +11123,36 @@
         <v>5</v>
       </c>
       <c r="G203" s="7" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="I203" s="1">
         <v>0</v>
       </c>
       <c r="J203" s="9" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="K203" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L203" s="8" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="204" customHeight="1" spans="3:12">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="1:12">
+      <c r="A204" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C204" s="1" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="E204" s="1">
         <v>5</v>
@@ -11014,30 +11161,36 @@
         <v>5</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="I204" s="1">
         <v>0</v>
       </c>
       <c r="J204" s="9" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="K204" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L204" s="8" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="205" customHeight="1" spans="3:12">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="1:12">
+      <c r="A205" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C205" s="1" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="E205" s="1">
         <v>5</v>
@@ -11046,30 +11199,36 @@
         <v>5</v>
       </c>
       <c r="G205" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="I205" s="1">
         <v>0</v>
       </c>
       <c r="J205" s="9" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="K205" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L205" s="8" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="206" customHeight="1" spans="3:12">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" spans="1:12">
+      <c r="A206" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C206" s="1" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E206" s="1">
         <v>5</v>
@@ -11078,30 +11237,36 @@
         <v>5</v>
       </c>
       <c r="G206" s="7" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="I206" s="1">
         <v>0</v>
       </c>
       <c r="J206" s="9" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="K206" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L206" s="8" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="207" customHeight="1" spans="3:12">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="1:12">
+      <c r="A207" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C207" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E207" s="1">
         <v>5</v>
@@ -11110,30 +11275,36 @@
         <v>5</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="I207" s="1">
         <v>0</v>
       </c>
       <c r="J207" s="9" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="K207" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L207" s="8" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="208" customHeight="1" spans="3:12">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" spans="1:12">
+      <c r="A208" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C208" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="E208" s="1">
         <v>5</v>
@@ -11142,30 +11313,36 @@
         <v>5</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="I208" s="1">
         <v>0</v>
       </c>
       <c r="J208" s="9" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="K208" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L208" s="8" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="209" customHeight="1" spans="3:12">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" spans="1:12">
+      <c r="A209" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C209" s="1" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="E209" s="1">
         <v>5</v>
@@ -11174,30 +11351,36 @@
         <v>5</v>
       </c>
       <c r="G209" s="7" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="I209" s="1">
         <v>0</v>
       </c>
       <c r="J209" s="9" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="K209" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L209" s="8" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="210" customHeight="1" spans="3:12">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" spans="1:12">
+      <c r="A210" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C210" s="1" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="E210" s="1">
         <v>5</v>
@@ -11206,30 +11389,36 @@
         <v>5</v>
       </c>
       <c r="G210" s="7" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="I210" s="1">
         <v>0</v>
       </c>
       <c r="J210" s="9" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="K210" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L210" s="8" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="211" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A211" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C211" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="E211" s="1">
         <v>5</v>
@@ -11238,30 +11427,36 @@
         <v>5</v>
       </c>
       <c r="G211" s="7" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="I211" s="1">
         <v>0</v>
       </c>
       <c r="J211" s="9" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="K211" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L211" s="8" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="212" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A212" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C212" s="1" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E212" s="1">
         <v>5</v>
@@ -11270,30 +11465,36 @@
         <v>5</v>
       </c>
       <c r="G212" s="7" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="I212" s="1">
         <v>0</v>
       </c>
       <c r="J212" s="9" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="K212" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L212" s="8" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="213" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A213" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C213" s="1" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E213" s="1">
         <v>5</v>
@@ -11302,30 +11503,36 @@
         <v>5</v>
       </c>
       <c r="G213" s="7" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="I213" s="1">
         <v>0</v>
       </c>
       <c r="J213" s="9" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="K213" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L213" s="8" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="214" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A214" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C214" s="1" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E214" s="1">
         <v>5</v>
@@ -11334,30 +11541,36 @@
         <v>5</v>
       </c>
       <c r="G214" s="7" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="I214" s="1">
         <v>0</v>
       </c>
       <c r="J214" s="9" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="K214" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L214" s="8" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="215" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A215" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>1014</v>
+      </c>
       <c r="C215" s="1" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E215" s="1">
         <v>5</v>
@@ -11366,22 +11579,22 @@
         <v>5</v>
       </c>
       <c r="G215" s="7" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="I215" s="1">
         <v>0</v>
       </c>
       <c r="J215" s="9" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="K215" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L215" s="8" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
   </sheetData>
@@ -11389,7 +11602,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C179 C180:C215 C216:C1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C1048576" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1202">
   <si>
     <t>_Id</t>
   </si>
@@ -3103,88 +3103,100 @@
     <t>10174</t>
   </si>
   <si>
+    <t>1175</t>
+  </si>
+  <si>
+    <t>混沌小村</t>
+  </si>
+  <si>
+    <t>1800-1</t>
+  </si>
+  <si>
+    <t>混沌装备</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,202004</t>
+  </si>
+  <si>
+    <t>100,25000,10000,180000,1000000,140000,600000,20000</t>
+  </si>
+  <si>
+    <t>10175</t>
+  </si>
+  <si>
+    <t>1176</t>
+  </si>
+  <si>
+    <t>混沌村外</t>
+  </si>
+  <si>
+    <t>1800-2</t>
+  </si>
+  <si>
+    <t>混沌鹿茸</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,202005</t>
+  </si>
+  <si>
+    <t>10176</t>
+  </si>
+  <si>
+    <t>1177</t>
+  </si>
+  <si>
+    <t>混沌农场</t>
+  </si>
+  <si>
+    <t>1800-3</t>
+  </si>
+  <si>
+    <t>混沌草帽</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,202006</t>
+  </si>
+  <si>
+    <t>10177</t>
+  </si>
+  <si>
+    <t>1178</t>
+  </si>
+  <si>
+    <t>混沌老城</t>
+  </si>
+  <si>
+    <t>1800-4</t>
+  </si>
+  <si>
+    <t>混沌猫爪</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,202007</t>
+  </si>
+  <si>
+    <t>10178</t>
+  </si>
+  <si>
+    <t>1179</t>
+  </si>
+  <si>
+    <t>混沌森林</t>
+  </si>
+  <si>
+    <t>1800-5</t>
+  </si>
+  <si>
+    <t>混沌花朵</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,202003</t>
+  </si>
+  <si>
+    <t>10179</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1175</t>
-  </si>
-  <si>
-    <t>混沌小村</t>
-  </si>
-  <si>
-    <t>1800-1</t>
-  </si>
-  <si>
-    <t>混沌装备</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210077,1009,505,202003</t>
-  </si>
-  <si>
-    <t>100,25000,10000,180000,1000000,140000,600000,20000</t>
-  </si>
-  <si>
-    <t>10175</t>
-  </si>
-  <si>
-    <t>1176</t>
-  </si>
-  <si>
-    <t>混沌村外</t>
-  </si>
-  <si>
-    <t>1800-2</t>
-  </si>
-  <si>
-    <t>混沌鹿茸</t>
-  </si>
-  <si>
-    <t>10176</t>
-  </si>
-  <si>
-    <t>1177</t>
-  </si>
-  <si>
-    <t>混沌农场</t>
-  </si>
-  <si>
-    <t>1800-3</t>
-  </si>
-  <si>
-    <t>混沌草帽</t>
-  </si>
-  <si>
-    <t>10177</t>
-  </si>
-  <si>
-    <t>1178</t>
-  </si>
-  <si>
-    <t>混沌老城</t>
-  </si>
-  <si>
-    <t>1800-4</t>
-  </si>
-  <si>
-    <t>混沌猫爪</t>
-  </si>
-  <si>
-    <t>10178</t>
-  </si>
-  <si>
-    <t>1179</t>
-  </si>
-  <si>
-    <t>混沌森林</t>
-  </si>
-  <si>
-    <t>1800-5</t>
-  </si>
-  <si>
-    <t>混沌花朵</t>
-  </si>
-  <si>
-    <t>10179</t>
   </si>
   <si>
     <t>1180</t>
@@ -10267,89 +10279,71 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="181" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A181" s="3" t="s">
+    <row r="181" s="3" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C181" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="B181" s="3" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C181" s="1" t="s">
+      <c r="D181" s="3" t="s">
         <v>1015</v>
       </c>
-      <c r="D181" s="3" t="s">
+      <c r="E181" s="3">
+        <v>5</v>
+      </c>
+      <c r="F181" s="3">
+        <v>5</v>
+      </c>
+      <c r="G181" s="3" t="s">
         <v>1016</v>
       </c>
-      <c r="E181" s="3">
-        <v>5</v>
-      </c>
-      <c r="F181" s="3">
-        <v>5</v>
-      </c>
-      <c r="G181" s="3" t="s">
+      <c r="H181" s="3" t="s">
         <v>1017</v>
-      </c>
-      <c r="H181" s="3" t="s">
-        <v>1018</v>
       </c>
       <c r="I181" s="3">
         <v>0</v>
       </c>
       <c r="J181" s="10" t="s">
+        <v>1018</v>
+      </c>
+      <c r="K181" s="10" t="s">
         <v>1019</v>
       </c>
-      <c r="K181" s="10" t="s">
+      <c r="L181" s="8" t="s">
         <v>1020</v>
       </c>
-      <c r="L181" s="8" t="s">
+    </row>
+    <row r="182" customHeight="1" spans="3:12">
+      <c r="C182" s="1" t="s">
         <v>1021</v>
       </c>
-    </row>
-    <row r="182" customHeight="1" spans="1:12">
-      <c r="A182" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C182" s="1" t="s">
+      <c r="D182" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="D182" s="1" t="s">
+      <c r="E182" s="1">
+        <v>5</v>
+      </c>
+      <c r="F182" s="1">
+        <v>5</v>
+      </c>
+      <c r="G182" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="E182" s="1">
-        <v>5</v>
-      </c>
-      <c r="F182" s="1">
-        <v>5</v>
-      </c>
-      <c r="G182" s="1" t="s">
+      <c r="H182" s="1" t="s">
         <v>1024</v>
-      </c>
-      <c r="H182" s="1" t="s">
-        <v>1025</v>
       </c>
       <c r="I182" s="1">
         <v>0</v>
       </c>
       <c r="J182" s="9" t="s">
+        <v>1025</v>
+      </c>
+      <c r="K182" s="9" t="s">
         <v>1019</v>
-      </c>
-      <c r="K182" s="9" t="s">
-        <v>1020</v>
       </c>
       <c r="L182" s="8" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="183" customHeight="1" spans="1:12">
-      <c r="A183" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>1014</v>
-      </c>
+    <row r="183" customHeight="1" spans="3:12">
       <c r="C183" s="1" t="s">
         <v>1027</v>
       </c>
@@ -10372,27 +10366,21 @@
         <v>0</v>
       </c>
       <c r="J183" s="9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K183" s="9" t="s">
         <v>1019</v>
       </c>
-      <c r="K183" s="9" t="s">
-        <v>1020</v>
-      </c>
       <c r="L183" s="8" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="184" customHeight="1" spans="1:12">
-      <c r="A184" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>1014</v>
-      </c>
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="3:12">
       <c r="C184" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E184" s="1">
         <v>5</v>
@@ -10401,36 +10389,30 @@
         <v>5</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="I184" s="1">
         <v>0</v>
       </c>
       <c r="J184" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="K184" s="9" t="s">
         <v>1019</v>
       </c>
-      <c r="K184" s="9" t="s">
-        <v>1020</v>
-      </c>
       <c r="L184" s="8" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="185" customHeight="1" spans="1:12">
-      <c r="A185" s="1" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>1014</v>
-      </c>
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="3:12">
       <c r="C185" s="1" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="E185" s="1">
         <v>5</v>
@@ -10439,36 +10421,36 @@
         <v>5</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="I185" s="1">
         <v>0</v>
       </c>
       <c r="J185" s="9" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K185" s="9" t="s">
         <v>1019</v>
       </c>
-      <c r="K185" s="9" t="s">
-        <v>1020</v>
-      </c>
       <c r="L185" s="8" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="186" customHeight="1" spans="1:12">
       <c r="A186" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="E186" s="1">
         <v>5</v>
@@ -10477,36 +10459,36 @@
         <v>5</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="I186" s="1">
         <v>0</v>
       </c>
       <c r="J186" s="9" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="K186" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L186" s="8" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="187" customHeight="1" spans="1:12">
       <c r="A187" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="E187" s="1">
         <v>5</v>
@@ -10515,36 +10497,36 @@
         <v>5</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="I187" s="1">
         <v>0</v>
       </c>
       <c r="J187" s="9" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="K187" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L187" s="8" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="188" customHeight="1" spans="1:12">
       <c r="A188" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="E188" s="1">
         <v>5</v>
@@ -10553,36 +10535,36 @@
         <v>5</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="I188" s="1">
         <v>0</v>
       </c>
       <c r="J188" s="9" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="K188" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L188" s="8" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="189" customHeight="1" spans="1:12">
       <c r="A189" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="E189" s="1">
         <v>5</v>
@@ -10591,36 +10573,36 @@
         <v>5</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="I189" s="1">
         <v>0</v>
       </c>
       <c r="J189" s="9" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="K189" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L189" s="8" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="190" customHeight="1" spans="1:12">
       <c r="A190" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="E190" s="1">
         <v>5</v>
@@ -10629,36 +10611,36 @@
         <v>5</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="I190" s="1">
         <v>0</v>
       </c>
       <c r="J190" s="9" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="K190" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L190" s="8" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="191" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A191" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="E191" s="1">
         <v>5</v>
@@ -10667,36 +10649,36 @@
         <v>5</v>
       </c>
       <c r="G191" s="7" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="I191" s="1">
         <v>0</v>
       </c>
       <c r="J191" s="9" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="K191" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L191" s="8" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="192" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A192" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="E192" s="1">
         <v>5</v>
@@ -10705,36 +10687,36 @@
         <v>5</v>
       </c>
       <c r="G192" s="7" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="I192" s="1">
         <v>0</v>
       </c>
       <c r="J192" s="9" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="K192" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L192" s="8" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="193" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A193" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="E193" s="1">
         <v>5</v>
@@ -10743,36 +10725,36 @@
         <v>5</v>
       </c>
       <c r="G193" s="7" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
       </c>
       <c r="J193" s="9" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="K193" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L193" s="8" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="194" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A194" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="E194" s="1">
         <v>5</v>
@@ -10781,36 +10763,36 @@
         <v>5</v>
       </c>
       <c r="G194" s="7" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
       </c>
       <c r="J194" s="9" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="K194" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L194" s="8" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="195" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A195" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="E195" s="1">
         <v>5</v>
@@ -10819,36 +10801,36 @@
         <v>5</v>
       </c>
       <c r="G195" s="7" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="I195" s="1">
         <v>0</v>
       </c>
       <c r="J195" s="9" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="K195" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L195" s="8" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="196" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A196" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="E196" s="1">
         <v>5</v>
@@ -10857,36 +10839,36 @@
         <v>5</v>
       </c>
       <c r="G196" s="7" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="I196" s="1">
         <v>0</v>
       </c>
       <c r="J196" s="9" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="K196" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L196" s="8" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="197" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A197" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="E197" s="1">
         <v>5</v>
@@ -10895,36 +10877,36 @@
         <v>5</v>
       </c>
       <c r="G197" s="7" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="I197" s="1">
         <v>0</v>
       </c>
       <c r="J197" s="9" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="K197" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L197" s="8" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="198" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A198" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="E198" s="1">
         <v>5</v>
@@ -10933,36 +10915,36 @@
         <v>5</v>
       </c>
       <c r="G198" s="7" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="I198" s="1">
         <v>0</v>
       </c>
       <c r="J198" s="9" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="K198" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L198" s="8" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="199" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A199" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="E199" s="1">
         <v>5</v>
@@ -10971,36 +10953,36 @@
         <v>5</v>
       </c>
       <c r="G199" s="7" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="I199" s="1">
         <v>0</v>
       </c>
       <c r="J199" s="9" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="K199" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L199" s="8" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="200" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A200" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="E200" s="1">
         <v>5</v>
@@ -11009,36 +10991,36 @@
         <v>5</v>
       </c>
       <c r="G200" s="7" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="I200" s="1">
         <v>0</v>
       </c>
       <c r="J200" s="9" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="K200" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L200" s="8" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="201" customHeight="1" spans="1:12">
       <c r="A201" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="E201" s="1">
         <v>5</v>
@@ -11047,36 +11029,36 @@
         <v>5</v>
       </c>
       <c r="G201" s="7" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="I201" s="1">
         <v>0</v>
       </c>
       <c r="J201" s="9" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="K201" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L201" s="8" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="202" customHeight="1" spans="1:12">
       <c r="A202" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="E202" s="1">
         <v>5</v>
@@ -11085,36 +11067,36 @@
         <v>5</v>
       </c>
       <c r="G202" s="7" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="I202" s="1">
         <v>0</v>
       </c>
       <c r="J202" s="9" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="K202" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L202" s="8" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="203" customHeight="1" spans="1:12">
       <c r="A203" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="E203" s="1">
         <v>5</v>
@@ -11123,36 +11105,36 @@
         <v>5</v>
       </c>
       <c r="G203" s="7" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="I203" s="1">
         <v>0</v>
       </c>
       <c r="J203" s="9" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="K203" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L203" s="8" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="204" customHeight="1" spans="1:12">
       <c r="A204" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="E204" s="1">
         <v>5</v>
@@ -11161,36 +11143,36 @@
         <v>5</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="I204" s="1">
         <v>0</v>
       </c>
       <c r="J204" s="9" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="K204" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L204" s="8" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="205" customHeight="1" spans="1:12">
       <c r="A205" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="E205" s="1">
         <v>5</v>
@@ -11199,36 +11181,36 @@
         <v>5</v>
       </c>
       <c r="G205" s="7" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="I205" s="1">
         <v>0</v>
       </c>
       <c r="J205" s="9" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="K205" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L205" s="8" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="206" customHeight="1" spans="1:12">
       <c r="A206" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="E206" s="1">
         <v>5</v>
@@ -11237,36 +11219,36 @@
         <v>5</v>
       </c>
       <c r="G206" s="7" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="I206" s="1">
         <v>0</v>
       </c>
       <c r="J206" s="9" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="K206" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L206" s="8" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="207" customHeight="1" spans="1:12">
       <c r="A207" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="E207" s="1">
         <v>5</v>
@@ -11275,36 +11257,36 @@
         <v>5</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="I207" s="1">
         <v>0</v>
       </c>
       <c r="J207" s="9" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="K207" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L207" s="8" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="208" customHeight="1" spans="1:12">
       <c r="A208" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E208" s="1">
         <v>5</v>
@@ -11313,36 +11295,36 @@
         <v>5</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="I208" s="1">
         <v>0</v>
       </c>
       <c r="J208" s="9" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="K208" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L208" s="8" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="209" customHeight="1" spans="1:12">
       <c r="A209" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="E209" s="1">
         <v>5</v>
@@ -11351,36 +11333,36 @@
         <v>5</v>
       </c>
       <c r="G209" s="7" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="I209" s="1">
         <v>0</v>
       </c>
       <c r="J209" s="9" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="K209" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L209" s="8" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="210" customHeight="1" spans="1:12">
       <c r="A210" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="E210" s="1">
         <v>5</v>
@@ -11389,36 +11371,36 @@
         <v>5</v>
       </c>
       <c r="G210" s="7" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="I210" s="1">
         <v>0</v>
       </c>
       <c r="J210" s="9" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="K210" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L210" s="8" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A211" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="E211" s="1">
         <v>5</v>
@@ -11427,36 +11409,36 @@
         <v>5</v>
       </c>
       <c r="G211" s="7" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="I211" s="1">
         <v>0</v>
       </c>
       <c r="J211" s="9" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="K211" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L211" s="8" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A212" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="E212" s="1">
         <v>5</v>
@@ -11465,36 +11447,36 @@
         <v>5</v>
       </c>
       <c r="G212" s="7" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="I212" s="1">
         <v>0</v>
       </c>
       <c r="J212" s="9" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="K212" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L212" s="8" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A213" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="E213" s="1">
         <v>5</v>
@@ -11503,36 +11485,36 @@
         <v>5</v>
       </c>
       <c r="G213" s="7" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="I213" s="1">
         <v>0</v>
       </c>
       <c r="J213" s="9" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="K213" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L213" s="8" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A214" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="E214" s="1">
         <v>5</v>
@@ -11541,36 +11523,36 @@
         <v>5</v>
       </c>
       <c r="G214" s="7" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="I214" s="1">
         <v>0</v>
       </c>
       <c r="J214" s="9" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="K214" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L214" s="8" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A215" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1014</v>
+        <v>1045</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="E215" s="1">
         <v>5</v>
@@ -11579,22 +11561,22 @@
         <v>5</v>
       </c>
       <c r="G215" s="7" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="I215" s="1">
         <v>0</v>
       </c>
       <c r="J215" s="9" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="K215" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L215" s="8" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1201">
   <si>
     <t>_Id</t>
   </si>
@@ -3118,7 +3118,7 @@
     <t>202002,300091,105,504,210077,1009,505,202004</t>
   </si>
   <si>
-    <t>100,25000,10000,180000,1000000,140000,600000,20000</t>
+    <t>100,25000,10000,180000,1000000,140000,600000,1000000</t>
   </si>
   <si>
     <t>10175</t>
@@ -3194,9 +3194,6 @@
   </si>
   <si>
     <t>10179</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>1180</t>
@@ -4687,7 +4684,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M215"/>
+  <dimension ref="B3:M215"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
@@ -10439,1144 +10436,964 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="186" customHeight="1" spans="1:12">
-      <c r="A186" s="1" t="s">
+    <row r="186" customHeight="1" spans="3:12">
+      <c r="C186" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C186" s="1" t="s">
+      <c r="D186" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="D186" s="1" t="s">
+      <c r="E186" s="1">
+        <v>5</v>
+      </c>
+      <c r="F186" s="1">
+        <v>5</v>
+      </c>
+      <c r="G186" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="E186" s="1">
-        <v>5</v>
-      </c>
-      <c r="F186" s="1">
-        <v>5</v>
-      </c>
-      <c r="G186" s="1" t="s">
+      <c r="H186" s="1" t="s">
         <v>1048</v>
-      </c>
-      <c r="H186" s="1" t="s">
-        <v>1049</v>
       </c>
       <c r="I186" s="1">
         <v>0</v>
       </c>
       <c r="J186" s="9" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="K186" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L186" s="8" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="3:12">
+      <c r="C187" s="1" t="s">
         <v>1051</v>
       </c>
-    </row>
-    <row r="187" customHeight="1" spans="1:12">
-      <c r="A187" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C187" s="1" t="s">
+      <c r="D187" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="D187" s="1" t="s">
+      <c r="E187" s="1">
+        <v>5</v>
+      </c>
+      <c r="F187" s="1">
+        <v>5</v>
+      </c>
+      <c r="G187" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="E187" s="1">
-        <v>5</v>
-      </c>
-      <c r="F187" s="1">
-        <v>5</v>
-      </c>
-      <c r="G187" s="1" t="s">
+      <c r="H187" s="1" t="s">
         <v>1054</v>
-      </c>
-      <c r="H187" s="1" t="s">
-        <v>1055</v>
       </c>
       <c r="I187" s="1">
         <v>0</v>
       </c>
       <c r="J187" s="9" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="K187" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L187" s="8" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="3:12">
+      <c r="C188" s="1" t="s">
         <v>1056</v>
       </c>
-    </row>
-    <row r="188" customHeight="1" spans="1:12">
-      <c r="A188" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C188" s="1" t="s">
+      <c r="D188" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="D188" s="1" t="s">
+      <c r="E188" s="1">
+        <v>5</v>
+      </c>
+      <c r="F188" s="1">
+        <v>5</v>
+      </c>
+      <c r="G188" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="E188" s="1">
-        <v>5</v>
-      </c>
-      <c r="F188" s="1">
-        <v>5</v>
-      </c>
-      <c r="G188" s="1" t="s">
+      <c r="H188" s="1" t="s">
         <v>1059</v>
-      </c>
-      <c r="H188" s="1" t="s">
-        <v>1060</v>
       </c>
       <c r="I188" s="1">
         <v>0</v>
       </c>
       <c r="J188" s="9" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="K188" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L188" s="8" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="3:12">
+      <c r="C189" s="1" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="189" customHeight="1" spans="1:12">
-      <c r="A189" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C189" s="1" t="s">
+      <c r="D189" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="E189" s="1">
+        <v>5</v>
+      </c>
+      <c r="F189" s="1">
+        <v>5</v>
+      </c>
+      <c r="G189" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="E189" s="1">
-        <v>5</v>
-      </c>
-      <c r="F189" s="1">
-        <v>5</v>
-      </c>
-      <c r="G189" s="1" t="s">
+      <c r="H189" s="1" t="s">
         <v>1064</v>
-      </c>
-      <c r="H189" s="1" t="s">
-        <v>1065</v>
       </c>
       <c r="I189" s="1">
         <v>0</v>
       </c>
       <c r="J189" s="9" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="K189" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L189" s="8" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="3:12">
+      <c r="C190" s="1" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="190" customHeight="1" spans="1:12">
-      <c r="A190" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C190" s="1" t="s">
+      <c r="D190" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="D190" s="1" t="s">
+      <c r="E190" s="1">
+        <v>5</v>
+      </c>
+      <c r="F190" s="1">
+        <v>5</v>
+      </c>
+      <c r="G190" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="E190" s="1">
-        <v>5</v>
-      </c>
-      <c r="F190" s="1">
-        <v>5</v>
-      </c>
-      <c r="G190" s="1" t="s">
+      <c r="H190" s="1" t="s">
         <v>1069</v>
-      </c>
-      <c r="H190" s="1" t="s">
-        <v>1070</v>
       </c>
       <c r="I190" s="1">
         <v>0</v>
       </c>
       <c r="J190" s="9" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="K190" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L190" s="8" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="191" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C191" s="1" t="s">
         <v>1071</v>
       </c>
-    </row>
-    <row r="191" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A191" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C191" s="1" t="s">
+      <c r="D191" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="D191" s="1" t="s">
+      <c r="E191" s="1">
+        <v>5</v>
+      </c>
+      <c r="F191" s="1">
+        <v>5</v>
+      </c>
+      <c r="G191" s="7" t="s">
         <v>1073</v>
       </c>
-      <c r="E191" s="1">
-        <v>5</v>
-      </c>
-      <c r="F191" s="1">
-        <v>5</v>
-      </c>
-      <c r="G191" s="7" t="s">
+      <c r="H191" s="1" t="s">
         <v>1074</v>
-      </c>
-      <c r="H191" s="1" t="s">
-        <v>1075</v>
       </c>
       <c r="I191" s="1">
         <v>0</v>
       </c>
       <c r="J191" s="9" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="K191" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L191" s="8" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="192" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C192" s="1" t="s">
         <v>1077</v>
       </c>
-    </row>
-    <row r="192" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A192" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C192" s="1" t="s">
+      <c r="D192" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="E192" s="1">
+        <v>5</v>
+      </c>
+      <c r="F192" s="1">
+        <v>5</v>
+      </c>
+      <c r="G192" s="7" t="s">
         <v>1079</v>
       </c>
-      <c r="E192" s="1">
-        <v>5</v>
-      </c>
-      <c r="F192" s="1">
-        <v>5</v>
-      </c>
-      <c r="G192" s="7" t="s">
+      <c r="H192" s="1" t="s">
         <v>1080</v>
-      </c>
-      <c r="H192" s="1" t="s">
-        <v>1081</v>
       </c>
       <c r="I192" s="1">
         <v>0</v>
       </c>
       <c r="J192" s="9" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="K192" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L192" s="8" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="193" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C193" s="1" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="193" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A193" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C193" s="1" t="s">
+      <c r="D193" s="1" t="s">
         <v>1083</v>
       </c>
-      <c r="D193" s="1" t="s">
+      <c r="E193" s="1">
+        <v>5</v>
+      </c>
+      <c r="F193" s="1">
+        <v>5</v>
+      </c>
+      <c r="G193" s="7" t="s">
         <v>1084</v>
       </c>
-      <c r="E193" s="1">
-        <v>5</v>
-      </c>
-      <c r="F193" s="1">
-        <v>5</v>
-      </c>
-      <c r="G193" s="7" t="s">
+      <c r="H193" s="1" t="s">
         <v>1085</v>
-      </c>
-      <c r="H193" s="1" t="s">
-        <v>1086</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
       </c>
       <c r="J193" s="9" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="K193" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L193" s="8" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="194" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C194" s="1" t="s">
         <v>1087</v>
       </c>
-    </row>
-    <row r="194" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A194" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C194" s="1" t="s">
+      <c r="D194" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="E194" s="1">
+        <v>5</v>
+      </c>
+      <c r="F194" s="1">
+        <v>5</v>
+      </c>
+      <c r="G194" s="7" t="s">
         <v>1089</v>
       </c>
-      <c r="E194" s="1">
-        <v>5</v>
-      </c>
-      <c r="F194" s="1">
-        <v>5</v>
-      </c>
-      <c r="G194" s="7" t="s">
+      <c r="H194" s="1" t="s">
         <v>1090</v>
-      </c>
-      <c r="H194" s="1" t="s">
-        <v>1091</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
       </c>
       <c r="J194" s="9" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="K194" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L194" s="8" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="195" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C195" s="1" t="s">
         <v>1092</v>
       </c>
-    </row>
-    <row r="195" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A195" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C195" s="1" t="s">
+      <c r="D195" s="1" t="s">
         <v>1093</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="E195" s="1">
+        <v>5</v>
+      </c>
+      <c r="F195" s="1">
+        <v>5</v>
+      </c>
+      <c r="G195" s="7" t="s">
         <v>1094</v>
       </c>
-      <c r="E195" s="1">
-        <v>5</v>
-      </c>
-      <c r="F195" s="1">
-        <v>5</v>
-      </c>
-      <c r="G195" s="7" t="s">
+      <c r="H195" s="1" t="s">
         <v>1095</v>
-      </c>
-      <c r="H195" s="1" t="s">
-        <v>1096</v>
       </c>
       <c r="I195" s="1">
         <v>0</v>
       </c>
       <c r="J195" s="9" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="K195" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L195" s="8" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="196" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C196" s="1" t="s">
         <v>1097</v>
       </c>
-    </row>
-    <row r="196" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A196" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C196" s="1" t="s">
+      <c r="D196" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="D196" s="1" t="s">
+      <c r="E196" s="1">
+        <v>5</v>
+      </c>
+      <c r="F196" s="1">
+        <v>5</v>
+      </c>
+      <c r="G196" s="7" t="s">
         <v>1099</v>
       </c>
-      <c r="E196" s="1">
-        <v>5</v>
-      </c>
-      <c r="F196" s="1">
-        <v>5</v>
-      </c>
-      <c r="G196" s="7" t="s">
+      <c r="H196" s="1" t="s">
         <v>1100</v>
-      </c>
-      <c r="H196" s="1" t="s">
-        <v>1101</v>
       </c>
       <c r="I196" s="1">
         <v>0</v>
       </c>
       <c r="J196" s="9" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="K196" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L196" s="8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="197" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C197" s="1" t="s">
         <v>1103</v>
       </c>
-    </row>
-    <row r="197" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A197" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C197" s="1" t="s">
+      <c r="D197" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="D197" s="1" t="s">
+      <c r="E197" s="1">
+        <v>5</v>
+      </c>
+      <c r="F197" s="1">
+        <v>5</v>
+      </c>
+      <c r="G197" s="7" t="s">
         <v>1105</v>
       </c>
-      <c r="E197" s="1">
-        <v>5</v>
-      </c>
-      <c r="F197" s="1">
-        <v>5</v>
-      </c>
-      <c r="G197" s="7" t="s">
+      <c r="H197" s="1" t="s">
         <v>1106</v>
-      </c>
-      <c r="H197" s="1" t="s">
-        <v>1107</v>
       </c>
       <c r="I197" s="1">
         <v>0</v>
       </c>
       <c r="J197" s="9" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="K197" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L197" s="8" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="198" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C198" s="1" t="s">
         <v>1108</v>
       </c>
-    </row>
-    <row r="198" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A198" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C198" s="1" t="s">
+      <c r="D198" s="1" t="s">
         <v>1109</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="E198" s="1">
+        <v>5</v>
+      </c>
+      <c r="F198" s="1">
+        <v>5</v>
+      </c>
+      <c r="G198" s="7" t="s">
         <v>1110</v>
       </c>
-      <c r="E198" s="1">
-        <v>5</v>
-      </c>
-      <c r="F198" s="1">
-        <v>5</v>
-      </c>
-      <c r="G198" s="7" t="s">
+      <c r="H198" s="1" t="s">
         <v>1111</v>
-      </c>
-      <c r="H198" s="1" t="s">
-        <v>1112</v>
       </c>
       <c r="I198" s="1">
         <v>0</v>
       </c>
       <c r="J198" s="9" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="K198" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L198" s="8" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="199" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C199" s="1" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="199" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A199" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C199" s="1" t="s">
+      <c r="D199" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="E199" s="1">
+        <v>5</v>
+      </c>
+      <c r="F199" s="1">
+        <v>5</v>
+      </c>
+      <c r="G199" s="7" t="s">
         <v>1115</v>
       </c>
-      <c r="E199" s="1">
-        <v>5</v>
-      </c>
-      <c r="F199" s="1">
-        <v>5</v>
-      </c>
-      <c r="G199" s="7" t="s">
+      <c r="H199" s="1" t="s">
         <v>1116</v>
-      </c>
-      <c r="H199" s="1" t="s">
-        <v>1117</v>
       </c>
       <c r="I199" s="1">
         <v>0</v>
       </c>
       <c r="J199" s="9" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="K199" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L199" s="8" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="200" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C200" s="1" t="s">
         <v>1118</v>
       </c>
-    </row>
-    <row r="200" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A200" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C200" s="1" t="s">
+      <c r="D200" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="D200" s="1" t="s">
+      <c r="E200" s="1">
+        <v>5</v>
+      </c>
+      <c r="F200" s="1">
+        <v>5</v>
+      </c>
+      <c r="G200" s="7" t="s">
         <v>1120</v>
       </c>
-      <c r="E200" s="1">
-        <v>5</v>
-      </c>
-      <c r="F200" s="1">
-        <v>5</v>
-      </c>
-      <c r="G200" s="7" t="s">
+      <c r="H200" s="1" t="s">
         <v>1121</v>
-      </c>
-      <c r="H200" s="1" t="s">
-        <v>1122</v>
       </c>
       <c r="I200" s="1">
         <v>0</v>
       </c>
       <c r="J200" s="9" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="K200" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L200" s="8" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" spans="3:12">
+      <c r="C201" s="1" t="s">
         <v>1123</v>
       </c>
-    </row>
-    <row r="201" customHeight="1" spans="1:12">
-      <c r="A201" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C201" s="1" t="s">
+      <c r="D201" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="D201" s="2" t="s">
+      <c r="E201" s="1">
+        <v>5</v>
+      </c>
+      <c r="F201" s="1">
+        <v>5</v>
+      </c>
+      <c r="G201" s="7" t="s">
         <v>1125</v>
       </c>
-      <c r="E201" s="1">
-        <v>5</v>
-      </c>
-      <c r="F201" s="1">
-        <v>5</v>
-      </c>
-      <c r="G201" s="7" t="s">
+      <c r="H201" s="1" t="s">
         <v>1126</v>
-      </c>
-      <c r="H201" s="1" t="s">
-        <v>1127</v>
       </c>
       <c r="I201" s="1">
         <v>0</v>
       </c>
       <c r="J201" s="9" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="K201" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L201" s="8" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" spans="3:12">
+      <c r="C202" s="1" t="s">
         <v>1129</v>
       </c>
-    </row>
-    <row r="202" customHeight="1" spans="1:12">
-      <c r="A202" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C202" s="1" t="s">
+      <c r="D202" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="D202" s="2" t="s">
+      <c r="E202" s="1">
+        <v>5</v>
+      </c>
+      <c r="F202" s="1">
+        <v>5</v>
+      </c>
+      <c r="G202" s="7" t="s">
         <v>1131</v>
       </c>
-      <c r="E202" s="1">
-        <v>5</v>
-      </c>
-      <c r="F202" s="1">
-        <v>5</v>
-      </c>
-      <c r="G202" s="7" t="s">
+      <c r="H202" s="1" t="s">
         <v>1132</v>
-      </c>
-      <c r="H202" s="1" t="s">
-        <v>1133</v>
       </c>
       <c r="I202" s="1">
         <v>0</v>
       </c>
       <c r="J202" s="9" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="K202" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L202" s="8" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="3:12">
+      <c r="C203" s="1" t="s">
         <v>1134</v>
       </c>
-    </row>
-    <row r="203" customHeight="1" spans="1:12">
-      <c r="A203" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C203" s="1" t="s">
+      <c r="D203" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="D203" s="2" t="s">
+      <c r="E203" s="1">
+        <v>5</v>
+      </c>
+      <c r="F203" s="1">
+        <v>5</v>
+      </c>
+      <c r="G203" s="7" t="s">
         <v>1136</v>
       </c>
-      <c r="E203" s="1">
-        <v>5</v>
-      </c>
-      <c r="F203" s="1">
-        <v>5</v>
-      </c>
-      <c r="G203" s="7" t="s">
+      <c r="H203" s="1" t="s">
         <v>1137</v>
-      </c>
-      <c r="H203" s="1" t="s">
-        <v>1138</v>
       </c>
       <c r="I203" s="1">
         <v>0</v>
       </c>
       <c r="J203" s="9" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="K203" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L203" s="8" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="3:12">
+      <c r="C204" s="1" t="s">
         <v>1139</v>
       </c>
-    </row>
-    <row r="204" customHeight="1" spans="1:12">
-      <c r="A204" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C204" s="1" t="s">
+      <c r="D204" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="D204" s="2" t="s">
+      <c r="E204" s="1">
+        <v>5</v>
+      </c>
+      <c r="F204" s="1">
+        <v>5</v>
+      </c>
+      <c r="G204" s="7" t="s">
         <v>1141</v>
       </c>
-      <c r="E204" s="1">
-        <v>5</v>
-      </c>
-      <c r="F204" s="1">
-        <v>5</v>
-      </c>
-      <c r="G204" s="7" t="s">
+      <c r="H204" s="1" t="s">
         <v>1142</v>
-      </c>
-      <c r="H204" s="1" t="s">
-        <v>1143</v>
       </c>
       <c r="I204" s="1">
         <v>0</v>
       </c>
       <c r="J204" s="9" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="K204" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L204" s="8" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="3:12">
+      <c r="C205" s="1" t="s">
         <v>1144</v>
       </c>
-    </row>
-    <row r="205" customHeight="1" spans="1:12">
-      <c r="A205" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C205" s="1" t="s">
+      <c r="D205" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="D205" s="2" t="s">
+      <c r="E205" s="1">
+        <v>5</v>
+      </c>
+      <c r="F205" s="1">
+        <v>5</v>
+      </c>
+      <c r="G205" s="7" t="s">
         <v>1146</v>
       </c>
-      <c r="E205" s="1">
-        <v>5</v>
-      </c>
-      <c r="F205" s="1">
-        <v>5</v>
-      </c>
-      <c r="G205" s="7" t="s">
+      <c r="H205" s="1" t="s">
         <v>1147</v>
-      </c>
-      <c r="H205" s="1" t="s">
-        <v>1148</v>
       </c>
       <c r="I205" s="1">
         <v>0</v>
       </c>
       <c r="J205" s="9" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="K205" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L205" s="8" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" spans="3:12">
+      <c r="C206" s="1" t="s">
         <v>1149</v>
       </c>
-    </row>
-    <row r="206" customHeight="1" spans="1:12">
-      <c r="A206" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C206" s="1" t="s">
+      <c r="D206" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="D206" s="1" t="s">
+      <c r="E206" s="1">
+        <v>5</v>
+      </c>
+      <c r="F206" s="1">
+        <v>5</v>
+      </c>
+      <c r="G206" s="7" t="s">
         <v>1151</v>
       </c>
-      <c r="E206" s="1">
-        <v>5</v>
-      </c>
-      <c r="F206" s="1">
-        <v>5</v>
-      </c>
-      <c r="G206" s="7" t="s">
+      <c r="H206" s="1" t="s">
         <v>1152</v>
-      </c>
-      <c r="H206" s="1" t="s">
-        <v>1153</v>
       </c>
       <c r="I206" s="1">
         <v>0</v>
       </c>
       <c r="J206" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K206" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L206" s="8" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="3:12">
+      <c r="C207" s="1" t="s">
         <v>1155</v>
       </c>
-    </row>
-    <row r="207" customHeight="1" spans="1:12">
-      <c r="A207" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C207" s="1" t="s">
+      <c r="D207" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="D207" s="1" t="s">
+      <c r="E207" s="1">
+        <v>5</v>
+      </c>
+      <c r="F207" s="1">
+        <v>5</v>
+      </c>
+      <c r="G207" s="7" t="s">
         <v>1157</v>
       </c>
-      <c r="E207" s="1">
-        <v>5</v>
-      </c>
-      <c r="F207" s="1">
-        <v>5</v>
-      </c>
-      <c r="G207" s="7" t="s">
+      <c r="H207" s="1" t="s">
         <v>1158</v>
-      </c>
-      <c r="H207" s="1" t="s">
-        <v>1159</v>
       </c>
       <c r="I207" s="1">
         <v>0</v>
       </c>
       <c r="J207" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K207" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L207" s="8" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" spans="3:12">
+      <c r="C208" s="1" t="s">
         <v>1160</v>
       </c>
-    </row>
-    <row r="208" customHeight="1" spans="1:12">
-      <c r="A208" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C208" s="1" t="s">
+      <c r="D208" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="E208" s="1">
+        <v>5</v>
+      </c>
+      <c r="F208" s="1">
+        <v>5</v>
+      </c>
+      <c r="G208" s="7" t="s">
         <v>1162</v>
       </c>
-      <c r="E208" s="1">
-        <v>5</v>
-      </c>
-      <c r="F208" s="1">
-        <v>5</v>
-      </c>
-      <c r="G208" s="7" t="s">
+      <c r="H208" s="1" t="s">
         <v>1163</v>
-      </c>
-      <c r="H208" s="1" t="s">
-        <v>1164</v>
       </c>
       <c r="I208" s="1">
         <v>0</v>
       </c>
       <c r="J208" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K208" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L208" s="8" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" spans="3:12">
+      <c r="C209" s="1" t="s">
         <v>1165</v>
       </c>
-    </row>
-    <row r="209" customHeight="1" spans="1:12">
-      <c r="A209" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C209" s="1" t="s">
+      <c r="D209" s="1" t="s">
         <v>1166</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="E209" s="1">
+        <v>5</v>
+      </c>
+      <c r="F209" s="1">
+        <v>5</v>
+      </c>
+      <c r="G209" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="E209" s="1">
-        <v>5</v>
-      </c>
-      <c r="F209" s="1">
-        <v>5</v>
-      </c>
-      <c r="G209" s="7" t="s">
+      <c r="H209" s="1" t="s">
         <v>1168</v>
-      </c>
-      <c r="H209" s="1" t="s">
-        <v>1169</v>
       </c>
       <c r="I209" s="1">
         <v>0</v>
       </c>
       <c r="J209" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K209" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L209" s="8" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" spans="3:12">
+      <c r="C210" s="1" t="s">
         <v>1170</v>
       </c>
-    </row>
-    <row r="210" customHeight="1" spans="1:12">
-      <c r="A210" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C210" s="1" t="s">
+      <c r="D210" s="1" t="s">
         <v>1171</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="E210" s="1">
+        <v>5</v>
+      </c>
+      <c r="F210" s="1">
+        <v>5</v>
+      </c>
+      <c r="G210" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="E210" s="1">
-        <v>5</v>
-      </c>
-      <c r="F210" s="1">
-        <v>5</v>
-      </c>
-      <c r="G210" s="7" t="s">
+      <c r="H210" s="1" t="s">
         <v>1173</v>
-      </c>
-      <c r="H210" s="1" t="s">
-        <v>1174</v>
       </c>
       <c r="I210" s="1">
         <v>0</v>
       </c>
       <c r="J210" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K210" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L210" s="8" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="211" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C211" s="1" t="s">
         <v>1175</v>
       </c>
-    </row>
-    <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A211" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C211" s="1" t="s">
+      <c r="D211" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="E211" s="1">
+        <v>5</v>
+      </c>
+      <c r="F211" s="1">
+        <v>5</v>
+      </c>
+      <c r="G211" s="7" t="s">
         <v>1177</v>
       </c>
-      <c r="E211" s="1">
-        <v>5</v>
-      </c>
-      <c r="F211" s="1">
-        <v>5</v>
-      </c>
-      <c r="G211" s="7" t="s">
+      <c r="H211" s="1" t="s">
         <v>1178</v>
-      </c>
-      <c r="H211" s="1" t="s">
-        <v>1179</v>
       </c>
       <c r="I211" s="1">
         <v>0</v>
       </c>
       <c r="J211" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="K211" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L211" s="8" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C212" s="1" t="s">
         <v>1181</v>
       </c>
-    </row>
-    <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A212" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C212" s="1" t="s">
+      <c r="D212" s="1" t="s">
         <v>1182</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="E212" s="1">
+        <v>5</v>
+      </c>
+      <c r="F212" s="1">
+        <v>5</v>
+      </c>
+      <c r="G212" s="7" t="s">
         <v>1183</v>
       </c>
-      <c r="E212" s="1">
-        <v>5</v>
-      </c>
-      <c r="F212" s="1">
-        <v>5</v>
-      </c>
-      <c r="G212" s="7" t="s">
+      <c r="H212" s="1" t="s">
         <v>1184</v>
-      </c>
-      <c r="H212" s="1" t="s">
-        <v>1185</v>
       </c>
       <c r="I212" s="1">
         <v>0</v>
       </c>
       <c r="J212" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="K212" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L212" s="8" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="213" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C213" s="1" t="s">
         <v>1186</v>
       </c>
-    </row>
-    <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A213" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C213" s="1" t="s">
+      <c r="D213" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="E213" s="1">
+        <v>5</v>
+      </c>
+      <c r="F213" s="1">
+        <v>5</v>
+      </c>
+      <c r="G213" s="7" t="s">
         <v>1188</v>
       </c>
-      <c r="E213" s="1">
-        <v>5</v>
-      </c>
-      <c r="F213" s="1">
-        <v>5</v>
-      </c>
-      <c r="G213" s="7" t="s">
+      <c r="H213" s="1" t="s">
         <v>1189</v>
-      </c>
-      <c r="H213" s="1" t="s">
-        <v>1190</v>
       </c>
       <c r="I213" s="1">
         <v>0</v>
       </c>
       <c r="J213" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="K213" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L213" s="8" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="214" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C214" s="1" t="s">
         <v>1191</v>
       </c>
-    </row>
-    <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A214" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C214" s="1" t="s">
+      <c r="D214" s="1" t="s">
         <v>1192</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="E214" s="1">
+        <v>5</v>
+      </c>
+      <c r="F214" s="1">
+        <v>5</v>
+      </c>
+      <c r="G214" s="7" t="s">
         <v>1193</v>
       </c>
-      <c r="E214" s="1">
-        <v>5</v>
-      </c>
-      <c r="F214" s="1">
-        <v>5</v>
-      </c>
-      <c r="G214" s="7" t="s">
+      <c r="H214" s="1" t="s">
         <v>1194</v>
-      </c>
-      <c r="H214" s="1" t="s">
-        <v>1195</v>
       </c>
       <c r="I214" s="1">
         <v>0</v>
       </c>
       <c r="J214" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="K214" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L214" s="8" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="215" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C215" s="1" t="s">
         <v>1196</v>
       </c>
-    </row>
-    <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A215" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C215" s="1" t="s">
+      <c r="D215" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="E215" s="1">
+        <v>5</v>
+      </c>
+      <c r="F215" s="1">
+        <v>5</v>
+      </c>
+      <c r="G215" s="7" t="s">
         <v>1198</v>
       </c>
-      <c r="E215" s="1">
-        <v>5</v>
-      </c>
-      <c r="F215" s="1">
-        <v>5</v>
-      </c>
-      <c r="G215" s="7" t="s">
+      <c r="H215" s="1" t="s">
         <v>1199</v>
-      </c>
-      <c r="H215" s="1" t="s">
-        <v>1200</v>
       </c>
       <c r="I215" s="1">
         <v>0</v>
       </c>
       <c r="J215" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="K215" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L215" s="8" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1202">
   <si>
     <t>_Id</t>
   </si>
@@ -3194,6 +3194,9 @@
   </si>
   <si>
     <t>10179</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>1180</t>
@@ -4684,7 +4687,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:M215"/>
+  <dimension ref="A3:M215"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
@@ -10436,12 +10439,18 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="186" customHeight="1" spans="3:12">
+    <row r="186" customHeight="1" spans="1:12">
+      <c r="A186" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C186" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="E186" s="1">
         <v>5</v>
@@ -10450,30 +10459,36 @@
         <v>5</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="I186" s="1">
         <v>0</v>
       </c>
       <c r="J186" s="9" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="K186" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L186" s="8" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="187" customHeight="1" spans="3:12">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="1:12">
+      <c r="A187" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C187" s="1" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="E187" s="1">
         <v>5</v>
@@ -10482,30 +10497,36 @@
         <v>5</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="I187" s="1">
         <v>0</v>
       </c>
       <c r="J187" s="9" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="K187" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L187" s="8" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="188" customHeight="1" spans="3:12">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="1:12">
+      <c r="A188" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C188" s="1" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E188" s="1">
         <v>5</v>
@@ -10514,30 +10535,36 @@
         <v>5</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="I188" s="1">
         <v>0</v>
       </c>
       <c r="J188" s="9" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="K188" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L188" s="8" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="189" customHeight="1" spans="3:12">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="1:12">
+      <c r="A189" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C189" s="1" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="E189" s="1">
         <v>5</v>
@@ -10546,30 +10573,36 @@
         <v>5</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="I189" s="1">
         <v>0</v>
       </c>
       <c r="J189" s="9" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="K189" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L189" s="8" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="190" customHeight="1" spans="3:12">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="1:12">
+      <c r="A190" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C190" s="1" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="E190" s="1">
         <v>5</v>
@@ -10578,30 +10611,36 @@
         <v>5</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="I190" s="1">
         <v>0</v>
       </c>
       <c r="J190" s="9" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="K190" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L190" s="8" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="191" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="191" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A191" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C191" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E191" s="1">
         <v>5</v>
@@ -10610,30 +10649,36 @@
         <v>5</v>
       </c>
       <c r="G191" s="7" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="I191" s="1">
         <v>0</v>
       </c>
       <c r="J191" s="9" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="K191" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L191" s="8" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="192" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="192" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A192" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C192" s="1" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="E192" s="1">
         <v>5</v>
@@ -10642,30 +10687,36 @@
         <v>5</v>
       </c>
       <c r="G192" s="7" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="I192" s="1">
         <v>0</v>
       </c>
       <c r="J192" s="9" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="K192" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L192" s="8" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="193" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="193" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A193" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C193" s="1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="E193" s="1">
         <v>5</v>
@@ -10674,30 +10725,36 @@
         <v>5</v>
       </c>
       <c r="G193" s="7" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
       </c>
       <c r="J193" s="9" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="K193" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L193" s="8" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="194" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="194" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A194" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C194" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E194" s="1">
         <v>5</v>
@@ -10706,30 +10763,36 @@
         <v>5</v>
       </c>
       <c r="G194" s="7" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
       </c>
       <c r="J194" s="9" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="K194" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L194" s="8" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="195" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="195" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A195" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C195" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E195" s="1">
         <v>5</v>
@@ -10738,30 +10801,36 @@
         <v>5</v>
       </c>
       <c r="G195" s="7" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="I195" s="1">
         <v>0</v>
       </c>
       <c r="J195" s="9" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="K195" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L195" s="8" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="196" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="196" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A196" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C196" s="1" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="E196" s="1">
         <v>5</v>
@@ -10770,30 +10839,36 @@
         <v>5</v>
       </c>
       <c r="G196" s="7" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="I196" s="1">
         <v>0</v>
       </c>
       <c r="J196" s="9" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="K196" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L196" s="8" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="197" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="197" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A197" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C197" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="E197" s="1">
         <v>5</v>
@@ -10802,30 +10877,36 @@
         <v>5</v>
       </c>
       <c r="G197" s="7" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="I197" s="1">
         <v>0</v>
       </c>
       <c r="J197" s="9" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="K197" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L197" s="8" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="198" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="198" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A198" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C198" s="1" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E198" s="1">
         <v>5</v>
@@ -10834,30 +10915,36 @@
         <v>5</v>
       </c>
       <c r="G198" s="7" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="I198" s="1">
         <v>0</v>
       </c>
       <c r="J198" s="9" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="K198" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L198" s="8" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="199" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="199" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A199" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C199" s="1" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="E199" s="1">
         <v>5</v>
@@ -10866,30 +10953,36 @@
         <v>5</v>
       </c>
       <c r="G199" s="7" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="I199" s="1">
         <v>0</v>
       </c>
       <c r="J199" s="9" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="K199" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L199" s="8" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="200" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="200" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A200" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C200" s="1" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E200" s="1">
         <v>5</v>
@@ -10898,30 +10991,36 @@
         <v>5</v>
       </c>
       <c r="G200" s="7" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="I200" s="1">
         <v>0</v>
       </c>
       <c r="J200" s="9" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="K200" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L200" s="8" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="201" customHeight="1" spans="3:12">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="201" customHeight="1" spans="1:12">
+      <c r="A201" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C201" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="E201" s="1">
         <v>5</v>
@@ -10930,30 +11029,36 @@
         <v>5</v>
       </c>
       <c r="G201" s="7" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="I201" s="1">
         <v>0</v>
       </c>
       <c r="J201" s="9" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="K201" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L201" s="8" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="202" customHeight="1" spans="3:12">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" spans="1:12">
+      <c r="A202" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C202" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="E202" s="1">
         <v>5</v>
@@ -10962,30 +11067,36 @@
         <v>5</v>
       </c>
       <c r="G202" s="7" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="I202" s="1">
         <v>0</v>
       </c>
       <c r="J202" s="9" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="K202" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L202" s="8" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="203" customHeight="1" spans="3:12">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="1:12">
+      <c r="A203" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C203" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="E203" s="1">
         <v>5</v>
@@ -10994,30 +11105,36 @@
         <v>5</v>
       </c>
       <c r="G203" s="7" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="I203" s="1">
         <v>0</v>
       </c>
       <c r="J203" s="9" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="K203" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L203" s="8" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="204" customHeight="1" spans="3:12">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="1:12">
+      <c r="A204" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C204" s="1" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E204" s="1">
         <v>5</v>
@@ -11026,30 +11143,36 @@
         <v>5</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="I204" s="1">
         <v>0</v>
       </c>
       <c r="J204" s="9" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="K204" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L204" s="8" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="205" customHeight="1" spans="3:12">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="1:12">
+      <c r="A205" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C205" s="1" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="E205" s="1">
         <v>5</v>
@@ -11058,30 +11181,36 @@
         <v>5</v>
       </c>
       <c r="G205" s="7" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="I205" s="1">
         <v>0</v>
       </c>
       <c r="J205" s="9" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="K205" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L205" s="8" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="206" customHeight="1" spans="3:12">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="206" customHeight="1" spans="1:12">
+      <c r="A206" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C206" s="1" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="E206" s="1">
         <v>5</v>
@@ -11090,30 +11219,36 @@
         <v>5</v>
       </c>
       <c r="G206" s="7" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="I206" s="1">
         <v>0</v>
       </c>
       <c r="J206" s="9" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="K206" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L206" s="8" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="207" customHeight="1" spans="3:12">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="1:12">
+      <c r="A207" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C207" s="1" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E207" s="1">
         <v>5</v>
@@ -11122,30 +11257,36 @@
         <v>5</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="I207" s="1">
         <v>0</v>
       </c>
       <c r="J207" s="9" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="K207" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L207" s="8" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="208" customHeight="1" spans="3:12">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" spans="1:12">
+      <c r="A208" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C208" s="1" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E208" s="1">
         <v>5</v>
@@ -11154,30 +11295,36 @@
         <v>5</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="I208" s="1">
         <v>0</v>
       </c>
       <c r="J208" s="9" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="K208" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L208" s="8" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="209" customHeight="1" spans="3:12">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" spans="1:12">
+      <c r="A209" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C209" s="1" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="E209" s="1">
         <v>5</v>
@@ -11186,30 +11333,36 @@
         <v>5</v>
       </c>
       <c r="G209" s="7" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="I209" s="1">
         <v>0</v>
       </c>
       <c r="J209" s="9" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="K209" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L209" s="8" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="210" customHeight="1" spans="3:12">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" spans="1:12">
+      <c r="A210" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C210" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E210" s="1">
         <v>5</v>
@@ -11218,30 +11371,36 @@
         <v>5</v>
       </c>
       <c r="G210" s="7" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="I210" s="1">
         <v>0</v>
       </c>
       <c r="J210" s="9" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="K210" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L210" s="8" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="211" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A211" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C211" s="1" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="E211" s="1">
         <v>5</v>
@@ -11250,30 +11409,36 @@
         <v>5</v>
       </c>
       <c r="G211" s="7" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="I211" s="1">
         <v>0</v>
       </c>
       <c r="J211" s="9" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="K211" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L211" s="8" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="212" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A212" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C212" s="1" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E212" s="1">
         <v>5</v>
@@ -11282,30 +11447,36 @@
         <v>5</v>
       </c>
       <c r="G212" s="7" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="I212" s="1">
         <v>0</v>
       </c>
       <c r="J212" s="9" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="K212" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L212" s="8" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="213" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A213" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C213" s="1" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E213" s="1">
         <v>5</v>
@@ -11314,30 +11485,36 @@
         <v>5</v>
       </c>
       <c r="G213" s="7" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="I213" s="1">
         <v>0</v>
       </c>
       <c r="J213" s="9" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="K213" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L213" s="8" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="214" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A214" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C214" s="1" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="E214" s="1">
         <v>5</v>
@@ -11346,30 +11523,36 @@
         <v>5</v>
       </c>
       <c r="G214" s="7" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="I214" s="1">
         <v>0</v>
       </c>
       <c r="J214" s="9" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="K214" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L214" s="8" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="215" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A215" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>1045</v>
+      </c>
       <c r="C215" s="1" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E215" s="1">
         <v>5</v>
@@ -11378,22 +11561,22 @@
         <v>5</v>
       </c>
       <c r="G215" s="7" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="I215" s="1">
         <v>0</v>
       </c>
       <c r="J215" s="9" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="K215" s="9" t="s">
         <v>1019</v>
       </c>
       <c r="L215" s="8" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -3118,7 +3118,7 @@
     <t>202002,300091,105,504,210077,1009,505,202004</t>
   </si>
   <si>
-    <t>100,25000,10000,180000,1000000,140000,600000,1000000</t>
+    <t>10,25000,10000,180000,1000000,140000,400000,400000</t>
   </si>
   <si>
     <t>10175</t>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -1936,7 +1936,7 @@
     <t>202001,300091,104,504,210035,1009</t>
   </si>
   <si>
-    <t>10,2500,1000,18000,600000,140000</t>
+    <t>10,2500,1000,18000,450000,140000</t>
   </si>
   <si>
     <t>10105</t>
@@ -2389,7 +2389,7 @@
     <t>202001,300091,104,504,210060,1009,505</t>
   </si>
   <si>
-    <t>10,2500,1000,18000,600000,140000,600000</t>
+    <t>10,2500,1000,18000,450000,140000,600000</t>
   </si>
   <si>
     <t>10130</t>
@@ -3118,7 +3118,7 @@
     <t>202002,300091,105,504,210077,1009,505,202004</t>
   </si>
   <si>
-    <t>10,25000,10000,180000,1000000,140000,400000,400000</t>
+    <t>10,9500,9000,98000,600000,140000,600000,600000</t>
   </si>
   <si>
     <t>10175</t>
@@ -3843,12 +3843,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1203">
   <si>
     <t>_Id</t>
   </si>
@@ -3037,7 +3037,10 @@
     <t>深渊战锤</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210076,1009,505</t>
+    <t>202002,300091,105,504,210076,1009,505,506</t>
+  </si>
+  <si>
+    <t>10,2500,1000,18000,450000,140000,600000,600000</t>
   </si>
   <si>
     <t>10170</t>
@@ -3115,10 +3118,10 @@
     <t>混沌装备</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210077,1009,505,202004</t>
-  </si>
-  <si>
-    <t>10,9500,9000,98000,600000,140000,600000,600000</t>
+    <t>202002,300091,105,504,210077,1009,505,506,202004</t>
+  </si>
+  <si>
+    <t>10,9500,9000,98000,600000,140000,600000,600000,600000</t>
   </si>
   <si>
     <t>10175</t>
@@ -3136,7 +3139,7 @@
     <t>混沌鹿茸</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210077,1009,505,202005</t>
+    <t>202002,300091,105,504,210077,1009,505,506,202005</t>
   </si>
   <si>
     <t>10176</t>
@@ -3154,7 +3157,7 @@
     <t>混沌草帽</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210077,1009,505,202006</t>
+    <t>202002,300091,105,504,210077,1009,505,506,202006</t>
   </si>
   <si>
     <t>10177</t>
@@ -3172,7 +3175,7 @@
     <t>混沌猫爪</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210077,1009,505,202007</t>
+    <t>202002,300091,105,504,210077,1009,505,506,202007</t>
   </si>
   <si>
     <t>10178</t>
@@ -3190,7 +3193,7 @@
     <t>混沌花朵</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210077,1009,505,202003</t>
+    <t>202002,300091,105,504,210077,1009,505,506,202003</t>
   </si>
   <si>
     <t>10179</t>
@@ -3211,7 +3214,7 @@
     <t>混沌冰晶</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210078,1009,505,202003</t>
+    <t>202002,300091,105,504,210078,1009,505,506,202003</t>
   </si>
   <si>
     <t>10180</t>
@@ -3289,7 +3292,7 @@
     <t>混沌狼爪</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210079,1009,505,202003</t>
+    <t>202002,300091,105,504,210079,1009,505,506,202003</t>
   </si>
   <si>
     <t>10185</t>
@@ -3367,7 +3370,7 @@
     <t>混沌虫心</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210080,1009,505,202003</t>
+    <t>202002,300091,105,504,210080,1009,505,506,202003</t>
   </si>
   <si>
     <t>10190</t>
@@ -3445,7 +3448,7 @@
     <t>混沌宝甲</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210081,1009,505,202003</t>
+    <t>202002,300091,105,504,210081,1009,505,506,202003</t>
   </si>
   <si>
     <t>10195</t>
@@ -3523,7 +3526,7 @@
     <t>混沌树心</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210082,1009,505,202003</t>
+    <t>202002,300091,105,504,210082,1009,505,506,202003</t>
   </si>
   <si>
     <t>10200</t>
@@ -3601,7 +3604,7 @@
     <t>混沌战锤</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210083,1009,505,202003</t>
+    <t>202002,300091,105,504,210083,1009,505,506,202003</t>
   </si>
   <si>
     <t>10205</t>
@@ -3843,12 +3846,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -10145,18 +10148,18 @@
         <v>992</v>
       </c>
       <c r="K176" s="9" t="s">
-        <v>776</v>
+        <v>993</v>
       </c>
       <c r="L176" s="8" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C177" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
@@ -10165,10 +10168,10 @@
         <v>5</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="I177" s="1">
         <v>0</v>
@@ -10177,18 +10180,18 @@
         <v>992</v>
       </c>
       <c r="K177" s="9" t="s">
-        <v>776</v>
+        <v>993</v>
       </c>
       <c r="L177" s="8" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C178" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
@@ -10197,10 +10200,10 @@
         <v>5</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
@@ -10209,18 +10212,18 @@
         <v>992</v>
       </c>
       <c r="K178" s="9" t="s">
-        <v>776</v>
+        <v>993</v>
       </c>
       <c r="L178" s="8" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C179" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -10229,10 +10232,10 @@
         <v>5</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
@@ -10241,18 +10244,18 @@
         <v>992</v>
       </c>
       <c r="K179" s="9" t="s">
-        <v>776</v>
+        <v>993</v>
       </c>
       <c r="L179" s="8" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C180" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
@@ -10261,10 +10264,10 @@
         <v>5</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
@@ -10273,18 +10276,18 @@
         <v>992</v>
       </c>
       <c r="K180" s="9" t="s">
-        <v>776</v>
+        <v>993</v>
       </c>
       <c r="L180" s="8" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="181" s="3" customFormat="1" customHeight="1" spans="3:12">
       <c r="C181" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E181" s="3">
         <v>5</v>
@@ -10293,30 +10296,30 @@
         <v>5</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="I181" s="3">
         <v>0</v>
       </c>
       <c r="J181" s="10" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="K181" s="10" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L181" s="8" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="182" customHeight="1" spans="3:12">
       <c r="C182" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="E182" s="1">
         <v>5</v>
@@ -10325,30 +10328,30 @@
         <v>5</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="I182" s="1">
         <v>0</v>
       </c>
       <c r="J182" s="9" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="K182" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L182" s="8" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="183" customHeight="1" spans="3:12">
       <c r="C183" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="E183" s="1">
         <v>5</v>
@@ -10357,30 +10360,30 @@
         <v>5</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="I183" s="1">
         <v>0</v>
       </c>
       <c r="J183" s="9" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="K183" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L183" s="8" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="184" customHeight="1" spans="3:12">
       <c r="C184" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="E184" s="1">
         <v>5</v>
@@ -10389,30 +10392,30 @@
         <v>5</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="I184" s="1">
         <v>0</v>
       </c>
       <c r="J184" s="9" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="K184" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L184" s="8" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="185" customHeight="1" spans="3:12">
       <c r="C185" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E185" s="1">
         <v>5</v>
@@ -10421,36 +10424,36 @@
         <v>5</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="I185" s="1">
         <v>0</v>
       </c>
       <c r="J185" s="9" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="K185" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L185" s="8" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="186" customHeight="1" spans="1:12">
       <c r="A186" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E186" s="1">
         <v>5</v>
@@ -10459,36 +10462,36 @@
         <v>5</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="I186" s="1">
         <v>0</v>
       </c>
       <c r="J186" s="9" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="K186" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L186" s="8" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="187" customHeight="1" spans="1:12">
       <c r="A187" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="E187" s="1">
         <v>5</v>
@@ -10497,36 +10500,36 @@
         <v>5</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="I187" s="1">
         <v>0</v>
       </c>
       <c r="J187" s="9" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="K187" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L187" s="8" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="188" customHeight="1" spans="1:12">
       <c r="A188" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="E188" s="1">
         <v>5</v>
@@ -10535,36 +10538,36 @@
         <v>5</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="I188" s="1">
         <v>0</v>
       </c>
       <c r="J188" s="9" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="K188" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L188" s="8" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="189" customHeight="1" spans="1:12">
       <c r="A189" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E189" s="1">
         <v>5</v>
@@ -10573,36 +10576,36 @@
         <v>5</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="I189" s="1">
         <v>0</v>
       </c>
       <c r="J189" s="9" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="K189" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L189" s="8" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="190" customHeight="1" spans="1:12">
       <c r="A190" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="E190" s="1">
         <v>5</v>
@@ -10611,36 +10614,36 @@
         <v>5</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="I190" s="1">
         <v>0</v>
       </c>
       <c r="J190" s="9" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="K190" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L190" s="8" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="191" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A191" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="E191" s="1">
         <v>5</v>
@@ -10649,36 +10652,36 @@
         <v>5</v>
       </c>
       <c r="G191" s="7" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="I191" s="1">
         <v>0</v>
       </c>
       <c r="J191" s="9" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="K191" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L191" s="8" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="192" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A192" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="E192" s="1">
         <v>5</v>
@@ -10687,36 +10690,36 @@
         <v>5</v>
       </c>
       <c r="G192" s="7" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="I192" s="1">
         <v>0</v>
       </c>
       <c r="J192" s="9" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="K192" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L192" s="8" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="193" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A193" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E193" s="1">
         <v>5</v>
@@ -10725,36 +10728,36 @@
         <v>5</v>
       </c>
       <c r="G193" s="7" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
       </c>
       <c r="J193" s="9" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="K193" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L193" s="8" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="194" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A194" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E194" s="1">
         <v>5</v>
@@ -10763,36 +10766,36 @@
         <v>5</v>
       </c>
       <c r="G194" s="7" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
       </c>
       <c r="J194" s="9" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="K194" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L194" s="8" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="195" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A195" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E195" s="1">
         <v>5</v>
@@ -10801,36 +10804,36 @@
         <v>5</v>
       </c>
       <c r="G195" s="7" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="I195" s="1">
         <v>0</v>
       </c>
       <c r="J195" s="9" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="K195" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L195" s="8" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="196" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A196" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="E196" s="1">
         <v>5</v>
@@ -10839,36 +10842,36 @@
         <v>5</v>
       </c>
       <c r="G196" s="7" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="I196" s="1">
         <v>0</v>
       </c>
       <c r="J196" s="9" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K196" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L196" s="8" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="197" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A197" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="E197" s="1">
         <v>5</v>
@@ -10877,36 +10880,36 @@
         <v>5</v>
       </c>
       <c r="G197" s="7" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="I197" s="1">
         <v>0</v>
       </c>
       <c r="J197" s="9" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K197" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L197" s="8" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="198" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A198" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="E198" s="1">
         <v>5</v>
@@ -10915,36 +10918,36 @@
         <v>5</v>
       </c>
       <c r="G198" s="7" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="I198" s="1">
         <v>0</v>
       </c>
       <c r="J198" s="9" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K198" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L198" s="8" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="199" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A199" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E199" s="1">
         <v>5</v>
@@ -10953,36 +10956,36 @@
         <v>5</v>
       </c>
       <c r="G199" s="7" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="I199" s="1">
         <v>0</v>
       </c>
       <c r="J199" s="9" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K199" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L199" s="8" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="200" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A200" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="E200" s="1">
         <v>5</v>
@@ -10991,36 +10994,36 @@
         <v>5</v>
       </c>
       <c r="G200" s="7" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="I200" s="1">
         <v>0</v>
       </c>
       <c r="J200" s="9" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="K200" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L200" s="8" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="201" customHeight="1" spans="1:12">
       <c r="A201" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="E201" s="1">
         <v>5</v>
@@ -11029,36 +11032,36 @@
         <v>5</v>
       </c>
       <c r="G201" s="7" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="I201" s="1">
         <v>0</v>
       </c>
       <c r="J201" s="9" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="K201" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L201" s="8" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="202" customHeight="1" spans="1:12">
       <c r="A202" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E202" s="1">
         <v>5</v>
@@ -11067,36 +11070,36 @@
         <v>5</v>
       </c>
       <c r="G202" s="7" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="I202" s="1">
         <v>0</v>
       </c>
       <c r="J202" s="9" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="K202" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L202" s="8" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="203" customHeight="1" spans="1:12">
       <c r="A203" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="E203" s="1">
         <v>5</v>
@@ -11105,36 +11108,36 @@
         <v>5</v>
       </c>
       <c r="G203" s="7" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="I203" s="1">
         <v>0</v>
       </c>
       <c r="J203" s="9" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="K203" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L203" s="8" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="204" customHeight="1" spans="1:12">
       <c r="A204" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="E204" s="1">
         <v>5</v>
@@ -11143,36 +11146,36 @@
         <v>5</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="I204" s="1">
         <v>0</v>
       </c>
       <c r="J204" s="9" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="K204" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L204" s="8" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="205" customHeight="1" spans="1:12">
       <c r="A205" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E205" s="1">
         <v>5</v>
@@ -11181,36 +11184,36 @@
         <v>5</v>
       </c>
       <c r="G205" s="7" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="I205" s="1">
         <v>0</v>
       </c>
       <c r="J205" s="9" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="K205" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L205" s="8" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="206" customHeight="1" spans="1:12">
       <c r="A206" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="E206" s="1">
         <v>5</v>
@@ -11219,36 +11222,36 @@
         <v>5</v>
       </c>
       <c r="G206" s="7" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="I206" s="1">
         <v>0</v>
       </c>
       <c r="J206" s="9" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="K206" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L206" s="8" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="207" customHeight="1" spans="1:12">
       <c r="A207" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="E207" s="1">
         <v>5</v>
@@ -11257,36 +11260,36 @@
         <v>5</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="I207" s="1">
         <v>0</v>
       </c>
       <c r="J207" s="9" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="K207" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L207" s="8" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="208" customHeight="1" spans="1:12">
       <c r="A208" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="E208" s="1">
         <v>5</v>
@@ -11295,36 +11298,36 @@
         <v>5</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="I208" s="1">
         <v>0</v>
       </c>
       <c r="J208" s="9" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="K208" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L208" s="8" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="209" customHeight="1" spans="1:12">
       <c r="A209" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="E209" s="1">
         <v>5</v>
@@ -11333,36 +11336,36 @@
         <v>5</v>
       </c>
       <c r="G209" s="7" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="I209" s="1">
         <v>0</v>
       </c>
       <c r="J209" s="9" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="K209" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L209" s="8" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="210" customHeight="1" spans="1:12">
       <c r="A210" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="E210" s="1">
         <v>5</v>
@@ -11371,36 +11374,36 @@
         <v>5</v>
       </c>
       <c r="G210" s="7" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="I210" s="1">
         <v>0</v>
       </c>
       <c r="J210" s="9" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="K210" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L210" s="8" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A211" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="E211" s="1">
         <v>5</v>
@@ -11409,36 +11412,36 @@
         <v>5</v>
       </c>
       <c r="G211" s="7" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="I211" s="1">
         <v>0</v>
       </c>
       <c r="J211" s="9" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="K211" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L211" s="8" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A212" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E212" s="1">
         <v>5</v>
@@ -11447,36 +11450,36 @@
         <v>5</v>
       </c>
       <c r="G212" s="7" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="I212" s="1">
         <v>0</v>
       </c>
       <c r="J212" s="9" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="K212" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L212" s="8" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A213" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E213" s="1">
         <v>5</v>
@@ -11485,36 +11488,36 @@
         <v>5</v>
       </c>
       <c r="G213" s="7" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="I213" s="1">
         <v>0</v>
       </c>
       <c r="J213" s="9" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="K213" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L213" s="8" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A214" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E214" s="1">
         <v>5</v>
@@ -11523,36 +11526,36 @@
         <v>5</v>
       </c>
       <c r="G214" s="7" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="I214" s="1">
         <v>0</v>
       </c>
       <c r="J214" s="9" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="K214" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L214" s="8" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A215" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="E215" s="1">
         <v>5</v>
@@ -11561,22 +11564,22 @@
         <v>5</v>
       </c>
       <c r="G215" s="7" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="I215" s="1">
         <v>0</v>
       </c>
       <c r="J215" s="9" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="K215" s="9" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L215" s="8" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -3040,7 +3040,7 @@
     <t>202002,300091,105,504,210076,1009,505,506</t>
   </si>
   <si>
-    <t>10,2500,1000,18000,450000,140000,600000,600000</t>
+    <t>10,2500,1000,18000,450000,140000,600000,1000000</t>
   </si>
   <si>
     <t>10170</t>
@@ -3121,7 +3121,7 @@
     <t>202002,300091,105,504,210077,1009,505,506,202004</t>
   </si>
   <si>
-    <t>10,9500,9000,98000,600000,140000,600000,600000,600000</t>
+    <t>10,9500,9000,98000,600000,140000,600000,1000000,600000</t>
   </si>
   <si>
     <t>10175</t>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -3040,7 +3040,7 @@
     <t>202002,300091,105,504,210076,1009,505,506</t>
   </si>
   <si>
-    <t>10,2500,1000,18000,450000,140000,600000,1000000</t>
+    <t>10,2500,1000,18000,450000,140000,600000,700000</t>
   </si>
   <si>
     <t>10170</t>
@@ -3121,7 +3121,7 @@
     <t>202002,300091,105,504,210077,1009,505,506,202004</t>
   </si>
   <si>
-    <t>10,9500,9000,98000,600000,140000,600000,1000000,600000</t>
+    <t>10,9500,9000,98000,600000,140000,600000,700000,600000</t>
   </si>
   <si>
     <t>10175</t>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="1203">
   <si>
     <t>_Id</t>
   </si>
@@ -3199,85 +3199,85 @@
     <t>10179</t>
   </si>
   <si>
+    <t>1180</t>
+  </si>
+  <si>
+    <t>混沌蝠洞</t>
+  </si>
+  <si>
+    <t>1850-1</t>
+  </si>
+  <si>
+    <t>混沌冰晶</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210078,1009,505,506,202003</t>
+  </si>
+  <si>
+    <t>10180</t>
+  </si>
+  <si>
+    <t>1181</t>
+  </si>
+  <si>
+    <t>混沌骷髅洞</t>
+  </si>
+  <si>
+    <t>1850-2</t>
+  </si>
+  <si>
+    <t>混沌蝠翼</t>
+  </si>
+  <si>
+    <t>10181</t>
+  </si>
+  <si>
+    <t>1182</t>
+  </si>
+  <si>
+    <t>混沌通道</t>
+  </si>
+  <si>
+    <t>1850-3</t>
+  </si>
+  <si>
+    <t>混沌魂火</t>
+  </si>
+  <si>
+    <t>10182</t>
+  </si>
+  <si>
+    <t>1183</t>
+  </si>
+  <si>
+    <t>混沌尸洞</t>
+  </si>
+  <si>
+    <t>1850-4</t>
+  </si>
+  <si>
+    <t>混沌腐肉</t>
+  </si>
+  <si>
+    <t>10183</t>
+  </si>
+  <si>
+    <t>1184</t>
+  </si>
+  <si>
+    <t>混沌蛇谷</t>
+  </si>
+  <si>
+    <t>1850-5</t>
+  </si>
+  <si>
+    <t>混沌蛇胆</t>
+  </si>
+  <si>
+    <t>10184</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1180</t>
-  </si>
-  <si>
-    <t>混沌蝠洞</t>
-  </si>
-  <si>
-    <t>1850-1</t>
-  </si>
-  <si>
-    <t>混沌冰晶</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210078,1009,505,506,202003</t>
-  </si>
-  <si>
-    <t>10180</t>
-  </si>
-  <si>
-    <t>1181</t>
-  </si>
-  <si>
-    <t>混沌骷髅洞</t>
-  </si>
-  <si>
-    <t>1850-2</t>
-  </si>
-  <si>
-    <t>混沌蝠翼</t>
-  </si>
-  <si>
-    <t>10181</t>
-  </si>
-  <si>
-    <t>1182</t>
-  </si>
-  <si>
-    <t>混沌通道</t>
-  </si>
-  <si>
-    <t>1850-3</t>
-  </si>
-  <si>
-    <t>混沌魂火</t>
-  </si>
-  <si>
-    <t>10182</t>
-  </si>
-  <si>
-    <t>1183</t>
-  </si>
-  <si>
-    <t>混沌尸洞</t>
-  </si>
-  <si>
-    <t>1850-4</t>
-  </si>
-  <si>
-    <t>混沌腐肉</t>
-  </si>
-  <si>
-    <t>10183</t>
-  </si>
-  <si>
-    <t>1184</t>
-  </si>
-  <si>
-    <t>混沌蛇谷</t>
-  </si>
-  <si>
-    <t>1850-5</t>
-  </si>
-  <si>
-    <t>混沌蛇胆</t>
-  </si>
-  <si>
-    <t>10184</t>
   </si>
   <si>
     <t>1185</t>
@@ -10442,202 +10442,172 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="186" customHeight="1" spans="1:12">
-      <c r="A186" s="1" t="s">
+    <row r="186" customHeight="1" spans="3:12">
+      <c r="C186" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C186" s="1" t="s">
+      <c r="D186" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="D186" s="1" t="s">
+      <c r="E186" s="1">
+        <v>5</v>
+      </c>
+      <c r="F186" s="1">
+        <v>5</v>
+      </c>
+      <c r="G186" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="E186" s="1">
-        <v>5</v>
-      </c>
-      <c r="F186" s="1">
-        <v>5</v>
-      </c>
-      <c r="G186" s="1" t="s">
+      <c r="H186" s="1" t="s">
         <v>1049</v>
-      </c>
-      <c r="H186" s="1" t="s">
-        <v>1050</v>
       </c>
       <c r="I186" s="1">
         <v>0</v>
       </c>
       <c r="J186" s="9" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="K186" s="9" t="s">
         <v>1020</v>
       </c>
       <c r="L186" s="8" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="3:12">
+      <c r="C187" s="1" t="s">
         <v>1052</v>
       </c>
-    </row>
-    <row r="187" customHeight="1" spans="1:12">
-      <c r="A187" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C187" s="1" t="s">
+      <c r="D187" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="D187" s="1" t="s">
+      <c r="E187" s="1">
+        <v>5</v>
+      </c>
+      <c r="F187" s="1">
+        <v>5</v>
+      </c>
+      <c r="G187" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="E187" s="1">
-        <v>5</v>
-      </c>
-      <c r="F187" s="1">
-        <v>5</v>
-      </c>
-      <c r="G187" s="1" t="s">
+      <c r="H187" s="1" t="s">
         <v>1055</v>
-      </c>
-      <c r="H187" s="1" t="s">
-        <v>1056</v>
       </c>
       <c r="I187" s="1">
         <v>0</v>
       </c>
       <c r="J187" s="9" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="K187" s="9" t="s">
         <v>1020</v>
       </c>
       <c r="L187" s="8" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="3:12">
+      <c r="C188" s="1" t="s">
         <v>1057</v>
       </c>
-    </row>
-    <row r="188" customHeight="1" spans="1:12">
-      <c r="A188" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C188" s="1" t="s">
+      <c r="D188" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="D188" s="1" t="s">
+      <c r="E188" s="1">
+        <v>5</v>
+      </c>
+      <c r="F188" s="1">
+        <v>5</v>
+      </c>
+      <c r="G188" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="E188" s="1">
-        <v>5</v>
-      </c>
-      <c r="F188" s="1">
-        <v>5</v>
-      </c>
-      <c r="G188" s="1" t="s">
+      <c r="H188" s="1" t="s">
         <v>1060</v>
-      </c>
-      <c r="H188" s="1" t="s">
-        <v>1061</v>
       </c>
       <c r="I188" s="1">
         <v>0</v>
       </c>
       <c r="J188" s="9" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="K188" s="9" t="s">
         <v>1020</v>
       </c>
       <c r="L188" s="8" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="3:12">
+      <c r="C189" s="1" t="s">
         <v>1062</v>
       </c>
-    </row>
-    <row r="189" customHeight="1" spans="1:12">
-      <c r="A189" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C189" s="1" t="s">
+      <c r="D189" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="E189" s="1">
+        <v>5</v>
+      </c>
+      <c r="F189" s="1">
+        <v>5</v>
+      </c>
+      <c r="G189" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="E189" s="1">
-        <v>5</v>
-      </c>
-      <c r="F189" s="1">
-        <v>5</v>
-      </c>
-      <c r="G189" s="1" t="s">
+      <c r="H189" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="H189" s="1" t="s">
-        <v>1066</v>
       </c>
       <c r="I189" s="1">
         <v>0</v>
       </c>
       <c r="J189" s="9" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="K189" s="9" t="s">
         <v>1020</v>
       </c>
       <c r="L189" s="8" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="3:12">
+      <c r="C190" s="1" t="s">
         <v>1067</v>
       </c>
-    </row>
-    <row r="190" customHeight="1" spans="1:12">
-      <c r="A190" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C190" s="1" t="s">
+      <c r="D190" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="D190" s="1" t="s">
+      <c r="E190" s="1">
+        <v>5</v>
+      </c>
+      <c r="F190" s="1">
+        <v>5</v>
+      </c>
+      <c r="G190" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="E190" s="1">
-        <v>5</v>
-      </c>
-      <c r="F190" s="1">
-        <v>5</v>
-      </c>
-      <c r="G190" s="1" t="s">
+      <c r="H190" s="1" t="s">
         <v>1070</v>
-      </c>
-      <c r="H190" s="1" t="s">
-        <v>1071</v>
       </c>
       <c r="I190" s="1">
         <v>0</v>
       </c>
       <c r="J190" s="9" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="K190" s="9" t="s">
         <v>1020</v>
       </c>
       <c r="L190" s="8" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="191" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A191" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>1073</v>
@@ -10672,10 +10642,10 @@
     </row>
     <row r="192" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A192" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>1079</v>
@@ -10710,10 +10680,10 @@
     </row>
     <row r="193" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A193" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>1084</v>
@@ -10748,10 +10718,10 @@
     </row>
     <row r="194" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A194" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>1089</v>
@@ -10786,10 +10756,10 @@
     </row>
     <row r="195" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A195" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>1094</v>
@@ -10824,10 +10794,10 @@
     </row>
     <row r="196" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A196" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>1099</v>
@@ -10862,10 +10832,10 @@
     </row>
     <row r="197" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A197" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>1105</v>
@@ -10900,10 +10870,10 @@
     </row>
     <row r="198" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A198" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>1110</v>
@@ -10938,10 +10908,10 @@
     </row>
     <row r="199" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A199" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>1115</v>
@@ -10976,10 +10946,10 @@
     </row>
     <row r="200" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A200" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>1120</v>
@@ -11014,10 +10984,10 @@
     </row>
     <row r="201" customHeight="1" spans="1:12">
       <c r="A201" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>1125</v>
@@ -11052,10 +11022,10 @@
     </row>
     <row r="202" customHeight="1" spans="1:12">
       <c r="A202" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>1131</v>
@@ -11090,10 +11060,10 @@
     </row>
     <row r="203" customHeight="1" spans="1:12">
       <c r="A203" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>1136</v>
@@ -11128,10 +11098,10 @@
     </row>
     <row r="204" customHeight="1" spans="1:12">
       <c r="A204" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>1141</v>
@@ -11166,10 +11136,10 @@
     </row>
     <row r="205" customHeight="1" spans="1:12">
       <c r="A205" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>1146</v>
@@ -11204,10 +11174,10 @@
     </row>
     <row r="206" customHeight="1" spans="1:12">
       <c r="A206" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>1151</v>
@@ -11242,10 +11212,10 @@
     </row>
     <row r="207" customHeight="1" spans="1:12">
       <c r="A207" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>1157</v>
@@ -11280,10 +11250,10 @@
     </row>
     <row r="208" customHeight="1" spans="1:12">
       <c r="A208" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>1162</v>
@@ -11318,10 +11288,10 @@
     </row>
     <row r="209" customHeight="1" spans="1:12">
       <c r="A209" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>1167</v>
@@ -11356,10 +11326,10 @@
     </row>
     <row r="210" customHeight="1" spans="1:12">
       <c r="A210" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>1172</v>
@@ -11394,10 +11364,10 @@
     </row>
     <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A211" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>1177</v>
@@ -11432,10 +11402,10 @@
     </row>
     <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A212" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>1183</v>
@@ -11470,10 +11440,10 @@
     </row>
     <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A213" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>1188</v>
@@ -11508,10 +11478,10 @@
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A214" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>1193</v>
@@ -11546,10 +11516,10 @@
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A215" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1046</v>
+        <v>1072</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>1198</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1203">
   <si>
     <t>_Id</t>
   </si>
@@ -3277,85 +3277,85 @@
     <t>10184</t>
   </si>
   <si>
+    <t>1185</t>
+  </si>
+  <si>
+    <t>混沌狼山</t>
+  </si>
+  <si>
+    <t>1900-1</t>
+  </si>
+  <si>
+    <t>混沌狼爪</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210079,1009,505,506,202003</t>
+  </si>
+  <si>
+    <t>10185</t>
+  </si>
+  <si>
+    <t>1186</t>
+  </si>
+  <si>
+    <t>混沌沙洞</t>
+  </si>
+  <si>
+    <t>1900-2</t>
+  </si>
+  <si>
+    <t>混沌虫皮</t>
+  </si>
+  <si>
+    <t>10186</t>
+  </si>
+  <si>
+    <t>1187</t>
+  </si>
+  <si>
+    <t>混沌鹰崖</t>
+  </si>
+  <si>
+    <t>1900-3</t>
+  </si>
+  <si>
+    <t>混沌鹰羽</t>
+  </si>
+  <si>
+    <t>10187</t>
+  </si>
+  <si>
+    <t>1188</t>
+  </si>
+  <si>
+    <t>混沌虫谷</t>
+  </si>
+  <si>
+    <t>1900-4</t>
+  </si>
+  <si>
+    <t>混沌虫角</t>
+  </si>
+  <si>
+    <t>10188</t>
+  </si>
+  <si>
+    <t>1189</t>
+  </si>
+  <si>
+    <t>混沌虫洞</t>
+  </si>
+  <si>
+    <t>1900-5</t>
+  </si>
+  <si>
+    <t>混沌蜈膏</t>
+  </si>
+  <si>
+    <t>10189</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1185</t>
-  </si>
-  <si>
-    <t>混沌狼山</t>
-  </si>
-  <si>
-    <t>1900-1</t>
-  </si>
-  <si>
-    <t>混沌狼爪</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210079,1009,505,506,202003</t>
-  </si>
-  <si>
-    <t>10185</t>
-  </si>
-  <si>
-    <t>1186</t>
-  </si>
-  <si>
-    <t>混沌沙洞</t>
-  </si>
-  <si>
-    <t>1900-2</t>
-  </si>
-  <si>
-    <t>混沌虫皮</t>
-  </si>
-  <si>
-    <t>10186</t>
-  </si>
-  <si>
-    <t>1187</t>
-  </si>
-  <si>
-    <t>混沌鹰崖</t>
-  </si>
-  <si>
-    <t>1900-3</t>
-  </si>
-  <si>
-    <t>混沌鹰羽</t>
-  </si>
-  <si>
-    <t>10187</t>
-  </si>
-  <si>
-    <t>1188</t>
-  </si>
-  <si>
-    <t>混沌虫谷</t>
-  </si>
-  <si>
-    <t>1900-4</t>
-  </si>
-  <si>
-    <t>混沌虫角</t>
-  </si>
-  <si>
-    <t>10188</t>
-  </si>
-  <si>
-    <t>1189</t>
-  </si>
-  <si>
-    <t>混沌虫洞</t>
-  </si>
-  <si>
-    <t>1900-5</t>
-  </si>
-  <si>
-    <t>混沌蜈膏</t>
-  </si>
-  <si>
-    <t>10189</t>
   </si>
   <si>
     <t>1190</t>
@@ -10602,202 +10602,172 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="191" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A191" s="1" t="s">
+    <row r="191" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C191" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C191" s="1" t="s">
+      <c r="D191" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="D191" s="1" t="s">
+      <c r="E191" s="1">
+        <v>5</v>
+      </c>
+      <c r="F191" s="1">
+        <v>5</v>
+      </c>
+      <c r="G191" s="7" t="s">
         <v>1074</v>
       </c>
-      <c r="E191" s="1">
-        <v>5</v>
-      </c>
-      <c r="F191" s="1">
-        <v>5</v>
-      </c>
-      <c r="G191" s="7" t="s">
+      <c r="H191" s="1" t="s">
         <v>1075</v>
-      </c>
-      <c r="H191" s="1" t="s">
-        <v>1076</v>
       </c>
       <c r="I191" s="1">
         <v>0</v>
       </c>
       <c r="J191" s="9" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="K191" s="9" t="s">
         <v>1020</v>
       </c>
       <c r="L191" s="8" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="192" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C192" s="1" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="192" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A192" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C192" s="1" t="s">
+      <c r="D192" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="E192" s="1">
+        <v>5</v>
+      </c>
+      <c r="F192" s="1">
+        <v>5</v>
+      </c>
+      <c r="G192" s="7" t="s">
         <v>1080</v>
       </c>
-      <c r="E192" s="1">
-        <v>5</v>
-      </c>
-      <c r="F192" s="1">
-        <v>5</v>
-      </c>
-      <c r="G192" s="7" t="s">
+      <c r="H192" s="1" t="s">
         <v>1081</v>
-      </c>
-      <c r="H192" s="1" t="s">
-        <v>1082</v>
       </c>
       <c r="I192" s="1">
         <v>0</v>
       </c>
       <c r="J192" s="9" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="K192" s="9" t="s">
         <v>1020</v>
       </c>
       <c r="L192" s="8" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="193" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C193" s="1" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="193" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A193" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C193" s="1" t="s">
+      <c r="D193" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="D193" s="1" t="s">
+      <c r="E193" s="1">
+        <v>5</v>
+      </c>
+      <c r="F193" s="1">
+        <v>5</v>
+      </c>
+      <c r="G193" s="7" t="s">
         <v>1085</v>
       </c>
-      <c r="E193" s="1">
-        <v>5</v>
-      </c>
-      <c r="F193" s="1">
-        <v>5</v>
-      </c>
-      <c r="G193" s="7" t="s">
+      <c r="H193" s="1" t="s">
         <v>1086</v>
-      </c>
-      <c r="H193" s="1" t="s">
-        <v>1087</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
       </c>
       <c r="J193" s="9" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="K193" s="9" t="s">
         <v>1020</v>
       </c>
       <c r="L193" s="8" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="194" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C194" s="1" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="194" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A194" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C194" s="1" t="s">
+      <c r="D194" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="E194" s="1">
+        <v>5</v>
+      </c>
+      <c r="F194" s="1">
+        <v>5</v>
+      </c>
+      <c r="G194" s="7" t="s">
         <v>1090</v>
       </c>
-      <c r="E194" s="1">
-        <v>5</v>
-      </c>
-      <c r="F194" s="1">
-        <v>5</v>
-      </c>
-      <c r="G194" s="7" t="s">
+      <c r="H194" s="1" t="s">
         <v>1091</v>
-      </c>
-      <c r="H194" s="1" t="s">
-        <v>1092</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
       </c>
       <c r="J194" s="9" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="K194" s="9" t="s">
         <v>1020</v>
       </c>
       <c r="L194" s="8" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="195" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C195" s="1" t="s">
         <v>1093</v>
       </c>
-    </row>
-    <row r="195" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A195" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C195" s="1" t="s">
+      <c r="D195" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="E195" s="1">
+        <v>5</v>
+      </c>
+      <c r="F195" s="1">
+        <v>5</v>
+      </c>
+      <c r="G195" s="7" t="s">
         <v>1095</v>
       </c>
-      <c r="E195" s="1">
-        <v>5</v>
-      </c>
-      <c r="F195" s="1">
-        <v>5</v>
-      </c>
-      <c r="G195" s="7" t="s">
+      <c r="H195" s="1" t="s">
         <v>1096</v>
-      </c>
-      <c r="H195" s="1" t="s">
-        <v>1097</v>
       </c>
       <c r="I195" s="1">
         <v>0</v>
       </c>
       <c r="J195" s="9" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="K195" s="9" t="s">
         <v>1020</v>
       </c>
       <c r="L195" s="8" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="196" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A196" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>1099</v>
@@ -10832,10 +10802,10 @@
     </row>
     <row r="197" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A197" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>1105</v>
@@ -10870,10 +10840,10 @@
     </row>
     <row r="198" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A198" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>1110</v>
@@ -10908,10 +10878,10 @@
     </row>
     <row r="199" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A199" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>1115</v>
@@ -10946,10 +10916,10 @@
     </row>
     <row r="200" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A200" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>1120</v>
@@ -10984,10 +10954,10 @@
     </row>
     <row r="201" customHeight="1" spans="1:12">
       <c r="A201" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>1125</v>
@@ -11022,10 +10992,10 @@
     </row>
     <row r="202" customHeight="1" spans="1:12">
       <c r="A202" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>1131</v>
@@ -11060,10 +11030,10 @@
     </row>
     <row r="203" customHeight="1" spans="1:12">
       <c r="A203" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>1136</v>
@@ -11098,10 +11068,10 @@
     </row>
     <row r="204" customHeight="1" spans="1:12">
       <c r="A204" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>1141</v>
@@ -11136,10 +11106,10 @@
     </row>
     <row r="205" customHeight="1" spans="1:12">
       <c r="A205" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>1146</v>
@@ -11174,10 +11144,10 @@
     </row>
     <row r="206" customHeight="1" spans="1:12">
       <c r="A206" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>1151</v>
@@ -11212,10 +11182,10 @@
     </row>
     <row r="207" customHeight="1" spans="1:12">
       <c r="A207" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>1157</v>
@@ -11250,10 +11220,10 @@
     </row>
     <row r="208" customHeight="1" spans="1:12">
       <c r="A208" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>1162</v>
@@ -11288,10 +11258,10 @@
     </row>
     <row r="209" customHeight="1" spans="1:12">
       <c r="A209" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>1167</v>
@@ -11326,10 +11296,10 @@
     </row>
     <row r="210" customHeight="1" spans="1:12">
       <c r="A210" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>1172</v>
@@ -11364,10 +11334,10 @@
     </row>
     <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A211" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>1177</v>
@@ -11402,10 +11372,10 @@
     </row>
     <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A212" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>1183</v>
@@ -11440,10 +11410,10 @@
     </row>
     <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A213" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>1188</v>
@@ -11478,10 +11448,10 @@
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A214" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>1193</v>
@@ -11516,10 +11486,10 @@
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A215" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1072</v>
+        <v>1098</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>1198</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="1203">
   <si>
     <t>_Id</t>
   </si>
@@ -3355,85 +3355,85 @@
     <t>10189</t>
   </si>
   <si>
+    <t>1190</t>
+  </si>
+  <si>
+    <t>混沌虫穴</t>
+  </si>
+  <si>
+    <t>1950-1</t>
+  </si>
+  <si>
+    <t>混沌虫心</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210080,1009,505,506,202003</t>
+  </si>
+  <si>
+    <t>10190</t>
+  </si>
+  <si>
+    <t>1191</t>
+  </si>
+  <si>
+    <t>混沌虫巢</t>
+  </si>
+  <si>
+    <t>1950-2</t>
+  </si>
+  <si>
+    <t>混沌龙皮</t>
+  </si>
+  <si>
+    <t>10191</t>
+  </si>
+  <si>
+    <t>1192</t>
+  </si>
+  <si>
+    <t>混沌魔猪厅</t>
+  </si>
+  <si>
+    <t>1950-3</t>
+  </si>
+  <si>
+    <t>混沌猪皮</t>
+  </si>
+  <si>
+    <t>10192</t>
+  </si>
+  <si>
+    <t>1193</t>
+  </si>
+  <si>
+    <t>混沌魔猪殿</t>
+  </si>
+  <si>
+    <t>1950-4</t>
+  </si>
+  <si>
+    <t>混沌猪心</t>
+  </si>
+  <si>
+    <t>10193</t>
+  </si>
+  <si>
+    <t>1194</t>
+  </si>
+  <si>
+    <t>混沌桃源</t>
+  </si>
+  <si>
+    <t>1950-5</t>
+  </si>
+  <si>
+    <t>混沌蝎皮</t>
+  </si>
+  <si>
+    <t>10194</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1190</t>
-  </si>
-  <si>
-    <t>混沌虫穴</t>
-  </si>
-  <si>
-    <t>1950-1</t>
-  </si>
-  <si>
-    <t>混沌虫心</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210080,1009,505,506,202003</t>
-  </si>
-  <si>
-    <t>10190</t>
-  </si>
-  <si>
-    <t>1191</t>
-  </si>
-  <si>
-    <t>混沌虫巢</t>
-  </si>
-  <si>
-    <t>1950-2</t>
-  </si>
-  <si>
-    <t>混沌龙皮</t>
-  </si>
-  <si>
-    <t>10191</t>
-  </si>
-  <si>
-    <t>1192</t>
-  </si>
-  <si>
-    <t>混沌魔猪厅</t>
-  </si>
-  <si>
-    <t>1950-3</t>
-  </si>
-  <si>
-    <t>混沌猪皮</t>
-  </si>
-  <si>
-    <t>10192</t>
-  </si>
-  <si>
-    <t>1193</t>
-  </si>
-  <si>
-    <t>混沌魔猪殿</t>
-  </si>
-  <si>
-    <t>1950-4</t>
-  </si>
-  <si>
-    <t>混沌猪心</t>
-  </si>
-  <si>
-    <t>10193</t>
-  </si>
-  <si>
-    <t>1194</t>
-  </si>
-  <si>
-    <t>混沌桃源</t>
-  </si>
-  <si>
-    <t>1950-5</t>
-  </si>
-  <si>
-    <t>混沌蝎皮</t>
-  </si>
-  <si>
-    <t>10194</t>
   </si>
   <si>
     <t>1195</t>
@@ -4317,11 +4317,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4330,9 +4331,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4697,110 +4700,110 @@
     <col min="4" max="9" width="11.6272727272727" style="1" customWidth="1"/>
     <col min="10" max="10" width="75.8181818181818" style="1" customWidth="1"/>
     <col min="11" max="11" width="70.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="39.3727272727273" style="4" customWidth="1"/>
+    <col min="12" max="12" width="39.3727272727273" style="5" customWidth="1"/>
     <col min="13" max="16384" width="9.25454545454545" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:13">
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="5"/>
+      <c r="M3" s="6"/>
     </row>
     <row r="4" customHeight="1" spans="3:13">
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="5"/>
+      <c r="M4" s="6"/>
     </row>
     <row r="5" customHeight="1" spans="3:13">
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="5"/>
-    </row>
-    <row r="6" customHeight="1" spans="3:12">
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" customHeight="1" spans="3:13">
       <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
@@ -4829,7 +4832,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:12">
+    <row r="7" customHeight="1" spans="3:13">
       <c r="C7" s="1" t="s">
         <v>23</v>
       </c>
@@ -4861,7 +4864,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:12">
+    <row r="8" customHeight="1" spans="3:13">
       <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
@@ -4890,7 +4893,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:12">
+    <row r="9" customHeight="1" spans="3:13">
       <c r="C9" s="1" t="s">
         <v>35</v>
       </c>
@@ -4922,7 +4925,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:12">
+    <row r="10" customHeight="1" spans="3:13">
       <c r="C10" s="1" t="s">
         <v>42</v>
       </c>
@@ -4951,7 +4954,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:12">
+    <row r="11" customHeight="1" spans="3:13">
       <c r="C11" s="1" t="s">
         <v>47</v>
       </c>
@@ -4980,7 +4983,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:12">
+    <row r="12" customHeight="1" spans="3:13">
       <c r="C12" s="1" t="s">
         <v>52</v>
       </c>
@@ -5012,7 +5015,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:12">
+    <row r="13" customHeight="1" spans="3:13">
       <c r="C13" s="1" t="s">
         <v>59</v>
       </c>
@@ -5041,7 +5044,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:12">
+    <row r="14" customHeight="1" spans="3:13">
       <c r="C14" s="1" t="s">
         <v>64</v>
       </c>
@@ -5070,7 +5073,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:12">
+    <row r="15" customHeight="1" spans="3:13">
       <c r="C15" s="1" t="s">
         <v>69</v>
       </c>
@@ -5099,7 +5102,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:12">
+    <row r="16" customHeight="1" spans="3:13">
       <c r="C16" s="1" t="s">
         <v>74</v>
       </c>
@@ -6003,10 +6006,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="8" t="s">
+      <c r="J46" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="8" t="s">
+      <c r="K46" s="10" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -6032,10 +6035,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="8" t="s">
+      <c r="J47" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="8" t="s">
+      <c r="K47" s="10" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -6061,17 +6064,17 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="8" t="s">
+      <c r="J48" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="8" t="s">
+      <c r="K48" s="10" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C49" s="1" t="s">
         <v>249</v>
       </c>
@@ -6090,17 +6093,17 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="8" t="s">
+      <c r="J49" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="8" t="s">
+      <c r="K49" s="10" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C50" s="1" t="s">
         <v>254</v>
       </c>
@@ -6119,17 +6122,17 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="8" t="s">
+      <c r="J50" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="8" t="s">
+      <c r="K50" s="10" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C51" s="1" t="s">
         <v>259</v>
       </c>
@@ -6151,17 +6154,17 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="8" t="s">
+      <c r="J51" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="8" t="s">
+      <c r="K51" s="10" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C52" s="1" t="s">
         <v>266</v>
       </c>
@@ -6180,17 +6183,17 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="8" t="s">
+      <c r="J52" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="8" t="s">
+      <c r="K52" s="10" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C53" s="1" t="s">
         <v>271</v>
       </c>
@@ -6209,17 +6212,17 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="8" t="s">
+      <c r="J53" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="8" t="s">
+      <c r="K53" s="10" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C54" s="1" t="s">
         <v>276</v>
       </c>
@@ -6238,17 +6241,17 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="8" t="s">
+      <c r="J54" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="8" t="s">
+      <c r="K54" s="10" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C55" s="1" t="s">
         <v>281</v>
       </c>
@@ -6267,17 +6270,17 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="8" t="s">
+      <c r="J55" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="8" t="s">
+      <c r="K55" s="10" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C56" s="1" t="s">
         <v>286</v>
       </c>
@@ -6299,17 +6302,17 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="8" t="s">
+      <c r="J56" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="8" t="s">
+      <c r="K56" s="10" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C57" s="1" t="s">
         <v>293</v>
       </c>
@@ -6331,17 +6334,17 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="8" t="s">
+      <c r="J57" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="8" t="s">
+      <c r="K57" s="10" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C58" s="1" t="s">
         <v>299</v>
       </c>
@@ -6363,17 +6366,17 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="8" t="s">
+      <c r="J58" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="8" t="s">
+      <c r="K58" s="10" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C59" s="1" t="s">
         <v>305</v>
       </c>
@@ -6395,17 +6398,17 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="8" t="s">
+      <c r="J59" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="8" t="s">
+      <c r="K59" s="10" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C60" s="1" t="s">
         <v>311</v>
       </c>
@@ -6427,10 +6430,10 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="8" t="s">
+      <c r="J60" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="8" t="s">
+      <c r="K60" s="10" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -6460,10 +6463,10 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="9" t="s">
+      <c r="J61" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="9" t="s">
+      <c r="K61" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -6493,10 +6496,10 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="9" t="s">
+      <c r="J62" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="9" t="s">
+      <c r="K62" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -6526,10 +6529,10 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="9" t="s">
+      <c r="J63" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="9" t="s">
+      <c r="K63" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
@@ -6559,10 +6562,10 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="9" t="s">
+      <c r="J64" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="9" t="s">
+      <c r="K64" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
@@ -6592,17 +6595,17 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="9" t="s">
+      <c r="J65" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="9" t="s">
+      <c r="K65" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C66" s="1" t="s">
         <v>348</v>
       </c>
@@ -6624,17 +6627,17 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="9" t="s">
+      <c r="J66" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="9" t="s">
+      <c r="K66" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C67" s="1" t="s">
         <v>354</v>
       </c>
@@ -6656,17 +6659,17 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="9" t="s">
+      <c r="J67" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="9" t="s">
+      <c r="K67" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C68" s="1" t="s">
         <v>360</v>
       </c>
@@ -6688,17 +6691,17 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="9" t="s">
+      <c r="J68" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="9" t="s">
+      <c r="K68" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C69" s="1" t="s">
         <v>366</v>
       </c>
@@ -6720,17 +6723,17 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="9" t="s">
+      <c r="J69" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="9" t="s">
+      <c r="K69" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C70" s="1" t="s">
         <v>372</v>
       </c>
@@ -6752,17 +6755,17 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="9" t="s">
+      <c r="J70" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="9" t="s">
+      <c r="K70" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C71" s="1" t="s">
         <v>378</v>
       </c>
@@ -6784,17 +6787,17 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="9" t="s">
+      <c r="J71" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="9" t="s">
+      <c r="K71" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C72" s="1" t="s">
         <v>384</v>
       </c>
@@ -6816,17 +6819,17 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="9" t="s">
+      <c r="J72" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="9" t="s">
+      <c r="K72" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C73" s="1" t="s">
         <v>390</v>
       </c>
@@ -6848,17 +6851,17 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="9" t="s">
+      <c r="J73" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="9" t="s">
+      <c r="K73" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C74" s="1" t="s">
         <v>396</v>
       </c>
@@ -6880,17 +6883,17 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="9" t="s">
+      <c r="J74" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="9" t="s">
+      <c r="K74" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="2:12">
       <c r="C75" s="1" t="s">
         <v>402</v>
       </c>
@@ -6912,17 +6915,17 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="9" t="s">
+      <c r="J75" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="9" t="s">
+      <c r="K75" s="11" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="3:12">
+    <row r="76" customHeight="1" spans="2:12">
       <c r="C76" s="1" t="s">
         <v>408</v>
       </c>
@@ -6944,17 +6947,17 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="9" t="s">
+      <c r="J76" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="9" t="s">
+      <c r="K76" s="11" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="3:12">
+    <row r="77" customHeight="1" spans="2:12">
       <c r="C77" s="1" t="s">
         <v>415</v>
       </c>
@@ -6976,17 +6979,17 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="9" t="s">
+      <c r="J77" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="9" t="s">
+      <c r="K77" s="11" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="3:12">
+    <row r="78" customHeight="1" spans="2:12">
       <c r="C78" s="1" t="s">
         <v>421</v>
       </c>
@@ -7008,17 +7011,17 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="9" t="s">
+      <c r="J78" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="9" t="s">
+      <c r="K78" s="11" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="3:12">
+    <row r="79" customHeight="1" spans="2:12">
       <c r="C79" s="1" t="s">
         <v>427</v>
       </c>
@@ -7040,17 +7043,17 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="9" t="s">
+      <c r="J79" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="9" t="s">
+      <c r="K79" s="11" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="3:12">
+    <row r="80" customHeight="1" spans="2:12">
       <c r="C80" s="1" t="s">
         <v>433</v>
       </c>
@@ -7072,10 +7075,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="9" t="s">
+      <c r="J80" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="9" t="s">
+      <c r="K80" s="11" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -7104,10 +7107,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="9" t="s">
+      <c r="J81" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="9" t="s">
+      <c r="K81" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -7136,10 +7139,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="9" t="s">
+      <c r="J82" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="9" t="s">
+      <c r="K82" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -7168,10 +7171,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="9" t="s">
+      <c r="J83" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="9" t="s">
+      <c r="K83" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -7200,10 +7203,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="9" t="s">
+      <c r="J84" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="9" t="s">
+      <c r="K84" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -7232,10 +7235,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="9" t="s">
+      <c r="J85" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="9" t="s">
+      <c r="K85" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -7264,10 +7267,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="9" t="s">
+      <c r="J86" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="9" t="s">
+      <c r="K86" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -7296,10 +7299,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="9" t="s">
+      <c r="J87" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="9" t="s">
+      <c r="K87" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -7328,10 +7331,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="9" t="s">
+      <c r="J88" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="9" t="s">
+      <c r="K88" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -7360,10 +7363,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="9" t="s">
+      <c r="J89" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="9" t="s">
+      <c r="K89" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -7392,10 +7395,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="9" t="s">
+      <c r="J90" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="9" t="s">
+      <c r="K90" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -7424,10 +7427,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="9" t="s">
+      <c r="J91" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="9" t="s">
+      <c r="K91" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -7456,10 +7459,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="9" t="s">
+      <c r="J92" s="11" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="9" t="s">
+      <c r="K92" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -7488,10 +7491,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="9" t="s">
+      <c r="J93" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="9" t="s">
+      <c r="K93" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -7520,10 +7523,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="9" t="s">
+      <c r="J94" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="9" t="s">
+      <c r="K94" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -7552,10 +7555,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="9" t="s">
+      <c r="J95" s="11" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="9" t="s">
+      <c r="K95" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -7584,10 +7587,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="9" t="s">
+      <c r="J96" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="9" t="s">
+      <c r="K96" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -7616,10 +7619,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="9" t="s">
+      <c r="J97" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="9" t="s">
+      <c r="K97" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -7648,10 +7651,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="9" t="s">
+      <c r="J98" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="9" t="s">
+      <c r="K98" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -7680,10 +7683,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="9" t="s">
+      <c r="J99" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="9" t="s">
+      <c r="K99" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -7712,10 +7715,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="9" t="s">
+      <c r="J100" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="9" t="s">
+      <c r="K100" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -7744,10 +7747,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="9" t="s">
+      <c r="J101" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="9" t="s">
+      <c r="K101" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -7776,10 +7779,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="9" t="s">
+      <c r="J102" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="9" t="s">
+      <c r="K102" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -7808,10 +7811,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="9" t="s">
+      <c r="J103" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="9" t="s">
+      <c r="K103" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -7840,10 +7843,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="9" t="s">
+      <c r="J104" s="11" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="9" t="s">
+      <c r="K104" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -7872,10 +7875,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="9" t="s">
+      <c r="J105" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="9" t="s">
+      <c r="K105" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -7904,10 +7907,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="9" t="s">
+      <c r="J106" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="9" t="s">
+      <c r="K106" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -7936,10 +7939,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="9" t="s">
+      <c r="J107" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="9" t="s">
+      <c r="K107" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -7968,10 +7971,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="9" t="s">
+      <c r="J108" s="11" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="9" t="s">
+      <c r="K108" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -8000,10 +8003,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="9" t="s">
+      <c r="J109" s="11" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="9" t="s">
+      <c r="K109" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -8032,10 +8035,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="9" t="s">
+      <c r="J110" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="9" t="s">
+      <c r="K110" s="11" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -8064,10 +8067,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="9" t="s">
+      <c r="J111" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="9" t="s">
+      <c r="K111" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -8096,10 +8099,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="9" t="s">
+      <c r="J112" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="9" t="s">
+      <c r="K112" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -8128,10 +8131,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="9" t="s">
+      <c r="J113" s="11" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="9" t="s">
+      <c r="K113" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -8160,10 +8163,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="9" t="s">
+      <c r="J114" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="9" t="s">
+      <c r="K114" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -8192,10 +8195,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="9" t="s">
+      <c r="J115" s="11" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="9" t="s">
+      <c r="K115" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -8224,10 +8227,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="9" t="s">
+      <c r="J116" s="11" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="9" t="s">
+      <c r="K116" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -8256,10 +8259,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="9" t="s">
+      <c r="J117" s="11" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="9" t="s">
+      <c r="K117" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -8288,10 +8291,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="9" t="s">
+      <c r="J118" s="11" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="9" t="s">
+      <c r="K118" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -8320,10 +8323,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="9" t="s">
+      <c r="J119" s="11" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="9" t="s">
+      <c r="K119" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -8352,10 +8355,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="9" t="s">
+      <c r="J120" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="9" t="s">
+      <c r="K120" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -8384,10 +8387,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="9" t="s">
+      <c r="J121" s="11" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="9" t="s">
+      <c r="K121" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -8416,10 +8419,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="9" t="s">
+      <c r="J122" s="11" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="9" t="s">
+      <c r="K122" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -8448,10 +8451,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="9" t="s">
+      <c r="J123" s="11" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="9" t="s">
+      <c r="K123" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -8480,10 +8483,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="9" t="s">
+      <c r="J124" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="9" t="s">
+      <c r="K124" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -8512,10 +8515,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="9" t="s">
+      <c r="J125" s="11" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="9" t="s">
+      <c r="K125" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -8544,10 +8547,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="9" t="s">
+      <c r="J126" s="11" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="9" t="s">
+      <c r="K126" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -8576,10 +8579,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="9" t="s">
+      <c r="J127" s="11" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="9" t="s">
+      <c r="K127" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -8608,10 +8611,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="9" t="s">
+      <c r="J128" s="11" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="9" t="s">
+      <c r="K128" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -8640,10 +8643,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="9" t="s">
+      <c r="J129" s="11" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="9" t="s">
+      <c r="K129" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -8672,10 +8675,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="9" t="s">
+      <c r="J130" s="11" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="9" t="s">
+      <c r="K130" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -8704,10 +8707,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="9" t="s">
+      <c r="J131" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="9" t="s">
+      <c r="K131" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -8736,10 +8739,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="9" t="s">
+      <c r="J132" s="11" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="9" t="s">
+      <c r="K132" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -8768,10 +8771,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="9" t="s">
+      <c r="J133" s="11" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="9" t="s">
+      <c r="K133" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -8800,10 +8803,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="9" t="s">
+      <c r="J134" s="11" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="9" t="s">
+      <c r="K134" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -8832,10 +8835,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="9" t="s">
+      <c r="J135" s="11" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="9" t="s">
+      <c r="K135" s="11" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -8864,10 +8867,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="9" t="s">
+      <c r="J136" s="11" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="9" t="s">
+      <c r="K136" s="11" t="s">
         <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -8896,10 +8899,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="9" t="s">
+      <c r="J137" s="11" t="s">
         <v>782</v>
       </c>
-      <c r="K137" s="9" t="s">
+      <c r="K137" s="11" t="s">
         <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -8928,10 +8931,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="9" t="s">
+      <c r="J138" s="11" t="s">
         <v>788</v>
       </c>
-      <c r="K138" s="9" t="s">
+      <c r="K138" s="11" t="s">
         <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -8960,10 +8963,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="9" t="s">
+      <c r="J139" s="11" t="s">
         <v>794</v>
       </c>
-      <c r="K139" s="9" t="s">
+      <c r="K139" s="11" t="s">
         <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -8992,10 +8995,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="9" t="s">
+      <c r="J140" s="11" t="s">
         <v>800</v>
       </c>
-      <c r="K140" s="9" t="s">
+      <c r="K140" s="11" t="s">
         <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -9024,10 +9027,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="9" t="s">
+      <c r="J141" s="11" t="s">
         <v>806</v>
       </c>
-      <c r="K141" s="9" t="s">
+      <c r="K141" s="11" t="s">
         <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -9056,10 +9059,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="9" t="s">
+      <c r="J142" s="11" t="s">
         <v>812</v>
       </c>
-      <c r="K142" s="9" t="s">
+      <c r="K142" s="11" t="s">
         <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -9088,10 +9091,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="9" t="s">
+      <c r="J143" s="11" t="s">
         <v>818</v>
       </c>
-      <c r="K143" s="9" t="s">
+      <c r="K143" s="11" t="s">
         <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -9120,10 +9123,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="9" t="s">
+      <c r="J144" s="11" t="s">
         <v>824</v>
       </c>
-      <c r="K144" s="9" t="s">
+      <c r="K144" s="11" t="s">
         <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -9152,10 +9155,10 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="9" t="s">
+      <c r="J145" s="11" t="s">
         <v>830</v>
       </c>
-      <c r="K145" s="9" t="s">
+      <c r="K145" s="11" t="s">
         <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
@@ -9184,13 +9187,13 @@
       <c r="I146" s="3">
         <v>0</v>
       </c>
-      <c r="J146" s="10" t="s">
+      <c r="J146" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="K146" s="10" t="s">
+      <c r="K146" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L146" s="10" t="s">
+      <c r="L146" s="12" t="s">
         <v>837</v>
       </c>
     </row>
@@ -9216,13 +9219,13 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="9" t="s">
+      <c r="J147" s="11" t="s">
         <v>836</v>
       </c>
-      <c r="K147" s="9" t="s">
+      <c r="K147" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L147" s="8" t="s">
+      <c r="L147" s="10" t="s">
         <v>842</v>
       </c>
     </row>
@@ -9248,13 +9251,13 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="9" t="s">
+      <c r="J148" s="11" t="s">
         <v>836</v>
       </c>
-      <c r="K148" s="9" t="s">
+      <c r="K148" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L148" s="8" t="s">
+      <c r="L148" s="10" t="s">
         <v>847</v>
       </c>
     </row>
@@ -9280,13 +9283,13 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="9" t="s">
+      <c r="J149" s="11" t="s">
         <v>836</v>
       </c>
-      <c r="K149" s="9" t="s">
+      <c r="K149" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L149" s="8" t="s">
+      <c r="L149" s="10" t="s">
         <v>852</v>
       </c>
     </row>
@@ -9312,13 +9315,13 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="9" t="s">
+      <c r="J150" s="11" t="s">
         <v>836</v>
       </c>
-      <c r="K150" s="9" t="s">
+      <c r="K150" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L150" s="8" t="s">
+      <c r="L150" s="10" t="s">
         <v>857</v>
       </c>
     </row>
@@ -9344,13 +9347,13 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="9" t="s">
+      <c r="J151" s="11" t="s">
         <v>862</v>
       </c>
-      <c r="K151" s="9" t="s">
+      <c r="K151" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L151" s="8" t="s">
+      <c r="L151" s="10" t="s">
         <v>863</v>
       </c>
     </row>
@@ -9376,13 +9379,13 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="9" t="s">
+      <c r="J152" s="11" t="s">
         <v>862</v>
       </c>
-      <c r="K152" s="9" t="s">
+      <c r="K152" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L152" s="8" t="s">
+      <c r="L152" s="10" t="s">
         <v>868</v>
       </c>
     </row>
@@ -9408,13 +9411,13 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="9" t="s">
+      <c r="J153" s="11" t="s">
         <v>862</v>
       </c>
-      <c r="K153" s="9" t="s">
+      <c r="K153" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L153" s="8" t="s">
+      <c r="L153" s="10" t="s">
         <v>873</v>
       </c>
     </row>
@@ -9440,13 +9443,13 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="9" t="s">
+      <c r="J154" s="11" t="s">
         <v>862</v>
       </c>
-      <c r="K154" s="9" t="s">
+      <c r="K154" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L154" s="8" t="s">
+      <c r="L154" s="10" t="s">
         <v>878</v>
       </c>
     </row>
@@ -9472,13 +9475,13 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="9" t="s">
+      <c r="J155" s="11" t="s">
         <v>862</v>
       </c>
-      <c r="K155" s="9" t="s">
+      <c r="K155" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L155" s="8" t="s">
+      <c r="L155" s="10" t="s">
         <v>883</v>
       </c>
     </row>
@@ -9504,13 +9507,13 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="9" t="s">
+      <c r="J156" s="11" t="s">
         <v>888</v>
       </c>
-      <c r="K156" s="9" t="s">
+      <c r="K156" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L156" s="8" t="s">
+      <c r="L156" s="10" t="s">
         <v>889</v>
       </c>
     </row>
@@ -9536,13 +9539,13 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="9" t="s">
+      <c r="J157" s="11" t="s">
         <v>888</v>
       </c>
-      <c r="K157" s="9" t="s">
+      <c r="K157" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L157" s="8" t="s">
+      <c r="L157" s="10" t="s">
         <v>894</v>
       </c>
     </row>
@@ -9568,13 +9571,13 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="9" t="s">
+      <c r="J158" s="11" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="9" t="s">
+      <c r="K158" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L158" s="8" t="s">
+      <c r="L158" s="10" t="s">
         <v>899</v>
       </c>
     </row>
@@ -9600,13 +9603,13 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="9" t="s">
+      <c r="J159" s="11" t="s">
         <v>888</v>
       </c>
-      <c r="K159" s="9" t="s">
+      <c r="K159" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L159" s="8" t="s">
+      <c r="L159" s="10" t="s">
         <v>904</v>
       </c>
     </row>
@@ -9632,13 +9635,13 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="9" t="s">
+      <c r="J160" s="11" t="s">
         <v>888</v>
       </c>
-      <c r="K160" s="9" t="s">
+      <c r="K160" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L160" s="8" t="s">
+      <c r="L160" s="10" t="s">
         <v>909</v>
       </c>
     </row>
@@ -9664,13 +9667,13 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="9" t="s">
+      <c r="J161" s="11" t="s">
         <v>914</v>
       </c>
-      <c r="K161" s="9" t="s">
+      <c r="K161" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L161" s="8" t="s">
+      <c r="L161" s="10" t="s">
         <v>915</v>
       </c>
     </row>
@@ -9696,13 +9699,13 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="9" t="s">
+      <c r="J162" s="11" t="s">
         <v>914</v>
       </c>
-      <c r="K162" s="9" t="s">
+      <c r="K162" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L162" s="8" t="s">
+      <c r="L162" s="10" t="s">
         <v>920</v>
       </c>
     </row>
@@ -9728,13 +9731,13 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="9" t="s">
+      <c r="J163" s="11" t="s">
         <v>914</v>
       </c>
-      <c r="K163" s="9" t="s">
+      <c r="K163" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L163" s="8" t="s">
+      <c r="L163" s="10" t="s">
         <v>925</v>
       </c>
     </row>
@@ -9760,13 +9763,13 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="9" t="s">
+      <c r="J164" s="11" t="s">
         <v>914</v>
       </c>
-      <c r="K164" s="9" t="s">
+      <c r="K164" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L164" s="8" t="s">
+      <c r="L164" s="10" t="s">
         <v>930</v>
       </c>
     </row>
@@ -9792,13 +9795,13 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="9" t="s">
+      <c r="J165" s="11" t="s">
         <v>914</v>
       </c>
-      <c r="K165" s="9" t="s">
+      <c r="K165" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L165" s="8" t="s">
+      <c r="L165" s="10" t="s">
         <v>935</v>
       </c>
     </row>
@@ -9824,13 +9827,13 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="9" t="s">
+      <c r="J166" s="11" t="s">
         <v>940</v>
       </c>
-      <c r="K166" s="9" t="s">
+      <c r="K166" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L166" s="8" t="s">
+      <c r="L166" s="10" t="s">
         <v>941</v>
       </c>
     </row>
@@ -9856,13 +9859,13 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="9" t="s">
+      <c r="J167" s="11" t="s">
         <v>940</v>
       </c>
-      <c r="K167" s="9" t="s">
+      <c r="K167" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L167" s="8" t="s">
+      <c r="L167" s="10" t="s">
         <v>946</v>
       </c>
     </row>
@@ -9888,13 +9891,13 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="9" t="s">
+      <c r="J168" s="11" t="s">
         <v>940</v>
       </c>
-      <c r="K168" s="9" t="s">
+      <c r="K168" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L168" s="8" t="s">
+      <c r="L168" s="10" t="s">
         <v>951</v>
       </c>
     </row>
@@ -9920,13 +9923,13 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="9" t="s">
+      <c r="J169" s="11" t="s">
         <v>940</v>
       </c>
-      <c r="K169" s="9" t="s">
+      <c r="K169" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L169" s="8" t="s">
+      <c r="L169" s="10" t="s">
         <v>956</v>
       </c>
     </row>
@@ -9952,13 +9955,13 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="9" t="s">
+      <c r="J170" s="11" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="9" t="s">
+      <c r="K170" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L170" s="8" t="s">
+      <c r="L170" s="10" t="s">
         <v>961</v>
       </c>
     </row>
@@ -9984,13 +9987,13 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="9" t="s">
+      <c r="J171" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="K171" s="9" t="s">
+      <c r="K171" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L171" s="8" t="s">
+      <c r="L171" s="10" t="s">
         <v>967</v>
       </c>
     </row>
@@ -10016,13 +10019,13 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="9" t="s">
+      <c r="J172" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="K172" s="9" t="s">
+      <c r="K172" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L172" s="8" t="s">
+      <c r="L172" s="10" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10048,13 +10051,13 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="9" t="s">
+      <c r="J173" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="K173" s="9" t="s">
+      <c r="K173" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L173" s="8" t="s">
+      <c r="L173" s="10" t="s">
         <v>977</v>
       </c>
     </row>
@@ -10080,13 +10083,13 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="9" t="s">
+      <c r="J174" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="K174" s="9" t="s">
+      <c r="K174" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L174" s="8" t="s">
+      <c r="L174" s="10" t="s">
         <v>982</v>
       </c>
     </row>
@@ -10112,13 +10115,13 @@
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="9" t="s">
+      <c r="J175" s="11" t="s">
         <v>966</v>
       </c>
-      <c r="K175" s="9" t="s">
+      <c r="K175" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="L175" s="8" t="s">
+      <c r="L175" s="10" t="s">
         <v>987</v>
       </c>
     </row>
@@ -10144,13 +10147,13 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="9" t="s">
+      <c r="J176" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="K176" s="9" t="s">
+      <c r="K176" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="L176" s="8" t="s">
+      <c r="L176" s="10" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10176,13 +10179,13 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="9" t="s">
+      <c r="J177" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="K177" s="9" t="s">
+      <c r="K177" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="L177" s="8" t="s">
+      <c r="L177" s="10" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10208,13 +10211,13 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="9" t="s">
+      <c r="J178" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="K178" s="9" t="s">
+      <c r="K178" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="L178" s="8" t="s">
+      <c r="L178" s="10" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -10240,13 +10243,13 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="9" t="s">
+      <c r="J179" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="K179" s="9" t="s">
+      <c r="K179" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="L179" s="8" t="s">
+      <c r="L179" s="10" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -10272,13 +10275,13 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="9" t="s">
+      <c r="J180" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="K180" s="9" t="s">
+      <c r="K180" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="L180" s="8" t="s">
+      <c r="L180" s="10" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -10304,13 +10307,13 @@
       <c r="I181" s="3">
         <v>0</v>
       </c>
-      <c r="J181" s="10" t="s">
+      <c r="J181" s="12" t="s">
         <v>1019</v>
       </c>
-      <c r="K181" s="10" t="s">
+      <c r="K181" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L181" s="8" t="s">
+      <c r="L181" s="10" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -10336,13 +10339,13 @@
       <c r="I182" s="1">
         <v>0</v>
       </c>
-      <c r="J182" s="9" t="s">
+      <c r="J182" s="11" t="s">
         <v>1026</v>
       </c>
-      <c r="K182" s="9" t="s">
+      <c r="K182" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L182" s="8" t="s">
+      <c r="L182" s="10" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -10368,13 +10371,13 @@
       <c r="I183" s="1">
         <v>0</v>
       </c>
-      <c r="J183" s="9" t="s">
+      <c r="J183" s="11" t="s">
         <v>1032</v>
       </c>
-      <c r="K183" s="9" t="s">
+      <c r="K183" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L183" s="8" t="s">
+      <c r="L183" s="10" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10400,13 +10403,13 @@
       <c r="I184" s="1">
         <v>0</v>
       </c>
-      <c r="J184" s="9" t="s">
+      <c r="J184" s="11" t="s">
         <v>1038</v>
       </c>
-      <c r="K184" s="9" t="s">
+      <c r="K184" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L184" s="8" t="s">
+      <c r="L184" s="10" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10432,13 +10435,13 @@
       <c r="I185" s="1">
         <v>0</v>
       </c>
-      <c r="J185" s="9" t="s">
+      <c r="J185" s="11" t="s">
         <v>1044</v>
       </c>
-      <c r="K185" s="9" t="s">
+      <c r="K185" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L185" s="8" t="s">
+      <c r="L185" s="10" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -10464,13 +10467,13 @@
       <c r="I186" s="1">
         <v>0</v>
       </c>
-      <c r="J186" s="9" t="s">
+      <c r="J186" s="11" t="s">
         <v>1050</v>
       </c>
-      <c r="K186" s="9" t="s">
+      <c r="K186" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L186" s="8" t="s">
+      <c r="L186" s="10" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -10496,13 +10499,13 @@
       <c r="I187" s="1">
         <v>0</v>
       </c>
-      <c r="J187" s="9" t="s">
+      <c r="J187" s="11" t="s">
         <v>1050</v>
       </c>
-      <c r="K187" s="9" t="s">
+      <c r="K187" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L187" s="8" t="s">
+      <c r="L187" s="10" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -10528,13 +10531,13 @@
       <c r="I188" s="1">
         <v>0</v>
       </c>
-      <c r="J188" s="9" t="s">
+      <c r="J188" s="11" t="s">
         <v>1050</v>
       </c>
-      <c r="K188" s="9" t="s">
+      <c r="K188" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L188" s="8" t="s">
+      <c r="L188" s="10" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -10560,13 +10563,13 @@
       <c r="I189" s="1">
         <v>0</v>
       </c>
-      <c r="J189" s="9" t="s">
+      <c r="J189" s="11" t="s">
         <v>1050</v>
       </c>
-      <c r="K189" s="9" t="s">
+      <c r="K189" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L189" s="8" t="s">
+      <c r="L189" s="10" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -10592,13 +10595,13 @@
       <c r="I190" s="1">
         <v>0</v>
       </c>
-      <c r="J190" s="9" t="s">
+      <c r="J190" s="11" t="s">
         <v>1050</v>
       </c>
-      <c r="K190" s="9" t="s">
+      <c r="K190" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L190" s="8" t="s">
+      <c r="L190" s="10" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -10615,7 +10618,7 @@
       <c r="F191" s="1">
         <v>5</v>
       </c>
-      <c r="G191" s="7" t="s">
+      <c r="G191" s="8" t="s">
         <v>1074</v>
       </c>
       <c r="H191" s="1" t="s">
@@ -10624,13 +10627,13 @@
       <c r="I191" s="1">
         <v>0</v>
       </c>
-      <c r="J191" s="9" t="s">
+      <c r="J191" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="K191" s="9" t="s">
+      <c r="K191" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L191" s="8" t="s">
+      <c r="L191" s="10" t="s">
         <v>1077</v>
       </c>
     </row>
@@ -10647,7 +10650,7 @@
       <c r="F192" s="1">
         <v>5</v>
       </c>
-      <c r="G192" s="7" t="s">
+      <c r="G192" s="8" t="s">
         <v>1080</v>
       </c>
       <c r="H192" s="1" t="s">
@@ -10656,17 +10659,17 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-      <c r="J192" s="9" t="s">
+      <c r="J192" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="K192" s="9" t="s">
+      <c r="K192" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L192" s="8" t="s">
+      <c r="L192" s="10" t="s">
         <v>1082</v>
       </c>
     </row>
-    <row r="193" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="193" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C193" s="1" t="s">
         <v>1083</v>
       </c>
@@ -10679,7 +10682,7 @@
       <c r="F193" s="1">
         <v>5</v>
       </c>
-      <c r="G193" s="7" t="s">
+      <c r="G193" s="8" t="s">
         <v>1085</v>
       </c>
       <c r="H193" s="1" t="s">
@@ -10688,17 +10691,17 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-      <c r="J193" s="9" t="s">
+      <c r="J193" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="K193" s="9" t="s">
+      <c r="K193" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L193" s="8" t="s">
+      <c r="L193" s="10" t="s">
         <v>1087</v>
       </c>
     </row>
-    <row r="194" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="194" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C194" s="1" t="s">
         <v>1088</v>
       </c>
@@ -10711,7 +10714,7 @@
       <c r="F194" s="1">
         <v>5</v>
       </c>
-      <c r="G194" s="7" t="s">
+      <c r="G194" s="8" t="s">
         <v>1090</v>
       </c>
       <c r="H194" s="1" t="s">
@@ -10720,17 +10723,17 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-      <c r="J194" s="9" t="s">
+      <c r="J194" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="K194" s="9" t="s">
+      <c r="K194" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L194" s="8" t="s">
+      <c r="L194" s="10" t="s">
         <v>1092</v>
       </c>
     </row>
-    <row r="195" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="195" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C195" s="1" t="s">
         <v>1093</v>
       </c>
@@ -10743,7 +10746,7 @@
       <c r="F195" s="1">
         <v>5</v>
       </c>
-      <c r="G195" s="7" t="s">
+      <c r="G195" s="8" t="s">
         <v>1095</v>
       </c>
       <c r="H195" s="1" t="s">
@@ -10752,212 +10755,182 @@
       <c r="I195" s="1">
         <v>0</v>
       </c>
-      <c r="J195" s="9" t="s">
+      <c r="J195" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="K195" s="9" t="s">
+      <c r="K195" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L195" s="8" t="s">
+      <c r="L195" s="10" t="s">
         <v>1097</v>
       </c>
     </row>
-    <row r="196" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A196" s="1" t="s">
+    <row r="196" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C196" s="4" t="s">
         <v>1098</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C196" s="1" t="s">
+      <c r="D196" s="4" t="s">
         <v>1099</v>
       </c>
-      <c r="D196" s="1" t="s">
+      <c r="E196" s="4">
+        <v>5</v>
+      </c>
+      <c r="F196" s="4">
+        <v>5</v>
+      </c>
+      <c r="G196" s="9" t="s">
         <v>1100</v>
       </c>
-      <c r="E196" s="1">
-        <v>5</v>
-      </c>
-      <c r="F196" s="1">
-        <v>5</v>
-      </c>
-      <c r="G196" s="7" t="s">
+      <c r="H196" s="4" t="s">
         <v>1101</v>
       </c>
-      <c r="H196" s="1" t="s">
+      <c r="I196" s="4">
+        <v>0</v>
+      </c>
+      <c r="J196" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="I196" s="1">
-        <v>0</v>
-      </c>
-      <c r="J196" s="9" t="s">
+      <c r="K196" s="13" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L196" s="13" t="s">
         <v>1103</v>
       </c>
-      <c r="K196" s="9" t="s">
-        <v>1020</v>
-      </c>
-      <c r="L196" s="8" t="s">
+    </row>
+    <row r="197" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C197" s="1" t="s">
         <v>1104</v>
       </c>
-    </row>
-    <row r="197" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A197" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C197" s="1" t="s">
+      <c r="D197" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="D197" s="1" t="s">
+      <c r="E197" s="1">
+        <v>5</v>
+      </c>
+      <c r="F197" s="1">
+        <v>5</v>
+      </c>
+      <c r="G197" s="8" t="s">
         <v>1106</v>
       </c>
-      <c r="E197" s="1">
-        <v>5</v>
-      </c>
-      <c r="F197" s="1">
-        <v>5</v>
-      </c>
-      <c r="G197" s="7" t="s">
+      <c r="H197" s="1" t="s">
         <v>1107</v>
-      </c>
-      <c r="H197" s="1" t="s">
-        <v>1108</v>
       </c>
       <c r="I197" s="1">
         <v>0</v>
       </c>
-      <c r="J197" s="9" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K197" s="9" t="s">
+      <c r="J197" s="11" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K197" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L197" s="8" t="s">
+      <c r="L197" s="10" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="198" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C198" s="1" t="s">
         <v>1109</v>
       </c>
-    </row>
-    <row r="198" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A198" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C198" s="1" t="s">
+      <c r="D198" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="E198" s="1">
+        <v>5</v>
+      </c>
+      <c r="F198" s="1">
+        <v>5</v>
+      </c>
+      <c r="G198" s="8" t="s">
         <v>1111</v>
       </c>
-      <c r="E198" s="1">
-        <v>5</v>
-      </c>
-      <c r="F198" s="1">
-        <v>5</v>
-      </c>
-      <c r="G198" s="7" t="s">
+      <c r="H198" s="1" t="s">
         <v>1112</v>
-      </c>
-      <c r="H198" s="1" t="s">
-        <v>1113</v>
       </c>
       <c r="I198" s="1">
         <v>0</v>
       </c>
-      <c r="J198" s="9" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K198" s="9" t="s">
+      <c r="J198" s="11" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K198" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L198" s="8" t="s">
+      <c r="L198" s="10" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="199" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C199" s="1" t="s">
         <v>1114</v>
       </c>
-    </row>
-    <row r="199" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A199" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C199" s="1" t="s">
+      <c r="D199" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="E199" s="1">
+        <v>5</v>
+      </c>
+      <c r="F199" s="1">
+        <v>5</v>
+      </c>
+      <c r="G199" s="8" t="s">
         <v>1116</v>
       </c>
-      <c r="E199" s="1">
-        <v>5</v>
-      </c>
-      <c r="F199" s="1">
-        <v>5</v>
-      </c>
-      <c r="G199" s="7" t="s">
+      <c r="H199" s="1" t="s">
         <v>1117</v>
-      </c>
-      <c r="H199" s="1" t="s">
-        <v>1118</v>
       </c>
       <c r="I199" s="1">
         <v>0</v>
       </c>
-      <c r="J199" s="9" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K199" s="9" t="s">
+      <c r="J199" s="11" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K199" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L199" s="8" t="s">
+      <c r="L199" s="10" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="200" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="C200" s="1" t="s">
         <v>1119</v>
       </c>
-    </row>
-    <row r="200" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A200" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C200" s="1" t="s">
+      <c r="D200" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="D200" s="1" t="s">
+      <c r="E200" s="1">
+        <v>5</v>
+      </c>
+      <c r="F200" s="1">
+        <v>5</v>
+      </c>
+      <c r="G200" s="8" t="s">
         <v>1121</v>
       </c>
-      <c r="E200" s="1">
-        <v>5</v>
-      </c>
-      <c r="F200" s="1">
-        <v>5</v>
-      </c>
-      <c r="G200" s="7" t="s">
+      <c r="H200" s="1" t="s">
         <v>1122</v>
-      </c>
-      <c r="H200" s="1" t="s">
-        <v>1123</v>
       </c>
       <c r="I200" s="1">
         <v>0</v>
       </c>
-      <c r="J200" s="9" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K200" s="9" t="s">
+      <c r="J200" s="11" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K200" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L200" s="8" t="s">
-        <v>1124</v>
+      <c r="L200" s="10" t="s">
+        <v>1123</v>
       </c>
     </row>
     <row r="201" customHeight="1" spans="1:12">
       <c r="A201" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>1125</v>
@@ -10971,7 +10944,7 @@
       <c r="F201" s="1">
         <v>5</v>
       </c>
-      <c r="G201" s="7" t="s">
+      <c r="G201" s="8" t="s">
         <v>1127</v>
       </c>
       <c r="H201" s="1" t="s">
@@ -10980,22 +10953,22 @@
       <c r="I201" s="1">
         <v>0</v>
       </c>
-      <c r="J201" s="9" t="s">
+      <c r="J201" s="11" t="s">
         <v>1129</v>
       </c>
-      <c r="K201" s="9" t="s">
+      <c r="K201" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L201" s="8" t="s">
+      <c r="L201" s="10" t="s">
         <v>1130</v>
       </c>
     </row>
     <row r="202" customHeight="1" spans="1:12">
       <c r="A202" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>1131</v>
@@ -11009,7 +10982,7 @@
       <c r="F202" s="1">
         <v>5</v>
       </c>
-      <c r="G202" s="7" t="s">
+      <c r="G202" s="8" t="s">
         <v>1133</v>
       </c>
       <c r="H202" s="1" t="s">
@@ -11018,22 +10991,22 @@
       <c r="I202" s="1">
         <v>0</v>
       </c>
-      <c r="J202" s="9" t="s">
+      <c r="J202" s="11" t="s">
         <v>1129</v>
       </c>
-      <c r="K202" s="9" t="s">
+      <c r="K202" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L202" s="8" t="s">
+      <c r="L202" s="10" t="s">
         <v>1135</v>
       </c>
     </row>
     <row r="203" customHeight="1" spans="1:12">
       <c r="A203" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>1136</v>
@@ -11047,7 +11020,7 @@
       <c r="F203" s="1">
         <v>5</v>
       </c>
-      <c r="G203" s="7" t="s">
+      <c r="G203" s="8" t="s">
         <v>1138</v>
       </c>
       <c r="H203" s="1" t="s">
@@ -11056,22 +11029,22 @@
       <c r="I203" s="1">
         <v>0</v>
       </c>
-      <c r="J203" s="9" t="s">
+      <c r="J203" s="11" t="s">
         <v>1129</v>
       </c>
-      <c r="K203" s="9" t="s">
+      <c r="K203" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L203" s="8" t="s">
+      <c r="L203" s="10" t="s">
         <v>1140</v>
       </c>
     </row>
     <row r="204" customHeight="1" spans="1:12">
       <c r="A204" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>1141</v>
@@ -11085,7 +11058,7 @@
       <c r="F204" s="1">
         <v>5</v>
       </c>
-      <c r="G204" s="7" t="s">
+      <c r="G204" s="8" t="s">
         <v>1143</v>
       </c>
       <c r="H204" s="1" t="s">
@@ -11094,22 +11067,22 @@
       <c r="I204" s="1">
         <v>0</v>
       </c>
-      <c r="J204" s="9" t="s">
+      <c r="J204" s="11" t="s">
         <v>1129</v>
       </c>
-      <c r="K204" s="9" t="s">
+      <c r="K204" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L204" s="8" t="s">
+      <c r="L204" s="10" t="s">
         <v>1145</v>
       </c>
     </row>
     <row r="205" customHeight="1" spans="1:12">
       <c r="A205" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>1146</v>
@@ -11123,7 +11096,7 @@
       <c r="F205" s="1">
         <v>5</v>
       </c>
-      <c r="G205" s="7" t="s">
+      <c r="G205" s="8" t="s">
         <v>1148</v>
       </c>
       <c r="H205" s="1" t="s">
@@ -11132,22 +11105,22 @@
       <c r="I205" s="1">
         <v>0</v>
       </c>
-      <c r="J205" s="9" t="s">
+      <c r="J205" s="11" t="s">
         <v>1129</v>
       </c>
-      <c r="K205" s="9" t="s">
+      <c r="K205" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L205" s="8" t="s">
+      <c r="L205" s="10" t="s">
         <v>1150</v>
       </c>
     </row>
     <row r="206" customHeight="1" spans="1:12">
       <c r="A206" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>1151</v>
@@ -11161,7 +11134,7 @@
       <c r="F206" s="1">
         <v>5</v>
       </c>
-      <c r="G206" s="7" t="s">
+      <c r="G206" s="8" t="s">
         <v>1153</v>
       </c>
       <c r="H206" s="1" t="s">
@@ -11170,22 +11143,22 @@
       <c r="I206" s="1">
         <v>0</v>
       </c>
-      <c r="J206" s="9" t="s">
+      <c r="J206" s="11" t="s">
         <v>1155</v>
       </c>
-      <c r="K206" s="9" t="s">
+      <c r="K206" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L206" s="8" t="s">
+      <c r="L206" s="10" t="s">
         <v>1156</v>
       </c>
     </row>
     <row r="207" customHeight="1" spans="1:12">
       <c r="A207" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>1157</v>
@@ -11199,7 +11172,7 @@
       <c r="F207" s="1">
         <v>5</v>
       </c>
-      <c r="G207" s="7" t="s">
+      <c r="G207" s="8" t="s">
         <v>1159</v>
       </c>
       <c r="H207" s="1" t="s">
@@ -11208,22 +11181,22 @@
       <c r="I207" s="1">
         <v>0</v>
       </c>
-      <c r="J207" s="9" t="s">
+      <c r="J207" s="11" t="s">
         <v>1155</v>
       </c>
-      <c r="K207" s="9" t="s">
+      <c r="K207" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L207" s="8" t="s">
+      <c r="L207" s="10" t="s">
         <v>1161</v>
       </c>
     </row>
     <row r="208" customHeight="1" spans="1:12">
       <c r="A208" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>1162</v>
@@ -11237,7 +11210,7 @@
       <c r="F208" s="1">
         <v>5</v>
       </c>
-      <c r="G208" s="7" t="s">
+      <c r="G208" s="8" t="s">
         <v>1164</v>
       </c>
       <c r="H208" s="1" t="s">
@@ -11246,22 +11219,22 @@
       <c r="I208" s="1">
         <v>0</v>
       </c>
-      <c r="J208" s="9" t="s">
+      <c r="J208" s="11" t="s">
         <v>1155</v>
       </c>
-      <c r="K208" s="9" t="s">
+      <c r="K208" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L208" s="8" t="s">
+      <c r="L208" s="10" t="s">
         <v>1166</v>
       </c>
     </row>
     <row r="209" customHeight="1" spans="1:12">
       <c r="A209" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>1167</v>
@@ -11275,7 +11248,7 @@
       <c r="F209" s="1">
         <v>5</v>
       </c>
-      <c r="G209" s="7" t="s">
+      <c r="G209" s="8" t="s">
         <v>1169</v>
       </c>
       <c r="H209" s="1" t="s">
@@ -11284,22 +11257,22 @@
       <c r="I209" s="1">
         <v>0</v>
       </c>
-      <c r="J209" s="9" t="s">
+      <c r="J209" s="11" t="s">
         <v>1155</v>
       </c>
-      <c r="K209" s="9" t="s">
+      <c r="K209" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L209" s="8" t="s">
+      <c r="L209" s="10" t="s">
         <v>1171</v>
       </c>
     </row>
     <row r="210" customHeight="1" spans="1:12">
       <c r="A210" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>1172</v>
@@ -11313,7 +11286,7 @@
       <c r="F210" s="1">
         <v>5</v>
       </c>
-      <c r="G210" s="7" t="s">
+      <c r="G210" s="8" t="s">
         <v>1174</v>
       </c>
       <c r="H210" s="1" t="s">
@@ -11322,22 +11295,22 @@
       <c r="I210" s="1">
         <v>0</v>
       </c>
-      <c r="J210" s="9" t="s">
+      <c r="J210" s="11" t="s">
         <v>1155</v>
       </c>
-      <c r="K210" s="9" t="s">
+      <c r="K210" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L210" s="8" t="s">
+      <c r="L210" s="10" t="s">
         <v>1176</v>
       </c>
     </row>
     <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A211" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>1177</v>
@@ -11351,7 +11324,7 @@
       <c r="F211" s="1">
         <v>5</v>
       </c>
-      <c r="G211" s="7" t="s">
+      <c r="G211" s="8" t="s">
         <v>1179</v>
       </c>
       <c r="H211" s="1" t="s">
@@ -11360,22 +11333,22 @@
       <c r="I211" s="1">
         <v>0</v>
       </c>
-      <c r="J211" s="9" t="s">
+      <c r="J211" s="11" t="s">
         <v>1181</v>
       </c>
-      <c r="K211" s="9" t="s">
+      <c r="K211" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L211" s="8" t="s">
+      <c r="L211" s="10" t="s">
         <v>1182</v>
       </c>
     </row>
     <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A212" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>1183</v>
@@ -11389,7 +11362,7 @@
       <c r="F212" s="1">
         <v>5</v>
       </c>
-      <c r="G212" s="7" t="s">
+      <c r="G212" s="8" t="s">
         <v>1185</v>
       </c>
       <c r="H212" s="1" t="s">
@@ -11398,22 +11371,22 @@
       <c r="I212" s="1">
         <v>0</v>
       </c>
-      <c r="J212" s="9" t="s">
+      <c r="J212" s="11" t="s">
         <v>1181</v>
       </c>
-      <c r="K212" s="9" t="s">
+      <c r="K212" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L212" s="8" t="s">
+      <c r="L212" s="10" t="s">
         <v>1187</v>
       </c>
     </row>
     <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A213" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>1188</v>
@@ -11427,7 +11400,7 @@
       <c r="F213" s="1">
         <v>5</v>
       </c>
-      <c r="G213" s="7" t="s">
+      <c r="G213" s="8" t="s">
         <v>1190</v>
       </c>
       <c r="H213" s="1" t="s">
@@ -11436,22 +11409,22 @@
       <c r="I213" s="1">
         <v>0</v>
       </c>
-      <c r="J213" s="9" t="s">
+      <c r="J213" s="11" t="s">
         <v>1181</v>
       </c>
-      <c r="K213" s="9" t="s">
+      <c r="K213" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L213" s="8" t="s">
+      <c r="L213" s="10" t="s">
         <v>1192</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A214" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>1193</v>
@@ -11465,7 +11438,7 @@
       <c r="F214" s="1">
         <v>5</v>
       </c>
-      <c r="G214" s="7" t="s">
+      <c r="G214" s="8" t="s">
         <v>1195</v>
       </c>
       <c r="H214" s="1" t="s">
@@ -11474,22 +11447,22 @@
       <c r="I214" s="1">
         <v>0</v>
       </c>
-      <c r="J214" s="9" t="s">
+      <c r="J214" s="11" t="s">
         <v>1181</v>
       </c>
-      <c r="K214" s="9" t="s">
+      <c r="K214" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L214" s="8" t="s">
+      <c r="L214" s="10" t="s">
         <v>1197</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A215" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>1198</v>
@@ -11503,7 +11476,7 @@
       <c r="F215" s="1">
         <v>5</v>
       </c>
-      <c r="G215" s="7" t="s">
+      <c r="G215" s="8" t="s">
         <v>1200</v>
       </c>
       <c r="H215" s="1" t="s">
@@ -11512,13 +11485,13 @@
       <c r="I215" s="1">
         <v>0</v>
       </c>
-      <c r="J215" s="9" t="s">
+      <c r="J215" s="11" t="s">
         <v>1181</v>
       </c>
-      <c r="K215" s="9" t="s">
+      <c r="K215" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="L215" s="8" t="s">
+      <c r="L215" s="10" t="s">
         <v>1202</v>
       </c>
     </row>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="1203">
   <si>
     <t>_Id</t>
   </si>
@@ -3433,85 +3433,85 @@
     <t>10194</t>
   </si>
   <si>
+    <t>1195</t>
+  </si>
+  <si>
+    <t>混沌魔禁地</t>
+  </si>
+  <si>
+    <t>2000-1</t>
+  </si>
+  <si>
+    <t>混沌宝甲</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210081,1009,505,506,202003</t>
+  </si>
+  <si>
+    <t>10195</t>
+  </si>
+  <si>
+    <t>1196</t>
+  </si>
+  <si>
+    <t>混沌魔神殿</t>
+  </si>
+  <si>
+    <t>2000-2</t>
+  </si>
+  <si>
+    <t>混沌号角</t>
+  </si>
+  <si>
+    <t>10196</t>
+  </si>
+  <si>
+    <t>1197</t>
+  </si>
+  <si>
+    <t>混沌邪禁地</t>
+  </si>
+  <si>
+    <t>2000-3</t>
+  </si>
+  <si>
+    <t>混沌雕像</t>
+  </si>
+  <si>
+    <t>10197</t>
+  </si>
+  <si>
+    <t>1198</t>
+  </si>
+  <si>
+    <t>混沌邪魔殿</t>
+  </si>
+  <si>
+    <t>2000-4</t>
+  </si>
+  <si>
+    <t>混沌神像</t>
+  </si>
+  <si>
+    <t>10198</t>
+  </si>
+  <si>
+    <t>1199</t>
+  </si>
+  <si>
+    <t>混沌封魔殿</t>
+  </si>
+  <si>
+    <t>2000-5</t>
+  </si>
+  <si>
+    <t>混沌獠牙</t>
+  </si>
+  <si>
+    <t>10199</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1195</t>
-  </si>
-  <si>
-    <t>混沌魔禁地</t>
-  </si>
-  <si>
-    <t>2000-1</t>
-  </si>
-  <si>
-    <t>混沌宝甲</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210081,1009,505,506,202003</t>
-  </si>
-  <si>
-    <t>10195</t>
-  </si>
-  <si>
-    <t>1196</t>
-  </si>
-  <si>
-    <t>混沌魔神殿</t>
-  </si>
-  <si>
-    <t>2000-2</t>
-  </si>
-  <si>
-    <t>混沌号角</t>
-  </si>
-  <si>
-    <t>10196</t>
-  </si>
-  <si>
-    <t>1197</t>
-  </si>
-  <si>
-    <t>混沌邪禁地</t>
-  </si>
-  <si>
-    <t>2000-3</t>
-  </si>
-  <si>
-    <t>混沌雕像</t>
-  </si>
-  <si>
-    <t>10197</t>
-  </si>
-  <si>
-    <t>1198</t>
-  </si>
-  <si>
-    <t>混沌邪魔殿</t>
-  </si>
-  <si>
-    <t>2000-4</t>
-  </si>
-  <si>
-    <t>混沌神像</t>
-  </si>
-  <si>
-    <t>10198</t>
-  </si>
-  <si>
-    <t>1199</t>
-  </si>
-  <si>
-    <t>混沌封魔殿</t>
-  </si>
-  <si>
-    <t>2000-5</t>
-  </si>
-  <si>
-    <t>混沌獠牙</t>
-  </si>
-  <si>
-    <t>10199</t>
   </si>
   <si>
     <t>1200</t>
@@ -10926,201 +10926,171 @@
       </c>
     </row>
     <row r="201" customHeight="1" spans="1:12">
-      <c r="A201" s="1" t="s">
+      <c r="C201" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C201" s="1" t="s">
+      <c r="D201" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="D201" s="2" t="s">
+      <c r="E201" s="1">
+        <v>5</v>
+      </c>
+      <c r="F201" s="1">
+        <v>5</v>
+      </c>
+      <c r="G201" s="8" t="s">
         <v>1126</v>
       </c>
-      <c r="E201" s="1">
-        <v>5</v>
-      </c>
-      <c r="F201" s="1">
-        <v>5</v>
-      </c>
-      <c r="G201" s="8" t="s">
+      <c r="H201" s="1" t="s">
         <v>1127</v>
-      </c>
-      <c r="H201" s="1" t="s">
-        <v>1128</v>
       </c>
       <c r="I201" s="1">
         <v>0</v>
       </c>
       <c r="J201" s="11" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="K201" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L201" s="10" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="202" customHeight="1" spans="1:12">
+      <c r="C202" s="1" t="s">
         <v>1130</v>
       </c>
-    </row>
-    <row r="202" customHeight="1" spans="1:12">
-      <c r="A202" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C202" s="1" t="s">
+      <c r="D202" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="D202" s="2" t="s">
+      <c r="E202" s="1">
+        <v>5</v>
+      </c>
+      <c r="F202" s="1">
+        <v>5</v>
+      </c>
+      <c r="G202" s="8" t="s">
         <v>1132</v>
       </c>
-      <c r="E202" s="1">
-        <v>5</v>
-      </c>
-      <c r="F202" s="1">
-        <v>5</v>
-      </c>
-      <c r="G202" s="8" t="s">
+      <c r="H202" s="1" t="s">
         <v>1133</v>
-      </c>
-      <c r="H202" s="1" t="s">
-        <v>1134</v>
       </c>
       <c r="I202" s="1">
         <v>0</v>
       </c>
       <c r="J202" s="11" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="K202" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L202" s="10" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="203" customHeight="1" spans="1:12">
+      <c r="C203" s="1" t="s">
         <v>1135</v>
       </c>
-    </row>
-    <row r="203" customHeight="1" spans="1:12">
-      <c r="A203" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C203" s="1" t="s">
+      <c r="D203" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="D203" s="2" t="s">
+      <c r="E203" s="1">
+        <v>5</v>
+      </c>
+      <c r="F203" s="1">
+        <v>5</v>
+      </c>
+      <c r="G203" s="8" t="s">
         <v>1137</v>
       </c>
-      <c r="E203" s="1">
-        <v>5</v>
-      </c>
-      <c r="F203" s="1">
-        <v>5</v>
-      </c>
-      <c r="G203" s="8" t="s">
+      <c r="H203" s="1" t="s">
         <v>1138</v>
-      </c>
-      <c r="H203" s="1" t="s">
-        <v>1139</v>
       </c>
       <c r="I203" s="1">
         <v>0</v>
       </c>
       <c r="J203" s="11" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="K203" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L203" s="10" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="204" customHeight="1" spans="1:12">
+      <c r="C204" s="1" t="s">
         <v>1140</v>
       </c>
-    </row>
-    <row r="204" customHeight="1" spans="1:12">
-      <c r="A204" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C204" s="1" t="s">
+      <c r="D204" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="D204" s="2" t="s">
+      <c r="E204" s="1">
+        <v>5</v>
+      </c>
+      <c r="F204" s="1">
+        <v>5</v>
+      </c>
+      <c r="G204" s="8" t="s">
         <v>1142</v>
       </c>
-      <c r="E204" s="1">
-        <v>5</v>
-      </c>
-      <c r="F204" s="1">
-        <v>5</v>
-      </c>
-      <c r="G204" s="8" t="s">
+      <c r="H204" s="1" t="s">
         <v>1143</v>
-      </c>
-      <c r="H204" s="1" t="s">
-        <v>1144</v>
       </c>
       <c r="I204" s="1">
         <v>0</v>
       </c>
       <c r="J204" s="11" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="K204" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L204" s="10" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="205" customHeight="1" spans="1:12">
+      <c r="C205" s="1" t="s">
         <v>1145</v>
       </c>
-    </row>
-    <row r="205" customHeight="1" spans="1:12">
-      <c r="A205" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C205" s="1" t="s">
+      <c r="D205" s="2" t="s">
         <v>1146</v>
       </c>
-      <c r="D205" s="2" t="s">
+      <c r="E205" s="1">
+        <v>5</v>
+      </c>
+      <c r="F205" s="1">
+        <v>5</v>
+      </c>
+      <c r="G205" s="8" t="s">
         <v>1147</v>
       </c>
-      <c r="E205" s="1">
-        <v>5</v>
-      </c>
-      <c r="F205" s="1">
-        <v>5</v>
-      </c>
-      <c r="G205" s="8" t="s">
+      <c r="H205" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="H205" s="1" t="s">
-        <v>1149</v>
       </c>
       <c r="I205" s="1">
         <v>0</v>
       </c>
       <c r="J205" s="11" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="K205" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L205" s="10" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="206" customHeight="1" spans="1:12">
       <c r="A206" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>1151</v>
@@ -11155,10 +11125,10 @@
     </row>
     <row r="207" customHeight="1" spans="1:12">
       <c r="A207" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>1157</v>
@@ -11193,10 +11163,10 @@
     </row>
     <row r="208" customHeight="1" spans="1:12">
       <c r="A208" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>1162</v>
@@ -11231,10 +11201,10 @@
     </row>
     <row r="209" customHeight="1" spans="1:12">
       <c r="A209" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>1167</v>
@@ -11269,10 +11239,10 @@
     </row>
     <row r="210" customHeight="1" spans="1:12">
       <c r="A210" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>1172</v>
@@ -11307,10 +11277,10 @@
     </row>
     <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A211" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>1177</v>
@@ -11345,10 +11315,10 @@
     </row>
     <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A212" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>1183</v>
@@ -11383,10 +11353,10 @@
     </row>
     <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A213" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>1188</v>
@@ -11421,10 +11391,10 @@
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A214" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>1193</v>
@@ -11459,10 +11429,10 @@
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A215" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1124</v>
+        <v>1150</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>1198</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="1203">
   <si>
     <t>_Id</t>
   </si>
@@ -3511,85 +3511,85 @@
     <t>10199</t>
   </si>
   <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>混沌烈焰殿</t>
+  </si>
+  <si>
+    <t>2050-1</t>
+  </si>
+  <si>
+    <t>混沌树心</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210082,1009,505,506,202003</t>
+  </si>
+  <si>
+    <t>10200</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>混沌封邪殿</t>
+  </si>
+  <si>
+    <t>2050-2</t>
+  </si>
+  <si>
+    <t>混沌魔心</t>
+  </si>
+  <si>
+    <t>10201</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>混沌尸魔殿</t>
+  </si>
+  <si>
+    <t>2050-3</t>
+  </si>
+  <si>
+    <t>混沌尸心</t>
+  </si>
+  <si>
+    <t>10202</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>混沌骨魔殿</t>
+  </si>
+  <si>
+    <t>2050-4</t>
+  </si>
+  <si>
+    <t>混沌法杖</t>
+  </si>
+  <si>
+    <t>10203</t>
+  </si>
+  <si>
+    <t>1204</t>
+  </si>
+  <si>
+    <t>混沌魔牛殿</t>
+  </si>
+  <si>
+    <t>2050-5</t>
+  </si>
+  <si>
+    <t>混沌权杖</t>
+  </si>
+  <si>
+    <t>10204</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>混沌烈焰殿</t>
-  </si>
-  <si>
-    <t>2050-1</t>
-  </si>
-  <si>
-    <t>混沌树心</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210082,1009,505,506,202003</t>
-  </si>
-  <si>
-    <t>10200</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>混沌封邪殿</t>
-  </si>
-  <si>
-    <t>2050-2</t>
-  </si>
-  <si>
-    <t>混沌魔心</t>
-  </si>
-  <si>
-    <t>10201</t>
-  </si>
-  <si>
-    <t>1202</t>
-  </si>
-  <si>
-    <t>混沌尸魔殿</t>
-  </si>
-  <si>
-    <t>2050-3</t>
-  </si>
-  <si>
-    <t>混沌尸心</t>
-  </si>
-  <si>
-    <t>10202</t>
-  </si>
-  <si>
-    <t>1203</t>
-  </si>
-  <si>
-    <t>混沌骨魔殿</t>
-  </si>
-  <si>
-    <t>2050-4</t>
-  </si>
-  <si>
-    <t>混沌法杖</t>
-  </si>
-  <si>
-    <t>10203</t>
-  </si>
-  <si>
-    <t>1204</t>
-  </si>
-  <si>
-    <t>混沌魔牛殿</t>
-  </si>
-  <si>
-    <t>2050-5</t>
-  </si>
-  <si>
-    <t>混沌权杖</t>
-  </si>
-  <si>
-    <t>10204</t>
   </si>
   <si>
     <t>1205</t>
@@ -10669,7 +10669,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="193" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="193" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C193" s="1" t="s">
         <v>1083</v>
       </c>
@@ -10701,7 +10701,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="194" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="194" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C194" s="1" t="s">
         <v>1088</v>
       </c>
@@ -10733,7 +10733,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="195" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="195" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C195" s="1" t="s">
         <v>1093</v>
       </c>
@@ -10765,7 +10765,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="196" s="4" customFormat="1" customHeight="1" spans="1:12">
+    <row r="196" s="4" customFormat="1" customHeight="1" spans="3:12">
       <c r="C196" s="4" t="s">
         <v>1098</v>
       </c>
@@ -10797,7 +10797,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="197" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="197" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C197" s="1" t="s">
         <v>1104</v>
       </c>
@@ -10829,7 +10829,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="198" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="198" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C198" s="1" t="s">
         <v>1109</v>
       </c>
@@ -10861,7 +10861,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="199" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="199" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C199" s="1" t="s">
         <v>1114</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="200" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="200" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C200" s="1" t="s">
         <v>1119</v>
       </c>
@@ -10925,7 +10925,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="201" customHeight="1" spans="1:12">
+    <row r="201" customHeight="1" spans="3:12">
       <c r="C201" s="1" t="s">
         <v>1124</v>
       </c>
@@ -10957,7 +10957,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="202" customHeight="1" spans="1:12">
+    <row r="202" customHeight="1" spans="3:12">
       <c r="C202" s="1" t="s">
         <v>1130</v>
       </c>
@@ -10989,7 +10989,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="203" customHeight="1" spans="1:12">
+    <row r="203" customHeight="1" spans="3:12">
       <c r="C203" s="1" t="s">
         <v>1135</v>
       </c>
@@ -11021,7 +11021,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="204" customHeight="1" spans="1:12">
+    <row r="204" customHeight="1" spans="3:12">
       <c r="C204" s="1" t="s">
         <v>1140</v>
       </c>
@@ -11053,7 +11053,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="205" customHeight="1" spans="1:12">
+    <row r="205" customHeight="1" spans="3:12">
       <c r="C205" s="1" t="s">
         <v>1145</v>
       </c>
@@ -11085,202 +11085,172 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="206" customHeight="1" spans="1:12">
-      <c r="A206" s="1" t="s">
+    <row r="206" customHeight="1" spans="3:12">
+      <c r="C206" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C206" s="1" t="s">
+      <c r="D206" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="D206" s="1" t="s">
+      <c r="E206" s="1">
+        <v>5</v>
+      </c>
+      <c r="F206" s="1">
+        <v>5</v>
+      </c>
+      <c r="G206" s="8" t="s">
         <v>1152</v>
       </c>
-      <c r="E206" s="1">
-        <v>5</v>
-      </c>
-      <c r="F206" s="1">
-        <v>5</v>
-      </c>
-      <c r="G206" s="8" t="s">
+      <c r="H206" s="1" t="s">
         <v>1153</v>
-      </c>
-      <c r="H206" s="1" t="s">
-        <v>1154</v>
       </c>
       <c r="I206" s="1">
         <v>0</v>
       </c>
       <c r="J206" s="11" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K206" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L206" s="10" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="207" customHeight="1" spans="3:12">
+      <c r="C207" s="1" t="s">
         <v>1156</v>
       </c>
-    </row>
-    <row r="207" customHeight="1" spans="1:12">
-      <c r="A207" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C207" s="1" t="s">
+      <c r="D207" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="D207" s="1" t="s">
+      <c r="E207" s="1">
+        <v>5</v>
+      </c>
+      <c r="F207" s="1">
+        <v>5</v>
+      </c>
+      <c r="G207" s="8" t="s">
         <v>1158</v>
       </c>
-      <c r="E207" s="1">
-        <v>5</v>
-      </c>
-      <c r="F207" s="1">
-        <v>5</v>
-      </c>
-      <c r="G207" s="8" t="s">
+      <c r="H207" s="1" t="s">
         <v>1159</v>
-      </c>
-      <c r="H207" s="1" t="s">
-        <v>1160</v>
       </c>
       <c r="I207" s="1">
         <v>0</v>
       </c>
       <c r="J207" s="11" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K207" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L207" s="10" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="208" customHeight="1" spans="3:12">
+      <c r="C208" s="1" t="s">
         <v>1161</v>
       </c>
-    </row>
-    <row r="208" customHeight="1" spans="1:12">
-      <c r="A208" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C208" s="1" t="s">
+      <c r="D208" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="E208" s="1">
+        <v>5</v>
+      </c>
+      <c r="F208" s="1">
+        <v>5</v>
+      </c>
+      <c r="G208" s="8" t="s">
         <v>1163</v>
       </c>
-      <c r="E208" s="1">
-        <v>5</v>
-      </c>
-      <c r="F208" s="1">
-        <v>5</v>
-      </c>
-      <c r="G208" s="8" t="s">
+      <c r="H208" s="1" t="s">
         <v>1164</v>
-      </c>
-      <c r="H208" s="1" t="s">
-        <v>1165</v>
       </c>
       <c r="I208" s="1">
         <v>0</v>
       </c>
       <c r="J208" s="11" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K208" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L208" s="10" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="209" customHeight="1" spans="1:12">
+      <c r="C209" s="1" t="s">
         <v>1166</v>
       </c>
-    </row>
-    <row r="209" customHeight="1" spans="1:12">
-      <c r="A209" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C209" s="1" t="s">
+      <c r="D209" s="1" t="s">
         <v>1167</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="E209" s="1">
+        <v>5</v>
+      </c>
+      <c r="F209" s="1">
+        <v>5</v>
+      </c>
+      <c r="G209" s="8" t="s">
         <v>1168</v>
       </c>
-      <c r="E209" s="1">
-        <v>5</v>
-      </c>
-      <c r="F209" s="1">
-        <v>5</v>
-      </c>
-      <c r="G209" s="8" t="s">
+      <c r="H209" s="1" t="s">
         <v>1169</v>
-      </c>
-      <c r="H209" s="1" t="s">
-        <v>1170</v>
       </c>
       <c r="I209" s="1">
         <v>0</v>
       </c>
       <c r="J209" s="11" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K209" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L209" s="10" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="210" customHeight="1" spans="1:12">
+      <c r="C210" s="1" t="s">
         <v>1171</v>
       </c>
-    </row>
-    <row r="210" customHeight="1" spans="1:12">
-      <c r="A210" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C210" s="1" t="s">
+      <c r="D210" s="1" t="s">
         <v>1172</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="E210" s="1">
+        <v>5</v>
+      </c>
+      <c r="F210" s="1">
+        <v>5</v>
+      </c>
+      <c r="G210" s="8" t="s">
         <v>1173</v>
       </c>
-      <c r="E210" s="1">
-        <v>5</v>
-      </c>
-      <c r="F210" s="1">
-        <v>5</v>
-      </c>
-      <c r="G210" s="8" t="s">
+      <c r="H210" s="1" t="s">
         <v>1174</v>
-      </c>
-      <c r="H210" s="1" t="s">
-        <v>1175</v>
       </c>
       <c r="I210" s="1">
         <v>0</v>
       </c>
       <c r="J210" s="11" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K210" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L210" s="10" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A211" s="1" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>1177</v>
@@ -11315,10 +11285,10 @@
     </row>
     <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A212" s="1" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>1183</v>
@@ -11353,10 +11323,10 @@
     </row>
     <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A213" s="1" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>1188</v>
@@ -11391,10 +11361,10 @@
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A214" s="1" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>1193</v>
@@ -11429,10 +11399,10 @@
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A215" s="1" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1150</v>
+        <v>1176</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>1198</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1202">
   <si>
     <t>_Id</t>
   </si>
@@ -3587,9 +3587,6 @@
   </si>
   <si>
     <t>10204</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>1205</t>
@@ -4693,7 +4690,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M215"/>
+  <dimension ref="B3:M215"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
@@ -11181,7 +11178,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="209" customHeight="1" spans="1:12">
+    <row r="209" customHeight="1" spans="3:12">
       <c r="C209" s="1" t="s">
         <v>1166</v>
       </c>
@@ -11213,7 +11210,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="210" customHeight="1" spans="1:12">
+    <row r="210" customHeight="1" spans="3:12">
       <c r="C210" s="1" t="s">
         <v>1171</v>
       </c>
@@ -11245,194 +11242,164 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A211" s="1" t="s">
+    <row r="211" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C211" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C211" s="1" t="s">
+      <c r="D211" s="1" t="s">
         <v>1177</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="E211" s="1">
+        <v>5</v>
+      </c>
+      <c r="F211" s="1">
+        <v>5</v>
+      </c>
+      <c r="G211" s="8" t="s">
         <v>1178</v>
       </c>
-      <c r="E211" s="1">
-        <v>5</v>
-      </c>
-      <c r="F211" s="1">
-        <v>5</v>
-      </c>
-      <c r="G211" s="8" t="s">
+      <c r="H211" s="1" t="s">
         <v>1179</v>
-      </c>
-      <c r="H211" s="1" t="s">
-        <v>1180</v>
       </c>
       <c r="I211" s="1">
         <v>0</v>
       </c>
       <c r="J211" s="11" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="K211" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L211" s="10" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C212" s="1" t="s">
         <v>1182</v>
       </c>
-    </row>
-    <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A212" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C212" s="1" t="s">
+      <c r="D212" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="E212" s="1">
+        <v>5</v>
+      </c>
+      <c r="F212" s="1">
+        <v>5</v>
+      </c>
+      <c r="G212" s="8" t="s">
         <v>1184</v>
       </c>
-      <c r="E212" s="1">
-        <v>5</v>
-      </c>
-      <c r="F212" s="1">
-        <v>5</v>
-      </c>
-      <c r="G212" s="8" t="s">
+      <c r="H212" s="1" t="s">
         <v>1185</v>
-      </c>
-      <c r="H212" s="1" t="s">
-        <v>1186</v>
       </c>
       <c r="I212" s="1">
         <v>0</v>
       </c>
       <c r="J212" s="11" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="K212" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L212" s="10" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="213" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C213" s="1" t="s">
         <v>1187</v>
       </c>
-    </row>
-    <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A213" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C213" s="1" t="s">
+      <c r="D213" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="E213" s="1">
+        <v>5</v>
+      </c>
+      <c r="F213" s="1">
+        <v>5</v>
+      </c>
+      <c r="G213" s="8" t="s">
         <v>1189</v>
       </c>
-      <c r="E213" s="1">
-        <v>5</v>
-      </c>
-      <c r="F213" s="1">
-        <v>5</v>
-      </c>
-      <c r="G213" s="8" t="s">
+      <c r="H213" s="1" t="s">
         <v>1190</v>
-      </c>
-      <c r="H213" s="1" t="s">
-        <v>1191</v>
       </c>
       <c r="I213" s="1">
         <v>0</v>
       </c>
       <c r="J213" s="11" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="K213" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L213" s="10" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="214" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C214" s="1" t="s">
         <v>1192</v>
       </c>
-    </row>
-    <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A214" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C214" s="1" t="s">
+      <c r="D214" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="E214" s="1">
+        <v>5</v>
+      </c>
+      <c r="F214" s="1">
+        <v>5</v>
+      </c>
+      <c r="G214" s="8" t="s">
         <v>1194</v>
       </c>
-      <c r="E214" s="1">
-        <v>5</v>
-      </c>
-      <c r="F214" s="1">
-        <v>5</v>
-      </c>
-      <c r="G214" s="8" t="s">
+      <c r="H214" s="1" t="s">
         <v>1195</v>
-      </c>
-      <c r="H214" s="1" t="s">
-        <v>1196</v>
       </c>
       <c r="I214" s="1">
         <v>0</v>
       </c>
       <c r="J214" s="11" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="K214" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L214" s="10" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="215" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C215" s="1" t="s">
         <v>1197</v>
       </c>
-    </row>
-    <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A215" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C215" s="1" t="s">
+      <c r="D215" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="E215" s="1">
+        <v>5</v>
+      </c>
+      <c r="F215" s="1">
+        <v>5</v>
+      </c>
+      <c r="G215" s="8" t="s">
         <v>1199</v>
       </c>
-      <c r="E215" s="1">
-        <v>5</v>
-      </c>
-      <c r="F215" s="1">
-        <v>5</v>
-      </c>
-      <c r="G215" s="8" t="s">
+      <c r="H215" s="1" t="s">
         <v>1200</v>
-      </c>
-      <c r="H215" s="1" t="s">
-        <v>1201</v>
       </c>
       <c r="I215" s="1">
         <v>0</v>
       </c>
       <c r="J215" s="11" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="K215" s="11" t="s">
         <v>1020</v>
       </c>
       <c r="L215" s="10" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="1202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="1222">
   <si>
     <t>_Id</t>
   </si>
@@ -3665,6 +3665,66 @@
   </si>
   <si>
     <t>10209</t>
+  </si>
+  <si>
+    <t>虚无小村</t>
+  </si>
+  <si>
+    <t>2150-1</t>
+  </si>
+  <si>
+    <t>粉色专属</t>
+  </si>
+  <si>
+    <t>10210</t>
+  </si>
+  <si>
+    <t>虚无村外</t>
+  </si>
+  <si>
+    <t>2150-2</t>
+  </si>
+  <si>
+    <t>虚无鹿茸</t>
+  </si>
+  <si>
+    <t>10211</t>
+  </si>
+  <si>
+    <t>虚无农场</t>
+  </si>
+  <si>
+    <t>2150-3</t>
+  </si>
+  <si>
+    <t>虚无草帽</t>
+  </si>
+  <si>
+    <t>10212</t>
+  </si>
+  <si>
+    <t>虚无老城</t>
+  </si>
+  <si>
+    <t>2150-4</t>
+  </si>
+  <si>
+    <t>虚无猫爪</t>
+  </si>
+  <si>
+    <t>10213</t>
+  </si>
+  <si>
+    <t>虚无森林</t>
+  </si>
+  <si>
+    <t>2150-5</t>
+  </si>
+  <si>
+    <t>虚无花朵</t>
+  </si>
+  <si>
+    <t>10214</t>
   </si>
 </sst>
 </file>
@@ -3843,12 +3903,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4314,7 +4374,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4329,6 +4389,7 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -4690,7 +4751,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:M215"/>
+  <dimension ref="B3:M220"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
@@ -6003,10 +6064,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="10" t="s">
+      <c r="J46" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="10" t="s">
+      <c r="K46" s="11" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -6032,10 +6093,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="10" t="s">
+      <c r="J47" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="10" t="s">
+      <c r="K47" s="11" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -6061,10 +6122,10 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="10" t="s">
+      <c r="J48" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="10" t="s">
+      <c r="K48" s="11" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
@@ -6090,10 +6151,10 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="10" t="s">
+      <c r="J49" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="10" t="s">
+      <c r="K49" s="11" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
@@ -6119,10 +6180,10 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="10" t="s">
+      <c r="J50" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="10" t="s">
+      <c r="K50" s="11" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
@@ -6151,10 +6212,10 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="10" t="s">
+      <c r="J51" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="10" t="s">
+      <c r="K51" s="11" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
@@ -6180,10 +6241,10 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="10" t="s">
+      <c r="J52" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="10" t="s">
+      <c r="K52" s="11" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -6209,10 +6270,10 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="10" t="s">
+      <c r="J53" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="10" t="s">
+      <c r="K53" s="11" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
@@ -6238,10 +6299,10 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="10" t="s">
+      <c r="J54" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="10" t="s">
+      <c r="K54" s="11" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
@@ -6267,10 +6328,10 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="10" t="s">
+      <c r="J55" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="10" t="s">
+      <c r="K55" s="11" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -6299,10 +6360,10 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="10" t="s">
+      <c r="J56" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="10" t="s">
+      <c r="K56" s="11" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
@@ -6331,10 +6392,10 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="10" t="s">
+      <c r="J57" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="10" t="s">
+      <c r="K57" s="11" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
@@ -6363,10 +6424,10 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="10" t="s">
+      <c r="J58" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="10" t="s">
+      <c r="K58" s="11" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -6395,10 +6456,10 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="10" t="s">
+      <c r="J59" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="10" t="s">
+      <c r="K59" s="11" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
@@ -6427,10 +6488,10 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="10" t="s">
+      <c r="J60" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="10" t="s">
+      <c r="K60" s="11" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -6460,10 +6521,10 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="J61" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="11" t="s">
+      <c r="K61" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -6493,10 +6554,10 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="11" t="s">
+      <c r="J62" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="11" t="s">
+      <c r="K62" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -6526,10 +6587,10 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="11" t="s">
+      <c r="J63" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="11" t="s">
+      <c r="K63" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
@@ -6559,10 +6620,10 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="11" t="s">
+      <c r="J64" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="11" t="s">
+      <c r="K64" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
@@ -6592,10 +6653,10 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="11" t="s">
+      <c r="J65" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="11" t="s">
+      <c r="K65" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
@@ -6624,10 +6685,10 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="11" t="s">
+      <c r="J66" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="11" t="s">
+      <c r="K66" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
@@ -6656,10 +6717,10 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="11" t="s">
+      <c r="J67" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="11" t="s">
+      <c r="K67" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
@@ -6688,10 +6749,10 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="11" t="s">
+      <c r="J68" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="11" t="s">
+      <c r="K68" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -6720,10 +6781,10 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="11" t="s">
+      <c r="J69" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="11" t="s">
+      <c r="K69" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
@@ -6752,10 +6813,10 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="11" t="s">
+      <c r="J70" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="11" t="s">
+      <c r="K70" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
@@ -6784,10 +6845,10 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="11" t="s">
+      <c r="J71" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="11" t="s">
+      <c r="K71" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -6816,10 +6877,10 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="11" t="s">
+      <c r="J72" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="11" t="s">
+      <c r="K72" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -6848,10 +6909,10 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="11" t="s">
+      <c r="J73" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="11" t="s">
+      <c r="K73" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -6880,10 +6941,10 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="11" t="s">
+      <c r="J74" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="11" t="s">
+      <c r="K74" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
@@ -6912,10 +6973,10 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="11" t="s">
+      <c r="J75" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="11" t="s">
+      <c r="K75" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
@@ -6944,10 +7005,10 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="11" t="s">
+      <c r="J76" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="11" t="s">
+      <c r="K76" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
@@ -6976,10 +7037,10 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="11" t="s">
+      <c r="J77" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="11" t="s">
+      <c r="K77" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
@@ -7008,10 +7069,10 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="11" t="s">
+      <c r="J78" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="11" t="s">
+      <c r="K78" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
@@ -7040,10 +7101,10 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="11" t="s">
+      <c r="J79" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="11" t="s">
+      <c r="K79" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
@@ -7072,10 +7133,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="11" t="s">
+      <c r="J80" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="11" t="s">
+      <c r="K80" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -7104,10 +7165,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="11" t="s">
+      <c r="J81" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="K81" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -7136,10 +7197,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="11" t="s">
+      <c r="J82" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="11" t="s">
+      <c r="K82" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -7168,10 +7229,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="11" t="s">
+      <c r="J83" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="11" t="s">
+      <c r="K83" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -7200,10 +7261,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="11" t="s">
+      <c r="J84" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="11" t="s">
+      <c r="K84" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -7232,10 +7293,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="11" t="s">
+      <c r="J85" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="11" t="s">
+      <c r="K85" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -7264,10 +7325,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="11" t="s">
+      <c r="J86" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="11" t="s">
+      <c r="K86" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -7296,10 +7357,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="11" t="s">
+      <c r="J87" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="11" t="s">
+      <c r="K87" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -7328,10 +7389,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="11" t="s">
+      <c r="J88" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="11" t="s">
+      <c r="K88" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -7360,10 +7421,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="11" t="s">
+      <c r="J89" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="11" t="s">
+      <c r="K89" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -7392,10 +7453,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="11" t="s">
+      <c r="J90" s="12" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="11" t="s">
+      <c r="K90" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -7424,10 +7485,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="11" t="s">
+      <c r="J91" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="11" t="s">
+      <c r="K91" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -7456,10 +7517,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="11" t="s">
+      <c r="J92" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="11" t="s">
+      <c r="K92" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -7488,10 +7549,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="11" t="s">
+      <c r="J93" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="11" t="s">
+      <c r="K93" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -7520,10 +7581,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="11" t="s">
+      <c r="J94" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="11" t="s">
+      <c r="K94" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -7552,10 +7613,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="11" t="s">
+      <c r="J95" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="11" t="s">
+      <c r="K95" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -7584,10 +7645,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="11" t="s">
+      <c r="J96" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="11" t="s">
+      <c r="K96" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -7616,10 +7677,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="11" t="s">
+      <c r="J97" s="12" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="11" t="s">
+      <c r="K97" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -7648,10 +7709,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="11" t="s">
+      <c r="J98" s="12" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="11" t="s">
+      <c r="K98" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -7680,10 +7741,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="11" t="s">
+      <c r="J99" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="11" t="s">
+      <c r="K99" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -7712,10 +7773,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="11" t="s">
+      <c r="J100" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="11" t="s">
+      <c r="K100" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -7744,10 +7805,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="11" t="s">
+      <c r="J101" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="11" t="s">
+      <c r="K101" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -7776,10 +7837,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="11" t="s">
+      <c r="J102" s="12" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="11" t="s">
+      <c r="K102" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -7808,10 +7869,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="11" t="s">
+      <c r="J103" s="12" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="11" t="s">
+      <c r="K103" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -7840,10 +7901,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="11" t="s">
+      <c r="J104" s="12" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="11" t="s">
+      <c r="K104" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -7872,10 +7933,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="11" t="s">
+      <c r="J105" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="11" t="s">
+      <c r="K105" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -7904,10 +7965,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="11" t="s">
+      <c r="J106" s="12" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="11" t="s">
+      <c r="K106" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -7936,10 +7997,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="11" t="s">
+      <c r="J107" s="12" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="11" t="s">
+      <c r="K107" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -7968,10 +8029,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="11" t="s">
+      <c r="J108" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="11" t="s">
+      <c r="K108" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -8000,10 +8061,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="11" t="s">
+      <c r="J109" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="11" t="s">
+      <c r="K109" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -8032,10 +8093,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="11" t="s">
+      <c r="J110" s="12" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="11" t="s">
+      <c r="K110" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -8064,10 +8125,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="11" t="s">
+      <c r="J111" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="11" t="s">
+      <c r="K111" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -8096,10 +8157,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="11" t="s">
+      <c r="J112" s="12" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="11" t="s">
+      <c r="K112" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -8128,10 +8189,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="11" t="s">
+      <c r="J113" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="11" t="s">
+      <c r="K113" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -8160,10 +8221,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="11" t="s">
+      <c r="J114" s="12" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="11" t="s">
+      <c r="K114" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -8192,10 +8253,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="11" t="s">
+      <c r="J115" s="12" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="11" t="s">
+      <c r="K115" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -8224,10 +8285,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="11" t="s">
+      <c r="J116" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="11" t="s">
+      <c r="K116" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -8256,10 +8317,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="11" t="s">
+      <c r="J117" s="12" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="11" t="s">
+      <c r="K117" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -8288,10 +8349,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="11" t="s">
+      <c r="J118" s="12" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="11" t="s">
+      <c r="K118" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -8320,10 +8381,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="11" t="s">
+      <c r="J119" s="12" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="11" t="s">
+      <c r="K119" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -8352,10 +8413,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="11" t="s">
+      <c r="J120" s="12" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="11" t="s">
+      <c r="K120" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -8384,10 +8445,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="11" t="s">
+      <c r="J121" s="12" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="11" t="s">
+      <c r="K121" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -8416,10 +8477,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="11" t="s">
+      <c r="J122" s="12" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="11" t="s">
+      <c r="K122" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -8448,10 +8509,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="11" t="s">
+      <c r="J123" s="12" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="11" t="s">
+      <c r="K123" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -8480,10 +8541,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="11" t="s">
+      <c r="J124" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="11" t="s">
+      <c r="K124" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -8512,10 +8573,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="11" t="s">
+      <c r="J125" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="11" t="s">
+      <c r="K125" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -8544,10 +8605,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="11" t="s">
+      <c r="J126" s="12" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="11" t="s">
+      <c r="K126" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -8576,10 +8637,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="11" t="s">
+      <c r="J127" s="12" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="11" t="s">
+      <c r="K127" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -8608,10 +8669,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="11" t="s">
+      <c r="J128" s="12" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="11" t="s">
+      <c r="K128" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -8640,10 +8701,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="11" t="s">
+      <c r="J129" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="11" t="s">
+      <c r="K129" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -8672,10 +8733,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="11" t="s">
+      <c r="J130" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="11" t="s">
+      <c r="K130" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -8704,10 +8765,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="11" t="s">
+      <c r="J131" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="11" t="s">
+      <c r="K131" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -8736,10 +8797,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="11" t="s">
+      <c r="J132" s="12" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="11" t="s">
+      <c r="K132" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -8768,10 +8829,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="11" t="s">
+      <c r="J133" s="12" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="11" t="s">
+      <c r="K133" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -8800,10 +8861,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="11" t="s">
+      <c r="J134" s="12" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="11" t="s">
+      <c r="K134" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -8832,10 +8893,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="11" t="s">
+      <c r="J135" s="12" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="11" t="s">
+      <c r="K135" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -8864,10 +8925,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="11" t="s">
+      <c r="J136" s="12" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="11" t="s">
+      <c r="K136" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -8896,10 +8957,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="11" t="s">
+      <c r="J137" s="12" t="s">
         <v>782</v>
       </c>
-      <c r="K137" s="11" t="s">
+      <c r="K137" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -8928,10 +8989,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="11" t="s">
+      <c r="J138" s="12" t="s">
         <v>788</v>
       </c>
-      <c r="K138" s="11" t="s">
+      <c r="K138" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -8960,10 +9021,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="11" t="s">
+      <c r="J139" s="12" t="s">
         <v>794</v>
       </c>
-      <c r="K139" s="11" t="s">
+      <c r="K139" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -8992,10 +9053,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="11" t="s">
+      <c r="J140" s="12" t="s">
         <v>800</v>
       </c>
-      <c r="K140" s="11" t="s">
+      <c r="K140" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -9024,10 +9085,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="11" t="s">
+      <c r="J141" s="12" t="s">
         <v>806</v>
       </c>
-      <c r="K141" s="11" t="s">
+      <c r="K141" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -9056,10 +9117,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="11" t="s">
+      <c r="J142" s="12" t="s">
         <v>812</v>
       </c>
-      <c r="K142" s="11" t="s">
+      <c r="K142" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -9088,10 +9149,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="11" t="s">
+      <c r="J143" s="12" t="s">
         <v>818</v>
       </c>
-      <c r="K143" s="11" t="s">
+      <c r="K143" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -9120,10 +9181,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="11" t="s">
+      <c r="J144" s="12" t="s">
         <v>824</v>
       </c>
-      <c r="K144" s="11" t="s">
+      <c r="K144" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -9152,10 +9213,10 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="11" t="s">
+      <c r="J145" s="12" t="s">
         <v>830</v>
       </c>
-      <c r="K145" s="11" t="s">
+      <c r="K145" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
@@ -9184,13 +9245,13 @@
       <c r="I146" s="3">
         <v>0</v>
       </c>
-      <c r="J146" s="12" t="s">
+      <c r="J146" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K146" s="12" t="s">
+      <c r="K146" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L146" s="12" t="s">
+      <c r="L146" s="13" t="s">
         <v>837</v>
       </c>
     </row>
@@ -9216,13 +9277,13 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="11" t="s">
+      <c r="J147" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="K147" s="11" t="s">
+      <c r="K147" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L147" s="10" t="s">
+      <c r="L147" s="11" t="s">
         <v>842</v>
       </c>
     </row>
@@ -9248,13 +9309,13 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="11" t="s">
+      <c r="J148" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="K148" s="11" t="s">
+      <c r="K148" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L148" s="10" t="s">
+      <c r="L148" s="11" t="s">
         <v>847</v>
       </c>
     </row>
@@ -9280,13 +9341,13 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="11" t="s">
+      <c r="J149" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="K149" s="11" t="s">
+      <c r="K149" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L149" s="10" t="s">
+      <c r="L149" s="11" t="s">
         <v>852</v>
       </c>
     </row>
@@ -9312,13 +9373,13 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="11" t="s">
+      <c r="J150" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="K150" s="11" t="s">
+      <c r="K150" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L150" s="10" t="s">
+      <c r="L150" s="11" t="s">
         <v>857</v>
       </c>
     </row>
@@ -9344,13 +9405,13 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="11" t="s">
+      <c r="J151" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="K151" s="11" t="s">
+      <c r="K151" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L151" s="10" t="s">
+      <c r="L151" s="11" t="s">
         <v>863</v>
       </c>
     </row>
@@ -9376,13 +9437,13 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="11" t="s">
+      <c r="J152" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="K152" s="11" t="s">
+      <c r="K152" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L152" s="10" t="s">
+      <c r="L152" s="11" t="s">
         <v>868</v>
       </c>
     </row>
@@ -9408,13 +9469,13 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="11" t="s">
+      <c r="J153" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="K153" s="11" t="s">
+      <c r="K153" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L153" s="10" t="s">
+      <c r="L153" s="11" t="s">
         <v>873</v>
       </c>
     </row>
@@ -9440,13 +9501,13 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="11" t="s">
+      <c r="J154" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="K154" s="11" t="s">
+      <c r="K154" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L154" s="10" t="s">
+      <c r="L154" s="11" t="s">
         <v>878</v>
       </c>
     </row>
@@ -9472,13 +9533,13 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="11" t="s">
+      <c r="J155" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="K155" s="11" t="s">
+      <c r="K155" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L155" s="10" t="s">
+      <c r="L155" s="11" t="s">
         <v>883</v>
       </c>
     </row>
@@ -9504,13 +9565,13 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="11" t="s">
+      <c r="J156" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="K156" s="11" t="s">
+      <c r="K156" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L156" s="10" t="s">
+      <c r="L156" s="11" t="s">
         <v>889</v>
       </c>
     </row>
@@ -9536,13 +9597,13 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="11" t="s">
+      <c r="J157" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="K157" s="11" t="s">
+      <c r="K157" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L157" s="10" t="s">
+      <c r="L157" s="11" t="s">
         <v>894</v>
       </c>
     </row>
@@ -9568,13 +9629,13 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="11" t="s">
+      <c r="J158" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="11" t="s">
+      <c r="K158" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L158" s="10" t="s">
+      <c r="L158" s="11" t="s">
         <v>899</v>
       </c>
     </row>
@@ -9600,13 +9661,13 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="11" t="s">
+      <c r="J159" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="K159" s="11" t="s">
+      <c r="K159" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L159" s="10" t="s">
+      <c r="L159" s="11" t="s">
         <v>904</v>
       </c>
     </row>
@@ -9632,13 +9693,13 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="11" t="s">
+      <c r="J160" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="K160" s="11" t="s">
+      <c r="K160" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L160" s="10" t="s">
+      <c r="L160" s="11" t="s">
         <v>909</v>
       </c>
     </row>
@@ -9664,13 +9725,13 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="11" t="s">
+      <c r="J161" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="K161" s="11" t="s">
+      <c r="K161" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L161" s="10" t="s">
+      <c r="L161" s="11" t="s">
         <v>915</v>
       </c>
     </row>
@@ -9696,13 +9757,13 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="11" t="s">
+      <c r="J162" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="K162" s="11" t="s">
+      <c r="K162" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L162" s="10" t="s">
+      <c r="L162" s="11" t="s">
         <v>920</v>
       </c>
     </row>
@@ -9728,13 +9789,13 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="11" t="s">
+      <c r="J163" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="K163" s="11" t="s">
+      <c r="K163" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L163" s="10" t="s">
+      <c r="L163" s="11" t="s">
         <v>925</v>
       </c>
     </row>
@@ -9760,13 +9821,13 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="11" t="s">
+      <c r="J164" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="K164" s="11" t="s">
+      <c r="K164" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L164" s="10" t="s">
+      <c r="L164" s="11" t="s">
         <v>930</v>
       </c>
     </row>
@@ -9792,13 +9853,13 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="11" t="s">
+      <c r="J165" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="K165" s="11" t="s">
+      <c r="K165" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L165" s="10" t="s">
+      <c r="L165" s="11" t="s">
         <v>935</v>
       </c>
     </row>
@@ -9824,13 +9885,13 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="11" t="s">
+      <c r="J166" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="K166" s="11" t="s">
+      <c r="K166" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L166" s="10" t="s">
+      <c r="L166" s="11" t="s">
         <v>941</v>
       </c>
     </row>
@@ -9856,13 +9917,13 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="11" t="s">
+      <c r="J167" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="K167" s="11" t="s">
+      <c r="K167" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L167" s="10" t="s">
+      <c r="L167" s="11" t="s">
         <v>946</v>
       </c>
     </row>
@@ -9888,13 +9949,13 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="11" t="s">
+      <c r="J168" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="K168" s="11" t="s">
+      <c r="K168" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L168" s="10" t="s">
+      <c r="L168" s="11" t="s">
         <v>951</v>
       </c>
     </row>
@@ -9920,13 +9981,13 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="11" t="s">
+      <c r="J169" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="K169" s="11" t="s">
+      <c r="K169" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L169" s="10" t="s">
+      <c r="L169" s="11" t="s">
         <v>956</v>
       </c>
     </row>
@@ -9952,13 +10013,13 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="11" t="s">
+      <c r="J170" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="11" t="s">
+      <c r="K170" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L170" s="10" t="s">
+      <c r="L170" s="11" t="s">
         <v>961</v>
       </c>
     </row>
@@ -9984,13 +10045,13 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="11" t="s">
+      <c r="J171" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="K171" s="11" t="s">
+      <c r="K171" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L171" s="10" t="s">
+      <c r="L171" s="11" t="s">
         <v>967</v>
       </c>
     </row>
@@ -10016,13 +10077,13 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="11" t="s">
+      <c r="J172" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="K172" s="11" t="s">
+      <c r="K172" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L172" s="10" t="s">
+      <c r="L172" s="11" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10048,13 +10109,13 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="11" t="s">
+      <c r="J173" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="K173" s="11" t="s">
+      <c r="K173" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L173" s="10" t="s">
+      <c r="L173" s="11" t="s">
         <v>977</v>
       </c>
     </row>
@@ -10080,13 +10141,13 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="11" t="s">
+      <c r="J174" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="K174" s="11" t="s">
+      <c r="K174" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L174" s="10" t="s">
+      <c r="L174" s="11" t="s">
         <v>982</v>
       </c>
     </row>
@@ -10112,13 +10173,13 @@
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="11" t="s">
+      <c r="J175" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="K175" s="11" t="s">
+      <c r="K175" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L175" s="10" t="s">
+      <c r="L175" s="11" t="s">
         <v>987</v>
       </c>
     </row>
@@ -10144,13 +10205,13 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="11" t="s">
+      <c r="J176" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="K176" s="11" t="s">
+      <c r="K176" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="L176" s="10" t="s">
+      <c r="L176" s="11" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10176,13 +10237,13 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="11" t="s">
+      <c r="J177" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="K177" s="11" t="s">
+      <c r="K177" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="L177" s="10" t="s">
+      <c r="L177" s="11" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10208,13 +10269,13 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="11" t="s">
+      <c r="J178" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="K178" s="11" t="s">
+      <c r="K178" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="L178" s="10" t="s">
+      <c r="L178" s="11" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -10240,13 +10301,13 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="11" t="s">
+      <c r="J179" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="K179" s="11" t="s">
+      <c r="K179" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="L179" s="10" t="s">
+      <c r="L179" s="11" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -10272,13 +10333,13 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="11" t="s">
+      <c r="J180" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="K180" s="11" t="s">
+      <c r="K180" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="L180" s="10" t="s">
+      <c r="L180" s="11" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -10304,13 +10365,13 @@
       <c r="I181" s="3">
         <v>0</v>
       </c>
-      <c r="J181" s="12" t="s">
+      <c r="J181" s="13" t="s">
         <v>1019</v>
       </c>
-      <c r="K181" s="12" t="s">
+      <c r="K181" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L181" s="10" t="s">
+      <c r="L181" s="11" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -10336,13 +10397,13 @@
       <c r="I182" s="1">
         <v>0</v>
       </c>
-      <c r="J182" s="11" t="s">
+      <c r="J182" s="12" t="s">
         <v>1026</v>
       </c>
-      <c r="K182" s="11" t="s">
+      <c r="K182" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L182" s="10" t="s">
+      <c r="L182" s="11" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -10368,13 +10429,13 @@
       <c r="I183" s="1">
         <v>0</v>
       </c>
-      <c r="J183" s="11" t="s">
+      <c r="J183" s="12" t="s">
         <v>1032</v>
       </c>
-      <c r="K183" s="11" t="s">
+      <c r="K183" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L183" s="10" t="s">
+      <c r="L183" s="11" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10400,13 +10461,13 @@
       <c r="I184" s="1">
         <v>0</v>
       </c>
-      <c r="J184" s="11" t="s">
+      <c r="J184" s="12" t="s">
         <v>1038</v>
       </c>
-      <c r="K184" s="11" t="s">
+      <c r="K184" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L184" s="10" t="s">
+      <c r="L184" s="11" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10432,13 +10493,13 @@
       <c r="I185" s="1">
         <v>0</v>
       </c>
-      <c r="J185" s="11" t="s">
+      <c r="J185" s="12" t="s">
         <v>1044</v>
       </c>
-      <c r="K185" s="11" t="s">
+      <c r="K185" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L185" s="10" t="s">
+      <c r="L185" s="11" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -10464,13 +10525,13 @@
       <c r="I186" s="1">
         <v>0</v>
       </c>
-      <c r="J186" s="11" t="s">
+      <c r="J186" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="K186" s="11" t="s">
+      <c r="K186" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L186" s="10" t="s">
+      <c r="L186" s="11" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -10496,13 +10557,13 @@
       <c r="I187" s="1">
         <v>0</v>
       </c>
-      <c r="J187" s="11" t="s">
+      <c r="J187" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="K187" s="11" t="s">
+      <c r="K187" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L187" s="10" t="s">
+      <c r="L187" s="11" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -10528,13 +10589,13 @@
       <c r="I188" s="1">
         <v>0</v>
       </c>
-      <c r="J188" s="11" t="s">
+      <c r="J188" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="K188" s="11" t="s">
+      <c r="K188" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L188" s="10" t="s">
+      <c r="L188" s="11" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -10560,13 +10621,13 @@
       <c r="I189" s="1">
         <v>0</v>
       </c>
-      <c r="J189" s="11" t="s">
+      <c r="J189" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="K189" s="11" t="s">
+      <c r="K189" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L189" s="10" t="s">
+      <c r="L189" s="11" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -10592,13 +10653,13 @@
       <c r="I190" s="1">
         <v>0</v>
       </c>
-      <c r="J190" s="11" t="s">
+      <c r="J190" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="K190" s="11" t="s">
+      <c r="K190" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L190" s="10" t="s">
+      <c r="L190" s="11" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -10624,13 +10685,13 @@
       <c r="I191" s="1">
         <v>0</v>
       </c>
-      <c r="J191" s="11" t="s">
+      <c r="J191" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K191" s="11" t="s">
+      <c r="K191" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L191" s="10" t="s">
+      <c r="L191" s="11" t="s">
         <v>1077</v>
       </c>
     </row>
@@ -10656,13 +10717,13 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-      <c r="J192" s="11" t="s">
+      <c r="J192" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K192" s="11" t="s">
+      <c r="K192" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L192" s="10" t="s">
+      <c r="L192" s="11" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -10688,13 +10749,13 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-      <c r="J193" s="11" t="s">
+      <c r="J193" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K193" s="11" t="s">
+      <c r="K193" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L193" s="10" t="s">
+      <c r="L193" s="11" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -10720,13 +10781,13 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-      <c r="J194" s="11" t="s">
+      <c r="J194" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K194" s="11" t="s">
+      <c r="K194" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L194" s="10" t="s">
+      <c r="L194" s="11" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -10752,13 +10813,13 @@
       <c r="I195" s="1">
         <v>0</v>
       </c>
-      <c r="J195" s="11" t="s">
+      <c r="J195" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K195" s="11" t="s">
+      <c r="K195" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L195" s="10" t="s">
+      <c r="L195" s="11" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -10784,13 +10845,13 @@
       <c r="I196" s="4">
         <v>0</v>
       </c>
-      <c r="J196" s="13" t="s">
+      <c r="J196" s="14" t="s">
         <v>1102</v>
       </c>
-      <c r="K196" s="13" t="s">
+      <c r="K196" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L196" s="13" t="s">
+      <c r="L196" s="14" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -10816,13 +10877,13 @@
       <c r="I197" s="1">
         <v>0</v>
       </c>
-      <c r="J197" s="11" t="s">
+      <c r="J197" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="K197" s="11" t="s">
+      <c r="K197" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L197" s="10" t="s">
+      <c r="L197" s="11" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -10848,13 +10909,13 @@
       <c r="I198" s="1">
         <v>0</v>
       </c>
-      <c r="J198" s="11" t="s">
+      <c r="J198" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="K198" s="11" t="s">
+      <c r="K198" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L198" s="10" t="s">
+      <c r="L198" s="11" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -10880,13 +10941,13 @@
       <c r="I199" s="1">
         <v>0</v>
       </c>
-      <c r="J199" s="11" t="s">
+      <c r="J199" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="K199" s="11" t="s">
+      <c r="K199" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L199" s="10" t="s">
+      <c r="L199" s="11" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -10912,13 +10973,13 @@
       <c r="I200" s="1">
         <v>0</v>
       </c>
-      <c r="J200" s="11" t="s">
+      <c r="J200" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="K200" s="11" t="s">
+      <c r="K200" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L200" s="10" t="s">
+      <c r="L200" s="11" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -10944,13 +11005,13 @@
       <c r="I201" s="1">
         <v>0</v>
       </c>
-      <c r="J201" s="11" t="s">
+      <c r="J201" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K201" s="11" t="s">
+      <c r="K201" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L201" s="10" t="s">
+      <c r="L201" s="11" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -10976,13 +11037,13 @@
       <c r="I202" s="1">
         <v>0</v>
       </c>
-      <c r="J202" s="11" t="s">
+      <c r="J202" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K202" s="11" t="s">
+      <c r="K202" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L202" s="10" t="s">
+      <c r="L202" s="11" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -11008,13 +11069,13 @@
       <c r="I203" s="1">
         <v>0</v>
       </c>
-      <c r="J203" s="11" t="s">
+      <c r="J203" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K203" s="11" t="s">
+      <c r="K203" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L203" s="10" t="s">
+      <c r="L203" s="11" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -11040,13 +11101,13 @@
       <c r="I204" s="1">
         <v>0</v>
       </c>
-      <c r="J204" s="11" t="s">
+      <c r="J204" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K204" s="11" t="s">
+      <c r="K204" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L204" s="10" t="s">
+      <c r="L204" s="11" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -11072,13 +11133,13 @@
       <c r="I205" s="1">
         <v>0</v>
       </c>
-      <c r="J205" s="11" t="s">
+      <c r="J205" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K205" s="11" t="s">
+      <c r="K205" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L205" s="10" t="s">
+      <c r="L205" s="11" t="s">
         <v>1149</v>
       </c>
     </row>
@@ -11104,13 +11165,13 @@
       <c r="I206" s="1">
         <v>0</v>
       </c>
-      <c r="J206" s="11" t="s">
+      <c r="J206" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K206" s="11" t="s">
+      <c r="K206" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L206" s="10" t="s">
+      <c r="L206" s="11" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -11136,13 +11197,13 @@
       <c r="I207" s="1">
         <v>0</v>
       </c>
-      <c r="J207" s="11" t="s">
+      <c r="J207" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K207" s="11" t="s">
+      <c r="K207" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L207" s="10" t="s">
+      <c r="L207" s="11" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -11168,13 +11229,13 @@
       <c r="I208" s="1">
         <v>0</v>
       </c>
-      <c r="J208" s="11" t="s">
+      <c r="J208" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K208" s="11" t="s">
+      <c r="K208" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L208" s="10" t="s">
+      <c r="L208" s="11" t="s">
         <v>1165</v>
       </c>
     </row>
@@ -11200,13 +11261,13 @@
       <c r="I209" s="1">
         <v>0</v>
       </c>
-      <c r="J209" s="11" t="s">
+      <c r="J209" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K209" s="11" t="s">
+      <c r="K209" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L209" s="10" t="s">
+      <c r="L209" s="11" t="s">
         <v>1170</v>
       </c>
     </row>
@@ -11232,13 +11293,13 @@
       <c r="I210" s="1">
         <v>0</v>
       </c>
-      <c r="J210" s="11" t="s">
+      <c r="J210" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K210" s="11" t="s">
+      <c r="K210" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L210" s="10" t="s">
+      <c r="L210" s="11" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -11264,13 +11325,13 @@
       <c r="I211" s="1">
         <v>0</v>
       </c>
-      <c r="J211" s="11" t="s">
+      <c r="J211" s="12" t="s">
         <v>1180</v>
       </c>
-      <c r="K211" s="11" t="s">
+      <c r="K211" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L211" s="10" t="s">
+      <c r="L211" s="11" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -11296,13 +11357,13 @@
       <c r="I212" s="1">
         <v>0</v>
       </c>
-      <c r="J212" s="11" t="s">
+      <c r="J212" s="12" t="s">
         <v>1180</v>
       </c>
-      <c r="K212" s="11" t="s">
+      <c r="K212" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L212" s="10" t="s">
+      <c r="L212" s="11" t="s">
         <v>1186</v>
       </c>
     </row>
@@ -11328,13 +11389,13 @@
       <c r="I213" s="1">
         <v>0</v>
       </c>
-      <c r="J213" s="11" t="s">
+      <c r="J213" s="12" t="s">
         <v>1180</v>
       </c>
-      <c r="K213" s="11" t="s">
+      <c r="K213" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L213" s="10" t="s">
+      <c r="L213" s="11" t="s">
         <v>1191</v>
       </c>
     </row>
@@ -11360,13 +11421,13 @@
       <c r="I214" s="1">
         <v>0</v>
       </c>
-      <c r="J214" s="11" t="s">
+      <c r="J214" s="12" t="s">
         <v>1180</v>
       </c>
-      <c r="K214" s="11" t="s">
+      <c r="K214" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L214" s="10" t="s">
+      <c r="L214" s="11" t="s">
         <v>1196</v>
       </c>
     </row>
@@ -11392,22 +11453,185 @@
       <c r="I215" s="1">
         <v>0</v>
       </c>
-      <c r="J215" s="11" t="s">
+      <c r="J215" s="12" t="s">
         <v>1180</v>
       </c>
-      <c r="K215" s="11" t="s">
+      <c r="K215" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L215" s="10" t="s">
+      <c r="L215" s="11" t="s">
         <v>1201</v>
       </c>
     </row>
+    <row r="216" s="3" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C216" s="1">
+        <v>1210</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E216" s="3">
+        <v>5</v>
+      </c>
+      <c r="F216" s="3">
+        <v>5</v>
+      </c>
+      <c r="G216" s="10" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="I216" s="3">
+        <v>0</v>
+      </c>
+      <c r="J216" s="13" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K216" s="13" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L216" s="11" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" spans="3:12">
+      <c r="C217" s="1">
+        <v>1211</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E217" s="1">
+        <v>5</v>
+      </c>
+      <c r="F217" s="1">
+        <v>5</v>
+      </c>
+      <c r="G217" s="8" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I217" s="1">
+        <v>0</v>
+      </c>
+      <c r="J217" s="12" t="s">
+        <v>1026</v>
+      </c>
+      <c r="K217" s="12" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L217" s="11" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" spans="3:12">
+      <c r="C218" s="1">
+        <v>1212</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E218" s="1">
+        <v>5</v>
+      </c>
+      <c r="F218" s="1">
+        <v>5</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="I218" s="1">
+        <v>0</v>
+      </c>
+      <c r="J218" s="12" t="s">
+        <v>1032</v>
+      </c>
+      <c r="K218" s="12" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L218" s="11" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" spans="3:12">
+      <c r="C219" s="1">
+        <v>1213</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E219" s="1">
+        <v>5</v>
+      </c>
+      <c r="F219" s="1">
+        <v>5</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="I219" s="1">
+        <v>0</v>
+      </c>
+      <c r="J219" s="12" t="s">
+        <v>1038</v>
+      </c>
+      <c r="K219" s="12" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L219" s="11" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" spans="3:12">
+      <c r="C220" s="1">
+        <v>1214</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E220" s="1">
+        <v>5</v>
+      </c>
+      <c r="F220" s="1">
+        <v>5</v>
+      </c>
+      <c r="G220" s="8" t="s">
+        <v>1219</v>
+      </c>
+      <c r="H220" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="I220" s="1">
+        <v>0</v>
+      </c>
+      <c r="J220" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="K220" s="12" t="s">
+        <v>1020</v>
+      </c>
+      <c r="L220" s="11" t="s">
+        <v>1221</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C3:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="C216:C220">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:C215 C221:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C215 C216:C220 C221:C1048576" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="1222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1231">
   <si>
     <t>_Id</t>
   </si>
@@ -3664,9 +3664,18 @@
     <t>混沌龙爪</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210083,1009,505,506,202003,507</t>
+  </si>
+  <si>
+    <t>10,9500,9000,98000,600000,140000,600000,700000,600000,90</t>
+  </si>
+  <si>
     <t>10209</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>虚无小村</t>
   </si>
   <si>
@@ -3676,6 +3685,12 @@
     <t>粉色专属</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210077,1009,505,506,202004,507</t>
+  </si>
+  <si>
+    <t>10,9500,9000,98000,600000,140000,600000,700000,600000,900000</t>
+  </si>
+  <si>
     <t>10210</t>
   </si>
   <si>
@@ -3688,6 +3703,9 @@
     <t>虚无鹿茸</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210077,1009,505,506,202005,507</t>
+  </si>
+  <si>
     <t>10211</t>
   </si>
   <si>
@@ -3700,6 +3718,9 @@
     <t>虚无草帽</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210077,1009,505,506,202006,507</t>
+  </si>
+  <si>
     <t>10212</t>
   </si>
   <si>
@@ -3712,6 +3733,9 @@
     <t>虚无猫爪</t>
   </si>
   <si>
+    <t>202002,300091,105,504,210077,1009,505,506,202007,507</t>
+  </si>
+  <si>
     <t>10213</t>
   </si>
   <si>
@@ -3722,6 +3746,9 @@
   </si>
   <si>
     <t>虚无花朵</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,506,202003,507</t>
   </si>
   <si>
     <t>10214</t>
@@ -3903,12 +3930,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4751,7 +4778,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:M220"/>
+  <dimension ref="A3:M220"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
@@ -11239,7 +11266,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="209" customHeight="1" spans="3:12">
+    <row r="209" customHeight="1" spans="1:12">
       <c r="C209" s="1" t="s">
         <v>1166</v>
       </c>
@@ -11271,7 +11298,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="210" customHeight="1" spans="3:12">
+    <row r="210" customHeight="1" spans="1:12">
       <c r="C210" s="1" t="s">
         <v>1171</v>
       </c>
@@ -11303,7 +11330,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="211" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C211" s="1" t="s">
         <v>1176</v>
       </c>
@@ -11335,7 +11362,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="212" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C212" s="1" t="s">
         <v>1182</v>
       </c>
@@ -11367,7 +11394,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="213" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C213" s="1" t="s">
         <v>1187</v>
       </c>
@@ -11399,7 +11426,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="214" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C214" s="1" t="s">
         <v>1192</v>
       </c>
@@ -11431,7 +11458,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="215" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C215" s="1" t="s">
         <v>1197</v>
       </c>
@@ -11454,21 +11481,27 @@
         <v>0</v>
       </c>
       <c r="J215" s="12" t="s">
-        <v>1180</v>
+        <v>1201</v>
       </c>
       <c r="K215" s="12" t="s">
-        <v>1020</v>
+        <v>1202</v>
       </c>
       <c r="L215" s="11" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="216" s="3" customFormat="1" customHeight="1" spans="3:12">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="216" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A216" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>1204</v>
+      </c>
       <c r="C216" s="1">
         <v>1210</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="E216" s="3">
         <v>5</v>
@@ -11477,30 +11510,36 @@
         <v>5</v>
       </c>
       <c r="G216" s="10" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="I216" s="3">
         <v>0</v>
       </c>
       <c r="J216" s="13" t="s">
-        <v>1019</v>
+        <v>1208</v>
       </c>
       <c r="K216" s="13" t="s">
-        <v>1020</v>
+        <v>1209</v>
       </c>
       <c r="L216" s="11" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="217" customHeight="1" spans="3:12">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" spans="1:12">
+      <c r="A217" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>1204</v>
+      </c>
       <c r="C217" s="1">
         <v>1211</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>1206</v>
+        <v>1211</v>
       </c>
       <c r="E217" s="1">
         <v>5</v>
@@ -11509,30 +11548,36 @@
         <v>5</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="I217" s="1">
         <v>0</v>
       </c>
       <c r="J217" s="12" t="s">
-        <v>1026</v>
+        <v>1214</v>
       </c>
       <c r="K217" s="12" t="s">
-        <v>1020</v>
+        <v>1209</v>
       </c>
       <c r="L217" s="11" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" spans="3:12">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" spans="1:12">
+      <c r="A218" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>1204</v>
+      </c>
       <c r="C218" s="1">
         <v>1212</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="E218" s="1">
         <v>5</v>
@@ -11541,30 +11586,36 @@
         <v>5</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="I218" s="1">
         <v>0</v>
       </c>
       <c r="J218" s="12" t="s">
-        <v>1032</v>
+        <v>1219</v>
       </c>
       <c r="K218" s="12" t="s">
-        <v>1020</v>
+        <v>1209</v>
       </c>
       <c r="L218" s="11" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" spans="3:12">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" spans="1:12">
+      <c r="A219" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>1204</v>
+      </c>
       <c r="C219" s="1">
         <v>1213</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="E219" s="1">
         <v>5</v>
@@ -11573,30 +11624,36 @@
         <v>5</v>
       </c>
       <c r="G219" s="8" t="s">
-        <v>1215</v>
+        <v>1222</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="I219" s="1">
         <v>0</v>
       </c>
       <c r="J219" s="12" t="s">
-        <v>1038</v>
+        <v>1224</v>
       </c>
       <c r="K219" s="12" t="s">
-        <v>1020</v>
+        <v>1209</v>
       </c>
       <c r="L219" s="11" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="220" customHeight="1" spans="3:12">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" spans="1:12">
+      <c r="A220" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>1204</v>
+      </c>
       <c r="C220" s="1">
         <v>1214</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="E220" s="1">
         <v>5</v>
@@ -11605,22 +11662,22 @@
         <v>5</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="I220" s="1">
         <v>0</v>
       </c>
       <c r="J220" s="12" t="s">
-        <v>1044</v>
+        <v>1229</v>
       </c>
       <c r="K220" s="12" t="s">
-        <v>1020</v>
+        <v>1209</v>
       </c>
       <c r="L220" s="11" t="s">
-        <v>1221</v>
+        <v>1230</v>
       </c>
     </row>
   </sheetData>
@@ -11631,7 +11688,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C215 C216:C220 C221:C1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C1048576" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1230">
   <si>
     <t>_Id</t>
   </si>
@@ -3667,7 +3667,7 @@
     <t>202002,300091,105,504,210083,1009,505,506,202003,507</t>
   </si>
   <si>
-    <t>10,9500,9000,98000,600000,140000,600000,700000,600000,90</t>
+    <t>10,9500,9000,98000,600000,140000,600000,700000,600000,900000</t>
   </si>
   <si>
     <t>10209</t>
@@ -3686,9 +3686,6 @@
   </si>
   <si>
     <t>202002,300091,105,504,210077,1009,505,506,202004,507</t>
-  </si>
-  <si>
-    <t>10,9500,9000,98000,600000,140000,600000,700000,600000,900000</t>
   </si>
   <si>
     <t>10210</t>
@@ -3930,12 +3927,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -11522,10 +11519,10 @@
         <v>1208</v>
       </c>
       <c r="K216" s="13" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L216" s="11" t="s">
         <v>1209</v>
-      </c>
-      <c r="L216" s="11" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="217" customHeight="1" spans="1:12">
@@ -11539,31 +11536,31 @@
         <v>1211</v>
       </c>
       <c r="D217" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E217" s="1">
+        <v>5</v>
+      </c>
+      <c r="F217" s="1">
+        <v>5</v>
+      </c>
+      <c r="G217" s="8" t="s">
         <v>1211</v>
       </c>
-      <c r="E217" s="1">
-        <v>5</v>
-      </c>
-      <c r="F217" s="1">
-        <v>5</v>
-      </c>
-      <c r="G217" s="8" t="s">
+      <c r="H217" s="1" t="s">
         <v>1212</v>
-      </c>
-      <c r="H217" s="1" t="s">
-        <v>1213</v>
       </c>
       <c r="I217" s="1">
         <v>0</v>
       </c>
       <c r="J217" s="12" t="s">
+        <v>1213</v>
+      </c>
+      <c r="K217" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L217" s="11" t="s">
         <v>1214</v>
-      </c>
-      <c r="K217" s="12" t="s">
-        <v>1209</v>
-      </c>
-      <c r="L217" s="11" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="218" customHeight="1" spans="1:12">
@@ -11577,31 +11574,31 @@
         <v>1212</v>
       </c>
       <c r="D218" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E218" s="1">
+        <v>5</v>
+      </c>
+      <c r="F218" s="1">
+        <v>5</v>
+      </c>
+      <c r="G218" s="8" t="s">
         <v>1216</v>
       </c>
-      <c r="E218" s="1">
-        <v>5</v>
-      </c>
-      <c r="F218" s="1">
-        <v>5</v>
-      </c>
-      <c r="G218" s="8" t="s">
+      <c r="H218" s="1" t="s">
         <v>1217</v>
-      </c>
-      <c r="H218" s="1" t="s">
-        <v>1218</v>
       </c>
       <c r="I218" s="1">
         <v>0</v>
       </c>
       <c r="J218" s="12" t="s">
+        <v>1218</v>
+      </c>
+      <c r="K218" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L218" s="11" t="s">
         <v>1219</v>
-      </c>
-      <c r="K218" s="12" t="s">
-        <v>1209</v>
-      </c>
-      <c r="L218" s="11" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="219" customHeight="1" spans="1:12">
@@ -11615,31 +11612,31 @@
         <v>1213</v>
       </c>
       <c r="D219" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E219" s="1">
+        <v>5</v>
+      </c>
+      <c r="F219" s="1">
+        <v>5</v>
+      </c>
+      <c r="G219" s="8" t="s">
         <v>1221</v>
       </c>
-      <c r="E219" s="1">
-        <v>5</v>
-      </c>
-      <c r="F219" s="1">
-        <v>5</v>
-      </c>
-      <c r="G219" s="8" t="s">
+      <c r="H219" s="1" t="s">
         <v>1222</v>
-      </c>
-      <c r="H219" s="1" t="s">
-        <v>1223</v>
       </c>
       <c r="I219" s="1">
         <v>0</v>
       </c>
       <c r="J219" s="12" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K219" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L219" s="11" t="s">
         <v>1224</v>
-      </c>
-      <c r="K219" s="12" t="s">
-        <v>1209</v>
-      </c>
-      <c r="L219" s="11" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="220" customHeight="1" spans="1:12">
@@ -11653,31 +11650,31 @@
         <v>1214</v>
       </c>
       <c r="D220" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E220" s="1">
+        <v>5</v>
+      </c>
+      <c r="F220" s="1">
+        <v>5</v>
+      </c>
+      <c r="G220" s="8" t="s">
         <v>1226</v>
       </c>
-      <c r="E220" s="1">
-        <v>5</v>
-      </c>
-      <c r="F220" s="1">
-        <v>5</v>
-      </c>
-      <c r="G220" s="8" t="s">
+      <c r="H220" s="1" t="s">
         <v>1227</v>
-      </c>
-      <c r="H220" s="1" t="s">
-        <v>1228</v>
       </c>
       <c r="I220" s="1">
         <v>0</v>
       </c>
       <c r="J220" s="12" t="s">
+        <v>1228</v>
+      </c>
+      <c r="K220" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L220" s="11" t="s">
         <v>1229</v>
-      </c>
-      <c r="K220" s="12" t="s">
-        <v>1209</v>
-      </c>
-      <c r="L220" s="11" t="s">
-        <v>1230</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1173">
   <si>
     <t>_Id</t>
   </si>
@@ -1294,7 +1294,7 @@
     <t>750-1</t>
   </si>
   <si>
-    <t>红装,梦魇鸡爪</t>
+    <t>红装、遗物</t>
   </si>
   <si>
     <t>200750,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
@@ -1315,9 +1315,6 @@
     <t>750-2</t>
   </si>
   <si>
-    <t>梦魇鹿茸</t>
-  </si>
-  <si>
     <t>200751,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
@@ -1333,9 +1330,6 @@
     <t>750-3</t>
   </si>
   <si>
-    <t>梦魇草帽</t>
-  </si>
-  <si>
     <t>200752,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
@@ -1351,9 +1345,6 @@
     <t>750-4</t>
   </si>
   <si>
-    <t>梦魇猫爪</t>
-  </si>
-  <si>
     <t>200753,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
@@ -1369,9 +1360,6 @@
     <t>750-5</t>
   </si>
   <si>
-    <t>梦魇花朵</t>
-  </si>
-  <si>
     <t>200754,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
@@ -1387,7 +1375,7 @@
     <t>800-1</t>
   </si>
   <si>
-    <t>梦魇冰晶</t>
+    <t>二阶随机升阶石</t>
   </si>
   <si>
     <t>200800,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210005,1009</t>
@@ -1408,7 +1396,7 @@
     <t>800-2</t>
   </si>
   <si>
-    <t>梦魇蝠翼</t>
+    <t>二阶剑甲升阶石</t>
   </si>
   <si>
     <t>200801,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210006,1009</t>
@@ -1426,7 +1414,7 @@
     <t>800-3</t>
   </si>
   <si>
-    <t>梦魇魂火</t>
+    <t>二阶链头升阶石</t>
   </si>
   <si>
     <t>200802,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210007,1009</t>
@@ -1444,7 +1432,7 @@
     <t>800-4</t>
   </si>
   <si>
-    <t>梦魇腐肉</t>
+    <t>二阶镯戒升阶石</t>
   </si>
   <si>
     <t>200803,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210008,1009</t>
@@ -1462,7 +1450,7 @@
     <t>800-5</t>
   </si>
   <si>
-    <t>梦魇蛇胆</t>
+    <t>二阶腰靴升阶石</t>
   </si>
   <si>
     <t>200804,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210009,1009</t>
@@ -1480,7 +1468,7 @@
     <t>850-1</t>
   </si>
   <si>
-    <t>梦魇狼爪</t>
+    <t>三阶随机升阶石</t>
   </si>
   <si>
     <t>200850,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210010,1009</t>
@@ -1498,7 +1486,7 @@
     <t>850-2</t>
   </si>
   <si>
-    <t>梦魇虫皮</t>
+    <t>三阶剑甲升阶石</t>
   </si>
   <si>
     <t>200851,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210011,1009</t>
@@ -1516,7 +1504,7 @@
     <t>850-3</t>
   </si>
   <si>
-    <t>梦魇鹰羽</t>
+    <t>三阶链头升阶石</t>
   </si>
   <si>
     <t>200852,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210012,1009</t>
@@ -1534,7 +1522,7 @@
     <t>850-4</t>
   </si>
   <si>
-    <t>梦魇虫角</t>
+    <t>三阶镯戒升阶石</t>
   </si>
   <si>
     <t>200853,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210013,1009</t>
@@ -1552,7 +1540,7 @@
     <t>850-5</t>
   </si>
   <si>
-    <t>梦魇蜈膏</t>
+    <t>三阶腰靴升阶石</t>
   </si>
   <si>
     <t>200854,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210014,1009</t>
@@ -1570,7 +1558,7 @@
     <t>900-1</t>
   </si>
   <si>
-    <t>梦魇虫心</t>
+    <t>四阶随机升阶石</t>
   </si>
   <si>
     <t>200900,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210015,1009</t>
@@ -1588,7 +1576,7 @@
     <t>900-2</t>
   </si>
   <si>
-    <t>梦魇龙皮</t>
+    <t>四阶剑甲升阶石</t>
   </si>
   <si>
     <t>200901,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210016,1009</t>
@@ -1606,7 +1594,7 @@
     <t>900-3</t>
   </si>
   <si>
-    <t>梦魇猪皮</t>
+    <t>四阶链头升阶石</t>
   </si>
   <si>
     <t>200902,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210017,1009</t>
@@ -1624,7 +1612,7 @@
     <t>900-4</t>
   </si>
   <si>
-    <t>梦魇猪心</t>
+    <t>四阶镯戒升阶石</t>
   </si>
   <si>
     <t>200903,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210018,1009</t>
@@ -1642,7 +1630,7 @@
     <t>900-5</t>
   </si>
   <si>
-    <t>梦魇蝎皮</t>
+    <t>四阶腰靴升阶石</t>
   </si>
   <si>
     <t>200904,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210019,1009</t>
@@ -1660,7 +1648,7 @@
     <t>950-1</t>
   </si>
   <si>
-    <t>噩梦宝甲</t>
+    <t>五阶剑甲升阶石</t>
   </si>
   <si>
     <t>200950,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210020,1009</t>
@@ -1678,7 +1666,7 @@
     <t>950-2</t>
   </si>
   <si>
-    <t>噩梦号角</t>
+    <t>五阶链头升阶石</t>
   </si>
   <si>
     <t>200951,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210021,1009</t>
@@ -1696,7 +1684,7 @@
     <t>950-3</t>
   </si>
   <si>
-    <t>噩梦雕像</t>
+    <t>五阶镯戒升阶石</t>
   </si>
   <si>
     <t>200952,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210022,1009</t>
@@ -1714,7 +1702,7 @@
     <t>950-4</t>
   </si>
   <si>
-    <t>噩梦神像</t>
+    <t>五阶腰靴升阶石</t>
   </si>
   <si>
     <t>200953,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210023,1009</t>
@@ -1732,7 +1720,7 @@
     <t>950-5</t>
   </si>
   <si>
-    <t>噩梦獠牙</t>
+    <t>五阶随机升阶石</t>
   </si>
   <si>
     <t>200954,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210024,1009</t>
@@ -1750,7 +1738,7 @@
     <t>1000-1</t>
   </si>
   <si>
-    <t>噩梦树心</t>
+    <t>六阶剑甲升阶石</t>
   </si>
   <si>
     <t>201000,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210025,1009</t>
@@ -1768,7 +1756,7 @@
     <t>1000-2</t>
   </si>
   <si>
-    <t>噩梦魔心</t>
+    <t>六阶链头升阶石</t>
   </si>
   <si>
     <t>201001,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210026,1009</t>
@@ -1786,7 +1774,7 @@
     <t>1000-3</t>
   </si>
   <si>
-    <t>噩梦尸心</t>
+    <t>六阶镯戒升阶石</t>
   </si>
   <si>
     <t>201002,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210027,1009</t>
@@ -1804,7 +1792,7 @@
     <t>1000-4</t>
   </si>
   <si>
-    <t>噩梦法杖</t>
+    <t>六阶腰靴升阶石</t>
   </si>
   <si>
     <t>201003,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210028,1009</t>
@@ -1822,7 +1810,7 @@
     <t>1000-5</t>
   </si>
   <si>
-    <t>噩梦权杖</t>
+    <t>六阶随机升阶石</t>
   </si>
   <si>
     <t>201004,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210029,1009</t>
@@ -1840,7 +1828,7 @@
     <t>1050-1</t>
   </si>
   <si>
-    <t>噩梦战锤</t>
+    <t>七阶剑甲升阶石</t>
   </si>
   <si>
     <t>201050,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210030,1009</t>
@@ -1858,7 +1846,7 @@
     <t>1050-2</t>
   </si>
   <si>
-    <t>噩梦血核</t>
+    <t>七阶链头升阶石</t>
   </si>
   <si>
     <t>201051,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210031,1009</t>
@@ -1876,7 +1864,7 @@
     <t>1050-3</t>
   </si>
   <si>
-    <t>噩梦魔核</t>
+    <t>七阶镯戒升阶石</t>
   </si>
   <si>
     <t>201052,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210032,1009</t>
@@ -1894,7 +1882,7 @@
     <t>1050-4</t>
   </si>
   <si>
-    <t>噩梦龙甲</t>
+    <t>七阶腰靴升阶石</t>
   </si>
   <si>
     <t>201053,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210033,1009</t>
@@ -1912,7 +1900,7 @@
     <t>1050-5</t>
   </si>
   <si>
-    <t>噩梦龙爪</t>
+    <t>七阶随机升阶石</t>
   </si>
   <si>
     <t>201054,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210034,1009</t>
@@ -1951,7 +1939,7 @@
     <t>1100-2</t>
   </si>
   <si>
-    <t>地狱鹿茸</t>
+    <t>八阶链头升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210036,1009</t>
@@ -1969,7 +1957,7 @@
     <t>1100-3</t>
   </si>
   <si>
-    <t>地狱草帽</t>
+    <t>八阶镯戒升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210037,1009</t>
@@ -1987,7 +1975,7 @@
     <t>1100-4</t>
   </si>
   <si>
-    <t>地狱猫爪</t>
+    <t>八阶腰靴升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210038,1009</t>
@@ -2005,7 +1993,7 @@
     <t>1100-5</t>
   </si>
   <si>
-    <t>地狱花朵</t>
+    <t>八阶随机升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210039,1009</t>
@@ -2023,7 +2011,7 @@
     <t>1150-1</t>
   </si>
   <si>
-    <t>地狱冰晶</t>
+    <t>九阶剑甲升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210040,1009</t>
@@ -2041,7 +2029,7 @@
     <t>1150-2</t>
   </si>
   <si>
-    <t>地狱蝠翼</t>
+    <t>九阶链头升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210041,1009</t>
@@ -2059,7 +2047,7 @@
     <t>1150-3</t>
   </si>
   <si>
-    <t>地狱魂火</t>
+    <t>九阶镯戒升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210042,1009</t>
@@ -2077,7 +2065,7 @@
     <t>1150-4</t>
   </si>
   <si>
-    <t>地狱腐肉</t>
+    <t>九阶腰靴升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210043,1009</t>
@@ -2095,7 +2083,7 @@
     <t>1150-5</t>
   </si>
   <si>
-    <t>地狱蛇胆</t>
+    <t>九阶随机升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210044,1009</t>
@@ -2113,7 +2101,7 @@
     <t>1200-1</t>
   </si>
   <si>
-    <t>地狱狼爪</t>
+    <t>十阶剑甲升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210045,1009</t>
@@ -2131,7 +2119,7 @@
     <t>1200-2</t>
   </si>
   <si>
-    <t>地狱虫皮</t>
+    <t>十阶链头升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210046,1009</t>
@@ -2149,7 +2137,7 @@
     <t>1200-3</t>
   </si>
   <si>
-    <t>地狱鹰羽</t>
+    <t>十阶镯戒升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210047,1009</t>
@@ -2167,7 +2155,7 @@
     <t>1200-4</t>
   </si>
   <si>
-    <t>地狱虫角</t>
+    <t>十阶腰靴升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210048,1009</t>
@@ -2185,7 +2173,7 @@
     <t>1200-5</t>
   </si>
   <si>
-    <t>地狱蜈膏</t>
+    <t>十阶随机升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210049,1009</t>
@@ -2203,7 +2191,7 @@
     <t>1250-1</t>
   </si>
   <si>
-    <t>地狱虫心</t>
+    <t>十一阶剑甲升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210050,1009</t>
@@ -2221,7 +2209,7 @@
     <t>1250-2</t>
   </si>
   <si>
-    <t>地狱龙皮</t>
+    <t>十一阶链头升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210051,1009</t>
@@ -2239,7 +2227,7 @@
     <t>1250-3</t>
   </si>
   <si>
-    <t>地狱猪皮</t>
+    <t>十一阶镯戒升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210052,1009</t>
@@ -2257,7 +2245,7 @@
     <t>1250-4</t>
   </si>
   <si>
-    <t>地狱猪心</t>
+    <t>十一阶腰靴升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210053,1009</t>
@@ -2275,7 +2263,7 @@
     <t>1250-5</t>
   </si>
   <si>
-    <t>地狱蝎皮</t>
+    <t>十一阶随机升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210054,1009</t>
@@ -2293,7 +2281,7 @@
     <t>1300-1</t>
   </si>
   <si>
-    <t>地狱宝甲</t>
+    <t>十二阶剑甲升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210055,1009</t>
@@ -2311,7 +2299,7 @@
     <t>1300-2</t>
   </si>
   <si>
-    <t>地狱号角</t>
+    <t>十二阶链头升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210056,1009</t>
@@ -2329,7 +2317,7 @@
     <t>1300-3</t>
   </si>
   <si>
-    <t>地狱雕像</t>
+    <t>十二阶镯戒升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210057,1009</t>
@@ -2347,7 +2335,7 @@
     <t>1300-4</t>
   </si>
   <si>
-    <t>地狱神像</t>
+    <t>十二阶腰靴升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210058,1009</t>
@@ -2365,7 +2353,7 @@
     <t>1300-5</t>
   </si>
   <si>
-    <t>地狱獠牙</t>
+    <t>十二阶随机升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210059,1009</t>
@@ -2383,7 +2371,7 @@
     <t>1350-1</t>
   </si>
   <si>
-    <t>地狱树心</t>
+    <t>金色专属</t>
   </si>
   <si>
     <t>202001,300091,104,504,210060,1009,505</t>
@@ -2404,7 +2392,7 @@
     <t>1350-2</t>
   </si>
   <si>
-    <t>地狱魔心</t>
+    <t>十三阶链头升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210061,1009,505</t>
@@ -2422,7 +2410,7 @@
     <t>1350-3</t>
   </si>
   <si>
-    <t>地狱尸心</t>
+    <t>十三阶镯戒升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210062,1009,505</t>
@@ -2440,7 +2428,7 @@
     <t>1350-4</t>
   </si>
   <si>
-    <t>地狱法杖</t>
+    <t>十三阶腰靴升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210063,1009,505</t>
@@ -2458,7 +2446,7 @@
     <t>1350-5</t>
   </si>
   <si>
-    <t>地狱权杖</t>
+    <t>十三阶随机升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210064,1009,505</t>
@@ -2476,7 +2464,7 @@
     <t>1400-1</t>
   </si>
   <si>
-    <t>地狱战锤</t>
+    <t>十四阶剑甲升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210065,1009,505</t>
@@ -2494,7 +2482,7 @@
     <t>1400-2</t>
   </si>
   <si>
-    <t>地狱血核</t>
+    <t>十四阶链头升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210066,1009,505</t>
@@ -2512,7 +2500,7 @@
     <t>1400-3</t>
   </si>
   <si>
-    <t>地狱魔核</t>
+    <t>十四阶镯戒升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210067,1009,505</t>
@@ -2530,7 +2518,7 @@
     <t>1400-4</t>
   </si>
   <si>
-    <t>地狱龙甲</t>
+    <t>十四阶腰靴升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210068,1009,505</t>
@@ -2548,7 +2536,7 @@
     <t>1400-5</t>
   </si>
   <si>
-    <t>地狱龙爪</t>
+    <t>十四阶随机升阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210069,1009,505</t>
@@ -2584,7 +2572,7 @@
     <t>1450-2</t>
   </si>
   <si>
-    <t>深渊鹿茸</t>
+    <t>十五阶升阶石</t>
   </si>
   <si>
     <t>10141</t>
@@ -2599,9 +2587,6 @@
     <t>1450-3</t>
   </si>
   <si>
-    <t>深渊草帽</t>
-  </si>
-  <si>
     <t>10142</t>
   </si>
   <si>
@@ -2614,9 +2599,6 @@
     <t>1450-4</t>
   </si>
   <si>
-    <t>深渊猫爪</t>
-  </si>
-  <si>
     <t>10143</t>
   </si>
   <si>
@@ -2629,9 +2611,6 @@
     <t>1450-5</t>
   </si>
   <si>
-    <t>深渊花朵</t>
-  </si>
-  <si>
     <t>10144</t>
   </si>
   <si>
@@ -2644,7 +2623,7 @@
     <t>1500-1</t>
   </si>
   <si>
-    <t>深渊冰晶</t>
+    <t>十六阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210071,1009,505</t>
@@ -2662,9 +2641,6 @@
     <t>1500-2</t>
   </si>
   <si>
-    <t>深渊蝠翼</t>
-  </si>
-  <si>
     <t>10146</t>
   </si>
   <si>
@@ -2677,9 +2653,6 @@
     <t>1500-3</t>
   </si>
   <si>
-    <t>深渊魂火</t>
-  </si>
-  <si>
     <t>10147</t>
   </si>
   <si>
@@ -2692,9 +2665,6 @@
     <t>1500-4</t>
   </si>
   <si>
-    <t>深渊腐肉</t>
-  </si>
-  <si>
     <t>10148</t>
   </si>
   <si>
@@ -2707,9 +2677,6 @@
     <t>1500-5</t>
   </si>
   <si>
-    <t>深渊蛇胆</t>
-  </si>
-  <si>
     <t>10149</t>
   </si>
   <si>
@@ -2722,7 +2689,7 @@
     <t>1550-1</t>
   </si>
   <si>
-    <t>深渊狼爪</t>
+    <t>十七阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210072,1009,505</t>
@@ -2740,9 +2707,6 @@
     <t>1550-2</t>
   </si>
   <si>
-    <t>深渊虫皮</t>
-  </si>
-  <si>
     <t>10151</t>
   </si>
   <si>
@@ -2755,9 +2719,6 @@
     <t>1550-3</t>
   </si>
   <si>
-    <t>深渊鹰羽</t>
-  </si>
-  <si>
     <t>10152</t>
   </si>
   <si>
@@ -2770,9 +2731,6 @@
     <t>1550-4</t>
   </si>
   <si>
-    <t>深渊虫角</t>
-  </si>
-  <si>
     <t>10153</t>
   </si>
   <si>
@@ -2785,9 +2743,6 @@
     <t>1550-5</t>
   </si>
   <si>
-    <t>深渊蜈膏</t>
-  </si>
-  <si>
     <t>10154</t>
   </si>
   <si>
@@ -2800,7 +2755,7 @@
     <t>1600-1</t>
   </si>
   <si>
-    <t>深渊虫心</t>
+    <t>十八阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210073,1009,505</t>
@@ -2818,9 +2773,6 @@
     <t>1600-2</t>
   </si>
   <si>
-    <t>深渊龙皮</t>
-  </si>
-  <si>
     <t>10156</t>
   </si>
   <si>
@@ -2833,9 +2785,6 @@
     <t>1600-3</t>
   </si>
   <si>
-    <t>深渊猪皮</t>
-  </si>
-  <si>
     <t>10157</t>
   </si>
   <si>
@@ -2848,9 +2797,6 @@
     <t>1600-4</t>
   </si>
   <si>
-    <t>深渊猪心</t>
-  </si>
-  <si>
     <t>10158</t>
   </si>
   <si>
@@ -2863,9 +2809,6 @@
     <t>1600-5</t>
   </si>
   <si>
-    <t>深渊蝎皮</t>
-  </si>
-  <si>
     <t>10159</t>
   </si>
   <si>
@@ -2878,7 +2821,7 @@
     <t>1650-1</t>
   </si>
   <si>
-    <t>深渊宝甲</t>
+    <t>十九阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210074,1009,505</t>
@@ -2896,9 +2839,6 @@
     <t>1650-2</t>
   </si>
   <si>
-    <t>深渊号角</t>
-  </si>
-  <si>
     <t>10161</t>
   </si>
   <si>
@@ -2911,9 +2851,6 @@
     <t>1650-3</t>
   </si>
   <si>
-    <t>深渊雕像</t>
-  </si>
-  <si>
     <t>10162</t>
   </si>
   <si>
@@ -2926,9 +2863,6 @@
     <t>1650-4</t>
   </si>
   <si>
-    <t>深渊神像</t>
-  </si>
-  <si>
     <t>10163</t>
   </si>
   <si>
@@ -2941,9 +2875,6 @@
     <t>1650-5</t>
   </si>
   <si>
-    <t>深渊獠牙</t>
-  </si>
-  <si>
     <t>10164</t>
   </si>
   <si>
@@ -2956,7 +2887,7 @@
     <t>1700-1</t>
   </si>
   <si>
-    <t>深渊树心</t>
+    <t>二十阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210075,1009,505</t>
@@ -2974,9 +2905,6 @@
     <t>1700-2</t>
   </si>
   <si>
-    <t>深渊魔心</t>
-  </si>
-  <si>
     <t>10166</t>
   </si>
   <si>
@@ -2989,9 +2917,6 @@
     <t>1700-3</t>
   </si>
   <si>
-    <t>深渊尸心</t>
-  </si>
-  <si>
     <t>10167</t>
   </si>
   <si>
@@ -3004,9 +2929,6 @@
     <t>1700-4</t>
   </si>
   <si>
-    <t>深渊法杖</t>
-  </si>
-  <si>
     <t>10168</t>
   </si>
   <si>
@@ -3019,9 +2941,6 @@
     <t>1700-5</t>
   </si>
   <si>
-    <t>深渊权杖</t>
-  </si>
-  <si>
     <t>10169</t>
   </si>
   <si>
@@ -3034,7 +2953,7 @@
     <t>1750-1</t>
   </si>
   <si>
-    <t>深渊战锤</t>
+    <t>暗金专属</t>
   </si>
   <si>
     <t>202002,300091,105,504,210076,1009,505,506</t>
@@ -3055,7 +2974,7 @@
     <t>1750-2</t>
   </si>
   <si>
-    <t>深渊血核</t>
+    <t>二一阶升阶石</t>
   </si>
   <si>
     <t>10171</t>
@@ -3070,9 +2989,6 @@
     <t>1750-3</t>
   </si>
   <si>
-    <t>深渊魔核</t>
-  </si>
-  <si>
     <t>10172</t>
   </si>
   <si>
@@ -3085,9 +3001,6 @@
     <t>1750-4</t>
   </si>
   <si>
-    <t>深渊龙甲</t>
-  </si>
-  <si>
     <t>10173</t>
   </si>
   <si>
@@ -3100,9 +3013,6 @@
     <t>1750-5</t>
   </si>
   <si>
-    <t>深渊龙爪</t>
-  </si>
-  <si>
     <t>10174</t>
   </si>
   <si>
@@ -3115,7 +3025,7 @@
     <t>1800-1</t>
   </si>
   <si>
-    <t>混沌装备</t>
+    <t>粉色装备</t>
   </si>
   <si>
     <t>202002,300091,105,504,210077,1009,505,506,202004</t>
@@ -3136,7 +3046,7 @@
     <t>1800-2</t>
   </si>
   <si>
-    <t>混沌鹿茸</t>
+    <t>二二阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210077,1009,505,506,202005</t>
@@ -3154,9 +3064,6 @@
     <t>1800-3</t>
   </si>
   <si>
-    <t>混沌草帽</t>
-  </si>
-  <si>
     <t>202002,300091,105,504,210077,1009,505,506,202006</t>
   </si>
   <si>
@@ -3172,9 +3079,6 @@
     <t>1800-4</t>
   </si>
   <si>
-    <t>混沌猫爪</t>
-  </si>
-  <si>
     <t>202002,300091,105,504,210077,1009,505,506,202007</t>
   </si>
   <si>
@@ -3190,9 +3094,6 @@
     <t>1800-5</t>
   </si>
   <si>
-    <t>混沌花朵</t>
-  </si>
-  <si>
     <t>202002,300091,105,504,210077,1009,505,506,202003</t>
   </si>
   <si>
@@ -3208,7 +3109,7 @@
     <t>1850-1</t>
   </si>
   <si>
-    <t>混沌冰晶</t>
+    <t>二三阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210078,1009,505,506,202003</t>
@@ -3226,9 +3127,6 @@
     <t>1850-2</t>
   </si>
   <si>
-    <t>混沌蝠翼</t>
-  </si>
-  <si>
     <t>10181</t>
   </si>
   <si>
@@ -3241,9 +3139,6 @@
     <t>1850-3</t>
   </si>
   <si>
-    <t>混沌魂火</t>
-  </si>
-  <si>
     <t>10182</t>
   </si>
   <si>
@@ -3256,9 +3151,6 @@
     <t>1850-4</t>
   </si>
   <si>
-    <t>混沌腐肉</t>
-  </si>
-  <si>
     <t>10183</t>
   </si>
   <si>
@@ -3271,9 +3163,6 @@
     <t>1850-5</t>
   </si>
   <si>
-    <t>混沌蛇胆</t>
-  </si>
-  <si>
     <t>10184</t>
   </si>
   <si>
@@ -3286,7 +3175,7 @@
     <t>1900-1</t>
   </si>
   <si>
-    <t>混沌狼爪</t>
+    <t>二四阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210079,1009,505,506,202003</t>
@@ -3304,9 +3193,6 @@
     <t>1900-2</t>
   </si>
   <si>
-    <t>混沌虫皮</t>
-  </si>
-  <si>
     <t>10186</t>
   </si>
   <si>
@@ -3319,9 +3205,6 @@
     <t>1900-3</t>
   </si>
   <si>
-    <t>混沌鹰羽</t>
-  </si>
-  <si>
     <t>10187</t>
   </si>
   <si>
@@ -3334,9 +3217,6 @@
     <t>1900-4</t>
   </si>
   <si>
-    <t>混沌虫角</t>
-  </si>
-  <si>
     <t>10188</t>
   </si>
   <si>
@@ -3349,9 +3229,6 @@
     <t>1900-5</t>
   </si>
   <si>
-    <t>混沌蜈膏</t>
-  </si>
-  <si>
     <t>10189</t>
   </si>
   <si>
@@ -3364,7 +3241,7 @@
     <t>1950-1</t>
   </si>
   <si>
-    <t>混沌虫心</t>
+    <t>二五阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210080,1009,505,506,202003</t>
@@ -3382,9 +3259,6 @@
     <t>1950-2</t>
   </si>
   <si>
-    <t>混沌龙皮</t>
-  </si>
-  <si>
     <t>10191</t>
   </si>
   <si>
@@ -3397,9 +3271,6 @@
     <t>1950-3</t>
   </si>
   <si>
-    <t>混沌猪皮</t>
-  </si>
-  <si>
     <t>10192</t>
   </si>
   <si>
@@ -3412,9 +3283,6 @@
     <t>1950-4</t>
   </si>
   <si>
-    <t>混沌猪心</t>
-  </si>
-  <si>
     <t>10193</t>
   </si>
   <si>
@@ -3427,9 +3295,6 @@
     <t>1950-5</t>
   </si>
   <si>
-    <t>混沌蝎皮</t>
-  </si>
-  <si>
     <t>10194</t>
   </si>
   <si>
@@ -3442,7 +3307,7 @@
     <t>2000-1</t>
   </si>
   <si>
-    <t>混沌宝甲</t>
+    <t>二六阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210081,1009,505,506,202003</t>
@@ -3460,9 +3325,6 @@
     <t>2000-2</t>
   </si>
   <si>
-    <t>混沌号角</t>
-  </si>
-  <si>
     <t>10196</t>
   </si>
   <si>
@@ -3475,9 +3337,6 @@
     <t>2000-3</t>
   </si>
   <si>
-    <t>混沌雕像</t>
-  </si>
-  <si>
     <t>10197</t>
   </si>
   <si>
@@ -3490,9 +3349,6 @@
     <t>2000-4</t>
   </si>
   <si>
-    <t>混沌神像</t>
-  </si>
-  <si>
     <t>10198</t>
   </si>
   <si>
@@ -3505,9 +3361,6 @@
     <t>2000-5</t>
   </si>
   <si>
-    <t>混沌獠牙</t>
-  </si>
-  <si>
     <t>10199</t>
   </si>
   <si>
@@ -3520,7 +3373,7 @@
     <t>2050-1</t>
   </si>
   <si>
-    <t>混沌树心</t>
+    <t>二七阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210082,1009,505,506,202003</t>
@@ -3538,9 +3391,6 @@
     <t>2050-2</t>
   </si>
   <si>
-    <t>混沌魔心</t>
-  </si>
-  <si>
     <t>10201</t>
   </si>
   <si>
@@ -3553,9 +3403,6 @@
     <t>2050-3</t>
   </si>
   <si>
-    <t>混沌尸心</t>
-  </si>
-  <si>
     <t>10202</t>
   </si>
   <si>
@@ -3568,9 +3415,6 @@
     <t>2050-4</t>
   </si>
   <si>
-    <t>混沌法杖</t>
-  </si>
-  <si>
     <t>10203</t>
   </si>
   <si>
@@ -3583,9 +3427,6 @@
     <t>2050-5</t>
   </si>
   <si>
-    <t>混沌权杖</t>
-  </si>
-  <si>
     <t>10204</t>
   </si>
   <si>
@@ -3598,7 +3439,7 @@
     <t>2100-1</t>
   </si>
   <si>
-    <t>混沌战锤</t>
+    <t>二八阶升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210083,1009,505,506,202003</t>
@@ -3616,9 +3457,6 @@
     <t>2100-2</t>
   </si>
   <si>
-    <t>混沌血核</t>
-  </si>
-  <si>
     <t>10206</t>
   </si>
   <si>
@@ -3631,9 +3469,6 @@
     <t>2100-3</t>
   </si>
   <si>
-    <t>混沌魔核</t>
-  </si>
-  <si>
     <t>10207</t>
   </si>
   <si>
@@ -3646,9 +3481,6 @@
     <t>2100-4</t>
   </si>
   <si>
-    <t>混沌龙甲</t>
-  </si>
-  <si>
     <t>10208</t>
   </si>
   <si>
@@ -3661,7 +3493,7 @@
     <t>2100-5</t>
   </si>
   <si>
-    <t>混沌龙爪</t>
+    <t>粉色专属</t>
   </si>
   <si>
     <t>202002,300091,105,504,210083,1009,505,506,202003,507</t>
@@ -3680,9 +3512,6 @@
   </si>
   <si>
     <t>2150-1</t>
-  </si>
-  <si>
-    <t>粉色专属</t>
   </si>
   <si>
     <t>202002,300091,105,504,210077,1009,505,506,202004,507</t>
@@ -4779,7 +4608,9 @@
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
-    <col min="4" max="9" width="11.6272727272727" style="1" customWidth="1"/>
+    <col min="4" max="7" width="11.6272727272727" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6272727272727" style="1" customWidth="1"/>
     <col min="10" max="10" width="75.8181818181818" style="1" customWidth="1"/>
     <col min="11" max="11" width="70.5" style="1" customWidth="1"/>
     <col min="12" max="12" width="39.3727272727273" style="5" customWidth="1"/>
@@ -7056,27 +6887,27 @@
         <v>417</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="I77" s="1">
         <v>750</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K77" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:12">
       <c r="C78" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="E78" s="1">
         <v>3</v>
@@ -7085,30 +6916,30 @@
         <v>3</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="I78" s="1">
         <v>750</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K78" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="2:12">
       <c r="C79" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E79" s="1">
         <v>3</v>
@@ -7117,30 +6948,30 @@
         <v>3</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="I79" s="1">
         <v>750</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="K79" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:12">
       <c r="C80" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E80" s="1">
         <v>3</v>
@@ -7149,30 +6980,30 @@
         <v>3</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>436</v>
+        <v>411</v>
       </c>
       <c r="I80" s="1">
         <v>750</v>
       </c>
       <c r="J80" s="12" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="K80" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E81" s="1">
         <v>3</v>
@@ -7181,30 +7012,30 @@
         <v>3</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="I81" s="1">
         <v>800</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K81" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E82" s="1">
         <v>3</v>
@@ -7213,30 +7044,30 @@
         <v>3</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="I82" s="1">
         <v>800</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="K82" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E83" s="1">
         <v>3</v>
@@ -7245,30 +7076,30 @@
         <v>3</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="I83" s="1">
         <v>800</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="K83" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E84" s="1">
         <v>3</v>
@@ -7277,30 +7108,30 @@
         <v>3</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="I84" s="1">
         <v>800</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="K84" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E85" s="1">
         <v>3</v>
@@ -7309,30 +7140,30 @@
         <v>3</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="I85" s="1">
         <v>800</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="K85" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C86" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E86" s="1">
         <v>3</v>
@@ -7341,30 +7172,30 @@
         <v>3</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="I86" s="1">
         <v>850</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="K86" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C87" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E87" s="1">
         <v>3</v>
@@ -7373,30 +7204,30 @@
         <v>3</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="I87" s="1">
         <v>850</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="K87" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C88" s="1" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E88" s="1">
         <v>3</v>
@@ -7405,30 +7236,30 @@
         <v>3</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="I88" s="1">
         <v>850</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="K88" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C89" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="E89" s="1">
         <v>3</v>
@@ -7437,30 +7268,30 @@
         <v>3</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="I89" s="1">
         <v>850</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="K89" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C90" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E90" s="1">
         <v>3</v>
@@ -7469,30 +7300,30 @@
         <v>3</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="I90" s="1">
         <v>850</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="K90" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C91" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E91" s="1">
         <v>3</v>
@@ -7501,30 +7332,30 @@
         <v>3</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="I91" s="1">
         <v>900</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="K91" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C92" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E92" s="1">
         <v>3</v>
@@ -7533,30 +7364,30 @@
         <v>3</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="I92" s="1">
         <v>900</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="K92" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C93" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E93" s="1">
         <v>3</v>
@@ -7565,30 +7396,30 @@
         <v>3</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="I93" s="1">
         <v>900</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="K93" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C94" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E94" s="1">
         <v>3</v>
@@ -7597,30 +7428,30 @@
         <v>3</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="I94" s="1">
         <v>900</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="K94" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C95" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E95" s="1">
         <v>3</v>
@@ -7629,30 +7460,30 @@
         <v>3</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="I95" s="1">
         <v>900</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="K95" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="E96" s="1">
         <v>3</v>
@@ -7661,30 +7492,30 @@
         <v>3</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="I96" s="1">
         <v>950</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="K96" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E97" s="1">
         <v>3</v>
@@ -7693,30 +7524,30 @@
         <v>3</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="I97" s="1">
         <v>950</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="K97" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="E98" s="1">
         <v>3</v>
@@ -7725,30 +7556,30 @@
         <v>3</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="I98" s="1">
         <v>950</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="K98" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E99" s="1">
         <v>3</v>
@@ -7757,30 +7588,30 @@
         <v>3</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="I99" s="1">
         <v>950</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="K99" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E100" s="1">
         <v>3</v>
@@ -7789,30 +7620,30 @@
         <v>3</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I100" s="1">
         <v>950</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="K100" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E101" s="1">
         <v>3</v>
@@ -7821,30 +7652,30 @@
         <v>3</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="I101" s="1">
         <v>1000</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="K101" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="E102" s="1">
         <v>3</v>
@@ -7853,30 +7684,30 @@
         <v>3</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="I102" s="1">
         <v>1000</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="K102" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="E103" s="1">
         <v>3</v>
@@ -7885,30 +7716,30 @@
         <v>3</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="I103" s="1">
         <v>1000</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="K103" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="E104" s="1">
         <v>3</v>
@@ -7917,30 +7748,30 @@
         <v>3</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="I104" s="1">
         <v>1000</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="K104" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="E105" s="1">
         <v>3</v>
@@ -7949,30 +7780,30 @@
         <v>3</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="I105" s="1">
         <v>1000</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="K105" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C106" s="1" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="E106" s="1">
         <v>3</v>
@@ -7981,30 +7812,30 @@
         <v>3</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="I106" s="1">
         <v>1050</v>
       </c>
       <c r="J106" s="12" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="K106" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C107" s="1" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="E107" s="1">
         <v>3</v>
@@ -8013,30 +7844,30 @@
         <v>3</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="I107" s="1">
         <v>1050</v>
       </c>
       <c r="J107" s="12" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="K107" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C108" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E108" s="1">
         <v>3</v>
@@ -8045,30 +7876,30 @@
         <v>3</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="I108" s="1">
         <v>1050</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="K108" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C109" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E109" s="1">
         <v>3</v>
@@ -8077,30 +7908,30 @@
         <v>3</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="I109" s="1">
         <v>1050</v>
       </c>
       <c r="J109" s="12" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="K109" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C110" s="1" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="E110" s="1">
         <v>3</v>
@@ -8109,30 +7940,30 @@
         <v>3</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="I110" s="1">
         <v>1050</v>
       </c>
       <c r="J110" s="12" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="K110" s="12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E111" s="1">
         <v>4</v>
@@ -8141,30 +7972,30 @@
         <v>4</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="I111" s="1">
         <v>0</v>
       </c>
       <c r="J111" s="12" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="K111" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="E112" s="1">
         <v>4</v>
@@ -8173,30 +8004,30 @@
         <v>4</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="I112" s="1">
         <v>0</v>
       </c>
       <c r="J112" s="12" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="K112" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:12">
       <c r="C113" s="1" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="E113" s="1">
         <v>4</v>
@@ -8205,30 +8036,30 @@
         <v>4</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="I113" s="1">
         <v>0</v>
       </c>
       <c r="J113" s="12" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="K113" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="E114" s="1">
         <v>4</v>
@@ -8237,30 +8068,30 @@
         <v>4</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I114" s="1">
         <v>0</v>
       </c>
       <c r="J114" s="12" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="K114" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E115" s="1">
         <v>4</v>
@@ -8269,30 +8100,30 @@
         <v>4</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="I115" s="1">
         <v>0</v>
       </c>
       <c r="J115" s="12" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="K115" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="E116" s="1">
         <v>4</v>
@@ -8301,30 +8132,30 @@
         <v>4</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="I116" s="1">
         <v>0</v>
       </c>
       <c r="J116" s="12" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="K116" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:12">
       <c r="C117" s="1" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E117" s="1">
         <v>4</v>
@@ -8333,30 +8164,30 @@
         <v>4</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="I117" s="1">
         <v>0</v>
       </c>
       <c r="J117" s="12" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="K117" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="3:12">
       <c r="C118" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="E118" s="1">
         <v>4</v>
@@ -8365,30 +8196,30 @@
         <v>4</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="I118" s="1">
         <v>0</v>
       </c>
       <c r="J118" s="12" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="K118" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:12">
       <c r="C119" s="1" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="E119" s="1">
         <v>4</v>
@@ -8397,30 +8228,30 @@
         <v>4</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="I119" s="1">
         <v>0</v>
       </c>
       <c r="J119" s="12" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="K119" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:12">
       <c r="C120" s="1" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="E120" s="1">
         <v>4</v>
@@ -8429,30 +8260,30 @@
         <v>4</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="I120" s="1">
         <v>0</v>
       </c>
       <c r="J120" s="12" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="K120" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C121" s="1" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
@@ -8461,30 +8292,30 @@
         <v>4</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I121" s="1">
         <v>0</v>
       </c>
       <c r="J121" s="12" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="K121" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C122" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
@@ -8493,30 +8324,30 @@
         <v>4</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="I122" s="1">
         <v>0</v>
       </c>
       <c r="J122" s="12" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="K122" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C123" s="1" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
@@ -8525,30 +8356,30 @@
         <v>4</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="I123" s="1">
         <v>0</v>
       </c>
       <c r="J123" s="12" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="K123" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C124" s="1" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
@@ -8557,30 +8388,30 @@
         <v>4</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="I124" s="1">
         <v>0</v>
       </c>
       <c r="J124" s="12" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="K124" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C125" s="1" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
@@ -8589,30 +8420,30 @@
         <v>4</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="I125" s="1">
         <v>0</v>
       </c>
       <c r="J125" s="12" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="K125" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C126" s="1" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
@@ -8621,30 +8452,30 @@
         <v>4</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="I126" s="1">
         <v>0</v>
       </c>
       <c r="J126" s="12" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="K126" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C127" s="1" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
@@ -8653,30 +8484,30 @@
         <v>4</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="I127" s="1">
         <v>0</v>
       </c>
       <c r="J127" s="12" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="K127" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C128" s="1" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
@@ -8685,30 +8516,30 @@
         <v>4</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="I128" s="1">
         <v>0</v>
       </c>
       <c r="J128" s="12" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="K128" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C129" s="1" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
@@ -8717,30 +8548,30 @@
         <v>4</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="I129" s="1">
         <v>0</v>
       </c>
       <c r="J129" s="12" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="K129" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C130" s="1" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
@@ -8749,30 +8580,30 @@
         <v>4</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="I130" s="1">
         <v>0</v>
       </c>
       <c r="J130" s="12" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="K130" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="3:12">
       <c r="C131" s="1" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
@@ -8781,30 +8612,30 @@
         <v>4</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="I131" s="1">
         <v>0</v>
       </c>
       <c r="J131" s="12" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="K131" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="3:12">
       <c r="C132" s="1" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
@@ -8813,30 +8644,30 @@
         <v>4</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="I132" s="1">
         <v>0</v>
       </c>
       <c r="J132" s="12" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="K132" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="3:12">
       <c r="C133" s="1" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
@@ -8845,30 +8676,30 @@
         <v>4</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="I133" s="1">
         <v>0</v>
       </c>
       <c r="J133" s="12" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="K133" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="3:12">
       <c r="C134" s="1" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
@@ -8877,30 +8708,30 @@
         <v>4</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="I134" s="1">
         <v>0</v>
       </c>
       <c r="J134" s="12" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="K134" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="3:12">
       <c r="C135" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
@@ -8909,30 +8740,30 @@
         <v>4</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="I135" s="1">
         <v>0</v>
       </c>
       <c r="J135" s="12" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="K135" s="12" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="3:12">
       <c r="C136" s="1" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
@@ -8941,30 +8772,30 @@
         <v>4</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="I136" s="1">
         <v>0</v>
       </c>
       <c r="J136" s="12" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="K136" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="3:12">
       <c r="C137" s="1" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
@@ -8973,30 +8804,30 @@
         <v>4</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="I137" s="1">
         <v>0</v>
       </c>
       <c r="J137" s="12" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="K137" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
@@ -9005,30 +8836,30 @@
         <v>4</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="I138" s="1">
         <v>0</v>
       </c>
       <c r="J138" s="12" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="K138" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
@@ -9037,30 +8868,30 @@
         <v>4</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="I139" s="1">
         <v>0</v>
       </c>
       <c r="J139" s="12" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="K139" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="3:12">
       <c r="C140" s="1" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
@@ -9069,30 +8900,30 @@
         <v>4</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="I140" s="1">
         <v>0</v>
       </c>
       <c r="J140" s="12" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="K140" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C141" s="1" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
@@ -9101,30 +8932,30 @@
         <v>4</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="I141" s="1">
         <v>0</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="K141" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C142" s="1" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
@@ -9133,30 +8964,30 @@
         <v>4</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="I142" s="1">
         <v>0</v>
       </c>
       <c r="J142" s="12" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="K142" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C143" s="1" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
@@ -9165,30 +8996,30 @@
         <v>4</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="I143" s="1">
         <v>0</v>
       </c>
       <c r="J143" s="12" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="K143" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C144" s="1" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
@@ -9197,30 +9028,30 @@
         <v>4</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="I144" s="1">
         <v>0</v>
       </c>
       <c r="J144" s="12" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="K144" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C145" s="1" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
@@ -9229,30 +9060,30 @@
         <v>4</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="I145" s="1">
         <v>0</v>
       </c>
       <c r="J145" s="12" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="K145" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="146" s="3" customFormat="1" customHeight="1" spans="3:12">
       <c r="C146" s="3" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="E146" s="3">
         <v>5</v>
@@ -9261,30 +9092,30 @@
         <v>5</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="H146" s="3" t="s">
-        <v>835</v>
+        <v>830</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>831</v>
       </c>
       <c r="I146" s="3">
         <v>0</v>
       </c>
       <c r="J146" s="13" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="K146" s="13" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L146" s="13" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="E147" s="1">
         <v>5</v>
@@ -9293,30 +9124,30 @@
         <v>5</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="I147" s="1">
         <v>0</v>
       </c>
       <c r="J147" s="12" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="K147" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L147" s="11" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="E148" s="1">
         <v>5</v>
@@ -9325,30 +9156,30 @@
         <v>5</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="I148" s="1">
         <v>0</v>
       </c>
       <c r="J148" s="12" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="K148" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L148" s="11" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="E149" s="1">
         <v>5</v>
@@ -9357,30 +9188,30 @@
         <v>5</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>851</v>
+        <v>837</v>
       </c>
       <c r="I149" s="1">
         <v>0</v>
       </c>
       <c r="J149" s="12" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="K149" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L149" s="11" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="3:12">
       <c r="C150" s="1" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="E150" s="1">
         <v>5</v>
@@ -9389,30 +9220,30 @@
         <v>5</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>856</v>
+        <v>837</v>
       </c>
       <c r="I150" s="1">
         <v>0</v>
       </c>
       <c r="J150" s="12" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="K150" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L150" s="11" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="3:12">
       <c r="C151" s="1" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
@@ -9421,30 +9252,30 @@
         <v>5</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="I151" s="1">
         <v>0</v>
       </c>
       <c r="J151" s="12" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="K151" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L151" s="11" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="3:12">
       <c r="C152" s="1" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
@@ -9453,30 +9284,30 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>867</v>
+        <v>854</v>
       </c>
       <c r="I152" s="1">
         <v>0</v>
       </c>
       <c r="J152" s="12" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="K152" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L152" s="11" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="3:12">
       <c r="C153" s="1" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
@@ -9485,30 +9316,30 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>872</v>
+        <v>854</v>
       </c>
       <c r="I153" s="1">
         <v>0</v>
       </c>
       <c r="J153" s="12" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="K153" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L153" s="11" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="3:12">
       <c r="C154" s="1" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
@@ -9517,30 +9348,30 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>877</v>
+        <v>854</v>
       </c>
       <c r="I154" s="1">
         <v>0</v>
       </c>
       <c r="J154" s="12" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="K154" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L154" s="11" t="s">
-        <v>878</v>
+        <v>868</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="3:12">
       <c r="C155" s="1" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
@@ -9549,30 +9380,30 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>882</v>
+        <v>854</v>
       </c>
       <c r="I155" s="1">
         <v>0</v>
       </c>
       <c r="J155" s="12" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="K155" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L155" s="11" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C156" s="1" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>885</v>
+        <v>874</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
@@ -9581,30 +9412,30 @@
         <v>5</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>886</v>
+        <v>875</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="I156" s="1">
         <v>0</v>
       </c>
       <c r="J156" s="12" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="K156" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L156" s="11" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C157" s="1" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
@@ -9613,30 +9444,30 @@
         <v>5</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>893</v>
+        <v>876</v>
       </c>
       <c r="I157" s="1">
         <v>0</v>
       </c>
       <c r="J157" s="12" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="K157" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L157" s="11" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C158" s="1" t="s">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>896</v>
+        <v>884</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
@@ -9645,30 +9476,30 @@
         <v>5</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>897</v>
+        <v>885</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>898</v>
+        <v>876</v>
       </c>
       <c r="I158" s="1">
         <v>0</v>
       </c>
       <c r="J158" s="12" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="K158" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L158" s="11" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C159" s="1" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
@@ -9677,30 +9508,30 @@
         <v>5</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>902</v>
+        <v>889</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>903</v>
+        <v>876</v>
       </c>
       <c r="I159" s="1">
         <v>0</v>
       </c>
       <c r="J159" s="12" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="K159" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L159" s="11" t="s">
-        <v>904</v>
+        <v>890</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C160" s="1" t="s">
-        <v>905</v>
+        <v>891</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>906</v>
+        <v>892</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
@@ -9709,30 +9540,30 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>907</v>
+        <v>893</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>908</v>
+        <v>876</v>
       </c>
       <c r="I160" s="1">
         <v>0</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="K160" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L160" s="11" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C161" s="1" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
@@ -9741,30 +9572,30 @@
         <v>5</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
       <c r="J161" s="12" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="K161" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L161" s="11" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C162" s="1" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
@@ -9773,30 +9604,30 @@
         <v>5</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>918</v>
+        <v>903</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>919</v>
+        <v>898</v>
       </c>
       <c r="I162" s="1">
         <v>0</v>
       </c>
       <c r="J162" s="12" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="K162" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L162" s="11" t="s">
-        <v>920</v>
+        <v>904</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C163" s="1" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>922</v>
+        <v>906</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9805,30 +9636,30 @@
         <v>5</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>924</v>
+        <v>898</v>
       </c>
       <c r="I163" s="1">
         <v>0</v>
       </c>
       <c r="J163" s="12" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="K163" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L163" s="11" t="s">
-        <v>925</v>
+        <v>908</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C164" s="1" t="s">
-        <v>926</v>
+        <v>909</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>927</v>
+        <v>910</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
@@ -9837,30 +9668,30 @@
         <v>5</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>928</v>
+        <v>911</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>929</v>
+        <v>898</v>
       </c>
       <c r="I164" s="1">
         <v>0</v>
       </c>
       <c r="J164" s="12" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="K164" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L164" s="11" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C165" s="1" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -9869,30 +9700,30 @@
         <v>5</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>934</v>
+        <v>898</v>
       </c>
       <c r="I165" s="1">
         <v>0</v>
       </c>
       <c r="J165" s="12" t="s">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="K165" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L165" s="11" t="s">
-        <v>935</v>
+        <v>916</v>
       </c>
     </row>
     <row r="166" customHeight="1" spans="3:12">
       <c r="C166" s="1" t="s">
-        <v>936</v>
+        <v>917</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>937</v>
+        <v>918</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
@@ -9901,30 +9732,30 @@
         <v>5</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>938</v>
+        <v>919</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
       </c>
       <c r="J166" s="12" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="K166" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L166" s="11" t="s">
-        <v>941</v>
+        <v>922</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="3:12">
       <c r="C167" s="1" t="s">
-        <v>942</v>
+        <v>923</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>943</v>
+        <v>924</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
@@ -9933,30 +9764,30 @@
         <v>5</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>944</v>
+        <v>925</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>945</v>
+        <v>920</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
       </c>
       <c r="J167" s="12" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="K167" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L167" s="11" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
     </row>
     <row r="168" customHeight="1" spans="3:12">
       <c r="C168" s="1" t="s">
-        <v>947</v>
+        <v>927</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>948</v>
+        <v>928</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -9965,30 +9796,30 @@
         <v>5</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>949</v>
+        <v>929</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>950</v>
+        <v>920</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
       </c>
       <c r="J168" s="12" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="K168" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L168" s="11" t="s">
-        <v>951</v>
+        <v>930</v>
       </c>
     </row>
     <row r="169" customHeight="1" spans="3:12">
       <c r="C169" s="1" t="s">
-        <v>952</v>
+        <v>931</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>953</v>
+        <v>932</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
@@ -9997,30 +9828,30 @@
         <v>5</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>954</v>
+        <v>933</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
       </c>
       <c r="J169" s="12" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="K169" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L169" s="11" t="s">
-        <v>956</v>
+        <v>934</v>
       </c>
     </row>
     <row r="170" customHeight="1" spans="3:12">
       <c r="C170" s="1" t="s">
-        <v>957</v>
+        <v>935</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>958</v>
+        <v>936</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -10029,30 +9860,30 @@
         <v>5</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>959</v>
+        <v>937</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>960</v>
+        <v>920</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
       </c>
       <c r="J170" s="12" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="K170" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L170" s="11" t="s">
-        <v>961</v>
+        <v>938</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="3:12">
       <c r="C171" s="1" t="s">
-        <v>962</v>
+        <v>939</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>963</v>
+        <v>940</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -10061,30 +9892,30 @@
         <v>5</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>964</v>
+        <v>941</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>965</v>
+        <v>942</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
       </c>
       <c r="J171" s="12" t="s">
-        <v>966</v>
+        <v>943</v>
       </c>
       <c r="K171" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L171" s="11" t="s">
-        <v>967</v>
+        <v>944</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="3:12">
       <c r="C172" s="1" t="s">
-        <v>968</v>
+        <v>945</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>969</v>
+        <v>946</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
@@ -10093,30 +9924,30 @@
         <v>5</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>970</v>
+        <v>947</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>971</v>
+        <v>942</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
       </c>
       <c r="J172" s="12" t="s">
-        <v>966</v>
+        <v>943</v>
       </c>
       <c r="K172" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L172" s="11" t="s">
-        <v>972</v>
+        <v>948</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="3:12">
       <c r="C173" s="1" t="s">
-        <v>973</v>
+        <v>949</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>974</v>
+        <v>950</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
@@ -10125,30 +9956,30 @@
         <v>5</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>975</v>
+        <v>951</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>976</v>
+        <v>942</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
       </c>
       <c r="J173" s="12" t="s">
-        <v>966</v>
+        <v>943</v>
       </c>
       <c r="K173" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L173" s="11" t="s">
-        <v>977</v>
+        <v>952</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="3:12">
       <c r="C174" s="1" t="s">
-        <v>978</v>
+        <v>953</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>979</v>
+        <v>954</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -10157,30 +9988,30 @@
         <v>5</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>980</v>
+        <v>955</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>981</v>
+        <v>942</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
       </c>
       <c r="J174" s="12" t="s">
-        <v>966</v>
+        <v>943</v>
       </c>
       <c r="K174" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L174" s="11" t="s">
-        <v>982</v>
+        <v>956</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="3:12">
       <c r="C175" s="1" t="s">
-        <v>983</v>
+        <v>957</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>984</v>
+        <v>958</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
@@ -10189,30 +10020,30 @@
         <v>5</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>985</v>
+        <v>959</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>986</v>
+        <v>942</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
       </c>
       <c r="J175" s="12" t="s">
-        <v>966</v>
+        <v>943</v>
       </c>
       <c r="K175" s="12" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L175" s="11" t="s">
-        <v>987</v>
+        <v>960</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C176" s="1" t="s">
-        <v>988</v>
+        <v>961</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>989</v>
+        <v>962</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
@@ -10221,30 +10052,30 @@
         <v>5</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>990</v>
+        <v>963</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>991</v>
+        <v>964</v>
       </c>
       <c r="I176" s="1">
         <v>0</v>
       </c>
       <c r="J176" s="12" t="s">
-        <v>992</v>
+        <v>965</v>
       </c>
       <c r="K176" s="12" t="s">
-        <v>993</v>
+        <v>966</v>
       </c>
       <c r="L176" s="11" t="s">
-        <v>994</v>
+        <v>967</v>
       </c>
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C177" s="1" t="s">
-        <v>995</v>
+        <v>968</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>996</v>
+        <v>969</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
@@ -10253,30 +10084,30 @@
         <v>5</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>997</v>
+        <v>970</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>998</v>
+        <v>971</v>
       </c>
       <c r="I177" s="1">
         <v>0</v>
       </c>
       <c r="J177" s="12" t="s">
-        <v>992</v>
+        <v>965</v>
       </c>
       <c r="K177" s="12" t="s">
-        <v>993</v>
+        <v>966</v>
       </c>
       <c r="L177" s="11" t="s">
-        <v>999</v>
+        <v>972</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C178" s="1" t="s">
-        <v>1000</v>
+        <v>973</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1001</v>
+        <v>974</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
@@ -10285,30 +10116,30 @@
         <v>5</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>1002</v>
+        <v>975</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>1003</v>
+        <v>971</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
       </c>
       <c r="J178" s="12" t="s">
-        <v>992</v>
+        <v>965</v>
       </c>
       <c r="K178" s="12" t="s">
-        <v>993</v>
+        <v>966</v>
       </c>
       <c r="L178" s="11" t="s">
-        <v>1004</v>
+        <v>976</v>
       </c>
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C179" s="1" t="s">
-        <v>1005</v>
+        <v>977</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>1006</v>
+        <v>978</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -10317,30 +10148,30 @@
         <v>5</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>1007</v>
+        <v>979</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>1008</v>
+        <v>971</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
       </c>
       <c r="J179" s="12" t="s">
-        <v>992</v>
+        <v>965</v>
       </c>
       <c r="K179" s="12" t="s">
-        <v>993</v>
+        <v>966</v>
       </c>
       <c r="L179" s="11" t="s">
-        <v>1009</v>
+        <v>980</v>
       </c>
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C180" s="1" t="s">
-        <v>1010</v>
+        <v>981</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>1011</v>
+        <v>982</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
@@ -10349,30 +10180,30 @@
         <v>5</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1012</v>
+        <v>983</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>1013</v>
+        <v>971</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
       </c>
       <c r="J180" s="12" t="s">
-        <v>992</v>
+        <v>965</v>
       </c>
       <c r="K180" s="12" t="s">
-        <v>993</v>
+        <v>966</v>
       </c>
       <c r="L180" s="11" t="s">
-        <v>1014</v>
+        <v>984</v>
       </c>
     </row>
     <row r="181" s="3" customFormat="1" customHeight="1" spans="3:12">
       <c r="C181" s="1" t="s">
-        <v>1015</v>
+        <v>985</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>1016</v>
+        <v>986</v>
       </c>
       <c r="E181" s="3">
         <v>5</v>
@@ -10381,30 +10212,30 @@
         <v>5</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="H181" s="3" t="s">
-        <v>1018</v>
+        <v>987</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>988</v>
       </c>
       <c r="I181" s="3">
         <v>0</v>
       </c>
       <c r="J181" s="13" t="s">
-        <v>1019</v>
+        <v>989</v>
       </c>
       <c r="K181" s="13" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L181" s="11" t="s">
-        <v>1021</v>
+        <v>991</v>
       </c>
     </row>
     <row r="182" customHeight="1" spans="3:12">
       <c r="C182" s="1" t="s">
-        <v>1022</v>
+        <v>992</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>1023</v>
+        <v>993</v>
       </c>
       <c r="E182" s="1">
         <v>5</v>
@@ -10413,30 +10244,30 @@
         <v>5</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>1024</v>
+        <v>994</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>1025</v>
+        <v>995</v>
       </c>
       <c r="I182" s="1">
         <v>0</v>
       </c>
       <c r="J182" s="12" t="s">
-        <v>1026</v>
+        <v>996</v>
       </c>
       <c r="K182" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L182" s="11" t="s">
-        <v>1027</v>
+        <v>997</v>
       </c>
     </row>
     <row r="183" customHeight="1" spans="3:12">
       <c r="C183" s="1" t="s">
-        <v>1028</v>
+        <v>998</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>1029</v>
+        <v>999</v>
       </c>
       <c r="E183" s="1">
         <v>5</v>
@@ -10445,30 +10276,30 @@
         <v>5</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>1031</v>
+        <v>995</v>
       </c>
       <c r="I183" s="1">
         <v>0</v>
       </c>
       <c r="J183" s="12" t="s">
-        <v>1032</v>
+        <v>1001</v>
       </c>
       <c r="K183" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L183" s="11" t="s">
-        <v>1033</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="184" customHeight="1" spans="3:12">
       <c r="C184" s="1" t="s">
-        <v>1034</v>
+        <v>1003</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>1035</v>
+        <v>1004</v>
       </c>
       <c r="E184" s="1">
         <v>5</v>
@@ -10477,30 +10308,30 @@
         <v>5</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>1036</v>
+        <v>1005</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>1037</v>
+        <v>995</v>
       </c>
       <c r="I184" s="1">
         <v>0</v>
       </c>
       <c r="J184" s="12" t="s">
-        <v>1038</v>
+        <v>1006</v>
       </c>
       <c r="K184" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L184" s="11" t="s">
-        <v>1039</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="185" customHeight="1" spans="3:12">
       <c r="C185" s="1" t="s">
-        <v>1040</v>
+        <v>1008</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>1041</v>
+        <v>1009</v>
       </c>
       <c r="E185" s="1">
         <v>5</v>
@@ -10509,30 +10340,30 @@
         <v>5</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1042</v>
+        <v>1010</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>1043</v>
+        <v>995</v>
       </c>
       <c r="I185" s="1">
         <v>0</v>
       </c>
       <c r="J185" s="12" t="s">
-        <v>1044</v>
+        <v>1011</v>
       </c>
       <c r="K185" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L185" s="11" t="s">
-        <v>1045</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="186" customHeight="1" spans="3:12">
       <c r="C186" s="1" t="s">
-        <v>1046</v>
+        <v>1013</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>1047</v>
+        <v>1014</v>
       </c>
       <c r="E186" s="1">
         <v>5</v>
@@ -10541,30 +10372,30 @@
         <v>5</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1048</v>
+        <v>1015</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>1049</v>
+        <v>1016</v>
       </c>
       <c r="I186" s="1">
         <v>0</v>
       </c>
       <c r="J186" s="12" t="s">
-        <v>1050</v>
+        <v>1017</v>
       </c>
       <c r="K186" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L186" s="11" t="s">
-        <v>1051</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="187" customHeight="1" spans="3:12">
       <c r="C187" s="1" t="s">
-        <v>1052</v>
+        <v>1019</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>1053</v>
+        <v>1020</v>
       </c>
       <c r="E187" s="1">
         <v>5</v>
@@ -10573,30 +10404,30 @@
         <v>5</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1054</v>
+        <v>1021</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>1055</v>
+        <v>1016</v>
       </c>
       <c r="I187" s="1">
         <v>0</v>
       </c>
       <c r="J187" s="12" t="s">
-        <v>1050</v>
+        <v>1017</v>
       </c>
       <c r="K187" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L187" s="11" t="s">
-        <v>1056</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="188" customHeight="1" spans="3:12">
       <c r="C188" s="1" t="s">
-        <v>1057</v>
+        <v>1023</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>1058</v>
+        <v>1024</v>
       </c>
       <c r="E188" s="1">
         <v>5</v>
@@ -10605,30 +10436,30 @@
         <v>5</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1059</v>
+        <v>1025</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>1060</v>
+        <v>1016</v>
       </c>
       <c r="I188" s="1">
         <v>0</v>
       </c>
       <c r="J188" s="12" t="s">
-        <v>1050</v>
+        <v>1017</v>
       </c>
       <c r="K188" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L188" s="11" t="s">
-        <v>1061</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="189" customHeight="1" spans="3:12">
       <c r="C189" s="1" t="s">
-        <v>1062</v>
+        <v>1027</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>1063</v>
+        <v>1028</v>
       </c>
       <c r="E189" s="1">
         <v>5</v>
@@ -10637,30 +10468,30 @@
         <v>5</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1064</v>
+        <v>1029</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>1065</v>
+        <v>1016</v>
       </c>
       <c r="I189" s="1">
         <v>0</v>
       </c>
       <c r="J189" s="12" t="s">
-        <v>1050</v>
+        <v>1017</v>
       </c>
       <c r="K189" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L189" s="11" t="s">
-        <v>1066</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="190" customHeight="1" spans="3:12">
       <c r="C190" s="1" t="s">
-        <v>1067</v>
+        <v>1031</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>1068</v>
+        <v>1032</v>
       </c>
       <c r="E190" s="1">
         <v>5</v>
@@ -10669,30 +10500,30 @@
         <v>5</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1069</v>
+        <v>1033</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>1070</v>
+        <v>1016</v>
       </c>
       <c r="I190" s="1">
         <v>0</v>
       </c>
       <c r="J190" s="12" t="s">
-        <v>1050</v>
+        <v>1017</v>
       </c>
       <c r="K190" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L190" s="11" t="s">
-        <v>1071</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="191" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C191" s="1" t="s">
-        <v>1072</v>
+        <v>1035</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>1073</v>
+        <v>1036</v>
       </c>
       <c r="E191" s="1">
         <v>5</v>
@@ -10701,30 +10532,30 @@
         <v>5</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>1074</v>
+        <v>1037</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>1075</v>
+        <v>1038</v>
       </c>
       <c r="I191" s="1">
         <v>0</v>
       </c>
       <c r="J191" s="12" t="s">
-        <v>1076</v>
+        <v>1039</v>
       </c>
       <c r="K191" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L191" s="11" t="s">
-        <v>1077</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="192" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C192" s="1" t="s">
-        <v>1078</v>
+        <v>1041</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>1079</v>
+        <v>1042</v>
       </c>
       <c r="E192" s="1">
         <v>5</v>
@@ -10733,30 +10564,30 @@
         <v>5</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>1080</v>
+        <v>1043</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>1081</v>
+        <v>1038</v>
       </c>
       <c r="I192" s="1">
         <v>0</v>
       </c>
       <c r="J192" s="12" t="s">
-        <v>1076</v>
+        <v>1039</v>
       </c>
       <c r="K192" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L192" s="11" t="s">
-        <v>1082</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="193" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C193" s="1" t="s">
-        <v>1083</v>
+        <v>1045</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>1084</v>
+        <v>1046</v>
       </c>
       <c r="E193" s="1">
         <v>5</v>
@@ -10765,30 +10596,30 @@
         <v>5</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>1085</v>
+        <v>1047</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>1086</v>
+        <v>1038</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
       </c>
       <c r="J193" s="12" t="s">
-        <v>1076</v>
+        <v>1039</v>
       </c>
       <c r="K193" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L193" s="11" t="s">
-        <v>1087</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="194" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C194" s="1" t="s">
-        <v>1088</v>
+        <v>1049</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>1089</v>
+        <v>1050</v>
       </c>
       <c r="E194" s="1">
         <v>5</v>
@@ -10797,30 +10628,30 @@
         <v>5</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>1090</v>
+        <v>1051</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>1091</v>
+        <v>1038</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
       </c>
       <c r="J194" s="12" t="s">
-        <v>1076</v>
+        <v>1039</v>
       </c>
       <c r="K194" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L194" s="11" t="s">
-        <v>1092</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="195" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C195" s="1" t="s">
-        <v>1093</v>
+        <v>1053</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>1094</v>
+        <v>1054</v>
       </c>
       <c r="E195" s="1">
         <v>5</v>
@@ -10829,30 +10660,30 @@
         <v>5</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>1095</v>
+        <v>1055</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>1096</v>
+        <v>1038</v>
       </c>
       <c r="I195" s="1">
         <v>0</v>
       </c>
       <c r="J195" s="12" t="s">
-        <v>1076</v>
+        <v>1039</v>
       </c>
       <c r="K195" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L195" s="11" t="s">
-        <v>1097</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="196" s="4" customFormat="1" customHeight="1" spans="3:12">
       <c r="C196" s="4" t="s">
-        <v>1098</v>
+        <v>1057</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>1099</v>
+        <v>1058</v>
       </c>
       <c r="E196" s="4">
         <v>5</v>
@@ -10861,30 +10692,30 @@
         <v>5</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H196" s="4" t="s">
-        <v>1101</v>
+        <v>1059</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>1060</v>
       </c>
       <c r="I196" s="4">
         <v>0</v>
       </c>
       <c r="J196" s="14" t="s">
-        <v>1102</v>
+        <v>1061</v>
       </c>
       <c r="K196" s="14" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L196" s="14" t="s">
-        <v>1103</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="197" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C197" s="1" t="s">
-        <v>1104</v>
+        <v>1063</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>1105</v>
+        <v>1064</v>
       </c>
       <c r="E197" s="1">
         <v>5</v>
@@ -10893,30 +10724,30 @@
         <v>5</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>1106</v>
+        <v>1065</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1107</v>
+        <v>1060</v>
       </c>
       <c r="I197" s="1">
         <v>0</v>
       </c>
       <c r="J197" s="12" t="s">
-        <v>1102</v>
+        <v>1061</v>
       </c>
       <c r="K197" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L197" s="11" t="s">
-        <v>1108</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="198" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C198" s="1" t="s">
-        <v>1109</v>
+        <v>1067</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>1110</v>
+        <v>1068</v>
       </c>
       <c r="E198" s="1">
         <v>5</v>
@@ -10925,30 +10756,30 @@
         <v>5</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>1111</v>
+        <v>1069</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>1112</v>
+        <v>1060</v>
       </c>
       <c r="I198" s="1">
         <v>0</v>
       </c>
       <c r="J198" s="12" t="s">
-        <v>1102</v>
+        <v>1061</v>
       </c>
       <c r="K198" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L198" s="11" t="s">
-        <v>1113</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="199" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C199" s="1" t="s">
-        <v>1114</v>
+        <v>1071</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>1115</v>
+        <v>1072</v>
       </c>
       <c r="E199" s="1">
         <v>5</v>
@@ -10957,30 +10788,30 @@
         <v>5</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>1116</v>
+        <v>1073</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>1117</v>
+        <v>1060</v>
       </c>
       <c r="I199" s="1">
         <v>0</v>
       </c>
       <c r="J199" s="12" t="s">
-        <v>1102</v>
+        <v>1061</v>
       </c>
       <c r="K199" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L199" s="11" t="s">
-        <v>1118</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="200" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C200" s="1" t="s">
-        <v>1119</v>
+        <v>1075</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>1120</v>
+        <v>1076</v>
       </c>
       <c r="E200" s="1">
         <v>5</v>
@@ -10989,30 +10820,30 @@
         <v>5</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>1121</v>
+        <v>1077</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1122</v>
+        <v>1060</v>
       </c>
       <c r="I200" s="1">
         <v>0</v>
       </c>
       <c r="J200" s="12" t="s">
-        <v>1102</v>
+        <v>1061</v>
       </c>
       <c r="K200" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L200" s="11" t="s">
-        <v>1123</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="201" customHeight="1" spans="3:12">
       <c r="C201" s="1" t="s">
-        <v>1124</v>
+        <v>1079</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1125</v>
+        <v>1080</v>
       </c>
       <c r="E201" s="1">
         <v>5</v>
@@ -11021,30 +10852,30 @@
         <v>5</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>1126</v>
+        <v>1081</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1127</v>
+        <v>1082</v>
       </c>
       <c r="I201" s="1">
         <v>0</v>
       </c>
       <c r="J201" s="12" t="s">
-        <v>1128</v>
+        <v>1083</v>
       </c>
       <c r="K201" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L201" s="11" t="s">
-        <v>1129</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="202" customHeight="1" spans="3:12">
       <c r="C202" s="1" t="s">
-        <v>1130</v>
+        <v>1085</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1131</v>
+        <v>1086</v>
       </c>
       <c r="E202" s="1">
         <v>5</v>
@@ -11053,30 +10884,30 @@
         <v>5</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>1132</v>
+        <v>1087</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>1133</v>
+        <v>1082</v>
       </c>
       <c r="I202" s="1">
         <v>0</v>
       </c>
       <c r="J202" s="12" t="s">
-        <v>1128</v>
+        <v>1083</v>
       </c>
       <c r="K202" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L202" s="11" t="s">
-        <v>1134</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="203" customHeight="1" spans="3:12">
       <c r="C203" s="1" t="s">
-        <v>1135</v>
+        <v>1089</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>1136</v>
+        <v>1090</v>
       </c>
       <c r="E203" s="1">
         <v>5</v>
@@ -11085,30 +10916,30 @@
         <v>5</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>1137</v>
+        <v>1091</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>1138</v>
+        <v>1082</v>
       </c>
       <c r="I203" s="1">
         <v>0</v>
       </c>
       <c r="J203" s="12" t="s">
-        <v>1128</v>
+        <v>1083</v>
       </c>
       <c r="K203" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L203" s="11" t="s">
-        <v>1139</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="204" customHeight="1" spans="3:12">
       <c r="C204" s="1" t="s">
-        <v>1140</v>
+        <v>1093</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1141</v>
+        <v>1094</v>
       </c>
       <c r="E204" s="1">
         <v>5</v>
@@ -11117,30 +10948,30 @@
         <v>5</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>1142</v>
+        <v>1095</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>1143</v>
+        <v>1082</v>
       </c>
       <c r="I204" s="1">
         <v>0</v>
       </c>
       <c r="J204" s="12" t="s">
-        <v>1128</v>
+        <v>1083</v>
       </c>
       <c r="K204" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L204" s="11" t="s">
-        <v>1144</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="205" customHeight="1" spans="3:12">
       <c r="C205" s="1" t="s">
-        <v>1145</v>
+        <v>1097</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1146</v>
+        <v>1098</v>
       </c>
       <c r="E205" s="1">
         <v>5</v>
@@ -11149,30 +10980,30 @@
         <v>5</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>1147</v>
+        <v>1099</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>1148</v>
+        <v>1082</v>
       </c>
       <c r="I205" s="1">
         <v>0</v>
       </c>
       <c r="J205" s="12" t="s">
-        <v>1128</v>
+        <v>1083</v>
       </c>
       <c r="K205" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L205" s="11" t="s">
-        <v>1149</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="206" customHeight="1" spans="3:12">
       <c r="C206" s="1" t="s">
-        <v>1150</v>
+        <v>1101</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>1151</v>
+        <v>1102</v>
       </c>
       <c r="E206" s="1">
         <v>5</v>
@@ -11181,30 +11012,30 @@
         <v>5</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>1152</v>
+        <v>1103</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>1153</v>
+        <v>1104</v>
       </c>
       <c r="I206" s="1">
         <v>0</v>
       </c>
       <c r="J206" s="12" t="s">
-        <v>1154</v>
+        <v>1105</v>
       </c>
       <c r="K206" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L206" s="11" t="s">
-        <v>1155</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="207" customHeight="1" spans="3:12">
       <c r="C207" s="1" t="s">
-        <v>1156</v>
+        <v>1107</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1157</v>
+        <v>1108</v>
       </c>
       <c r="E207" s="1">
         <v>5</v>
@@ -11213,30 +11044,30 @@
         <v>5</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>1158</v>
+        <v>1109</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>1159</v>
+        <v>1104</v>
       </c>
       <c r="I207" s="1">
         <v>0</v>
       </c>
       <c r="J207" s="12" t="s">
-        <v>1154</v>
+        <v>1105</v>
       </c>
       <c r="K207" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L207" s="11" t="s">
-        <v>1160</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="208" customHeight="1" spans="3:12">
       <c r="C208" s="1" t="s">
-        <v>1161</v>
+        <v>1111</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1162</v>
+        <v>1112</v>
       </c>
       <c r="E208" s="1">
         <v>5</v>
@@ -11245,30 +11076,30 @@
         <v>5</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>1163</v>
+        <v>1113</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>1164</v>
+        <v>1104</v>
       </c>
       <c r="I208" s="1">
         <v>0</v>
       </c>
       <c r="J208" s="12" t="s">
-        <v>1154</v>
+        <v>1105</v>
       </c>
       <c r="K208" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L208" s="11" t="s">
-        <v>1165</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="209" customHeight="1" spans="1:12">
       <c r="C209" s="1" t="s">
-        <v>1166</v>
+        <v>1115</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1167</v>
+        <v>1116</v>
       </c>
       <c r="E209" s="1">
         <v>5</v>
@@ -11277,30 +11108,30 @@
         <v>5</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>1168</v>
+        <v>1117</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>1169</v>
+        <v>1104</v>
       </c>
       <c r="I209" s="1">
         <v>0</v>
       </c>
       <c r="J209" s="12" t="s">
-        <v>1154</v>
+        <v>1105</v>
       </c>
       <c r="K209" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L209" s="11" t="s">
-        <v>1170</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="210" customHeight="1" spans="1:12">
       <c r="C210" s="1" t="s">
-        <v>1171</v>
+        <v>1119</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1172</v>
+        <v>1120</v>
       </c>
       <c r="E210" s="1">
         <v>5</v>
@@ -11309,30 +11140,30 @@
         <v>5</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>1173</v>
+        <v>1121</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>1174</v>
+        <v>1104</v>
       </c>
       <c r="I210" s="1">
         <v>0</v>
       </c>
       <c r="J210" s="12" t="s">
-        <v>1154</v>
+        <v>1105</v>
       </c>
       <c r="K210" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L210" s="11" t="s">
-        <v>1175</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C211" s="1" t="s">
-        <v>1176</v>
+        <v>1123</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1177</v>
+        <v>1124</v>
       </c>
       <c r="E211" s="1">
         <v>5</v>
@@ -11341,30 +11172,30 @@
         <v>5</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>1178</v>
+        <v>1125</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>1179</v>
+        <v>1126</v>
       </c>
       <c r="I211" s="1">
         <v>0</v>
       </c>
       <c r="J211" s="12" t="s">
-        <v>1180</v>
+        <v>1127</v>
       </c>
       <c r="K211" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L211" s="11" t="s">
-        <v>1181</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C212" s="1" t="s">
-        <v>1182</v>
+        <v>1129</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1183</v>
+        <v>1130</v>
       </c>
       <c r="E212" s="1">
         <v>5</v>
@@ -11373,30 +11204,30 @@
         <v>5</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>1184</v>
+        <v>1131</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1185</v>
+        <v>1126</v>
       </c>
       <c r="I212" s="1">
         <v>0</v>
       </c>
       <c r="J212" s="12" t="s">
-        <v>1180</v>
+        <v>1127</v>
       </c>
       <c r="K212" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L212" s="11" t="s">
-        <v>1186</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C213" s="1" t="s">
-        <v>1187</v>
+        <v>1133</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1188</v>
+        <v>1134</v>
       </c>
       <c r="E213" s="1">
         <v>5</v>
@@ -11405,30 +11236,30 @@
         <v>5</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>1189</v>
+        <v>1135</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>1190</v>
+        <v>1126</v>
       </c>
       <c r="I213" s="1">
         <v>0</v>
       </c>
       <c r="J213" s="12" t="s">
-        <v>1180</v>
+        <v>1127</v>
       </c>
       <c r="K213" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L213" s="11" t="s">
-        <v>1191</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C214" s="1" t="s">
-        <v>1192</v>
+        <v>1137</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>1193</v>
+        <v>1138</v>
       </c>
       <c r="E214" s="1">
         <v>5</v>
@@ -11437,30 +11268,30 @@
         <v>5</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>1194</v>
+        <v>1139</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>1195</v>
+        <v>1126</v>
       </c>
       <c r="I214" s="1">
         <v>0</v>
       </c>
       <c r="J214" s="12" t="s">
-        <v>1180</v>
+        <v>1127</v>
       </c>
       <c r="K214" s="12" t="s">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="L214" s="11" t="s">
-        <v>1196</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C215" s="1" t="s">
-        <v>1197</v>
+        <v>1141</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1198</v>
+        <v>1142</v>
       </c>
       <c r="E215" s="1">
         <v>5</v>
@@ -11469,36 +11300,36 @@
         <v>5</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>1199</v>
+        <v>1143</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>1200</v>
+        <v>1144</v>
       </c>
       <c r="I215" s="1">
         <v>0</v>
       </c>
       <c r="J215" s="12" t="s">
-        <v>1201</v>
+        <v>1145</v>
       </c>
       <c r="K215" s="12" t="s">
-        <v>1202</v>
+        <v>1146</v>
       </c>
       <c r="L215" s="11" t="s">
-        <v>1203</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="216" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A216" s="3" t="s">
-        <v>1204</v>
+        <v>1148</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>1204</v>
+        <v>1148</v>
       </c>
       <c r="C216" s="1">
         <v>1210</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>1205</v>
+        <v>1149</v>
       </c>
       <c r="E216" s="3">
         <v>5</v>
@@ -11507,36 +11338,36 @@
         <v>5</v>
       </c>
       <c r="G216" s="10" t="s">
-        <v>1206</v>
+        <v>1150</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>1207</v>
+        <v>1144</v>
       </c>
       <c r="I216" s="3">
         <v>0</v>
       </c>
       <c r="J216" s="13" t="s">
-        <v>1208</v>
+        <v>1151</v>
       </c>
       <c r="K216" s="13" t="s">
-        <v>1202</v>
+        <v>1146</v>
       </c>
       <c r="L216" s="11" t="s">
-        <v>1209</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="217" customHeight="1" spans="1:12">
       <c r="A217" s="3" t="s">
-        <v>1204</v>
+        <v>1148</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>1204</v>
+        <v>1148</v>
       </c>
       <c r="C217" s="1">
         <v>1211</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>1210</v>
+        <v>1153</v>
       </c>
       <c r="E217" s="1">
         <v>5</v>
@@ -11545,36 +11376,36 @@
         <v>5</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1211</v>
+        <v>1154</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>1212</v>
+        <v>1155</v>
       </c>
       <c r="I217" s="1">
         <v>0</v>
       </c>
       <c r="J217" s="12" t="s">
-        <v>1213</v>
+        <v>1156</v>
       </c>
       <c r="K217" s="12" t="s">
-        <v>1202</v>
+        <v>1146</v>
       </c>
       <c r="L217" s="11" t="s">
-        <v>1214</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="218" customHeight="1" spans="1:12">
       <c r="A218" s="3" t="s">
-        <v>1204</v>
+        <v>1148</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>1204</v>
+        <v>1148</v>
       </c>
       <c r="C218" s="1">
         <v>1212</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>1215</v>
+        <v>1158</v>
       </c>
       <c r="E218" s="1">
         <v>5</v>
@@ -11583,36 +11414,36 @@
         <v>5</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1216</v>
+        <v>1159</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>1217</v>
+        <v>1160</v>
       </c>
       <c r="I218" s="1">
         <v>0</v>
       </c>
       <c r="J218" s="12" t="s">
-        <v>1218</v>
+        <v>1161</v>
       </c>
       <c r="K218" s="12" t="s">
-        <v>1202</v>
+        <v>1146</v>
       </c>
       <c r="L218" s="11" t="s">
-        <v>1219</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="219" customHeight="1" spans="1:12">
       <c r="A219" s="3" t="s">
-        <v>1204</v>
+        <v>1148</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>1204</v>
+        <v>1148</v>
       </c>
       <c r="C219" s="1">
         <v>1213</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>1220</v>
+        <v>1163</v>
       </c>
       <c r="E219" s="1">
         <v>5</v>
@@ -11621,36 +11452,36 @@
         <v>5</v>
       </c>
       <c r="G219" s="8" t="s">
-        <v>1221</v>
+        <v>1164</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>1222</v>
+        <v>1165</v>
       </c>
       <c r="I219" s="1">
         <v>0</v>
       </c>
       <c r="J219" s="12" t="s">
-        <v>1223</v>
+        <v>1166</v>
       </c>
       <c r="K219" s="12" t="s">
-        <v>1202</v>
+        <v>1146</v>
       </c>
       <c r="L219" s="11" t="s">
-        <v>1224</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="220" customHeight="1" spans="1:12">
       <c r="A220" s="3" t="s">
-        <v>1204</v>
+        <v>1148</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>1204</v>
+        <v>1148</v>
       </c>
       <c r="C220" s="1">
         <v>1214</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>1225</v>
+        <v>1168</v>
       </c>
       <c r="E220" s="1">
         <v>5</v>
@@ -11659,22 +11490,22 @@
         <v>5</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>1226</v>
+        <v>1169</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>1227</v>
+        <v>1170</v>
       </c>
       <c r="I220" s="1">
         <v>0</v>
       </c>
       <c r="J220" s="12" t="s">
-        <v>1228</v>
+        <v>1171</v>
       </c>
       <c r="K220" s="12" t="s">
-        <v>1202</v>
+        <v>1146</v>
       </c>
       <c r="L220" s="11" t="s">
-        <v>1229</v>
+        <v>1172</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1230">
   <si>
     <t>_Id</t>
   </si>
@@ -1294,7 +1294,7 @@
     <t>750-1</t>
   </si>
   <si>
-    <t>红装、遗物</t>
+    <t>红装</t>
   </si>
   <si>
     <t>200750,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
@@ -1315,6 +1315,9 @@
     <t>750-2</t>
   </si>
   <si>
+    <t>梦魇鹿茸</t>
+  </si>
+  <si>
     <t>200751,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
@@ -1330,6 +1333,9 @@
     <t>750-3</t>
   </si>
   <si>
+    <t>梦魇草帽</t>
+  </si>
+  <si>
     <t>200752,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
@@ -1345,6 +1351,9 @@
     <t>750-4</t>
   </si>
   <si>
+    <t>梦魇猫爪</t>
+  </si>
+  <si>
     <t>200753,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
@@ -1360,6 +1369,9 @@
     <t>750-5</t>
   </si>
   <si>
+    <t>梦魇花朵</t>
+  </si>
+  <si>
     <t>200754,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,1009</t>
   </si>
   <si>
@@ -1375,7 +1387,7 @@
     <t>800-1</t>
   </si>
   <si>
-    <t>二阶随机升阶石</t>
+    <t>梦魇冰晶，2阶剑甲石</t>
   </si>
   <si>
     <t>200800,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210005,1009</t>
@@ -1396,7 +1408,7 @@
     <t>800-2</t>
   </si>
   <si>
-    <t>二阶剑甲升阶石</t>
+    <t>梦魇蝠翼，2阶链头石</t>
   </si>
   <si>
     <t>200801,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210006,1009</t>
@@ -1414,7 +1426,7 @@
     <t>800-3</t>
   </si>
   <si>
-    <t>二阶链头升阶石</t>
+    <t>梦魇魂火，2阶镯戒石</t>
   </si>
   <si>
     <t>200802,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210007,1009</t>
@@ -1432,7 +1444,7 @@
     <t>800-4</t>
   </si>
   <si>
-    <t>二阶镯戒升阶石</t>
+    <t>梦魇腐肉，2阶腰靴石</t>
   </si>
   <si>
     <t>200803,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210008,1009</t>
@@ -1450,7 +1462,7 @@
     <t>800-5</t>
   </si>
   <si>
-    <t>二阶腰靴升阶石</t>
+    <t>梦魇蛇胆，随机2阶石</t>
   </si>
   <si>
     <t>200804,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210009,1009</t>
@@ -1468,7 +1480,7 @@
     <t>850-1</t>
   </si>
   <si>
-    <t>三阶随机升阶石</t>
+    <t>梦魇狼爪，3阶剑甲石</t>
   </si>
   <si>
     <t>200850,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210010,1009</t>
@@ -1486,7 +1498,7 @@
     <t>850-2</t>
   </si>
   <si>
-    <t>三阶剑甲升阶石</t>
+    <t>梦魇虫皮，3阶链头石</t>
   </si>
   <si>
     <t>200851,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210011,1009</t>
@@ -1504,7 +1516,7 @@
     <t>850-3</t>
   </si>
   <si>
-    <t>三阶链头升阶石</t>
+    <t>梦魇鹰羽，3阶镯戒石</t>
   </si>
   <si>
     <t>200852,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210012,1009</t>
@@ -1522,7 +1534,7 @@
     <t>850-4</t>
   </si>
   <si>
-    <t>三阶镯戒升阶石</t>
+    <t>梦魇虫角，3阶腰靴石</t>
   </si>
   <si>
     <t>200853,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210013,1009</t>
@@ -1540,7 +1552,7 @@
     <t>850-5</t>
   </si>
   <si>
-    <t>三阶腰靴升阶石</t>
+    <t>梦魇蜈膏，随机3阶石</t>
   </si>
   <si>
     <t>200854,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210014,1009</t>
@@ -1558,7 +1570,7 @@
     <t>900-1</t>
   </si>
   <si>
-    <t>四阶随机升阶石</t>
+    <t>梦魇虫心，4阶剑甲石</t>
   </si>
   <si>
     <t>200900,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210015,1009</t>
@@ -1576,7 +1588,7 @@
     <t>900-2</t>
   </si>
   <si>
-    <t>四阶剑甲升阶石</t>
+    <t>梦魇龙皮，4阶链头石</t>
   </si>
   <si>
     <t>200901,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210016,1009</t>
@@ -1594,7 +1606,7 @@
     <t>900-3</t>
   </si>
   <si>
-    <t>四阶链头升阶石</t>
+    <t>梦魇猪皮，4阶镯戒石</t>
   </si>
   <si>
     <t>200902,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210017,1009</t>
@@ -1612,7 +1624,7 @@
     <t>900-4</t>
   </si>
   <si>
-    <t>四阶镯戒升阶石</t>
+    <t>梦魇猪心，4阶腰靴石</t>
   </si>
   <si>
     <t>200903,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210018,1009</t>
@@ -1630,7 +1642,7 @@
     <t>900-5</t>
   </si>
   <si>
-    <t>四阶腰靴升阶石</t>
+    <t>梦魇蝎皮，随机4阶石</t>
   </si>
   <si>
     <t>200904,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210019,1009</t>
@@ -1648,7 +1660,7 @@
     <t>950-1</t>
   </si>
   <si>
-    <t>五阶剑甲升阶石</t>
+    <t>噩梦宝甲，5阶剑甲石</t>
   </si>
   <si>
     <t>200950,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210020,1009</t>
@@ -1666,7 +1678,7 @@
     <t>950-2</t>
   </si>
   <si>
-    <t>五阶链头升阶石</t>
+    <t>噩梦号角，5阶链头石</t>
   </si>
   <si>
     <t>200951,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210021,1009</t>
@@ -1684,7 +1696,7 @@
     <t>950-3</t>
   </si>
   <si>
-    <t>五阶镯戒升阶石</t>
+    <t>噩梦雕像，5阶镯戒石</t>
   </si>
   <si>
     <t>200952,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210022,1009</t>
@@ -1702,7 +1714,7 @@
     <t>950-4</t>
   </si>
   <si>
-    <t>五阶腰靴升阶石</t>
+    <t>噩梦神像，5阶腰靴石</t>
   </si>
   <si>
     <t>200953,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210023,1009</t>
@@ -1720,7 +1732,7 @@
     <t>950-5</t>
   </si>
   <si>
-    <t>五阶随机升阶石</t>
+    <t>噩梦獠牙，随机5阶石</t>
   </si>
   <si>
     <t>200954,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210024,1009</t>
@@ -1738,7 +1750,7 @@
     <t>1000-1</t>
   </si>
   <si>
-    <t>六阶剑甲升阶石</t>
+    <t>噩梦树心，6阶剑甲石</t>
   </si>
   <si>
     <t>201000,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210025,1009</t>
@@ -1756,7 +1768,7 @@
     <t>1000-2</t>
   </si>
   <si>
-    <t>六阶链头升阶石</t>
+    <t>噩梦魔心，6阶链头石</t>
   </si>
   <si>
     <t>201001,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210026,1009</t>
@@ -1774,7 +1786,7 @@
     <t>1000-3</t>
   </si>
   <si>
-    <t>六阶镯戒升阶石</t>
+    <t>噩梦尸心，6阶镯戒石</t>
   </si>
   <si>
     <t>201002,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210027,1009</t>
@@ -1792,7 +1804,7 @@
     <t>1000-4</t>
   </si>
   <si>
-    <t>六阶腰靴升阶石</t>
+    <t>噩梦法杖，6阶腰靴石</t>
   </si>
   <si>
     <t>201003,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210028,1009</t>
@@ -1810,7 +1822,7 @@
     <t>1000-5</t>
   </si>
   <si>
-    <t>六阶随机升阶石</t>
+    <t>噩梦权杖，随机6阶石</t>
   </si>
   <si>
     <t>201004,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210029,1009</t>
@@ -1828,7 +1840,7 @@
     <t>1050-1</t>
   </si>
   <si>
-    <t>七阶剑甲升阶石</t>
+    <t>噩梦战锤，7阶剑甲石</t>
   </si>
   <si>
     <t>201050,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210030,1009</t>
@@ -1846,7 +1858,7 @@
     <t>1050-2</t>
   </si>
   <si>
-    <t>七阶链头升阶石</t>
+    <t>噩梦血核，7阶链头石</t>
   </si>
   <si>
     <t>201051,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210031,1009</t>
@@ -1864,7 +1876,7 @@
     <t>1050-3</t>
   </si>
   <si>
-    <t>七阶镯戒升阶石</t>
+    <t>噩梦魔核，7阶镯戒石</t>
   </si>
   <si>
     <t>201052,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210032,1009</t>
@@ -1882,7 +1894,7 @@
     <t>1050-4</t>
   </si>
   <si>
-    <t>七阶腰靴升阶石</t>
+    <t>噩梦龙甲，7阶腰靴石</t>
   </si>
   <si>
     <t>201053,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210033,1009</t>
@@ -1900,7 +1912,7 @@
     <t>1050-5</t>
   </si>
   <si>
-    <t>七阶随机升阶石</t>
+    <t>噩梦龙爪，随机7阶石</t>
   </si>
   <si>
     <t>201054,300010,300020,300030,300040,300050,300060,300070,300080,300090,103,504,210034,1009</t>
@@ -1939,7 +1951,7 @@
     <t>1100-2</t>
   </si>
   <si>
-    <t>八阶链头升阶石</t>
+    <t>地狱鹿茸，8阶链头石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210036,1009</t>
@@ -1957,7 +1969,7 @@
     <t>1100-3</t>
   </si>
   <si>
-    <t>八阶镯戒升阶石</t>
+    <t>地狱草帽，8阶镯戒石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210037,1009</t>
@@ -1975,7 +1987,7 @@
     <t>1100-4</t>
   </si>
   <si>
-    <t>八阶腰靴升阶石</t>
+    <t>地狱猫爪，8阶腰靴石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210038,1009</t>
@@ -1993,7 +2005,7 @@
     <t>1100-5</t>
   </si>
   <si>
-    <t>八阶随机升阶石</t>
+    <t>地狱花朵，随机8阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210039,1009</t>
@@ -2011,7 +2023,7 @@
     <t>1150-1</t>
   </si>
   <si>
-    <t>九阶剑甲升阶石</t>
+    <t>地狱冰晶，9阶剑甲石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210040,1009</t>
@@ -2029,7 +2041,7 @@
     <t>1150-2</t>
   </si>
   <si>
-    <t>九阶链头升阶石</t>
+    <t>地狱蝠翼，9阶链头石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210041,1009</t>
@@ -2047,7 +2059,7 @@
     <t>1150-3</t>
   </si>
   <si>
-    <t>九阶镯戒升阶石</t>
+    <t>地狱魂火，9阶镯戒石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210042,1009</t>
@@ -2065,7 +2077,7 @@
     <t>1150-4</t>
   </si>
   <si>
-    <t>九阶腰靴升阶石</t>
+    <t>地狱腐肉，9阶腰靴石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210043,1009</t>
@@ -2083,7 +2095,7 @@
     <t>1150-5</t>
   </si>
   <si>
-    <t>九阶随机升阶石</t>
+    <t>地狱蛇胆，随机9阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210044,1009</t>
@@ -2101,7 +2113,7 @@
     <t>1200-1</t>
   </si>
   <si>
-    <t>十阶剑甲升阶石</t>
+    <t>地狱狼爪，10阶剑甲石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210045,1009</t>
@@ -2119,7 +2131,7 @@
     <t>1200-2</t>
   </si>
   <si>
-    <t>十阶链头升阶石</t>
+    <t>地狱虫皮，10阶链头石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210046,1009</t>
@@ -2137,7 +2149,7 @@
     <t>1200-3</t>
   </si>
   <si>
-    <t>十阶镯戒升阶石</t>
+    <t>地狱鹰羽，10阶镯戒石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210047,1009</t>
@@ -2155,7 +2167,7 @@
     <t>1200-4</t>
   </si>
   <si>
-    <t>十阶腰靴升阶石</t>
+    <t>地狱虫角，10阶腰靴石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210048,1009</t>
@@ -2173,7 +2185,7 @@
     <t>1200-5</t>
   </si>
   <si>
-    <t>十阶随机升阶石</t>
+    <t>地狱蜈膏，随机10阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210049,1009</t>
@@ -2191,7 +2203,7 @@
     <t>1250-1</t>
   </si>
   <si>
-    <t>十一阶剑甲升阶石</t>
+    <t>地狱虫心，11阶剑甲石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210050,1009</t>
@@ -2209,7 +2221,7 @@
     <t>1250-2</t>
   </si>
   <si>
-    <t>十一阶链头升阶石</t>
+    <t>地狱龙皮，11阶链头石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210051,1009</t>
@@ -2227,7 +2239,7 @@
     <t>1250-3</t>
   </si>
   <si>
-    <t>十一阶镯戒升阶石</t>
+    <t>地狱猪皮，11阶镯戒石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210052,1009</t>
@@ -2245,7 +2257,7 @@
     <t>1250-4</t>
   </si>
   <si>
-    <t>十一阶腰靴升阶石</t>
+    <t>地狱猪心，11阶腰靴石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210053,1009</t>
@@ -2263,7 +2275,7 @@
     <t>1250-5</t>
   </si>
   <si>
-    <t>十一阶随机升阶石</t>
+    <t>地狱蝎皮，随机11阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210054,1009</t>
@@ -2281,7 +2293,7 @@
     <t>1300-1</t>
   </si>
   <si>
-    <t>十二阶剑甲升阶石</t>
+    <t>地狱宝甲，12阶剑甲石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210055,1009</t>
@@ -2299,7 +2311,7 @@
     <t>1300-2</t>
   </si>
   <si>
-    <t>十二阶链头升阶石</t>
+    <t>地狱号角，12阶链头石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210056,1009</t>
@@ -2317,7 +2329,7 @@
     <t>1300-3</t>
   </si>
   <si>
-    <t>十二阶镯戒升阶石</t>
+    <t>地狱雕像，12阶镯戒石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210057,1009</t>
@@ -2335,7 +2347,7 @@
     <t>1300-4</t>
   </si>
   <si>
-    <t>十二阶腰靴升阶石</t>
+    <t>地狱神像，12阶腰靴石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210058,1009</t>
@@ -2353,7 +2365,7 @@
     <t>1300-5</t>
   </si>
   <si>
-    <t>十二阶随机升阶石</t>
+    <t>地狱獠牙，随机12阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210059,1009</t>
@@ -2371,7 +2383,7 @@
     <t>1350-1</t>
   </si>
   <si>
-    <t>金色专属</t>
+    <t>地狱树心，金色专属</t>
   </si>
   <si>
     <t>202001,300091,104,504,210060,1009,505</t>
@@ -2392,7 +2404,7 @@
     <t>1350-2</t>
   </si>
   <si>
-    <t>十三阶链头升阶石</t>
+    <t>地狱魔心，13阶链头石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210061,1009,505</t>
@@ -2410,7 +2422,7 @@
     <t>1350-3</t>
   </si>
   <si>
-    <t>十三阶镯戒升阶石</t>
+    <t>地狱尸心，13阶镯戒石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210062,1009,505</t>
@@ -2428,7 +2440,7 @@
     <t>1350-4</t>
   </si>
   <si>
-    <t>十三阶腰靴升阶石</t>
+    <t>地狱法杖，13阶腰靴石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210063,1009,505</t>
@@ -2446,7 +2458,7 @@
     <t>1350-5</t>
   </si>
   <si>
-    <t>十三阶随机升阶石</t>
+    <t>地狱权杖，随机13阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210064,1009,505</t>
@@ -2464,7 +2476,7 @@
     <t>1400-1</t>
   </si>
   <si>
-    <t>十四阶剑甲升阶石</t>
+    <t>地狱战锤，14阶剑甲石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210065,1009,505</t>
@@ -2482,7 +2494,7 @@
     <t>1400-2</t>
   </si>
   <si>
-    <t>十四阶链头升阶石</t>
+    <t>地狱血核，14阶链头石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210066,1009,505</t>
@@ -2500,7 +2512,7 @@
     <t>1400-3</t>
   </si>
   <si>
-    <t>十四阶镯戒升阶石</t>
+    <t>地狱魔核，14阶镯戒石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210067,1009,505</t>
@@ -2518,7 +2530,7 @@
     <t>1400-4</t>
   </si>
   <si>
-    <t>十四阶腰靴升阶石</t>
+    <t>地狱龙甲，14阶腰靴石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210068,1009,505</t>
@@ -2536,7 +2548,7 @@
     <t>1400-5</t>
   </si>
   <si>
-    <t>十四阶随机升阶石</t>
+    <t>地狱龙爪，随机14阶石</t>
   </si>
   <si>
     <t>202001,300091,104,504,210069,1009,505</t>
@@ -2572,7 +2584,7 @@
     <t>1450-2</t>
   </si>
   <si>
-    <t>十五阶升阶石</t>
+    <t>深渊鹿茸，15升阶石</t>
   </si>
   <si>
     <t>10141</t>
@@ -2587,6 +2599,9 @@
     <t>1450-3</t>
   </si>
   <si>
+    <t>深渊草帽，15升阶石</t>
+  </si>
+  <si>
     <t>10142</t>
   </si>
   <si>
@@ -2599,6 +2614,9 @@
     <t>1450-4</t>
   </si>
   <si>
+    <t>深渊猫爪，15升阶石</t>
+  </si>
+  <si>
     <t>10143</t>
   </si>
   <si>
@@ -2611,6 +2629,9 @@
     <t>1450-5</t>
   </si>
   <si>
+    <t>深渊花朵，15升阶石</t>
+  </si>
+  <si>
     <t>10144</t>
   </si>
   <si>
@@ -2623,7 +2644,7 @@
     <t>1500-1</t>
   </si>
   <si>
-    <t>十六阶升阶石</t>
+    <t>深渊冰晶，16升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210071,1009,505</t>
@@ -2641,6 +2662,9 @@
     <t>1500-2</t>
   </si>
   <si>
+    <t>深渊蝠翼，16升阶石</t>
+  </si>
+  <si>
     <t>10146</t>
   </si>
   <si>
@@ -2653,6 +2677,9 @@
     <t>1500-3</t>
   </si>
   <si>
+    <t>深渊魂火，16升阶石</t>
+  </si>
+  <si>
     <t>10147</t>
   </si>
   <si>
@@ -2665,6 +2692,9 @@
     <t>1500-4</t>
   </si>
   <si>
+    <t>深渊腐肉，16升阶石</t>
+  </si>
+  <si>
     <t>10148</t>
   </si>
   <si>
@@ -2677,6 +2707,9 @@
     <t>1500-5</t>
   </si>
   <si>
+    <t>深渊蛇胆，16升阶石</t>
+  </si>
+  <si>
     <t>10149</t>
   </si>
   <si>
@@ -2689,7 +2722,7 @@
     <t>1550-1</t>
   </si>
   <si>
-    <t>十七阶升阶石</t>
+    <t>深渊狼爪，17升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210072,1009,505</t>
@@ -2707,6 +2740,9 @@
     <t>1550-2</t>
   </si>
   <si>
+    <t>深渊虫皮，17升阶石</t>
+  </si>
+  <si>
     <t>10151</t>
   </si>
   <si>
@@ -2719,6 +2755,9 @@
     <t>1550-3</t>
   </si>
   <si>
+    <t>深渊鹰羽，17升阶石</t>
+  </si>
+  <si>
     <t>10152</t>
   </si>
   <si>
@@ -2731,6 +2770,9 @@
     <t>1550-4</t>
   </si>
   <si>
+    <t>深渊虫角，17升阶石</t>
+  </si>
+  <si>
     <t>10153</t>
   </si>
   <si>
@@ -2743,6 +2785,9 @@
     <t>1550-5</t>
   </si>
   <si>
+    <t>深渊蜈膏，17升阶石</t>
+  </si>
+  <si>
     <t>10154</t>
   </si>
   <si>
@@ -2755,7 +2800,7 @@
     <t>1600-1</t>
   </si>
   <si>
-    <t>十八阶升阶石</t>
+    <t>深渊虫心，18升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210073,1009,505</t>
@@ -2773,6 +2818,9 @@
     <t>1600-2</t>
   </si>
   <si>
+    <t>深渊龙皮，18升阶石</t>
+  </si>
+  <si>
     <t>10156</t>
   </si>
   <si>
@@ -2785,6 +2833,9 @@
     <t>1600-3</t>
   </si>
   <si>
+    <t>深渊猪皮，18升阶石</t>
+  </si>
+  <si>
     <t>10157</t>
   </si>
   <si>
@@ -2797,6 +2848,9 @@
     <t>1600-4</t>
   </si>
   <si>
+    <t>深渊猪心，18升阶石</t>
+  </si>
+  <si>
     <t>10158</t>
   </si>
   <si>
@@ -2809,6 +2863,9 @@
     <t>1600-5</t>
   </si>
   <si>
+    <t>深渊蝎皮，18升阶石</t>
+  </si>
+  <si>
     <t>10159</t>
   </si>
   <si>
@@ -2821,7 +2878,7 @@
     <t>1650-1</t>
   </si>
   <si>
-    <t>十九阶升阶石</t>
+    <t>深渊宝甲，19升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210074,1009,505</t>
@@ -2839,6 +2896,9 @@
     <t>1650-2</t>
   </si>
   <si>
+    <t>深渊号角，19升阶石</t>
+  </si>
+  <si>
     <t>10161</t>
   </si>
   <si>
@@ -2851,6 +2911,9 @@
     <t>1650-3</t>
   </si>
   <si>
+    <t>深渊雕像，19升阶石</t>
+  </si>
+  <si>
     <t>10162</t>
   </si>
   <si>
@@ -2863,6 +2926,9 @@
     <t>1650-4</t>
   </si>
   <si>
+    <t>深渊神像，19升阶石</t>
+  </si>
+  <si>
     <t>10163</t>
   </si>
   <si>
@@ -2875,6 +2941,9 @@
     <t>1650-5</t>
   </si>
   <si>
+    <t>深渊獠牙，19升阶石</t>
+  </si>
+  <si>
     <t>10164</t>
   </si>
   <si>
@@ -2887,7 +2956,7 @@
     <t>1700-1</t>
   </si>
   <si>
-    <t>二十阶升阶石</t>
+    <t>深渊树心，20升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210075,1009,505</t>
@@ -2905,6 +2974,9 @@
     <t>1700-2</t>
   </si>
   <si>
+    <t>深渊魔心，20升阶石</t>
+  </si>
+  <si>
     <t>10166</t>
   </si>
   <si>
@@ -2917,6 +2989,9 @@
     <t>1700-3</t>
   </si>
   <si>
+    <t>深渊尸心，20升阶石</t>
+  </si>
+  <si>
     <t>10167</t>
   </si>
   <si>
@@ -2929,6 +3004,9 @@
     <t>1700-4</t>
   </si>
   <si>
+    <t>深渊法杖，20升阶石</t>
+  </si>
+  <si>
     <t>10168</t>
   </si>
   <si>
@@ -2941,6 +3019,9 @@
     <t>1700-5</t>
   </si>
   <si>
+    <t>深渊权杖，20升阶石</t>
+  </si>
+  <si>
     <t>10169</t>
   </si>
   <si>
@@ -2953,7 +3034,7 @@
     <t>1750-1</t>
   </si>
   <si>
-    <t>暗金专属</t>
+    <t>深渊战锤，暗金专属</t>
   </si>
   <si>
     <t>202002,300091,105,504,210076,1009,505,506</t>
@@ -2974,7 +3055,7 @@
     <t>1750-2</t>
   </si>
   <si>
-    <t>二一阶升阶石</t>
+    <t>深渊血核，21升阶石</t>
   </si>
   <si>
     <t>10171</t>
@@ -2989,6 +3070,9 @@
     <t>1750-3</t>
   </si>
   <si>
+    <t>深渊魔核，21升阶石</t>
+  </si>
+  <si>
     <t>10172</t>
   </si>
   <si>
@@ -3001,6 +3085,9 @@
     <t>1750-4</t>
   </si>
   <si>
+    <t>深渊龙甲，21升阶石</t>
+  </si>
+  <si>
     <t>10173</t>
   </si>
   <si>
@@ -3013,6 +3100,9 @@
     <t>1750-5</t>
   </si>
   <si>
+    <t>深渊龙爪，21升阶石</t>
+  </si>
+  <si>
     <t>10174</t>
   </si>
   <si>
@@ -3046,7 +3136,7 @@
     <t>1800-2</t>
   </si>
   <si>
-    <t>二二阶升阶石</t>
+    <t>混沌鹿茸，22升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210077,1009,505,506,202005</t>
@@ -3064,6 +3154,9 @@
     <t>1800-3</t>
   </si>
   <si>
+    <t>混沌草帽，22升阶石</t>
+  </si>
+  <si>
     <t>202002,300091,105,504,210077,1009,505,506,202006</t>
   </si>
   <si>
@@ -3079,6 +3172,9 @@
     <t>1800-4</t>
   </si>
   <si>
+    <t>混沌猫爪，22升阶石</t>
+  </si>
+  <si>
     <t>202002,300091,105,504,210077,1009,505,506,202007</t>
   </si>
   <si>
@@ -3094,6 +3190,9 @@
     <t>1800-5</t>
   </si>
   <si>
+    <t>混沌花朵，22升阶石</t>
+  </si>
+  <si>
     <t>202002,300091,105,504,210077,1009,505,506,202003</t>
   </si>
   <si>
@@ -3109,7 +3208,7 @@
     <t>1850-1</t>
   </si>
   <si>
-    <t>二三阶升阶石</t>
+    <t>混沌冰晶，22升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210078,1009,505,506,202003</t>
@@ -3127,6 +3226,9 @@
     <t>1850-2</t>
   </si>
   <si>
+    <t>混沌蝠翼，23升阶石</t>
+  </si>
+  <si>
     <t>10181</t>
   </si>
   <si>
@@ -3139,6 +3241,9 @@
     <t>1850-3</t>
   </si>
   <si>
+    <t>混沌魂火，23升阶石</t>
+  </si>
+  <si>
     <t>10182</t>
   </si>
   <si>
@@ -3151,6 +3256,9 @@
     <t>1850-4</t>
   </si>
   <si>
+    <t>混沌腐肉，23升阶石</t>
+  </si>
+  <si>
     <t>10183</t>
   </si>
   <si>
@@ -3163,6 +3271,9 @@
     <t>1850-5</t>
   </si>
   <si>
+    <t>混沌蛇胆，23升阶石</t>
+  </si>
+  <si>
     <t>10184</t>
   </si>
   <si>
@@ -3175,7 +3286,7 @@
     <t>1900-1</t>
   </si>
   <si>
-    <t>二四阶升阶石</t>
+    <t>混沌狼爪，24升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210079,1009,505,506,202003</t>
@@ -3193,6 +3304,9 @@
     <t>1900-2</t>
   </si>
   <si>
+    <t>混沌虫皮，24升阶石</t>
+  </si>
+  <si>
     <t>10186</t>
   </si>
   <si>
@@ -3205,6 +3319,9 @@
     <t>1900-3</t>
   </si>
   <si>
+    <t>混沌鹰羽，24升阶石</t>
+  </si>
+  <si>
     <t>10187</t>
   </si>
   <si>
@@ -3217,6 +3334,9 @@
     <t>1900-4</t>
   </si>
   <si>
+    <t>混沌虫角，24升阶石</t>
+  </si>
+  <si>
     <t>10188</t>
   </si>
   <si>
@@ -3229,6 +3349,9 @@
     <t>1900-5</t>
   </si>
   <si>
+    <t>混沌蜈膏，24升阶石</t>
+  </si>
+  <si>
     <t>10189</t>
   </si>
   <si>
@@ -3241,7 +3364,7 @@
     <t>1950-1</t>
   </si>
   <si>
-    <t>二五阶升阶石</t>
+    <t>混沌虫心，25升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210080,1009,505,506,202003</t>
@@ -3259,6 +3382,9 @@
     <t>1950-2</t>
   </si>
   <si>
+    <t>混沌龙皮，25升阶石</t>
+  </si>
+  <si>
     <t>10191</t>
   </si>
   <si>
@@ -3271,6 +3397,9 @@
     <t>1950-3</t>
   </si>
   <si>
+    <t>混沌猪皮，25升阶石</t>
+  </si>
+  <si>
     <t>10192</t>
   </si>
   <si>
@@ -3283,6 +3412,9 @@
     <t>1950-4</t>
   </si>
   <si>
+    <t>混沌猪心，25升阶石</t>
+  </si>
+  <si>
     <t>10193</t>
   </si>
   <si>
@@ -3295,6 +3427,9 @@
     <t>1950-5</t>
   </si>
   <si>
+    <t>混沌蝎皮，25升阶石</t>
+  </si>
+  <si>
     <t>10194</t>
   </si>
   <si>
@@ -3307,7 +3442,7 @@
     <t>2000-1</t>
   </si>
   <si>
-    <t>二六阶升阶石</t>
+    <t>混沌宝甲，26升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210081,1009,505,506,202003</t>
@@ -3325,6 +3460,9 @@
     <t>2000-2</t>
   </si>
   <si>
+    <t>混沌号角，26升阶石</t>
+  </si>
+  <si>
     <t>10196</t>
   </si>
   <si>
@@ -3337,6 +3475,9 @@
     <t>2000-3</t>
   </si>
   <si>
+    <t>混沌雕像，26升阶石</t>
+  </si>
+  <si>
     <t>10197</t>
   </si>
   <si>
@@ -3349,6 +3490,9 @@
     <t>2000-4</t>
   </si>
   <si>
+    <t>混沌神像，26升阶石</t>
+  </si>
+  <si>
     <t>10198</t>
   </si>
   <si>
@@ -3361,6 +3505,9 @@
     <t>2000-5</t>
   </si>
   <si>
+    <t>混沌獠牙，26升阶石</t>
+  </si>
+  <si>
     <t>10199</t>
   </si>
   <si>
@@ -3373,7 +3520,7 @@
     <t>2050-1</t>
   </si>
   <si>
-    <t>二七阶升阶石</t>
+    <t>混沌树心，27升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210082,1009,505,506,202003</t>
@@ -3391,6 +3538,9 @@
     <t>2050-2</t>
   </si>
   <si>
+    <t>混沌魔心，27升阶石</t>
+  </si>
+  <si>
     <t>10201</t>
   </si>
   <si>
@@ -3403,6 +3553,9 @@
     <t>2050-3</t>
   </si>
   <si>
+    <t>混沌尸心，27升阶石</t>
+  </si>
+  <si>
     <t>10202</t>
   </si>
   <si>
@@ -3415,6 +3568,9 @@
     <t>2050-4</t>
   </si>
   <si>
+    <t>混沌法杖，27升阶石</t>
+  </si>
+  <si>
     <t>10203</t>
   </si>
   <si>
@@ -3427,6 +3583,9 @@
     <t>2050-5</t>
   </si>
   <si>
+    <t>混沌权杖，27升阶石</t>
+  </si>
+  <si>
     <t>10204</t>
   </si>
   <si>
@@ -3439,7 +3598,7 @@
     <t>2100-1</t>
   </si>
   <si>
-    <t>二八阶升阶石</t>
+    <t>混沌战锤，28升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210083,1009,505,506,202003</t>
@@ -3457,6 +3616,9 @@
     <t>2100-2</t>
   </si>
   <si>
+    <t>混沌血核，28升阶石</t>
+  </si>
+  <si>
     <t>10206</t>
   </si>
   <si>
@@ -3469,6 +3631,9 @@
     <t>2100-3</t>
   </si>
   <si>
+    <t>混沌魔核，28升阶石</t>
+  </si>
+  <si>
     <t>10207</t>
   </si>
   <si>
@@ -3481,6 +3646,9 @@
     <t>2100-4</t>
   </si>
   <si>
+    <t>混沌龙甲，28升阶石</t>
+  </si>
+  <si>
     <t>10208</t>
   </si>
   <si>
@@ -3493,25 +3661,28 @@
     <t>2100-5</t>
   </si>
   <si>
+    <t>混沌龙爪，粉色专属</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210083,1009,505,506,202003,507</t>
+  </si>
+  <si>
+    <t>10,9500,9000,98000,600000,140000,600000,700000,600000,900000</t>
+  </si>
+  <si>
+    <t>10209</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>虚无小村</t>
+  </si>
+  <si>
+    <t>2150-1</t>
+  </si>
+  <si>
     <t>粉色专属</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210083,1009,505,506,202003,507</t>
-  </si>
-  <si>
-    <t>10,9500,9000,98000,600000,140000,600000,700000,600000,900000</t>
-  </si>
-  <si>
-    <t>10209</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>虚无小村</t>
-  </si>
-  <si>
-    <t>2150-1</t>
   </si>
   <si>
     <t>202002,300091,105,504,210077,1009,505,506,202004,507</t>
@@ -3756,12 +3927,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6887,27 +7058,27 @@
         <v>417</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="I77" s="1">
         <v>750</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K77" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="2:12">
       <c r="C78" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E78" s="1">
         <v>3</v>
@@ -6916,30 +7087,30 @@
         <v>3</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="I78" s="1">
         <v>750</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K78" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="2:12">
       <c r="C79" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E79" s="1">
         <v>3</v>
@@ -6948,30 +7119,30 @@
         <v>3</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="I79" s="1">
         <v>750</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K79" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="2:12">
       <c r="C80" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E80" s="1">
         <v>3</v>
@@ -6980,30 +7151,30 @@
         <v>3</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="I80" s="1">
         <v>750</v>
       </c>
       <c r="J80" s="12" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K80" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E81" s="1">
         <v>3</v>
@@ -7012,30 +7183,30 @@
         <v>3</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="I81" s="1">
         <v>800</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="K81" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E82" s="1">
         <v>3</v>
@@ -7044,30 +7215,30 @@
         <v>3</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="I82" s="1">
         <v>800</v>
       </c>
       <c r="J82" s="12" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="K82" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E83" s="1">
         <v>3</v>
@@ -7076,30 +7247,30 @@
         <v>3</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="I83" s="1">
         <v>800</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="K83" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E84" s="1">
         <v>3</v>
@@ -7108,30 +7279,30 @@
         <v>3</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="I84" s="1">
         <v>800</v>
       </c>
       <c r="J84" s="12" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="K84" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E85" s="1">
         <v>3</v>
@@ -7140,30 +7311,30 @@
         <v>3</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="I85" s="1">
         <v>800</v>
       </c>
       <c r="J85" s="12" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="K85" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C86" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E86" s="1">
         <v>3</v>
@@ -7172,30 +7343,30 @@
         <v>3</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="I86" s="1">
         <v>850</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="K86" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C87" s="1" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E87" s="1">
         <v>3</v>
@@ -7204,30 +7375,30 @@
         <v>3</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="I87" s="1">
         <v>850</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K87" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C88" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E88" s="1">
         <v>3</v>
@@ -7236,30 +7407,30 @@
         <v>3</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="I88" s="1">
         <v>850</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="K88" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C89" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E89" s="1">
         <v>3</v>
@@ -7268,30 +7439,30 @@
         <v>3</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="I89" s="1">
         <v>850</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="K89" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C90" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E90" s="1">
         <v>3</v>
@@ -7300,30 +7471,30 @@
         <v>3</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="I90" s="1">
         <v>850</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="K90" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C91" s="1" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E91" s="1">
         <v>3</v>
@@ -7332,30 +7503,30 @@
         <v>3</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="I91" s="1">
         <v>900</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K91" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C92" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="E92" s="1">
         <v>3</v>
@@ -7364,30 +7535,30 @@
         <v>3</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="I92" s="1">
         <v>900</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="K92" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C93" s="1" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="E93" s="1">
         <v>3</v>
@@ -7396,30 +7567,30 @@
         <v>3</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="I93" s="1">
         <v>900</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="K93" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C94" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E94" s="1">
         <v>3</v>
@@ -7428,30 +7599,30 @@
         <v>3</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I94" s="1">
         <v>900</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="K94" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C95" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="E95" s="1">
         <v>3</v>
@@ -7460,30 +7631,30 @@
         <v>3</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="I95" s="1">
         <v>900</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="K95" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E96" s="1">
         <v>3</v>
@@ -7492,30 +7663,30 @@
         <v>3</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="I96" s="1">
         <v>950</v>
       </c>
       <c r="J96" s="12" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="K96" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="E97" s="1">
         <v>3</v>
@@ -7524,30 +7695,30 @@
         <v>3</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="I97" s="1">
         <v>950</v>
       </c>
       <c r="J97" s="12" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="K97" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E98" s="1">
         <v>3</v>
@@ -7556,30 +7727,30 @@
         <v>3</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="I98" s="1">
         <v>950</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="K98" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E99" s="1">
         <v>3</v>
@@ -7588,30 +7759,30 @@
         <v>3</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="I99" s="1">
         <v>950</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="K99" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="E100" s="1">
         <v>3</v>
@@ -7620,30 +7791,30 @@
         <v>3</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I100" s="1">
         <v>950</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="K100" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="E101" s="1">
         <v>3</v>
@@ -7652,30 +7823,30 @@
         <v>3</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="I101" s="1">
         <v>1000</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="K101" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="E102" s="1">
         <v>3</v>
@@ -7684,30 +7855,30 @@
         <v>3</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="I102" s="1">
         <v>1000</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="K102" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="E103" s="1">
         <v>3</v>
@@ -7716,30 +7887,30 @@
         <v>3</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="I103" s="1">
         <v>1000</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K103" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E104" s="1">
         <v>3</v>
@@ -7748,30 +7919,30 @@
         <v>3</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="I104" s="1">
         <v>1000</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K104" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="E105" s="1">
         <v>3</v>
@@ -7780,30 +7951,30 @@
         <v>3</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="I105" s="1">
         <v>1000</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K105" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C106" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="E106" s="1">
         <v>3</v>
@@ -7812,30 +7983,30 @@
         <v>3</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="I106" s="1">
         <v>1050</v>
       </c>
       <c r="J106" s="12" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="K106" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C107" s="1" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E107" s="1">
         <v>3</v>
@@ -7844,30 +8015,30 @@
         <v>3</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="I107" s="1">
         <v>1050</v>
       </c>
       <c r="J107" s="12" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="K107" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C108" s="1" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E108" s="1">
         <v>3</v>
@@ -7876,30 +8047,30 @@
         <v>3</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="I108" s="1">
         <v>1050</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="K108" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C109" s="1" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E109" s="1">
         <v>3</v>
@@ -7908,30 +8079,30 @@
         <v>3</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="I109" s="1">
         <v>1050</v>
       </c>
       <c r="J109" s="12" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="K109" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C110" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="E110" s="1">
         <v>3</v>
@@ -7940,30 +8111,30 @@
         <v>3</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I110" s="1">
         <v>1050</v>
       </c>
       <c r="J110" s="12" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="K110" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="E111" s="1">
         <v>4</v>
@@ -7972,30 +8143,30 @@
         <v>4</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="I111" s="1">
         <v>0</v>
       </c>
       <c r="J111" s="12" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="K111" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E112" s="1">
         <v>4</v>
@@ -8004,30 +8175,30 @@
         <v>4</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="I112" s="1">
         <v>0</v>
       </c>
       <c r="J112" s="12" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="K112" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:12">
       <c r="C113" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="E113" s="1">
         <v>4</v>
@@ -8036,30 +8207,30 @@
         <v>4</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="I113" s="1">
         <v>0</v>
       </c>
       <c r="J113" s="12" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="K113" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="E114" s="1">
         <v>4</v>
@@ -8068,30 +8239,30 @@
         <v>4</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="I114" s="1">
         <v>0</v>
       </c>
       <c r="J114" s="12" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="K114" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E115" s="1">
         <v>4</v>
@@ -8100,30 +8271,30 @@
         <v>4</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="I115" s="1">
         <v>0</v>
       </c>
       <c r="J115" s="12" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="K115" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E116" s="1">
         <v>4</v>
@@ -8132,30 +8303,30 @@
         <v>4</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="I116" s="1">
         <v>0</v>
       </c>
       <c r="J116" s="12" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K116" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:12">
       <c r="C117" s="1" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E117" s="1">
         <v>4</v>
@@ -8164,30 +8335,30 @@
         <v>4</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="I117" s="1">
         <v>0</v>
       </c>
       <c r="J117" s="12" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="K117" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="3:12">
       <c r="C118" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="E118" s="1">
         <v>4</v>
@@ -8196,30 +8367,30 @@
         <v>4</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="I118" s="1">
         <v>0</v>
       </c>
       <c r="J118" s="12" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K118" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:12">
       <c r="C119" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E119" s="1">
         <v>4</v>
@@ -8228,30 +8399,30 @@
         <v>4</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="I119" s="1">
         <v>0</v>
       </c>
       <c r="J119" s="12" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="K119" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:12">
       <c r="C120" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E120" s="1">
         <v>4</v>
@@ -8260,30 +8431,30 @@
         <v>4</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="I120" s="1">
         <v>0</v>
       </c>
       <c r="J120" s="12" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="K120" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C121" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E121" s="1">
         <v>4</v>
@@ -8292,30 +8463,30 @@
         <v>4</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="I121" s="1">
         <v>0</v>
       </c>
       <c r="J121" s="12" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="K121" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C122" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E122" s="1">
         <v>4</v>
@@ -8324,30 +8495,30 @@
         <v>4</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="I122" s="1">
         <v>0</v>
       </c>
       <c r="J122" s="12" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="K122" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C123" s="1" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E123" s="1">
         <v>4</v>
@@ -8356,30 +8527,30 @@
         <v>4</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="I123" s="1">
         <v>0</v>
       </c>
       <c r="J123" s="12" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="K123" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C124" s="1" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E124" s="1">
         <v>4</v>
@@ -8388,30 +8559,30 @@
         <v>4</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="I124" s="1">
         <v>0</v>
       </c>
       <c r="J124" s="12" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="K124" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C125" s="1" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="E125" s="1">
         <v>4</v>
@@ -8420,30 +8591,30 @@
         <v>4</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="I125" s="1">
         <v>0</v>
       </c>
       <c r="J125" s="12" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="K125" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C126" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="E126" s="1">
         <v>4</v>
@@ -8452,30 +8623,30 @@
         <v>4</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="I126" s="1">
         <v>0</v>
       </c>
       <c r="J126" s="12" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="K126" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C127" s="1" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="E127" s="1">
         <v>4</v>
@@ -8484,30 +8655,30 @@
         <v>4</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="I127" s="1">
         <v>0</v>
       </c>
       <c r="J127" s="12" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="K127" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C128" s="1" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E128" s="1">
         <v>4</v>
@@ -8516,30 +8687,30 @@
         <v>4</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="I128" s="1">
         <v>0</v>
       </c>
       <c r="J128" s="12" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="K128" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C129" s="1" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E129" s="1">
         <v>4</v>
@@ -8548,30 +8719,30 @@
         <v>4</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="I129" s="1">
         <v>0</v>
       </c>
       <c r="J129" s="12" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="K129" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C130" s="1" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="E130" s="1">
         <v>4</v>
@@ -8580,30 +8751,30 @@
         <v>4</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="I130" s="1">
         <v>0</v>
       </c>
       <c r="J130" s="12" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="K130" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="3:12">
       <c r="C131" s="1" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="E131" s="1">
         <v>4</v>
@@ -8612,30 +8783,30 @@
         <v>4</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="I131" s="1">
         <v>0</v>
       </c>
       <c r="J131" s="12" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="K131" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="3:12">
       <c r="C132" s="1" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="E132" s="1">
         <v>4</v>
@@ -8644,30 +8815,30 @@
         <v>4</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="I132" s="1">
         <v>0</v>
       </c>
       <c r="J132" s="12" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="K132" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="3:12">
       <c r="C133" s="1" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="E133" s="1">
         <v>4</v>
@@ -8676,30 +8847,30 @@
         <v>4</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="I133" s="1">
         <v>0</v>
       </c>
       <c r="J133" s="12" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="K133" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="3:12">
       <c r="C134" s="1" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="E134" s="1">
         <v>4</v>
@@ -8708,30 +8879,30 @@
         <v>4</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="I134" s="1">
         <v>0</v>
       </c>
       <c r="J134" s="12" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="K134" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="3:12">
       <c r="C135" s="1" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="E135" s="1">
         <v>4</v>
@@ -8740,30 +8911,30 @@
         <v>4</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="I135" s="1">
         <v>0</v>
       </c>
       <c r="J135" s="12" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="K135" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="3:12">
       <c r="C136" s="1" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="E136" s="1">
         <v>4</v>
@@ -8772,30 +8943,30 @@
         <v>4</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="I136" s="1">
         <v>0</v>
       </c>
       <c r="J136" s="12" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="K136" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="3:12">
       <c r="C137" s="1" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="E137" s="1">
         <v>4</v>
@@ -8804,30 +8975,30 @@
         <v>4</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="I137" s="1">
         <v>0</v>
       </c>
       <c r="J137" s="12" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="K137" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="E138" s="1">
         <v>4</v>
@@ -8836,30 +9007,30 @@
         <v>4</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="I138" s="1">
         <v>0</v>
       </c>
       <c r="J138" s="12" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="K138" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="E139" s="1">
         <v>4</v>
@@ -8868,30 +9039,30 @@
         <v>4</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="I139" s="1">
         <v>0</v>
       </c>
       <c r="J139" s="12" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="K139" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="3:12">
       <c r="C140" s="1" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="E140" s="1">
         <v>4</v>
@@ -8900,30 +9071,30 @@
         <v>4</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="I140" s="1">
         <v>0</v>
       </c>
       <c r="J140" s="12" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="K140" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C141" s="1" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="E141" s="1">
         <v>4</v>
@@ -8932,30 +9103,30 @@
         <v>4</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="I141" s="1">
         <v>0</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="K141" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C142" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E142" s="1">
         <v>4</v>
@@ -8964,30 +9135,30 @@
         <v>4</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="I142" s="1">
         <v>0</v>
       </c>
       <c r="J142" s="12" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="K142" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C143" s="1" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="E143" s="1">
         <v>4</v>
@@ -8996,30 +9167,30 @@
         <v>4</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="I143" s="1">
         <v>0</v>
       </c>
       <c r="J143" s="12" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="K143" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C144" s="1" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="E144" s="1">
         <v>4</v>
@@ -9028,30 +9199,30 @@
         <v>4</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="I144" s="1">
         <v>0</v>
       </c>
       <c r="J144" s="12" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="K144" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C145" s="1" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="E145" s="1">
         <v>4</v>
@@ -9060,30 +9231,30 @@
         <v>4</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="I145" s="1">
         <v>0</v>
       </c>
       <c r="J145" s="12" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="K145" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
     </row>
     <row r="146" s="3" customFormat="1" customHeight="1" spans="3:12">
       <c r="C146" s="3" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="E146" s="3">
         <v>5</v>
@@ -9092,30 +9263,30 @@
         <v>5</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="I146" s="3">
         <v>0</v>
       </c>
       <c r="J146" s="13" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="K146" s="13" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L146" s="13" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="E147" s="1">
         <v>5</v>
@@ -9124,30 +9295,30 @@
         <v>5</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="I147" s="1">
         <v>0</v>
       </c>
       <c r="J147" s="12" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="K147" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L147" s="11" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="E148" s="1">
         <v>5</v>
@@ -9156,30 +9327,30 @@
         <v>5</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="I148" s="1">
         <v>0</v>
       </c>
       <c r="J148" s="12" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="K148" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L148" s="11" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="E149" s="1">
         <v>5</v>
@@ -9188,30 +9359,30 @@
         <v>5</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="I149" s="1">
         <v>0</v>
       </c>
       <c r="J149" s="12" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="K149" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L149" s="11" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="3:12">
       <c r="C150" s="1" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="E150" s="1">
         <v>5</v>
@@ -9220,30 +9391,30 @@
         <v>5</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>837</v>
+        <v>856</v>
       </c>
       <c r="I150" s="1">
         <v>0</v>
       </c>
       <c r="J150" s="12" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="K150" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L150" s="11" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="3:12">
       <c r="C151" s="1" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
@@ -9252,30 +9423,30 @@
         <v>5</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="I151" s="1">
         <v>0</v>
       </c>
       <c r="J151" s="12" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="K151" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L151" s="11" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="3:12">
       <c r="C152" s="1" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="E152" s="1">
         <v>5</v>
@@ -9284,30 +9455,30 @@
         <v>5</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>854</v>
+        <v>867</v>
       </c>
       <c r="I152" s="1">
         <v>0</v>
       </c>
       <c r="J152" s="12" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="K152" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L152" s="11" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="3:12">
       <c r="C153" s="1" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="E153" s="1">
         <v>5</v>
@@ -9316,30 +9487,30 @@
         <v>5</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>854</v>
+        <v>872</v>
       </c>
       <c r="I153" s="1">
         <v>0</v>
       </c>
       <c r="J153" s="12" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="K153" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L153" s="11" t="s">
-        <v>864</v>
+        <v>873</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="3:12">
       <c r="C154" s="1" t="s">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="E154" s="1">
         <v>5</v>
@@ -9348,30 +9519,30 @@
         <v>5</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>854</v>
+        <v>877</v>
       </c>
       <c r="I154" s="1">
         <v>0</v>
       </c>
       <c r="J154" s="12" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="K154" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L154" s="11" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="3:12">
       <c r="C155" s="1" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="E155" s="1">
         <v>5</v>
@@ -9380,30 +9551,30 @@
         <v>5</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>854</v>
+        <v>882</v>
       </c>
       <c r="I155" s="1">
         <v>0</v>
       </c>
       <c r="J155" s="12" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="K155" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L155" s="11" t="s">
-        <v>872</v>
+        <v>883</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C156" s="1" t="s">
-        <v>873</v>
+        <v>884</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="E156" s="1">
         <v>5</v>
@@ -9412,30 +9583,30 @@
         <v>5</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>875</v>
+        <v>886</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="I156" s="1">
         <v>0</v>
       </c>
       <c r="J156" s="12" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="K156" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L156" s="11" t="s">
-        <v>878</v>
+        <v>889</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C157" s="1" t="s">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>880</v>
+        <v>891</v>
       </c>
       <c r="E157" s="1">
         <v>5</v>
@@ -9444,30 +9615,30 @@
         <v>5</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>876</v>
+        <v>893</v>
       </c>
       <c r="I157" s="1">
         <v>0</v>
       </c>
       <c r="J157" s="12" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="K157" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L157" s="11" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C158" s="1" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="E158" s="1">
         <v>5</v>
@@ -9476,30 +9647,30 @@
         <v>5</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>876</v>
+        <v>898</v>
       </c>
       <c r="I158" s="1">
         <v>0</v>
       </c>
       <c r="J158" s="12" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="K158" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L158" s="11" t="s">
-        <v>886</v>
+        <v>899</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C159" s="1" t="s">
-        <v>887</v>
+        <v>900</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>888</v>
+        <v>901</v>
       </c>
       <c r="E159" s="1">
         <v>5</v>
@@ -9508,30 +9679,30 @@
         <v>5</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>876</v>
+        <v>903</v>
       </c>
       <c r="I159" s="1">
         <v>0</v>
       </c>
       <c r="J159" s="12" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="K159" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L159" s="11" t="s">
-        <v>890</v>
+        <v>904</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C160" s="1" t="s">
-        <v>891</v>
+        <v>905</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>892</v>
+        <v>906</v>
       </c>
       <c r="E160" s="1">
         <v>5</v>
@@ -9540,30 +9711,30 @@
         <v>5</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>893</v>
+        <v>907</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>876</v>
+        <v>908</v>
       </c>
       <c r="I160" s="1">
         <v>0</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="K160" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L160" s="11" t="s">
-        <v>894</v>
+        <v>909</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C161" s="1" t="s">
-        <v>895</v>
+        <v>910</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="E161" s="1">
         <v>5</v>
@@ -9572,30 +9743,30 @@
         <v>5</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>897</v>
+        <v>912</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="I161" s="1">
         <v>0</v>
       </c>
       <c r="J161" s="12" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="K161" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L161" s="11" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C162" s="1" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="E162" s="1">
         <v>5</v>
@@ -9604,30 +9775,30 @@
         <v>5</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>898</v>
+        <v>919</v>
       </c>
       <c r="I162" s="1">
         <v>0</v>
       </c>
       <c r="J162" s="12" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="K162" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L162" s="11" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C163" s="1" t="s">
-        <v>905</v>
+        <v>921</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>906</v>
+        <v>922</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9636,30 +9807,30 @@
         <v>5</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>907</v>
+        <v>923</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>898</v>
+        <v>924</v>
       </c>
       <c r="I163" s="1">
         <v>0</v>
       </c>
       <c r="J163" s="12" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="K163" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L163" s="11" t="s">
-        <v>908</v>
+        <v>925</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C164" s="1" t="s">
-        <v>909</v>
+        <v>926</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>910</v>
+        <v>927</v>
       </c>
       <c r="E164" s="1">
         <v>5</v>
@@ -9668,30 +9839,30 @@
         <v>5</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>911</v>
+        <v>928</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>898</v>
+        <v>929</v>
       </c>
       <c r="I164" s="1">
         <v>0</v>
       </c>
       <c r="J164" s="12" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="K164" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L164" s="11" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C165" s="1" t="s">
-        <v>913</v>
+        <v>931</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>914</v>
+        <v>932</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -9700,30 +9871,30 @@
         <v>5</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>898</v>
+        <v>934</v>
       </c>
       <c r="I165" s="1">
         <v>0</v>
       </c>
       <c r="J165" s="12" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="K165" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L165" s="11" t="s">
-        <v>916</v>
+        <v>935</v>
       </c>
     </row>
     <row r="166" customHeight="1" spans="3:12">
       <c r="C166" s="1" t="s">
-        <v>917</v>
+        <v>936</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>918</v>
+        <v>937</v>
       </c>
       <c r="E166" s="1">
         <v>5</v>
@@ -9732,30 +9903,30 @@
         <v>5</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>919</v>
+        <v>938</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>920</v>
+        <v>939</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
       </c>
       <c r="J166" s="12" t="s">
-        <v>921</v>
+        <v>940</v>
       </c>
       <c r="K166" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L166" s="11" t="s">
-        <v>922</v>
+        <v>941</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="3:12">
       <c r="C167" s="1" t="s">
-        <v>923</v>
+        <v>942</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>924</v>
+        <v>943</v>
       </c>
       <c r="E167" s="1">
         <v>5</v>
@@ -9764,30 +9935,30 @@
         <v>5</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>925</v>
+        <v>944</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>920</v>
+        <v>945</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
       </c>
       <c r="J167" s="12" t="s">
-        <v>921</v>
+        <v>940</v>
       </c>
       <c r="K167" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L167" s="11" t="s">
-        <v>926</v>
+        <v>946</v>
       </c>
     </row>
     <row r="168" customHeight="1" spans="3:12">
       <c r="C168" s="1" t="s">
-        <v>927</v>
+        <v>947</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>928</v>
+        <v>948</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -9796,30 +9967,30 @@
         <v>5</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>929</v>
+        <v>949</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>920</v>
+        <v>950</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
       </c>
       <c r="J168" s="12" t="s">
-        <v>921</v>
+        <v>940</v>
       </c>
       <c r="K168" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L168" s="11" t="s">
-        <v>930</v>
+        <v>951</v>
       </c>
     </row>
     <row r="169" customHeight="1" spans="3:12">
       <c r="C169" s="1" t="s">
-        <v>931</v>
+        <v>952</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>932</v>
+        <v>953</v>
       </c>
       <c r="E169" s="1">
         <v>5</v>
@@ -9828,30 +9999,30 @@
         <v>5</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>933</v>
+        <v>954</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>920</v>
+        <v>955</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
       </c>
       <c r="J169" s="12" t="s">
-        <v>921</v>
+        <v>940</v>
       </c>
       <c r="K169" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L169" s="11" t="s">
-        <v>934</v>
+        <v>956</v>
       </c>
     </row>
     <row r="170" customHeight="1" spans="3:12">
       <c r="C170" s="1" t="s">
-        <v>935</v>
+        <v>957</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>936</v>
+        <v>958</v>
       </c>
       <c r="E170" s="1">
         <v>5</v>
@@ -9860,30 +10031,30 @@
         <v>5</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>937</v>
+        <v>959</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>920</v>
+        <v>960</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
       </c>
       <c r="J170" s="12" t="s">
-        <v>921</v>
+        <v>940</v>
       </c>
       <c r="K170" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L170" s="11" t="s">
-        <v>938</v>
+        <v>961</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="3:12">
       <c r="C171" s="1" t="s">
-        <v>939</v>
+        <v>962</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>940</v>
+        <v>963</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -9892,30 +10063,30 @@
         <v>5</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>941</v>
+        <v>964</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>942</v>
+        <v>965</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
       </c>
       <c r="J171" s="12" t="s">
-        <v>943</v>
+        <v>966</v>
       </c>
       <c r="K171" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L171" s="11" t="s">
-        <v>944</v>
+        <v>967</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="3:12">
       <c r="C172" s="1" t="s">
-        <v>945</v>
+        <v>968</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>946</v>
+        <v>969</v>
       </c>
       <c r="E172" s="1">
         <v>5</v>
@@ -9924,30 +10095,30 @@
         <v>5</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>947</v>
+        <v>970</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>942</v>
+        <v>971</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
       </c>
       <c r="J172" s="12" t="s">
-        <v>943</v>
+        <v>966</v>
       </c>
       <c r="K172" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L172" s="11" t="s">
-        <v>948</v>
+        <v>972</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="3:12">
       <c r="C173" s="1" t="s">
-        <v>949</v>
+        <v>973</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>950</v>
+        <v>974</v>
       </c>
       <c r="E173" s="1">
         <v>5</v>
@@ -9956,30 +10127,30 @@
         <v>5</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>951</v>
+        <v>975</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>942</v>
+        <v>976</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
       </c>
       <c r="J173" s="12" t="s">
-        <v>943</v>
+        <v>966</v>
       </c>
       <c r="K173" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L173" s="11" t="s">
-        <v>952</v>
+        <v>977</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="3:12">
       <c r="C174" s="1" t="s">
-        <v>953</v>
+        <v>978</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>954</v>
+        <v>979</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -9988,30 +10159,30 @@
         <v>5</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>955</v>
+        <v>980</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>942</v>
+        <v>981</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
       </c>
       <c r="J174" s="12" t="s">
-        <v>943</v>
+        <v>966</v>
       </c>
       <c r="K174" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L174" s="11" t="s">
-        <v>956</v>
+        <v>982</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="3:12">
       <c r="C175" s="1" t="s">
-        <v>957</v>
+        <v>983</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>958</v>
+        <v>984</v>
       </c>
       <c r="E175" s="1">
         <v>5</v>
@@ -10020,30 +10191,30 @@
         <v>5</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>959</v>
+        <v>985</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>942</v>
+        <v>986</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
       </c>
       <c r="J175" s="12" t="s">
-        <v>943</v>
+        <v>966</v>
       </c>
       <c r="K175" s="12" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="L175" s="11" t="s">
-        <v>960</v>
+        <v>987</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C176" s="1" t="s">
-        <v>961</v>
+        <v>988</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="E176" s="1">
         <v>5</v>
@@ -10052,30 +10223,30 @@
         <v>5</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>963</v>
+        <v>990</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>964</v>
+        <v>991</v>
       </c>
       <c r="I176" s="1">
         <v>0</v>
       </c>
       <c r="J176" s="12" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
       <c r="K176" s="12" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
       <c r="L176" s="11" t="s">
-        <v>967</v>
+        <v>994</v>
       </c>
     </row>
     <row r="177" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C177" s="1" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>969</v>
+        <v>996</v>
       </c>
       <c r="E177" s="1">
         <v>5</v>
@@ -10084,30 +10255,30 @@
         <v>5</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>971</v>
+        <v>998</v>
       </c>
       <c r="I177" s="1">
         <v>0</v>
       </c>
       <c r="J177" s="12" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
       <c r="K177" s="12" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
       <c r="L177" s="11" t="s">
-        <v>972</v>
+        <v>999</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C178" s="1" t="s">
-        <v>973</v>
+        <v>1000</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>974</v>
+        <v>1001</v>
       </c>
       <c r="E178" s="1">
         <v>5</v>
@@ -10116,30 +10287,30 @@
         <v>5</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>975</v>
+        <v>1002</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>971</v>
+        <v>1003</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
       </c>
       <c r="J178" s="12" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
       <c r="K178" s="12" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
       <c r="L178" s="11" t="s">
-        <v>976</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="179" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C179" s="1" t="s">
-        <v>977</v>
+        <v>1005</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>978</v>
+        <v>1006</v>
       </c>
       <c r="E179" s="1">
         <v>5</v>
@@ -10148,30 +10319,30 @@
         <v>5</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>979</v>
+        <v>1007</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>971</v>
+        <v>1008</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
       </c>
       <c r="J179" s="12" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
       <c r="K179" s="12" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
       <c r="L179" s="11" t="s">
-        <v>980</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="180" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C180" s="1" t="s">
-        <v>981</v>
+        <v>1010</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>982</v>
+        <v>1011</v>
       </c>
       <c r="E180" s="1">
         <v>5</v>
@@ -10180,30 +10351,30 @@
         <v>5</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>983</v>
+        <v>1012</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>971</v>
+        <v>1013</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
       </c>
       <c r="J180" s="12" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
       <c r="K180" s="12" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
       <c r="L180" s="11" t="s">
-        <v>984</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="181" s="3" customFormat="1" customHeight="1" spans="3:12">
       <c r="C181" s="1" t="s">
-        <v>985</v>
+        <v>1015</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>986</v>
+        <v>1016</v>
       </c>
       <c r="E181" s="3">
         <v>5</v>
@@ -10212,30 +10383,30 @@
         <v>5</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>987</v>
+        <v>1017</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>988</v>
+        <v>1018</v>
       </c>
       <c r="I181" s="3">
         <v>0</v>
       </c>
       <c r="J181" s="13" t="s">
-        <v>989</v>
+        <v>1019</v>
       </c>
       <c r="K181" s="13" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L181" s="11" t="s">
-        <v>991</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="182" customHeight="1" spans="3:12">
       <c r="C182" s="1" t="s">
-        <v>992</v>
+        <v>1022</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>993</v>
+        <v>1023</v>
       </c>
       <c r="E182" s="1">
         <v>5</v>
@@ -10244,30 +10415,30 @@
         <v>5</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>994</v>
+        <v>1024</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>995</v>
+        <v>1025</v>
       </c>
       <c r="I182" s="1">
         <v>0</v>
       </c>
       <c r="J182" s="12" t="s">
-        <v>996</v>
+        <v>1026</v>
       </c>
       <c r="K182" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L182" s="11" t="s">
-        <v>997</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="183" customHeight="1" spans="3:12">
       <c r="C183" s="1" t="s">
-        <v>998</v>
+        <v>1028</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>999</v>
+        <v>1029</v>
       </c>
       <c r="E183" s="1">
         <v>5</v>
@@ -10276,30 +10447,30 @@
         <v>5</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>995</v>
+        <v>1031</v>
       </c>
       <c r="I183" s="1">
         <v>0</v>
       </c>
       <c r="J183" s="12" t="s">
-        <v>1001</v>
+        <v>1032</v>
       </c>
       <c r="K183" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L183" s="11" t="s">
-        <v>1002</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="184" customHeight="1" spans="3:12">
       <c r="C184" s="1" t="s">
-        <v>1003</v>
+        <v>1034</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>1004</v>
+        <v>1035</v>
       </c>
       <c r="E184" s="1">
         <v>5</v>
@@ -10308,30 +10479,30 @@
         <v>5</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>1005</v>
+        <v>1036</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>995</v>
+        <v>1037</v>
       </c>
       <c r="I184" s="1">
         <v>0</v>
       </c>
       <c r="J184" s="12" t="s">
-        <v>1006</v>
+        <v>1038</v>
       </c>
       <c r="K184" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L184" s="11" t="s">
-        <v>1007</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="185" customHeight="1" spans="3:12">
       <c r="C185" s="1" t="s">
-        <v>1008</v>
+        <v>1040</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>1009</v>
+        <v>1041</v>
       </c>
       <c r="E185" s="1">
         <v>5</v>
@@ -10340,30 +10511,30 @@
         <v>5</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>1010</v>
+        <v>1042</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>995</v>
+        <v>1043</v>
       </c>
       <c r="I185" s="1">
         <v>0</v>
       </c>
       <c r="J185" s="12" t="s">
-        <v>1011</v>
+        <v>1044</v>
       </c>
       <c r="K185" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L185" s="11" t="s">
-        <v>1012</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="186" customHeight="1" spans="3:12">
       <c r="C186" s="1" t="s">
-        <v>1013</v>
+        <v>1046</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>1014</v>
+        <v>1047</v>
       </c>
       <c r="E186" s="1">
         <v>5</v>
@@ -10372,30 +10543,30 @@
         <v>5</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>1015</v>
+        <v>1048</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>1016</v>
+        <v>1049</v>
       </c>
       <c r="I186" s="1">
         <v>0</v>
       </c>
       <c r="J186" s="12" t="s">
-        <v>1017</v>
+        <v>1050</v>
       </c>
       <c r="K186" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L186" s="11" t="s">
-        <v>1018</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="187" customHeight="1" spans="3:12">
       <c r="C187" s="1" t="s">
-        <v>1019</v>
+        <v>1052</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>1020</v>
+        <v>1053</v>
       </c>
       <c r="E187" s="1">
         <v>5</v>
@@ -10404,30 +10575,30 @@
         <v>5</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>1021</v>
+        <v>1054</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>1016</v>
+        <v>1055</v>
       </c>
       <c r="I187" s="1">
         <v>0</v>
       </c>
       <c r="J187" s="12" t="s">
-        <v>1017</v>
+        <v>1050</v>
       </c>
       <c r="K187" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L187" s="11" t="s">
-        <v>1022</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="188" customHeight="1" spans="3:12">
       <c r="C188" s="1" t="s">
-        <v>1023</v>
+        <v>1057</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>1024</v>
+        <v>1058</v>
       </c>
       <c r="E188" s="1">
         <v>5</v>
@@ -10436,30 +10607,30 @@
         <v>5</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>1025</v>
+        <v>1059</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>1016</v>
+        <v>1060</v>
       </c>
       <c r="I188" s="1">
         <v>0</v>
       </c>
       <c r="J188" s="12" t="s">
-        <v>1017</v>
+        <v>1050</v>
       </c>
       <c r="K188" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L188" s="11" t="s">
-        <v>1026</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="189" customHeight="1" spans="3:12">
       <c r="C189" s="1" t="s">
-        <v>1027</v>
+        <v>1062</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>1028</v>
+        <v>1063</v>
       </c>
       <c r="E189" s="1">
         <v>5</v>
@@ -10468,30 +10639,30 @@
         <v>5</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>1029</v>
+        <v>1064</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>1016</v>
+        <v>1065</v>
       </c>
       <c r="I189" s="1">
         <v>0</v>
       </c>
       <c r="J189" s="12" t="s">
-        <v>1017</v>
+        <v>1050</v>
       </c>
       <c r="K189" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L189" s="11" t="s">
-        <v>1030</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="190" customHeight="1" spans="3:12">
       <c r="C190" s="1" t="s">
-        <v>1031</v>
+        <v>1067</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>1032</v>
+        <v>1068</v>
       </c>
       <c r="E190" s="1">
         <v>5</v>
@@ -10500,30 +10671,30 @@
         <v>5</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>1033</v>
+        <v>1069</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>1016</v>
+        <v>1070</v>
       </c>
       <c r="I190" s="1">
         <v>0</v>
       </c>
       <c r="J190" s="12" t="s">
-        <v>1017</v>
+        <v>1050</v>
       </c>
       <c r="K190" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L190" s="11" t="s">
-        <v>1034</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="191" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C191" s="1" t="s">
-        <v>1035</v>
+        <v>1072</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>1036</v>
+        <v>1073</v>
       </c>
       <c r="E191" s="1">
         <v>5</v>
@@ -10532,30 +10703,30 @@
         <v>5</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>1037</v>
+        <v>1074</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>1038</v>
+        <v>1075</v>
       </c>
       <c r="I191" s="1">
         <v>0</v>
       </c>
       <c r="J191" s="12" t="s">
-        <v>1039</v>
+        <v>1076</v>
       </c>
       <c r="K191" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L191" s="11" t="s">
-        <v>1040</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="192" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C192" s="1" t="s">
-        <v>1041</v>
+        <v>1078</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>1042</v>
+        <v>1079</v>
       </c>
       <c r="E192" s="1">
         <v>5</v>
@@ -10564,30 +10735,30 @@
         <v>5</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>1043</v>
+        <v>1080</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>1038</v>
+        <v>1081</v>
       </c>
       <c r="I192" s="1">
         <v>0</v>
       </c>
       <c r="J192" s="12" t="s">
-        <v>1039</v>
+        <v>1076</v>
       </c>
       <c r="K192" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L192" s="11" t="s">
-        <v>1044</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="193" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C193" s="1" t="s">
-        <v>1045</v>
+        <v>1083</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>1046</v>
+        <v>1084</v>
       </c>
       <c r="E193" s="1">
         <v>5</v>
@@ -10596,30 +10767,30 @@
         <v>5</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>1047</v>
+        <v>1085</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>1038</v>
+        <v>1086</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
       </c>
       <c r="J193" s="12" t="s">
-        <v>1039</v>
+        <v>1076</v>
       </c>
       <c r="K193" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L193" s="11" t="s">
-        <v>1048</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="194" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C194" s="1" t="s">
-        <v>1049</v>
+        <v>1088</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>1050</v>
+        <v>1089</v>
       </c>
       <c r="E194" s="1">
         <v>5</v>
@@ -10628,30 +10799,30 @@
         <v>5</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>1051</v>
+        <v>1090</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>1038</v>
+        <v>1091</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
       </c>
       <c r="J194" s="12" t="s">
-        <v>1039</v>
+        <v>1076</v>
       </c>
       <c r="K194" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L194" s="11" t="s">
-        <v>1052</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="195" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C195" s="1" t="s">
-        <v>1053</v>
+        <v>1093</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>1054</v>
+        <v>1094</v>
       </c>
       <c r="E195" s="1">
         <v>5</v>
@@ -10660,30 +10831,30 @@
         <v>5</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>1055</v>
+        <v>1095</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>1038</v>
+        <v>1096</v>
       </c>
       <c r="I195" s="1">
         <v>0</v>
       </c>
       <c r="J195" s="12" t="s">
-        <v>1039</v>
+        <v>1076</v>
       </c>
       <c r="K195" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L195" s="11" t="s">
-        <v>1056</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="196" s="4" customFormat="1" customHeight="1" spans="3:12">
       <c r="C196" s="4" t="s">
-        <v>1057</v>
+        <v>1098</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>1058</v>
+        <v>1099</v>
       </c>
       <c r="E196" s="4">
         <v>5</v>
@@ -10692,30 +10863,30 @@
         <v>5</v>
       </c>
       <c r="G196" s="9" t="s">
-        <v>1059</v>
+        <v>1100</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>1060</v>
+        <v>1101</v>
       </c>
       <c r="I196" s="4">
         <v>0</v>
       </c>
       <c r="J196" s="14" t="s">
-        <v>1061</v>
+        <v>1102</v>
       </c>
       <c r="K196" s="14" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L196" s="14" t="s">
-        <v>1062</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="197" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C197" s="1" t="s">
-        <v>1063</v>
+        <v>1104</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>1064</v>
+        <v>1105</v>
       </c>
       <c r="E197" s="1">
         <v>5</v>
@@ -10724,30 +10895,30 @@
         <v>5</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>1065</v>
+        <v>1106</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1060</v>
+        <v>1107</v>
       </c>
       <c r="I197" s="1">
         <v>0</v>
       </c>
       <c r="J197" s="12" t="s">
-        <v>1061</v>
+        <v>1102</v>
       </c>
       <c r="K197" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L197" s="11" t="s">
-        <v>1066</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="198" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C198" s="1" t="s">
-        <v>1067</v>
+        <v>1109</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>1068</v>
+        <v>1110</v>
       </c>
       <c r="E198" s="1">
         <v>5</v>
@@ -10756,30 +10927,30 @@
         <v>5</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>1069</v>
+        <v>1111</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>1060</v>
+        <v>1112</v>
       </c>
       <c r="I198" s="1">
         <v>0</v>
       </c>
       <c r="J198" s="12" t="s">
-        <v>1061</v>
+        <v>1102</v>
       </c>
       <c r="K198" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L198" s="11" t="s">
-        <v>1070</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="199" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C199" s="1" t="s">
-        <v>1071</v>
+        <v>1114</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>1072</v>
+        <v>1115</v>
       </c>
       <c r="E199" s="1">
         <v>5</v>
@@ -10788,30 +10959,30 @@
         <v>5</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>1073</v>
+        <v>1116</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>1060</v>
+        <v>1117</v>
       </c>
       <c r="I199" s="1">
         <v>0</v>
       </c>
       <c r="J199" s="12" t="s">
-        <v>1061</v>
+        <v>1102</v>
       </c>
       <c r="K199" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L199" s="11" t="s">
-        <v>1074</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="200" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C200" s="1" t="s">
-        <v>1075</v>
+        <v>1119</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>1076</v>
+        <v>1120</v>
       </c>
       <c r="E200" s="1">
         <v>5</v>
@@ -10820,30 +10991,30 @@
         <v>5</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>1077</v>
+        <v>1121</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>1060</v>
+        <v>1122</v>
       </c>
       <c r="I200" s="1">
         <v>0</v>
       </c>
       <c r="J200" s="12" t="s">
-        <v>1061</v>
+        <v>1102</v>
       </c>
       <c r="K200" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L200" s="11" t="s">
-        <v>1078</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="201" customHeight="1" spans="3:12">
       <c r="C201" s="1" t="s">
-        <v>1079</v>
+        <v>1124</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1080</v>
+        <v>1125</v>
       </c>
       <c r="E201" s="1">
         <v>5</v>
@@ -10852,30 +11023,30 @@
         <v>5</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>1081</v>
+        <v>1126</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>1082</v>
+        <v>1127</v>
       </c>
       <c r="I201" s="1">
         <v>0</v>
       </c>
       <c r="J201" s="12" t="s">
-        <v>1083</v>
+        <v>1128</v>
       </c>
       <c r="K201" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L201" s="11" t="s">
-        <v>1084</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="202" customHeight="1" spans="3:12">
       <c r="C202" s="1" t="s">
-        <v>1085</v>
+        <v>1130</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1086</v>
+        <v>1131</v>
       </c>
       <c r="E202" s="1">
         <v>5</v>
@@ -10884,30 +11055,30 @@
         <v>5</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>1087</v>
+        <v>1132</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>1082</v>
+        <v>1133</v>
       </c>
       <c r="I202" s="1">
         <v>0</v>
       </c>
       <c r="J202" s="12" t="s">
-        <v>1083</v>
+        <v>1128</v>
       </c>
       <c r="K202" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L202" s="11" t="s">
-        <v>1088</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="203" customHeight="1" spans="3:12">
       <c r="C203" s="1" t="s">
-        <v>1089</v>
+        <v>1135</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>1090</v>
+        <v>1136</v>
       </c>
       <c r="E203" s="1">
         <v>5</v>
@@ -10916,30 +11087,30 @@
         <v>5</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>1091</v>
+        <v>1137</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>1082</v>
+        <v>1138</v>
       </c>
       <c r="I203" s="1">
         <v>0</v>
       </c>
       <c r="J203" s="12" t="s">
-        <v>1083</v>
+        <v>1128</v>
       </c>
       <c r="K203" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L203" s="11" t="s">
-        <v>1092</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="204" customHeight="1" spans="3:12">
       <c r="C204" s="1" t="s">
-        <v>1093</v>
+        <v>1140</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1094</v>
+        <v>1141</v>
       </c>
       <c r="E204" s="1">
         <v>5</v>
@@ -10948,30 +11119,30 @@
         <v>5</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>1095</v>
+        <v>1142</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>1082</v>
+        <v>1143</v>
       </c>
       <c r="I204" s="1">
         <v>0</v>
       </c>
       <c r="J204" s="12" t="s">
-        <v>1083</v>
+        <v>1128</v>
       </c>
       <c r="K204" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L204" s="11" t="s">
-        <v>1096</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="205" customHeight="1" spans="3:12">
       <c r="C205" s="1" t="s">
-        <v>1097</v>
+        <v>1145</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1098</v>
+        <v>1146</v>
       </c>
       <c r="E205" s="1">
         <v>5</v>
@@ -10980,30 +11151,30 @@
         <v>5</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>1099</v>
+        <v>1147</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>1082</v>
+        <v>1148</v>
       </c>
       <c r="I205" s="1">
         <v>0</v>
       </c>
       <c r="J205" s="12" t="s">
-        <v>1083</v>
+        <v>1128</v>
       </c>
       <c r="K205" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L205" s="11" t="s">
-        <v>1100</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="206" customHeight="1" spans="3:12">
       <c r="C206" s="1" t="s">
-        <v>1101</v>
+        <v>1150</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>1102</v>
+        <v>1151</v>
       </c>
       <c r="E206" s="1">
         <v>5</v>
@@ -11012,30 +11183,30 @@
         <v>5</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>1103</v>
+        <v>1152</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>1104</v>
+        <v>1153</v>
       </c>
       <c r="I206" s="1">
         <v>0</v>
       </c>
       <c r="J206" s="12" t="s">
-        <v>1105</v>
+        <v>1154</v>
       </c>
       <c r="K206" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L206" s="11" t="s">
-        <v>1106</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="207" customHeight="1" spans="3:12">
       <c r="C207" s="1" t="s">
-        <v>1107</v>
+        <v>1156</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1108</v>
+        <v>1157</v>
       </c>
       <c r="E207" s="1">
         <v>5</v>
@@ -11044,30 +11215,30 @@
         <v>5</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>1109</v>
+        <v>1158</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>1104</v>
+        <v>1159</v>
       </c>
       <c r="I207" s="1">
         <v>0</v>
       </c>
       <c r="J207" s="12" t="s">
-        <v>1105</v>
+        <v>1154</v>
       </c>
       <c r="K207" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L207" s="11" t="s">
-        <v>1110</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="208" customHeight="1" spans="3:12">
       <c r="C208" s="1" t="s">
-        <v>1111</v>
+        <v>1161</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1112</v>
+        <v>1162</v>
       </c>
       <c r="E208" s="1">
         <v>5</v>
@@ -11076,30 +11247,30 @@
         <v>5</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>1113</v>
+        <v>1163</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>1104</v>
+        <v>1164</v>
       </c>
       <c r="I208" s="1">
         <v>0</v>
       </c>
       <c r="J208" s="12" t="s">
-        <v>1105</v>
+        <v>1154</v>
       </c>
       <c r="K208" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L208" s="11" t="s">
-        <v>1114</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="209" customHeight="1" spans="1:12">
       <c r="C209" s="1" t="s">
-        <v>1115</v>
+        <v>1166</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1116</v>
+        <v>1167</v>
       </c>
       <c r="E209" s="1">
         <v>5</v>
@@ -11108,30 +11279,30 @@
         <v>5</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>1117</v>
+        <v>1168</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>1104</v>
+        <v>1169</v>
       </c>
       <c r="I209" s="1">
         <v>0</v>
       </c>
       <c r="J209" s="12" t="s">
-        <v>1105</v>
+        <v>1154</v>
       </c>
       <c r="K209" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L209" s="11" t="s">
-        <v>1118</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="210" customHeight="1" spans="1:12">
       <c r="C210" s="1" t="s">
-        <v>1119</v>
+        <v>1171</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1120</v>
+        <v>1172</v>
       </c>
       <c r="E210" s="1">
         <v>5</v>
@@ -11140,30 +11311,30 @@
         <v>5</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>1121</v>
+        <v>1173</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>1104</v>
+        <v>1174</v>
       </c>
       <c r="I210" s="1">
         <v>0</v>
       </c>
       <c r="J210" s="12" t="s">
-        <v>1105</v>
+        <v>1154</v>
       </c>
       <c r="K210" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L210" s="11" t="s">
-        <v>1122</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C211" s="1" t="s">
-        <v>1123</v>
+        <v>1176</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1124</v>
+        <v>1177</v>
       </c>
       <c r="E211" s="1">
         <v>5</v>
@@ -11172,30 +11343,30 @@
         <v>5</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>1125</v>
+        <v>1178</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>1126</v>
+        <v>1179</v>
       </c>
       <c r="I211" s="1">
         <v>0</v>
       </c>
       <c r="J211" s="12" t="s">
-        <v>1127</v>
+        <v>1180</v>
       </c>
       <c r="K211" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L211" s="11" t="s">
-        <v>1128</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C212" s="1" t="s">
-        <v>1129</v>
+        <v>1182</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1130</v>
+        <v>1183</v>
       </c>
       <c r="E212" s="1">
         <v>5</v>
@@ -11204,30 +11375,30 @@
         <v>5</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>1131</v>
+        <v>1184</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1126</v>
+        <v>1185</v>
       </c>
       <c r="I212" s="1">
         <v>0</v>
       </c>
       <c r="J212" s="12" t="s">
-        <v>1127</v>
+        <v>1180</v>
       </c>
       <c r="K212" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L212" s="11" t="s">
-        <v>1132</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C213" s="1" t="s">
-        <v>1133</v>
+        <v>1187</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1134</v>
+        <v>1188</v>
       </c>
       <c r="E213" s="1">
         <v>5</v>
@@ -11236,30 +11407,30 @@
         <v>5</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>1135</v>
+        <v>1189</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>1126</v>
+        <v>1190</v>
       </c>
       <c r="I213" s="1">
         <v>0</v>
       </c>
       <c r="J213" s="12" t="s">
-        <v>1127</v>
+        <v>1180</v>
       </c>
       <c r="K213" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L213" s="11" t="s">
-        <v>1136</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C214" s="1" t="s">
-        <v>1137</v>
+        <v>1192</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>1138</v>
+        <v>1193</v>
       </c>
       <c r="E214" s="1">
         <v>5</v>
@@ -11268,30 +11439,30 @@
         <v>5</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>1139</v>
+        <v>1194</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>1126</v>
+        <v>1195</v>
       </c>
       <c r="I214" s="1">
         <v>0</v>
       </c>
       <c r="J214" s="12" t="s">
-        <v>1127</v>
+        <v>1180</v>
       </c>
       <c r="K214" s="12" t="s">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="L214" s="11" t="s">
-        <v>1140</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C215" s="1" t="s">
-        <v>1141</v>
+        <v>1197</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1142</v>
+        <v>1198</v>
       </c>
       <c r="E215" s="1">
         <v>5</v>
@@ -11300,36 +11471,36 @@
         <v>5</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>1143</v>
+        <v>1199</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>1144</v>
+        <v>1200</v>
       </c>
       <c r="I215" s="1">
         <v>0</v>
       </c>
       <c r="J215" s="12" t="s">
-        <v>1145</v>
+        <v>1201</v>
       </c>
       <c r="K215" s="12" t="s">
-        <v>1146</v>
+        <v>1202</v>
       </c>
       <c r="L215" s="11" t="s">
-        <v>1147</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="216" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A216" s="3" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="C216" s="1">
         <v>1210</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>1149</v>
+        <v>1205</v>
       </c>
       <c r="E216" s="3">
         <v>5</v>
@@ -11338,36 +11509,36 @@
         <v>5</v>
       </c>
       <c r="G216" s="10" t="s">
-        <v>1150</v>
+        <v>1206</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>1144</v>
+        <v>1207</v>
       </c>
       <c r="I216" s="3">
         <v>0</v>
       </c>
       <c r="J216" s="13" t="s">
-        <v>1151</v>
+        <v>1208</v>
       </c>
       <c r="K216" s="13" t="s">
-        <v>1146</v>
+        <v>1202</v>
       </c>
       <c r="L216" s="11" t="s">
-        <v>1152</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="217" customHeight="1" spans="1:12">
       <c r="A217" s="3" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="C217" s="1">
         <v>1211</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>1153</v>
+        <v>1210</v>
       </c>
       <c r="E217" s="1">
         <v>5</v>
@@ -11376,36 +11547,36 @@
         <v>5</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1154</v>
+        <v>1211</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>1155</v>
+        <v>1212</v>
       </c>
       <c r="I217" s="1">
         <v>0</v>
       </c>
       <c r="J217" s="12" t="s">
-        <v>1156</v>
+        <v>1213</v>
       </c>
       <c r="K217" s="12" t="s">
-        <v>1146</v>
+        <v>1202</v>
       </c>
       <c r="L217" s="11" t="s">
-        <v>1157</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="218" customHeight="1" spans="1:12">
       <c r="A218" s="3" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="C218" s="1">
         <v>1212</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>1158</v>
+        <v>1215</v>
       </c>
       <c r="E218" s="1">
         <v>5</v>
@@ -11414,36 +11585,36 @@
         <v>5</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1159</v>
+        <v>1216</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>1160</v>
+        <v>1217</v>
       </c>
       <c r="I218" s="1">
         <v>0</v>
       </c>
       <c r="J218" s="12" t="s">
-        <v>1161</v>
+        <v>1218</v>
       </c>
       <c r="K218" s="12" t="s">
-        <v>1146</v>
+        <v>1202</v>
       </c>
       <c r="L218" s="11" t="s">
-        <v>1162</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="219" customHeight="1" spans="1:12">
       <c r="A219" s="3" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="C219" s="1">
         <v>1213</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>1163</v>
+        <v>1220</v>
       </c>
       <c r="E219" s="1">
         <v>5</v>
@@ -11452,36 +11623,36 @@
         <v>5</v>
       </c>
       <c r="G219" s="8" t="s">
-        <v>1164</v>
+        <v>1221</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>1165</v>
+        <v>1222</v>
       </c>
       <c r="I219" s="1">
         <v>0</v>
       </c>
       <c r="J219" s="12" t="s">
-        <v>1166</v>
+        <v>1223</v>
       </c>
       <c r="K219" s="12" t="s">
-        <v>1146</v>
+        <v>1202</v>
       </c>
       <c r="L219" s="11" t="s">
-        <v>1167</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="220" customHeight="1" spans="1:12">
       <c r="A220" s="3" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="C220" s="1">
         <v>1214</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>1168</v>
+        <v>1225</v>
       </c>
       <c r="E220" s="1">
         <v>5</v>
@@ -11490,22 +11661,22 @@
         <v>5</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>1169</v>
+        <v>1226</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>1170</v>
+        <v>1227</v>
       </c>
       <c r="I220" s="1">
         <v>0</v>
       </c>
       <c r="J220" s="12" t="s">
-        <v>1171</v>
+        <v>1228</v>
       </c>
       <c r="K220" s="12" t="s">
-        <v>1146</v>
+        <v>1202</v>
       </c>
       <c r="L220" s="11" t="s">
-        <v>1172</v>
+        <v>1229</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="1230">
   <si>
     <t>_Id</t>
   </si>
@@ -3208,7 +3208,7 @@
     <t>1850-1</t>
   </si>
   <si>
-    <t>混沌冰晶，22升阶石</t>
+    <t>混沌冰晶，23升阶石</t>
   </si>
   <si>
     <t>202002,300091,105,504,210078,1009,505,506,202003</t>
@@ -3673,19 +3673,19 @@
     <t>10209</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>虚无小村</t>
   </si>
   <si>
     <t>2150-1</t>
   </si>
   <si>
-    <t>粉色专属</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210077,1009,505,506,202004,507</t>
+    <t>虚无装备，29升阶石</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,506,202009,507</t>
+  </si>
+  <si>
+    <t>10,9500,9000,98000,600000,140000,600000,700000,800000,900000</t>
   </si>
   <si>
     <t>10210</t>
@@ -3697,10 +3697,10 @@
     <t>2150-2</t>
   </si>
   <si>
-    <t>虚无鹿茸</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210077,1009,505,506,202005,507</t>
+    <t>虚无鹿茸，29升阶石</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,506,202010,507</t>
   </si>
   <si>
     <t>10211</t>
@@ -3712,10 +3712,10 @@
     <t>2150-3</t>
   </si>
   <si>
-    <t>虚无草帽</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210077,1009,505,506,202006,507</t>
+    <t>虚无草帽，29升阶石</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,506,202011,507</t>
   </si>
   <si>
     <t>10212</t>
@@ -3727,10 +3727,10 @@
     <t>2150-4</t>
   </si>
   <si>
-    <t>虚无猫爪</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210077,1009,505,506,202007,507</t>
+    <t>虚无猫爪，29升阶石</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,506,202012,507</t>
   </si>
   <si>
     <t>10213</t>
@@ -3742,10 +3742,10 @@
     <t>2150-5</t>
   </si>
   <si>
-    <t>虚无花朵</t>
-  </si>
-  <si>
-    <t>202002,300091,105,504,210077,1009,505,506,202003,507</t>
+    <t>虚无花朵，29升阶石</t>
+  </si>
+  <si>
+    <t>202002,300091,105,504,210077,1009,505,506,202008,507</t>
   </si>
   <si>
     <t>10214</t>
@@ -11490,50 +11490,40 @@
       </c>
     </row>
     <row r="216" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A216" s="3" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B216" s="3" t="s">
-        <v>1204</v>
-      </c>
       <c r="C216" s="1">
         <v>1210</v>
       </c>
       <c r="D216" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E216" s="3">
+        <v>5</v>
+      </c>
+      <c r="F216" s="3">
+        <v>5</v>
+      </c>
+      <c r="G216" s="10" t="s">
         <v>1205</v>
       </c>
-      <c r="E216" s="3">
-        <v>5</v>
-      </c>
-      <c r="F216" s="3">
-        <v>5</v>
-      </c>
-      <c r="G216" s="10" t="s">
+      <c r="H216" s="3" t="s">
         <v>1206</v>
-      </c>
-      <c r="H216" s="3" t="s">
-        <v>1207</v>
       </c>
       <c r="I216" s="3">
         <v>0</v>
       </c>
       <c r="J216" s="13" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K216" s="13" t="s">
         <v>1208</v>
-      </c>
-      <c r="K216" s="13" t="s">
-        <v>1202</v>
       </c>
       <c r="L216" s="11" t="s">
         <v>1209</v>
       </c>
     </row>
     <row r="217" customHeight="1" spans="1:12">
-      <c r="A217" s="3" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B217" s="3" t="s">
-        <v>1204</v>
-      </c>
+      <c r="A217" s="3"/>
+      <c r="B217" s="3"/>
       <c r="C217" s="1">
         <v>1211</v>
       </c>
@@ -11559,19 +11549,15 @@
         <v>1213</v>
       </c>
       <c r="K217" s="12" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="L217" s="11" t="s">
         <v>1214</v>
       </c>
     </row>
     <row r="218" customHeight="1" spans="1:12">
-      <c r="A218" s="3" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>1204</v>
-      </c>
+      <c r="A218" s="3"/>
+      <c r="B218" s="3"/>
       <c r="C218" s="1">
         <v>1212</v>
       </c>
@@ -11597,19 +11583,15 @@
         <v>1218</v>
       </c>
       <c r="K218" s="12" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="L218" s="11" t="s">
         <v>1219</v>
       </c>
     </row>
     <row r="219" customHeight="1" spans="1:12">
-      <c r="A219" s="3" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B219" s="3" t="s">
-        <v>1204</v>
-      </c>
+      <c r="A219" s="3"/>
+      <c r="B219" s="3"/>
       <c r="C219" s="1">
         <v>1213</v>
       </c>
@@ -11635,19 +11617,15 @@
         <v>1223</v>
       </c>
       <c r="K219" s="12" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="L219" s="11" t="s">
         <v>1224</v>
       </c>
     </row>
     <row r="220" customHeight="1" spans="1:12">
-      <c r="A220" s="3" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B220" s="3" t="s">
-        <v>1204</v>
-      </c>
+      <c r="A220" s="3"/>
+      <c r="B220" s="3"/>
       <c r="C220" s="1">
         <v>1214</v>
       </c>
@@ -11673,7 +11651,7 @@
         <v>1228</v>
       </c>
       <c r="K220" s="12" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="L220" s="11" t="s">
         <v>1229</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="1231">
   <si>
     <t>_Id</t>
   </si>
@@ -3682,15 +3682,18 @@
     <t>虚无装备，29升阶石</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210077,1009,505,506,202009,507</t>
-  </si>
-  <si>
-    <t>10,9500,9000,98000,600000,140000,600000,700000,800000,900000</t>
+    <t>202002,106,504,210084,1009,506,202009,507</t>
+  </si>
+  <si>
+    <t>10,18000,98000,600000,140000,700000,800000,900000</t>
   </si>
   <si>
     <t>10210</t>
   </si>
   <si>
+    <t>基础装备，四格，基础专属，生阶石，口粮，不朽，虚无，永恒</t>
+  </si>
+  <si>
     <t>虚无村外</t>
   </si>
   <si>
@@ -3700,7 +3703,7 @@
     <t>虚无鹿茸，29升阶石</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210077,1009,505,506,202010,507</t>
+    <t>202002,106,504,210084,1009,506,202010,507</t>
   </si>
   <si>
     <t>10211</t>
@@ -3715,7 +3718,7 @@
     <t>虚无草帽，29升阶石</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210077,1009,505,506,202011,507</t>
+    <t>202002,106,504,210084,1009,506,202011,507</t>
   </si>
   <si>
     <t>10212</t>
@@ -3730,7 +3733,7 @@
     <t>虚无猫爪，29升阶石</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210077,1009,505,506,202012,507</t>
+    <t>202002,106,504,210084,1009,506,202012,507</t>
   </si>
   <si>
     <t>10213</t>
@@ -3745,7 +3748,7 @@
     <t>虚无花朵，29升阶石</t>
   </si>
   <si>
-    <t>202002,300091,105,504,210077,1009,505,506,202008,507</t>
+    <t>202002,106,504,210084,1009,506,202008,507</t>
   </si>
   <si>
     <t>10214</t>
@@ -3927,12 +3930,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4398,7 +4401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4413,11 +4416,14 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4775,17 +4781,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M220"/>
+  <dimension ref="A3:M221"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
     <col min="4" max="7" width="11.6272727272727" style="1" customWidth="1"/>
     <col min="8" max="8" width="24" style="1" customWidth="1"/>
     <col min="9" max="9" width="11.6272727272727" style="1" customWidth="1"/>
-    <col min="10" max="10" width="75.8181818181818" style="1" customWidth="1"/>
-    <col min="11" max="11" width="70.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="39.3727272727273" style="5" customWidth="1"/>
-    <col min="13" max="16384" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="10" max="10" width="61.0909090909091" style="1" customWidth="1"/>
+    <col min="11" max="11" width="62.8181818181818" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5454545454545" style="5" customWidth="1"/>
+    <col min="13" max="13" width="57.4545454545455" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.25454545454545" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:13">
@@ -6090,10 +6097,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="11" t="s">
+      <c r="J46" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="K46" s="13" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -6119,10 +6126,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="11" t="s">
+      <c r="J47" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="K47" s="13" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -6148,10 +6155,10 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="J48" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="K48" s="13" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
@@ -6177,10 +6184,10 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J49" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="13" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
@@ -6206,10 +6213,10 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J50" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="K50" s="13" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
@@ -6238,10 +6245,10 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J51" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="K51" s="13" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
@@ -6267,10 +6274,10 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="K52" s="13" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -6296,10 +6303,10 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="11" t="s">
+      <c r="J53" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="11" t="s">
+      <c r="K53" s="13" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
@@ -6325,10 +6332,10 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="J54" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="11" t="s">
+      <c r="K54" s="13" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
@@ -6354,10 +6361,10 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="11" t="s">
+      <c r="J55" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="11" t="s">
+      <c r="K55" s="13" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -6386,10 +6393,10 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="J56" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="11" t="s">
+      <c r="K56" s="13" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
@@ -6418,10 +6425,10 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="J57" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="11" t="s">
+      <c r="K57" s="13" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
@@ -6450,10 +6457,10 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="11" t="s">
+      <c r="K58" s="13" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -6482,10 +6489,10 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="11" t="s">
+      <c r="J59" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="11" t="s">
+      <c r="K59" s="13" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
@@ -6514,10 +6521,10 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="11" t="s">
+      <c r="J60" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="11" t="s">
+      <c r="K60" s="13" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -6547,10 +6554,10 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="12" t="s">
+      <c r="J61" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="12" t="s">
+      <c r="K61" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -6580,10 +6587,10 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="12" t="s">
+      <c r="J62" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="12" t="s">
+      <c r="K62" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -6613,10 +6620,10 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="12" t="s">
+      <c r="J63" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="12" t="s">
+      <c r="K63" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
@@ -6646,10 +6653,10 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="12" t="s">
+      <c r="J64" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="12" t="s">
+      <c r="K64" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
@@ -6679,10 +6686,10 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="12" t="s">
+      <c r="J65" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="12" t="s">
+      <c r="K65" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
@@ -6711,10 +6718,10 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="12" t="s">
+      <c r="J66" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="12" t="s">
+      <c r="K66" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
@@ -6743,10 +6750,10 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="12" t="s">
+      <c r="J67" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="12" t="s">
+      <c r="K67" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
@@ -6775,10 +6782,10 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="12" t="s">
+      <c r="J68" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="12" t="s">
+      <c r="K68" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -6807,10 +6814,10 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="12" t="s">
+      <c r="J69" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="12" t="s">
+      <c r="K69" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
@@ -6839,10 +6846,10 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="12" t="s">
+      <c r="J70" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="12" t="s">
+      <c r="K70" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
@@ -6871,10 +6878,10 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="12" t="s">
+      <c r="J71" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="12" t="s">
+      <c r="K71" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -6903,10 +6910,10 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="12" t="s">
+      <c r="J72" s="14" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="12" t="s">
+      <c r="K72" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -6935,10 +6942,10 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="12" t="s">
+      <c r="J73" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="12" t="s">
+      <c r="K73" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -6967,10 +6974,10 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="12" t="s">
+      <c r="J74" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="12" t="s">
+      <c r="K74" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
@@ -6999,10 +7006,10 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="12" t="s">
+      <c r="J75" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="12" t="s">
+      <c r="K75" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
@@ -7031,10 +7038,10 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="12" t="s">
+      <c r="J76" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="12" t="s">
+      <c r="K76" s="14" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
@@ -7063,10 +7070,10 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="12" t="s">
+      <c r="J77" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="12" t="s">
+      <c r="K77" s="14" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
@@ -7095,10 +7102,10 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="12" t="s">
+      <c r="J78" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="12" t="s">
+      <c r="K78" s="14" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
@@ -7127,10 +7134,10 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="12" t="s">
+      <c r="J79" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="12" t="s">
+      <c r="K79" s="14" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
@@ -7159,10 +7166,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="12" t="s">
+      <c r="J80" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="12" t="s">
+      <c r="K80" s="14" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -7191,10 +7198,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="12" t="s">
+      <c r="J81" s="14" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="12" t="s">
+      <c r="K81" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -7223,10 +7230,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="12" t="s">
+      <c r="J82" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="12" t="s">
+      <c r="K82" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -7255,10 +7262,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="12" t="s">
+      <c r="J83" s="14" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="12" t="s">
+      <c r="K83" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -7287,10 +7294,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="12" t="s">
+      <c r="J84" s="14" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="12" t="s">
+      <c r="K84" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -7319,10 +7326,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="12" t="s">
+      <c r="J85" s="14" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="12" t="s">
+      <c r="K85" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -7351,10 +7358,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="12" t="s">
+      <c r="J86" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="12" t="s">
+      <c r="K86" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -7383,10 +7390,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="12" t="s">
+      <c r="J87" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="12" t="s">
+      <c r="K87" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -7415,10 +7422,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="12" t="s">
+      <c r="J88" s="14" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="12" t="s">
+      <c r="K88" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -7447,10 +7454,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="12" t="s">
+      <c r="J89" s="14" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="12" t="s">
+      <c r="K89" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -7479,10 +7486,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="12" t="s">
+      <c r="J90" s="14" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="12" t="s">
+      <c r="K90" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -7511,10 +7518,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="12" t="s">
+      <c r="J91" s="14" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="12" t="s">
+      <c r="K91" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -7543,10 +7550,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="12" t="s">
+      <c r="J92" s="14" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="12" t="s">
+      <c r="K92" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -7575,10 +7582,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="12" t="s">
+      <c r="J93" s="14" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="12" t="s">
+      <c r="K93" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -7607,10 +7614,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="12" t="s">
+      <c r="J94" s="14" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="12" t="s">
+      <c r="K94" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -7639,10 +7646,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="12" t="s">
+      <c r="J95" s="14" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="12" t="s">
+      <c r="K95" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -7671,10 +7678,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="12" t="s">
+      <c r="J96" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="12" t="s">
+      <c r="K96" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -7703,10 +7710,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="12" t="s">
+      <c r="J97" s="14" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="12" t="s">
+      <c r="K97" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -7735,10 +7742,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="12" t="s">
+      <c r="J98" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="12" t="s">
+      <c r="K98" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -7767,10 +7774,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="12" t="s">
+      <c r="J99" s="14" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="12" t="s">
+      <c r="K99" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -7799,10 +7806,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="12" t="s">
+      <c r="J100" s="14" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="12" t="s">
+      <c r="K100" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -7831,10 +7838,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="12" t="s">
+      <c r="J101" s="14" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="12" t="s">
+      <c r="K101" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -7863,10 +7870,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="12" t="s">
+      <c r="J102" s="14" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="12" t="s">
+      <c r="K102" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -7895,10 +7902,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="12" t="s">
+      <c r="J103" s="14" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="12" t="s">
+      <c r="K103" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -7927,10 +7934,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="12" t="s">
+      <c r="J104" s="14" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="12" t="s">
+      <c r="K104" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -7959,10 +7966,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="12" t="s">
+      <c r="J105" s="14" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="12" t="s">
+      <c r="K105" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -7991,10 +7998,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="12" t="s">
+      <c r="J106" s="14" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="12" t="s">
+      <c r="K106" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -8023,10 +8030,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="12" t="s">
+      <c r="J107" s="14" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="12" t="s">
+      <c r="K107" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -8055,10 +8062,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="12" t="s">
+      <c r="J108" s="14" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="12" t="s">
+      <c r="K108" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -8087,10 +8094,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="12" t="s">
+      <c r="J109" s="14" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="12" t="s">
+      <c r="K109" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -8119,10 +8126,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="12" t="s">
+      <c r="J110" s="14" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="12" t="s">
+      <c r="K110" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -8151,10 +8158,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="12" t="s">
+      <c r="J111" s="14" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="12" t="s">
+      <c r="K111" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -8183,10 +8190,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="12" t="s">
+      <c r="J112" s="14" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="12" t="s">
+      <c r="K112" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -8215,10 +8222,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="12" t="s">
+      <c r="J113" s="14" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="12" t="s">
+      <c r="K113" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -8247,10 +8254,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="12" t="s">
+      <c r="J114" s="14" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="12" t="s">
+      <c r="K114" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -8279,10 +8286,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="12" t="s">
+      <c r="J115" s="14" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="12" t="s">
+      <c r="K115" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -8311,10 +8318,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="12" t="s">
+      <c r="J116" s="14" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="12" t="s">
+      <c r="K116" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -8343,10 +8350,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="12" t="s">
+      <c r="J117" s="14" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="12" t="s">
+      <c r="K117" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -8375,10 +8382,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="12" t="s">
+      <c r="J118" s="14" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="12" t="s">
+      <c r="K118" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -8407,10 +8414,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="12" t="s">
+      <c r="J119" s="14" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="12" t="s">
+      <c r="K119" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -8439,10 +8446,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="12" t="s">
+      <c r="J120" s="14" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="12" t="s">
+      <c r="K120" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -8471,10 +8478,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="12" t="s">
+      <c r="J121" s="14" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="12" t="s">
+      <c r="K121" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -8503,10 +8510,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="12" t="s">
+      <c r="J122" s="14" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="12" t="s">
+      <c r="K122" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -8535,10 +8542,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="12" t="s">
+      <c r="J123" s="14" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="12" t="s">
+      <c r="K123" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -8567,10 +8574,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="12" t="s">
+      <c r="J124" s="14" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="12" t="s">
+      <c r="K124" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -8599,10 +8606,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="12" t="s">
+      <c r="J125" s="14" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="12" t="s">
+      <c r="K125" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -8631,10 +8638,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="12" t="s">
+      <c r="J126" s="14" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="12" t="s">
+      <c r="K126" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -8663,10 +8670,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="12" t="s">
+      <c r="J127" s="14" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="12" t="s">
+      <c r="K127" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -8695,10 +8702,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="12" t="s">
+      <c r="J128" s="14" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="12" t="s">
+      <c r="K128" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -8727,10 +8734,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="12" t="s">
+      <c r="J129" s="14" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="12" t="s">
+      <c r="K129" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -8759,10 +8766,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="12" t="s">
+      <c r="J130" s="14" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="12" t="s">
+      <c r="K130" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -8791,10 +8798,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="12" t="s">
+      <c r="J131" s="14" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="12" t="s">
+      <c r="K131" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -8823,10 +8830,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="12" t="s">
+      <c r="J132" s="14" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="12" t="s">
+      <c r="K132" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -8855,10 +8862,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="12" t="s">
+      <c r="J133" s="14" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="12" t="s">
+      <c r="K133" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -8887,10 +8894,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="12" t="s">
+      <c r="J134" s="14" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="12" t="s">
+      <c r="K134" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -8919,10 +8926,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="12" t="s">
+      <c r="J135" s="14" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="12" t="s">
+      <c r="K135" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -8951,10 +8958,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="12" t="s">
+      <c r="J136" s="14" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="12" t="s">
+      <c r="K136" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -8983,10 +8990,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="12" t="s">
+      <c r="J137" s="14" t="s">
         <v>782</v>
       </c>
-      <c r="K137" s="12" t="s">
+      <c r="K137" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -9015,10 +9022,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="12" t="s">
+      <c r="J138" s="14" t="s">
         <v>788</v>
       </c>
-      <c r="K138" s="12" t="s">
+      <c r="K138" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -9047,10 +9054,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="12" t="s">
+      <c r="J139" s="14" t="s">
         <v>794</v>
       </c>
-      <c r="K139" s="12" t="s">
+      <c r="K139" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -9079,10 +9086,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="12" t="s">
+      <c r="J140" s="14" t="s">
         <v>800</v>
       </c>
-      <c r="K140" s="12" t="s">
+      <c r="K140" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -9111,10 +9118,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="12" t="s">
+      <c r="J141" s="14" t="s">
         <v>806</v>
       </c>
-      <c r="K141" s="12" t="s">
+      <c r="K141" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -9143,10 +9150,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="12" t="s">
+      <c r="J142" s="14" t="s">
         <v>812</v>
       </c>
-      <c r="K142" s="12" t="s">
+      <c r="K142" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -9175,10 +9182,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="12" t="s">
+      <c r="J143" s="14" t="s">
         <v>818</v>
       </c>
-      <c r="K143" s="12" t="s">
+      <c r="K143" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -9207,10 +9214,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="12" t="s">
+      <c r="J144" s="14" t="s">
         <v>824</v>
       </c>
-      <c r="K144" s="12" t="s">
+      <c r="K144" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -9239,10 +9246,10 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="12" t="s">
+      <c r="J145" s="14" t="s">
         <v>830</v>
       </c>
-      <c r="K145" s="12" t="s">
+      <c r="K145" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
@@ -9271,13 +9278,13 @@
       <c r="I146" s="3">
         <v>0</v>
       </c>
-      <c r="J146" s="13" t="s">
+      <c r="J146" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="K146" s="13" t="s">
+      <c r="K146" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L146" s="13" t="s">
+      <c r="L146" s="15" t="s">
         <v>837</v>
       </c>
     </row>
@@ -9303,13 +9310,13 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="12" t="s">
+      <c r="J147" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K147" s="12" t="s">
+      <c r="K147" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L147" s="11" t="s">
+      <c r="L147" s="13" t="s">
         <v>842</v>
       </c>
     </row>
@@ -9335,13 +9342,13 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="12" t="s">
+      <c r="J148" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K148" s="12" t="s">
+      <c r="K148" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L148" s="11" t="s">
+      <c r="L148" s="13" t="s">
         <v>847</v>
       </c>
     </row>
@@ -9367,13 +9374,13 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="12" t="s">
+      <c r="J149" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K149" s="12" t="s">
+      <c r="K149" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L149" s="11" t="s">
+      <c r="L149" s="13" t="s">
         <v>852</v>
       </c>
     </row>
@@ -9399,13 +9406,13 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="12" t="s">
+      <c r="J150" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K150" s="12" t="s">
+      <c r="K150" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L150" s="11" t="s">
+      <c r="L150" s="13" t="s">
         <v>857</v>
       </c>
     </row>
@@ -9431,13 +9438,13 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="12" t="s">
+      <c r="J151" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="K151" s="12" t="s">
+      <c r="K151" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L151" s="11" t="s">
+      <c r="L151" s="13" t="s">
         <v>863</v>
       </c>
     </row>
@@ -9463,13 +9470,13 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="12" t="s">
+      <c r="J152" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="K152" s="12" t="s">
+      <c r="K152" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L152" s="11" t="s">
+      <c r="L152" s="13" t="s">
         <v>868</v>
       </c>
     </row>
@@ -9495,13 +9502,13 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="12" t="s">
+      <c r="J153" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="K153" s="12" t="s">
+      <c r="K153" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L153" s="11" t="s">
+      <c r="L153" s="13" t="s">
         <v>873</v>
       </c>
     </row>
@@ -9527,13 +9534,13 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="12" t="s">
+      <c r="J154" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="K154" s="12" t="s">
+      <c r="K154" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L154" s="11" t="s">
+      <c r="L154" s="13" t="s">
         <v>878</v>
       </c>
     </row>
@@ -9559,13 +9566,13 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="12" t="s">
+      <c r="J155" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="K155" s="12" t="s">
+      <c r="K155" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L155" s="11" t="s">
+      <c r="L155" s="13" t="s">
         <v>883</v>
       </c>
     </row>
@@ -9591,13 +9598,13 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="12" t="s">
+      <c r="J156" s="14" t="s">
         <v>888</v>
       </c>
-      <c r="K156" s="12" t="s">
+      <c r="K156" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L156" s="11" t="s">
+      <c r="L156" s="13" t="s">
         <v>889</v>
       </c>
     </row>
@@ -9623,13 +9630,13 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="12" t="s">
+      <c r="J157" s="14" t="s">
         <v>888</v>
       </c>
-      <c r="K157" s="12" t="s">
+      <c r="K157" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L157" s="11" t="s">
+      <c r="L157" s="13" t="s">
         <v>894</v>
       </c>
     </row>
@@ -9655,13 +9662,13 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="12" t="s">
+      <c r="J158" s="14" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="12" t="s">
+      <c r="K158" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L158" s="11" t="s">
+      <c r="L158" s="13" t="s">
         <v>899</v>
       </c>
     </row>
@@ -9687,13 +9694,13 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="12" t="s">
+      <c r="J159" s="14" t="s">
         <v>888</v>
       </c>
-      <c r="K159" s="12" t="s">
+      <c r="K159" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L159" s="11" t="s">
+      <c r="L159" s="13" t="s">
         <v>904</v>
       </c>
     </row>
@@ -9719,13 +9726,13 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="12" t="s">
+      <c r="J160" s="14" t="s">
         <v>888</v>
       </c>
-      <c r="K160" s="12" t="s">
+      <c r="K160" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L160" s="11" t="s">
+      <c r="L160" s="13" t="s">
         <v>909</v>
       </c>
     </row>
@@ -9751,13 +9758,13 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="12" t="s">
+      <c r="J161" s="14" t="s">
         <v>914</v>
       </c>
-      <c r="K161" s="12" t="s">
+      <c r="K161" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L161" s="11" t="s">
+      <c r="L161" s="13" t="s">
         <v>915</v>
       </c>
     </row>
@@ -9783,13 +9790,13 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="12" t="s">
+      <c r="J162" s="14" t="s">
         <v>914</v>
       </c>
-      <c r="K162" s="12" t="s">
+      <c r="K162" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L162" s="11" t="s">
+      <c r="L162" s="13" t="s">
         <v>920</v>
       </c>
     </row>
@@ -9815,13 +9822,13 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="12" t="s">
+      <c r="J163" s="14" t="s">
         <v>914</v>
       </c>
-      <c r="K163" s="12" t="s">
+      <c r="K163" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L163" s="11" t="s">
+      <c r="L163" s="13" t="s">
         <v>925</v>
       </c>
     </row>
@@ -9847,13 +9854,13 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="12" t="s">
+      <c r="J164" s="14" t="s">
         <v>914</v>
       </c>
-      <c r="K164" s="12" t="s">
+      <c r="K164" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L164" s="11" t="s">
+      <c r="L164" s="13" t="s">
         <v>930</v>
       </c>
     </row>
@@ -9879,13 +9886,13 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="12" t="s">
+      <c r="J165" s="14" t="s">
         <v>914</v>
       </c>
-      <c r="K165" s="12" t="s">
+      <c r="K165" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L165" s="11" t="s">
+      <c r="L165" s="13" t="s">
         <v>935</v>
       </c>
     </row>
@@ -9911,13 +9918,13 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="12" t="s">
+      <c r="J166" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="K166" s="12" t="s">
+      <c r="K166" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L166" s="11" t="s">
+      <c r="L166" s="13" t="s">
         <v>941</v>
       </c>
     </row>
@@ -9943,13 +9950,13 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="12" t="s">
+      <c r="J167" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="K167" s="12" t="s">
+      <c r="K167" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L167" s="11" t="s">
+      <c r="L167" s="13" t="s">
         <v>946</v>
       </c>
     </row>
@@ -9975,13 +9982,13 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="12" t="s">
+      <c r="J168" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="K168" s="12" t="s">
+      <c r="K168" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L168" s="11" t="s">
+      <c r="L168" s="13" t="s">
         <v>951</v>
       </c>
     </row>
@@ -10007,13 +10014,13 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="12" t="s">
+      <c r="J169" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="K169" s="12" t="s">
+      <c r="K169" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L169" s="11" t="s">
+      <c r="L169" s="13" t="s">
         <v>956</v>
       </c>
     </row>
@@ -10039,13 +10046,13 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="12" t="s">
+      <c r="J170" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="12" t="s">
+      <c r="K170" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L170" s="11" t="s">
+      <c r="L170" s="13" t="s">
         <v>961</v>
       </c>
     </row>
@@ -10071,13 +10078,13 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="12" t="s">
+      <c r="J171" s="14" t="s">
         <v>966</v>
       </c>
-      <c r="K171" s="12" t="s">
+      <c r="K171" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L171" s="11" t="s">
+      <c r="L171" s="13" t="s">
         <v>967</v>
       </c>
     </row>
@@ -10103,13 +10110,13 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="12" t="s">
+      <c r="J172" s="14" t="s">
         <v>966</v>
       </c>
-      <c r="K172" s="12" t="s">
+      <c r="K172" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L172" s="11" t="s">
+      <c r="L172" s="13" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10135,13 +10142,13 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="12" t="s">
+      <c r="J173" s="14" t="s">
         <v>966</v>
       </c>
-      <c r="K173" s="12" t="s">
+      <c r="K173" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L173" s="11" t="s">
+      <c r="L173" s="13" t="s">
         <v>977</v>
       </c>
     </row>
@@ -10167,13 +10174,13 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="12" t="s">
+      <c r="J174" s="14" t="s">
         <v>966</v>
       </c>
-      <c r="K174" s="12" t="s">
+      <c r="K174" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L174" s="11" t="s">
+      <c r="L174" s="13" t="s">
         <v>982</v>
       </c>
     </row>
@@ -10199,13 +10206,13 @@
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="12" t="s">
+      <c r="J175" s="14" t="s">
         <v>966</v>
       </c>
-      <c r="K175" s="12" t="s">
+      <c r="K175" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L175" s="11" t="s">
+      <c r="L175" s="13" t="s">
         <v>987</v>
       </c>
     </row>
@@ -10231,13 +10238,13 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="12" t="s">
+      <c r="J176" s="14" t="s">
         <v>992</v>
       </c>
-      <c r="K176" s="12" t="s">
+      <c r="K176" s="14" t="s">
         <v>993</v>
       </c>
-      <c r="L176" s="11" t="s">
+      <c r="L176" s="13" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10263,13 +10270,13 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="12" t="s">
+      <c r="J177" s="14" t="s">
         <v>992</v>
       </c>
-      <c r="K177" s="12" t="s">
+      <c r="K177" s="14" t="s">
         <v>993</v>
       </c>
-      <c r="L177" s="11" t="s">
+      <c r="L177" s="13" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10295,13 +10302,13 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="12" t="s">
+      <c r="J178" s="14" t="s">
         <v>992</v>
       </c>
-      <c r="K178" s="12" t="s">
+      <c r="K178" s="14" t="s">
         <v>993</v>
       </c>
-      <c r="L178" s="11" t="s">
+      <c r="L178" s="13" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -10327,13 +10334,13 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="12" t="s">
+      <c r="J179" s="14" t="s">
         <v>992</v>
       </c>
-      <c r="K179" s="12" t="s">
+      <c r="K179" s="14" t="s">
         <v>993</v>
       </c>
-      <c r="L179" s="11" t="s">
+      <c r="L179" s="13" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -10359,13 +10366,13 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="12" t="s">
+      <c r="J180" s="14" t="s">
         <v>992</v>
       </c>
-      <c r="K180" s="12" t="s">
+      <c r="K180" s="14" t="s">
         <v>993</v>
       </c>
-      <c r="L180" s="11" t="s">
+      <c r="L180" s="13" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -10391,13 +10398,13 @@
       <c r="I181" s="3">
         <v>0</v>
       </c>
-      <c r="J181" s="13" t="s">
+      <c r="J181" s="15" t="s">
         <v>1019</v>
       </c>
-      <c r="K181" s="13" t="s">
+      <c r="K181" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L181" s="11" t="s">
+      <c r="L181" s="13" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -10423,13 +10430,13 @@
       <c r="I182" s="1">
         <v>0</v>
       </c>
-      <c r="J182" s="12" t="s">
+      <c r="J182" s="14" t="s">
         <v>1026</v>
       </c>
-      <c r="K182" s="12" t="s">
+      <c r="K182" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L182" s="11" t="s">
+      <c r="L182" s="13" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -10455,13 +10462,13 @@
       <c r="I183" s="1">
         <v>0</v>
       </c>
-      <c r="J183" s="12" t="s">
+      <c r="J183" s="14" t="s">
         <v>1032</v>
       </c>
-      <c r="K183" s="12" t="s">
+      <c r="K183" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L183" s="11" t="s">
+      <c r="L183" s="13" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10487,13 +10494,13 @@
       <c r="I184" s="1">
         <v>0</v>
       </c>
-      <c r="J184" s="12" t="s">
+      <c r="J184" s="14" t="s">
         <v>1038</v>
       </c>
-      <c r="K184" s="12" t="s">
+      <c r="K184" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L184" s="11" t="s">
+      <c r="L184" s="13" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10519,13 +10526,13 @@
       <c r="I185" s="1">
         <v>0</v>
       </c>
-      <c r="J185" s="12" t="s">
+      <c r="J185" s="14" t="s">
         <v>1044</v>
       </c>
-      <c r="K185" s="12" t="s">
+      <c r="K185" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L185" s="11" t="s">
+      <c r="L185" s="13" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -10551,13 +10558,13 @@
       <c r="I186" s="1">
         <v>0</v>
       </c>
-      <c r="J186" s="12" t="s">
+      <c r="J186" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="K186" s="12" t="s">
+      <c r="K186" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L186" s="11" t="s">
+      <c r="L186" s="13" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -10583,13 +10590,13 @@
       <c r="I187" s="1">
         <v>0</v>
       </c>
-      <c r="J187" s="12" t="s">
+      <c r="J187" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="K187" s="12" t="s">
+      <c r="K187" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L187" s="11" t="s">
+      <c r="L187" s="13" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -10615,13 +10622,13 @@
       <c r="I188" s="1">
         <v>0</v>
       </c>
-      <c r="J188" s="12" t="s">
+      <c r="J188" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="K188" s="12" t="s">
+      <c r="K188" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L188" s="11" t="s">
+      <c r="L188" s="13" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -10647,13 +10654,13 @@
       <c r="I189" s="1">
         <v>0</v>
       </c>
-      <c r="J189" s="12" t="s">
+      <c r="J189" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="K189" s="12" t="s">
+      <c r="K189" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L189" s="11" t="s">
+      <c r="L189" s="13" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -10679,13 +10686,13 @@
       <c r="I190" s="1">
         <v>0</v>
       </c>
-      <c r="J190" s="12" t="s">
+      <c r="J190" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="K190" s="12" t="s">
+      <c r="K190" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L190" s="11" t="s">
+      <c r="L190" s="13" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -10711,13 +10718,13 @@
       <c r="I191" s="1">
         <v>0</v>
       </c>
-      <c r="J191" s="12" t="s">
+      <c r="J191" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="K191" s="12" t="s">
+      <c r="K191" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L191" s="11" t="s">
+      <c r="L191" s="13" t="s">
         <v>1077</v>
       </c>
     </row>
@@ -10743,13 +10750,13 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-      <c r="J192" s="12" t="s">
+      <c r="J192" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="K192" s="12" t="s">
+      <c r="K192" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L192" s="11" t="s">
+      <c r="L192" s="13" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -10775,13 +10782,13 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-      <c r="J193" s="12" t="s">
+      <c r="J193" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="K193" s="12" t="s">
+      <c r="K193" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L193" s="11" t="s">
+      <c r="L193" s="13" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -10807,13 +10814,13 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-      <c r="J194" s="12" t="s">
+      <c r="J194" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="K194" s="12" t="s">
+      <c r="K194" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L194" s="11" t="s">
+      <c r="L194" s="13" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -10839,13 +10846,13 @@
       <c r="I195" s="1">
         <v>0</v>
       </c>
-      <c r="J195" s="12" t="s">
+      <c r="J195" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="K195" s="12" t="s">
+      <c r="K195" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L195" s="11" t="s">
+      <c r="L195" s="13" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -10871,13 +10878,13 @@
       <c r="I196" s="4">
         <v>0</v>
       </c>
-      <c r="J196" s="14" t="s">
+      <c r="J196" s="16" t="s">
         <v>1102</v>
       </c>
-      <c r="K196" s="14" t="s">
+      <c r="K196" s="16" t="s">
         <v>1020</v>
       </c>
-      <c r="L196" s="14" t="s">
+      <c r="L196" s="16" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -10903,13 +10910,13 @@
       <c r="I197" s="1">
         <v>0</v>
       </c>
-      <c r="J197" s="12" t="s">
+      <c r="J197" s="14" t="s">
         <v>1102</v>
       </c>
-      <c r="K197" s="12" t="s">
+      <c r="K197" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L197" s="11" t="s">
+      <c r="L197" s="13" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -10935,13 +10942,13 @@
       <c r="I198" s="1">
         <v>0</v>
       </c>
-      <c r="J198" s="12" t="s">
+      <c r="J198" s="14" t="s">
         <v>1102</v>
       </c>
-      <c r="K198" s="12" t="s">
+      <c r="K198" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L198" s="11" t="s">
+      <c r="L198" s="13" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -10967,13 +10974,13 @@
       <c r="I199" s="1">
         <v>0</v>
       </c>
-      <c r="J199" s="12" t="s">
+      <c r="J199" s="14" t="s">
         <v>1102</v>
       </c>
-      <c r="K199" s="12" t="s">
+      <c r="K199" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L199" s="11" t="s">
+      <c r="L199" s="13" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -10999,13 +11006,13 @@
       <c r="I200" s="1">
         <v>0</v>
       </c>
-      <c r="J200" s="12" t="s">
+      <c r="J200" s="14" t="s">
         <v>1102</v>
       </c>
-      <c r="K200" s="12" t="s">
+      <c r="K200" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L200" s="11" t="s">
+      <c r="L200" s="13" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -11031,13 +11038,13 @@
       <c r="I201" s="1">
         <v>0</v>
       </c>
-      <c r="J201" s="12" t="s">
+      <c r="J201" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="K201" s="12" t="s">
+      <c r="K201" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L201" s="11" t="s">
+      <c r="L201" s="13" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -11063,13 +11070,13 @@
       <c r="I202" s="1">
         <v>0</v>
       </c>
-      <c r="J202" s="12" t="s">
+      <c r="J202" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="K202" s="12" t="s">
+      <c r="K202" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L202" s="11" t="s">
+      <c r="L202" s="13" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -11095,13 +11102,13 @@
       <c r="I203" s="1">
         <v>0</v>
       </c>
-      <c r="J203" s="12" t="s">
+      <c r="J203" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="K203" s="12" t="s">
+      <c r="K203" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L203" s="11" t="s">
+      <c r="L203" s="13" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -11127,13 +11134,13 @@
       <c r="I204" s="1">
         <v>0</v>
       </c>
-      <c r="J204" s="12" t="s">
+      <c r="J204" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="K204" s="12" t="s">
+      <c r="K204" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L204" s="11" t="s">
+      <c r="L204" s="13" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -11159,13 +11166,13 @@
       <c r="I205" s="1">
         <v>0</v>
       </c>
-      <c r="J205" s="12" t="s">
+      <c r="J205" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="K205" s="12" t="s">
+      <c r="K205" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L205" s="11" t="s">
+      <c r="L205" s="13" t="s">
         <v>1149</v>
       </c>
     </row>
@@ -11191,13 +11198,13 @@
       <c r="I206" s="1">
         <v>0</v>
       </c>
-      <c r="J206" s="12" t="s">
+      <c r="J206" s="14" t="s">
         <v>1154</v>
       </c>
-      <c r="K206" s="12" t="s">
+      <c r="K206" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L206" s="11" t="s">
+      <c r="L206" s="13" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -11223,13 +11230,13 @@
       <c r="I207" s="1">
         <v>0</v>
       </c>
-      <c r="J207" s="12" t="s">
+      <c r="J207" s="14" t="s">
         <v>1154</v>
       </c>
-      <c r="K207" s="12" t="s">
+      <c r="K207" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L207" s="11" t="s">
+      <c r="L207" s="13" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -11255,17 +11262,17 @@
       <c r="I208" s="1">
         <v>0</v>
       </c>
-      <c r="J208" s="12" t="s">
+      <c r="J208" s="14" t="s">
         <v>1154</v>
       </c>
-      <c r="K208" s="12" t="s">
+      <c r="K208" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L208" s="11" t="s">
+      <c r="L208" s="13" t="s">
         <v>1165</v>
       </c>
     </row>
-    <row r="209" customHeight="1" spans="1:12">
+    <row r="209" customHeight="1" spans="1:13">
       <c r="C209" s="1" t="s">
         <v>1166</v>
       </c>
@@ -11287,17 +11294,17 @@
       <c r="I209" s="1">
         <v>0</v>
       </c>
-      <c r="J209" s="12" t="s">
+      <c r="J209" s="14" t="s">
         <v>1154</v>
       </c>
-      <c r="K209" s="12" t="s">
+      <c r="K209" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L209" s="11" t="s">
+      <c r="L209" s="13" t="s">
         <v>1170</v>
       </c>
     </row>
-    <row r="210" customHeight="1" spans="1:12">
+    <row r="210" customHeight="1" spans="1:13">
       <c r="C210" s="1" t="s">
         <v>1171</v>
       </c>
@@ -11319,17 +11326,17 @@
       <c r="I210" s="1">
         <v>0</v>
       </c>
-      <c r="J210" s="12" t="s">
+      <c r="J210" s="14" t="s">
         <v>1154</v>
       </c>
-      <c r="K210" s="12" t="s">
+      <c r="K210" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L210" s="11" t="s">
+      <c r="L210" s="13" t="s">
         <v>1175</v>
       </c>
     </row>
-    <row r="211" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="211" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C211" s="1" t="s">
         <v>1176</v>
       </c>
@@ -11351,17 +11358,17 @@
       <c r="I211" s="1">
         <v>0</v>
       </c>
-      <c r="J211" s="12" t="s">
+      <c r="J211" s="14" t="s">
         <v>1180</v>
       </c>
-      <c r="K211" s="12" t="s">
+      <c r="K211" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L211" s="11" t="s">
+      <c r="L211" s="13" t="s">
         <v>1181</v>
       </c>
     </row>
-    <row r="212" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="212" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C212" s="1" t="s">
         <v>1182</v>
       </c>
@@ -11383,17 +11390,17 @@
       <c r="I212" s="1">
         <v>0</v>
       </c>
-      <c r="J212" s="12" t="s">
+      <c r="J212" s="14" t="s">
         <v>1180</v>
       </c>
-      <c r="K212" s="12" t="s">
+      <c r="K212" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L212" s="11" t="s">
+      <c r="L212" s="13" t="s">
         <v>1186</v>
       </c>
     </row>
-    <row r="213" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="213" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C213" s="1" t="s">
         <v>1187</v>
       </c>
@@ -11415,17 +11422,19 @@
       <c r="I213" s="1">
         <v>0</v>
       </c>
-      <c r="J213" s="12" t="s">
+      <c r="J213" s="14" t="s">
         <v>1180</v>
       </c>
-      <c r="K213" s="12" t="s">
+      <c r="K213" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L213" s="11" t="s">
+      <c r="L213" s="13" t="s">
         <v>1191</v>
       </c>
     </row>
-    <row r="214" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="214" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A214" s="10"/>
+      <c r="B214" s="10"/>
       <c r="C214" s="1" t="s">
         <v>1192</v>
       </c>
@@ -11447,17 +11456,19 @@
       <c r="I214" s="1">
         <v>0</v>
       </c>
-      <c r="J214" s="12" t="s">
+      <c r="J214" s="14" t="s">
         <v>1180</v>
       </c>
-      <c r="K214" s="12" t="s">
+      <c r="K214" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L214" s="11" t="s">
+      <c r="L214" s="13" t="s">
         <v>1196</v>
       </c>
     </row>
-    <row r="215" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="215" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A215" s="10"/>
+      <c r="B215" s="10"/>
       <c r="C215" s="1" t="s">
         <v>1197</v>
       </c>
@@ -11479,17 +11490,19 @@
       <c r="I215" s="1">
         <v>0</v>
       </c>
-      <c r="J215" s="12" t="s">
+      <c r="J215" s="14" t="s">
         <v>1201</v>
       </c>
-      <c r="K215" s="12" t="s">
+      <c r="K215" s="14" t="s">
         <v>1202</v>
       </c>
-      <c r="L215" s="11" t="s">
+      <c r="L215" s="13" t="s">
         <v>1203</v>
       </c>
     </row>
-    <row r="216" s="3" customFormat="1" customHeight="1" spans="1:12">
+    <row r="216" s="3" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A216" s="11"/>
+      <c r="B216" s="11"/>
       <c r="C216" s="1">
         <v>1210</v>
       </c>
@@ -11502,7 +11515,7 @@
       <c r="F216" s="3">
         <v>5</v>
       </c>
-      <c r="G216" s="10" t="s">
+      <c r="G216" s="12" t="s">
         <v>1205</v>
       </c>
       <c r="H216" s="3" t="s">
@@ -11511,24 +11524,27 @@
       <c r="I216" s="3">
         <v>0</v>
       </c>
-      <c r="J216" s="13" t="s">
+      <c r="J216" s="15" t="s">
         <v>1207</v>
       </c>
-      <c r="K216" s="13" t="s">
+      <c r="K216" s="15" t="s">
         <v>1208</v>
       </c>
-      <c r="L216" s="11" t="s">
+      <c r="L216" s="13" t="s">
         <v>1209</v>
       </c>
-    </row>
-    <row r="217" customHeight="1" spans="1:12">
-      <c r="A217" s="3"/>
-      <c r="B217" s="3"/>
+      <c r="M216" s="3" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="217" customHeight="1" spans="1:13">
+      <c r="A217" s="11"/>
+      <c r="B217" s="11"/>
       <c r="C217" s="1">
         <v>1211</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="E217" s="1">
         <v>5</v>
@@ -11537,32 +11553,32 @@
         <v>5</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="I217" s="1">
         <v>0</v>
       </c>
-      <c r="J217" s="12" t="s">
-        <v>1213</v>
-      </c>
-      <c r="K217" s="12" t="s">
+      <c r="J217" s="14" t="s">
+        <v>1214</v>
+      </c>
+      <c r="K217" s="17" t="s">
         <v>1208</v>
       </c>
-      <c r="L217" s="11" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="218" customHeight="1" spans="1:12">
-      <c r="A218" s="3"/>
-      <c r="B218" s="3"/>
+      <c r="L217" s="13" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="218" customHeight="1" spans="1:13">
+      <c r="A218" s="11"/>
+      <c r="B218" s="11"/>
       <c r="C218" s="1">
         <v>1212</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="E218" s="1">
         <v>5</v>
@@ -11571,32 +11587,32 @@
         <v>5</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="I218" s="1">
         <v>0</v>
       </c>
-      <c r="J218" s="12" t="s">
-        <v>1218</v>
-      </c>
-      <c r="K218" s="12" t="s">
+      <c r="J218" s="14" t="s">
+        <v>1219</v>
+      </c>
+      <c r="K218" s="17" t="s">
         <v>1208</v>
       </c>
-      <c r="L218" s="11" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="219" customHeight="1" spans="1:12">
-      <c r="A219" s="3"/>
-      <c r="B219" s="3"/>
+      <c r="L218" s="13" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="219" customHeight="1" spans="1:13">
+      <c r="A219" s="11"/>
+      <c r="B219" s="11"/>
       <c r="C219" s="1">
         <v>1213</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E219" s="1">
         <v>5</v>
@@ -11605,32 +11621,32 @@
         <v>5</v>
       </c>
       <c r="G219" s="8" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="I219" s="1">
         <v>0</v>
       </c>
-      <c r="J219" s="12" t="s">
-        <v>1223</v>
-      </c>
-      <c r="K219" s="12" t="s">
+      <c r="J219" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="K219" s="17" t="s">
         <v>1208</v>
       </c>
-      <c r="L219" s="11" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="220" customHeight="1" spans="1:12">
-      <c r="A220" s="3"/>
-      <c r="B220" s="3"/>
+      <c r="L219" s="13" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="220" customHeight="1" spans="1:13">
+      <c r="A220" s="11"/>
+      <c r="B220" s="11"/>
       <c r="C220" s="1">
         <v>1214</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="E220" s="1">
         <v>5</v>
@@ -11639,23 +11655,27 @@
         <v>5</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="I220" s="1">
         <v>0</v>
       </c>
-      <c r="J220" s="12" t="s">
-        <v>1228</v>
-      </c>
-      <c r="K220" s="12" t="s">
+      <c r="J220" s="14" t="s">
+        <v>1229</v>
+      </c>
+      <c r="K220" s="17" t="s">
         <v>1208</v>
       </c>
-      <c r="L220" s="11" t="s">
-        <v>1229</v>
-      </c>
+      <c r="L220" s="13" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="221" customHeight="1" spans="1:13">
+      <c r="A221" s="10"/>
+      <c r="B221" s="10"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C216:C220">

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -3682,16 +3682,16 @@
     <t>虚无装备，29升阶石</t>
   </si>
   <si>
-    <t>202002,106,504,210084,1009,506,202009,507</t>
-  </si>
-  <si>
-    <t>10,18000,98000,600000,140000,700000,800000,900000</t>
+    <t>202002,106,504,210084,1009,506,202009,202003,507</t>
+  </si>
+  <si>
+    <t>10,18000,98000,600000,140000,700000,800000,900000,900000</t>
   </si>
   <si>
     <t>10210</t>
   </si>
   <si>
-    <t>基础装备，四格，基础专属，生阶石，口粮，不朽，虚无，永恒</t>
+    <t>基础装备，四格，基础专属，生阶石，口粮，不朽，虚无，混沌，永恒</t>
   </si>
   <si>
     <t>虚无村外</t>
@@ -3703,7 +3703,7 @@
     <t>虚无鹿茸，29升阶石</t>
   </si>
   <si>
-    <t>202002,106,504,210084,1009,506,202010,507</t>
+    <t>202002,106,504,210084,1009,506,202010,202003,507</t>
   </si>
   <si>
     <t>10211</t>
@@ -3718,7 +3718,7 @@
     <t>虚无草帽，29升阶石</t>
   </si>
   <si>
-    <t>202002,106,504,210084,1009,506,202011,507</t>
+    <t>202002,106,504,210084,1009,506,202011,202003,507</t>
   </si>
   <si>
     <t>10212</t>
@@ -3733,7 +3733,7 @@
     <t>虚无猫爪，29升阶石</t>
   </si>
   <si>
-    <t>202002,106,504,210084,1009,506,202012,507</t>
+    <t>202002,106,504,210084,1009,506,202012,202003,507</t>
   </si>
   <si>
     <t>10213</t>
@@ -3748,7 +3748,7 @@
     <t>虚无花朵，29升阶石</t>
   </si>
   <si>
-    <t>202002,106,504,210084,1009,506,202008,507</t>
+    <t>202002,106,504,210084,1009,506,202008,202003,507</t>
   </si>
   <si>
     <t>10214</t>
@@ -4401,7 +4401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4416,9 +4416,8 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -6097,10 +6096,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="13" t="s">
+      <c r="J46" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="13" t="s">
+      <c r="K46" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -6126,10 +6125,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="13" t="s">
+      <c r="J47" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="13" t="s">
+      <c r="K47" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -6155,10 +6154,10 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="13" t="s">
+      <c r="J48" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="13" t="s">
+      <c r="K48" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
@@ -6184,10 +6183,10 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="13" t="s">
+      <c r="J49" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="13" t="s">
+      <c r="K49" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
@@ -6213,10 +6212,10 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="13" t="s">
+      <c r="J50" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="13" t="s">
+      <c r="K50" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
@@ -6245,10 +6244,10 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="13" t="s">
+      <c r="J51" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="13" t="s">
+      <c r="K51" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
@@ -6274,10 +6273,10 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="13" t="s">
+      <c r="J52" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="13" t="s">
+      <c r="K52" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -6303,10 +6302,10 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="13" t="s">
+      <c r="J53" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="13" t="s">
+      <c r="K53" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
@@ -6332,10 +6331,10 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="13" t="s">
+      <c r="J54" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="13" t="s">
+      <c r="K54" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
@@ -6361,10 +6360,10 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="13" t="s">
+      <c r="J55" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="13" t="s">
+      <c r="K55" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -6393,10 +6392,10 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="13" t="s">
+      <c r="J56" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="13" t="s">
+      <c r="K56" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
@@ -6425,10 +6424,10 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="13" t="s">
+      <c r="J57" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="13" t="s">
+      <c r="K57" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
@@ -6457,10 +6456,10 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="13" t="s">
+      <c r="J58" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="13" t="s">
+      <c r="K58" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -6489,10 +6488,10 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="13" t="s">
+      <c r="J59" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="13" t="s">
+      <c r="K59" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
@@ -6521,10 +6520,10 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="13" t="s">
+      <c r="J60" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="13" t="s">
+      <c r="K60" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -6554,10 +6553,10 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="14" t="s">
+      <c r="J61" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="14" t="s">
+      <c r="K61" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -6587,10 +6586,10 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="14" t="s">
+      <c r="J62" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="14" t="s">
+      <c r="K62" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -6620,10 +6619,10 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="14" t="s">
+      <c r="J63" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="14" t="s">
+      <c r="K63" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
@@ -6653,10 +6652,10 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="14" t="s">
+      <c r="J64" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="14" t="s">
+      <c r="K64" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
@@ -6686,10 +6685,10 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="14" t="s">
+      <c r="J65" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="14" t="s">
+      <c r="K65" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
@@ -6718,10 +6717,10 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="14" t="s">
+      <c r="J66" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="14" t="s">
+      <c r="K66" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
@@ -6750,10 +6749,10 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="14" t="s">
+      <c r="J67" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="14" t="s">
+      <c r="K67" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
@@ -6782,10 +6781,10 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="14" t="s">
+      <c r="J68" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="14" t="s">
+      <c r="K68" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -6814,10 +6813,10 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="14" t="s">
+      <c r="J69" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="14" t="s">
+      <c r="K69" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
@@ -6846,10 +6845,10 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="14" t="s">
+      <c r="J70" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="14" t="s">
+      <c r="K70" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
@@ -6878,10 +6877,10 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="14" t="s">
+      <c r="J71" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="14" t="s">
+      <c r="K71" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -6910,10 +6909,10 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="14" t="s">
+      <c r="J72" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="14" t="s">
+      <c r="K72" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -6942,10 +6941,10 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="14" t="s">
+      <c r="J73" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="14" t="s">
+      <c r="K73" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -6974,10 +6973,10 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="14" t="s">
+      <c r="J74" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="14" t="s">
+      <c r="K74" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
@@ -7006,10 +7005,10 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="14" t="s">
+      <c r="J75" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="14" t="s">
+      <c r="K75" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
@@ -7038,10 +7037,10 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="14" t="s">
+      <c r="J76" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="14" t="s">
+      <c r="K76" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
@@ -7070,10 +7069,10 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="14" t="s">
+      <c r="J77" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="14" t="s">
+      <c r="K77" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
@@ -7102,10 +7101,10 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="14" t="s">
+      <c r="J78" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="14" t="s">
+      <c r="K78" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
@@ -7134,10 +7133,10 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="14" t="s">
+      <c r="J79" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="14" t="s">
+      <c r="K79" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
@@ -7166,10 +7165,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="14" t="s">
+      <c r="J80" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="14" t="s">
+      <c r="K80" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -7198,10 +7197,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="14" t="s">
+      <c r="J81" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="14" t="s">
+      <c r="K81" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -7230,10 +7229,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="14" t="s">
+      <c r="J82" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="14" t="s">
+      <c r="K82" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -7262,10 +7261,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="14" t="s">
+      <c r="J83" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="14" t="s">
+      <c r="K83" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -7294,10 +7293,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="14" t="s">
+      <c r="J84" s="13" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="14" t="s">
+      <c r="K84" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -7326,10 +7325,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="14" t="s">
+      <c r="J85" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="14" t="s">
+      <c r="K85" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -7358,10 +7357,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="14" t="s">
+      <c r="J86" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="14" t="s">
+      <c r="K86" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -7390,10 +7389,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="14" t="s">
+      <c r="J87" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="14" t="s">
+      <c r="K87" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -7422,10 +7421,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="14" t="s">
+      <c r="J88" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="14" t="s">
+      <c r="K88" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -7454,10 +7453,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="14" t="s">
+      <c r="J89" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="14" t="s">
+      <c r="K89" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -7486,10 +7485,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="14" t="s">
+      <c r="J90" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="14" t="s">
+      <c r="K90" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -7518,10 +7517,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="14" t="s">
+      <c r="J91" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="14" t="s">
+      <c r="K91" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -7550,10 +7549,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="14" t="s">
+      <c r="J92" s="13" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="14" t="s">
+      <c r="K92" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -7582,10 +7581,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="14" t="s">
+      <c r="J93" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="14" t="s">
+      <c r="K93" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -7614,10 +7613,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="14" t="s">
+      <c r="J94" s="13" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="14" t="s">
+      <c r="K94" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -7646,10 +7645,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="14" t="s">
+      <c r="J95" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="14" t="s">
+      <c r="K95" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -7678,10 +7677,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="14" t="s">
+      <c r="J96" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="14" t="s">
+      <c r="K96" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -7710,10 +7709,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="14" t="s">
+      <c r="J97" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="14" t="s">
+      <c r="K97" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -7742,10 +7741,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="14" t="s">
+      <c r="J98" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="14" t="s">
+      <c r="K98" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -7774,10 +7773,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="14" t="s">
+      <c r="J99" s="13" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="14" t="s">
+      <c r="K99" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -7806,10 +7805,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="14" t="s">
+      <c r="J100" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="14" t="s">
+      <c r="K100" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -7838,10 +7837,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="14" t="s">
+      <c r="J101" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="14" t="s">
+      <c r="K101" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -7870,10 +7869,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="14" t="s">
+      <c r="J102" s="13" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="14" t="s">
+      <c r="K102" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -7902,10 +7901,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="14" t="s">
+      <c r="J103" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="14" t="s">
+      <c r="K103" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -7934,10 +7933,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="14" t="s">
+      <c r="J104" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="14" t="s">
+      <c r="K104" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -7966,10 +7965,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="14" t="s">
+      <c r="J105" s="13" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="14" t="s">
+      <c r="K105" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -7998,10 +7997,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="14" t="s">
+      <c r="J106" s="13" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="14" t="s">
+      <c r="K106" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -8030,10 +8029,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="14" t="s">
+      <c r="J107" s="13" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="14" t="s">
+      <c r="K107" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -8062,10 +8061,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="14" t="s">
+      <c r="J108" s="13" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="14" t="s">
+      <c r="K108" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -8094,10 +8093,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="14" t="s">
+      <c r="J109" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="14" t="s">
+      <c r="K109" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -8126,10 +8125,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="14" t="s">
+      <c r="J110" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="14" t="s">
+      <c r="K110" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -8158,10 +8157,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="14" t="s">
+      <c r="J111" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="14" t="s">
+      <c r="K111" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -8190,10 +8189,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="14" t="s">
+      <c r="J112" s="13" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="14" t="s">
+      <c r="K112" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -8222,10 +8221,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="14" t="s">
+      <c r="J113" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="14" t="s">
+      <c r="K113" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -8254,10 +8253,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="14" t="s">
+      <c r="J114" s="13" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="14" t="s">
+      <c r="K114" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -8286,10 +8285,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="14" t="s">
+      <c r="J115" s="13" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="14" t="s">
+      <c r="K115" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -8318,10 +8317,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="14" t="s">
+      <c r="J116" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="14" t="s">
+      <c r="K116" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -8350,10 +8349,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="14" t="s">
+      <c r="J117" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="14" t="s">
+      <c r="K117" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -8382,10 +8381,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="14" t="s">
+      <c r="J118" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="14" t="s">
+      <c r="K118" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -8414,10 +8413,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="14" t="s">
+      <c r="J119" s="13" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="14" t="s">
+      <c r="K119" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -8446,10 +8445,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="14" t="s">
+      <c r="J120" s="13" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="14" t="s">
+      <c r="K120" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -8478,10 +8477,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="14" t="s">
+      <c r="J121" s="13" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="14" t="s">
+      <c r="K121" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -8510,10 +8509,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="14" t="s">
+      <c r="J122" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="14" t="s">
+      <c r="K122" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -8542,10 +8541,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="14" t="s">
+      <c r="J123" s="13" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="14" t="s">
+      <c r="K123" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -8574,10 +8573,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="14" t="s">
+      <c r="J124" s="13" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="14" t="s">
+      <c r="K124" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -8606,10 +8605,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="14" t="s">
+      <c r="J125" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="14" t="s">
+      <c r="K125" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -8638,10 +8637,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="14" t="s">
+      <c r="J126" s="13" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="14" t="s">
+      <c r="K126" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -8670,10 +8669,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="14" t="s">
+      <c r="J127" s="13" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="14" t="s">
+      <c r="K127" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -8702,10 +8701,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="14" t="s">
+      <c r="J128" s="13" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="14" t="s">
+      <c r="K128" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -8734,10 +8733,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="14" t="s">
+      <c r="J129" s="13" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="14" t="s">
+      <c r="K129" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -8766,10 +8765,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="14" t="s">
+      <c r="J130" s="13" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="14" t="s">
+      <c r="K130" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -8798,10 +8797,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="14" t="s">
+      <c r="J131" s="13" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="14" t="s">
+      <c r="K131" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -8830,10 +8829,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="14" t="s">
+      <c r="J132" s="13" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="14" t="s">
+      <c r="K132" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -8862,10 +8861,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="14" t="s">
+      <c r="J133" s="13" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="14" t="s">
+      <c r="K133" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -8894,10 +8893,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="14" t="s">
+      <c r="J134" s="13" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="14" t="s">
+      <c r="K134" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -8926,10 +8925,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="14" t="s">
+      <c r="J135" s="13" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="14" t="s">
+      <c r="K135" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -8958,10 +8957,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="14" t="s">
+      <c r="J136" s="13" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="14" t="s">
+      <c r="K136" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -8990,10 +8989,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="14" t="s">
+      <c r="J137" s="13" t="s">
         <v>782</v>
       </c>
-      <c r="K137" s="14" t="s">
+      <c r="K137" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -9022,10 +9021,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="14" t="s">
+      <c r="J138" s="13" t="s">
         <v>788</v>
       </c>
-      <c r="K138" s="14" t="s">
+      <c r="K138" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -9054,10 +9053,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="14" t="s">
+      <c r="J139" s="13" t="s">
         <v>794</v>
       </c>
-      <c r="K139" s="14" t="s">
+      <c r="K139" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -9086,10 +9085,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="14" t="s">
+      <c r="J140" s="13" t="s">
         <v>800</v>
       </c>
-      <c r="K140" s="14" t="s">
+      <c r="K140" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -9118,10 +9117,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="14" t="s">
+      <c r="J141" s="13" t="s">
         <v>806</v>
       </c>
-      <c r="K141" s="14" t="s">
+      <c r="K141" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -9150,10 +9149,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="14" t="s">
+      <c r="J142" s="13" t="s">
         <v>812</v>
       </c>
-      <c r="K142" s="14" t="s">
+      <c r="K142" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -9182,10 +9181,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="14" t="s">
+      <c r="J143" s="13" t="s">
         <v>818</v>
       </c>
-      <c r="K143" s="14" t="s">
+      <c r="K143" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -9214,10 +9213,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="14" t="s">
+      <c r="J144" s="13" t="s">
         <v>824</v>
       </c>
-      <c r="K144" s="14" t="s">
+      <c r="K144" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -9246,10 +9245,10 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="14" t="s">
+      <c r="J145" s="13" t="s">
         <v>830</v>
       </c>
-      <c r="K145" s="14" t="s">
+      <c r="K145" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
@@ -9278,13 +9277,13 @@
       <c r="I146" s="3">
         <v>0</v>
       </c>
-      <c r="J146" s="15" t="s">
+      <c r="J146" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K146" s="15" t="s">
+      <c r="K146" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L146" s="15" t="s">
+      <c r="L146" s="14" t="s">
         <v>837</v>
       </c>
     </row>
@@ -9310,13 +9309,13 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="14" t="s">
+      <c r="J147" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K147" s="14" t="s">
+      <c r="K147" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L147" s="13" t="s">
+      <c r="L147" s="12" t="s">
         <v>842</v>
       </c>
     </row>
@@ -9342,13 +9341,13 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="14" t="s">
+      <c r="J148" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K148" s="14" t="s">
+      <c r="K148" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L148" s="13" t="s">
+      <c r="L148" s="12" t="s">
         <v>847</v>
       </c>
     </row>
@@ -9374,13 +9373,13 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="14" t="s">
+      <c r="J149" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K149" s="14" t="s">
+      <c r="K149" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L149" s="13" t="s">
+      <c r="L149" s="12" t="s">
         <v>852</v>
       </c>
     </row>
@@ -9406,13 +9405,13 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="14" t="s">
+      <c r="J150" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K150" s="14" t="s">
+      <c r="K150" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L150" s="13" t="s">
+      <c r="L150" s="12" t="s">
         <v>857</v>
       </c>
     </row>
@@ -9438,13 +9437,13 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="14" t="s">
+      <c r="J151" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K151" s="14" t="s">
+      <c r="K151" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L151" s="13" t="s">
+      <c r="L151" s="12" t="s">
         <v>863</v>
       </c>
     </row>
@@ -9470,13 +9469,13 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="14" t="s">
+      <c r="J152" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K152" s="14" t="s">
+      <c r="K152" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L152" s="13" t="s">
+      <c r="L152" s="12" t="s">
         <v>868</v>
       </c>
     </row>
@@ -9502,13 +9501,13 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="14" t="s">
+      <c r="J153" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K153" s="14" t="s">
+      <c r="K153" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L153" s="13" t="s">
+      <c r="L153" s="12" t="s">
         <v>873</v>
       </c>
     </row>
@@ -9534,13 +9533,13 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="14" t="s">
+      <c r="J154" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K154" s="14" t="s">
+      <c r="K154" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L154" s="13" t="s">
+      <c r="L154" s="12" t="s">
         <v>878</v>
       </c>
     </row>
@@ -9566,13 +9565,13 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="14" t="s">
+      <c r="J155" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K155" s="14" t="s">
+      <c r="K155" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L155" s="13" t="s">
+      <c r="L155" s="12" t="s">
         <v>883</v>
       </c>
     </row>
@@ -9598,13 +9597,13 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="14" t="s">
+      <c r="J156" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K156" s="14" t="s">
+      <c r="K156" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L156" s="13" t="s">
+      <c r="L156" s="12" t="s">
         <v>889</v>
       </c>
     </row>
@@ -9630,13 +9629,13 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="14" t="s">
+      <c r="J157" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K157" s="14" t="s">
+      <c r="K157" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L157" s="13" t="s">
+      <c r="L157" s="12" t="s">
         <v>894</v>
       </c>
     </row>
@@ -9662,13 +9661,13 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="14" t="s">
+      <c r="J158" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="14" t="s">
+      <c r="K158" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L158" s="13" t="s">
+      <c r="L158" s="12" t="s">
         <v>899</v>
       </c>
     </row>
@@ -9694,13 +9693,13 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="14" t="s">
+      <c r="J159" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K159" s="14" t="s">
+      <c r="K159" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L159" s="13" t="s">
+      <c r="L159" s="12" t="s">
         <v>904</v>
       </c>
     </row>
@@ -9726,13 +9725,13 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="14" t="s">
+      <c r="J160" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K160" s="14" t="s">
+      <c r="K160" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L160" s="13" t="s">
+      <c r="L160" s="12" t="s">
         <v>909</v>
       </c>
     </row>
@@ -9758,13 +9757,13 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="14" t="s">
+      <c r="J161" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K161" s="14" t="s">
+      <c r="K161" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L161" s="13" t="s">
+      <c r="L161" s="12" t="s">
         <v>915</v>
       </c>
     </row>
@@ -9790,13 +9789,13 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="14" t="s">
+      <c r="J162" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K162" s="14" t="s">
+      <c r="K162" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L162" s="13" t="s">
+      <c r="L162" s="12" t="s">
         <v>920</v>
       </c>
     </row>
@@ -9822,13 +9821,13 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="14" t="s">
+      <c r="J163" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K163" s="14" t="s">
+      <c r="K163" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L163" s="13" t="s">
+      <c r="L163" s="12" t="s">
         <v>925</v>
       </c>
     </row>
@@ -9854,13 +9853,13 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="14" t="s">
+      <c r="J164" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K164" s="14" t="s">
+      <c r="K164" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L164" s="13" t="s">
+      <c r="L164" s="12" t="s">
         <v>930</v>
       </c>
     </row>
@@ -9886,13 +9885,13 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="14" t="s">
+      <c r="J165" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K165" s="14" t="s">
+      <c r="K165" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L165" s="13" t="s">
+      <c r="L165" s="12" t="s">
         <v>935</v>
       </c>
     </row>
@@ -9918,13 +9917,13 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="14" t="s">
+      <c r="J166" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K166" s="14" t="s">
+      <c r="K166" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L166" s="13" t="s">
+      <c r="L166" s="12" t="s">
         <v>941</v>
       </c>
     </row>
@@ -9950,13 +9949,13 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="14" t="s">
+      <c r="J167" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K167" s="14" t="s">
+      <c r="K167" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L167" s="13" t="s">
+      <c r="L167" s="12" t="s">
         <v>946</v>
       </c>
     </row>
@@ -9982,13 +9981,13 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="14" t="s">
+      <c r="J168" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K168" s="14" t="s">
+      <c r="K168" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L168" s="13" t="s">
+      <c r="L168" s="12" t="s">
         <v>951</v>
       </c>
     </row>
@@ -10014,13 +10013,13 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="14" t="s">
+      <c r="J169" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K169" s="14" t="s">
+      <c r="K169" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L169" s="13" t="s">
+      <c r="L169" s="12" t="s">
         <v>956</v>
       </c>
     </row>
@@ -10046,13 +10045,13 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="14" t="s">
+      <c r="J170" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="14" t="s">
+      <c r="K170" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L170" s="13" t="s">
+      <c r="L170" s="12" t="s">
         <v>961</v>
       </c>
     </row>
@@ -10078,13 +10077,13 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="14" t="s">
+      <c r="J171" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K171" s="14" t="s">
+      <c r="K171" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L171" s="13" t="s">
+      <c r="L171" s="12" t="s">
         <v>967</v>
       </c>
     </row>
@@ -10110,13 +10109,13 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="14" t="s">
+      <c r="J172" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K172" s="14" t="s">
+      <c r="K172" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L172" s="13" t="s">
+      <c r="L172" s="12" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10142,13 +10141,13 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="14" t="s">
+      <c r="J173" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K173" s="14" t="s">
+      <c r="K173" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L173" s="13" t="s">
+      <c r="L173" s="12" t="s">
         <v>977</v>
       </c>
     </row>
@@ -10174,13 +10173,13 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="14" t="s">
+      <c r="J174" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K174" s="14" t="s">
+      <c r="K174" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L174" s="13" t="s">
+      <c r="L174" s="12" t="s">
         <v>982</v>
       </c>
     </row>
@@ -10206,13 +10205,13 @@
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="14" t="s">
+      <c r="J175" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K175" s="14" t="s">
+      <c r="K175" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L175" s="13" t="s">
+      <c r="L175" s="12" t="s">
         <v>987</v>
       </c>
     </row>
@@ -10238,13 +10237,13 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="14" t="s">
+      <c r="J176" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K176" s="14" t="s">
+      <c r="K176" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L176" s="13" t="s">
+      <c r="L176" s="12" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10270,13 +10269,13 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="14" t="s">
+      <c r="J177" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K177" s="14" t="s">
+      <c r="K177" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L177" s="13" t="s">
+      <c r="L177" s="12" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10302,13 +10301,13 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="14" t="s">
+      <c r="J178" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K178" s="14" t="s">
+      <c r="K178" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L178" s="13" t="s">
+      <c r="L178" s="12" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -10334,13 +10333,13 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="14" t="s">
+      <c r="J179" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K179" s="14" t="s">
+      <c r="K179" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L179" s="13" t="s">
+      <c r="L179" s="12" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -10366,13 +10365,13 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="14" t="s">
+      <c r="J180" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K180" s="14" t="s">
+      <c r="K180" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L180" s="13" t="s">
+      <c r="L180" s="12" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -10398,13 +10397,13 @@
       <c r="I181" s="3">
         <v>0</v>
       </c>
-      <c r="J181" s="15" t="s">
+      <c r="J181" s="14" t="s">
         <v>1019</v>
       </c>
-      <c r="K181" s="15" t="s">
+      <c r="K181" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L181" s="13" t="s">
+      <c r="L181" s="12" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -10430,13 +10429,13 @@
       <c r="I182" s="1">
         <v>0</v>
       </c>
-      <c r="J182" s="14" t="s">
+      <c r="J182" s="13" t="s">
         <v>1026</v>
       </c>
-      <c r="K182" s="14" t="s">
+      <c r="K182" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L182" s="13" t="s">
+      <c r="L182" s="12" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -10462,13 +10461,13 @@
       <c r="I183" s="1">
         <v>0</v>
       </c>
-      <c r="J183" s="14" t="s">
+      <c r="J183" s="13" t="s">
         <v>1032</v>
       </c>
-      <c r="K183" s="14" t="s">
+      <c r="K183" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L183" s="13" t="s">
+      <c r="L183" s="12" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10494,13 +10493,13 @@
       <c r="I184" s="1">
         <v>0</v>
       </c>
-      <c r="J184" s="14" t="s">
+      <c r="J184" s="13" t="s">
         <v>1038</v>
       </c>
-      <c r="K184" s="14" t="s">
+      <c r="K184" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L184" s="13" t="s">
+      <c r="L184" s="12" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10526,13 +10525,13 @@
       <c r="I185" s="1">
         <v>0</v>
       </c>
-      <c r="J185" s="14" t="s">
+      <c r="J185" s="13" t="s">
         <v>1044</v>
       </c>
-      <c r="K185" s="14" t="s">
+      <c r="K185" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L185" s="13" t="s">
+      <c r="L185" s="12" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -10558,13 +10557,13 @@
       <c r="I186" s="1">
         <v>0</v>
       </c>
-      <c r="J186" s="14" t="s">
+      <c r="J186" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K186" s="14" t="s">
+      <c r="K186" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L186" s="13" t="s">
+      <c r="L186" s="12" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -10590,13 +10589,13 @@
       <c r="I187" s="1">
         <v>0</v>
       </c>
-      <c r="J187" s="14" t="s">
+      <c r="J187" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K187" s="14" t="s">
+      <c r="K187" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L187" s="13" t="s">
+      <c r="L187" s="12" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -10622,13 +10621,13 @@
       <c r="I188" s="1">
         <v>0</v>
       </c>
-      <c r="J188" s="14" t="s">
+      <c r="J188" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K188" s="14" t="s">
+      <c r="K188" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L188" s="13" t="s">
+      <c r="L188" s="12" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -10654,13 +10653,13 @@
       <c r="I189" s="1">
         <v>0</v>
       </c>
-      <c r="J189" s="14" t="s">
+      <c r="J189" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K189" s="14" t="s">
+      <c r="K189" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L189" s="13" t="s">
+      <c r="L189" s="12" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -10686,13 +10685,13 @@
       <c r="I190" s="1">
         <v>0</v>
       </c>
-      <c r="J190" s="14" t="s">
+      <c r="J190" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K190" s="14" t="s">
+      <c r="K190" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L190" s="13" t="s">
+      <c r="L190" s="12" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -10718,13 +10717,13 @@
       <c r="I191" s="1">
         <v>0</v>
       </c>
-      <c r="J191" s="14" t="s">
+      <c r="J191" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K191" s="14" t="s">
+      <c r="K191" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L191" s="13" t="s">
+      <c r="L191" s="12" t="s">
         <v>1077</v>
       </c>
     </row>
@@ -10750,13 +10749,13 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-      <c r="J192" s="14" t="s">
+      <c r="J192" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K192" s="14" t="s">
+      <c r="K192" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L192" s="13" t="s">
+      <c r="L192" s="12" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -10782,13 +10781,13 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-      <c r="J193" s="14" t="s">
+      <c r="J193" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K193" s="14" t="s">
+      <c r="K193" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L193" s="13" t="s">
+      <c r="L193" s="12" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -10814,13 +10813,13 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-      <c r="J194" s="14" t="s">
+      <c r="J194" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K194" s="14" t="s">
+      <c r="K194" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L194" s="13" t="s">
+      <c r="L194" s="12" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -10846,13 +10845,13 @@
       <c r="I195" s="1">
         <v>0</v>
       </c>
-      <c r="J195" s="14" t="s">
+      <c r="J195" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K195" s="14" t="s">
+      <c r="K195" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L195" s="13" t="s">
+      <c r="L195" s="12" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -10878,13 +10877,13 @@
       <c r="I196" s="4">
         <v>0</v>
       </c>
-      <c r="J196" s="16" t="s">
+      <c r="J196" s="15" t="s">
         <v>1102</v>
       </c>
-      <c r="K196" s="16" t="s">
+      <c r="K196" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L196" s="16" t="s">
+      <c r="L196" s="15" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -10910,13 +10909,13 @@
       <c r="I197" s="1">
         <v>0</v>
       </c>
-      <c r="J197" s="14" t="s">
+      <c r="J197" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K197" s="14" t="s">
+      <c r="K197" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L197" s="13" t="s">
+      <c r="L197" s="12" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -10942,13 +10941,13 @@
       <c r="I198" s="1">
         <v>0</v>
       </c>
-      <c r="J198" s="14" t="s">
+      <c r="J198" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K198" s="14" t="s">
+      <c r="K198" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L198" s="13" t="s">
+      <c r="L198" s="12" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -10974,13 +10973,13 @@
       <c r="I199" s="1">
         <v>0</v>
       </c>
-      <c r="J199" s="14" t="s">
+      <c r="J199" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K199" s="14" t="s">
+      <c r="K199" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L199" s="13" t="s">
+      <c r="L199" s="12" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -11006,13 +11005,13 @@
       <c r="I200" s="1">
         <v>0</v>
       </c>
-      <c r="J200" s="14" t="s">
+      <c r="J200" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K200" s="14" t="s">
+      <c r="K200" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L200" s="13" t="s">
+      <c r="L200" s="12" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -11038,13 +11037,13 @@
       <c r="I201" s="1">
         <v>0</v>
       </c>
-      <c r="J201" s="14" t="s">
+      <c r="J201" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K201" s="14" t="s">
+      <c r="K201" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L201" s="13" t="s">
+      <c r="L201" s="12" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -11070,13 +11069,13 @@
       <c r="I202" s="1">
         <v>0</v>
       </c>
-      <c r="J202" s="14" t="s">
+      <c r="J202" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K202" s="14" t="s">
+      <c r="K202" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L202" s="13" t="s">
+      <c r="L202" s="12" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -11102,13 +11101,13 @@
       <c r="I203" s="1">
         <v>0</v>
       </c>
-      <c r="J203" s="14" t="s">
+      <c r="J203" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K203" s="14" t="s">
+      <c r="K203" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L203" s="13" t="s">
+      <c r="L203" s="12" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -11134,13 +11133,13 @@
       <c r="I204" s="1">
         <v>0</v>
       </c>
-      <c r="J204" s="14" t="s">
+      <c r="J204" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K204" s="14" t="s">
+      <c r="K204" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L204" s="13" t="s">
+      <c r="L204" s="12" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -11166,13 +11165,13 @@
       <c r="I205" s="1">
         <v>0</v>
       </c>
-      <c r="J205" s="14" t="s">
+      <c r="J205" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K205" s="14" t="s">
+      <c r="K205" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L205" s="13" t="s">
+      <c r="L205" s="12" t="s">
         <v>1149</v>
       </c>
     </row>
@@ -11198,13 +11197,13 @@
       <c r="I206" s="1">
         <v>0</v>
       </c>
-      <c r="J206" s="14" t="s">
+      <c r="J206" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K206" s="14" t="s">
+      <c r="K206" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L206" s="13" t="s">
+      <c r="L206" s="12" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -11230,13 +11229,13 @@
       <c r="I207" s="1">
         <v>0</v>
       </c>
-      <c r="J207" s="14" t="s">
+      <c r="J207" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K207" s="14" t="s">
+      <c r="K207" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L207" s="13" t="s">
+      <c r="L207" s="12" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -11262,13 +11261,13 @@
       <c r="I208" s="1">
         <v>0</v>
       </c>
-      <c r="J208" s="14" t="s">
+      <c r="J208" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K208" s="14" t="s">
+      <c r="K208" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L208" s="13" t="s">
+      <c r="L208" s="12" t="s">
         <v>1165</v>
       </c>
     </row>
@@ -11294,13 +11293,13 @@
       <c r="I209" s="1">
         <v>0</v>
       </c>
-      <c r="J209" s="14" t="s">
+      <c r="J209" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K209" s="14" t="s">
+      <c r="K209" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L209" s="13" t="s">
+      <c r="L209" s="12" t="s">
         <v>1170</v>
       </c>
     </row>
@@ -11326,13 +11325,13 @@
       <c r="I210" s="1">
         <v>0</v>
       </c>
-      <c r="J210" s="14" t="s">
+      <c r="J210" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K210" s="14" t="s">
+      <c r="K210" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L210" s="13" t="s">
+      <c r="L210" s="12" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -11358,13 +11357,13 @@
       <c r="I211" s="1">
         <v>0</v>
       </c>
-      <c r="J211" s="14" t="s">
+      <c r="J211" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K211" s="14" t="s">
+      <c r="K211" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L211" s="13" t="s">
+      <c r="L211" s="12" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -11390,13 +11389,13 @@
       <c r="I212" s="1">
         <v>0</v>
       </c>
-      <c r="J212" s="14" t="s">
+      <c r="J212" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K212" s="14" t="s">
+      <c r="K212" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L212" s="13" t="s">
+      <c r="L212" s="12" t="s">
         <v>1186</v>
       </c>
     </row>
@@ -11422,19 +11421,19 @@
       <c r="I213" s="1">
         <v>0</v>
       </c>
-      <c r="J213" s="14" t="s">
+      <c r="J213" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K213" s="14" t="s">
+      <c r="K213" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L213" s="13" t="s">
+      <c r="L213" s="12" t="s">
         <v>1191</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A214" s="10"/>
-      <c r="B214" s="10"/>
+      <c r="A214" s="2"/>
+      <c r="B214" s="2"/>
       <c r="C214" s="1" t="s">
         <v>1192</v>
       </c>
@@ -11456,19 +11455,19 @@
       <c r="I214" s="1">
         <v>0</v>
       </c>
-      <c r="J214" s="14" t="s">
+      <c r="J214" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K214" s="14" t="s">
+      <c r="K214" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L214" s="13" t="s">
+      <c r="L214" s="12" t="s">
         <v>1196</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A215" s="10"/>
-      <c r="B215" s="10"/>
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
       <c r="C215" s="1" t="s">
         <v>1197</v>
       </c>
@@ -11490,19 +11489,19 @@
       <c r="I215" s="1">
         <v>0</v>
       </c>
-      <c r="J215" s="14" t="s">
+      <c r="J215" s="13" t="s">
         <v>1201</v>
       </c>
-      <c r="K215" s="14" t="s">
+      <c r="K215" s="13" t="s">
         <v>1202</v>
       </c>
-      <c r="L215" s="13" t="s">
+      <c r="L215" s="12" t="s">
         <v>1203</v>
       </c>
     </row>
     <row r="216" s="3" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A216" s="11"/>
-      <c r="B216" s="11"/>
+      <c r="A216" s="2"/>
+      <c r="B216" s="2"/>
       <c r="C216" s="1">
         <v>1210</v>
       </c>
@@ -11515,7 +11514,7 @@
       <c r="F216" s="3">
         <v>5</v>
       </c>
-      <c r="G216" s="12" t="s">
+      <c r="G216" s="10" t="s">
         <v>1205</v>
       </c>
       <c r="H216" s="3" t="s">
@@ -11524,13 +11523,13 @@
       <c r="I216" s="3">
         <v>0</v>
       </c>
-      <c r="J216" s="15" t="s">
+      <c r="J216" s="14" t="s">
         <v>1207</v>
       </c>
-      <c r="K216" s="15" t="s">
+      <c r="K216" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L216" s="13" t="s">
+      <c r="L216" s="12" t="s">
         <v>1209</v>
       </c>
       <c r="M216" s="3" t="s">
@@ -11538,8 +11537,8 @@
       </c>
     </row>
     <row r="217" customHeight="1" spans="1:13">
-      <c r="A217" s="11"/>
-      <c r="B217" s="11"/>
+      <c r="A217" s="2"/>
+      <c r="B217" s="2"/>
       <c r="C217" s="1">
         <v>1211</v>
       </c>
@@ -11561,19 +11560,19 @@
       <c r="I217" s="1">
         <v>0</v>
       </c>
-      <c r="J217" s="14" t="s">
+      <c r="J217" s="13" t="s">
         <v>1214</v>
       </c>
-      <c r="K217" s="17" t="s">
+      <c r="K217" s="16" t="s">
         <v>1208</v>
       </c>
-      <c r="L217" s="13" t="s">
+      <c r="L217" s="12" t="s">
         <v>1215</v>
       </c>
     </row>
     <row r="218" customHeight="1" spans="1:13">
-      <c r="A218" s="11"/>
-      <c r="B218" s="11"/>
+      <c r="A218" s="2"/>
+      <c r="B218" s="2"/>
       <c r="C218" s="1">
         <v>1212</v>
       </c>
@@ -11595,19 +11594,19 @@
       <c r="I218" s="1">
         <v>0</v>
       </c>
-      <c r="J218" s="14" t="s">
+      <c r="J218" s="13" t="s">
         <v>1219</v>
       </c>
-      <c r="K218" s="17" t="s">
+      <c r="K218" s="16" t="s">
         <v>1208</v>
       </c>
-      <c r="L218" s="13" t="s">
+      <c r="L218" s="12" t="s">
         <v>1220</v>
       </c>
     </row>
     <row r="219" customHeight="1" spans="1:13">
-      <c r="A219" s="11"/>
-      <c r="B219" s="11"/>
+      <c r="A219" s="2"/>
+      <c r="B219" s="2"/>
       <c r="C219" s="1">
         <v>1213</v>
       </c>
@@ -11629,19 +11628,19 @@
       <c r="I219" s="1">
         <v>0</v>
       </c>
-      <c r="J219" s="14" t="s">
+      <c r="J219" s="13" t="s">
         <v>1224</v>
       </c>
-      <c r="K219" s="17" t="s">
+      <c r="K219" s="16" t="s">
         <v>1208</v>
       </c>
-      <c r="L219" s="13" t="s">
+      <c r="L219" s="12" t="s">
         <v>1225</v>
       </c>
     </row>
     <row r="220" customHeight="1" spans="1:13">
-      <c r="A220" s="11"/>
-      <c r="B220" s="11"/>
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
       <c r="C220" s="1">
         <v>1214</v>
       </c>
@@ -11663,19 +11662,19 @@
       <c r="I220" s="1">
         <v>0</v>
       </c>
-      <c r="J220" s="14" t="s">
+      <c r="J220" s="13" t="s">
         <v>1229</v>
       </c>
-      <c r="K220" s="17" t="s">
+      <c r="K220" s="16" t="s">
         <v>1208</v>
       </c>
-      <c r="L220" s="13" t="s">
+      <c r="L220" s="12" t="s">
         <v>1230</v>
       </c>
     </row>
     <row r="221" customHeight="1" spans="1:13">
-      <c r="A221" s="10"/>
-      <c r="B221" s="10"/>
+      <c r="A221" s="2"/>
+      <c r="B221" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C216:C220">

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -3930,12 +3930,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4401,7 +4401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4417,12 +4417,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6096,10 +6094,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="12" t="s">
+      <c r="J46" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="12" t="s">
+      <c r="K46" s="11" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -6125,10 +6123,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="12" t="s">
+      <c r="J47" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="12" t="s">
+      <c r="K47" s="11" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -6154,10 +6152,10 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="12" t="s">
+      <c r="J48" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="12" t="s">
+      <c r="K48" s="11" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
@@ -6183,10 +6181,10 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="12" t="s">
+      <c r="J49" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="12" t="s">
+      <c r="K49" s="11" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
@@ -6212,10 +6210,10 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="12" t="s">
+      <c r="J50" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="12" t="s">
+      <c r="K50" s="11" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
@@ -6244,10 +6242,10 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="12" t="s">
+      <c r="J51" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="12" t="s">
+      <c r="K51" s="11" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
@@ -6273,10 +6271,10 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="12" t="s">
+      <c r="J52" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="12" t="s">
+      <c r="K52" s="11" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -6302,10 +6300,10 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="12" t="s">
+      <c r="J53" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="12" t="s">
+      <c r="K53" s="11" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
@@ -6331,10 +6329,10 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="12" t="s">
+      <c r="J54" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="12" t="s">
+      <c r="K54" s="11" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
@@ -6360,10 +6358,10 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="12" t="s">
+      <c r="J55" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="12" t="s">
+      <c r="K55" s="11" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -6392,10 +6390,10 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="12" t="s">
+      <c r="J56" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="12" t="s">
+      <c r="K56" s="11" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
@@ -6424,10 +6422,10 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="12" t="s">
+      <c r="J57" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="12" t="s">
+      <c r="K57" s="11" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
@@ -6456,10 +6454,10 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="12" t="s">
+      <c r="J58" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="12" t="s">
+      <c r="K58" s="11" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -6488,10 +6486,10 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="12" t="s">
+      <c r="J59" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="12" t="s">
+      <c r="K59" s="11" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
@@ -6520,10 +6518,10 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="12" t="s">
+      <c r="J60" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="12" t="s">
+      <c r="K60" s="11" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -6553,10 +6551,10 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="13" t="s">
+      <c r="J61" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="13" t="s">
+      <c r="K61" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -6586,10 +6584,10 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="13" t="s">
+      <c r="J62" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="13" t="s">
+      <c r="K62" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -6619,10 +6617,10 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="13" t="s">
+      <c r="J63" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="13" t="s">
+      <c r="K63" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
@@ -6652,10 +6650,10 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="13" t="s">
+      <c r="J64" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="13" t="s">
+      <c r="K64" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
@@ -6685,10 +6683,10 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="13" t="s">
+      <c r="J65" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="13" t="s">
+      <c r="K65" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
@@ -6717,10 +6715,10 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="13" t="s">
+      <c r="J66" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="13" t="s">
+      <c r="K66" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
@@ -6749,10 +6747,10 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="13" t="s">
+      <c r="J67" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="13" t="s">
+      <c r="K67" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
@@ -6781,10 +6779,10 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="13" t="s">
+      <c r="J68" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="13" t="s">
+      <c r="K68" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -6813,10 +6811,10 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="13" t="s">
+      <c r="J69" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="13" t="s">
+      <c r="K69" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
@@ -6845,10 +6843,10 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="13" t="s">
+      <c r="J70" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="13" t="s">
+      <c r="K70" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
@@ -6877,10 +6875,10 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="13" t="s">
+      <c r="J71" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="13" t="s">
+      <c r="K71" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -6909,10 +6907,10 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="13" t="s">
+      <c r="J72" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="13" t="s">
+      <c r="K72" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -6941,10 +6939,10 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="13" t="s">
+      <c r="J73" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="13" t="s">
+      <c r="K73" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -6973,10 +6971,10 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="13" t="s">
+      <c r="J74" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="13" t="s">
+      <c r="K74" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
@@ -7005,10 +7003,10 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="13" t="s">
+      <c r="J75" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="13" t="s">
+      <c r="K75" s="12" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
@@ -7037,10 +7035,10 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="13" t="s">
+      <c r="J76" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="13" t="s">
+      <c r="K76" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
@@ -7069,10 +7067,10 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="13" t="s">
+      <c r="J77" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="13" t="s">
+      <c r="K77" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
@@ -7101,10 +7099,10 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="13" t="s">
+      <c r="J78" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="13" t="s">
+      <c r="K78" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
@@ -7133,10 +7131,10 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="13" t="s">
+      <c r="J79" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="13" t="s">
+      <c r="K79" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
@@ -7165,10 +7163,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="13" t="s">
+      <c r="J80" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="13" t="s">
+      <c r="K80" s="12" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -7197,10 +7195,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="13" t="s">
+      <c r="J81" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="13" t="s">
+      <c r="K81" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -7229,10 +7227,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="13" t="s">
+      <c r="J82" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="13" t="s">
+      <c r="K82" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -7261,10 +7259,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="13" t="s">
+      <c r="J83" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="13" t="s">
+      <c r="K83" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -7293,10 +7291,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="13" t="s">
+      <c r="J84" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="13" t="s">
+      <c r="K84" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -7325,10 +7323,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="13" t="s">
+      <c r="J85" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="13" t="s">
+      <c r="K85" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -7357,10 +7355,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="13" t="s">
+      <c r="J86" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="13" t="s">
+      <c r="K86" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -7389,10 +7387,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="13" t="s">
+      <c r="J87" s="12" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="13" t="s">
+      <c r="K87" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -7421,10 +7419,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="13" t="s">
+      <c r="J88" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="13" t="s">
+      <c r="K88" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -7453,10 +7451,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="13" t="s">
+      <c r="J89" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="13" t="s">
+      <c r="K89" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -7485,10 +7483,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="13" t="s">
+      <c r="J90" s="12" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="13" t="s">
+      <c r="K90" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -7517,10 +7515,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="13" t="s">
+      <c r="J91" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="13" t="s">
+      <c r="K91" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -7549,10 +7547,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="13" t="s">
+      <c r="J92" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="13" t="s">
+      <c r="K92" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -7581,10 +7579,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="13" t="s">
+      <c r="J93" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="13" t="s">
+      <c r="K93" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -7613,10 +7611,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="13" t="s">
+      <c r="J94" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="13" t="s">
+      <c r="K94" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -7645,10 +7643,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="13" t="s">
+      <c r="J95" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="13" t="s">
+      <c r="K95" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -7677,10 +7675,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="13" t="s">
+      <c r="J96" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="13" t="s">
+      <c r="K96" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -7709,10 +7707,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="13" t="s">
+      <c r="J97" s="12" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="13" t="s">
+      <c r="K97" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -7741,10 +7739,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="13" t="s">
+      <c r="J98" s="12" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="13" t="s">
+      <c r="K98" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -7773,10 +7771,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="13" t="s">
+      <c r="J99" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="13" t="s">
+      <c r="K99" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -7805,10 +7803,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="13" t="s">
+      <c r="J100" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="13" t="s">
+      <c r="K100" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -7837,10 +7835,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="13" t="s">
+      <c r="J101" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="13" t="s">
+      <c r="K101" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -7869,10 +7867,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="13" t="s">
+      <c r="J102" s="12" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="13" t="s">
+      <c r="K102" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -7901,10 +7899,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="13" t="s">
+      <c r="J103" s="12" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="13" t="s">
+      <c r="K103" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -7933,10 +7931,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="13" t="s">
+      <c r="J104" s="12" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="13" t="s">
+      <c r="K104" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -7965,10 +7963,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="13" t="s">
+      <c r="J105" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="13" t="s">
+      <c r="K105" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -7997,10 +7995,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="13" t="s">
+      <c r="J106" s="12" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="13" t="s">
+      <c r="K106" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -8029,10 +8027,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="13" t="s">
+      <c r="J107" s="12" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="13" t="s">
+      <c r="K107" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -8061,10 +8059,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="13" t="s">
+      <c r="J108" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="13" t="s">
+      <c r="K108" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -8093,10 +8091,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="13" t="s">
+      <c r="J109" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="13" t="s">
+      <c r="K109" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -8125,10 +8123,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="13" t="s">
+      <c r="J110" s="12" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="13" t="s">
+      <c r="K110" s="12" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -8157,10 +8155,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="13" t="s">
+      <c r="J111" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="13" t="s">
+      <c r="K111" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -8189,10 +8187,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="13" t="s">
+      <c r="J112" s="12" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="13" t="s">
+      <c r="K112" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -8221,10 +8219,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="13" t="s">
+      <c r="J113" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="13" t="s">
+      <c r="K113" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -8253,10 +8251,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="13" t="s">
+      <c r="J114" s="12" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="13" t="s">
+      <c r="K114" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -8285,10 +8283,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="13" t="s">
+      <c r="J115" s="12" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="13" t="s">
+      <c r="K115" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -8317,10 +8315,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="13" t="s">
+      <c r="J116" s="12" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="13" t="s">
+      <c r="K116" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -8349,10 +8347,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="13" t="s">
+      <c r="J117" s="12" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="13" t="s">
+      <c r="K117" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -8381,10 +8379,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="13" t="s">
+      <c r="J118" s="12" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="13" t="s">
+      <c r="K118" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -8413,10 +8411,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="13" t="s">
+      <c r="J119" s="12" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="13" t="s">
+      <c r="K119" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -8445,10 +8443,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="13" t="s">
+      <c r="J120" s="12" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="13" t="s">
+      <c r="K120" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -8477,10 +8475,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="13" t="s">
+      <c r="J121" s="12" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="13" t="s">
+      <c r="K121" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -8509,10 +8507,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="13" t="s">
+      <c r="J122" s="12" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="13" t="s">
+      <c r="K122" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -8541,10 +8539,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="13" t="s">
+      <c r="J123" s="12" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="13" t="s">
+      <c r="K123" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -8573,10 +8571,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="13" t="s">
+      <c r="J124" s="12" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="13" t="s">
+      <c r="K124" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -8605,10 +8603,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="13" t="s">
+      <c r="J125" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="13" t="s">
+      <c r="K125" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -8637,10 +8635,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="13" t="s">
+      <c r="J126" s="12" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="13" t="s">
+      <c r="K126" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -8669,10 +8667,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="13" t="s">
+      <c r="J127" s="12" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="13" t="s">
+      <c r="K127" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -8701,10 +8699,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="13" t="s">
+      <c r="J128" s="12" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="13" t="s">
+      <c r="K128" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -8733,10 +8731,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="13" t="s">
+      <c r="J129" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="13" t="s">
+      <c r="K129" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -8765,10 +8763,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="13" t="s">
+      <c r="J130" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="13" t="s">
+      <c r="K130" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -8797,10 +8795,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="13" t="s">
+      <c r="J131" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="13" t="s">
+      <c r="K131" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -8829,10 +8827,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="13" t="s">
+      <c r="J132" s="12" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="13" t="s">
+      <c r="K132" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -8861,10 +8859,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="13" t="s">
+      <c r="J133" s="12" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="13" t="s">
+      <c r="K133" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -8893,10 +8891,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="13" t="s">
+      <c r="J134" s="12" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="13" t="s">
+      <c r="K134" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -8925,10 +8923,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="13" t="s">
+      <c r="J135" s="12" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="13" t="s">
+      <c r="K135" s="12" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -8957,10 +8955,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="13" t="s">
+      <c r="J136" s="12" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="13" t="s">
+      <c r="K136" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -8989,10 +8987,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="13" t="s">
+      <c r="J137" s="12" t="s">
         <v>782</v>
       </c>
-      <c r="K137" s="13" t="s">
+      <c r="K137" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -9021,10 +9019,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="13" t="s">
+      <c r="J138" s="12" t="s">
         <v>788</v>
       </c>
-      <c r="K138" s="13" t="s">
+      <c r="K138" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -9053,10 +9051,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="13" t="s">
+      <c r="J139" s="12" t="s">
         <v>794</v>
       </c>
-      <c r="K139" s="13" t="s">
+      <c r="K139" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -9085,10 +9083,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="13" t="s">
+      <c r="J140" s="12" t="s">
         <v>800</v>
       </c>
-      <c r="K140" s="13" t="s">
+      <c r="K140" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -9117,10 +9115,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="13" t="s">
+      <c r="J141" s="12" t="s">
         <v>806</v>
       </c>
-      <c r="K141" s="13" t="s">
+      <c r="K141" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -9149,10 +9147,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="13" t="s">
+      <c r="J142" s="12" t="s">
         <v>812</v>
       </c>
-      <c r="K142" s="13" t="s">
+      <c r="K142" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -9181,10 +9179,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="13" t="s">
+      <c r="J143" s="12" t="s">
         <v>818</v>
       </c>
-      <c r="K143" s="13" t="s">
+      <c r="K143" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -9213,10 +9211,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="13" t="s">
+      <c r="J144" s="12" t="s">
         <v>824</v>
       </c>
-      <c r="K144" s="13" t="s">
+      <c r="K144" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -9245,10 +9243,10 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="13" t="s">
+      <c r="J145" s="12" t="s">
         <v>830</v>
       </c>
-      <c r="K145" s="13" t="s">
+      <c r="K145" s="12" t="s">
         <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
@@ -9277,13 +9275,13 @@
       <c r="I146" s="3">
         <v>0</v>
       </c>
-      <c r="J146" s="14" t="s">
+      <c r="J146" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K146" s="14" t="s">
+      <c r="K146" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L146" s="14" t="s">
+      <c r="L146" s="13" t="s">
         <v>837</v>
       </c>
     </row>
@@ -9309,13 +9307,13 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="13" t="s">
+      <c r="J147" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="K147" s="13" t="s">
+      <c r="K147" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L147" s="12" t="s">
+      <c r="L147" s="11" t="s">
         <v>842</v>
       </c>
     </row>
@@ -9341,13 +9339,13 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="13" t="s">
+      <c r="J148" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="K148" s="13" t="s">
+      <c r="K148" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L148" s="12" t="s">
+      <c r="L148" s="11" t="s">
         <v>847</v>
       </c>
     </row>
@@ -9373,13 +9371,13 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="13" t="s">
+      <c r="J149" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="K149" s="13" t="s">
+      <c r="K149" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L149" s="12" t="s">
+      <c r="L149" s="11" t="s">
         <v>852</v>
       </c>
     </row>
@@ -9405,13 +9403,13 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="13" t="s">
+      <c r="J150" s="12" t="s">
         <v>836</v>
       </c>
-      <c r="K150" s="13" t="s">
+      <c r="K150" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L150" s="12" t="s">
+      <c r="L150" s="11" t="s">
         <v>857</v>
       </c>
     </row>
@@ -9437,13 +9435,13 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="13" t="s">
+      <c r="J151" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="K151" s="13" t="s">
+      <c r="K151" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L151" s="12" t="s">
+      <c r="L151" s="11" t="s">
         <v>863</v>
       </c>
     </row>
@@ -9469,13 +9467,13 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="13" t="s">
+      <c r="J152" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="K152" s="13" t="s">
+      <c r="K152" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L152" s="12" t="s">
+      <c r="L152" s="11" t="s">
         <v>868</v>
       </c>
     </row>
@@ -9501,13 +9499,13 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="13" t="s">
+      <c r="J153" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="K153" s="13" t="s">
+      <c r="K153" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L153" s="12" t="s">
+      <c r="L153" s="11" t="s">
         <v>873</v>
       </c>
     </row>
@@ -9533,13 +9531,13 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="13" t="s">
+      <c r="J154" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="K154" s="13" t="s">
+      <c r="K154" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L154" s="12" t="s">
+      <c r="L154" s="11" t="s">
         <v>878</v>
       </c>
     </row>
@@ -9565,13 +9563,13 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="13" t="s">
+      <c r="J155" s="12" t="s">
         <v>862</v>
       </c>
-      <c r="K155" s="13" t="s">
+      <c r="K155" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L155" s="12" t="s">
+      <c r="L155" s="11" t="s">
         <v>883</v>
       </c>
     </row>
@@ -9597,13 +9595,13 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="13" t="s">
+      <c r="J156" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="K156" s="13" t="s">
+      <c r="K156" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L156" s="12" t="s">
+      <c r="L156" s="11" t="s">
         <v>889</v>
       </c>
     </row>
@@ -9629,13 +9627,13 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="13" t="s">
+      <c r="J157" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="K157" s="13" t="s">
+      <c r="K157" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L157" s="12" t="s">
+      <c r="L157" s="11" t="s">
         <v>894</v>
       </c>
     </row>
@@ -9661,13 +9659,13 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="13" t="s">
+      <c r="J158" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="13" t="s">
+      <c r="K158" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L158" s="12" t="s">
+      <c r="L158" s="11" t="s">
         <v>899</v>
       </c>
     </row>
@@ -9693,13 +9691,13 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="13" t="s">
+      <c r="J159" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="K159" s="13" t="s">
+      <c r="K159" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L159" s="12" t="s">
+      <c r="L159" s="11" t="s">
         <v>904</v>
       </c>
     </row>
@@ -9725,13 +9723,13 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="13" t="s">
+      <c r="J160" s="12" t="s">
         <v>888</v>
       </c>
-      <c r="K160" s="13" t="s">
+      <c r="K160" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L160" s="12" t="s">
+      <c r="L160" s="11" t="s">
         <v>909</v>
       </c>
     </row>
@@ -9757,13 +9755,13 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="13" t="s">
+      <c r="J161" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="K161" s="13" t="s">
+      <c r="K161" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L161" s="12" t="s">
+      <c r="L161" s="11" t="s">
         <v>915</v>
       </c>
     </row>
@@ -9789,13 +9787,13 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="13" t="s">
+      <c r="J162" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="K162" s="13" t="s">
+      <c r="K162" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L162" s="12" t="s">
+      <c r="L162" s="11" t="s">
         <v>920</v>
       </c>
     </row>
@@ -9821,13 +9819,13 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="13" t="s">
+      <c r="J163" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="K163" s="13" t="s">
+      <c r="K163" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L163" s="12" t="s">
+      <c r="L163" s="11" t="s">
         <v>925</v>
       </c>
     </row>
@@ -9853,13 +9851,13 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="13" t="s">
+      <c r="J164" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="K164" s="13" t="s">
+      <c r="K164" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L164" s="12" t="s">
+      <c r="L164" s="11" t="s">
         <v>930</v>
       </c>
     </row>
@@ -9885,13 +9883,13 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="13" t="s">
+      <c r="J165" s="12" t="s">
         <v>914</v>
       </c>
-      <c r="K165" s="13" t="s">
+      <c r="K165" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L165" s="12" t="s">
+      <c r="L165" s="11" t="s">
         <v>935</v>
       </c>
     </row>
@@ -9917,13 +9915,13 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="13" t="s">
+      <c r="J166" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="K166" s="13" t="s">
+      <c r="K166" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L166" s="12" t="s">
+      <c r="L166" s="11" t="s">
         <v>941</v>
       </c>
     </row>
@@ -9949,13 +9947,13 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="13" t="s">
+      <c r="J167" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="K167" s="13" t="s">
+      <c r="K167" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L167" s="12" t="s">
+      <c r="L167" s="11" t="s">
         <v>946</v>
       </c>
     </row>
@@ -9981,13 +9979,13 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="13" t="s">
+      <c r="J168" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="K168" s="13" t="s">
+      <c r="K168" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L168" s="12" t="s">
+      <c r="L168" s="11" t="s">
         <v>951</v>
       </c>
     </row>
@@ -10013,13 +10011,13 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="13" t="s">
+      <c r="J169" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="K169" s="13" t="s">
+      <c r="K169" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L169" s="12" t="s">
+      <c r="L169" s="11" t="s">
         <v>956</v>
       </c>
     </row>
@@ -10045,13 +10043,13 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="13" t="s">
+      <c r="J170" s="12" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="13" t="s">
+      <c r="K170" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L170" s="12" t="s">
+      <c r="L170" s="11" t="s">
         <v>961</v>
       </c>
     </row>
@@ -10077,13 +10075,13 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="13" t="s">
+      <c r="J171" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="K171" s="13" t="s">
+      <c r="K171" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L171" s="12" t="s">
+      <c r="L171" s="11" t="s">
         <v>967</v>
       </c>
     </row>
@@ -10109,13 +10107,13 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="13" t="s">
+      <c r="J172" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="K172" s="13" t="s">
+      <c r="K172" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L172" s="12" t="s">
+      <c r="L172" s="11" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10141,13 +10139,13 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="13" t="s">
+      <c r="J173" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="K173" s="13" t="s">
+      <c r="K173" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L173" s="12" t="s">
+      <c r="L173" s="11" t="s">
         <v>977</v>
       </c>
     </row>
@@ -10173,13 +10171,13 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="13" t="s">
+      <c r="J174" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="K174" s="13" t="s">
+      <c r="K174" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L174" s="12" t="s">
+      <c r="L174" s="11" t="s">
         <v>982</v>
       </c>
     </row>
@@ -10205,13 +10203,13 @@
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="13" t="s">
+      <c r="J175" s="12" t="s">
         <v>966</v>
       </c>
-      <c r="K175" s="13" t="s">
+      <c r="K175" s="12" t="s">
         <v>776</v>
       </c>
-      <c r="L175" s="12" t="s">
+      <c r="L175" s="11" t="s">
         <v>987</v>
       </c>
     </row>
@@ -10237,13 +10235,13 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="13" t="s">
+      <c r="J176" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="K176" s="13" t="s">
+      <c r="K176" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="L176" s="12" t="s">
+      <c r="L176" s="11" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10269,13 +10267,13 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="13" t="s">
+      <c r="J177" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="K177" s="13" t="s">
+      <c r="K177" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="L177" s="12" t="s">
+      <c r="L177" s="11" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10301,13 +10299,13 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="13" t="s">
+      <c r="J178" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="K178" s="13" t="s">
+      <c r="K178" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="L178" s="12" t="s">
+      <c r="L178" s="11" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -10333,13 +10331,13 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="13" t="s">
+      <c r="J179" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="K179" s="13" t="s">
+      <c r="K179" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="L179" s="12" t="s">
+      <c r="L179" s="11" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -10365,13 +10363,13 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="13" t="s">
+      <c r="J180" s="12" t="s">
         <v>992</v>
       </c>
-      <c r="K180" s="13" t="s">
+      <c r="K180" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="L180" s="12" t="s">
+      <c r="L180" s="11" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -10397,13 +10395,13 @@
       <c r="I181" s="3">
         <v>0</v>
       </c>
-      <c r="J181" s="14" t="s">
+      <c r="J181" s="13" t="s">
         <v>1019</v>
       </c>
-      <c r="K181" s="14" t="s">
+      <c r="K181" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L181" s="12" t="s">
+      <c r="L181" s="11" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -10429,13 +10427,13 @@
       <c r="I182" s="1">
         <v>0</v>
       </c>
-      <c r="J182" s="13" t="s">
+      <c r="J182" s="12" t="s">
         <v>1026</v>
       </c>
-      <c r="K182" s="13" t="s">
+      <c r="K182" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L182" s="12" t="s">
+      <c r="L182" s="11" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -10461,13 +10459,13 @@
       <c r="I183" s="1">
         <v>0</v>
       </c>
-      <c r="J183" s="13" t="s">
+      <c r="J183" s="12" t="s">
         <v>1032</v>
       </c>
-      <c r="K183" s="13" t="s">
+      <c r="K183" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L183" s="12" t="s">
+      <c r="L183" s="11" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10493,13 +10491,13 @@
       <c r="I184" s="1">
         <v>0</v>
       </c>
-      <c r="J184" s="13" t="s">
+      <c r="J184" s="12" t="s">
         <v>1038</v>
       </c>
-      <c r="K184" s="13" t="s">
+      <c r="K184" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L184" s="12" t="s">
+      <c r="L184" s="11" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10525,13 +10523,13 @@
       <c r="I185" s="1">
         <v>0</v>
       </c>
-      <c r="J185" s="13" t="s">
+      <c r="J185" s="12" t="s">
         <v>1044</v>
       </c>
-      <c r="K185" s="13" t="s">
+      <c r="K185" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L185" s="12" t="s">
+      <c r="L185" s="11" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -10557,13 +10555,13 @@
       <c r="I186" s="1">
         <v>0</v>
       </c>
-      <c r="J186" s="13" t="s">
+      <c r="J186" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="K186" s="13" t="s">
+      <c r="K186" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L186" s="12" t="s">
+      <c r="L186" s="11" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -10589,13 +10587,13 @@
       <c r="I187" s="1">
         <v>0</v>
       </c>
-      <c r="J187" s="13" t="s">
+      <c r="J187" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="K187" s="13" t="s">
+      <c r="K187" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L187" s="12" t="s">
+      <c r="L187" s="11" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -10621,13 +10619,13 @@
       <c r="I188" s="1">
         <v>0</v>
       </c>
-      <c r="J188" s="13" t="s">
+      <c r="J188" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="K188" s="13" t="s">
+      <c r="K188" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L188" s="12" t="s">
+      <c r="L188" s="11" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -10653,13 +10651,13 @@
       <c r="I189" s="1">
         <v>0</v>
       </c>
-      <c r="J189" s="13" t="s">
+      <c r="J189" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="K189" s="13" t="s">
+      <c r="K189" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L189" s="12" t="s">
+      <c r="L189" s="11" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -10685,13 +10683,13 @@
       <c r="I190" s="1">
         <v>0</v>
       </c>
-      <c r="J190" s="13" t="s">
+      <c r="J190" s="12" t="s">
         <v>1050</v>
       </c>
-      <c r="K190" s="13" t="s">
+      <c r="K190" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L190" s="12" t="s">
+      <c r="L190" s="11" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -10717,13 +10715,13 @@
       <c r="I191" s="1">
         <v>0</v>
       </c>
-      <c r="J191" s="13" t="s">
+      <c r="J191" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K191" s="13" t="s">
+      <c r="K191" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L191" s="12" t="s">
+      <c r="L191" s="11" t="s">
         <v>1077</v>
       </c>
     </row>
@@ -10749,13 +10747,13 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-      <c r="J192" s="13" t="s">
+      <c r="J192" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K192" s="13" t="s">
+      <c r="K192" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L192" s="12" t="s">
+      <c r="L192" s="11" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -10781,13 +10779,13 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-      <c r="J193" s="13" t="s">
+      <c r="J193" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K193" s="13" t="s">
+      <c r="K193" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L193" s="12" t="s">
+      <c r="L193" s="11" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -10813,13 +10811,13 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-      <c r="J194" s="13" t="s">
+      <c r="J194" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K194" s="13" t="s">
+      <c r="K194" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L194" s="12" t="s">
+      <c r="L194" s="11" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -10845,13 +10843,13 @@
       <c r="I195" s="1">
         <v>0</v>
       </c>
-      <c r="J195" s="13" t="s">
+      <c r="J195" s="12" t="s">
         <v>1076</v>
       </c>
-      <c r="K195" s="13" t="s">
+      <c r="K195" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L195" s="12" t="s">
+      <c r="L195" s="11" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -10877,13 +10875,13 @@
       <c r="I196" s="4">
         <v>0</v>
       </c>
-      <c r="J196" s="15" t="s">
+      <c r="J196" s="14" t="s">
         <v>1102</v>
       </c>
-      <c r="K196" s="15" t="s">
+      <c r="K196" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L196" s="15" t="s">
+      <c r="L196" s="14" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -10909,13 +10907,13 @@
       <c r="I197" s="1">
         <v>0</v>
       </c>
-      <c r="J197" s="13" t="s">
+      <c r="J197" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="K197" s="13" t="s">
+      <c r="K197" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L197" s="12" t="s">
+      <c r="L197" s="11" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -10941,13 +10939,13 @@
       <c r="I198" s="1">
         <v>0</v>
       </c>
-      <c r="J198" s="13" t="s">
+      <c r="J198" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="K198" s="13" t="s">
+      <c r="K198" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L198" s="12" t="s">
+      <c r="L198" s="11" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -10973,13 +10971,13 @@
       <c r="I199" s="1">
         <v>0</v>
       </c>
-      <c r="J199" s="13" t="s">
+      <c r="J199" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="K199" s="13" t="s">
+      <c r="K199" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L199" s="12" t="s">
+      <c r="L199" s="11" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -11005,13 +11003,13 @@
       <c r="I200" s="1">
         <v>0</v>
       </c>
-      <c r="J200" s="13" t="s">
+      <c r="J200" s="12" t="s">
         <v>1102</v>
       </c>
-      <c r="K200" s="13" t="s">
+      <c r="K200" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L200" s="12" t="s">
+      <c r="L200" s="11" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -11037,13 +11035,13 @@
       <c r="I201" s="1">
         <v>0</v>
       </c>
-      <c r="J201" s="13" t="s">
+      <c r="J201" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K201" s="13" t="s">
+      <c r="K201" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L201" s="12" t="s">
+      <c r="L201" s="11" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -11069,13 +11067,13 @@
       <c r="I202" s="1">
         <v>0</v>
       </c>
-      <c r="J202" s="13" t="s">
+      <c r="J202" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K202" s="13" t="s">
+      <c r="K202" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L202" s="12" t="s">
+      <c r="L202" s="11" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -11101,13 +11099,13 @@
       <c r="I203" s="1">
         <v>0</v>
       </c>
-      <c r="J203" s="13" t="s">
+      <c r="J203" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K203" s="13" t="s">
+      <c r="K203" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L203" s="12" t="s">
+      <c r="L203" s="11" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -11133,13 +11131,13 @@
       <c r="I204" s="1">
         <v>0</v>
       </c>
-      <c r="J204" s="13" t="s">
+      <c r="J204" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K204" s="13" t="s">
+      <c r="K204" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L204" s="12" t="s">
+      <c r="L204" s="11" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -11165,13 +11163,13 @@
       <c r="I205" s="1">
         <v>0</v>
       </c>
-      <c r="J205" s="13" t="s">
+      <c r="J205" s="12" t="s">
         <v>1128</v>
       </c>
-      <c r="K205" s="13" t="s">
+      <c r="K205" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L205" s="12" t="s">
+      <c r="L205" s="11" t="s">
         <v>1149</v>
       </c>
     </row>
@@ -11197,13 +11195,13 @@
       <c r="I206" s="1">
         <v>0</v>
       </c>
-      <c r="J206" s="13" t="s">
+      <c r="J206" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K206" s="13" t="s">
+      <c r="K206" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L206" s="12" t="s">
+      <c r="L206" s="11" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -11229,13 +11227,13 @@
       <c r="I207" s="1">
         <v>0</v>
       </c>
-      <c r="J207" s="13" t="s">
+      <c r="J207" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K207" s="13" t="s">
+      <c r="K207" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L207" s="12" t="s">
+      <c r="L207" s="11" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -11261,13 +11259,13 @@
       <c r="I208" s="1">
         <v>0</v>
       </c>
-      <c r="J208" s="13" t="s">
+      <c r="J208" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K208" s="13" t="s">
+      <c r="K208" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L208" s="12" t="s">
+      <c r="L208" s="11" t="s">
         <v>1165</v>
       </c>
     </row>
@@ -11293,13 +11291,13 @@
       <c r="I209" s="1">
         <v>0</v>
       </c>
-      <c r="J209" s="13" t="s">
+      <c r="J209" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K209" s="13" t="s">
+      <c r="K209" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L209" s="12" t="s">
+      <c r="L209" s="11" t="s">
         <v>1170</v>
       </c>
     </row>
@@ -11325,13 +11323,13 @@
       <c r="I210" s="1">
         <v>0</v>
       </c>
-      <c r="J210" s="13" t="s">
+      <c r="J210" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="K210" s="13" t="s">
+      <c r="K210" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L210" s="12" t="s">
+      <c r="L210" s="11" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -11357,13 +11355,13 @@
       <c r="I211" s="1">
         <v>0</v>
       </c>
-      <c r="J211" s="13" t="s">
+      <c r="J211" s="12" t="s">
         <v>1180</v>
       </c>
-      <c r="K211" s="13" t="s">
+      <c r="K211" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L211" s="12" t="s">
+      <c r="L211" s="11" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -11389,13 +11387,13 @@
       <c r="I212" s="1">
         <v>0</v>
       </c>
-      <c r="J212" s="13" t="s">
+      <c r="J212" s="12" t="s">
         <v>1180</v>
       </c>
-      <c r="K212" s="13" t="s">
+      <c r="K212" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L212" s="12" t="s">
+      <c r="L212" s="11" t="s">
         <v>1186</v>
       </c>
     </row>
@@ -11421,13 +11419,13 @@
       <c r="I213" s="1">
         <v>0</v>
       </c>
-      <c r="J213" s="13" t="s">
+      <c r="J213" s="12" t="s">
         <v>1180</v>
       </c>
-      <c r="K213" s="13" t="s">
+      <c r="K213" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L213" s="12" t="s">
+      <c r="L213" s="11" t="s">
         <v>1191</v>
       </c>
     </row>
@@ -11455,13 +11453,13 @@
       <c r="I214" s="1">
         <v>0</v>
       </c>
-      <c r="J214" s="13" t="s">
+      <c r="J214" s="12" t="s">
         <v>1180</v>
       </c>
-      <c r="K214" s="13" t="s">
+      <c r="K214" s="12" t="s">
         <v>1020</v>
       </c>
-      <c r="L214" s="12" t="s">
+      <c r="L214" s="11" t="s">
         <v>1196</v>
       </c>
     </row>
@@ -11489,13 +11487,13 @@
       <c r="I215" s="1">
         <v>0</v>
       </c>
-      <c r="J215" s="13" t="s">
+      <c r="J215" s="12" t="s">
         <v>1201</v>
       </c>
-      <c r="K215" s="13" t="s">
+      <c r="K215" s="12" t="s">
         <v>1202</v>
       </c>
-      <c r="L215" s="12" t="s">
+      <c r="L215" s="11" t="s">
         <v>1203</v>
       </c>
     </row>
@@ -11523,13 +11521,13 @@
       <c r="I216" s="3">
         <v>0</v>
       </c>
-      <c r="J216" s="14" t="s">
+      <c r="J216" s="13" t="s">
         <v>1207</v>
       </c>
-      <c r="K216" s="14" t="s">
+      <c r="K216" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L216" s="12" t="s">
+      <c r="L216" s="11" t="s">
         <v>1209</v>
       </c>
       <c r="M216" s="3" t="s">
@@ -11560,13 +11558,13 @@
       <c r="I217" s="1">
         <v>0</v>
       </c>
-      <c r="J217" s="13" t="s">
+      <c r="J217" s="12" t="s">
         <v>1214</v>
       </c>
-      <c r="K217" s="16" t="s">
+      <c r="K217" s="12" t="s">
         <v>1208</v>
       </c>
-      <c r="L217" s="12" t="s">
+      <c r="L217" s="11" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -11594,13 +11592,13 @@
       <c r="I218" s="1">
         <v>0</v>
       </c>
-      <c r="J218" s="13" t="s">
+      <c r="J218" s="12" t="s">
         <v>1219</v>
       </c>
-      <c r="K218" s="16" t="s">
+      <c r="K218" s="12" t="s">
         <v>1208</v>
       </c>
-      <c r="L218" s="12" t="s">
+      <c r="L218" s="11" t="s">
         <v>1220</v>
       </c>
     </row>
@@ -11628,13 +11626,13 @@
       <c r="I219" s="1">
         <v>0</v>
       </c>
-      <c r="J219" s="13" t="s">
+      <c r="J219" s="12" t="s">
         <v>1224</v>
       </c>
-      <c r="K219" s="16" t="s">
+      <c r="K219" s="12" t="s">
         <v>1208</v>
       </c>
-      <c r="L219" s="12" t="s">
+      <c r="L219" s="11" t="s">
         <v>1225</v>
       </c>
     </row>
@@ -11662,13 +11660,13 @@
       <c r="I220" s="1">
         <v>0</v>
       </c>
-      <c r="J220" s="13" t="s">
+      <c r="J220" s="12" t="s">
         <v>1229</v>
       </c>
-      <c r="K220" s="16" t="s">
+      <c r="K220" s="12" t="s">
         <v>1208</v>
       </c>
-      <c r="L220" s="12" t="s">
+      <c r="L220" s="11" t="s">
         <v>1230</v>
       </c>
     </row>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -3685,7 +3685,7 @@
     <t>202002,106,504,210084,1009,506,202009,202003,507</t>
   </si>
   <si>
-    <t>10,18000,98000,600000,140000,700000,800000,900000,900000</t>
+    <t>10,18000,98000,600000,140000,700000,1000000,900000,900000</t>
   </si>
   <si>
     <t>10210</t>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -3667,7 +3667,7 @@
     <t>202002,300091,105,504,210083,1009,505,506,202003,507</t>
   </si>
   <si>
-    <t>10,9500,9000,98000,600000,140000,600000,700000,600000,900000</t>
+    <t>10,9500,9000,98000,600000,140000,600000,700000,600000,1000000</t>
   </si>
   <si>
     <t>10209</t>
@@ -3685,7 +3685,7 @@
     <t>202002,106,504,210084,1009,506,202009,202003,507</t>
   </si>
   <si>
-    <t>10,18000,98000,600000,140000,700000,1000000,900000,900000</t>
+    <t>10,18000,98000,600000,140000,900000,1200000,1000000,1000000</t>
   </si>
   <si>
     <t>10210</t>
@@ -4401,7 +4401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4417,10 +4417,12 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6094,10 +6096,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="11" t="s">
+      <c r="J46" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="K46" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -6123,10 +6125,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="11" t="s">
+      <c r="J47" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="K47" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -6152,10 +6154,10 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="J48" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="K48" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
@@ -6181,10 +6183,10 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="J49" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
@@ -6210,10 +6212,10 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="J50" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="K50" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
@@ -6242,10 +6244,10 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="J51" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="K51" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
@@ -6271,10 +6273,10 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="K52" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -6300,10 +6302,10 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="11" t="s">
+      <c r="J53" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="11" t="s">
+      <c r="K53" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
@@ -6329,10 +6331,10 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="J54" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="11" t="s">
+      <c r="K54" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
@@ -6358,10 +6360,10 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="11" t="s">
+      <c r="J55" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="11" t="s">
+      <c r="K55" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -6390,10 +6392,10 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="J56" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="11" t="s">
+      <c r="K56" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
@@ -6422,10 +6424,10 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="J57" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="11" t="s">
+      <c r="K57" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
@@ -6454,10 +6456,10 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="11" t="s">
+      <c r="K58" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -6486,10 +6488,10 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="11" t="s">
+      <c r="J59" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="11" t="s">
+      <c r="K59" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
@@ -6518,10 +6520,10 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="11" t="s">
+      <c r="J60" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="11" t="s">
+      <c r="K60" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -6551,10 +6553,10 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="12" t="s">
+      <c r="J61" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="12" t="s">
+      <c r="K61" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -6584,10 +6586,10 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="12" t="s">
+      <c r="J62" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="12" t="s">
+      <c r="K62" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -6617,10 +6619,10 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="12" t="s">
+      <c r="J63" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="12" t="s">
+      <c r="K63" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
@@ -6650,10 +6652,10 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="12" t="s">
+      <c r="J64" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="12" t="s">
+      <c r="K64" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
@@ -6683,10 +6685,10 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="12" t="s">
+      <c r="J65" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="12" t="s">
+      <c r="K65" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
@@ -6715,10 +6717,10 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="12" t="s">
+      <c r="J66" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="12" t="s">
+      <c r="K66" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
@@ -6747,10 +6749,10 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="12" t="s">
+      <c r="J67" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="12" t="s">
+      <c r="K67" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
@@ -6779,10 +6781,10 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="12" t="s">
+      <c r="J68" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="12" t="s">
+      <c r="K68" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -6811,10 +6813,10 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="12" t="s">
+      <c r="J69" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="12" t="s">
+      <c r="K69" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
@@ -6843,10 +6845,10 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="12" t="s">
+      <c r="J70" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="12" t="s">
+      <c r="K70" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
@@ -6875,10 +6877,10 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="12" t="s">
+      <c r="J71" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="12" t="s">
+      <c r="K71" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -6907,10 +6909,10 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="12" t="s">
+      <c r="J72" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="12" t="s">
+      <c r="K72" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -6939,10 +6941,10 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="12" t="s">
+      <c r="J73" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="12" t="s">
+      <c r="K73" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -6971,10 +6973,10 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="12" t="s">
+      <c r="J74" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="12" t="s">
+      <c r="K74" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
@@ -7003,10 +7005,10 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="12" t="s">
+      <c r="J75" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="12" t="s">
+      <c r="K75" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
@@ -7035,10 +7037,10 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="12" t="s">
+      <c r="J76" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="12" t="s">
+      <c r="K76" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
@@ -7067,10 +7069,10 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="12" t="s">
+      <c r="J77" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="12" t="s">
+      <c r="K77" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
@@ -7099,10 +7101,10 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="12" t="s">
+      <c r="J78" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="12" t="s">
+      <c r="K78" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
@@ -7131,10 +7133,10 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="12" t="s">
+      <c r="J79" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="12" t="s">
+      <c r="K79" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
@@ -7163,10 +7165,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="12" t="s">
+      <c r="J80" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="12" t="s">
+      <c r="K80" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -7195,10 +7197,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="12" t="s">
+      <c r="J81" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="12" t="s">
+      <c r="K81" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -7227,10 +7229,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="12" t="s">
+      <c r="J82" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="12" t="s">
+      <c r="K82" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -7259,10 +7261,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="12" t="s">
+      <c r="J83" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="12" t="s">
+      <c r="K83" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -7291,10 +7293,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="12" t="s">
+      <c r="J84" s="13" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="12" t="s">
+      <c r="K84" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -7323,10 +7325,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="12" t="s">
+      <c r="J85" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="12" t="s">
+      <c r="K85" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -7355,10 +7357,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="12" t="s">
+      <c r="J86" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="12" t="s">
+      <c r="K86" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -7387,10 +7389,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="12" t="s">
+      <c r="J87" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="12" t="s">
+      <c r="K87" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -7419,10 +7421,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="12" t="s">
+      <c r="J88" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="12" t="s">
+      <c r="K88" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -7451,10 +7453,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="12" t="s">
+      <c r="J89" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="12" t="s">
+      <c r="K89" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -7483,10 +7485,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="12" t="s">
+      <c r="J90" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="12" t="s">
+      <c r="K90" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -7515,10 +7517,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="12" t="s">
+      <c r="J91" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="12" t="s">
+      <c r="K91" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -7547,10 +7549,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="12" t="s">
+      <c r="J92" s="13" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="12" t="s">
+      <c r="K92" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -7579,10 +7581,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="12" t="s">
+      <c r="J93" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="12" t="s">
+      <c r="K93" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -7611,10 +7613,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="12" t="s">
+      <c r="J94" s="13" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="12" t="s">
+      <c r="K94" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -7643,10 +7645,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="12" t="s">
+      <c r="J95" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="12" t="s">
+      <c r="K95" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -7675,10 +7677,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="12" t="s">
+      <c r="J96" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="12" t="s">
+      <c r="K96" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -7707,10 +7709,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="12" t="s">
+      <c r="J97" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="12" t="s">
+      <c r="K97" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -7739,10 +7741,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="12" t="s">
+      <c r="J98" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="12" t="s">
+      <c r="K98" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -7771,10 +7773,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="12" t="s">
+      <c r="J99" s="13" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="12" t="s">
+      <c r="K99" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -7803,10 +7805,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="12" t="s">
+      <c r="J100" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="12" t="s">
+      <c r="K100" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -7835,10 +7837,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="12" t="s">
+      <c r="J101" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="12" t="s">
+      <c r="K101" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -7867,10 +7869,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="12" t="s">
+      <c r="J102" s="13" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="12" t="s">
+      <c r="K102" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -7899,10 +7901,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="12" t="s">
+      <c r="J103" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="12" t="s">
+      <c r="K103" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -7931,10 +7933,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="12" t="s">
+      <c r="J104" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="12" t="s">
+      <c r="K104" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -7963,10 +7965,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="12" t="s">
+      <c r="J105" s="13" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="12" t="s">
+      <c r="K105" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -7995,10 +7997,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="12" t="s">
+      <c r="J106" s="13" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="12" t="s">
+      <c r="K106" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -8027,10 +8029,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="12" t="s">
+      <c r="J107" s="13" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="12" t="s">
+      <c r="K107" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -8059,10 +8061,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="12" t="s">
+      <c r="J108" s="13" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="12" t="s">
+      <c r="K108" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -8091,10 +8093,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="12" t="s">
+      <c r="J109" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="12" t="s">
+      <c r="K109" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -8123,10 +8125,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="12" t="s">
+      <c r="J110" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="12" t="s">
+      <c r="K110" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -8155,10 +8157,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="12" t="s">
+      <c r="J111" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="12" t="s">
+      <c r="K111" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -8187,10 +8189,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="12" t="s">
+      <c r="J112" s="13" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="12" t="s">
+      <c r="K112" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -8219,10 +8221,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="12" t="s">
+      <c r="J113" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="12" t="s">
+      <c r="K113" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -8251,10 +8253,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="12" t="s">
+      <c r="J114" s="13" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="12" t="s">
+      <c r="K114" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -8283,10 +8285,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="12" t="s">
+      <c r="J115" s="13" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="12" t="s">
+      <c r="K115" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -8315,10 +8317,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="12" t="s">
+      <c r="J116" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="12" t="s">
+      <c r="K116" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -8347,10 +8349,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="12" t="s">
+      <c r="J117" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="12" t="s">
+      <c r="K117" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -8379,10 +8381,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="12" t="s">
+      <c r="J118" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="12" t="s">
+      <c r="K118" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -8411,10 +8413,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="12" t="s">
+      <c r="J119" s="13" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="12" t="s">
+      <c r="K119" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -8443,10 +8445,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="12" t="s">
+      <c r="J120" s="13" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="12" t="s">
+      <c r="K120" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -8475,10 +8477,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="12" t="s">
+      <c r="J121" s="13" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="12" t="s">
+      <c r="K121" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -8507,10 +8509,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="12" t="s">
+      <c r="J122" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="12" t="s">
+      <c r="K122" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -8539,10 +8541,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="12" t="s">
+      <c r="J123" s="13" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="12" t="s">
+      <c r="K123" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -8571,10 +8573,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="12" t="s">
+      <c r="J124" s="13" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="12" t="s">
+      <c r="K124" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -8603,10 +8605,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="12" t="s">
+      <c r="J125" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="12" t="s">
+      <c r="K125" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -8635,10 +8637,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="12" t="s">
+      <c r="J126" s="13" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="12" t="s">
+      <c r="K126" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -8667,10 +8669,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="12" t="s">
+      <c r="J127" s="13" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="12" t="s">
+      <c r="K127" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -8699,10 +8701,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="12" t="s">
+      <c r="J128" s="13" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="12" t="s">
+      <c r="K128" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -8731,10 +8733,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="12" t="s">
+      <c r="J129" s="13" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="12" t="s">
+      <c r="K129" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -8763,10 +8765,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="12" t="s">
+      <c r="J130" s="13" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="12" t="s">
+      <c r="K130" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -8795,10 +8797,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="12" t="s">
+      <c r="J131" s="13" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="12" t="s">
+      <c r="K131" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -8827,10 +8829,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="12" t="s">
+      <c r="J132" s="13" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="12" t="s">
+      <c r="K132" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -8859,10 +8861,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="12" t="s">
+      <c r="J133" s="13" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="12" t="s">
+      <c r="K133" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -8891,10 +8893,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="12" t="s">
+      <c r="J134" s="13" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="12" t="s">
+      <c r="K134" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -8923,10 +8925,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="12" t="s">
+      <c r="J135" s="13" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="12" t="s">
+      <c r="K135" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -8955,10 +8957,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="12" t="s">
+      <c r="J136" s="13" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="12" t="s">
+      <c r="K136" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -8987,10 +8989,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="12" t="s">
+      <c r="J137" s="13" t="s">
         <v>782</v>
       </c>
-      <c r="K137" s="12" t="s">
+      <c r="K137" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -9019,10 +9021,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="12" t="s">
+      <c r="J138" s="13" t="s">
         <v>788</v>
       </c>
-      <c r="K138" s="12" t="s">
+      <c r="K138" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -9051,10 +9053,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="12" t="s">
+      <c r="J139" s="13" t="s">
         <v>794</v>
       </c>
-      <c r="K139" s="12" t="s">
+      <c r="K139" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -9083,10 +9085,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="12" t="s">
+      <c r="J140" s="13" t="s">
         <v>800</v>
       </c>
-      <c r="K140" s="12" t="s">
+      <c r="K140" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -9115,10 +9117,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="12" t="s">
+      <c r="J141" s="13" t="s">
         <v>806</v>
       </c>
-      <c r="K141" s="12" t="s">
+      <c r="K141" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -9147,10 +9149,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="12" t="s">
+      <c r="J142" s="13" t="s">
         <v>812</v>
       </c>
-      <c r="K142" s="12" t="s">
+      <c r="K142" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -9179,10 +9181,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="12" t="s">
+      <c r="J143" s="13" t="s">
         <v>818</v>
       </c>
-      <c r="K143" s="12" t="s">
+      <c r="K143" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -9211,10 +9213,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="12" t="s">
+      <c r="J144" s="13" t="s">
         <v>824</v>
       </c>
-      <c r="K144" s="12" t="s">
+      <c r="K144" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -9243,10 +9245,10 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="12" t="s">
+      <c r="J145" s="13" t="s">
         <v>830</v>
       </c>
-      <c r="K145" s="12" t="s">
+      <c r="K145" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
@@ -9275,13 +9277,13 @@
       <c r="I146" s="3">
         <v>0</v>
       </c>
-      <c r="J146" s="13" t="s">
+      <c r="J146" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K146" s="13" t="s">
+      <c r="K146" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L146" s="13" t="s">
+      <c r="L146" s="14" t="s">
         <v>837</v>
       </c>
     </row>
@@ -9307,13 +9309,13 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="12" t="s">
+      <c r="J147" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K147" s="12" t="s">
+      <c r="K147" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L147" s="11" t="s">
+      <c r="L147" s="12" t="s">
         <v>842</v>
       </c>
     </row>
@@ -9339,13 +9341,13 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="12" t="s">
+      <c r="J148" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K148" s="12" t="s">
+      <c r="K148" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L148" s="11" t="s">
+      <c r="L148" s="12" t="s">
         <v>847</v>
       </c>
     </row>
@@ -9371,13 +9373,13 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="12" t="s">
+      <c r="J149" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K149" s="12" t="s">
+      <c r="K149" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L149" s="11" t="s">
+      <c r="L149" s="12" t="s">
         <v>852</v>
       </c>
     </row>
@@ -9403,13 +9405,13 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="12" t="s">
+      <c r="J150" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K150" s="12" t="s">
+      <c r="K150" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L150" s="11" t="s">
+      <c r="L150" s="12" t="s">
         <v>857</v>
       </c>
     </row>
@@ -9435,13 +9437,13 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="12" t="s">
+      <c r="J151" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K151" s="12" t="s">
+      <c r="K151" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L151" s="11" t="s">
+      <c r="L151" s="12" t="s">
         <v>863</v>
       </c>
     </row>
@@ -9467,13 +9469,13 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="12" t="s">
+      <c r="J152" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K152" s="12" t="s">
+      <c r="K152" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L152" s="11" t="s">
+      <c r="L152" s="12" t="s">
         <v>868</v>
       </c>
     </row>
@@ -9499,13 +9501,13 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="12" t="s">
+      <c r="J153" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K153" s="12" t="s">
+      <c r="K153" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L153" s="11" t="s">
+      <c r="L153" s="12" t="s">
         <v>873</v>
       </c>
     </row>
@@ -9531,13 +9533,13 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="12" t="s">
+      <c r="J154" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K154" s="12" t="s">
+      <c r="K154" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L154" s="11" t="s">
+      <c r="L154" s="12" t="s">
         <v>878</v>
       </c>
     </row>
@@ -9563,13 +9565,13 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="12" t="s">
+      <c r="J155" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K155" s="12" t="s">
+      <c r="K155" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L155" s="11" t="s">
+      <c r="L155" s="12" t="s">
         <v>883</v>
       </c>
     </row>
@@ -9595,13 +9597,13 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="12" t="s">
+      <c r="J156" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K156" s="12" t="s">
+      <c r="K156" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L156" s="11" t="s">
+      <c r="L156" s="12" t="s">
         <v>889</v>
       </c>
     </row>
@@ -9627,13 +9629,13 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="12" t="s">
+      <c r="J157" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K157" s="12" t="s">
+      <c r="K157" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L157" s="11" t="s">
+      <c r="L157" s="12" t="s">
         <v>894</v>
       </c>
     </row>
@@ -9659,13 +9661,13 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="12" t="s">
+      <c r="J158" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="12" t="s">
+      <c r="K158" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L158" s="11" t="s">
+      <c r="L158" s="12" t="s">
         <v>899</v>
       </c>
     </row>
@@ -9691,13 +9693,13 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="12" t="s">
+      <c r="J159" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K159" s="12" t="s">
+      <c r="K159" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L159" s="11" t="s">
+      <c r="L159" s="12" t="s">
         <v>904</v>
       </c>
     </row>
@@ -9723,13 +9725,13 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="12" t="s">
+      <c r="J160" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K160" s="12" t="s">
+      <c r="K160" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L160" s="11" t="s">
+      <c r="L160" s="12" t="s">
         <v>909</v>
       </c>
     </row>
@@ -9755,13 +9757,13 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="12" t="s">
+      <c r="J161" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K161" s="12" t="s">
+      <c r="K161" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L161" s="11" t="s">
+      <c r="L161" s="12" t="s">
         <v>915</v>
       </c>
     </row>
@@ -9787,13 +9789,13 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="12" t="s">
+      <c r="J162" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K162" s="12" t="s">
+      <c r="K162" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L162" s="11" t="s">
+      <c r="L162" s="12" t="s">
         <v>920</v>
       </c>
     </row>
@@ -9819,13 +9821,13 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="12" t="s">
+      <c r="J163" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K163" s="12" t="s">
+      <c r="K163" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L163" s="11" t="s">
+      <c r="L163" s="12" t="s">
         <v>925</v>
       </c>
     </row>
@@ -9851,13 +9853,13 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="12" t="s">
+      <c r="J164" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K164" s="12" t="s">
+      <c r="K164" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L164" s="11" t="s">
+      <c r="L164" s="12" t="s">
         <v>930</v>
       </c>
     </row>
@@ -9883,13 +9885,13 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="12" t="s">
+      <c r="J165" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K165" s="12" t="s">
+      <c r="K165" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L165" s="11" t="s">
+      <c r="L165" s="12" t="s">
         <v>935</v>
       </c>
     </row>
@@ -9915,13 +9917,13 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="12" t="s">
+      <c r="J166" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K166" s="12" t="s">
+      <c r="K166" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L166" s="11" t="s">
+      <c r="L166" s="12" t="s">
         <v>941</v>
       </c>
     </row>
@@ -9947,13 +9949,13 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="12" t="s">
+      <c r="J167" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K167" s="12" t="s">
+      <c r="K167" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L167" s="11" t="s">
+      <c r="L167" s="12" t="s">
         <v>946</v>
       </c>
     </row>
@@ -9979,13 +9981,13 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="12" t="s">
+      <c r="J168" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K168" s="12" t="s">
+      <c r="K168" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L168" s="11" t="s">
+      <c r="L168" s="12" t="s">
         <v>951</v>
       </c>
     </row>
@@ -10011,13 +10013,13 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="12" t="s">
+      <c r="J169" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K169" s="12" t="s">
+      <c r="K169" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L169" s="11" t="s">
+      <c r="L169" s="12" t="s">
         <v>956</v>
       </c>
     </row>
@@ -10043,13 +10045,13 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="12" t="s">
+      <c r="J170" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="12" t="s">
+      <c r="K170" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L170" s="11" t="s">
+      <c r="L170" s="12" t="s">
         <v>961</v>
       </c>
     </row>
@@ -10075,13 +10077,13 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="12" t="s">
+      <c r="J171" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K171" s="12" t="s">
+      <c r="K171" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L171" s="11" t="s">
+      <c r="L171" s="12" t="s">
         <v>967</v>
       </c>
     </row>
@@ -10107,13 +10109,13 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="12" t="s">
+      <c r="J172" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K172" s="12" t="s">
+      <c r="K172" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L172" s="11" t="s">
+      <c r="L172" s="12" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10139,13 +10141,13 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="12" t="s">
+      <c r="J173" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K173" s="12" t="s">
+      <c r="K173" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L173" s="11" t="s">
+      <c r="L173" s="12" t="s">
         <v>977</v>
       </c>
     </row>
@@ -10171,13 +10173,13 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="12" t="s">
+      <c r="J174" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K174" s="12" t="s">
+      <c r="K174" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L174" s="11" t="s">
+      <c r="L174" s="12" t="s">
         <v>982</v>
       </c>
     </row>
@@ -10203,13 +10205,13 @@
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="12" t="s">
+      <c r="J175" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K175" s="12" t="s">
+      <c r="K175" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L175" s="11" t="s">
+      <c r="L175" s="12" t="s">
         <v>987</v>
       </c>
     </row>
@@ -10235,13 +10237,13 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="12" t="s">
+      <c r="J176" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K176" s="12" t="s">
+      <c r="K176" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L176" s="11" t="s">
+      <c r="L176" s="12" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10267,13 +10269,13 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="12" t="s">
+      <c r="J177" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K177" s="12" t="s">
+      <c r="K177" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L177" s="11" t="s">
+      <c r="L177" s="12" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10299,13 +10301,13 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="12" t="s">
+      <c r="J178" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K178" s="12" t="s">
+      <c r="K178" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L178" s="11" t="s">
+      <c r="L178" s="12" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -10331,13 +10333,13 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="12" t="s">
+      <c r="J179" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K179" s="12" t="s">
+      <c r="K179" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L179" s="11" t="s">
+      <c r="L179" s="12" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -10363,13 +10365,13 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="12" t="s">
+      <c r="J180" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K180" s="12" t="s">
+      <c r="K180" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L180" s="11" t="s">
+      <c r="L180" s="12" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -10395,13 +10397,13 @@
       <c r="I181" s="3">
         <v>0</v>
       </c>
-      <c r="J181" s="13" t="s">
+      <c r="J181" s="14" t="s">
         <v>1019</v>
       </c>
-      <c r="K181" s="13" t="s">
+      <c r="K181" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L181" s="11" t="s">
+      <c r="L181" s="12" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -10427,13 +10429,13 @@
       <c r="I182" s="1">
         <v>0</v>
       </c>
-      <c r="J182" s="12" t="s">
+      <c r="J182" s="13" t="s">
         <v>1026</v>
       </c>
-      <c r="K182" s="12" t="s">
+      <c r="K182" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L182" s="11" t="s">
+      <c r="L182" s="12" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -10459,13 +10461,13 @@
       <c r="I183" s="1">
         <v>0</v>
       </c>
-      <c r="J183" s="12" t="s">
+      <c r="J183" s="13" t="s">
         <v>1032</v>
       </c>
-      <c r="K183" s="12" t="s">
+      <c r="K183" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L183" s="11" t="s">
+      <c r="L183" s="12" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10491,13 +10493,13 @@
       <c r="I184" s="1">
         <v>0</v>
       </c>
-      <c r="J184" s="12" t="s">
+      <c r="J184" s="13" t="s">
         <v>1038</v>
       </c>
-      <c r="K184" s="12" t="s">
+      <c r="K184" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L184" s="11" t="s">
+      <c r="L184" s="12" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10523,13 +10525,13 @@
       <c r="I185" s="1">
         <v>0</v>
       </c>
-      <c r="J185" s="12" t="s">
+      <c r="J185" s="13" t="s">
         <v>1044</v>
       </c>
-      <c r="K185" s="12" t="s">
+      <c r="K185" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L185" s="11" t="s">
+      <c r="L185" s="12" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -10555,13 +10557,13 @@
       <c r="I186" s="1">
         <v>0</v>
       </c>
-      <c r="J186" s="12" t="s">
+      <c r="J186" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K186" s="12" t="s">
+      <c r="K186" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L186" s="11" t="s">
+      <c r="L186" s="12" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -10587,13 +10589,13 @@
       <c r="I187" s="1">
         <v>0</v>
       </c>
-      <c r="J187" s="12" t="s">
+      <c r="J187" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K187" s="12" t="s">
+      <c r="K187" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L187" s="11" t="s">
+      <c r="L187" s="12" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -10619,13 +10621,13 @@
       <c r="I188" s="1">
         <v>0</v>
       </c>
-      <c r="J188" s="12" t="s">
+      <c r="J188" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K188" s="12" t="s">
+      <c r="K188" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L188" s="11" t="s">
+      <c r="L188" s="12" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -10651,13 +10653,13 @@
       <c r="I189" s="1">
         <v>0</v>
       </c>
-      <c r="J189" s="12" t="s">
+      <c r="J189" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K189" s="12" t="s">
+      <c r="K189" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L189" s="11" t="s">
+      <c r="L189" s="12" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -10683,13 +10685,13 @@
       <c r="I190" s="1">
         <v>0</v>
       </c>
-      <c r="J190" s="12" t="s">
+      <c r="J190" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K190" s="12" t="s">
+      <c r="K190" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L190" s="11" t="s">
+      <c r="L190" s="12" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -10715,13 +10717,13 @@
       <c r="I191" s="1">
         <v>0</v>
       </c>
-      <c r="J191" s="12" t="s">
+      <c r="J191" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K191" s="12" t="s">
+      <c r="K191" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L191" s="11" t="s">
+      <c r="L191" s="12" t="s">
         <v>1077</v>
       </c>
     </row>
@@ -10747,13 +10749,13 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-      <c r="J192" s="12" t="s">
+      <c r="J192" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K192" s="12" t="s">
+      <c r="K192" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L192" s="11" t="s">
+      <c r="L192" s="12" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -10779,13 +10781,13 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-      <c r="J193" s="12" t="s">
+      <c r="J193" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K193" s="12" t="s">
+      <c r="K193" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L193" s="11" t="s">
+      <c r="L193" s="12" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -10811,13 +10813,13 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-      <c r="J194" s="12" t="s">
+      <c r="J194" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K194" s="12" t="s">
+      <c r="K194" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L194" s="11" t="s">
+      <c r="L194" s="12" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -10843,13 +10845,13 @@
       <c r="I195" s="1">
         <v>0</v>
       </c>
-      <c r="J195" s="12" t="s">
+      <c r="J195" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K195" s="12" t="s">
+      <c r="K195" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L195" s="11" t="s">
+      <c r="L195" s="12" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -10875,13 +10877,13 @@
       <c r="I196" s="4">
         <v>0</v>
       </c>
-      <c r="J196" s="14" t="s">
+      <c r="J196" s="15" t="s">
         <v>1102</v>
       </c>
-      <c r="K196" s="14" t="s">
+      <c r="K196" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L196" s="14" t="s">
+      <c r="L196" s="15" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -10907,13 +10909,13 @@
       <c r="I197" s="1">
         <v>0</v>
       </c>
-      <c r="J197" s="12" t="s">
+      <c r="J197" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K197" s="12" t="s">
+      <c r="K197" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L197" s="11" t="s">
+      <c r="L197" s="12" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -10939,13 +10941,13 @@
       <c r="I198" s="1">
         <v>0</v>
       </c>
-      <c r="J198" s="12" t="s">
+      <c r="J198" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K198" s="12" t="s">
+      <c r="K198" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L198" s="11" t="s">
+      <c r="L198" s="12" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -10971,13 +10973,13 @@
       <c r="I199" s="1">
         <v>0</v>
       </c>
-      <c r="J199" s="12" t="s">
+      <c r="J199" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K199" s="12" t="s">
+      <c r="K199" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L199" s="11" t="s">
+      <c r="L199" s="12" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -11003,13 +11005,13 @@
       <c r="I200" s="1">
         <v>0</v>
       </c>
-      <c r="J200" s="12" t="s">
+      <c r="J200" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K200" s="12" t="s">
+      <c r="K200" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L200" s="11" t="s">
+      <c r="L200" s="12" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -11035,13 +11037,13 @@
       <c r="I201" s="1">
         <v>0</v>
       </c>
-      <c r="J201" s="12" t="s">
+      <c r="J201" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K201" s="12" t="s">
+      <c r="K201" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L201" s="11" t="s">
+      <c r="L201" s="12" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -11067,13 +11069,13 @@
       <c r="I202" s="1">
         <v>0</v>
       </c>
-      <c r="J202" s="12" t="s">
+      <c r="J202" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K202" s="12" t="s">
+      <c r="K202" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L202" s="11" t="s">
+      <c r="L202" s="12" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -11099,13 +11101,13 @@
       <c r="I203" s="1">
         <v>0</v>
       </c>
-      <c r="J203" s="12" t="s">
+      <c r="J203" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K203" s="12" t="s">
+      <c r="K203" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L203" s="11" t="s">
+      <c r="L203" s="12" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -11131,13 +11133,13 @@
       <c r="I204" s="1">
         <v>0</v>
       </c>
-      <c r="J204" s="12" t="s">
+      <c r="J204" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K204" s="12" t="s">
+      <c r="K204" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L204" s="11" t="s">
+      <c r="L204" s="12" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -11163,13 +11165,13 @@
       <c r="I205" s="1">
         <v>0</v>
       </c>
-      <c r="J205" s="12" t="s">
+      <c r="J205" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K205" s="12" t="s">
+      <c r="K205" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L205" s="11" t="s">
+      <c r="L205" s="12" t="s">
         <v>1149</v>
       </c>
     </row>
@@ -11195,13 +11197,13 @@
       <c r="I206" s="1">
         <v>0</v>
       </c>
-      <c r="J206" s="12" t="s">
+      <c r="J206" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K206" s="12" t="s">
+      <c r="K206" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L206" s="11" t="s">
+      <c r="L206" s="12" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -11227,13 +11229,13 @@
       <c r="I207" s="1">
         <v>0</v>
       </c>
-      <c r="J207" s="12" t="s">
+      <c r="J207" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K207" s="12" t="s">
+      <c r="K207" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L207" s="11" t="s">
+      <c r="L207" s="12" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -11259,13 +11261,13 @@
       <c r="I208" s="1">
         <v>0</v>
       </c>
-      <c r="J208" s="12" t="s">
+      <c r="J208" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K208" s="12" t="s">
+      <c r="K208" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L208" s="11" t="s">
+      <c r="L208" s="12" t="s">
         <v>1165</v>
       </c>
     </row>
@@ -11291,13 +11293,13 @@
       <c r="I209" s="1">
         <v>0</v>
       </c>
-      <c r="J209" s="12" t="s">
+      <c r="J209" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K209" s="12" t="s">
+      <c r="K209" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L209" s="11" t="s">
+      <c r="L209" s="12" t="s">
         <v>1170</v>
       </c>
     </row>
@@ -11323,13 +11325,13 @@
       <c r="I210" s="1">
         <v>0</v>
       </c>
-      <c r="J210" s="12" t="s">
+      <c r="J210" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K210" s="12" t="s">
+      <c r="K210" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L210" s="11" t="s">
+      <c r="L210" s="12" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -11355,13 +11357,13 @@
       <c r="I211" s="1">
         <v>0</v>
       </c>
-      <c r="J211" s="12" t="s">
+      <c r="J211" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K211" s="12" t="s">
+      <c r="K211" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L211" s="11" t="s">
+      <c r="L211" s="12" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -11387,13 +11389,13 @@
       <c r="I212" s="1">
         <v>0</v>
       </c>
-      <c r="J212" s="12" t="s">
+      <c r="J212" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K212" s="12" t="s">
+      <c r="K212" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L212" s="11" t="s">
+      <c r="L212" s="12" t="s">
         <v>1186</v>
       </c>
     </row>
@@ -11419,13 +11421,13 @@
       <c r="I213" s="1">
         <v>0</v>
       </c>
-      <c r="J213" s="12" t="s">
+      <c r="J213" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K213" s="12" t="s">
+      <c r="K213" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L213" s="11" t="s">
+      <c r="L213" s="12" t="s">
         <v>1191</v>
       </c>
     </row>
@@ -11453,13 +11455,13 @@
       <c r="I214" s="1">
         <v>0</v>
       </c>
-      <c r="J214" s="12" t="s">
+      <c r="J214" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K214" s="12" t="s">
+      <c r="K214" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L214" s="11" t="s">
+      <c r="L214" s="12" t="s">
         <v>1196</v>
       </c>
     </row>
@@ -11487,13 +11489,13 @@
       <c r="I215" s="1">
         <v>0</v>
       </c>
-      <c r="J215" s="12" t="s">
+      <c r="J215" s="13" t="s">
         <v>1201</v>
       </c>
-      <c r="K215" s="12" t="s">
+      <c r="K215" s="13" t="s">
         <v>1202</v>
       </c>
-      <c r="L215" s="11" t="s">
+      <c r="L215" s="12" t="s">
         <v>1203</v>
       </c>
     </row>
@@ -11521,13 +11523,13 @@
       <c r="I216" s="3">
         <v>0</v>
       </c>
-      <c r="J216" s="13" t="s">
+      <c r="J216" s="14" t="s">
         <v>1207</v>
       </c>
-      <c r="K216" s="13" t="s">
+      <c r="K216" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L216" s="11" t="s">
+      <c r="L216" s="12" t="s">
         <v>1209</v>
       </c>
       <c r="M216" s="3" t="s">
@@ -11558,13 +11560,13 @@
       <c r="I217" s="1">
         <v>0</v>
       </c>
-      <c r="J217" s="12" t="s">
+      <c r="J217" s="13" t="s">
         <v>1214</v>
       </c>
-      <c r="K217" s="12" t="s">
+      <c r="K217" s="16" t="s">
         <v>1208</v>
       </c>
-      <c r="L217" s="11" t="s">
+      <c r="L217" s="12" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -11592,13 +11594,13 @@
       <c r="I218" s="1">
         <v>0</v>
       </c>
-      <c r="J218" s="12" t="s">
+      <c r="J218" s="13" t="s">
         <v>1219</v>
       </c>
-      <c r="K218" s="12" t="s">
+      <c r="K218" s="16" t="s">
         <v>1208</v>
       </c>
-      <c r="L218" s="11" t="s">
+      <c r="L218" s="12" t="s">
         <v>1220</v>
       </c>
     </row>
@@ -11626,13 +11628,13 @@
       <c r="I219" s="1">
         <v>0</v>
       </c>
-      <c r="J219" s="12" t="s">
+      <c r="J219" s="13" t="s">
         <v>1224</v>
       </c>
-      <c r="K219" s="12" t="s">
+      <c r="K219" s="16" t="s">
         <v>1208</v>
       </c>
-      <c r="L219" s="11" t="s">
+      <c r="L219" s="12" t="s">
         <v>1225</v>
       </c>
     </row>
@@ -11660,13 +11662,13 @@
       <c r="I220" s="1">
         <v>0</v>
       </c>
-      <c r="J220" s="12" t="s">
+      <c r="J220" s="13" t="s">
         <v>1229</v>
       </c>
-      <c r="K220" s="12" t="s">
+      <c r="K220" s="16" t="s">
         <v>1208</v>
       </c>
-      <c r="L220" s="11" t="s">
+      <c r="L220" s="12" t="s">
         <v>1230</v>
       </c>
     </row>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="1231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="1358">
   <si>
     <t>_Id</t>
   </si>
@@ -3752,6 +3752,387 @@
   </si>
   <si>
     <t>10214</t>
+  </si>
+  <si>
+    <t>虚无蝠洞</t>
+  </si>
+  <si>
+    <t>2200-1</t>
+  </si>
+  <si>
+    <t>虚无冰晶，30升阶石</t>
+  </si>
+  <si>
+    <t>202002,106,504,210085,1009,506,202008,202003,507</t>
+  </si>
+  <si>
+    <t>10215</t>
+  </si>
+  <si>
+    <t>虚无骷髅洞</t>
+  </si>
+  <si>
+    <t>2200-2</t>
+  </si>
+  <si>
+    <t>虚无蝠翼，30升阶石</t>
+  </si>
+  <si>
+    <t>10216</t>
+  </si>
+  <si>
+    <t>虚无通道</t>
+  </si>
+  <si>
+    <t>2200-3</t>
+  </si>
+  <si>
+    <t>虚无魂火，30升阶石</t>
+  </si>
+  <si>
+    <t>10217</t>
+  </si>
+  <si>
+    <t>虚无尸洞</t>
+  </si>
+  <si>
+    <t>2200-4</t>
+  </si>
+  <si>
+    <t>虚无腐肉，30升阶石</t>
+  </si>
+  <si>
+    <t>10218</t>
+  </si>
+  <si>
+    <t>虚无蛇谷</t>
+  </si>
+  <si>
+    <t>2200-5</t>
+  </si>
+  <si>
+    <t>虚无蛇胆，30升阶石</t>
+  </si>
+  <si>
+    <t>10219</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>虚无狼山</t>
+  </si>
+  <si>
+    <t>2250-1</t>
+  </si>
+  <si>
+    <t>虚无狼爪，31升阶石</t>
+  </si>
+  <si>
+    <t>202002,106,504,210086,1009,506,202008,202003,507</t>
+  </si>
+  <si>
+    <t>10220</t>
+  </si>
+  <si>
+    <t>虚无沙洞</t>
+  </si>
+  <si>
+    <t>2250-2</t>
+  </si>
+  <si>
+    <t>虚无虫皮，31升阶石</t>
+  </si>
+  <si>
+    <t>10221</t>
+  </si>
+  <si>
+    <t>虚无鹰崖</t>
+  </si>
+  <si>
+    <t>2250-3</t>
+  </si>
+  <si>
+    <t>虚无鹰羽，31升阶石</t>
+  </si>
+  <si>
+    <t>10222</t>
+  </si>
+  <si>
+    <t>虚无虫谷</t>
+  </si>
+  <si>
+    <t>2250-4</t>
+  </si>
+  <si>
+    <t>虚无虫角，31升阶石</t>
+  </si>
+  <si>
+    <t>10223</t>
+  </si>
+  <si>
+    <t>虚无虫洞</t>
+  </si>
+  <si>
+    <t>2250-5</t>
+  </si>
+  <si>
+    <t>虚无蜈膏，31升阶石</t>
+  </si>
+  <si>
+    <t>10224</t>
+  </si>
+  <si>
+    <t>虚无虫穴</t>
+  </si>
+  <si>
+    <t>2300-1</t>
+  </si>
+  <si>
+    <t>虚无虫心，32升阶石</t>
+  </si>
+  <si>
+    <t>202002,106,504,210087,1009,506,202008,202003,507</t>
+  </si>
+  <si>
+    <t>10225</t>
+  </si>
+  <si>
+    <t>虚无虫巢</t>
+  </si>
+  <si>
+    <t>2300-2</t>
+  </si>
+  <si>
+    <t>虚无龙皮，32升阶石</t>
+  </si>
+  <si>
+    <t>10226</t>
+  </si>
+  <si>
+    <t>虚无魔猪厅</t>
+  </si>
+  <si>
+    <t>2300-3</t>
+  </si>
+  <si>
+    <t>虚无猪皮，32升阶石</t>
+  </si>
+  <si>
+    <t>10227</t>
+  </si>
+  <si>
+    <t>虚无魔猪殿</t>
+  </si>
+  <si>
+    <t>2300-4</t>
+  </si>
+  <si>
+    <t>虚无猪心，32升阶石</t>
+  </si>
+  <si>
+    <t>10228</t>
+  </si>
+  <si>
+    <t>虚无桃源</t>
+  </si>
+  <si>
+    <t>2300-5</t>
+  </si>
+  <si>
+    <t>虚无蝎皮，32升阶石</t>
+  </si>
+  <si>
+    <t>10229</t>
+  </si>
+  <si>
+    <t>虚无魔禁地</t>
+  </si>
+  <si>
+    <t>2350-1</t>
+  </si>
+  <si>
+    <t>虚无宝甲，33升阶石</t>
+  </si>
+  <si>
+    <t>202002,106,504,210088,1009,506,202008,202003,507</t>
+  </si>
+  <si>
+    <t>10230</t>
+  </si>
+  <si>
+    <t>虚无魔神殿</t>
+  </si>
+  <si>
+    <t>2350-2</t>
+  </si>
+  <si>
+    <t>虚无号角，33升阶石</t>
+  </si>
+  <si>
+    <t>10231</t>
+  </si>
+  <si>
+    <t>虚无邪禁地</t>
+  </si>
+  <si>
+    <t>2350-3</t>
+  </si>
+  <si>
+    <t>虚无雕像，33升阶石</t>
+  </si>
+  <si>
+    <t>10232</t>
+  </si>
+  <si>
+    <t>虚无邪魔殿</t>
+  </si>
+  <si>
+    <t>2350-4</t>
+  </si>
+  <si>
+    <t>虚无神像，33升阶石</t>
+  </si>
+  <si>
+    <t>10233</t>
+  </si>
+  <si>
+    <t>虚无封魔殿</t>
+  </si>
+  <si>
+    <t>2350-5</t>
+  </si>
+  <si>
+    <t>虚无獠牙，33升阶石</t>
+  </si>
+  <si>
+    <t>10234</t>
+  </si>
+  <si>
+    <t>虚无烈焰殿</t>
+  </si>
+  <si>
+    <t>2400-1</t>
+  </si>
+  <si>
+    <t>虚无树心，34升阶石</t>
+  </si>
+  <si>
+    <t>202002,106,504,210089,1009,506,202008,202003,507</t>
+  </si>
+  <si>
+    <t>10235</t>
+  </si>
+  <si>
+    <t>虚无封邪殿</t>
+  </si>
+  <si>
+    <t>2400-2</t>
+  </si>
+  <si>
+    <t>虚无魔心，34升阶石</t>
+  </si>
+  <si>
+    <t>10236</t>
+  </si>
+  <si>
+    <t>虚无尸魔殿</t>
+  </si>
+  <si>
+    <t>2400-3</t>
+  </si>
+  <si>
+    <t>虚无尸心，34升阶石</t>
+  </si>
+  <si>
+    <t>10237</t>
+  </si>
+  <si>
+    <t>虚无骨魔殿</t>
+  </si>
+  <si>
+    <t>2400-4</t>
+  </si>
+  <si>
+    <t>虚无法杖，34升阶石</t>
+  </si>
+  <si>
+    <t>10238</t>
+  </si>
+  <si>
+    <t>虚无魔牛殿</t>
+  </si>
+  <si>
+    <t>2400-5</t>
+  </si>
+  <si>
+    <t>虚无权杖，34升阶石</t>
+  </si>
+  <si>
+    <t>10239</t>
+  </si>
+  <si>
+    <t>虚无水龙谷</t>
+  </si>
+  <si>
+    <t>2450-1</t>
+  </si>
+  <si>
+    <t>虚无战锤，35升阶石</t>
+  </si>
+  <si>
+    <t>202002,106,504,210090,1009,506,202008,202003,507</t>
+  </si>
+  <si>
+    <t>10240</t>
+  </si>
+  <si>
+    <t>虚无土龙谷</t>
+  </si>
+  <si>
+    <t>2450-2</t>
+  </si>
+  <si>
+    <t>虚无血核，35升阶石</t>
+  </si>
+  <si>
+    <t>10241</t>
+  </si>
+  <si>
+    <t>虚无毒龙谷</t>
+  </si>
+  <si>
+    <t>2450-3</t>
+  </si>
+  <si>
+    <t>虚无魔核，35升阶石</t>
+  </si>
+  <si>
+    <t>10242</t>
+  </si>
+  <si>
+    <t>虚无火龙谷</t>
+  </si>
+  <si>
+    <t>2450-4</t>
+  </si>
+  <si>
+    <t>虚无龙甲，35升阶石</t>
+  </si>
+  <si>
+    <t>10243</t>
+  </si>
+  <si>
+    <t>虚无冰龙谷</t>
+  </si>
+  <si>
+    <t>2450-5</t>
+  </si>
+  <si>
+    <t>虚无龙爪，35升阶石</t>
+  </si>
+  <si>
+    <t>10244</t>
   </si>
 </sst>
 </file>
@@ -4401,7 +4782,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4418,11 +4799,12 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4780,7 +5162,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:M221"/>
+  <dimension ref="A3:M250"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
@@ -6096,10 +6478,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="12" t="s">
+      <c r="J46" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="12" t="s">
+      <c r="K46" s="14" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -6125,10 +6507,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="12" t="s">
+      <c r="J47" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="12" t="s">
+      <c r="K47" s="14" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -6154,10 +6536,10 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="12" t="s">
+      <c r="J48" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="12" t="s">
+      <c r="K48" s="14" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
@@ -6183,10 +6565,10 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="12" t="s">
+      <c r="J49" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="12" t="s">
+      <c r="K49" s="14" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
@@ -6212,10 +6594,10 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="12" t="s">
+      <c r="J50" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="12" t="s">
+      <c r="K50" s="14" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
@@ -6244,10 +6626,10 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="12" t="s">
+      <c r="J51" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="12" t="s">
+      <c r="K51" s="14" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
@@ -6273,10 +6655,10 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="12" t="s">
+      <c r="J52" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="12" t="s">
+      <c r="K52" s="14" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -6302,10 +6684,10 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="12" t="s">
+      <c r="J53" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="12" t="s">
+      <c r="K53" s="14" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
@@ -6331,10 +6713,10 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="12" t="s">
+      <c r="J54" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="12" t="s">
+      <c r="K54" s="14" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
@@ -6360,10 +6742,10 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="12" t="s">
+      <c r="J55" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="12" t="s">
+      <c r="K55" s="14" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -6392,10 +6774,10 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="12" t="s">
+      <c r="J56" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="12" t="s">
+      <c r="K56" s="14" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
@@ -6424,10 +6806,10 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="12" t="s">
+      <c r="J57" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="12" t="s">
+      <c r="K57" s="14" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
@@ -6456,10 +6838,10 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="12" t="s">
+      <c r="J58" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="12" t="s">
+      <c r="K58" s="14" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -6488,10 +6870,10 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="12" t="s">
+      <c r="J59" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="12" t="s">
+      <c r="K59" s="14" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
@@ -6520,10 +6902,10 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="12" t="s">
+      <c r="J60" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="12" t="s">
+      <c r="K60" s="14" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -6553,10 +6935,10 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="13" t="s">
+      <c r="J61" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="13" t="s">
+      <c r="K61" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -6586,10 +6968,10 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="13" t="s">
+      <c r="J62" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="13" t="s">
+      <c r="K62" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -6619,10 +7001,10 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="13" t="s">
+      <c r="J63" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="13" t="s">
+      <c r="K63" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
@@ -6652,10 +7034,10 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="13" t="s">
+      <c r="J64" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="13" t="s">
+      <c r="K64" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
@@ -6685,10 +7067,10 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="13" t="s">
+      <c r="J65" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="13" t="s">
+      <c r="K65" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
@@ -6717,10 +7099,10 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="13" t="s">
+      <c r="J66" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="13" t="s">
+      <c r="K66" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
@@ -6749,10 +7131,10 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="13" t="s">
+      <c r="J67" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="13" t="s">
+      <c r="K67" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
@@ -6781,10 +7163,10 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="13" t="s">
+      <c r="J68" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="13" t="s">
+      <c r="K68" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -6813,10 +7195,10 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="13" t="s">
+      <c r="J69" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="13" t="s">
+      <c r="K69" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
@@ -6845,10 +7227,10 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="13" t="s">
+      <c r="J70" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="13" t="s">
+      <c r="K70" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
@@ -6877,10 +7259,10 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="13" t="s">
+      <c r="J71" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="13" t="s">
+      <c r="K71" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -6909,10 +7291,10 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="13" t="s">
+      <c r="J72" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="13" t="s">
+      <c r="K72" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -6941,10 +7323,10 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="13" t="s">
+      <c r="J73" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="13" t="s">
+      <c r="K73" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -6973,10 +7355,10 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="13" t="s">
+      <c r="J74" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="13" t="s">
+      <c r="K74" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
@@ -7005,10 +7387,10 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="13" t="s">
+      <c r="J75" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="13" t="s">
+      <c r="K75" s="15" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
@@ -7037,10 +7419,10 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="13" t="s">
+      <c r="J76" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="13" t="s">
+      <c r="K76" s="15" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
@@ -7069,10 +7451,10 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="13" t="s">
+      <c r="J77" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="13" t="s">
+      <c r="K77" s="15" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
@@ -7101,10 +7483,10 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="13" t="s">
+      <c r="J78" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="13" t="s">
+      <c r="K78" s="15" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
@@ -7133,10 +7515,10 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="13" t="s">
+      <c r="J79" s="15" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="13" t="s">
+      <c r="K79" s="15" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
@@ -7165,10 +7547,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="13" t="s">
+      <c r="J80" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="13" t="s">
+      <c r="K80" s="15" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -7197,10 +7579,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="13" t="s">
+      <c r="J81" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="13" t="s">
+      <c r="K81" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -7229,10 +7611,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="13" t="s">
+      <c r="J82" s="15" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="13" t="s">
+      <c r="K82" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -7261,10 +7643,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="13" t="s">
+      <c r="J83" s="15" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="13" t="s">
+      <c r="K83" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -7293,10 +7675,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="13" t="s">
+      <c r="J84" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="13" t="s">
+      <c r="K84" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -7325,10 +7707,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="13" t="s">
+      <c r="J85" s="15" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="13" t="s">
+      <c r="K85" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -7357,10 +7739,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="13" t="s">
+      <c r="J86" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="13" t="s">
+      <c r="K86" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -7389,10 +7771,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="13" t="s">
+      <c r="J87" s="15" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="13" t="s">
+      <c r="K87" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -7421,10 +7803,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="13" t="s">
+      <c r="J88" s="15" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="13" t="s">
+      <c r="K88" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -7453,10 +7835,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="13" t="s">
+      <c r="J89" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="13" t="s">
+      <c r="K89" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -7485,10 +7867,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="13" t="s">
+      <c r="J90" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="13" t="s">
+      <c r="K90" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -7517,10 +7899,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="13" t="s">
+      <c r="J91" s="15" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="13" t="s">
+      <c r="K91" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -7549,10 +7931,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="13" t="s">
+      <c r="J92" s="15" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="13" t="s">
+      <c r="K92" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -7581,10 +7963,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="13" t="s">
+      <c r="J93" s="15" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="13" t="s">
+      <c r="K93" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -7613,10 +7995,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="13" t="s">
+      <c r="J94" s="15" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="13" t="s">
+      <c r="K94" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -7645,10 +8027,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="13" t="s">
+      <c r="J95" s="15" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="13" t="s">
+      <c r="K95" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -7677,10 +8059,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="13" t="s">
+      <c r="J96" s="15" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="13" t="s">
+      <c r="K96" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -7709,10 +8091,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="13" t="s">
+      <c r="J97" s="15" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="13" t="s">
+      <c r="K97" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -7741,10 +8123,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="13" t="s">
+      <c r="J98" s="15" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="13" t="s">
+      <c r="K98" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -7773,10 +8155,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="13" t="s">
+      <c r="J99" s="15" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="13" t="s">
+      <c r="K99" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -7805,10 +8187,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="13" t="s">
+      <c r="J100" s="15" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="13" t="s">
+      <c r="K100" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -7837,10 +8219,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="13" t="s">
+      <c r="J101" s="15" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="13" t="s">
+      <c r="K101" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -7869,10 +8251,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="13" t="s">
+      <c r="J102" s="15" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="13" t="s">
+      <c r="K102" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -7901,10 +8283,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="13" t="s">
+      <c r="J103" s="15" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="13" t="s">
+      <c r="K103" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -7933,10 +8315,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="13" t="s">
+      <c r="J104" s="15" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="13" t="s">
+      <c r="K104" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -7965,10 +8347,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="13" t="s">
+      <c r="J105" s="15" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="13" t="s">
+      <c r="K105" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -7997,10 +8379,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="13" t="s">
+      <c r="J106" s="15" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="13" t="s">
+      <c r="K106" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -8029,10 +8411,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="13" t="s">
+      <c r="J107" s="15" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="13" t="s">
+      <c r="K107" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -8061,10 +8443,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="13" t="s">
+      <c r="J108" s="15" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="13" t="s">
+      <c r="K108" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -8093,10 +8475,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="13" t="s">
+      <c r="J109" s="15" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="13" t="s">
+      <c r="K109" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -8125,10 +8507,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="13" t="s">
+      <c r="J110" s="15" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="13" t="s">
+      <c r="K110" s="15" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -8157,10 +8539,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="13" t="s">
+      <c r="J111" s="15" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="13" t="s">
+      <c r="K111" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -8189,10 +8571,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="13" t="s">
+      <c r="J112" s="15" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="13" t="s">
+      <c r="K112" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -8221,10 +8603,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="13" t="s">
+      <c r="J113" s="15" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="13" t="s">
+      <c r="K113" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -8253,10 +8635,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="13" t="s">
+      <c r="J114" s="15" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="13" t="s">
+      <c r="K114" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -8285,10 +8667,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="13" t="s">
+      <c r="J115" s="15" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="13" t="s">
+      <c r="K115" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -8317,10 +8699,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="13" t="s">
+      <c r="J116" s="15" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="13" t="s">
+      <c r="K116" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -8349,10 +8731,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="13" t="s">
+      <c r="J117" s="15" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="13" t="s">
+      <c r="K117" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -8381,10 +8763,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="13" t="s">
+      <c r="J118" s="15" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="13" t="s">
+      <c r="K118" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -8413,10 +8795,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="13" t="s">
+      <c r="J119" s="15" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="13" t="s">
+      <c r="K119" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -8445,10 +8827,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="13" t="s">
+      <c r="J120" s="15" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="13" t="s">
+      <c r="K120" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -8477,10 +8859,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="13" t="s">
+      <c r="J121" s="15" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="13" t="s">
+      <c r="K121" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -8509,10 +8891,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="13" t="s">
+      <c r="J122" s="15" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="13" t="s">
+      <c r="K122" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -8541,10 +8923,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="13" t="s">
+      <c r="J123" s="15" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="13" t="s">
+      <c r="K123" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -8573,10 +8955,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="13" t="s">
+      <c r="J124" s="15" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="13" t="s">
+      <c r="K124" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -8605,10 +8987,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="13" t="s">
+      <c r="J125" s="15" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="13" t="s">
+      <c r="K125" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -8637,10 +9019,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="13" t="s">
+      <c r="J126" s="15" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="13" t="s">
+      <c r="K126" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -8669,10 +9051,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="13" t="s">
+      <c r="J127" s="15" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="13" t="s">
+      <c r="K127" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -8701,10 +9083,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="13" t="s">
+      <c r="J128" s="15" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="13" t="s">
+      <c r="K128" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -8733,10 +9115,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="13" t="s">
+      <c r="J129" s="15" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="13" t="s">
+      <c r="K129" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -8765,10 +9147,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="13" t="s">
+      <c r="J130" s="15" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="13" t="s">
+      <c r="K130" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -8797,10 +9179,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="13" t="s">
+      <c r="J131" s="15" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="13" t="s">
+      <c r="K131" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -8829,10 +9211,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="13" t="s">
+      <c r="J132" s="15" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="13" t="s">
+      <c r="K132" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -8861,10 +9243,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="13" t="s">
+      <c r="J133" s="15" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="13" t="s">
+      <c r="K133" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -8893,10 +9275,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="13" t="s">
+      <c r="J134" s="15" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="13" t="s">
+      <c r="K134" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -8925,10 +9307,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="13" t="s">
+      <c r="J135" s="15" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="13" t="s">
+      <c r="K135" s="15" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -8957,10 +9339,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="13" t="s">
+      <c r="J136" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="13" t="s">
+      <c r="K136" s="15" t="s">
         <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -8989,10 +9371,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="13" t="s">
+      <c r="J137" s="15" t="s">
         <v>782</v>
       </c>
-      <c r="K137" s="13" t="s">
+      <c r="K137" s="15" t="s">
         <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -9021,10 +9403,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="13" t="s">
+      <c r="J138" s="15" t="s">
         <v>788</v>
       </c>
-      <c r="K138" s="13" t="s">
+      <c r="K138" s="15" t="s">
         <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -9053,10 +9435,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="13" t="s">
+      <c r="J139" s="15" t="s">
         <v>794</v>
       </c>
-      <c r="K139" s="13" t="s">
+      <c r="K139" s="15" t="s">
         <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -9085,10 +9467,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="13" t="s">
+      <c r="J140" s="15" t="s">
         <v>800</v>
       </c>
-      <c r="K140" s="13" t="s">
+      <c r="K140" s="15" t="s">
         <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -9117,10 +9499,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="13" t="s">
+      <c r="J141" s="15" t="s">
         <v>806</v>
       </c>
-      <c r="K141" s="13" t="s">
+      <c r="K141" s="15" t="s">
         <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -9149,10 +9531,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="13" t="s">
+      <c r="J142" s="15" t="s">
         <v>812</v>
       </c>
-      <c r="K142" s="13" t="s">
+      <c r="K142" s="15" t="s">
         <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -9181,10 +9563,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="13" t="s">
+      <c r="J143" s="15" t="s">
         <v>818</v>
       </c>
-      <c r="K143" s="13" t="s">
+      <c r="K143" s="15" t="s">
         <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -9213,10 +9595,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="13" t="s">
+      <c r="J144" s="15" t="s">
         <v>824</v>
       </c>
-      <c r="K144" s="13" t="s">
+      <c r="K144" s="15" t="s">
         <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -9245,10 +9627,10 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="13" t="s">
+      <c r="J145" s="15" t="s">
         <v>830</v>
       </c>
-      <c r="K145" s="13" t="s">
+      <c r="K145" s="15" t="s">
         <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
@@ -9277,13 +9659,13 @@
       <c r="I146" s="3">
         <v>0</v>
       </c>
-      <c r="J146" s="14" t="s">
+      <c r="J146" s="16" t="s">
         <v>836</v>
       </c>
-      <c r="K146" s="14" t="s">
+      <c r="K146" s="16" t="s">
         <v>776</v>
       </c>
-      <c r="L146" s="14" t="s">
+      <c r="L146" s="16" t="s">
         <v>837</v>
       </c>
     </row>
@@ -9309,13 +9691,13 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="13" t="s">
+      <c r="J147" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="K147" s="13" t="s">
+      <c r="K147" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L147" s="12" t="s">
+      <c r="L147" s="14" t="s">
         <v>842</v>
       </c>
     </row>
@@ -9341,13 +9723,13 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="13" t="s">
+      <c r="J148" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="K148" s="13" t="s">
+      <c r="K148" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L148" s="12" t="s">
+      <c r="L148" s="14" t="s">
         <v>847</v>
       </c>
     </row>
@@ -9373,13 +9755,13 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="13" t="s">
+      <c r="J149" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="K149" s="13" t="s">
+      <c r="K149" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L149" s="12" t="s">
+      <c r="L149" s="14" t="s">
         <v>852</v>
       </c>
     </row>
@@ -9405,13 +9787,13 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="13" t="s">
+      <c r="J150" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="K150" s="13" t="s">
+      <c r="K150" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L150" s="12" t="s">
+      <c r="L150" s="14" t="s">
         <v>857</v>
       </c>
     </row>
@@ -9437,13 +9819,13 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="13" t="s">
+      <c r="J151" s="15" t="s">
         <v>862</v>
       </c>
-      <c r="K151" s="13" t="s">
+      <c r="K151" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L151" s="12" t="s">
+      <c r="L151" s="14" t="s">
         <v>863</v>
       </c>
     </row>
@@ -9469,13 +9851,13 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="13" t="s">
+      <c r="J152" s="15" t="s">
         <v>862</v>
       </c>
-      <c r="K152" s="13" t="s">
+      <c r="K152" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L152" s="12" t="s">
+      <c r="L152" s="14" t="s">
         <v>868</v>
       </c>
     </row>
@@ -9501,13 +9883,13 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="13" t="s">
+      <c r="J153" s="15" t="s">
         <v>862</v>
       </c>
-      <c r="K153" s="13" t="s">
+      <c r="K153" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L153" s="12" t="s">
+      <c r="L153" s="14" t="s">
         <v>873</v>
       </c>
     </row>
@@ -9533,13 +9915,13 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="13" t="s">
+      <c r="J154" s="15" t="s">
         <v>862</v>
       </c>
-      <c r="K154" s="13" t="s">
+      <c r="K154" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L154" s="12" t="s">
+      <c r="L154" s="14" t="s">
         <v>878</v>
       </c>
     </row>
@@ -9565,13 +9947,13 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="13" t="s">
+      <c r="J155" s="15" t="s">
         <v>862</v>
       </c>
-      <c r="K155" s="13" t="s">
+      <c r="K155" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L155" s="12" t="s">
+      <c r="L155" s="14" t="s">
         <v>883</v>
       </c>
     </row>
@@ -9597,13 +9979,13 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="13" t="s">
+      <c r="J156" s="15" t="s">
         <v>888</v>
       </c>
-      <c r="K156" s="13" t="s">
+      <c r="K156" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L156" s="12" t="s">
+      <c r="L156" s="14" t="s">
         <v>889</v>
       </c>
     </row>
@@ -9629,13 +10011,13 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="13" t="s">
+      <c r="J157" s="15" t="s">
         <v>888</v>
       </c>
-      <c r="K157" s="13" t="s">
+      <c r="K157" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L157" s="12" t="s">
+      <c r="L157" s="14" t="s">
         <v>894</v>
       </c>
     </row>
@@ -9661,13 +10043,13 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="13" t="s">
+      <c r="J158" s="15" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="13" t="s">
+      <c r="K158" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L158" s="12" t="s">
+      <c r="L158" s="14" t="s">
         <v>899</v>
       </c>
     </row>
@@ -9693,13 +10075,13 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="13" t="s">
+      <c r="J159" s="15" t="s">
         <v>888</v>
       </c>
-      <c r="K159" s="13" t="s">
+      <c r="K159" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L159" s="12" t="s">
+      <c r="L159" s="14" t="s">
         <v>904</v>
       </c>
     </row>
@@ -9725,13 +10107,13 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="13" t="s">
+      <c r="J160" s="15" t="s">
         <v>888</v>
       </c>
-      <c r="K160" s="13" t="s">
+      <c r="K160" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L160" s="12" t="s">
+      <c r="L160" s="14" t="s">
         <v>909</v>
       </c>
     </row>
@@ -9757,13 +10139,13 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="13" t="s">
+      <c r="J161" s="15" t="s">
         <v>914</v>
       </c>
-      <c r="K161" s="13" t="s">
+      <c r="K161" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L161" s="12" t="s">
+      <c r="L161" s="14" t="s">
         <v>915</v>
       </c>
     </row>
@@ -9789,13 +10171,13 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="13" t="s">
+      <c r="J162" s="15" t="s">
         <v>914</v>
       </c>
-      <c r="K162" s="13" t="s">
+      <c r="K162" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L162" s="12" t="s">
+      <c r="L162" s="14" t="s">
         <v>920</v>
       </c>
     </row>
@@ -9821,13 +10203,13 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="13" t="s">
+      <c r="J163" s="15" t="s">
         <v>914</v>
       </c>
-      <c r="K163" s="13" t="s">
+      <c r="K163" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L163" s="12" t="s">
+      <c r="L163" s="14" t="s">
         <v>925</v>
       </c>
     </row>
@@ -9853,13 +10235,13 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="13" t="s">
+      <c r="J164" s="15" t="s">
         <v>914</v>
       </c>
-      <c r="K164" s="13" t="s">
+      <c r="K164" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L164" s="12" t="s">
+      <c r="L164" s="14" t="s">
         <v>930</v>
       </c>
     </row>
@@ -9885,13 +10267,13 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="13" t="s">
+      <c r="J165" s="15" t="s">
         <v>914</v>
       </c>
-      <c r="K165" s="13" t="s">
+      <c r="K165" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L165" s="12" t="s">
+      <c r="L165" s="14" t="s">
         <v>935</v>
       </c>
     </row>
@@ -9917,13 +10299,13 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="13" t="s">
+      <c r="J166" s="15" t="s">
         <v>940</v>
       </c>
-      <c r="K166" s="13" t="s">
+      <c r="K166" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L166" s="12" t="s">
+      <c r="L166" s="14" t="s">
         <v>941</v>
       </c>
     </row>
@@ -9949,13 +10331,13 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="13" t="s">
+      <c r="J167" s="15" t="s">
         <v>940</v>
       </c>
-      <c r="K167" s="13" t="s">
+      <c r="K167" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L167" s="12" t="s">
+      <c r="L167" s="14" t="s">
         <v>946</v>
       </c>
     </row>
@@ -9981,13 +10363,13 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="13" t="s">
+      <c r="J168" s="15" t="s">
         <v>940</v>
       </c>
-      <c r="K168" s="13" t="s">
+      <c r="K168" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L168" s="12" t="s">
+      <c r="L168" s="14" t="s">
         <v>951</v>
       </c>
     </row>
@@ -10013,13 +10395,13 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="13" t="s">
+      <c r="J169" s="15" t="s">
         <v>940</v>
       </c>
-      <c r="K169" s="13" t="s">
+      <c r="K169" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L169" s="12" t="s">
+      <c r="L169" s="14" t="s">
         <v>956</v>
       </c>
     </row>
@@ -10045,13 +10427,13 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="13" t="s">
+      <c r="J170" s="15" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="13" t="s">
+      <c r="K170" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L170" s="12" t="s">
+      <c r="L170" s="14" t="s">
         <v>961</v>
       </c>
     </row>
@@ -10077,13 +10459,13 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="13" t="s">
+      <c r="J171" s="15" t="s">
         <v>966</v>
       </c>
-      <c r="K171" s="13" t="s">
+      <c r="K171" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L171" s="12" t="s">
+      <c r="L171" s="14" t="s">
         <v>967</v>
       </c>
     </row>
@@ -10109,13 +10491,13 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="13" t="s">
+      <c r="J172" s="15" t="s">
         <v>966</v>
       </c>
-      <c r="K172" s="13" t="s">
+      <c r="K172" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L172" s="12" t="s">
+      <c r="L172" s="14" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10141,13 +10523,13 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="13" t="s">
+      <c r="J173" s="15" t="s">
         <v>966</v>
       </c>
-      <c r="K173" s="13" t="s">
+      <c r="K173" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L173" s="12" t="s">
+      <c r="L173" s="14" t="s">
         <v>977</v>
       </c>
     </row>
@@ -10173,13 +10555,13 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="13" t="s">
+      <c r="J174" s="15" t="s">
         <v>966</v>
       </c>
-      <c r="K174" s="13" t="s">
+      <c r="K174" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L174" s="12" t="s">
+      <c r="L174" s="14" t="s">
         <v>982</v>
       </c>
     </row>
@@ -10205,13 +10587,13 @@
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="13" t="s">
+      <c r="J175" s="15" t="s">
         <v>966</v>
       </c>
-      <c r="K175" s="13" t="s">
+      <c r="K175" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L175" s="12" t="s">
+      <c r="L175" s="14" t="s">
         <v>987</v>
       </c>
     </row>
@@ -10237,13 +10619,13 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="13" t="s">
+      <c r="J176" s="15" t="s">
         <v>992</v>
       </c>
-      <c r="K176" s="13" t="s">
+      <c r="K176" s="15" t="s">
         <v>993</v>
       </c>
-      <c r="L176" s="12" t="s">
+      <c r="L176" s="14" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10269,13 +10651,13 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="13" t="s">
+      <c r="J177" s="15" t="s">
         <v>992</v>
       </c>
-      <c r="K177" s="13" t="s">
+      <c r="K177" s="15" t="s">
         <v>993</v>
       </c>
-      <c r="L177" s="12" t="s">
+      <c r="L177" s="14" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10301,13 +10683,13 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="13" t="s">
+      <c r="J178" s="15" t="s">
         <v>992</v>
       </c>
-      <c r="K178" s="13" t="s">
+      <c r="K178" s="15" t="s">
         <v>993</v>
       </c>
-      <c r="L178" s="12" t="s">
+      <c r="L178" s="14" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -10333,13 +10715,13 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="13" t="s">
+      <c r="J179" s="15" t="s">
         <v>992</v>
       </c>
-      <c r="K179" s="13" t="s">
+      <c r="K179" s="15" t="s">
         <v>993</v>
       </c>
-      <c r="L179" s="12" t="s">
+      <c r="L179" s="14" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -10365,13 +10747,13 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="13" t="s">
+      <c r="J180" s="15" t="s">
         <v>992</v>
       </c>
-      <c r="K180" s="13" t="s">
+      <c r="K180" s="15" t="s">
         <v>993</v>
       </c>
-      <c r="L180" s="12" t="s">
+      <c r="L180" s="14" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -10397,13 +10779,13 @@
       <c r="I181" s="3">
         <v>0</v>
       </c>
-      <c r="J181" s="14" t="s">
+      <c r="J181" s="16" t="s">
         <v>1019</v>
       </c>
-      <c r="K181" s="14" t="s">
+      <c r="K181" s="16" t="s">
         <v>1020</v>
       </c>
-      <c r="L181" s="12" t="s">
+      <c r="L181" s="14" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -10429,13 +10811,13 @@
       <c r="I182" s="1">
         <v>0</v>
       </c>
-      <c r="J182" s="13" t="s">
+      <c r="J182" s="15" t="s">
         <v>1026</v>
       </c>
-      <c r="K182" s="13" t="s">
+      <c r="K182" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L182" s="12" t="s">
+      <c r="L182" s="14" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -10461,13 +10843,13 @@
       <c r="I183" s="1">
         <v>0</v>
       </c>
-      <c r="J183" s="13" t="s">
+      <c r="J183" s="15" t="s">
         <v>1032</v>
       </c>
-      <c r="K183" s="13" t="s">
+      <c r="K183" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L183" s="12" t="s">
+      <c r="L183" s="14" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10493,13 +10875,13 @@
       <c r="I184" s="1">
         <v>0</v>
       </c>
-      <c r="J184" s="13" t="s">
+      <c r="J184" s="15" t="s">
         <v>1038</v>
       </c>
-      <c r="K184" s="13" t="s">
+      <c r="K184" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L184" s="12" t="s">
+      <c r="L184" s="14" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10525,13 +10907,13 @@
       <c r="I185" s="1">
         <v>0</v>
       </c>
-      <c r="J185" s="13" t="s">
+      <c r="J185" s="15" t="s">
         <v>1044</v>
       </c>
-      <c r="K185" s="13" t="s">
+      <c r="K185" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L185" s="12" t="s">
+      <c r="L185" s="14" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -10557,13 +10939,13 @@
       <c r="I186" s="1">
         <v>0</v>
       </c>
-      <c r="J186" s="13" t="s">
+      <c r="J186" s="15" t="s">
         <v>1050</v>
       </c>
-      <c r="K186" s="13" t="s">
+      <c r="K186" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L186" s="12" t="s">
+      <c r="L186" s="14" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -10589,13 +10971,13 @@
       <c r="I187" s="1">
         <v>0</v>
       </c>
-      <c r="J187" s="13" t="s">
+      <c r="J187" s="15" t="s">
         <v>1050</v>
       </c>
-      <c r="K187" s="13" t="s">
+      <c r="K187" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L187" s="12" t="s">
+      <c r="L187" s="14" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -10621,13 +11003,13 @@
       <c r="I188" s="1">
         <v>0</v>
       </c>
-      <c r="J188" s="13" t="s">
+      <c r="J188" s="15" t="s">
         <v>1050</v>
       </c>
-      <c r="K188" s="13" t="s">
+      <c r="K188" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L188" s="12" t="s">
+      <c r="L188" s="14" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -10653,13 +11035,13 @@
       <c r="I189" s="1">
         <v>0</v>
       </c>
-      <c r="J189" s="13" t="s">
+      <c r="J189" s="15" t="s">
         <v>1050</v>
       </c>
-      <c r="K189" s="13" t="s">
+      <c r="K189" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L189" s="12" t="s">
+      <c r="L189" s="14" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -10685,13 +11067,13 @@
       <c r="I190" s="1">
         <v>0</v>
       </c>
-      <c r="J190" s="13" t="s">
+      <c r="J190" s="15" t="s">
         <v>1050</v>
       </c>
-      <c r="K190" s="13" t="s">
+      <c r="K190" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L190" s="12" t="s">
+      <c r="L190" s="14" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -10717,13 +11099,13 @@
       <c r="I191" s="1">
         <v>0</v>
       </c>
-      <c r="J191" s="13" t="s">
+      <c r="J191" s="15" t="s">
         <v>1076</v>
       </c>
-      <c r="K191" s="13" t="s">
+      <c r="K191" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L191" s="12" t="s">
+      <c r="L191" s="14" t="s">
         <v>1077</v>
       </c>
     </row>
@@ -10749,13 +11131,13 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-      <c r="J192" s="13" t="s">
+      <c r="J192" s="15" t="s">
         <v>1076</v>
       </c>
-      <c r="K192" s="13" t="s">
+      <c r="K192" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L192" s="12" t="s">
+      <c r="L192" s="14" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -10781,13 +11163,13 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-      <c r="J193" s="13" t="s">
+      <c r="J193" s="15" t="s">
         <v>1076</v>
       </c>
-      <c r="K193" s="13" t="s">
+      <c r="K193" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L193" s="12" t="s">
+      <c r="L193" s="14" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -10813,13 +11195,13 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-      <c r="J194" s="13" t="s">
+      <c r="J194" s="15" t="s">
         <v>1076</v>
       </c>
-      <c r="K194" s="13" t="s">
+      <c r="K194" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L194" s="12" t="s">
+      <c r="L194" s="14" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -10845,13 +11227,13 @@
       <c r="I195" s="1">
         <v>0</v>
       </c>
-      <c r="J195" s="13" t="s">
+      <c r="J195" s="15" t="s">
         <v>1076</v>
       </c>
-      <c r="K195" s="13" t="s">
+      <c r="K195" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L195" s="12" t="s">
+      <c r="L195" s="14" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -10877,13 +11259,13 @@
       <c r="I196" s="4">
         <v>0</v>
       </c>
-      <c r="J196" s="15" t="s">
+      <c r="J196" s="17" t="s">
         <v>1102</v>
       </c>
-      <c r="K196" s="15" t="s">
+      <c r="K196" s="17" t="s">
         <v>1020</v>
       </c>
-      <c r="L196" s="15" t="s">
+      <c r="L196" s="17" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -10909,13 +11291,13 @@
       <c r="I197" s="1">
         <v>0</v>
       </c>
-      <c r="J197" s="13" t="s">
+      <c r="J197" s="15" t="s">
         <v>1102</v>
       </c>
-      <c r="K197" s="13" t="s">
+      <c r="K197" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L197" s="12" t="s">
+      <c r="L197" s="14" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -10941,13 +11323,13 @@
       <c r="I198" s="1">
         <v>0</v>
       </c>
-      <c r="J198" s="13" t="s">
+      <c r="J198" s="15" t="s">
         <v>1102</v>
       </c>
-      <c r="K198" s="13" t="s">
+      <c r="K198" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L198" s="12" t="s">
+      <c r="L198" s="14" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -10973,13 +11355,13 @@
       <c r="I199" s="1">
         <v>0</v>
       </c>
-      <c r="J199" s="13" t="s">
+      <c r="J199" s="15" t="s">
         <v>1102</v>
       </c>
-      <c r="K199" s="13" t="s">
+      <c r="K199" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L199" s="12" t="s">
+      <c r="L199" s="14" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -11005,13 +11387,13 @@
       <c r="I200" s="1">
         <v>0</v>
       </c>
-      <c r="J200" s="13" t="s">
+      <c r="J200" s="15" t="s">
         <v>1102</v>
       </c>
-      <c r="K200" s="13" t="s">
+      <c r="K200" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L200" s="12" t="s">
+      <c r="L200" s="14" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -11037,13 +11419,13 @@
       <c r="I201" s="1">
         <v>0</v>
       </c>
-      <c r="J201" s="13" t="s">
+      <c r="J201" s="15" t="s">
         <v>1128</v>
       </c>
-      <c r="K201" s="13" t="s">
+      <c r="K201" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L201" s="12" t="s">
+      <c r="L201" s="14" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -11069,13 +11451,13 @@
       <c r="I202" s="1">
         <v>0</v>
       </c>
-      <c r="J202" s="13" t="s">
+      <c r="J202" s="15" t="s">
         <v>1128</v>
       </c>
-      <c r="K202" s="13" t="s">
+      <c r="K202" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L202" s="12" t="s">
+      <c r="L202" s="14" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -11101,13 +11483,13 @@
       <c r="I203" s="1">
         <v>0</v>
       </c>
-      <c r="J203" s="13" t="s">
+      <c r="J203" s="15" t="s">
         <v>1128</v>
       </c>
-      <c r="K203" s="13" t="s">
+      <c r="K203" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L203" s="12" t="s">
+      <c r="L203" s="14" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -11133,13 +11515,13 @@
       <c r="I204" s="1">
         <v>0</v>
       </c>
-      <c r="J204" s="13" t="s">
+      <c r="J204" s="15" t="s">
         <v>1128</v>
       </c>
-      <c r="K204" s="13" t="s">
+      <c r="K204" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L204" s="12" t="s">
+      <c r="L204" s="14" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -11165,13 +11547,13 @@
       <c r="I205" s="1">
         <v>0</v>
       </c>
-      <c r="J205" s="13" t="s">
+      <c r="J205" s="15" t="s">
         <v>1128</v>
       </c>
-      <c r="K205" s="13" t="s">
+      <c r="K205" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L205" s="12" t="s">
+      <c r="L205" s="14" t="s">
         <v>1149</v>
       </c>
     </row>
@@ -11197,13 +11579,13 @@
       <c r="I206" s="1">
         <v>0</v>
       </c>
-      <c r="J206" s="13" t="s">
+      <c r="J206" s="15" t="s">
         <v>1154</v>
       </c>
-      <c r="K206" s="13" t="s">
+      <c r="K206" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L206" s="12" t="s">
+      <c r="L206" s="14" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -11229,13 +11611,13 @@
       <c r="I207" s="1">
         <v>0</v>
       </c>
-      <c r="J207" s="13" t="s">
+      <c r="J207" s="15" t="s">
         <v>1154</v>
       </c>
-      <c r="K207" s="13" t="s">
+      <c r="K207" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L207" s="12" t="s">
+      <c r="L207" s="14" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -11261,13 +11643,13 @@
       <c r="I208" s="1">
         <v>0</v>
       </c>
-      <c r="J208" s="13" t="s">
+      <c r="J208" s="15" t="s">
         <v>1154</v>
       </c>
-      <c r="K208" s="13" t="s">
+      <c r="K208" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L208" s="12" t="s">
+      <c r="L208" s="14" t="s">
         <v>1165</v>
       </c>
     </row>
@@ -11293,13 +11675,13 @@
       <c r="I209" s="1">
         <v>0</v>
       </c>
-      <c r="J209" s="13" t="s">
+      <c r="J209" s="15" t="s">
         <v>1154</v>
       </c>
-      <c r="K209" s="13" t="s">
+      <c r="K209" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L209" s="12" t="s">
+      <c r="L209" s="14" t="s">
         <v>1170</v>
       </c>
     </row>
@@ -11325,13 +11707,13 @@
       <c r="I210" s="1">
         <v>0</v>
       </c>
-      <c r="J210" s="13" t="s">
+      <c r="J210" s="15" t="s">
         <v>1154</v>
       </c>
-      <c r="K210" s="13" t="s">
+      <c r="K210" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L210" s="12" t="s">
+      <c r="L210" s="14" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -11357,13 +11739,13 @@
       <c r="I211" s="1">
         <v>0</v>
       </c>
-      <c r="J211" s="13" t="s">
+      <c r="J211" s="15" t="s">
         <v>1180</v>
       </c>
-      <c r="K211" s="13" t="s">
+      <c r="K211" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L211" s="12" t="s">
+      <c r="L211" s="14" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -11389,13 +11771,13 @@
       <c r="I212" s="1">
         <v>0</v>
       </c>
-      <c r="J212" s="13" t="s">
+      <c r="J212" s="15" t="s">
         <v>1180</v>
       </c>
-      <c r="K212" s="13" t="s">
+      <c r="K212" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L212" s="12" t="s">
+      <c r="L212" s="14" t="s">
         <v>1186</v>
       </c>
     </row>
@@ -11421,13 +11803,13 @@
       <c r="I213" s="1">
         <v>0</v>
       </c>
-      <c r="J213" s="13" t="s">
+      <c r="J213" s="15" t="s">
         <v>1180</v>
       </c>
-      <c r="K213" s="13" t="s">
+      <c r="K213" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L213" s="12" t="s">
+      <c r="L213" s="14" t="s">
         <v>1191</v>
       </c>
     </row>
@@ -11455,13 +11837,13 @@
       <c r="I214" s="1">
         <v>0</v>
       </c>
-      <c r="J214" s="13" t="s">
+      <c r="J214" s="15" t="s">
         <v>1180</v>
       </c>
-      <c r="K214" s="13" t="s">
+      <c r="K214" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L214" s="12" t="s">
+      <c r="L214" s="14" t="s">
         <v>1196</v>
       </c>
     </row>
@@ -11489,13 +11871,13 @@
       <c r="I215" s="1">
         <v>0</v>
       </c>
-      <c r="J215" s="13" t="s">
+      <c r="J215" s="15" t="s">
         <v>1201</v>
       </c>
-      <c r="K215" s="13" t="s">
+      <c r="K215" s="15" t="s">
         <v>1202</v>
       </c>
-      <c r="L215" s="12" t="s">
+      <c r="L215" s="14" t="s">
         <v>1203</v>
       </c>
     </row>
@@ -11509,10 +11891,10 @@
         <v>1204</v>
       </c>
       <c r="E216" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F216" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G216" s="10" t="s">
         <v>1205</v>
@@ -11523,13 +11905,13 @@
       <c r="I216" s="3">
         <v>0</v>
       </c>
-      <c r="J216" s="14" t="s">
+      <c r="J216" s="16" t="s">
         <v>1207</v>
       </c>
-      <c r="K216" s="14" t="s">
+      <c r="K216" s="16" t="s">
         <v>1208</v>
       </c>
-      <c r="L216" s="12" t="s">
+      <c r="L216" s="14" t="s">
         <v>1209</v>
       </c>
       <c r="M216" s="3" t="s">
@@ -11542,14 +11924,14 @@
       <c r="C217" s="1">
         <v>1211</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="D217" s="11" t="s">
         <v>1211</v>
       </c>
-      <c r="E217" s="1">
-        <v>5</v>
-      </c>
-      <c r="F217" s="1">
-        <v>5</v>
+      <c r="E217" s="12">
+        <v>6</v>
+      </c>
+      <c r="F217" s="12">
+        <v>6</v>
       </c>
       <c r="G217" s="8" t="s">
         <v>1212</v>
@@ -11560,13 +11942,13 @@
       <c r="I217" s="1">
         <v>0</v>
       </c>
-      <c r="J217" s="13" t="s">
+      <c r="J217" s="15" t="s">
         <v>1214</v>
       </c>
-      <c r="K217" s="16" t="s">
+      <c r="K217" s="15" t="s">
         <v>1208</v>
       </c>
-      <c r="L217" s="12" t="s">
+      <c r="L217" s="14" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -11576,14 +11958,14 @@
       <c r="C218" s="1">
         <v>1212</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="D218" s="11" t="s">
         <v>1216</v>
       </c>
-      <c r="E218" s="1">
-        <v>5</v>
-      </c>
-      <c r="F218" s="1">
-        <v>5</v>
+      <c r="E218" s="12">
+        <v>6</v>
+      </c>
+      <c r="F218" s="12">
+        <v>6</v>
       </c>
       <c r="G218" s="8" t="s">
         <v>1217</v>
@@ -11594,13 +11976,13 @@
       <c r="I218" s="1">
         <v>0</v>
       </c>
-      <c r="J218" s="13" t="s">
+      <c r="J218" s="15" t="s">
         <v>1219</v>
       </c>
-      <c r="K218" s="16" t="s">
+      <c r="K218" s="15" t="s">
         <v>1208</v>
       </c>
-      <c r="L218" s="12" t="s">
+      <c r="L218" s="14" t="s">
         <v>1220</v>
       </c>
     </row>
@@ -11610,14 +11992,14 @@
       <c r="C219" s="1">
         <v>1213</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="D219" s="11" t="s">
         <v>1221</v>
       </c>
-      <c r="E219" s="1">
-        <v>5</v>
-      </c>
-      <c r="F219" s="1">
-        <v>5</v>
+      <c r="E219" s="12">
+        <v>6</v>
+      </c>
+      <c r="F219" s="12">
+        <v>6</v>
       </c>
       <c r="G219" s="8" t="s">
         <v>1222</v>
@@ -11628,13 +12010,13 @@
       <c r="I219" s="1">
         <v>0</v>
       </c>
-      <c r="J219" s="13" t="s">
+      <c r="J219" s="15" t="s">
         <v>1224</v>
       </c>
-      <c r="K219" s="16" t="s">
+      <c r="K219" s="15" t="s">
         <v>1208</v>
       </c>
-      <c r="L219" s="12" t="s">
+      <c r="L219" s="14" t="s">
         <v>1225</v>
       </c>
     </row>
@@ -11644,14 +12026,14 @@
       <c r="C220" s="1">
         <v>1214</v>
       </c>
-      <c r="D220" s="1" t="s">
+      <c r="D220" s="11" t="s">
         <v>1226</v>
       </c>
-      <c r="E220" s="1">
-        <v>5</v>
-      </c>
-      <c r="F220" s="1">
-        <v>5</v>
+      <c r="E220" s="12">
+        <v>6</v>
+      </c>
+      <c r="F220" s="12">
+        <v>6</v>
       </c>
       <c r="G220" s="8" t="s">
         <v>1227</v>
@@ -11662,29 +12044,1137 @@
       <c r="I220" s="1">
         <v>0</v>
       </c>
-      <c r="J220" s="13" t="s">
+      <c r="J220" s="15" t="s">
         <v>1229</v>
       </c>
-      <c r="K220" s="16" t="s">
+      <c r="K220" s="15" t="s">
         <v>1208</v>
       </c>
-      <c r="L220" s="12" t="s">
+      <c r="L220" s="14" t="s">
         <v>1230</v>
       </c>
     </row>
     <row r="221" customHeight="1" spans="1:13">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
+      <c r="C221" s="1">
+        <v>1215</v>
+      </c>
+      <c r="D221" s="11" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E221" s="12">
+        <v>6</v>
+      </c>
+      <c r="F221" s="12">
+        <v>6</v>
+      </c>
+      <c r="G221" s="10" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="I221" s="3">
+        <v>0</v>
+      </c>
+      <c r="J221" s="15" t="s">
+        <v>1234</v>
+      </c>
+      <c r="K221" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L221" s="14" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="222" customHeight="1" spans="1:13">
+      <c r="C222" s="1">
+        <v>1216</v>
+      </c>
+      <c r="D222" s="11" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E222" s="12">
+        <v>6</v>
+      </c>
+      <c r="F222" s="12">
+        <v>6</v>
+      </c>
+      <c r="G222" s="13" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H222" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I222" s="1">
+        <v>0</v>
+      </c>
+      <c r="J222" s="15" t="s">
+        <v>1234</v>
+      </c>
+      <c r="K222" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L222" s="14" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="223" customHeight="1" spans="1:13">
+      <c r="C223" s="1">
+        <v>1217</v>
+      </c>
+      <c r="D223" s="11" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E223" s="12">
+        <v>6</v>
+      </c>
+      <c r="F223" s="12">
+        <v>6</v>
+      </c>
+      <c r="G223" s="13" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H223" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="I223" s="1">
+        <v>0</v>
+      </c>
+      <c r="J223" s="15" t="s">
+        <v>1234</v>
+      </c>
+      <c r="K223" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L223" s="14" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="224" customHeight="1" spans="1:13">
+      <c r="C224" s="1">
+        <v>1218</v>
+      </c>
+      <c r="D224" s="11" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E224" s="12">
+        <v>6</v>
+      </c>
+      <c r="F224" s="12">
+        <v>6</v>
+      </c>
+      <c r="G224" s="13" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H224" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="I224" s="1">
+        <v>0</v>
+      </c>
+      <c r="J224" s="15" t="s">
+        <v>1234</v>
+      </c>
+      <c r="K224" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L224" s="14" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="225" customHeight="1" spans="1:12">
+      <c r="C225" s="1">
+        <v>1219</v>
+      </c>
+      <c r="D225" s="11" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E225" s="12">
+        <v>6</v>
+      </c>
+      <c r="F225" s="12">
+        <v>6</v>
+      </c>
+      <c r="G225" s="13" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H225" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="I225" s="1">
+        <v>0</v>
+      </c>
+      <c r="J225" s="15" t="s">
+        <v>1234</v>
+      </c>
+      <c r="K225" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L225" s="14" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="226" customHeight="1" spans="1:12">
+      <c r="A226" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C226" s="1">
+        <v>1220</v>
+      </c>
+      <c r="D226" s="11" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E226" s="12">
+        <v>6</v>
+      </c>
+      <c r="F226" s="12">
+        <v>6</v>
+      </c>
+      <c r="G226" s="13" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H226" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="I226" s="3">
+        <v>0</v>
+      </c>
+      <c r="J226" s="15" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K226" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L226" s="14" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="227" customHeight="1" spans="1:12">
+      <c r="A227" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C227" s="1">
+        <v>1221</v>
+      </c>
+      <c r="D227" s="11" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E227" s="12">
+        <v>6</v>
+      </c>
+      <c r="F227" s="12">
+        <v>6</v>
+      </c>
+      <c r="G227" s="13" t="s">
+        <v>1259</v>
+      </c>
+      <c r="H227" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="I227" s="1">
+        <v>0</v>
+      </c>
+      <c r="J227" s="15" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K227" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L227" s="14" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="228" customHeight="1" spans="1:12">
+      <c r="A228" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C228" s="1">
+        <v>1222</v>
+      </c>
+      <c r="D228" s="11" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E228" s="12">
+        <v>6</v>
+      </c>
+      <c r="F228" s="12">
+        <v>6</v>
+      </c>
+      <c r="G228" s="13" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H228" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I228" s="1">
+        <v>0</v>
+      </c>
+      <c r="J228" s="15" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K228" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L228" s="14" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="229" customHeight="1" spans="1:12">
+      <c r="A229" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C229" s="1">
+        <v>1223</v>
+      </c>
+      <c r="D229" s="11" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E229" s="12">
+        <v>6</v>
+      </c>
+      <c r="F229" s="12">
+        <v>6</v>
+      </c>
+      <c r="G229" s="13" t="s">
+        <v>1267</v>
+      </c>
+      <c r="H229" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I229" s="1">
+        <v>0</v>
+      </c>
+      <c r="J229" s="15" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K229" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L229" s="14" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="230" customHeight="1" spans="1:12">
+      <c r="A230" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C230" s="1">
+        <v>1224</v>
+      </c>
+      <c r="D230" s="11" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E230" s="12">
+        <v>6</v>
+      </c>
+      <c r="F230" s="12">
+        <v>6</v>
+      </c>
+      <c r="G230" s="13" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H230" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="I230" s="1">
+        <v>0</v>
+      </c>
+      <c r="J230" s="15" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K230" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L230" s="14" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="231" customHeight="1" spans="1:12">
+      <c r="A231" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C231" s="1">
+        <v>1225</v>
+      </c>
+      <c r="D231" s="12" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E231" s="12">
+        <v>6</v>
+      </c>
+      <c r="F231" s="12">
+        <v>6</v>
+      </c>
+      <c r="G231" s="13" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H231" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I231" s="3">
+        <v>0</v>
+      </c>
+      <c r="J231" s="15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="K231" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L231" s="14" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="232" customHeight="1" spans="1:12">
+      <c r="A232" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C232" s="1">
+        <v>1226</v>
+      </c>
+      <c r="D232" s="11" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E232" s="12">
+        <v>6</v>
+      </c>
+      <c r="F232" s="12">
+        <v>6</v>
+      </c>
+      <c r="G232" s="13" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H232" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="I232" s="1">
+        <v>0</v>
+      </c>
+      <c r="J232" s="15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="K232" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L232" s="14" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="233" customHeight="1" spans="1:12">
+      <c r="A233" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C233" s="1">
+        <v>1227</v>
+      </c>
+      <c r="D233" s="11" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E233" s="12">
+        <v>6</v>
+      </c>
+      <c r="F233" s="12">
+        <v>6</v>
+      </c>
+      <c r="G233" s="13" t="s">
+        <v>1284</v>
+      </c>
+      <c r="H233" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="I233" s="1">
+        <v>0</v>
+      </c>
+      <c r="J233" s="15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="K233" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L233" s="14" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" spans="1:12">
+      <c r="A234" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C234" s="1">
+        <v>1228</v>
+      </c>
+      <c r="D234" s="11" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E234" s="12">
+        <v>6</v>
+      </c>
+      <c r="F234" s="12">
+        <v>6</v>
+      </c>
+      <c r="G234" s="13" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H234" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="I234" s="1">
+        <v>0</v>
+      </c>
+      <c r="J234" s="15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="K234" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L234" s="14" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" spans="1:12">
+      <c r="A235" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C235" s="1">
+        <v>1229</v>
+      </c>
+      <c r="D235" s="11" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E235" s="12">
+        <v>6</v>
+      </c>
+      <c r="F235" s="12">
+        <v>6</v>
+      </c>
+      <c r="G235" s="13" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="I235" s="1">
+        <v>0</v>
+      </c>
+      <c r="J235" s="15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="K235" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L235" s="14" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" spans="1:12">
+      <c r="A236" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C236" s="1">
+        <v>1230</v>
+      </c>
+      <c r="D236" s="11" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E236" s="12">
+        <v>6</v>
+      </c>
+      <c r="F236" s="12">
+        <v>6</v>
+      </c>
+      <c r="G236" s="13" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="I236" s="3">
+        <v>0</v>
+      </c>
+      <c r="J236" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="K236" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L236" s="14" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="237" customHeight="1" spans="1:12">
+      <c r="A237" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C237" s="1">
+        <v>1231</v>
+      </c>
+      <c r="D237" s="11" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E237" s="12">
+        <v>6</v>
+      </c>
+      <c r="F237" s="12">
+        <v>6</v>
+      </c>
+      <c r="G237" s="13" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I237" s="1">
+        <v>0</v>
+      </c>
+      <c r="J237" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="K237" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L237" s="14" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" spans="1:12">
+      <c r="A238" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C238" s="1">
+        <v>1232</v>
+      </c>
+      <c r="D238" s="11" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E238" s="12">
+        <v>6</v>
+      </c>
+      <c r="F238" s="12">
+        <v>6</v>
+      </c>
+      <c r="G238" s="13" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="I238" s="1">
+        <v>0</v>
+      </c>
+      <c r="J238" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="K238" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L238" s="14" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" spans="1:12">
+      <c r="A239" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C239" s="1">
+        <v>1233</v>
+      </c>
+      <c r="D239" s="11" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E239" s="12">
+        <v>6</v>
+      </c>
+      <c r="F239" s="12">
+        <v>6</v>
+      </c>
+      <c r="G239" s="13" t="s">
+        <v>1309</v>
+      </c>
+      <c r="H239" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I239" s="1">
+        <v>0</v>
+      </c>
+      <c r="J239" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="K239" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L239" s="14" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" spans="1:12">
+      <c r="A240" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C240" s="1">
+        <v>1234</v>
+      </c>
+      <c r="D240" s="11" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E240" s="12">
+        <v>6</v>
+      </c>
+      <c r="F240" s="12">
+        <v>6</v>
+      </c>
+      <c r="G240" s="13" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="I240" s="1">
+        <v>0</v>
+      </c>
+      <c r="J240" s="15" t="s">
+        <v>1298</v>
+      </c>
+      <c r="K240" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L240" s="14" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" spans="1:12">
+      <c r="A241" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C241" s="1">
+        <v>1235</v>
+      </c>
+      <c r="D241" s="11" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E241" s="12">
+        <v>6</v>
+      </c>
+      <c r="F241" s="12">
+        <v>6</v>
+      </c>
+      <c r="G241" s="13" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H241" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="I241" s="3">
+        <v>0</v>
+      </c>
+      <c r="J241" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="K241" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L241" s="14" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="242" customHeight="1" spans="1:12">
+      <c r="A242" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C242" s="1">
+        <v>1236</v>
+      </c>
+      <c r="D242" s="11" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E242" s="12">
+        <v>6</v>
+      </c>
+      <c r="F242" s="12">
+        <v>6</v>
+      </c>
+      <c r="G242" s="13" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I242" s="1">
+        <v>0</v>
+      </c>
+      <c r="J242" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="K242" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L242" s="14" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="243" customHeight="1" spans="1:12">
+      <c r="A243" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C243" s="1">
+        <v>1237</v>
+      </c>
+      <c r="D243" s="11" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E243" s="12">
+        <v>6</v>
+      </c>
+      <c r="F243" s="12">
+        <v>6</v>
+      </c>
+      <c r="G243" s="13" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I243" s="1">
+        <v>0</v>
+      </c>
+      <c r="J243" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="K243" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L243" s="14" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" spans="1:12">
+      <c r="A244" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C244" s="1">
+        <v>1238</v>
+      </c>
+      <c r="D244" s="11" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E244" s="12">
+        <v>6</v>
+      </c>
+      <c r="F244" s="12">
+        <v>6</v>
+      </c>
+      <c r="G244" s="13" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="I244" s="1">
+        <v>0</v>
+      </c>
+      <c r="J244" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="K244" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L244" s="14" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" spans="1:12">
+      <c r="A245" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C245" s="1">
+        <v>1239</v>
+      </c>
+      <c r="D245" s="11" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E245" s="12">
+        <v>6</v>
+      </c>
+      <c r="F245" s="12">
+        <v>6</v>
+      </c>
+      <c r="G245" s="13" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="I245" s="1">
+        <v>0</v>
+      </c>
+      <c r="J245" s="15" t="s">
+        <v>1319</v>
+      </c>
+      <c r="K245" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L245" s="14" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" spans="1:12">
+      <c r="A246" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C246" s="1">
+        <v>1240</v>
+      </c>
+      <c r="D246" s="11" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E246" s="12">
+        <v>6</v>
+      </c>
+      <c r="F246" s="12">
+        <v>6</v>
+      </c>
+      <c r="G246" s="13" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H246" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="I246" s="3">
+        <v>0</v>
+      </c>
+      <c r="J246" s="15" t="s">
+        <v>1340</v>
+      </c>
+      <c r="K246" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L246" s="14" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" spans="1:12">
+      <c r="A247" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C247" s="1">
+        <v>1241</v>
+      </c>
+      <c r="D247" s="11" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E247" s="12">
+        <v>6</v>
+      </c>
+      <c r="F247" s="12">
+        <v>6</v>
+      </c>
+      <c r="G247" s="13" t="s">
+        <v>1343</v>
+      </c>
+      <c r="H247" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="I247" s="1">
+        <v>0</v>
+      </c>
+      <c r="J247" s="15" t="s">
+        <v>1340</v>
+      </c>
+      <c r="K247" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L247" s="14" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" spans="1:12">
+      <c r="A248" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C248" s="1">
+        <v>1242</v>
+      </c>
+      <c r="D248" s="11" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E248" s="12">
+        <v>6</v>
+      </c>
+      <c r="F248" s="12">
+        <v>6</v>
+      </c>
+      <c r="G248" s="13" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H248" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I248" s="1">
+        <v>0</v>
+      </c>
+      <c r="J248" s="15" t="s">
+        <v>1340</v>
+      </c>
+      <c r="K248" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L248" s="14" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" spans="1:12">
+      <c r="A249" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C249" s="1">
+        <v>1243</v>
+      </c>
+      <c r="D249" s="11" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E249" s="12">
+        <v>6</v>
+      </c>
+      <c r="F249" s="12">
+        <v>6</v>
+      </c>
+      <c r="G249" s="13" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H249" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="I249" s="1">
+        <v>0</v>
+      </c>
+      <c r="J249" s="15" t="s">
+        <v>1340</v>
+      </c>
+      <c r="K249" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L249" s="14" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="250" customHeight="1" spans="1:12">
+      <c r="A250" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C250" s="1">
+        <v>1244</v>
+      </c>
+      <c r="D250" s="11" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E250" s="12">
+        <v>6</v>
+      </c>
+      <c r="F250" s="12">
+        <v>6</v>
+      </c>
+      <c r="G250" s="13" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H250" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="I250" s="1">
+        <v>0</v>
+      </c>
+      <c r="J250" s="15" t="s">
+        <v>1340</v>
+      </c>
+      <c r="K250" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L250" s="14" t="s">
+        <v>1357</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C216:C220">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="C216:C250">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C215 C221:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  <conditionalFormatting sqref="C3:C215 C251:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C219 C220:C250 C251:C1048576" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4782,7 +4782,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4798,8 +4798,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -6478,10 +6476,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="14" t="s">
+      <c r="J46" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="14" t="s">
+      <c r="K46" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -6507,10 +6505,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="14" t="s">
+      <c r="J47" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="14" t="s">
+      <c r="K47" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -6536,10 +6534,10 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="14" t="s">
+      <c r="J48" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="14" t="s">
+      <c r="K48" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
@@ -6565,10 +6563,10 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="14" t="s">
+      <c r="J49" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="14" t="s">
+      <c r="K49" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
@@ -6594,10 +6592,10 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="14" t="s">
+      <c r="J50" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="14" t="s">
+      <c r="K50" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
@@ -6626,10 +6624,10 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="14" t="s">
+      <c r="J51" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="14" t="s">
+      <c r="K51" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
@@ -6655,10 +6653,10 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="14" t="s">
+      <c r="J52" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="14" t="s">
+      <c r="K52" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -6684,10 +6682,10 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="14" t="s">
+      <c r="J53" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="14" t="s">
+      <c r="K53" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
@@ -6713,10 +6711,10 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="14" t="s">
+      <c r="J54" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="14" t="s">
+      <c r="K54" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
@@ -6742,10 +6740,10 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="14" t="s">
+      <c r="J55" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="14" t="s">
+      <c r="K55" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -6774,10 +6772,10 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="14" t="s">
+      <c r="J56" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="14" t="s">
+      <c r="K56" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
@@ -6806,10 +6804,10 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="14" t="s">
+      <c r="J57" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="14" t="s">
+      <c r="K57" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
@@ -6838,10 +6836,10 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="14" t="s">
+      <c r="J58" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="14" t="s">
+      <c r="K58" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -6870,10 +6868,10 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="14" t="s">
+      <c r="J59" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="14" t="s">
+      <c r="K59" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
@@ -6902,10 +6900,10 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="14" t="s">
+      <c r="J60" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="14" t="s">
+      <c r="K60" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -6935,10 +6933,10 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="15" t="s">
+      <c r="J61" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="15" t="s">
+      <c r="K61" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -6968,10 +6966,10 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="15" t="s">
+      <c r="J62" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="15" t="s">
+      <c r="K62" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -7001,10 +6999,10 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="15" t="s">
+      <c r="J63" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="15" t="s">
+      <c r="K63" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
@@ -7034,10 +7032,10 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="15" t="s">
+      <c r="J64" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="15" t="s">
+      <c r="K64" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
@@ -7067,10 +7065,10 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="15" t="s">
+      <c r="J65" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="15" t="s">
+      <c r="K65" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
@@ -7099,10 +7097,10 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="15" t="s">
+      <c r="J66" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="15" t="s">
+      <c r="K66" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
@@ -7131,10 +7129,10 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="15" t="s">
+      <c r="J67" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="15" t="s">
+      <c r="K67" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
@@ -7163,10 +7161,10 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="15" t="s">
+      <c r="J68" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="15" t="s">
+      <c r="K68" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -7195,10 +7193,10 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="15" t="s">
+      <c r="J69" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="15" t="s">
+      <c r="K69" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
@@ -7227,10 +7225,10 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="15" t="s">
+      <c r="J70" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="15" t="s">
+      <c r="K70" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
@@ -7259,10 +7257,10 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="15" t="s">
+      <c r="J71" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="15" t="s">
+      <c r="K71" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -7291,10 +7289,10 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="15" t="s">
+      <c r="J72" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="15" t="s">
+      <c r="K72" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -7323,10 +7321,10 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="15" t="s">
+      <c r="J73" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="15" t="s">
+      <c r="K73" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -7355,10 +7353,10 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="15" t="s">
+      <c r="J74" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="15" t="s">
+      <c r="K74" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
@@ -7387,10 +7385,10 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="15" t="s">
+      <c r="J75" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="15" t="s">
+      <c r="K75" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
@@ -7419,10 +7417,10 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="15" t="s">
+      <c r="J76" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="15" t="s">
+      <c r="K76" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
@@ -7451,10 +7449,10 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="15" t="s">
+      <c r="J77" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="15" t="s">
+      <c r="K77" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
@@ -7483,10 +7481,10 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="15" t="s">
+      <c r="J78" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="15" t="s">
+      <c r="K78" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
@@ -7515,10 +7513,10 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="15" t="s">
+      <c r="J79" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="15" t="s">
+      <c r="K79" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
@@ -7547,10 +7545,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="15" t="s">
+      <c r="J80" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="15" t="s">
+      <c r="K80" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -7579,10 +7577,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="15" t="s">
+      <c r="J81" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="15" t="s">
+      <c r="K81" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -7611,10 +7609,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="15" t="s">
+      <c r="J82" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="15" t="s">
+      <c r="K82" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -7643,10 +7641,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="15" t="s">
+      <c r="J83" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="15" t="s">
+      <c r="K83" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -7675,10 +7673,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="15" t="s">
+      <c r="J84" s="13" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="15" t="s">
+      <c r="K84" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -7707,10 +7705,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="15" t="s">
+      <c r="J85" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="15" t="s">
+      <c r="K85" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -7739,10 +7737,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="15" t="s">
+      <c r="J86" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="15" t="s">
+      <c r="K86" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -7771,10 +7769,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="15" t="s">
+      <c r="J87" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="15" t="s">
+      <c r="K87" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -7803,10 +7801,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="15" t="s">
+      <c r="J88" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="15" t="s">
+      <c r="K88" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -7835,10 +7833,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="15" t="s">
+      <c r="J89" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="15" t="s">
+      <c r="K89" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -7867,10 +7865,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="15" t="s">
+      <c r="J90" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="15" t="s">
+      <c r="K90" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -7899,10 +7897,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="15" t="s">
+      <c r="J91" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="15" t="s">
+      <c r="K91" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -7931,10 +7929,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="15" t="s">
+      <c r="J92" s="13" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="15" t="s">
+      <c r="K92" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -7963,10 +7961,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="15" t="s">
+      <c r="J93" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="15" t="s">
+      <c r="K93" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -7995,10 +7993,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="15" t="s">
+      <c r="J94" s="13" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="15" t="s">
+      <c r="K94" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -8027,10 +8025,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="15" t="s">
+      <c r="J95" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="15" t="s">
+      <c r="K95" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -8059,10 +8057,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="15" t="s">
+      <c r="J96" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="15" t="s">
+      <c r="K96" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -8091,10 +8089,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="15" t="s">
+      <c r="J97" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="15" t="s">
+      <c r="K97" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -8123,10 +8121,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="15" t="s">
+      <c r="J98" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="15" t="s">
+      <c r="K98" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -8155,10 +8153,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="15" t="s">
+      <c r="J99" s="13" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="15" t="s">
+      <c r="K99" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -8187,10 +8185,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="15" t="s">
+      <c r="J100" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="15" t="s">
+      <c r="K100" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -8219,10 +8217,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="15" t="s">
+      <c r="J101" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="15" t="s">
+      <c r="K101" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -8251,10 +8249,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="15" t="s">
+      <c r="J102" s="13" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="15" t="s">
+      <c r="K102" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -8283,10 +8281,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="15" t="s">
+      <c r="J103" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="15" t="s">
+      <c r="K103" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -8315,10 +8313,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="15" t="s">
+      <c r="J104" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="15" t="s">
+      <c r="K104" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -8347,10 +8345,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="15" t="s">
+      <c r="J105" s="13" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="15" t="s">
+      <c r="K105" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -8379,10 +8377,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="15" t="s">
+      <c r="J106" s="13" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="15" t="s">
+      <c r="K106" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -8411,10 +8409,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="15" t="s">
+      <c r="J107" s="13" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="15" t="s">
+      <c r="K107" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -8443,10 +8441,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="15" t="s">
+      <c r="J108" s="13" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="15" t="s">
+      <c r="K108" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -8475,10 +8473,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="15" t="s">
+      <c r="J109" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="15" t="s">
+      <c r="K109" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -8507,10 +8505,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="15" t="s">
+      <c r="J110" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="15" t="s">
+      <c r="K110" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -8539,10 +8537,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="15" t="s">
+      <c r="J111" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="15" t="s">
+      <c r="K111" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -8571,10 +8569,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="15" t="s">
+      <c r="J112" s="13" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="15" t="s">
+      <c r="K112" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -8603,10 +8601,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="15" t="s">
+      <c r="J113" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="15" t="s">
+      <c r="K113" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -8635,10 +8633,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="15" t="s">
+      <c r="J114" s="13" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="15" t="s">
+      <c r="K114" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -8667,10 +8665,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="15" t="s">
+      <c r="J115" s="13" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="15" t="s">
+      <c r="K115" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -8699,10 +8697,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="15" t="s">
+      <c r="J116" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="15" t="s">
+      <c r="K116" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -8731,10 +8729,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="15" t="s">
+      <c r="J117" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="15" t="s">
+      <c r="K117" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -8763,10 +8761,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="15" t="s">
+      <c r="J118" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="15" t="s">
+      <c r="K118" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -8795,10 +8793,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="15" t="s">
+      <c r="J119" s="13" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="15" t="s">
+      <c r="K119" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -8827,10 +8825,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="15" t="s">
+      <c r="J120" s="13" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="15" t="s">
+      <c r="K120" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -8859,10 +8857,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="15" t="s">
+      <c r="J121" s="13" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="15" t="s">
+      <c r="K121" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -8891,10 +8889,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="15" t="s">
+      <c r="J122" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="15" t="s">
+      <c r="K122" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -8923,10 +8921,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="15" t="s">
+      <c r="J123" s="13" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="15" t="s">
+      <c r="K123" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -8955,10 +8953,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="15" t="s">
+      <c r="J124" s="13" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="15" t="s">
+      <c r="K124" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -8987,10 +8985,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="15" t="s">
+      <c r="J125" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="15" t="s">
+      <c r="K125" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -9019,10 +9017,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="15" t="s">
+      <c r="J126" s="13" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="15" t="s">
+      <c r="K126" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -9051,10 +9049,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="15" t="s">
+      <c r="J127" s="13" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="15" t="s">
+      <c r="K127" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -9083,10 +9081,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="15" t="s">
+      <c r="J128" s="13" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="15" t="s">
+      <c r="K128" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -9115,10 +9113,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="15" t="s">
+      <c r="J129" s="13" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="15" t="s">
+      <c r="K129" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -9147,10 +9145,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="15" t="s">
+      <c r="J130" s="13" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="15" t="s">
+      <c r="K130" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -9179,10 +9177,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="15" t="s">
+      <c r="J131" s="13" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="15" t="s">
+      <c r="K131" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -9211,10 +9209,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="15" t="s">
+      <c r="J132" s="13" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="15" t="s">
+      <c r="K132" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -9243,10 +9241,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="15" t="s">
+      <c r="J133" s="13" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="15" t="s">
+      <c r="K133" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -9275,10 +9273,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="15" t="s">
+      <c r="J134" s="13" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="15" t="s">
+      <c r="K134" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -9307,10 +9305,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="15" t="s">
+      <c r="J135" s="13" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="15" t="s">
+      <c r="K135" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -9339,10 +9337,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="15" t="s">
+      <c r="J136" s="13" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="15" t="s">
+      <c r="K136" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -9371,10 +9369,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="15" t="s">
+      <c r="J137" s="13" t="s">
         <v>782</v>
       </c>
-      <c r="K137" s="15" t="s">
+      <c r="K137" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -9403,10 +9401,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="15" t="s">
+      <c r="J138" s="13" t="s">
         <v>788</v>
       </c>
-      <c r="K138" s="15" t="s">
+      <c r="K138" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -9435,10 +9433,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="15" t="s">
+      <c r="J139" s="13" t="s">
         <v>794</v>
       </c>
-      <c r="K139" s="15" t="s">
+      <c r="K139" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -9467,10 +9465,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="15" t="s">
+      <c r="J140" s="13" t="s">
         <v>800</v>
       </c>
-      <c r="K140" s="15" t="s">
+      <c r="K140" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -9499,10 +9497,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="15" t="s">
+      <c r="J141" s="13" t="s">
         <v>806</v>
       </c>
-      <c r="K141" s="15" t="s">
+      <c r="K141" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -9531,10 +9529,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="15" t="s">
+      <c r="J142" s="13" t="s">
         <v>812</v>
       </c>
-      <c r="K142" s="15" t="s">
+      <c r="K142" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -9563,10 +9561,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="15" t="s">
+      <c r="J143" s="13" t="s">
         <v>818</v>
       </c>
-      <c r="K143" s="15" t="s">
+      <c r="K143" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -9595,10 +9593,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="15" t="s">
+      <c r="J144" s="13" t="s">
         <v>824</v>
       </c>
-      <c r="K144" s="15" t="s">
+      <c r="K144" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -9627,10 +9625,10 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="15" t="s">
+      <c r="J145" s="13" t="s">
         <v>830</v>
       </c>
-      <c r="K145" s="15" t="s">
+      <c r="K145" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
@@ -9659,13 +9657,13 @@
       <c r="I146" s="3">
         <v>0</v>
       </c>
-      <c r="J146" s="16" t="s">
+      <c r="J146" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K146" s="16" t="s">
+      <c r="K146" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L146" s="16" t="s">
+      <c r="L146" s="14" t="s">
         <v>837</v>
       </c>
     </row>
@@ -9691,13 +9689,13 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="15" t="s">
+      <c r="J147" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K147" s="15" t="s">
+      <c r="K147" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L147" s="14" t="s">
+      <c r="L147" s="12" t="s">
         <v>842</v>
       </c>
     </row>
@@ -9723,13 +9721,13 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="15" t="s">
+      <c r="J148" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K148" s="15" t="s">
+      <c r="K148" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L148" s="14" t="s">
+      <c r="L148" s="12" t="s">
         <v>847</v>
       </c>
     </row>
@@ -9755,13 +9753,13 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="15" t="s">
+      <c r="J149" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K149" s="15" t="s">
+      <c r="K149" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L149" s="14" t="s">
+      <c r="L149" s="12" t="s">
         <v>852</v>
       </c>
     </row>
@@ -9787,13 +9785,13 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="15" t="s">
+      <c r="J150" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K150" s="15" t="s">
+      <c r="K150" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L150" s="14" t="s">
+      <c r="L150" s="12" t="s">
         <v>857</v>
       </c>
     </row>
@@ -9819,13 +9817,13 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="15" t="s">
+      <c r="J151" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K151" s="15" t="s">
+      <c r="K151" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L151" s="14" t="s">
+      <c r="L151" s="12" t="s">
         <v>863</v>
       </c>
     </row>
@@ -9851,13 +9849,13 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="15" t="s">
+      <c r="J152" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K152" s="15" t="s">
+      <c r="K152" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L152" s="14" t="s">
+      <c r="L152" s="12" t="s">
         <v>868</v>
       </c>
     </row>
@@ -9883,13 +9881,13 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="15" t="s">
+      <c r="J153" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K153" s="15" t="s">
+      <c r="K153" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L153" s="14" t="s">
+      <c r="L153" s="12" t="s">
         <v>873</v>
       </c>
     </row>
@@ -9915,13 +9913,13 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="15" t="s">
+      <c r="J154" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K154" s="15" t="s">
+      <c r="K154" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L154" s="14" t="s">
+      <c r="L154" s="12" t="s">
         <v>878</v>
       </c>
     </row>
@@ -9947,13 +9945,13 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="15" t="s">
+      <c r="J155" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K155" s="15" t="s">
+      <c r="K155" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L155" s="14" t="s">
+      <c r="L155" s="12" t="s">
         <v>883</v>
       </c>
     </row>
@@ -9979,13 +9977,13 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="15" t="s">
+      <c r="J156" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K156" s="15" t="s">
+      <c r="K156" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L156" s="14" t="s">
+      <c r="L156" s="12" t="s">
         <v>889</v>
       </c>
     </row>
@@ -10011,13 +10009,13 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="15" t="s">
+      <c r="J157" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K157" s="15" t="s">
+      <c r="K157" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L157" s="14" t="s">
+      <c r="L157" s="12" t="s">
         <v>894</v>
       </c>
     </row>
@@ -10043,13 +10041,13 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="15" t="s">
+      <c r="J158" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="15" t="s">
+      <c r="K158" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L158" s="14" t="s">
+      <c r="L158" s="12" t="s">
         <v>899</v>
       </c>
     </row>
@@ -10075,13 +10073,13 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="15" t="s">
+      <c r="J159" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K159" s="15" t="s">
+      <c r="K159" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L159" s="14" t="s">
+      <c r="L159" s="12" t="s">
         <v>904</v>
       </c>
     </row>
@@ -10107,13 +10105,13 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="15" t="s">
+      <c r="J160" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K160" s="15" t="s">
+      <c r="K160" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L160" s="14" t="s">
+      <c r="L160" s="12" t="s">
         <v>909</v>
       </c>
     </row>
@@ -10139,13 +10137,13 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="15" t="s">
+      <c r="J161" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K161" s="15" t="s">
+      <c r="K161" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L161" s="14" t="s">
+      <c r="L161" s="12" t="s">
         <v>915</v>
       </c>
     </row>
@@ -10171,13 +10169,13 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="15" t="s">
+      <c r="J162" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K162" s="15" t="s">
+      <c r="K162" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L162" s="14" t="s">
+      <c r="L162" s="12" t="s">
         <v>920</v>
       </c>
     </row>
@@ -10203,13 +10201,13 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="15" t="s">
+      <c r="J163" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K163" s="15" t="s">
+      <c r="K163" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L163" s="14" t="s">
+      <c r="L163" s="12" t="s">
         <v>925</v>
       </c>
     </row>
@@ -10235,13 +10233,13 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="15" t="s">
+      <c r="J164" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K164" s="15" t="s">
+      <c r="K164" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L164" s="14" t="s">
+      <c r="L164" s="12" t="s">
         <v>930</v>
       </c>
     </row>
@@ -10267,13 +10265,13 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="15" t="s">
+      <c r="J165" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K165" s="15" t="s">
+      <c r="K165" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L165" s="14" t="s">
+      <c r="L165" s="12" t="s">
         <v>935</v>
       </c>
     </row>
@@ -10299,13 +10297,13 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="15" t="s">
+      <c r="J166" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K166" s="15" t="s">
+      <c r="K166" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L166" s="14" t="s">
+      <c r="L166" s="12" t="s">
         <v>941</v>
       </c>
     </row>
@@ -10331,13 +10329,13 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="15" t="s">
+      <c r="J167" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K167" s="15" t="s">
+      <c r="K167" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L167" s="14" t="s">
+      <c r="L167" s="12" t="s">
         <v>946</v>
       </c>
     </row>
@@ -10363,13 +10361,13 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="15" t="s">
+      <c r="J168" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K168" s="15" t="s">
+      <c r="K168" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L168" s="14" t="s">
+      <c r="L168" s="12" t="s">
         <v>951</v>
       </c>
     </row>
@@ -10395,13 +10393,13 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="15" t="s">
+      <c r="J169" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K169" s="15" t="s">
+      <c r="K169" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L169" s="14" t="s">
+      <c r="L169" s="12" t="s">
         <v>956</v>
       </c>
     </row>
@@ -10427,13 +10425,13 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="15" t="s">
+      <c r="J170" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="15" t="s">
+      <c r="K170" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L170" s="14" t="s">
+      <c r="L170" s="12" t="s">
         <v>961</v>
       </c>
     </row>
@@ -10459,13 +10457,13 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="15" t="s">
+      <c r="J171" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K171" s="15" t="s">
+      <c r="K171" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L171" s="14" t="s">
+      <c r="L171" s="12" t="s">
         <v>967</v>
       </c>
     </row>
@@ -10491,13 +10489,13 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="15" t="s">
+      <c r="J172" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K172" s="15" t="s">
+      <c r="K172" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L172" s="14" t="s">
+      <c r="L172" s="12" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10523,13 +10521,13 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="15" t="s">
+      <c r="J173" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K173" s="15" t="s">
+      <c r="K173" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L173" s="14" t="s">
+      <c r="L173" s="12" t="s">
         <v>977</v>
       </c>
     </row>
@@ -10555,13 +10553,13 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="15" t="s">
+      <c r="J174" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K174" s="15" t="s">
+      <c r="K174" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L174" s="14" t="s">
+      <c r="L174" s="12" t="s">
         <v>982</v>
       </c>
     </row>
@@ -10587,13 +10585,13 @@
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="15" t="s">
+      <c r="J175" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K175" s="15" t="s">
+      <c r="K175" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L175" s="14" t="s">
+      <c r="L175" s="12" t="s">
         <v>987</v>
       </c>
     </row>
@@ -10619,13 +10617,13 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="15" t="s">
+      <c r="J176" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K176" s="15" t="s">
+      <c r="K176" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L176" s="14" t="s">
+      <c r="L176" s="12" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10651,13 +10649,13 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="15" t="s">
+      <c r="J177" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K177" s="15" t="s">
+      <c r="K177" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L177" s="14" t="s">
+      <c r="L177" s="12" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10683,13 +10681,13 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="15" t="s">
+      <c r="J178" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K178" s="15" t="s">
+      <c r="K178" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L178" s="14" t="s">
+      <c r="L178" s="12" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -10715,13 +10713,13 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="15" t="s">
+      <c r="J179" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K179" s="15" t="s">
+      <c r="K179" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L179" s="14" t="s">
+      <c r="L179" s="12" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -10747,13 +10745,13 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="15" t="s">
+      <c r="J180" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K180" s="15" t="s">
+      <c r="K180" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L180" s="14" t="s">
+      <c r="L180" s="12" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -10779,13 +10777,13 @@
       <c r="I181" s="3">
         <v>0</v>
       </c>
-      <c r="J181" s="16" t="s">
+      <c r="J181" s="14" t="s">
         <v>1019</v>
       </c>
-      <c r="K181" s="16" t="s">
+      <c r="K181" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L181" s="14" t="s">
+      <c r="L181" s="12" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -10811,13 +10809,13 @@
       <c r="I182" s="1">
         <v>0</v>
       </c>
-      <c r="J182" s="15" t="s">
+      <c r="J182" s="13" t="s">
         <v>1026</v>
       </c>
-      <c r="K182" s="15" t="s">
+      <c r="K182" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L182" s="14" t="s">
+      <c r="L182" s="12" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -10843,13 +10841,13 @@
       <c r="I183" s="1">
         <v>0</v>
       </c>
-      <c r="J183" s="15" t="s">
+      <c r="J183" s="13" t="s">
         <v>1032</v>
       </c>
-      <c r="K183" s="15" t="s">
+      <c r="K183" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L183" s="14" t="s">
+      <c r="L183" s="12" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10875,13 +10873,13 @@
       <c r="I184" s="1">
         <v>0</v>
       </c>
-      <c r="J184" s="15" t="s">
+      <c r="J184" s="13" t="s">
         <v>1038</v>
       </c>
-      <c r="K184" s="15" t="s">
+      <c r="K184" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L184" s="14" t="s">
+      <c r="L184" s="12" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10907,13 +10905,13 @@
       <c r="I185" s="1">
         <v>0</v>
       </c>
-      <c r="J185" s="15" t="s">
+      <c r="J185" s="13" t="s">
         <v>1044</v>
       </c>
-      <c r="K185" s="15" t="s">
+      <c r="K185" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L185" s="14" t="s">
+      <c r="L185" s="12" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -10939,13 +10937,13 @@
       <c r="I186" s="1">
         <v>0</v>
       </c>
-      <c r="J186" s="15" t="s">
+      <c r="J186" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K186" s="15" t="s">
+      <c r="K186" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L186" s="14" t="s">
+      <c r="L186" s="12" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -10971,13 +10969,13 @@
       <c r="I187" s="1">
         <v>0</v>
       </c>
-      <c r="J187" s="15" t="s">
+      <c r="J187" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K187" s="15" t="s">
+      <c r="K187" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L187" s="14" t="s">
+      <c r="L187" s="12" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -11003,13 +11001,13 @@
       <c r="I188" s="1">
         <v>0</v>
       </c>
-      <c r="J188" s="15" t="s">
+      <c r="J188" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K188" s="15" t="s">
+      <c r="K188" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L188" s="14" t="s">
+      <c r="L188" s="12" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -11035,13 +11033,13 @@
       <c r="I189" s="1">
         <v>0</v>
       </c>
-      <c r="J189" s="15" t="s">
+      <c r="J189" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K189" s="15" t="s">
+      <c r="K189" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L189" s="14" t="s">
+      <c r="L189" s="12" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -11067,13 +11065,13 @@
       <c r="I190" s="1">
         <v>0</v>
       </c>
-      <c r="J190" s="15" t="s">
+      <c r="J190" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K190" s="15" t="s">
+      <c r="K190" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L190" s="14" t="s">
+      <c r="L190" s="12" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -11099,13 +11097,13 @@
       <c r="I191" s="1">
         <v>0</v>
       </c>
-      <c r="J191" s="15" t="s">
+      <c r="J191" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K191" s="15" t="s">
+      <c r="K191" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L191" s="14" t="s">
+      <c r="L191" s="12" t="s">
         <v>1077</v>
       </c>
     </row>
@@ -11131,13 +11129,13 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-      <c r="J192" s="15" t="s">
+      <c r="J192" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K192" s="15" t="s">
+      <c r="K192" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L192" s="14" t="s">
+      <c r="L192" s="12" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -11163,13 +11161,13 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-      <c r="J193" s="15" t="s">
+      <c r="J193" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K193" s="15" t="s">
+      <c r="K193" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L193" s="14" t="s">
+      <c r="L193" s="12" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -11195,13 +11193,13 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-      <c r="J194" s="15" t="s">
+      <c r="J194" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K194" s="15" t="s">
+      <c r="K194" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L194" s="14" t="s">
+      <c r="L194" s="12" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -11227,13 +11225,13 @@
       <c r="I195" s="1">
         <v>0</v>
       </c>
-      <c r="J195" s="15" t="s">
+      <c r="J195" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K195" s="15" t="s">
+      <c r="K195" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L195" s="14" t="s">
+      <c r="L195" s="12" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -11259,13 +11257,13 @@
       <c r="I196" s="4">
         <v>0</v>
       </c>
-      <c r="J196" s="17" t="s">
+      <c r="J196" s="15" t="s">
         <v>1102</v>
       </c>
-      <c r="K196" s="17" t="s">
+      <c r="K196" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L196" s="17" t="s">
+      <c r="L196" s="15" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -11291,13 +11289,13 @@
       <c r="I197" s="1">
         <v>0</v>
       </c>
-      <c r="J197" s="15" t="s">
+      <c r="J197" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K197" s="15" t="s">
+      <c r="K197" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L197" s="14" t="s">
+      <c r="L197" s="12" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -11323,13 +11321,13 @@
       <c r="I198" s="1">
         <v>0</v>
       </c>
-      <c r="J198" s="15" t="s">
+      <c r="J198" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K198" s="15" t="s">
+      <c r="K198" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L198" s="14" t="s">
+      <c r="L198" s="12" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -11355,13 +11353,13 @@
       <c r="I199" s="1">
         <v>0</v>
       </c>
-      <c r="J199" s="15" t="s">
+      <c r="J199" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K199" s="15" t="s">
+      <c r="K199" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L199" s="14" t="s">
+      <c r="L199" s="12" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -11387,13 +11385,13 @@
       <c r="I200" s="1">
         <v>0</v>
       </c>
-      <c r="J200" s="15" t="s">
+      <c r="J200" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K200" s="15" t="s">
+      <c r="K200" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L200" s="14" t="s">
+      <c r="L200" s="12" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -11419,13 +11417,13 @@
       <c r="I201" s="1">
         <v>0</v>
       </c>
-      <c r="J201" s="15" t="s">
+      <c r="J201" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K201" s="15" t="s">
+      <c r="K201" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L201" s="14" t="s">
+      <c r="L201" s="12" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -11451,13 +11449,13 @@
       <c r="I202" s="1">
         <v>0</v>
       </c>
-      <c r="J202" s="15" t="s">
+      <c r="J202" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K202" s="15" t="s">
+      <c r="K202" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L202" s="14" t="s">
+      <c r="L202" s="12" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -11483,13 +11481,13 @@
       <c r="I203" s="1">
         <v>0</v>
       </c>
-      <c r="J203" s="15" t="s">
+      <c r="J203" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K203" s="15" t="s">
+      <c r="K203" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L203" s="14" t="s">
+      <c r="L203" s="12" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -11515,13 +11513,13 @@
       <c r="I204" s="1">
         <v>0</v>
       </c>
-      <c r="J204" s="15" t="s">
+      <c r="J204" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K204" s="15" t="s">
+      <c r="K204" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L204" s="14" t="s">
+      <c r="L204" s="12" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -11547,13 +11545,13 @@
       <c r="I205" s="1">
         <v>0</v>
       </c>
-      <c r="J205" s="15" t="s">
+      <c r="J205" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K205" s="15" t="s">
+      <c r="K205" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L205" s="14" t="s">
+      <c r="L205" s="12" t="s">
         <v>1149</v>
       </c>
     </row>
@@ -11579,13 +11577,13 @@
       <c r="I206" s="1">
         <v>0</v>
       </c>
-      <c r="J206" s="15" t="s">
+      <c r="J206" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K206" s="15" t="s">
+      <c r="K206" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L206" s="14" t="s">
+      <c r="L206" s="12" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -11611,13 +11609,13 @@
       <c r="I207" s="1">
         <v>0</v>
       </c>
-      <c r="J207" s="15" t="s">
+      <c r="J207" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K207" s="15" t="s">
+      <c r="K207" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L207" s="14" t="s">
+      <c r="L207" s="12" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -11643,13 +11641,13 @@
       <c r="I208" s="1">
         <v>0</v>
       </c>
-      <c r="J208" s="15" t="s">
+      <c r="J208" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K208" s="15" t="s">
+      <c r="K208" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L208" s="14" t="s">
+      <c r="L208" s="12" t="s">
         <v>1165</v>
       </c>
     </row>
@@ -11675,13 +11673,13 @@
       <c r="I209" s="1">
         <v>0</v>
       </c>
-      <c r="J209" s="15" t="s">
+      <c r="J209" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K209" s="15" t="s">
+      <c r="K209" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L209" s="14" t="s">
+      <c r="L209" s="12" t="s">
         <v>1170</v>
       </c>
     </row>
@@ -11707,13 +11705,13 @@
       <c r="I210" s="1">
         <v>0</v>
       </c>
-      <c r="J210" s="15" t="s">
+      <c r="J210" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K210" s="15" t="s">
+      <c r="K210" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L210" s="14" t="s">
+      <c r="L210" s="12" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -11739,13 +11737,13 @@
       <c r="I211" s="1">
         <v>0</v>
       </c>
-      <c r="J211" s="15" t="s">
+      <c r="J211" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K211" s="15" t="s">
+      <c r="K211" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L211" s="14" t="s">
+      <c r="L211" s="12" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -11771,13 +11769,13 @@
       <c r="I212" s="1">
         <v>0</v>
       </c>
-      <c r="J212" s="15" t="s">
+      <c r="J212" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K212" s="15" t="s">
+      <c r="K212" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L212" s="14" t="s">
+      <c r="L212" s="12" t="s">
         <v>1186</v>
       </c>
     </row>
@@ -11803,13 +11801,13 @@
       <c r="I213" s="1">
         <v>0</v>
       </c>
-      <c r="J213" s="15" t="s">
+      <c r="J213" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K213" s="15" t="s">
+      <c r="K213" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L213" s="14" t="s">
+      <c r="L213" s="12" t="s">
         <v>1191</v>
       </c>
     </row>
@@ -11837,13 +11835,13 @@
       <c r="I214" s="1">
         <v>0</v>
       </c>
-      <c r="J214" s="15" t="s">
+      <c r="J214" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K214" s="15" t="s">
+      <c r="K214" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L214" s="14" t="s">
+      <c r="L214" s="12" t="s">
         <v>1196</v>
       </c>
     </row>
@@ -11871,13 +11869,13 @@
       <c r="I215" s="1">
         <v>0</v>
       </c>
-      <c r="J215" s="15" t="s">
+      <c r="J215" s="13" t="s">
         <v>1201</v>
       </c>
-      <c r="K215" s="15" t="s">
+      <c r="K215" s="13" t="s">
         <v>1202</v>
       </c>
-      <c r="L215" s="14" t="s">
+      <c r="L215" s="12" t="s">
         <v>1203</v>
       </c>
     </row>
@@ -11905,13 +11903,13 @@
       <c r="I216" s="3">
         <v>0</v>
       </c>
-      <c r="J216" s="16" t="s">
+      <c r="J216" s="14" t="s">
         <v>1207</v>
       </c>
-      <c r="K216" s="16" t="s">
+      <c r="K216" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L216" s="14" t="s">
+      <c r="L216" s="12" t="s">
         <v>1209</v>
       </c>
       <c r="M216" s="3" t="s">
@@ -11924,13 +11922,13 @@
       <c r="C217" s="1">
         <v>1211</v>
       </c>
-      <c r="D217" s="11" t="s">
+      <c r="D217" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="E217" s="12">
+      <c r="E217" s="2">
         <v>6</v>
       </c>
-      <c r="F217" s="12">
+      <c r="F217" s="2">
         <v>6</v>
       </c>
       <c r="G217" s="8" t="s">
@@ -11942,13 +11940,13 @@
       <c r="I217" s="1">
         <v>0</v>
       </c>
-      <c r="J217" s="15" t="s">
+      <c r="J217" s="13" t="s">
         <v>1214</v>
       </c>
-      <c r="K217" s="15" t="s">
+      <c r="K217" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L217" s="14" t="s">
+      <c r="L217" s="12" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -11958,13 +11956,13 @@
       <c r="C218" s="1">
         <v>1212</v>
       </c>
-      <c r="D218" s="11" t="s">
+      <c r="D218" s="2" t="s">
         <v>1216</v>
       </c>
-      <c r="E218" s="12">
+      <c r="E218" s="2">
         <v>6</v>
       </c>
-      <c r="F218" s="12">
+      <c r="F218" s="2">
         <v>6</v>
       </c>
       <c r="G218" s="8" t="s">
@@ -11976,13 +11974,13 @@
       <c r="I218" s="1">
         <v>0</v>
       </c>
-      <c r="J218" s="15" t="s">
+      <c r="J218" s="13" t="s">
         <v>1219</v>
       </c>
-      <c r="K218" s="15" t="s">
+      <c r="K218" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L218" s="14" t="s">
+      <c r="L218" s="12" t="s">
         <v>1220</v>
       </c>
     </row>
@@ -11992,13 +11990,13 @@
       <c r="C219" s="1">
         <v>1213</v>
       </c>
-      <c r="D219" s="11" t="s">
+      <c r="D219" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="E219" s="12">
+      <c r="E219" s="2">
         <v>6</v>
       </c>
-      <c r="F219" s="12">
+      <c r="F219" s="2">
         <v>6</v>
       </c>
       <c r="G219" s="8" t="s">
@@ -12010,13 +12008,13 @@
       <c r="I219" s="1">
         <v>0</v>
       </c>
-      <c r="J219" s="15" t="s">
+      <c r="J219" s="13" t="s">
         <v>1224</v>
       </c>
-      <c r="K219" s="15" t="s">
+      <c r="K219" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L219" s="14" t="s">
+      <c r="L219" s="12" t="s">
         <v>1225</v>
       </c>
     </row>
@@ -12026,13 +12024,13 @@
       <c r="C220" s="1">
         <v>1214</v>
       </c>
-      <c r="D220" s="11" t="s">
+      <c r="D220" s="2" t="s">
         <v>1226</v>
       </c>
-      <c r="E220" s="12">
+      <c r="E220" s="2">
         <v>6</v>
       </c>
-      <c r="F220" s="12">
+      <c r="F220" s="2">
         <v>6</v>
       </c>
       <c r="G220" s="8" t="s">
@@ -12044,13 +12042,13 @@
       <c r="I220" s="1">
         <v>0</v>
       </c>
-      <c r="J220" s="15" t="s">
+      <c r="J220" s="13" t="s">
         <v>1229</v>
       </c>
-      <c r="K220" s="15" t="s">
+      <c r="K220" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L220" s="14" t="s">
+      <c r="L220" s="12" t="s">
         <v>1230</v>
       </c>
     </row>
@@ -12060,13 +12058,13 @@
       <c r="C221" s="1">
         <v>1215</v>
       </c>
-      <c r="D221" s="11" t="s">
+      <c r="D221" s="2" t="s">
         <v>1231</v>
       </c>
-      <c r="E221" s="12">
+      <c r="E221" s="2">
         <v>6</v>
       </c>
-      <c r="F221" s="12">
+      <c r="F221" s="2">
         <v>6</v>
       </c>
       <c r="G221" s="10" t="s">
@@ -12078,13 +12076,13 @@
       <c r="I221" s="3">
         <v>0</v>
       </c>
-      <c r="J221" s="15" t="s">
+      <c r="J221" s="13" t="s">
         <v>1234</v>
       </c>
-      <c r="K221" s="16" t="s">
+      <c r="K221" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L221" s="14" t="s">
+      <c r="L221" s="12" t="s">
         <v>1235</v>
       </c>
     </row>
@@ -12092,16 +12090,16 @@
       <c r="C222" s="1">
         <v>1216</v>
       </c>
-      <c r="D222" s="11" t="s">
+      <c r="D222" s="2" t="s">
         <v>1236</v>
       </c>
-      <c r="E222" s="12">
+      <c r="E222" s="2">
         <v>6</v>
       </c>
-      <c r="F222" s="12">
+      <c r="F222" s="2">
         <v>6</v>
       </c>
-      <c r="G222" s="13" t="s">
+      <c r="G222" s="11" t="s">
         <v>1237</v>
       </c>
       <c r="H222" s="1" t="s">
@@ -12110,13 +12108,13 @@
       <c r="I222" s="1">
         <v>0</v>
       </c>
-      <c r="J222" s="15" t="s">
+      <c r="J222" s="13" t="s">
         <v>1234</v>
       </c>
-      <c r="K222" s="15" t="s">
+      <c r="K222" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L222" s="14" t="s">
+      <c r="L222" s="12" t="s">
         <v>1239</v>
       </c>
     </row>
@@ -12124,16 +12122,16 @@
       <c r="C223" s="1">
         <v>1217</v>
       </c>
-      <c r="D223" s="11" t="s">
+      <c r="D223" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="E223" s="12">
+      <c r="E223" s="2">
         <v>6</v>
       </c>
-      <c r="F223" s="12">
+      <c r="F223" s="2">
         <v>6</v>
       </c>
-      <c r="G223" s="13" t="s">
+      <c r="G223" s="11" t="s">
         <v>1241</v>
       </c>
       <c r="H223" s="1" t="s">
@@ -12142,13 +12140,13 @@
       <c r="I223" s="1">
         <v>0</v>
       </c>
-      <c r="J223" s="15" t="s">
+      <c r="J223" s="13" t="s">
         <v>1234</v>
       </c>
-      <c r="K223" s="15" t="s">
+      <c r="K223" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L223" s="14" t="s">
+      <c r="L223" s="12" t="s">
         <v>1243</v>
       </c>
     </row>
@@ -12156,16 +12154,16 @@
       <c r="C224" s="1">
         <v>1218</v>
       </c>
-      <c r="D224" s="11" t="s">
+      <c r="D224" s="2" t="s">
         <v>1244</v>
       </c>
-      <c r="E224" s="12">
+      <c r="E224" s="2">
         <v>6</v>
       </c>
-      <c r="F224" s="12">
+      <c r="F224" s="2">
         <v>6</v>
       </c>
-      <c r="G224" s="13" t="s">
+      <c r="G224" s="11" t="s">
         <v>1245</v>
       </c>
       <c r="H224" s="1" t="s">
@@ -12174,13 +12172,13 @@
       <c r="I224" s="1">
         <v>0</v>
       </c>
-      <c r="J224" s="15" t="s">
+      <c r="J224" s="13" t="s">
         <v>1234</v>
       </c>
-      <c r="K224" s="15" t="s">
+      <c r="K224" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L224" s="14" t="s">
+      <c r="L224" s="12" t="s">
         <v>1247</v>
       </c>
     </row>
@@ -12188,16 +12186,16 @@
       <c r="C225" s="1">
         <v>1219</v>
       </c>
-      <c r="D225" s="11" t="s">
+      <c r="D225" s="2" t="s">
         <v>1248</v>
       </c>
-      <c r="E225" s="12">
+      <c r="E225" s="2">
         <v>6</v>
       </c>
-      <c r="F225" s="12">
+      <c r="F225" s="2">
         <v>6</v>
       </c>
-      <c r="G225" s="13" t="s">
+      <c r="G225" s="11" t="s">
         <v>1249</v>
       </c>
       <c r="H225" s="1" t="s">
@@ -12206,13 +12204,13 @@
       <c r="I225" s="1">
         <v>0</v>
       </c>
-      <c r="J225" s="15" t="s">
+      <c r="J225" s="13" t="s">
         <v>1234</v>
       </c>
-      <c r="K225" s="15" t="s">
+      <c r="K225" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L225" s="14" t="s">
+      <c r="L225" s="12" t="s">
         <v>1251</v>
       </c>
     </row>
@@ -12226,16 +12224,16 @@
       <c r="C226" s="1">
         <v>1220</v>
       </c>
-      <c r="D226" s="11" t="s">
+      <c r="D226" s="2" t="s">
         <v>1253</v>
       </c>
-      <c r="E226" s="12">
+      <c r="E226" s="2">
         <v>6</v>
       </c>
-      <c r="F226" s="12">
+      <c r="F226" s="2">
         <v>6</v>
       </c>
-      <c r="G226" s="13" t="s">
+      <c r="G226" s="11" t="s">
         <v>1254</v>
       </c>
       <c r="H226" s="1" t="s">
@@ -12244,13 +12242,13 @@
       <c r="I226" s="3">
         <v>0</v>
       </c>
-      <c r="J226" s="15" t="s">
+      <c r="J226" s="13" t="s">
         <v>1256</v>
       </c>
-      <c r="K226" s="16" t="s">
+      <c r="K226" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L226" s="14" t="s">
+      <c r="L226" s="12" t="s">
         <v>1257</v>
       </c>
     </row>
@@ -12264,16 +12262,16 @@
       <c r="C227" s="1">
         <v>1221</v>
       </c>
-      <c r="D227" s="11" t="s">
+      <c r="D227" s="2" t="s">
         <v>1258</v>
       </c>
-      <c r="E227" s="12">
+      <c r="E227" s="2">
         <v>6</v>
       </c>
-      <c r="F227" s="12">
+      <c r="F227" s="2">
         <v>6</v>
       </c>
-      <c r="G227" s="13" t="s">
+      <c r="G227" s="11" t="s">
         <v>1259</v>
       </c>
       <c r="H227" s="1" t="s">
@@ -12282,13 +12280,13 @@
       <c r="I227" s="1">
         <v>0</v>
       </c>
-      <c r="J227" s="15" t="s">
+      <c r="J227" s="13" t="s">
         <v>1256</v>
       </c>
-      <c r="K227" s="15" t="s">
+      <c r="K227" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L227" s="14" t="s">
+      <c r="L227" s="12" t="s">
         <v>1261</v>
       </c>
     </row>
@@ -12302,16 +12300,16 @@
       <c r="C228" s="1">
         <v>1222</v>
       </c>
-      <c r="D228" s="11" t="s">
+      <c r="D228" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="E228" s="12">
+      <c r="E228" s="2">
         <v>6</v>
       </c>
-      <c r="F228" s="12">
+      <c r="F228" s="2">
         <v>6</v>
       </c>
-      <c r="G228" s="13" t="s">
+      <c r="G228" s="11" t="s">
         <v>1263</v>
       </c>
       <c r="H228" s="1" t="s">
@@ -12320,13 +12318,13 @@
       <c r="I228" s="1">
         <v>0</v>
       </c>
-      <c r="J228" s="15" t="s">
+      <c r="J228" s="13" t="s">
         <v>1256</v>
       </c>
-      <c r="K228" s="15" t="s">
+      <c r="K228" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L228" s="14" t="s">
+      <c r="L228" s="12" t="s">
         <v>1265</v>
       </c>
     </row>
@@ -12340,16 +12338,16 @@
       <c r="C229" s="1">
         <v>1223</v>
       </c>
-      <c r="D229" s="11" t="s">
+      <c r="D229" s="2" t="s">
         <v>1266</v>
       </c>
-      <c r="E229" s="12">
+      <c r="E229" s="2">
         <v>6</v>
       </c>
-      <c r="F229" s="12">
+      <c r="F229" s="2">
         <v>6</v>
       </c>
-      <c r="G229" s="13" t="s">
+      <c r="G229" s="11" t="s">
         <v>1267</v>
       </c>
       <c r="H229" s="1" t="s">
@@ -12358,13 +12356,13 @@
       <c r="I229" s="1">
         <v>0</v>
       </c>
-      <c r="J229" s="15" t="s">
+      <c r="J229" s="13" t="s">
         <v>1256</v>
       </c>
-      <c r="K229" s="15" t="s">
+      <c r="K229" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L229" s="14" t="s">
+      <c r="L229" s="12" t="s">
         <v>1269</v>
       </c>
     </row>
@@ -12378,16 +12376,16 @@
       <c r="C230" s="1">
         <v>1224</v>
       </c>
-      <c r="D230" s="11" t="s">
+      <c r="D230" s="2" t="s">
         <v>1270</v>
       </c>
-      <c r="E230" s="12">
+      <c r="E230" s="2">
         <v>6</v>
       </c>
-      <c r="F230" s="12">
+      <c r="F230" s="2">
         <v>6</v>
       </c>
-      <c r="G230" s="13" t="s">
+      <c r="G230" s="11" t="s">
         <v>1271</v>
       </c>
       <c r="H230" s="1" t="s">
@@ -12396,13 +12394,13 @@
       <c r="I230" s="1">
         <v>0</v>
       </c>
-      <c r="J230" s="15" t="s">
+      <c r="J230" s="13" t="s">
         <v>1256</v>
       </c>
-      <c r="K230" s="15" t="s">
+      <c r="K230" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L230" s="14" t="s">
+      <c r="L230" s="12" t="s">
         <v>1273</v>
       </c>
     </row>
@@ -12416,16 +12414,16 @@
       <c r="C231" s="1">
         <v>1225</v>
       </c>
-      <c r="D231" s="12" t="s">
+      <c r="D231" s="2" t="s">
         <v>1274</v>
       </c>
-      <c r="E231" s="12">
+      <c r="E231" s="2">
         <v>6</v>
       </c>
-      <c r="F231" s="12">
+      <c r="F231" s="2">
         <v>6</v>
       </c>
-      <c r="G231" s="13" t="s">
+      <c r="G231" s="11" t="s">
         <v>1275</v>
       </c>
       <c r="H231" s="1" t="s">
@@ -12434,13 +12432,13 @@
       <c r="I231" s="3">
         <v>0</v>
       </c>
-      <c r="J231" s="15" t="s">
+      <c r="J231" s="13" t="s">
         <v>1277</v>
       </c>
-      <c r="K231" s="16" t="s">
+      <c r="K231" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L231" s="14" t="s">
+      <c r="L231" s="12" t="s">
         <v>1278</v>
       </c>
     </row>
@@ -12454,16 +12452,16 @@
       <c r="C232" s="1">
         <v>1226</v>
       </c>
-      <c r="D232" s="11" t="s">
+      <c r="D232" s="2" t="s">
         <v>1279</v>
       </c>
-      <c r="E232" s="12">
+      <c r="E232" s="2">
         <v>6</v>
       </c>
-      <c r="F232" s="12">
+      <c r="F232" s="2">
         <v>6</v>
       </c>
-      <c r="G232" s="13" t="s">
+      <c r="G232" s="11" t="s">
         <v>1280</v>
       </c>
       <c r="H232" s="1" t="s">
@@ -12472,13 +12470,13 @@
       <c r="I232" s="1">
         <v>0</v>
       </c>
-      <c r="J232" s="15" t="s">
+      <c r="J232" s="13" t="s">
         <v>1277</v>
       </c>
-      <c r="K232" s="15" t="s">
+      <c r="K232" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L232" s="14" t="s">
+      <c r="L232" s="12" t="s">
         <v>1282</v>
       </c>
     </row>
@@ -12492,16 +12490,16 @@
       <c r="C233" s="1">
         <v>1227</v>
       </c>
-      <c r="D233" s="11" t="s">
+      <c r="D233" s="2" t="s">
         <v>1283</v>
       </c>
-      <c r="E233" s="12">
+      <c r="E233" s="2">
         <v>6</v>
       </c>
-      <c r="F233" s="12">
+      <c r="F233" s="2">
         <v>6</v>
       </c>
-      <c r="G233" s="13" t="s">
+      <c r="G233" s="11" t="s">
         <v>1284</v>
       </c>
       <c r="H233" s="1" t="s">
@@ -12510,13 +12508,13 @@
       <c r="I233" s="1">
         <v>0</v>
       </c>
-      <c r="J233" s="15" t="s">
+      <c r="J233" s="13" t="s">
         <v>1277</v>
       </c>
-      <c r="K233" s="15" t="s">
+      <c r="K233" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L233" s="14" t="s">
+      <c r="L233" s="12" t="s">
         <v>1286</v>
       </c>
     </row>
@@ -12530,16 +12528,16 @@
       <c r="C234" s="1">
         <v>1228</v>
       </c>
-      <c r="D234" s="11" t="s">
+      <c r="D234" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="E234" s="12">
+      <c r="E234" s="2">
         <v>6</v>
       </c>
-      <c r="F234" s="12">
+      <c r="F234" s="2">
         <v>6</v>
       </c>
-      <c r="G234" s="13" t="s">
+      <c r="G234" s="11" t="s">
         <v>1288</v>
       </c>
       <c r="H234" s="1" t="s">
@@ -12548,13 +12546,13 @@
       <c r="I234" s="1">
         <v>0</v>
       </c>
-      <c r="J234" s="15" t="s">
+      <c r="J234" s="13" t="s">
         <v>1277</v>
       </c>
-      <c r="K234" s="15" t="s">
+      <c r="K234" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L234" s="14" t="s">
+      <c r="L234" s="12" t="s">
         <v>1290</v>
       </c>
     </row>
@@ -12568,16 +12566,16 @@
       <c r="C235" s="1">
         <v>1229</v>
       </c>
-      <c r="D235" s="11" t="s">
+      <c r="D235" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="E235" s="12">
+      <c r="E235" s="2">
         <v>6</v>
       </c>
-      <c r="F235" s="12">
+      <c r="F235" s="2">
         <v>6</v>
       </c>
-      <c r="G235" s="13" t="s">
+      <c r="G235" s="11" t="s">
         <v>1292</v>
       </c>
       <c r="H235" s="1" t="s">
@@ -12586,13 +12584,13 @@
       <c r="I235" s="1">
         <v>0</v>
       </c>
-      <c r="J235" s="15" t="s">
+      <c r="J235" s="13" t="s">
         <v>1277</v>
       </c>
-      <c r="K235" s="15" t="s">
+      <c r="K235" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L235" s="14" t="s">
+      <c r="L235" s="12" t="s">
         <v>1294</v>
       </c>
     </row>
@@ -12606,16 +12604,16 @@
       <c r="C236" s="1">
         <v>1230</v>
       </c>
-      <c r="D236" s="11" t="s">
+      <c r="D236" s="2" t="s">
         <v>1295</v>
       </c>
-      <c r="E236" s="12">
+      <c r="E236" s="2">
         <v>6</v>
       </c>
-      <c r="F236" s="12">
+      <c r="F236" s="2">
         <v>6</v>
       </c>
-      <c r="G236" s="13" t="s">
+      <c r="G236" s="11" t="s">
         <v>1296</v>
       </c>
       <c r="H236" s="1" t="s">
@@ -12624,13 +12622,13 @@
       <c r="I236" s="3">
         <v>0</v>
       </c>
-      <c r="J236" s="15" t="s">
+      <c r="J236" s="13" t="s">
         <v>1298</v>
       </c>
-      <c r="K236" s="16" t="s">
+      <c r="K236" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L236" s="14" t="s">
+      <c r="L236" s="12" t="s">
         <v>1299</v>
       </c>
     </row>
@@ -12644,16 +12642,16 @@
       <c r="C237" s="1">
         <v>1231</v>
       </c>
-      <c r="D237" s="11" t="s">
+      <c r="D237" s="2" t="s">
         <v>1300</v>
       </c>
-      <c r="E237" s="12">
+      <c r="E237" s="2">
         <v>6</v>
       </c>
-      <c r="F237" s="12">
+      <c r="F237" s="2">
         <v>6</v>
       </c>
-      <c r="G237" s="13" t="s">
+      <c r="G237" s="11" t="s">
         <v>1301</v>
       </c>
       <c r="H237" s="1" t="s">
@@ -12662,13 +12660,13 @@
       <c r="I237" s="1">
         <v>0</v>
       </c>
-      <c r="J237" s="15" t="s">
+      <c r="J237" s="13" t="s">
         <v>1298</v>
       </c>
-      <c r="K237" s="15" t="s">
+      <c r="K237" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L237" s="14" t="s">
+      <c r="L237" s="12" t="s">
         <v>1303</v>
       </c>
     </row>
@@ -12682,16 +12680,16 @@
       <c r="C238" s="1">
         <v>1232</v>
       </c>
-      <c r="D238" s="11" t="s">
+      <c r="D238" s="2" t="s">
         <v>1304</v>
       </c>
-      <c r="E238" s="12">
+      <c r="E238" s="2">
         <v>6</v>
       </c>
-      <c r="F238" s="12">
+      <c r="F238" s="2">
         <v>6</v>
       </c>
-      <c r="G238" s="13" t="s">
+      <c r="G238" s="11" t="s">
         <v>1305</v>
       </c>
       <c r="H238" s="1" t="s">
@@ -12700,13 +12698,13 @@
       <c r="I238" s="1">
         <v>0</v>
       </c>
-      <c r="J238" s="15" t="s">
+      <c r="J238" s="13" t="s">
         <v>1298</v>
       </c>
-      <c r="K238" s="15" t="s">
+      <c r="K238" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L238" s="14" t="s">
+      <c r="L238" s="12" t="s">
         <v>1307</v>
       </c>
     </row>
@@ -12720,16 +12718,16 @@
       <c r="C239" s="1">
         <v>1233</v>
       </c>
-      <c r="D239" s="11" t="s">
+      <c r="D239" s="2" t="s">
         <v>1308</v>
       </c>
-      <c r="E239" s="12">
+      <c r="E239" s="2">
         <v>6</v>
       </c>
-      <c r="F239" s="12">
+      <c r="F239" s="2">
         <v>6</v>
       </c>
-      <c r="G239" s="13" t="s">
+      <c r="G239" s="11" t="s">
         <v>1309</v>
       </c>
       <c r="H239" s="1" t="s">
@@ -12738,13 +12736,13 @@
       <c r="I239" s="1">
         <v>0</v>
       </c>
-      <c r="J239" s="15" t="s">
+      <c r="J239" s="13" t="s">
         <v>1298</v>
       </c>
-      <c r="K239" s="15" t="s">
+      <c r="K239" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L239" s="14" t="s">
+      <c r="L239" s="12" t="s">
         <v>1311</v>
       </c>
     </row>
@@ -12758,16 +12756,16 @@
       <c r="C240" s="1">
         <v>1234</v>
       </c>
-      <c r="D240" s="11" t="s">
+      <c r="D240" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="E240" s="12">
+      <c r="E240" s="2">
         <v>6</v>
       </c>
-      <c r="F240" s="12">
+      <c r="F240" s="2">
         <v>6</v>
       </c>
-      <c r="G240" s="13" t="s">
+      <c r="G240" s="11" t="s">
         <v>1313</v>
       </c>
       <c r="H240" s="1" t="s">
@@ -12776,13 +12774,13 @@
       <c r="I240" s="1">
         <v>0</v>
       </c>
-      <c r="J240" s="15" t="s">
+      <c r="J240" s="13" t="s">
         <v>1298</v>
       </c>
-      <c r="K240" s="15" t="s">
+      <c r="K240" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L240" s="14" t="s">
+      <c r="L240" s="12" t="s">
         <v>1315</v>
       </c>
     </row>
@@ -12796,16 +12794,16 @@
       <c r="C241" s="1">
         <v>1235</v>
       </c>
-      <c r="D241" s="11" t="s">
+      <c r="D241" s="2" t="s">
         <v>1316</v>
       </c>
-      <c r="E241" s="12">
+      <c r="E241" s="2">
         <v>6</v>
       </c>
-      <c r="F241" s="12">
+      <c r="F241" s="2">
         <v>6</v>
       </c>
-      <c r="G241" s="13" t="s">
+      <c r="G241" s="11" t="s">
         <v>1317</v>
       </c>
       <c r="H241" s="1" t="s">
@@ -12814,13 +12812,13 @@
       <c r="I241" s="3">
         <v>0</v>
       </c>
-      <c r="J241" s="15" t="s">
+      <c r="J241" s="13" t="s">
         <v>1319</v>
       </c>
-      <c r="K241" s="16" t="s">
+      <c r="K241" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L241" s="14" t="s">
+      <c r="L241" s="12" t="s">
         <v>1320</v>
       </c>
     </row>
@@ -12834,16 +12832,16 @@
       <c r="C242" s="1">
         <v>1236</v>
       </c>
-      <c r="D242" s="11" t="s">
+      <c r="D242" s="2" t="s">
         <v>1321</v>
       </c>
-      <c r="E242" s="12">
+      <c r="E242" s="2">
         <v>6</v>
       </c>
-      <c r="F242" s="12">
+      <c r="F242" s="2">
         <v>6</v>
       </c>
-      <c r="G242" s="13" t="s">
+      <c r="G242" s="11" t="s">
         <v>1322</v>
       </c>
       <c r="H242" s="1" t="s">
@@ -12852,13 +12850,13 @@
       <c r="I242" s="1">
         <v>0</v>
       </c>
-      <c r="J242" s="15" t="s">
+      <c r="J242" s="13" t="s">
         <v>1319</v>
       </c>
-      <c r="K242" s="15" t="s">
+      <c r="K242" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L242" s="14" t="s">
+      <c r="L242" s="12" t="s">
         <v>1324</v>
       </c>
     </row>
@@ -12872,16 +12870,16 @@
       <c r="C243" s="1">
         <v>1237</v>
       </c>
-      <c r="D243" s="11" t="s">
+      <c r="D243" s="2" t="s">
         <v>1325</v>
       </c>
-      <c r="E243" s="12">
+      <c r="E243" s="2">
         <v>6</v>
       </c>
-      <c r="F243" s="12">
+      <c r="F243" s="2">
         <v>6</v>
       </c>
-      <c r="G243" s="13" t="s">
+      <c r="G243" s="11" t="s">
         <v>1326</v>
       </c>
       <c r="H243" s="1" t="s">
@@ -12890,13 +12888,13 @@
       <c r="I243" s="1">
         <v>0</v>
       </c>
-      <c r="J243" s="15" t="s">
+      <c r="J243" s="13" t="s">
         <v>1319</v>
       </c>
-      <c r="K243" s="15" t="s">
+      <c r="K243" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L243" s="14" t="s">
+      <c r="L243" s="12" t="s">
         <v>1328</v>
       </c>
     </row>
@@ -12910,16 +12908,16 @@
       <c r="C244" s="1">
         <v>1238</v>
       </c>
-      <c r="D244" s="11" t="s">
+      <c r="D244" s="2" t="s">
         <v>1329</v>
       </c>
-      <c r="E244" s="12">
+      <c r="E244" s="2">
         <v>6</v>
       </c>
-      <c r="F244" s="12">
+      <c r="F244" s="2">
         <v>6</v>
       </c>
-      <c r="G244" s="13" t="s">
+      <c r="G244" s="11" t="s">
         <v>1330</v>
       </c>
       <c r="H244" s="1" t="s">
@@ -12928,13 +12926,13 @@
       <c r="I244" s="1">
         <v>0</v>
       </c>
-      <c r="J244" s="15" t="s">
+      <c r="J244" s="13" t="s">
         <v>1319</v>
       </c>
-      <c r="K244" s="15" t="s">
+      <c r="K244" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L244" s="14" t="s">
+      <c r="L244" s="12" t="s">
         <v>1332</v>
       </c>
     </row>
@@ -12948,16 +12946,16 @@
       <c r="C245" s="1">
         <v>1239</v>
       </c>
-      <c r="D245" s="11" t="s">
+      <c r="D245" s="2" t="s">
         <v>1333</v>
       </c>
-      <c r="E245" s="12">
+      <c r="E245" s="2">
         <v>6</v>
       </c>
-      <c r="F245" s="12">
+      <c r="F245" s="2">
         <v>6</v>
       </c>
-      <c r="G245" s="13" t="s">
+      <c r="G245" s="11" t="s">
         <v>1334</v>
       </c>
       <c r="H245" s="1" t="s">
@@ -12966,13 +12964,13 @@
       <c r="I245" s="1">
         <v>0</v>
       </c>
-      <c r="J245" s="15" t="s">
+      <c r="J245" s="13" t="s">
         <v>1319</v>
       </c>
-      <c r="K245" s="15" t="s">
+      <c r="K245" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L245" s="14" t="s">
+      <c r="L245" s="12" t="s">
         <v>1336</v>
       </c>
     </row>
@@ -12986,16 +12984,16 @@
       <c r="C246" s="1">
         <v>1240</v>
       </c>
-      <c r="D246" s="11" t="s">
+      <c r="D246" s="2" t="s">
         <v>1337</v>
       </c>
-      <c r="E246" s="12">
+      <c r="E246" s="2">
         <v>6</v>
       </c>
-      <c r="F246" s="12">
+      <c r="F246" s="2">
         <v>6</v>
       </c>
-      <c r="G246" s="13" t="s">
+      <c r="G246" s="11" t="s">
         <v>1338</v>
       </c>
       <c r="H246" s="1" t="s">
@@ -13004,13 +13002,13 @@
       <c r="I246" s="3">
         <v>0</v>
       </c>
-      <c r="J246" s="15" t="s">
+      <c r="J246" s="13" t="s">
         <v>1340</v>
       </c>
-      <c r="K246" s="16" t="s">
+      <c r="K246" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L246" s="14" t="s">
+      <c r="L246" s="12" t="s">
         <v>1341</v>
       </c>
     </row>
@@ -13024,16 +13022,16 @@
       <c r="C247" s="1">
         <v>1241</v>
       </c>
-      <c r="D247" s="11" t="s">
+      <c r="D247" s="2" t="s">
         <v>1342</v>
       </c>
-      <c r="E247" s="12">
+      <c r="E247" s="2">
         <v>6</v>
       </c>
-      <c r="F247" s="12">
+      <c r="F247" s="2">
         <v>6</v>
       </c>
-      <c r="G247" s="13" t="s">
+      <c r="G247" s="11" t="s">
         <v>1343</v>
       </c>
       <c r="H247" s="1" t="s">
@@ -13042,13 +13040,13 @@
       <c r="I247" s="1">
         <v>0</v>
       </c>
-      <c r="J247" s="15" t="s">
+      <c r="J247" s="13" t="s">
         <v>1340</v>
       </c>
-      <c r="K247" s="15" t="s">
+      <c r="K247" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L247" s="14" t="s">
+      <c r="L247" s="12" t="s">
         <v>1345</v>
       </c>
     </row>
@@ -13062,16 +13060,16 @@
       <c r="C248" s="1">
         <v>1242</v>
       </c>
-      <c r="D248" s="11" t="s">
+      <c r="D248" s="2" t="s">
         <v>1346</v>
       </c>
-      <c r="E248" s="12">
+      <c r="E248" s="2">
         <v>6</v>
       </c>
-      <c r="F248" s="12">
+      <c r="F248" s="2">
         <v>6</v>
       </c>
-      <c r="G248" s="13" t="s">
+      <c r="G248" s="11" t="s">
         <v>1347</v>
       </c>
       <c r="H248" s="1" t="s">
@@ -13080,13 +13078,13 @@
       <c r="I248" s="1">
         <v>0</v>
       </c>
-      <c r="J248" s="15" t="s">
+      <c r="J248" s="13" t="s">
         <v>1340</v>
       </c>
-      <c r="K248" s="15" t="s">
+      <c r="K248" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L248" s="14" t="s">
+      <c r="L248" s="12" t="s">
         <v>1349</v>
       </c>
     </row>
@@ -13100,16 +13098,16 @@
       <c r="C249" s="1">
         <v>1243</v>
       </c>
-      <c r="D249" s="11" t="s">
+      <c r="D249" s="2" t="s">
         <v>1350</v>
       </c>
-      <c r="E249" s="12">
+      <c r="E249" s="2">
         <v>6</v>
       </c>
-      <c r="F249" s="12">
+      <c r="F249" s="2">
         <v>6</v>
       </c>
-      <c r="G249" s="13" t="s">
+      <c r="G249" s="11" t="s">
         <v>1351</v>
       </c>
       <c r="H249" s="1" t="s">
@@ -13118,13 +13116,13 @@
       <c r="I249" s="1">
         <v>0</v>
       </c>
-      <c r="J249" s="15" t="s">
+      <c r="J249" s="13" t="s">
         <v>1340</v>
       </c>
-      <c r="K249" s="15" t="s">
+      <c r="K249" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L249" s="14" t="s">
+      <c r="L249" s="12" t="s">
         <v>1353</v>
       </c>
     </row>
@@ -13138,16 +13136,16 @@
       <c r="C250" s="1">
         <v>1244</v>
       </c>
-      <c r="D250" s="11" t="s">
+      <c r="D250" s="2" t="s">
         <v>1354</v>
       </c>
-      <c r="E250" s="12">
+      <c r="E250" s="2">
         <v>6</v>
       </c>
-      <c r="F250" s="12">
+      <c r="F250" s="2">
         <v>6</v>
       </c>
-      <c r="G250" s="13" t="s">
+      <c r="G250" s="11" t="s">
         <v>1355</v>
       </c>
       <c r="H250" s="1" t="s">
@@ -13156,13 +13154,13 @@
       <c r="I250" s="1">
         <v>0</v>
       </c>
-      <c r="J250" s="15" t="s">
+      <c r="J250" s="13" t="s">
         <v>1340</v>
       </c>
-      <c r="K250" s="15" t="s">
+      <c r="K250" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L250" s="14" t="s">
+      <c r="L250" s="12" t="s">
         <v>1357</v>
       </c>
     </row>
@@ -13174,7 +13172,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C219 C220:C250 C251:C1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C1048576" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="1358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="1358">
   <si>
     <t>_Id</t>
   </si>
@@ -3817,70 +3817,70 @@
     <t>10219</t>
   </si>
   <si>
+    <t>虚无狼山</t>
+  </si>
+  <si>
+    <t>2250-1</t>
+  </si>
+  <si>
+    <t>虚无狼爪，31升阶石</t>
+  </si>
+  <si>
+    <t>202002,106,504,210086,1009,506,202008,202003,507</t>
+  </si>
+  <si>
+    <t>10220</t>
+  </si>
+  <si>
+    <t>虚无沙洞</t>
+  </si>
+  <si>
+    <t>2250-2</t>
+  </si>
+  <si>
+    <t>虚无虫皮，31升阶石</t>
+  </si>
+  <si>
+    <t>10221</t>
+  </si>
+  <si>
+    <t>虚无鹰崖</t>
+  </si>
+  <si>
+    <t>2250-3</t>
+  </si>
+  <si>
+    <t>虚无鹰羽，31升阶石</t>
+  </si>
+  <si>
+    <t>10222</t>
+  </si>
+  <si>
+    <t>虚无虫谷</t>
+  </si>
+  <si>
+    <t>2250-4</t>
+  </si>
+  <si>
+    <t>虚无虫角，31升阶石</t>
+  </si>
+  <si>
+    <t>10223</t>
+  </si>
+  <si>
+    <t>虚无虫洞</t>
+  </si>
+  <si>
+    <t>2250-5</t>
+  </si>
+  <si>
+    <t>虚无蜈膏，31升阶石</t>
+  </si>
+  <si>
+    <t>10224</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>虚无狼山</t>
-  </si>
-  <si>
-    <t>2250-1</t>
-  </si>
-  <si>
-    <t>虚无狼爪，31升阶石</t>
-  </si>
-  <si>
-    <t>202002,106,504,210086,1009,506,202008,202003,507</t>
-  </si>
-  <si>
-    <t>10220</t>
-  </si>
-  <si>
-    <t>虚无沙洞</t>
-  </si>
-  <si>
-    <t>2250-2</t>
-  </si>
-  <si>
-    <t>虚无虫皮，31升阶石</t>
-  </si>
-  <si>
-    <t>10221</t>
-  </si>
-  <si>
-    <t>虚无鹰崖</t>
-  </si>
-  <si>
-    <t>2250-3</t>
-  </si>
-  <si>
-    <t>虚无鹰羽，31升阶石</t>
-  </si>
-  <si>
-    <t>10222</t>
-  </si>
-  <si>
-    <t>虚无虫谷</t>
-  </si>
-  <si>
-    <t>2250-4</t>
-  </si>
-  <si>
-    <t>虚无虫角，31升阶石</t>
-  </si>
-  <si>
-    <t>10223</t>
-  </si>
-  <si>
-    <t>虚无虫洞</t>
-  </si>
-  <si>
-    <t>2250-5</t>
-  </si>
-  <si>
-    <t>虚无蜈膏，31升阶石</t>
-  </si>
-  <si>
-    <t>10224</t>
   </si>
   <si>
     <t>虚无虫穴</t>
@@ -12215,17 +12215,11 @@
       </c>
     </row>
     <row r="226" customHeight="1" spans="1:12">
-      <c r="A226" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>1252</v>
-      </c>
       <c r="C226" s="1">
         <v>1220</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E226" s="2">
         <v>6</v>
@@ -12234,36 +12228,30 @@
         <v>6</v>
       </c>
       <c r="G226" s="11" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H226" s="1" t="s">
         <v>1254</v>
       </c>
-      <c r="H226" s="1" t="s">
+      <c r="I226" s="3">
+        <v>0</v>
+      </c>
+      <c r="J226" s="13" t="s">
         <v>1255</v>
-      </c>
-      <c r="I226" s="3">
-        <v>0</v>
-      </c>
-      <c r="J226" s="13" t="s">
-        <v>1256</v>
       </c>
       <c r="K226" s="14" t="s">
         <v>1208</v>
       </c>
       <c r="L226" s="12" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="227" customHeight="1" spans="1:12">
-      <c r="A227" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>1252</v>
-      </c>
       <c r="C227" s="1">
         <v>1221</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E227" s="2">
         <v>6</v>
@@ -12272,36 +12260,30 @@
         <v>6</v>
       </c>
       <c r="G227" s="11" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H227" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="H227" s="1" t="s">
-        <v>1260</v>
-      </c>
       <c r="I227" s="1">
         <v>0</v>
       </c>
       <c r="J227" s="13" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="K227" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L227" s="12" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="228" customHeight="1" spans="1:12">
-      <c r="A228" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>1252</v>
-      </c>
       <c r="C228" s="1">
         <v>1222</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="E228" s="2">
         <v>6</v>
@@ -12310,36 +12292,30 @@
         <v>6</v>
       </c>
       <c r="G228" s="11" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H228" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="H228" s="1" t="s">
-        <v>1264</v>
-      </c>
       <c r="I228" s="1">
         <v>0</v>
       </c>
       <c r="J228" s="13" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="K228" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L228" s="12" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="229" customHeight="1" spans="1:12">
-      <c r="A229" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>1252</v>
-      </c>
       <c r="C229" s="1">
         <v>1223</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="E229" s="2">
         <v>6</v>
@@ -12348,36 +12324,30 @@
         <v>6</v>
       </c>
       <c r="G229" s="11" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H229" s="1" t="s">
         <v>1267</v>
       </c>
-      <c r="H229" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="I229" s="1">
         <v>0</v>
       </c>
       <c r="J229" s="13" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="K229" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L229" s="12" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="230" customHeight="1" spans="1:12">
-      <c r="A230" s="1" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>1252</v>
-      </c>
       <c r="C230" s="1">
         <v>1224</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="E230" s="2">
         <v>6</v>
@@ -12386,30 +12356,30 @@
         <v>6</v>
       </c>
       <c r="G230" s="11" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H230" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="H230" s="1" t="s">
-        <v>1272</v>
-      </c>
       <c r="I230" s="1">
         <v>0</v>
       </c>
       <c r="J230" s="13" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="K230" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L230" s="12" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="231" customHeight="1" spans="1:12">
       <c r="A231" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C231" s="1">
         <v>1225</v>
@@ -12444,10 +12414,10 @@
     </row>
     <row r="232" customHeight="1" spans="1:12">
       <c r="A232" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C232" s="1">
         <v>1226</v>
@@ -12482,10 +12452,10 @@
     </row>
     <row r="233" customHeight="1" spans="1:12">
       <c r="A233" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C233" s="1">
         <v>1227</v>
@@ -12520,10 +12490,10 @@
     </row>
     <row r="234" customHeight="1" spans="1:12">
       <c r="A234" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C234" s="1">
         <v>1228</v>
@@ -12558,10 +12528,10 @@
     </row>
     <row r="235" customHeight="1" spans="1:12">
       <c r="A235" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C235" s="1">
         <v>1229</v>
@@ -12596,10 +12566,10 @@
     </row>
     <row r="236" customHeight="1" spans="1:12">
       <c r="A236" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C236" s="1">
         <v>1230</v>
@@ -12634,10 +12604,10 @@
     </row>
     <row r="237" customHeight="1" spans="1:12">
       <c r="A237" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C237" s="1">
         <v>1231</v>
@@ -12672,10 +12642,10 @@
     </row>
     <row r="238" customHeight="1" spans="1:12">
       <c r="A238" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C238" s="1">
         <v>1232</v>
@@ -12710,10 +12680,10 @@
     </row>
     <row r="239" customHeight="1" spans="1:12">
       <c r="A239" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C239" s="1">
         <v>1233</v>
@@ -12748,10 +12718,10 @@
     </row>
     <row r="240" customHeight="1" spans="1:12">
       <c r="A240" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C240" s="1">
         <v>1234</v>
@@ -12786,10 +12756,10 @@
     </row>
     <row r="241" customHeight="1" spans="1:12">
       <c r="A241" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C241" s="1">
         <v>1235</v>
@@ -12824,10 +12794,10 @@
     </row>
     <row r="242" customHeight="1" spans="1:12">
       <c r="A242" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C242" s="1">
         <v>1236</v>
@@ -12862,10 +12832,10 @@
     </row>
     <row r="243" customHeight="1" spans="1:12">
       <c r="A243" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C243" s="1">
         <v>1237</v>
@@ -12900,10 +12870,10 @@
     </row>
     <row r="244" customHeight="1" spans="1:12">
       <c r="A244" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C244" s="1">
         <v>1238</v>
@@ -12938,10 +12908,10 @@
     </row>
     <row r="245" customHeight="1" spans="1:12">
       <c r="A245" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C245" s="1">
         <v>1239</v>
@@ -12976,10 +12946,10 @@
     </row>
     <row r="246" customHeight="1" spans="1:12">
       <c r="A246" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C246" s="1">
         <v>1240</v>
@@ -13014,10 +12984,10 @@
     </row>
     <row r="247" customHeight="1" spans="1:12">
       <c r="A247" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C247" s="1">
         <v>1241</v>
@@ -13052,10 +13022,10 @@
     </row>
     <row r="248" customHeight="1" spans="1:12">
       <c r="A248" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C248" s="1">
         <v>1242</v>
@@ -13090,10 +13060,10 @@
     </row>
     <row r="249" customHeight="1" spans="1:12">
       <c r="A249" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C249" s="1">
         <v>1243</v>
@@ -13128,10 +13098,10 @@
     </row>
     <row r="250" customHeight="1" spans="1:12">
       <c r="A250" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C250" s="1">
         <v>1244</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="1358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1358">
   <si>
     <t>_Id</t>
   </si>
@@ -3880,70 +3880,70 @@
     <t>10224</t>
   </si>
   <si>
+    <t>虚无虫穴</t>
+  </si>
+  <si>
+    <t>2300-1</t>
+  </si>
+  <si>
+    <t>虚无虫心，32升阶石</t>
+  </si>
+  <si>
+    <t>202002,106,504,210087,1009,506,202008,202003,507</t>
+  </si>
+  <si>
+    <t>10225</t>
+  </si>
+  <si>
+    <t>虚无虫巢</t>
+  </si>
+  <si>
+    <t>2300-2</t>
+  </si>
+  <si>
+    <t>虚无龙皮，32升阶石</t>
+  </si>
+  <si>
+    <t>10226</t>
+  </si>
+  <si>
+    <t>虚无魔猪厅</t>
+  </si>
+  <si>
+    <t>2300-3</t>
+  </si>
+  <si>
+    <t>虚无猪皮，32升阶石</t>
+  </si>
+  <si>
+    <t>10227</t>
+  </si>
+  <si>
+    <t>虚无魔猪殿</t>
+  </si>
+  <si>
+    <t>2300-4</t>
+  </si>
+  <si>
+    <t>虚无猪心，32升阶石</t>
+  </si>
+  <si>
+    <t>10228</t>
+  </si>
+  <si>
+    <t>虚无桃源</t>
+  </si>
+  <si>
+    <t>2300-5</t>
+  </si>
+  <si>
+    <t>虚无蝎皮，32升阶石</t>
+  </si>
+  <si>
+    <t>10229</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>虚无虫穴</t>
-  </si>
-  <si>
-    <t>2300-1</t>
-  </si>
-  <si>
-    <t>虚无虫心，32升阶石</t>
-  </si>
-  <si>
-    <t>202002,106,504,210087,1009,506,202008,202003,507</t>
-  </si>
-  <si>
-    <t>10225</t>
-  </si>
-  <si>
-    <t>虚无虫巢</t>
-  </si>
-  <si>
-    <t>2300-2</t>
-  </si>
-  <si>
-    <t>虚无龙皮，32升阶石</t>
-  </si>
-  <si>
-    <t>10226</t>
-  </si>
-  <si>
-    <t>虚无魔猪厅</t>
-  </si>
-  <si>
-    <t>2300-3</t>
-  </si>
-  <si>
-    <t>虚无猪皮，32升阶石</t>
-  </si>
-  <si>
-    <t>10227</t>
-  </si>
-  <si>
-    <t>虚无魔猪殿</t>
-  </si>
-  <si>
-    <t>2300-4</t>
-  </si>
-  <si>
-    <t>虚无猪心，32升阶石</t>
-  </si>
-  <si>
-    <t>10228</t>
-  </si>
-  <si>
-    <t>虚无桃源</t>
-  </si>
-  <si>
-    <t>2300-5</t>
-  </si>
-  <si>
-    <t>虚无蝎皮，32升阶石</t>
-  </si>
-  <si>
-    <t>10229</t>
   </si>
   <si>
     <t>虚无魔禁地</t>
@@ -12375,17 +12375,11 @@
       </c>
     </row>
     <row r="231" customHeight="1" spans="1:12">
-      <c r="A231" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>1273</v>
-      </c>
       <c r="C231" s="1">
         <v>1225</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="E231" s="2">
         <v>6</v>
@@ -12394,36 +12388,30 @@
         <v>6</v>
       </c>
       <c r="G231" s="11" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H231" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="H231" s="1" t="s">
+      <c r="I231" s="3">
+        <v>0</v>
+      </c>
+      <c r="J231" s="13" t="s">
         <v>1276</v>
-      </c>
-      <c r="I231" s="3">
-        <v>0</v>
-      </c>
-      <c r="J231" s="13" t="s">
-        <v>1277</v>
       </c>
       <c r="K231" s="14" t="s">
         <v>1208</v>
       </c>
       <c r="L231" s="12" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="232" customHeight="1" spans="1:12">
-      <c r="A232" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>1273</v>
-      </c>
       <c r="C232" s="1">
         <v>1226</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E232" s="2">
         <v>6</v>
@@ -12432,36 +12420,30 @@
         <v>6</v>
       </c>
       <c r="G232" s="11" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H232" s="1" t="s">
         <v>1280</v>
       </c>
-      <c r="H232" s="1" t="s">
-        <v>1281</v>
-      </c>
       <c r="I232" s="1">
         <v>0</v>
       </c>
       <c r="J232" s="13" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="K232" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L232" s="12" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="233" customHeight="1" spans="1:12">
-      <c r="A233" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>1273</v>
-      </c>
       <c r="C233" s="1">
         <v>1227</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E233" s="2">
         <v>6</v>
@@ -12470,36 +12452,30 @@
         <v>6</v>
       </c>
       <c r="G233" s="11" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H233" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="H233" s="1" t="s">
-        <v>1285</v>
-      </c>
       <c r="I233" s="1">
         <v>0</v>
       </c>
       <c r="J233" s="13" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="K233" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L233" s="12" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="234" customHeight="1" spans="1:12">
-      <c r="A234" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>1273</v>
-      </c>
       <c r="C234" s="1">
         <v>1228</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E234" s="2">
         <v>6</v>
@@ -12508,36 +12484,30 @@
         <v>6</v>
       </c>
       <c r="G234" s="11" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H234" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="H234" s="1" t="s">
-        <v>1289</v>
-      </c>
       <c r="I234" s="1">
         <v>0</v>
       </c>
       <c r="J234" s="13" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="K234" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L234" s="12" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="235" customHeight="1" spans="1:12">
-      <c r="A235" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>1273</v>
-      </c>
       <c r="C235" s="1">
         <v>1229</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E235" s="2">
         <v>6</v>
@@ -12546,30 +12516,30 @@
         <v>6</v>
       </c>
       <c r="G235" s="11" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H235" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="H235" s="1" t="s">
-        <v>1293</v>
-      </c>
       <c r="I235" s="1">
         <v>0</v>
       </c>
       <c r="J235" s="13" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="K235" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L235" s="12" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="236" customHeight="1" spans="1:12">
       <c r="A236" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C236" s="1">
         <v>1230</v>
@@ -12604,10 +12574,10 @@
     </row>
     <row r="237" customHeight="1" spans="1:12">
       <c r="A237" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C237" s="1">
         <v>1231</v>
@@ -12642,10 +12612,10 @@
     </row>
     <row r="238" customHeight="1" spans="1:12">
       <c r="A238" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C238" s="1">
         <v>1232</v>
@@ -12680,10 +12650,10 @@
     </row>
     <row r="239" customHeight="1" spans="1:12">
       <c r="A239" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C239" s="1">
         <v>1233</v>
@@ -12718,10 +12688,10 @@
     </row>
     <row r="240" customHeight="1" spans="1:12">
       <c r="A240" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C240" s="1">
         <v>1234</v>
@@ -12756,10 +12726,10 @@
     </row>
     <row r="241" customHeight="1" spans="1:12">
       <c r="A241" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C241" s="1">
         <v>1235</v>
@@ -12794,10 +12764,10 @@
     </row>
     <row r="242" customHeight="1" spans="1:12">
       <c r="A242" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C242" s="1">
         <v>1236</v>
@@ -12832,10 +12802,10 @@
     </row>
     <row r="243" customHeight="1" spans="1:12">
       <c r="A243" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C243" s="1">
         <v>1237</v>
@@ -12870,10 +12840,10 @@
     </row>
     <row r="244" customHeight="1" spans="1:12">
       <c r="A244" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C244" s="1">
         <v>1238</v>
@@ -12908,10 +12878,10 @@
     </row>
     <row r="245" customHeight="1" spans="1:12">
       <c r="A245" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C245" s="1">
         <v>1239</v>
@@ -12946,10 +12916,10 @@
     </row>
     <row r="246" customHeight="1" spans="1:12">
       <c r="A246" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C246" s="1">
         <v>1240</v>
@@ -12984,10 +12954,10 @@
     </row>
     <row r="247" customHeight="1" spans="1:12">
       <c r="A247" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C247" s="1">
         <v>1241</v>
@@ -13022,10 +12992,10 @@
     </row>
     <row r="248" customHeight="1" spans="1:12">
       <c r="A248" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C248" s="1">
         <v>1242</v>
@@ -13060,10 +13030,10 @@
     </row>
     <row r="249" customHeight="1" spans="1:12">
       <c r="A249" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C249" s="1">
         <v>1243</v>
@@ -13098,10 +13068,10 @@
     </row>
     <row r="250" customHeight="1" spans="1:12">
       <c r="A250" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1273</v>
+        <v>1294</v>
       </c>
       <c r="C250" s="1">
         <v>1244</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="1358">
   <si>
     <t>_Id</t>
   </si>
@@ -3943,70 +3943,70 @@
     <t>10229</t>
   </si>
   <si>
+    <t>虚无魔禁地</t>
+  </si>
+  <si>
+    <t>2350-1</t>
+  </si>
+  <si>
+    <t>虚无宝甲，33升阶石</t>
+  </si>
+  <si>
+    <t>202002,106,504,210088,1009,506,202008,202003,507</t>
+  </si>
+  <si>
+    <t>10230</t>
+  </si>
+  <si>
+    <t>虚无魔神殿</t>
+  </si>
+  <si>
+    <t>2350-2</t>
+  </si>
+  <si>
+    <t>虚无号角，33升阶石</t>
+  </si>
+  <si>
+    <t>10231</t>
+  </si>
+  <si>
+    <t>虚无邪禁地</t>
+  </si>
+  <si>
+    <t>2350-3</t>
+  </si>
+  <si>
+    <t>虚无雕像，33升阶石</t>
+  </si>
+  <si>
+    <t>10232</t>
+  </si>
+  <si>
+    <t>虚无邪魔殿</t>
+  </si>
+  <si>
+    <t>2350-4</t>
+  </si>
+  <si>
+    <t>虚无神像，33升阶石</t>
+  </si>
+  <si>
+    <t>10233</t>
+  </si>
+  <si>
+    <t>虚无封魔殿</t>
+  </si>
+  <si>
+    <t>2350-5</t>
+  </si>
+  <si>
+    <t>虚无獠牙，33升阶石</t>
+  </si>
+  <si>
+    <t>10234</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>虚无魔禁地</t>
-  </si>
-  <si>
-    <t>2350-1</t>
-  </si>
-  <si>
-    <t>虚无宝甲，33升阶石</t>
-  </si>
-  <si>
-    <t>202002,106,504,210088,1009,506,202008,202003,507</t>
-  </si>
-  <si>
-    <t>10230</t>
-  </si>
-  <si>
-    <t>虚无魔神殿</t>
-  </si>
-  <si>
-    <t>2350-2</t>
-  </si>
-  <si>
-    <t>虚无号角，33升阶石</t>
-  </si>
-  <si>
-    <t>10231</t>
-  </si>
-  <si>
-    <t>虚无邪禁地</t>
-  </si>
-  <si>
-    <t>2350-3</t>
-  </si>
-  <si>
-    <t>虚无雕像，33升阶石</t>
-  </si>
-  <si>
-    <t>10232</t>
-  </si>
-  <si>
-    <t>虚无邪魔殿</t>
-  </si>
-  <si>
-    <t>2350-4</t>
-  </si>
-  <si>
-    <t>虚无神像，33升阶石</t>
-  </si>
-  <si>
-    <t>10233</t>
-  </si>
-  <si>
-    <t>虚无封魔殿</t>
-  </si>
-  <si>
-    <t>2350-5</t>
-  </si>
-  <si>
-    <t>虚无獠牙，33升阶石</t>
-  </si>
-  <si>
-    <t>10234</t>
   </si>
   <si>
     <t>虚无烈焰殿</t>
@@ -12182,7 +12182,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="225" customHeight="1" spans="1:12">
+    <row r="225" customHeight="1" spans="3:12">
       <c r="C225" s="1">
         <v>1219</v>
       </c>
@@ -12214,7 +12214,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="226" customHeight="1" spans="1:12">
+    <row r="226" customHeight="1" spans="3:12">
       <c r="C226" s="1">
         <v>1220</v>
       </c>
@@ -12246,7 +12246,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="227" customHeight="1" spans="1:12">
+    <row r="227" customHeight="1" spans="3:12">
       <c r="C227" s="1">
         <v>1221</v>
       </c>
@@ -12278,7 +12278,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="228" customHeight="1" spans="1:12">
+    <row r="228" customHeight="1" spans="3:12">
       <c r="C228" s="1">
         <v>1222</v>
       </c>
@@ -12310,7 +12310,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="229" customHeight="1" spans="1:12">
+    <row r="229" customHeight="1" spans="3:12">
       <c r="C229" s="1">
         <v>1223</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="230" customHeight="1" spans="1:12">
+    <row r="230" customHeight="1" spans="3:12">
       <c r="C230" s="1">
         <v>1224</v>
       </c>
@@ -12374,7 +12374,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="231" customHeight="1" spans="1:12">
+    <row r="231" customHeight="1" spans="3:12">
       <c r="C231" s="1">
         <v>1225</v>
       </c>
@@ -12406,7 +12406,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="232" customHeight="1" spans="1:12">
+    <row r="232" customHeight="1" spans="3:12">
       <c r="C232" s="1">
         <v>1226</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="233" customHeight="1" spans="1:12">
+    <row r="233" customHeight="1" spans="3:12">
       <c r="C233" s="1">
         <v>1227</v>
       </c>
@@ -12470,7 +12470,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="234" customHeight="1" spans="1:12">
+    <row r="234" customHeight="1" spans="3:12">
       <c r="C234" s="1">
         <v>1228</v>
       </c>
@@ -12502,7 +12502,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="235" customHeight="1" spans="1:12">
+    <row r="235" customHeight="1" spans="3:12">
       <c r="C235" s="1">
         <v>1229</v>
       </c>
@@ -12534,18 +12534,12 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="236" customHeight="1" spans="1:12">
-      <c r="A236" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>1294</v>
-      </c>
+    <row r="236" customHeight="1" spans="3:12">
       <c r="C236" s="1">
         <v>1230</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="E236" s="2">
         <v>6</v>
@@ -12554,36 +12548,30 @@
         <v>6</v>
       </c>
       <c r="G236" s="11" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H236" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="H236" s="1" t="s">
+      <c r="I236" s="3">
+        <v>0</v>
+      </c>
+      <c r="J236" s="13" t="s">
         <v>1297</v>
-      </c>
-      <c r="I236" s="3">
-        <v>0</v>
-      </c>
-      <c r="J236" s="13" t="s">
-        <v>1298</v>
       </c>
       <c r="K236" s="14" t="s">
         <v>1208</v>
       </c>
       <c r="L236" s="12" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="237" customHeight="1" spans="1:12">
-      <c r="A237" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>1294</v>
-      </c>
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="237" customHeight="1" spans="3:12">
       <c r="C237" s="1">
         <v>1231</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="E237" s="2">
         <v>6</v>
@@ -12592,36 +12580,30 @@
         <v>6</v>
       </c>
       <c r="G237" s="11" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H237" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="H237" s="1" t="s">
-        <v>1302</v>
-      </c>
       <c r="I237" s="1">
         <v>0</v>
       </c>
       <c r="J237" s="13" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="K237" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L237" s="12" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="238" customHeight="1" spans="1:12">
-      <c r="A238" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>1294</v>
-      </c>
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" spans="3:12">
       <c r="C238" s="1">
         <v>1232</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="E238" s="2">
         <v>6</v>
@@ -12630,36 +12612,30 @@
         <v>6</v>
       </c>
       <c r="G238" s="11" t="s">
+        <v>1304</v>
+      </c>
+      <c r="H238" s="1" t="s">
         <v>1305</v>
       </c>
-      <c r="H238" s="1" t="s">
-        <v>1306</v>
-      </c>
       <c r="I238" s="1">
         <v>0</v>
       </c>
       <c r="J238" s="13" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="K238" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L238" s="12" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="239" customHeight="1" spans="1:12">
-      <c r="A239" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>1294</v>
-      </c>
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" spans="3:12">
       <c r="C239" s="1">
         <v>1233</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="E239" s="2">
         <v>6</v>
@@ -12668,36 +12644,30 @@
         <v>6</v>
       </c>
       <c r="G239" s="11" t="s">
+        <v>1308</v>
+      </c>
+      <c r="H239" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="H239" s="1" t="s">
-        <v>1310</v>
-      </c>
       <c r="I239" s="1">
         <v>0</v>
       </c>
       <c r="J239" s="13" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="K239" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L239" s="12" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="240" customHeight="1" spans="1:12">
-      <c r="A240" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>1294</v>
-      </c>
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" spans="3:12">
       <c r="C240" s="1">
         <v>1234</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E240" s="2">
         <v>6</v>
@@ -12706,30 +12676,30 @@
         <v>6</v>
       </c>
       <c r="G240" s="11" t="s">
+        <v>1312</v>
+      </c>
+      <c r="H240" s="1" t="s">
         <v>1313</v>
       </c>
-      <c r="H240" s="1" t="s">
-        <v>1314</v>
-      </c>
       <c r="I240" s="1">
         <v>0</v>
       </c>
       <c r="J240" s="13" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="K240" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L240" s="12" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="241" customHeight="1" spans="1:12">
       <c r="A241" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="C241" s="1">
         <v>1235</v>
@@ -12764,10 +12734,10 @@
     </row>
     <row r="242" customHeight="1" spans="1:12">
       <c r="A242" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="C242" s="1">
         <v>1236</v>
@@ -12802,10 +12772,10 @@
     </row>
     <row r="243" customHeight="1" spans="1:12">
       <c r="A243" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="C243" s="1">
         <v>1237</v>
@@ -12840,10 +12810,10 @@
     </row>
     <row r="244" customHeight="1" spans="1:12">
       <c r="A244" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="C244" s="1">
         <v>1238</v>
@@ -12878,10 +12848,10 @@
     </row>
     <row r="245" customHeight="1" spans="1:12">
       <c r="A245" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="C245" s="1">
         <v>1239</v>
@@ -12916,10 +12886,10 @@
     </row>
     <row r="246" customHeight="1" spans="1:12">
       <c r="A246" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="C246" s="1">
         <v>1240</v>
@@ -12954,10 +12924,10 @@
     </row>
     <row r="247" customHeight="1" spans="1:12">
       <c r="A247" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="C247" s="1">
         <v>1241</v>
@@ -12992,10 +12962,10 @@
     </row>
     <row r="248" customHeight="1" spans="1:12">
       <c r="A248" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="C248" s="1">
         <v>1242</v>
@@ -13030,10 +13000,10 @@
     </row>
     <row r="249" customHeight="1" spans="1:12">
       <c r="A249" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="C249" s="1">
         <v>1243</v>
@@ -13068,10 +13038,10 @@
     </row>
     <row r="250" customHeight="1" spans="1:12">
       <c r="A250" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1294</v>
+        <v>1315</v>
       </c>
       <c r="C250" s="1">
         <v>1244</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -59,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="1358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="1358">
   <si>
     <t>_Id</t>
   </si>
@@ -4006,70 +4011,70 @@
     <t>10234</t>
   </si>
   <si>
+    <t>虚无烈焰殿</t>
+  </si>
+  <si>
+    <t>2400-1</t>
+  </si>
+  <si>
+    <t>虚无树心，34升阶石</t>
+  </si>
+  <si>
+    <t>202002,106,504,210089,1009,506,202008,202003,507</t>
+  </si>
+  <si>
+    <t>10235</t>
+  </si>
+  <si>
+    <t>虚无封邪殿</t>
+  </si>
+  <si>
+    <t>2400-2</t>
+  </si>
+  <si>
+    <t>虚无魔心，34升阶石</t>
+  </si>
+  <si>
+    <t>10236</t>
+  </si>
+  <si>
+    <t>虚无尸魔殿</t>
+  </si>
+  <si>
+    <t>2400-3</t>
+  </si>
+  <si>
+    <t>虚无尸心，34升阶石</t>
+  </si>
+  <si>
+    <t>10237</t>
+  </si>
+  <si>
+    <t>虚无骨魔殿</t>
+  </si>
+  <si>
+    <t>2400-4</t>
+  </si>
+  <si>
+    <t>虚无法杖，34升阶石</t>
+  </si>
+  <si>
+    <t>10238</t>
+  </si>
+  <si>
+    <t>虚无魔牛殿</t>
+  </si>
+  <si>
+    <t>2400-5</t>
+  </si>
+  <si>
+    <t>虚无权杖，34升阶石</t>
+  </si>
+  <si>
+    <t>10239</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>虚无烈焰殿</t>
-  </si>
-  <si>
-    <t>2400-1</t>
-  </si>
-  <si>
-    <t>虚无树心，34升阶石</t>
-  </si>
-  <si>
-    <t>202002,106,504,210089,1009,506,202008,202003,507</t>
-  </si>
-  <si>
-    <t>10235</t>
-  </si>
-  <si>
-    <t>虚无封邪殿</t>
-  </si>
-  <si>
-    <t>2400-2</t>
-  </si>
-  <si>
-    <t>虚无魔心，34升阶石</t>
-  </si>
-  <si>
-    <t>10236</t>
-  </si>
-  <si>
-    <t>虚无尸魔殿</t>
-  </si>
-  <si>
-    <t>2400-3</t>
-  </si>
-  <si>
-    <t>虚无尸心，34升阶石</t>
-  </si>
-  <si>
-    <t>10237</t>
-  </si>
-  <si>
-    <t>虚无骨魔殿</t>
-  </si>
-  <si>
-    <t>2400-4</t>
-  </si>
-  <si>
-    <t>虚无法杖，34升阶石</t>
-  </si>
-  <si>
-    <t>10238</t>
-  </si>
-  <si>
-    <t>虚无魔牛殿</t>
-  </si>
-  <si>
-    <t>2400-5</t>
-  </si>
-  <si>
-    <t>虚无权杖，34升阶石</t>
-  </si>
-  <si>
-    <t>10239</t>
   </si>
   <si>
     <t>虚无水龙谷</t>
@@ -12695,17 +12700,11 @@
       </c>
     </row>
     <row r="241" customHeight="1" spans="1:12">
-      <c r="A241" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>1315</v>
-      </c>
       <c r="C241" s="1">
         <v>1235</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E241" s="2">
         <v>6</v>
@@ -12714,36 +12713,30 @@
         <v>6</v>
       </c>
       <c r="G241" s="11" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H241" s="1" t="s">
         <v>1317</v>
       </c>
-      <c r="H241" s="1" t="s">
+      <c r="I241" s="3">
+        <v>0</v>
+      </c>
+      <c r="J241" s="13" t="s">
         <v>1318</v>
-      </c>
-      <c r="I241" s="3">
-        <v>0</v>
-      </c>
-      <c r="J241" s="13" t="s">
-        <v>1319</v>
       </c>
       <c r="K241" s="14" t="s">
         <v>1208</v>
       </c>
       <c r="L241" s="12" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="242" customHeight="1" spans="1:12">
-      <c r="A242" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>1315</v>
-      </c>
       <c r="C242" s="1">
         <v>1236</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E242" s="2">
         <v>6</v>
@@ -12752,36 +12745,30 @@
         <v>6</v>
       </c>
       <c r="G242" s="11" t="s">
+        <v>1321</v>
+      </c>
+      <c r="H242" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="H242" s="1" t="s">
-        <v>1323</v>
-      </c>
       <c r="I242" s="1">
         <v>0</v>
       </c>
       <c r="J242" s="13" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="K242" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L242" s="12" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="243" customHeight="1" spans="1:12">
-      <c r="A243" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>1315</v>
-      </c>
       <c r="C243" s="1">
         <v>1237</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="E243" s="2">
         <v>6</v>
@@ -12790,36 +12777,30 @@
         <v>6</v>
       </c>
       <c r="G243" s="11" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H243" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="H243" s="1" t="s">
-        <v>1327</v>
-      </c>
       <c r="I243" s="1">
         <v>0</v>
       </c>
       <c r="J243" s="13" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="K243" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L243" s="12" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="244" customHeight="1" spans="1:12">
-      <c r="A244" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>1315</v>
-      </c>
       <c r="C244" s="1">
         <v>1238</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="E244" s="2">
         <v>6</v>
@@ -12828,36 +12809,30 @@
         <v>6</v>
       </c>
       <c r="G244" s="11" t="s">
+        <v>1329</v>
+      </c>
+      <c r="H244" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="H244" s="1" t="s">
-        <v>1331</v>
-      </c>
       <c r="I244" s="1">
         <v>0</v>
       </c>
       <c r="J244" s="13" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="K244" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L244" s="12" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="245" customHeight="1" spans="1:12">
-      <c r="A245" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>1315</v>
-      </c>
       <c r="C245" s="1">
         <v>1239</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="E245" s="2">
         <v>6</v>
@@ -12866,30 +12841,30 @@
         <v>6</v>
       </c>
       <c r="G245" s="11" t="s">
+        <v>1333</v>
+      </c>
+      <c r="H245" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="H245" s="1" t="s">
-        <v>1335</v>
-      </c>
       <c r="I245" s="1">
         <v>0</v>
       </c>
       <c r="J245" s="13" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="K245" s="13" t="s">
         <v>1208</v>
       </c>
       <c r="L245" s="12" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="246" customHeight="1" spans="1:12">
       <c r="A246" s="1" t="s">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="C246" s="1">
         <v>1240</v>
@@ -12924,10 +12899,10 @@
     </row>
     <row r="247" customHeight="1" spans="1:12">
       <c r="A247" s="1" t="s">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="C247" s="1">
         <v>1241</v>
@@ -12962,10 +12937,10 @@
     </row>
     <row r="248" customHeight="1" spans="1:12">
       <c r="A248" s="1" t="s">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="C248" s="1">
         <v>1242</v>
@@ -13000,10 +12975,10 @@
     </row>
     <row r="249" customHeight="1" spans="1:12">
       <c r="A249" s="1" t="s">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="C249" s="1">
         <v>1243</v>
@@ -13038,10 +13013,10 @@
     </row>
     <row r="250" customHeight="1" spans="1:12">
       <c r="A250" s="1" t="s">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1315</v>
+        <v>1336</v>
       </c>
       <c r="C250" s="1">
         <v>1244</v>
